--- a/Personal Finance Dashboard/Personal Finance Intelligence Dashboard.xlsx
+++ b/Personal Finance Dashboard/Personal Finance Intelligence Dashboard.xlsx
@@ -37,7 +37,7 @@
     <definedName name="VendorNameList">Dim_Vendor[VendorName]</definedName>
     <definedName name="AccountNameList">Dim_Account[AccountName]</definedName>
     <definedName name="SourceNameList">Dim_Source[SourceName]</definedName>
-    <definedName name="SignConvention">'Bank Import'!$D$11</definedName>
+    <definedName name="SignConvention">'Bank Import'!$D$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1155,8 +1155,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BankImportRaw" displayName="BankImportRaw" ref="A14:K514" headerRowCount="1">
-  <autoFilter ref="A14:K514"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BankImportRaw" displayName="BankImportRaw" ref="A15:K515" headerRowCount="1">
+  <autoFilter ref="A15:K515"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="Description"/>
@@ -1225,9 +1225,9 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Fact_Income" displayName="Fact_Income" ref="A11:M37" headerRowCount="1">
-  <autoFilter ref="A11:M37"/>
-  <tableColumns count="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Fact_Income" displayName="Fact_Income" ref="A11:N37" headerRowCount="1">
+  <autoFilter ref="A11:N37"/>
+  <tableColumns count="14">
     <tableColumn id="1" name="IncomeID"/>
     <tableColumn id="2" name="Date"/>
     <tableColumn id="3" name="SourceName"/>
@@ -1241,15 +1241,16 @@
     <tableColumn id="11" name="NetAmount"/>
     <tableColumn id="12" name="RecurringFlag"/>
     <tableColumn id="13" name="Notes"/>
+    <tableColumn id="14" name="Description"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Fact_Expenses" displayName="Fact_Expenses" ref="A5:O197" headerRowCount="1">
-  <autoFilter ref="A5:O197"/>
-  <tableColumns count="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Fact_Expenses" displayName="Fact_Expenses" ref="A5:P197" headerRowCount="1">
+  <autoFilter ref="A5:P197"/>
+  <tableColumns count="16">
     <tableColumn id="1" name="ExpenseID"/>
     <tableColumn id="2" name="Date"/>
     <tableColumn id="3" name="VendorName"/>
@@ -1264,7 +1265,8 @@
     <tableColumn id="12" name="NeedWantFlag"/>
     <tableColumn id="13" name="RecurringFlag"/>
     <tableColumn id="14" name="Notes"/>
-    <tableColumn id="15" name="CurMonthAmt"/>
+    <tableColumn id="15" name="Description"/>
+    <tableColumn id="16" name="CurMonthAmt"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showRowStripes="1"/>
 </table>
@@ -1335,8 +1337,8 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Dim_Vendor" displayName="Dim_Vendor" ref="A5:E22" headerRowCount="1">
-  <autoFilter ref="A5:E22"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Dim_Vendor" displayName="Dim_Vendor" ref="A5:E23" headerRowCount="1">
+  <autoFilter ref="A5:E23"/>
   <tableColumns count="5">
     <tableColumn id="1" name="VendorID"/>
     <tableColumn id="2" name="VendorName"/>
@@ -31129,7 +31131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K514"/>
+  <dimension ref="A1:K515"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -31206,127 +31208,122 @@
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="31" t="inlineStr">
         <is>
-          <t>4. For each row, pick a Vendor from the dropdown in column D — Category (E) auto-fills from that vendor's default category; override it if needed.</t>
+          <t>4. Column D (Vendor) tries to auto-fill itself from any past import where you picked a vendor for that exact same bank description — if it's blank (new or slightly different wording), pick a Vendor from the dropdown. Category (E) then auto-fills from that vendor's default category; override it if needed.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="31" t="inlineStr">
         <is>
-          <t>5. Column H tells you Expense or Income and column I gives the positive amount to enter. Copy the finished rows (Date, Vendor, Category, Account, Payment Method, AbsAmount, Notes) into the Expenses tab (or Income tab for deposits/paychecks), then delete the pasted rows here so this stays a scratch area for the next import.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
+          <t>5. Column H tells you Expense or Income and column I gives the positive amount to enter. Copy the finished rows — including column B (Description) — into the Expenses tab (or Income tab for deposits/paychecks), matching them to that tab's Description column: this is what lets column D recognize the same transaction next time. Then delete the pasted rows here so this stays a scratch area for the next import.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>Note: the auto-fill in step 4 only recognizes an EXACT repeat of a description string. Recurring bills and subscriptions usually post with identical text every time, so those learn fast. If your bank appends a unique date or reference number to every line, matching won't catch it — you'll just pick the vendor again, same as the first time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>Sign Convention for this import:</t>
         </is>
       </c>
-      <c r="D11" s="34" t="inlineStr">
+      <c r="D12" s="34" t="inlineStr">
         <is>
           <t>Negative = Expense</t>
         </is>
       </c>
-      <c r="E11" s="35" t="inlineStr">
+      <c r="E12" s="35" t="inlineStr">
         <is>
           <t>Most bank/debit exports show purchases as negative numbers (“Negative = Expense”). Most credit-card exports show charges as positive numbers and payments as negative (“Positive = Expense”). Check one real row against your bank statement to confirm.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="26" t="inlineStr">
-        <is>
-          <t>Paste your CSV's Date / Description / Amount into columns A-C, then set Vendor in D for each row</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
-      <c r="E13" s="2" t="n"/>
-      <c r="F13" s="2" t="n"/>
-      <c r="G13" s="2" t="n"/>
-      <c r="H13" s="2" t="n"/>
-      <c r="I13" s="2" t="n"/>
-      <c r="J13" s="2" t="n"/>
-      <c r="K13" s="2" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="36" t="inlineStr">
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="26" t="inlineStr">
+        <is>
+          <t>Paste your CSV's Date / Description / Amount into columns A-C — Vendor (D) auto-fills from past imports when it recognizes the description</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="n"/>
+      <c r="J14" s="2" t="n"/>
+      <c r="K14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="36" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B14" s="36" t="inlineStr">
+      <c r="B15" s="36" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C14" s="36" t="inlineStr">
+      <c r="C15" s="36" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="D14" s="36" t="inlineStr">
+      <c r="D15" s="36" t="inlineStr">
         <is>
           <t>VendorName</t>
         </is>
       </c>
-      <c r="E14" s="36" t="inlineStr">
+      <c r="E15" s="36" t="inlineStr">
         <is>
           <t>CategoryName</t>
         </is>
       </c>
-      <c r="F14" s="36" t="inlineStr">
+      <c r="F15" s="36" t="inlineStr">
         <is>
           <t>AccountName</t>
         </is>
       </c>
-      <c r="G14" s="36" t="inlineStr">
+      <c r="G15" s="36" t="inlineStr">
         <is>
           <t>PaymentMethod</t>
         </is>
       </c>
-      <c r="H14" s="36" t="inlineStr">
+      <c r="H15" s="36" t="inlineStr">
         <is>
           <t>TransactionType</t>
         </is>
       </c>
-      <c r="I14" s="36" t="inlineStr">
+      <c r="I15" s="36" t="inlineStr">
         <is>
           <t>AbsAmount</t>
         </is>
       </c>
-      <c r="J14" s="36" t="inlineStr">
+      <c r="J15" s="36" t="inlineStr">
         <is>
           <t>NeedWantFlag</t>
         </is>
       </c>
-      <c r="K14" s="36" t="inlineStr">
+      <c r="K15" s="36" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="37" t="n"/>
-      <c r="C15" s="27" t="n"/>
-      <c r="E15">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D15,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
-        <v/>
-      </c>
-      <c r="H15">
-        <f>IF($C15="","",IF(SignConvention="Negative = Expense",IF($C15&lt;0,"Expense","Income"),IF($C15&gt;0,"Expense","Income")))</f>
-        <v/>
-      </c>
-      <c r="I15" s="27">
-        <f>IF($C15="","",ABS($C15))</f>
-        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="37" t="n"/>
       <c r="C16" s="27" t="n"/>
+      <c r="D16">
+        <f>IF($B16="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B16,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B16,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E16">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D16,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -31343,6 +31340,10 @@
     <row r="17">
       <c r="A17" s="37" t="n"/>
       <c r="C17" s="27" t="n"/>
+      <c r="D17">
+        <f>IF($B17="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B17,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B17,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E17">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D17,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -31359,6 +31360,10 @@
     <row r="18">
       <c r="A18" s="37" t="n"/>
       <c r="C18" s="27" t="n"/>
+      <c r="D18">
+        <f>IF($B18="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B18,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B18,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E18">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D18,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -31375,6 +31380,10 @@
     <row r="19">
       <c r="A19" s="37" t="n"/>
       <c r="C19" s="27" t="n"/>
+      <c r="D19">
+        <f>IF($B19="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B19,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B19,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E19">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D19,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -31391,6 +31400,10 @@
     <row r="20">
       <c r="A20" s="37" t="n"/>
       <c r="C20" s="27" t="n"/>
+      <c r="D20">
+        <f>IF($B20="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B20,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B20,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E20">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D20,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -31407,6 +31420,10 @@
     <row r="21">
       <c r="A21" s="37" t="n"/>
       <c r="C21" s="27" t="n"/>
+      <c r="D21">
+        <f>IF($B21="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B21,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B21,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E21">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D21,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -31423,6 +31440,10 @@
     <row r="22">
       <c r="A22" s="37" t="n"/>
       <c r="C22" s="27" t="n"/>
+      <c r="D22">
+        <f>IF($B22="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B22,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B22,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E22">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D22,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -31439,6 +31460,10 @@
     <row r="23">
       <c r="A23" s="37" t="n"/>
       <c r="C23" s="27" t="n"/>
+      <c r="D23">
+        <f>IF($B23="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B23,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B23,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E23">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D23,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -31455,6 +31480,10 @@
     <row r="24">
       <c r="A24" s="37" t="n"/>
       <c r="C24" s="27" t="n"/>
+      <c r="D24">
+        <f>IF($B24="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B24,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B24,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E24">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D24,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -31471,6 +31500,10 @@
     <row r="25">
       <c r="A25" s="37" t="n"/>
       <c r="C25" s="27" t="n"/>
+      <c r="D25">
+        <f>IF($B25="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B25,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B25,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E25">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D25,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -31487,6 +31520,10 @@
     <row r="26">
       <c r="A26" s="37" t="n"/>
       <c r="C26" s="27" t="n"/>
+      <c r="D26">
+        <f>IF($B26="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B26,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B26,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E26">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D26,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -31503,6 +31540,10 @@
     <row r="27">
       <c r="A27" s="37" t="n"/>
       <c r="C27" s="27" t="n"/>
+      <c r="D27">
+        <f>IF($B27="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B27,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B27,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E27">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D27,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -31519,6 +31560,10 @@
     <row r="28">
       <c r="A28" s="37" t="n"/>
       <c r="C28" s="27" t="n"/>
+      <c r="D28">
+        <f>IF($B28="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B28,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B28,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E28">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D28,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -31535,6 +31580,10 @@
     <row r="29">
       <c r="A29" s="37" t="n"/>
       <c r="C29" s="27" t="n"/>
+      <c r="D29">
+        <f>IF($B29="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B29,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B29,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E29">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D29,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -31551,6 +31600,10 @@
     <row r="30">
       <c r="A30" s="37" t="n"/>
       <c r="C30" s="27" t="n"/>
+      <c r="D30">
+        <f>IF($B30="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B30,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B30,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E30">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D30,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -31567,6 +31620,10 @@
     <row r="31">
       <c r="A31" s="37" t="n"/>
       <c r="C31" s="27" t="n"/>
+      <c r="D31">
+        <f>IF($B31="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B31,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B31,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E31">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D31,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -31583,6 +31640,10 @@
     <row r="32">
       <c r="A32" s="37" t="n"/>
       <c r="C32" s="27" t="n"/>
+      <c r="D32">
+        <f>IF($B32="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B32,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B32,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E32">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D32,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -31599,6 +31660,10 @@
     <row r="33">
       <c r="A33" s="37" t="n"/>
       <c r="C33" s="27" t="n"/>
+      <c r="D33">
+        <f>IF($B33="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B33,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B33,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E33">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D33,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -31615,6 +31680,10 @@
     <row r="34">
       <c r="A34" s="37" t="n"/>
       <c r="C34" s="27" t="n"/>
+      <c r="D34">
+        <f>IF($B34="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B34,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B34,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E34">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D34,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -31631,6 +31700,10 @@
     <row r="35">
       <c r="A35" s="37" t="n"/>
       <c r="C35" s="27" t="n"/>
+      <c r="D35">
+        <f>IF($B35="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B35,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B35,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E35">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D35,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -31647,6 +31720,10 @@
     <row r="36">
       <c r="A36" s="37" t="n"/>
       <c r="C36" s="27" t="n"/>
+      <c r="D36">
+        <f>IF($B36="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B36,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B36,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E36">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D36,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -31663,6 +31740,10 @@
     <row r="37">
       <c r="A37" s="37" t="n"/>
       <c r="C37" s="27" t="n"/>
+      <c r="D37">
+        <f>IF($B37="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B37,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B37,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E37">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D37,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -31679,6 +31760,10 @@
     <row r="38">
       <c r="A38" s="37" t="n"/>
       <c r="C38" s="27" t="n"/>
+      <c r="D38">
+        <f>IF($B38="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B38,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B38,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E38">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D38,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -31695,6 +31780,10 @@
     <row r="39">
       <c r="A39" s="37" t="n"/>
       <c r="C39" s="27" t="n"/>
+      <c r="D39">
+        <f>IF($B39="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B39,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B39,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E39">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D39,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -31711,6 +31800,10 @@
     <row r="40">
       <c r="A40" s="37" t="n"/>
       <c r="C40" s="27" t="n"/>
+      <c r="D40">
+        <f>IF($B40="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B40,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B40,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E40">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D40,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -31727,6 +31820,10 @@
     <row r="41">
       <c r="A41" s="37" t="n"/>
       <c r="C41" s="27" t="n"/>
+      <c r="D41">
+        <f>IF($B41="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B41,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B41,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E41">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D41,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -31743,6 +31840,10 @@
     <row r="42">
       <c r="A42" s="37" t="n"/>
       <c r="C42" s="27" t="n"/>
+      <c r="D42">
+        <f>IF($B42="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B42,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B42,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E42">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D42,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -31759,6 +31860,10 @@
     <row r="43">
       <c r="A43" s="37" t="n"/>
       <c r="C43" s="27" t="n"/>
+      <c r="D43">
+        <f>IF($B43="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B43,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B43,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E43">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D43,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -31775,6 +31880,10 @@
     <row r="44">
       <c r="A44" s="37" t="n"/>
       <c r="C44" s="27" t="n"/>
+      <c r="D44">
+        <f>IF($B44="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B44,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B44,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E44">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D44,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -31791,6 +31900,10 @@
     <row r="45">
       <c r="A45" s="37" t="n"/>
       <c r="C45" s="27" t="n"/>
+      <c r="D45">
+        <f>IF($B45="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B45,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B45,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E45">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D45,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -31807,6 +31920,10 @@
     <row r="46">
       <c r="A46" s="37" t="n"/>
       <c r="C46" s="27" t="n"/>
+      <c r="D46">
+        <f>IF($B46="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B46,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B46,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E46">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D46,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -31823,6 +31940,10 @@
     <row r="47">
       <c r="A47" s="37" t="n"/>
       <c r="C47" s="27" t="n"/>
+      <c r="D47">
+        <f>IF($B47="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B47,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B47,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E47">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D47,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -31839,6 +31960,10 @@
     <row r="48">
       <c r="A48" s="37" t="n"/>
       <c r="C48" s="27" t="n"/>
+      <c r="D48">
+        <f>IF($B48="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B48,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B48,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E48">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D48,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -31855,6 +31980,10 @@
     <row r="49">
       <c r="A49" s="37" t="n"/>
       <c r="C49" s="27" t="n"/>
+      <c r="D49">
+        <f>IF($B49="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B49,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B49,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E49">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D49,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -31871,6 +32000,10 @@
     <row r="50">
       <c r="A50" s="37" t="n"/>
       <c r="C50" s="27" t="n"/>
+      <c r="D50">
+        <f>IF($B50="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B50,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B50,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E50">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D50,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -31887,6 +32020,10 @@
     <row r="51">
       <c r="A51" s="37" t="n"/>
       <c r="C51" s="27" t="n"/>
+      <c r="D51">
+        <f>IF($B51="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B51,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B51,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E51">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D51,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -31903,6 +32040,10 @@
     <row r="52">
       <c r="A52" s="37" t="n"/>
       <c r="C52" s="27" t="n"/>
+      <c r="D52">
+        <f>IF($B52="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B52,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B52,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E52">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D52,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -31919,6 +32060,10 @@
     <row r="53">
       <c r="A53" s="37" t="n"/>
       <c r="C53" s="27" t="n"/>
+      <c r="D53">
+        <f>IF($B53="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B53,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B53,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E53">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D53,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -31935,6 +32080,10 @@
     <row r="54">
       <c r="A54" s="37" t="n"/>
       <c r="C54" s="27" t="n"/>
+      <c r="D54">
+        <f>IF($B54="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B54,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B54,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E54">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D54,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -31951,6 +32100,10 @@
     <row r="55">
       <c r="A55" s="37" t="n"/>
       <c r="C55" s="27" t="n"/>
+      <c r="D55">
+        <f>IF($B55="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B55,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B55,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E55">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D55,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -31967,6 +32120,10 @@
     <row r="56">
       <c r="A56" s="37" t="n"/>
       <c r="C56" s="27" t="n"/>
+      <c r="D56">
+        <f>IF($B56="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B56,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B56,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E56">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D56,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -31983,6 +32140,10 @@
     <row r="57">
       <c r="A57" s="37" t="n"/>
       <c r="C57" s="27" t="n"/>
+      <c r="D57">
+        <f>IF($B57="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B57,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B57,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E57">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D57,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -31999,6 +32160,10 @@
     <row r="58">
       <c r="A58" s="37" t="n"/>
       <c r="C58" s="27" t="n"/>
+      <c r="D58">
+        <f>IF($B58="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B58,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B58,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E58">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D58,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32015,6 +32180,10 @@
     <row r="59">
       <c r="A59" s="37" t="n"/>
       <c r="C59" s="27" t="n"/>
+      <c r="D59">
+        <f>IF($B59="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B59,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B59,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E59">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D59,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32031,6 +32200,10 @@
     <row r="60">
       <c r="A60" s="37" t="n"/>
       <c r="C60" s="27" t="n"/>
+      <c r="D60">
+        <f>IF($B60="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B60,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B60,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E60">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D60,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32047,6 +32220,10 @@
     <row r="61">
       <c r="A61" s="37" t="n"/>
       <c r="C61" s="27" t="n"/>
+      <c r="D61">
+        <f>IF($B61="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B61,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B61,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E61">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D61,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32063,6 +32240,10 @@
     <row r="62">
       <c r="A62" s="37" t="n"/>
       <c r="C62" s="27" t="n"/>
+      <c r="D62">
+        <f>IF($B62="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B62,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B62,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E62">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D62,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32079,6 +32260,10 @@
     <row r="63">
       <c r="A63" s="37" t="n"/>
       <c r="C63" s="27" t="n"/>
+      <c r="D63">
+        <f>IF($B63="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B63,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B63,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E63">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D63,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32095,6 +32280,10 @@
     <row r="64">
       <c r="A64" s="37" t="n"/>
       <c r="C64" s="27" t="n"/>
+      <c r="D64">
+        <f>IF($B64="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B64,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B64,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E64">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D64,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32111,6 +32300,10 @@
     <row r="65">
       <c r="A65" s="37" t="n"/>
       <c r="C65" s="27" t="n"/>
+      <c r="D65">
+        <f>IF($B65="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B65,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B65,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E65">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D65,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32127,6 +32320,10 @@
     <row r="66">
       <c r="A66" s="37" t="n"/>
       <c r="C66" s="27" t="n"/>
+      <c r="D66">
+        <f>IF($B66="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B66,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B66,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E66">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D66,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32143,6 +32340,10 @@
     <row r="67">
       <c r="A67" s="37" t="n"/>
       <c r="C67" s="27" t="n"/>
+      <c r="D67">
+        <f>IF($B67="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B67,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B67,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E67">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D67,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32159,6 +32360,10 @@
     <row r="68">
       <c r="A68" s="37" t="n"/>
       <c r="C68" s="27" t="n"/>
+      <c r="D68">
+        <f>IF($B68="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B68,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B68,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E68">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D68,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32175,6 +32380,10 @@
     <row r="69">
       <c r="A69" s="37" t="n"/>
       <c r="C69" s="27" t="n"/>
+      <c r="D69">
+        <f>IF($B69="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B69,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B69,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E69">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D69,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32191,6 +32400,10 @@
     <row r="70">
       <c r="A70" s="37" t="n"/>
       <c r="C70" s="27" t="n"/>
+      <c r="D70">
+        <f>IF($B70="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B70,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B70,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E70">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D70,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32207,6 +32420,10 @@
     <row r="71">
       <c r="A71" s="37" t="n"/>
       <c r="C71" s="27" t="n"/>
+      <c r="D71">
+        <f>IF($B71="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B71,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B71,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E71">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D71,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32223,6 +32440,10 @@
     <row r="72">
       <c r="A72" s="37" t="n"/>
       <c r="C72" s="27" t="n"/>
+      <c r="D72">
+        <f>IF($B72="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B72,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B72,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E72">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D72,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32239,6 +32460,10 @@
     <row r="73">
       <c r="A73" s="37" t="n"/>
       <c r="C73" s="27" t="n"/>
+      <c r="D73">
+        <f>IF($B73="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B73,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B73,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E73">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D73,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32255,6 +32480,10 @@
     <row r="74">
       <c r="A74" s="37" t="n"/>
       <c r="C74" s="27" t="n"/>
+      <c r="D74">
+        <f>IF($B74="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B74,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B74,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E74">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D74,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32271,6 +32500,10 @@
     <row r="75">
       <c r="A75" s="37" t="n"/>
       <c r="C75" s="27" t="n"/>
+      <c r="D75">
+        <f>IF($B75="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B75,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B75,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E75">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D75,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32287,6 +32520,10 @@
     <row r="76">
       <c r="A76" s="37" t="n"/>
       <c r="C76" s="27" t="n"/>
+      <c r="D76">
+        <f>IF($B76="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B76,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B76,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E76">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D76,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32303,6 +32540,10 @@
     <row r="77">
       <c r="A77" s="37" t="n"/>
       <c r="C77" s="27" t="n"/>
+      <c r="D77">
+        <f>IF($B77="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B77,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B77,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E77">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D77,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32319,6 +32560,10 @@
     <row r="78">
       <c r="A78" s="37" t="n"/>
       <c r="C78" s="27" t="n"/>
+      <c r="D78">
+        <f>IF($B78="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B78,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B78,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E78">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D78,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32335,6 +32580,10 @@
     <row r="79">
       <c r="A79" s="37" t="n"/>
       <c r="C79" s="27" t="n"/>
+      <c r="D79">
+        <f>IF($B79="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B79,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B79,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E79">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D79,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32351,6 +32600,10 @@
     <row r="80">
       <c r="A80" s="37" t="n"/>
       <c r="C80" s="27" t="n"/>
+      <c r="D80">
+        <f>IF($B80="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B80,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B80,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E80">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D80,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32367,6 +32620,10 @@
     <row r="81">
       <c r="A81" s="37" t="n"/>
       <c r="C81" s="27" t="n"/>
+      <c r="D81">
+        <f>IF($B81="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B81,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B81,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E81">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D81,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32383,6 +32640,10 @@
     <row r="82">
       <c r="A82" s="37" t="n"/>
       <c r="C82" s="27" t="n"/>
+      <c r="D82">
+        <f>IF($B82="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B82,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B82,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E82">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D82,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32399,6 +32660,10 @@
     <row r="83">
       <c r="A83" s="37" t="n"/>
       <c r="C83" s="27" t="n"/>
+      <c r="D83">
+        <f>IF($B83="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B83,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B83,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E83">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D83,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32415,6 +32680,10 @@
     <row r="84">
       <c r="A84" s="37" t="n"/>
       <c r="C84" s="27" t="n"/>
+      <c r="D84">
+        <f>IF($B84="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B84,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B84,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E84">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D84,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32431,6 +32700,10 @@
     <row r="85">
       <c r="A85" s="37" t="n"/>
       <c r="C85" s="27" t="n"/>
+      <c r="D85">
+        <f>IF($B85="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B85,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B85,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E85">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D85,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32447,6 +32720,10 @@
     <row r="86">
       <c r="A86" s="37" t="n"/>
       <c r="C86" s="27" t="n"/>
+      <c r="D86">
+        <f>IF($B86="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B86,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B86,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E86">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D86,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32463,6 +32740,10 @@
     <row r="87">
       <c r="A87" s="37" t="n"/>
       <c r="C87" s="27" t="n"/>
+      <c r="D87">
+        <f>IF($B87="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B87,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B87,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E87">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D87,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32479,6 +32760,10 @@
     <row r="88">
       <c r="A88" s="37" t="n"/>
       <c r="C88" s="27" t="n"/>
+      <c r="D88">
+        <f>IF($B88="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B88,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B88,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E88">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D88,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32495,6 +32780,10 @@
     <row r="89">
       <c r="A89" s="37" t="n"/>
       <c r="C89" s="27" t="n"/>
+      <c r="D89">
+        <f>IF($B89="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B89,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B89,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E89">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D89,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32511,6 +32800,10 @@
     <row r="90">
       <c r="A90" s="37" t="n"/>
       <c r="C90" s="27" t="n"/>
+      <c r="D90">
+        <f>IF($B90="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B90,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B90,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E90">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D90,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32527,6 +32820,10 @@
     <row r="91">
       <c r="A91" s="37" t="n"/>
       <c r="C91" s="27" t="n"/>
+      <c r="D91">
+        <f>IF($B91="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B91,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B91,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E91">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D91,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32543,6 +32840,10 @@
     <row r="92">
       <c r="A92" s="37" t="n"/>
       <c r="C92" s="27" t="n"/>
+      <c r="D92">
+        <f>IF($B92="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B92,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B92,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E92">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D92,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32559,6 +32860,10 @@
     <row r="93">
       <c r="A93" s="37" t="n"/>
       <c r="C93" s="27" t="n"/>
+      <c r="D93">
+        <f>IF($B93="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B93,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B93,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E93">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D93,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32575,6 +32880,10 @@
     <row r="94">
       <c r="A94" s="37" t="n"/>
       <c r="C94" s="27" t="n"/>
+      <c r="D94">
+        <f>IF($B94="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B94,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B94,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E94">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D94,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32591,6 +32900,10 @@
     <row r="95">
       <c r="A95" s="37" t="n"/>
       <c r="C95" s="27" t="n"/>
+      <c r="D95">
+        <f>IF($B95="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B95,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B95,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E95">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D95,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32607,6 +32920,10 @@
     <row r="96">
       <c r="A96" s="37" t="n"/>
       <c r="C96" s="27" t="n"/>
+      <c r="D96">
+        <f>IF($B96="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B96,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B96,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E96">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D96,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32623,6 +32940,10 @@
     <row r="97">
       <c r="A97" s="37" t="n"/>
       <c r="C97" s="27" t="n"/>
+      <c r="D97">
+        <f>IF($B97="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B97,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B97,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E97">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D97,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32639,6 +32960,10 @@
     <row r="98">
       <c r="A98" s="37" t="n"/>
       <c r="C98" s="27" t="n"/>
+      <c r="D98">
+        <f>IF($B98="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B98,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B98,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E98">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D98,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32655,6 +32980,10 @@
     <row r="99">
       <c r="A99" s="37" t="n"/>
       <c r="C99" s="27" t="n"/>
+      <c r="D99">
+        <f>IF($B99="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B99,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B99,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E99">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D99,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32671,6 +33000,10 @@
     <row r="100">
       <c r="A100" s="37" t="n"/>
       <c r="C100" s="27" t="n"/>
+      <c r="D100">
+        <f>IF($B100="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B100,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B100,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E100">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D100,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32687,6 +33020,10 @@
     <row r="101">
       <c r="A101" s="37" t="n"/>
       <c r="C101" s="27" t="n"/>
+      <c r="D101">
+        <f>IF($B101="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B101,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B101,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E101">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D101,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32703,6 +33040,10 @@
     <row r="102">
       <c r="A102" s="37" t="n"/>
       <c r="C102" s="27" t="n"/>
+      <c r="D102">
+        <f>IF($B102="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B102,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B102,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E102">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D102,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32719,6 +33060,10 @@
     <row r="103">
       <c r="A103" s="37" t="n"/>
       <c r="C103" s="27" t="n"/>
+      <c r="D103">
+        <f>IF($B103="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B103,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B103,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E103">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D103,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32735,6 +33080,10 @@
     <row r="104">
       <c r="A104" s="37" t="n"/>
       <c r="C104" s="27" t="n"/>
+      <c r="D104">
+        <f>IF($B104="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B104,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B104,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E104">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D104,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32751,6 +33100,10 @@
     <row r="105">
       <c r="A105" s="37" t="n"/>
       <c r="C105" s="27" t="n"/>
+      <c r="D105">
+        <f>IF($B105="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B105,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B105,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E105">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D105,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32767,6 +33120,10 @@
     <row r="106">
       <c r="A106" s="37" t="n"/>
       <c r="C106" s="27" t="n"/>
+      <c r="D106">
+        <f>IF($B106="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B106,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B106,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E106">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D106,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32783,6 +33140,10 @@
     <row r="107">
       <c r="A107" s="37" t="n"/>
       <c r="C107" s="27" t="n"/>
+      <c r="D107">
+        <f>IF($B107="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B107,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B107,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E107">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D107,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32799,6 +33160,10 @@
     <row r="108">
       <c r="A108" s="37" t="n"/>
       <c r="C108" s="27" t="n"/>
+      <c r="D108">
+        <f>IF($B108="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B108,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B108,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E108">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D108,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32815,6 +33180,10 @@
     <row r="109">
       <c r="A109" s="37" t="n"/>
       <c r="C109" s="27" t="n"/>
+      <c r="D109">
+        <f>IF($B109="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B109,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B109,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E109">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D109,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32831,6 +33200,10 @@
     <row r="110">
       <c r="A110" s="37" t="n"/>
       <c r="C110" s="27" t="n"/>
+      <c r="D110">
+        <f>IF($B110="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B110,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B110,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E110">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D110,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32847,6 +33220,10 @@
     <row r="111">
       <c r="A111" s="37" t="n"/>
       <c r="C111" s="27" t="n"/>
+      <c r="D111">
+        <f>IF($B111="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B111,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B111,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E111">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D111,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32863,6 +33240,10 @@
     <row r="112">
       <c r="A112" s="37" t="n"/>
       <c r="C112" s="27" t="n"/>
+      <c r="D112">
+        <f>IF($B112="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B112,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B112,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E112">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D112,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32879,6 +33260,10 @@
     <row r="113">
       <c r="A113" s="37" t="n"/>
       <c r="C113" s="27" t="n"/>
+      <c r="D113">
+        <f>IF($B113="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B113,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B113,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E113">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D113,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32895,6 +33280,10 @@
     <row r="114">
       <c r="A114" s="37" t="n"/>
       <c r="C114" s="27" t="n"/>
+      <c r="D114">
+        <f>IF($B114="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B114,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B114,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E114">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D114,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32911,6 +33300,10 @@
     <row r="115">
       <c r="A115" s="37" t="n"/>
       <c r="C115" s="27" t="n"/>
+      <c r="D115">
+        <f>IF($B115="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B115,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B115,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E115">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D115,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32927,6 +33320,10 @@
     <row r="116">
       <c r="A116" s="37" t="n"/>
       <c r="C116" s="27" t="n"/>
+      <c r="D116">
+        <f>IF($B116="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B116,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B116,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E116">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D116,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32943,6 +33340,10 @@
     <row r="117">
       <c r="A117" s="37" t="n"/>
       <c r="C117" s="27" t="n"/>
+      <c r="D117">
+        <f>IF($B117="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B117,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B117,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E117">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D117,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32959,6 +33360,10 @@
     <row r="118">
       <c r="A118" s="37" t="n"/>
       <c r="C118" s="27" t="n"/>
+      <c r="D118">
+        <f>IF($B118="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B118,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B118,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E118">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D118,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32975,6 +33380,10 @@
     <row r="119">
       <c r="A119" s="37" t="n"/>
       <c r="C119" s="27" t="n"/>
+      <c r="D119">
+        <f>IF($B119="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B119,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B119,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E119">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D119,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -32991,6 +33400,10 @@
     <row r="120">
       <c r="A120" s="37" t="n"/>
       <c r="C120" s="27" t="n"/>
+      <c r="D120">
+        <f>IF($B120="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B120,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B120,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E120">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D120,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33007,6 +33420,10 @@
     <row r="121">
       <c r="A121" s="37" t="n"/>
       <c r="C121" s="27" t="n"/>
+      <c r="D121">
+        <f>IF($B121="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B121,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B121,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E121">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D121,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33023,6 +33440,10 @@
     <row r="122">
       <c r="A122" s="37" t="n"/>
       <c r="C122" s="27" t="n"/>
+      <c r="D122">
+        <f>IF($B122="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B122,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B122,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E122">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D122,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33039,6 +33460,10 @@
     <row r="123">
       <c r="A123" s="37" t="n"/>
       <c r="C123" s="27" t="n"/>
+      <c r="D123">
+        <f>IF($B123="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B123,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B123,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E123">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D123,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33055,6 +33480,10 @@
     <row r="124">
       <c r="A124" s="37" t="n"/>
       <c r="C124" s="27" t="n"/>
+      <c r="D124">
+        <f>IF($B124="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B124,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B124,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E124">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D124,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33071,6 +33500,10 @@
     <row r="125">
       <c r="A125" s="37" t="n"/>
       <c r="C125" s="27" t="n"/>
+      <c r="D125">
+        <f>IF($B125="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B125,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B125,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E125">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D125,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33087,6 +33520,10 @@
     <row r="126">
       <c r="A126" s="37" t="n"/>
       <c r="C126" s="27" t="n"/>
+      <c r="D126">
+        <f>IF($B126="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B126,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B126,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E126">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D126,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33103,6 +33540,10 @@
     <row r="127">
       <c r="A127" s="37" t="n"/>
       <c r="C127" s="27" t="n"/>
+      <c r="D127">
+        <f>IF($B127="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B127,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B127,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E127">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D127,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33119,6 +33560,10 @@
     <row r="128">
       <c r="A128" s="37" t="n"/>
       <c r="C128" s="27" t="n"/>
+      <c r="D128">
+        <f>IF($B128="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B128,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B128,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E128">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D128,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33135,6 +33580,10 @@
     <row r="129">
       <c r="A129" s="37" t="n"/>
       <c r="C129" s="27" t="n"/>
+      <c r="D129">
+        <f>IF($B129="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B129,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B129,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E129">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D129,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33151,6 +33600,10 @@
     <row r="130">
       <c r="A130" s="37" t="n"/>
       <c r="C130" s="27" t="n"/>
+      <c r="D130">
+        <f>IF($B130="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B130,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B130,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E130">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D130,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33167,6 +33620,10 @@
     <row r="131">
       <c r="A131" s="37" t="n"/>
       <c r="C131" s="27" t="n"/>
+      <c r="D131">
+        <f>IF($B131="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B131,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B131,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E131">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D131,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33183,6 +33640,10 @@
     <row r="132">
       <c r="A132" s="37" t="n"/>
       <c r="C132" s="27" t="n"/>
+      <c r="D132">
+        <f>IF($B132="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B132,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B132,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E132">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D132,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33199,6 +33660,10 @@
     <row r="133">
       <c r="A133" s="37" t="n"/>
       <c r="C133" s="27" t="n"/>
+      <c r="D133">
+        <f>IF($B133="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B133,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B133,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E133">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D133,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33215,6 +33680,10 @@
     <row r="134">
       <c r="A134" s="37" t="n"/>
       <c r="C134" s="27" t="n"/>
+      <c r="D134">
+        <f>IF($B134="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B134,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B134,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E134">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D134,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33231,6 +33700,10 @@
     <row r="135">
       <c r="A135" s="37" t="n"/>
       <c r="C135" s="27" t="n"/>
+      <c r="D135">
+        <f>IF($B135="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B135,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B135,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E135">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D135,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33247,6 +33720,10 @@
     <row r="136">
       <c r="A136" s="37" t="n"/>
       <c r="C136" s="27" t="n"/>
+      <c r="D136">
+        <f>IF($B136="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B136,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B136,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E136">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D136,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33263,6 +33740,10 @@
     <row r="137">
       <c r="A137" s="37" t="n"/>
       <c r="C137" s="27" t="n"/>
+      <c r="D137">
+        <f>IF($B137="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B137,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B137,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E137">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D137,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33279,6 +33760,10 @@
     <row r="138">
       <c r="A138" s="37" t="n"/>
       <c r="C138" s="27" t="n"/>
+      <c r="D138">
+        <f>IF($B138="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B138,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B138,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E138">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D138,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33295,6 +33780,10 @@
     <row r="139">
       <c r="A139" s="37" t="n"/>
       <c r="C139" s="27" t="n"/>
+      <c r="D139">
+        <f>IF($B139="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B139,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B139,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E139">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D139,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33311,6 +33800,10 @@
     <row r="140">
       <c r="A140" s="37" t="n"/>
       <c r="C140" s="27" t="n"/>
+      <c r="D140">
+        <f>IF($B140="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B140,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B140,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E140">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D140,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33327,6 +33820,10 @@
     <row r="141">
       <c r="A141" s="37" t="n"/>
       <c r="C141" s="27" t="n"/>
+      <c r="D141">
+        <f>IF($B141="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B141,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B141,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E141">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D141,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33343,6 +33840,10 @@
     <row r="142">
       <c r="A142" s="37" t="n"/>
       <c r="C142" s="27" t="n"/>
+      <c r="D142">
+        <f>IF($B142="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B142,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B142,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E142">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D142,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33359,6 +33860,10 @@
     <row r="143">
       <c r="A143" s="37" t="n"/>
       <c r="C143" s="27" t="n"/>
+      <c r="D143">
+        <f>IF($B143="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B143,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B143,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E143">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D143,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33375,6 +33880,10 @@
     <row r="144">
       <c r="A144" s="37" t="n"/>
       <c r="C144" s="27" t="n"/>
+      <c r="D144">
+        <f>IF($B144="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B144,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B144,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E144">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D144,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33391,6 +33900,10 @@
     <row r="145">
       <c r="A145" s="37" t="n"/>
       <c r="C145" s="27" t="n"/>
+      <c r="D145">
+        <f>IF($B145="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B145,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B145,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E145">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D145,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33407,6 +33920,10 @@
     <row r="146">
       <c r="A146" s="37" t="n"/>
       <c r="C146" s="27" t="n"/>
+      <c r="D146">
+        <f>IF($B146="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B146,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B146,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E146">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D146,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33423,6 +33940,10 @@
     <row r="147">
       <c r="A147" s="37" t="n"/>
       <c r="C147" s="27" t="n"/>
+      <c r="D147">
+        <f>IF($B147="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B147,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B147,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E147">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D147,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33439,6 +33960,10 @@
     <row r="148">
       <c r="A148" s="37" t="n"/>
       <c r="C148" s="27" t="n"/>
+      <c r="D148">
+        <f>IF($B148="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B148,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B148,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E148">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D148,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33455,6 +33980,10 @@
     <row r="149">
       <c r="A149" s="37" t="n"/>
       <c r="C149" s="27" t="n"/>
+      <c r="D149">
+        <f>IF($B149="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B149,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B149,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E149">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D149,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33471,6 +34000,10 @@
     <row r="150">
       <c r="A150" s="37" t="n"/>
       <c r="C150" s="27" t="n"/>
+      <c r="D150">
+        <f>IF($B150="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B150,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B150,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E150">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D150,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33487,6 +34020,10 @@
     <row r="151">
       <c r="A151" s="37" t="n"/>
       <c r="C151" s="27" t="n"/>
+      <c r="D151">
+        <f>IF($B151="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B151,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B151,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E151">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D151,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33503,6 +34040,10 @@
     <row r="152">
       <c r="A152" s="37" t="n"/>
       <c r="C152" s="27" t="n"/>
+      <c r="D152">
+        <f>IF($B152="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B152,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B152,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E152">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D152,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33519,6 +34060,10 @@
     <row r="153">
       <c r="A153" s="37" t="n"/>
       <c r="C153" s="27" t="n"/>
+      <c r="D153">
+        <f>IF($B153="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B153,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B153,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E153">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D153,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33535,6 +34080,10 @@
     <row r="154">
       <c r="A154" s="37" t="n"/>
       <c r="C154" s="27" t="n"/>
+      <c r="D154">
+        <f>IF($B154="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B154,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B154,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E154">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D154,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33551,6 +34100,10 @@
     <row r="155">
       <c r="A155" s="37" t="n"/>
       <c r="C155" s="27" t="n"/>
+      <c r="D155">
+        <f>IF($B155="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B155,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B155,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E155">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D155,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33567,6 +34120,10 @@
     <row r="156">
       <c r="A156" s="37" t="n"/>
       <c r="C156" s="27" t="n"/>
+      <c r="D156">
+        <f>IF($B156="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B156,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B156,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E156">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D156,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33583,6 +34140,10 @@
     <row r="157">
       <c r="A157" s="37" t="n"/>
       <c r="C157" s="27" t="n"/>
+      <c r="D157">
+        <f>IF($B157="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B157,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B157,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E157">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D157,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33599,6 +34160,10 @@
     <row r="158">
       <c r="A158" s="37" t="n"/>
       <c r="C158" s="27" t="n"/>
+      <c r="D158">
+        <f>IF($B158="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B158,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B158,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E158">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D158,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33615,6 +34180,10 @@
     <row r="159">
       <c r="A159" s="37" t="n"/>
       <c r="C159" s="27" t="n"/>
+      <c r="D159">
+        <f>IF($B159="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B159,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B159,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E159">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D159,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33631,6 +34200,10 @@
     <row r="160">
       <c r="A160" s="37" t="n"/>
       <c r="C160" s="27" t="n"/>
+      <c r="D160">
+        <f>IF($B160="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B160,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B160,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E160">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D160,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33647,6 +34220,10 @@
     <row r="161">
       <c r="A161" s="37" t="n"/>
       <c r="C161" s="27" t="n"/>
+      <c r="D161">
+        <f>IF($B161="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B161,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B161,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E161">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D161,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33663,6 +34240,10 @@
     <row r="162">
       <c r="A162" s="37" t="n"/>
       <c r="C162" s="27" t="n"/>
+      <c r="D162">
+        <f>IF($B162="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B162,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B162,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E162">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D162,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33679,6 +34260,10 @@
     <row r="163">
       <c r="A163" s="37" t="n"/>
       <c r="C163" s="27" t="n"/>
+      <c r="D163">
+        <f>IF($B163="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B163,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B163,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E163">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D163,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33695,6 +34280,10 @@
     <row r="164">
       <c r="A164" s="37" t="n"/>
       <c r="C164" s="27" t="n"/>
+      <c r="D164">
+        <f>IF($B164="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B164,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B164,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E164">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D164,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33711,6 +34300,10 @@
     <row r="165">
       <c r="A165" s="37" t="n"/>
       <c r="C165" s="27" t="n"/>
+      <c r="D165">
+        <f>IF($B165="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B165,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B165,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E165">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D165,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33727,6 +34320,10 @@
     <row r="166">
       <c r="A166" s="37" t="n"/>
       <c r="C166" s="27" t="n"/>
+      <c r="D166">
+        <f>IF($B166="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B166,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B166,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E166">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D166,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33743,6 +34340,10 @@
     <row r="167">
       <c r="A167" s="37" t="n"/>
       <c r="C167" s="27" t="n"/>
+      <c r="D167">
+        <f>IF($B167="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B167,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B167,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E167">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D167,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33759,6 +34360,10 @@
     <row r="168">
       <c r="A168" s="37" t="n"/>
       <c r="C168" s="27" t="n"/>
+      <c r="D168">
+        <f>IF($B168="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B168,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B168,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E168">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D168,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33775,6 +34380,10 @@
     <row r="169">
       <c r="A169" s="37" t="n"/>
       <c r="C169" s="27" t="n"/>
+      <c r="D169">
+        <f>IF($B169="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B169,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B169,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E169">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D169,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33791,6 +34400,10 @@
     <row r="170">
       <c r="A170" s="37" t="n"/>
       <c r="C170" s="27" t="n"/>
+      <c r="D170">
+        <f>IF($B170="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B170,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B170,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E170">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D170,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33807,6 +34420,10 @@
     <row r="171">
       <c r="A171" s="37" t="n"/>
       <c r="C171" s="27" t="n"/>
+      <c r="D171">
+        <f>IF($B171="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B171,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B171,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E171">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D171,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33823,6 +34440,10 @@
     <row r="172">
       <c r="A172" s="37" t="n"/>
       <c r="C172" s="27" t="n"/>
+      <c r="D172">
+        <f>IF($B172="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B172,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B172,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E172">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D172,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33839,6 +34460,10 @@
     <row r="173">
       <c r="A173" s="37" t="n"/>
       <c r="C173" s="27" t="n"/>
+      <c r="D173">
+        <f>IF($B173="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B173,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B173,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E173">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D173,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33855,6 +34480,10 @@
     <row r="174">
       <c r="A174" s="37" t="n"/>
       <c r="C174" s="27" t="n"/>
+      <c r="D174">
+        <f>IF($B174="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B174,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B174,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E174">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D174,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33871,6 +34500,10 @@
     <row r="175">
       <c r="A175" s="37" t="n"/>
       <c r="C175" s="27" t="n"/>
+      <c r="D175">
+        <f>IF($B175="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B175,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B175,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E175">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D175,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33887,6 +34520,10 @@
     <row r="176">
       <c r="A176" s="37" t="n"/>
       <c r="C176" s="27" t="n"/>
+      <c r="D176">
+        <f>IF($B176="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B176,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B176,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E176">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D176,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33903,6 +34540,10 @@
     <row r="177">
       <c r="A177" s="37" t="n"/>
       <c r="C177" s="27" t="n"/>
+      <c r="D177">
+        <f>IF($B177="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B177,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B177,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E177">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D177,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33919,6 +34560,10 @@
     <row r="178">
       <c r="A178" s="37" t="n"/>
       <c r="C178" s="27" t="n"/>
+      <c r="D178">
+        <f>IF($B178="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B178,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B178,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E178">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D178,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33935,6 +34580,10 @@
     <row r="179">
       <c r="A179" s="37" t="n"/>
       <c r="C179" s="27" t="n"/>
+      <c r="D179">
+        <f>IF($B179="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B179,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B179,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E179">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D179,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33951,6 +34600,10 @@
     <row r="180">
       <c r="A180" s="37" t="n"/>
       <c r="C180" s="27" t="n"/>
+      <c r="D180">
+        <f>IF($B180="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B180,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B180,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E180">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D180,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33967,6 +34620,10 @@
     <row r="181">
       <c r="A181" s="37" t="n"/>
       <c r="C181" s="27" t="n"/>
+      <c r="D181">
+        <f>IF($B181="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B181,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B181,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E181">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D181,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33983,6 +34640,10 @@
     <row r="182">
       <c r="A182" s="37" t="n"/>
       <c r="C182" s="27" t="n"/>
+      <c r="D182">
+        <f>IF($B182="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B182,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B182,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E182">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D182,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -33999,6 +34660,10 @@
     <row r="183">
       <c r="A183" s="37" t="n"/>
       <c r="C183" s="27" t="n"/>
+      <c r="D183">
+        <f>IF($B183="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B183,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B183,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E183">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D183,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34015,6 +34680,10 @@
     <row r="184">
       <c r="A184" s="37" t="n"/>
       <c r="C184" s="27" t="n"/>
+      <c r="D184">
+        <f>IF($B184="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B184,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B184,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E184">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D184,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34031,6 +34700,10 @@
     <row r="185">
       <c r="A185" s="37" t="n"/>
       <c r="C185" s="27" t="n"/>
+      <c r="D185">
+        <f>IF($B185="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B185,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B185,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E185">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D185,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34047,6 +34720,10 @@
     <row r="186">
       <c r="A186" s="37" t="n"/>
       <c r="C186" s="27" t="n"/>
+      <c r="D186">
+        <f>IF($B186="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B186,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B186,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E186">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D186,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34063,6 +34740,10 @@
     <row r="187">
       <c r="A187" s="37" t="n"/>
       <c r="C187" s="27" t="n"/>
+      <c r="D187">
+        <f>IF($B187="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B187,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B187,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E187">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D187,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34079,6 +34760,10 @@
     <row r="188">
       <c r="A188" s="37" t="n"/>
       <c r="C188" s="27" t="n"/>
+      <c r="D188">
+        <f>IF($B188="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B188,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B188,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E188">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D188,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34095,6 +34780,10 @@
     <row r="189">
       <c r="A189" s="37" t="n"/>
       <c r="C189" s="27" t="n"/>
+      <c r="D189">
+        <f>IF($B189="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B189,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B189,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E189">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D189,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34111,6 +34800,10 @@
     <row r="190">
       <c r="A190" s="37" t="n"/>
       <c r="C190" s="27" t="n"/>
+      <c r="D190">
+        <f>IF($B190="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B190,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B190,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E190">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D190,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34127,6 +34820,10 @@
     <row r="191">
       <c r="A191" s="37" t="n"/>
       <c r="C191" s="27" t="n"/>
+      <c r="D191">
+        <f>IF($B191="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B191,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B191,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E191">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D191,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34143,6 +34840,10 @@
     <row r="192">
       <c r="A192" s="37" t="n"/>
       <c r="C192" s="27" t="n"/>
+      <c r="D192">
+        <f>IF($B192="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B192,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B192,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E192">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D192,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34159,6 +34860,10 @@
     <row r="193">
       <c r="A193" s="37" t="n"/>
       <c r="C193" s="27" t="n"/>
+      <c r="D193">
+        <f>IF($B193="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B193,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B193,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E193">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D193,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34175,6 +34880,10 @@
     <row r="194">
       <c r="A194" s="37" t="n"/>
       <c r="C194" s="27" t="n"/>
+      <c r="D194">
+        <f>IF($B194="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B194,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B194,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E194">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D194,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34191,6 +34900,10 @@
     <row r="195">
       <c r="A195" s="37" t="n"/>
       <c r="C195" s="27" t="n"/>
+      <c r="D195">
+        <f>IF($B195="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B195,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B195,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E195">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D195,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34207,6 +34920,10 @@
     <row r="196">
       <c r="A196" s="37" t="n"/>
       <c r="C196" s="27" t="n"/>
+      <c r="D196">
+        <f>IF($B196="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B196,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B196,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E196">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D196,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34223,6 +34940,10 @@
     <row r="197">
       <c r="A197" s="37" t="n"/>
       <c r="C197" s="27" t="n"/>
+      <c r="D197">
+        <f>IF($B197="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B197,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B197,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E197">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D197,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34239,6 +34960,10 @@
     <row r="198">
       <c r="A198" s="37" t="n"/>
       <c r="C198" s="27" t="n"/>
+      <c r="D198">
+        <f>IF($B198="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B198,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B198,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E198">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D198,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34255,6 +34980,10 @@
     <row r="199">
       <c r="A199" s="37" t="n"/>
       <c r="C199" s="27" t="n"/>
+      <c r="D199">
+        <f>IF($B199="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B199,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B199,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E199">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D199,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34271,6 +35000,10 @@
     <row r="200">
       <c r="A200" s="37" t="n"/>
       <c r="C200" s="27" t="n"/>
+      <c r="D200">
+        <f>IF($B200="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B200,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B200,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E200">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D200,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34287,6 +35020,10 @@
     <row r="201">
       <c r="A201" s="37" t="n"/>
       <c r="C201" s="27" t="n"/>
+      <c r="D201">
+        <f>IF($B201="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B201,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B201,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E201">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D201,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34303,6 +35040,10 @@
     <row r="202">
       <c r="A202" s="37" t="n"/>
       <c r="C202" s="27" t="n"/>
+      <c r="D202">
+        <f>IF($B202="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B202,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B202,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E202">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D202,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34319,6 +35060,10 @@
     <row r="203">
       <c r="A203" s="37" t="n"/>
       <c r="C203" s="27" t="n"/>
+      <c r="D203">
+        <f>IF($B203="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B203,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B203,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E203">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D203,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34335,6 +35080,10 @@
     <row r="204">
       <c r="A204" s="37" t="n"/>
       <c r="C204" s="27" t="n"/>
+      <c r="D204">
+        <f>IF($B204="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B204,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B204,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E204">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D204,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34351,6 +35100,10 @@
     <row r="205">
       <c r="A205" s="37" t="n"/>
       <c r="C205" s="27" t="n"/>
+      <c r="D205">
+        <f>IF($B205="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B205,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B205,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E205">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D205,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34367,6 +35120,10 @@
     <row r="206">
       <c r="A206" s="37" t="n"/>
       <c r="C206" s="27" t="n"/>
+      <c r="D206">
+        <f>IF($B206="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B206,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B206,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E206">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D206,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34383,6 +35140,10 @@
     <row r="207">
       <c r="A207" s="37" t="n"/>
       <c r="C207" s="27" t="n"/>
+      <c r="D207">
+        <f>IF($B207="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B207,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B207,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E207">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D207,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34399,6 +35160,10 @@
     <row r="208">
       <c r="A208" s="37" t="n"/>
       <c r="C208" s="27" t="n"/>
+      <c r="D208">
+        <f>IF($B208="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B208,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B208,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E208">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D208,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34415,6 +35180,10 @@
     <row r="209">
       <c r="A209" s="37" t="n"/>
       <c r="C209" s="27" t="n"/>
+      <c r="D209">
+        <f>IF($B209="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B209,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B209,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E209">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D209,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34431,6 +35200,10 @@
     <row r="210">
       <c r="A210" s="37" t="n"/>
       <c r="C210" s="27" t="n"/>
+      <c r="D210">
+        <f>IF($B210="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B210,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B210,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E210">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D210,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34447,6 +35220,10 @@
     <row r="211">
       <c r="A211" s="37" t="n"/>
       <c r="C211" s="27" t="n"/>
+      <c r="D211">
+        <f>IF($B211="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B211,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B211,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E211">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D211,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34463,6 +35240,10 @@
     <row r="212">
       <c r="A212" s="37" t="n"/>
       <c r="C212" s="27" t="n"/>
+      <c r="D212">
+        <f>IF($B212="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B212,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B212,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E212">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D212,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34479,6 +35260,10 @@
     <row r="213">
       <c r="A213" s="37" t="n"/>
       <c r="C213" s="27" t="n"/>
+      <c r="D213">
+        <f>IF($B213="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B213,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B213,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E213">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D213,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34495,6 +35280,10 @@
     <row r="214">
       <c r="A214" s="37" t="n"/>
       <c r="C214" s="27" t="n"/>
+      <c r="D214">
+        <f>IF($B214="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B214,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B214,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E214">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D214,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34511,6 +35300,10 @@
     <row r="215">
       <c r="A215" s="37" t="n"/>
       <c r="C215" s="27" t="n"/>
+      <c r="D215">
+        <f>IF($B215="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B215,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B215,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E215">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D215,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34527,6 +35320,10 @@
     <row r="216">
       <c r="A216" s="37" t="n"/>
       <c r="C216" s="27" t="n"/>
+      <c r="D216">
+        <f>IF($B216="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B216,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B216,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E216">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D216,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34543,6 +35340,10 @@
     <row r="217">
       <c r="A217" s="37" t="n"/>
       <c r="C217" s="27" t="n"/>
+      <c r="D217">
+        <f>IF($B217="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B217,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B217,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E217">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D217,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34559,6 +35360,10 @@
     <row r="218">
       <c r="A218" s="37" t="n"/>
       <c r="C218" s="27" t="n"/>
+      <c r="D218">
+        <f>IF($B218="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B218,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B218,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E218">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D218,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34575,6 +35380,10 @@
     <row r="219">
       <c r="A219" s="37" t="n"/>
       <c r="C219" s="27" t="n"/>
+      <c r="D219">
+        <f>IF($B219="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B219,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B219,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E219">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D219,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34591,6 +35400,10 @@
     <row r="220">
       <c r="A220" s="37" t="n"/>
       <c r="C220" s="27" t="n"/>
+      <c r="D220">
+        <f>IF($B220="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B220,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B220,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E220">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D220,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34607,6 +35420,10 @@
     <row r="221">
       <c r="A221" s="37" t="n"/>
       <c r="C221" s="27" t="n"/>
+      <c r="D221">
+        <f>IF($B221="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B221,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B221,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E221">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D221,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34623,6 +35440,10 @@
     <row r="222">
       <c r="A222" s="37" t="n"/>
       <c r="C222" s="27" t="n"/>
+      <c r="D222">
+        <f>IF($B222="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B222,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B222,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E222">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D222,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34639,6 +35460,10 @@
     <row r="223">
       <c r="A223" s="37" t="n"/>
       <c r="C223" s="27" t="n"/>
+      <c r="D223">
+        <f>IF($B223="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B223,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B223,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E223">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D223,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34655,6 +35480,10 @@
     <row r="224">
       <c r="A224" s="37" t="n"/>
       <c r="C224" s="27" t="n"/>
+      <c r="D224">
+        <f>IF($B224="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B224,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B224,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E224">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D224,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34671,6 +35500,10 @@
     <row r="225">
       <c r="A225" s="37" t="n"/>
       <c r="C225" s="27" t="n"/>
+      <c r="D225">
+        <f>IF($B225="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B225,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B225,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E225">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D225,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34687,6 +35520,10 @@
     <row r="226">
       <c r="A226" s="37" t="n"/>
       <c r="C226" s="27" t="n"/>
+      <c r="D226">
+        <f>IF($B226="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B226,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B226,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E226">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D226,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34703,6 +35540,10 @@
     <row r="227">
       <c r="A227" s="37" t="n"/>
       <c r="C227" s="27" t="n"/>
+      <c r="D227">
+        <f>IF($B227="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B227,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B227,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E227">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D227,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34719,6 +35560,10 @@
     <row r="228">
       <c r="A228" s="37" t="n"/>
       <c r="C228" s="27" t="n"/>
+      <c r="D228">
+        <f>IF($B228="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B228,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B228,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E228">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D228,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34735,6 +35580,10 @@
     <row r="229">
       <c r="A229" s="37" t="n"/>
       <c r="C229" s="27" t="n"/>
+      <c r="D229">
+        <f>IF($B229="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B229,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B229,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E229">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D229,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34751,6 +35600,10 @@
     <row r="230">
       <c r="A230" s="37" t="n"/>
       <c r="C230" s="27" t="n"/>
+      <c r="D230">
+        <f>IF($B230="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B230,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B230,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E230">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D230,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34767,6 +35620,10 @@
     <row r="231">
       <c r="A231" s="37" t="n"/>
       <c r="C231" s="27" t="n"/>
+      <c r="D231">
+        <f>IF($B231="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B231,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B231,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E231">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D231,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34783,6 +35640,10 @@
     <row r="232">
       <c r="A232" s="37" t="n"/>
       <c r="C232" s="27" t="n"/>
+      <c r="D232">
+        <f>IF($B232="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B232,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B232,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E232">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D232,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34799,6 +35660,10 @@
     <row r="233">
       <c r="A233" s="37" t="n"/>
       <c r="C233" s="27" t="n"/>
+      <c r="D233">
+        <f>IF($B233="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B233,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B233,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E233">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D233,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34815,6 +35680,10 @@
     <row r="234">
       <c r="A234" s="37" t="n"/>
       <c r="C234" s="27" t="n"/>
+      <c r="D234">
+        <f>IF($B234="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B234,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B234,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E234">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D234,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34831,6 +35700,10 @@
     <row r="235">
       <c r="A235" s="37" t="n"/>
       <c r="C235" s="27" t="n"/>
+      <c r="D235">
+        <f>IF($B235="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B235,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B235,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E235">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D235,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34847,6 +35720,10 @@
     <row r="236">
       <c r="A236" s="37" t="n"/>
       <c r="C236" s="27" t="n"/>
+      <c r="D236">
+        <f>IF($B236="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B236,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B236,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E236">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D236,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34863,6 +35740,10 @@
     <row r="237">
       <c r="A237" s="37" t="n"/>
       <c r="C237" s="27" t="n"/>
+      <c r="D237">
+        <f>IF($B237="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B237,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B237,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E237">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D237,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34879,6 +35760,10 @@
     <row r="238">
       <c r="A238" s="37" t="n"/>
       <c r="C238" s="27" t="n"/>
+      <c r="D238">
+        <f>IF($B238="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B238,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B238,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E238">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D238,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34895,6 +35780,10 @@
     <row r="239">
       <c r="A239" s="37" t="n"/>
       <c r="C239" s="27" t="n"/>
+      <c r="D239">
+        <f>IF($B239="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B239,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B239,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E239">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D239,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34911,6 +35800,10 @@
     <row r="240">
       <c r="A240" s="37" t="n"/>
       <c r="C240" s="27" t="n"/>
+      <c r="D240">
+        <f>IF($B240="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B240,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B240,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E240">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D240,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34927,6 +35820,10 @@
     <row r="241">
       <c r="A241" s="37" t="n"/>
       <c r="C241" s="27" t="n"/>
+      <c r="D241">
+        <f>IF($B241="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B241,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B241,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E241">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D241,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34943,6 +35840,10 @@
     <row r="242">
       <c r="A242" s="37" t="n"/>
       <c r="C242" s="27" t="n"/>
+      <c r="D242">
+        <f>IF($B242="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B242,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B242,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E242">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D242,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34959,6 +35860,10 @@
     <row r="243">
       <c r="A243" s="37" t="n"/>
       <c r="C243" s="27" t="n"/>
+      <c r="D243">
+        <f>IF($B243="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B243,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B243,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E243">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D243,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34975,6 +35880,10 @@
     <row r="244">
       <c r="A244" s="37" t="n"/>
       <c r="C244" s="27" t="n"/>
+      <c r="D244">
+        <f>IF($B244="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B244,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B244,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E244">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D244,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -34991,6 +35900,10 @@
     <row r="245">
       <c r="A245" s="37" t="n"/>
       <c r="C245" s="27" t="n"/>
+      <c r="D245">
+        <f>IF($B245="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B245,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B245,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E245">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D245,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35007,6 +35920,10 @@
     <row r="246">
       <c r="A246" s="37" t="n"/>
       <c r="C246" s="27" t="n"/>
+      <c r="D246">
+        <f>IF($B246="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B246,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B246,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E246">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D246,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35023,6 +35940,10 @@
     <row r="247">
       <c r="A247" s="37" t="n"/>
       <c r="C247" s="27" t="n"/>
+      <c r="D247">
+        <f>IF($B247="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B247,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B247,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E247">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D247,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35039,6 +35960,10 @@
     <row r="248">
       <c r="A248" s="37" t="n"/>
       <c r="C248" s="27" t="n"/>
+      <c r="D248">
+        <f>IF($B248="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B248,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B248,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E248">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D248,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35055,6 +35980,10 @@
     <row r="249">
       <c r="A249" s="37" t="n"/>
       <c r="C249" s="27" t="n"/>
+      <c r="D249">
+        <f>IF($B249="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B249,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B249,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E249">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D249,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35071,6 +36000,10 @@
     <row r="250">
       <c r="A250" s="37" t="n"/>
       <c r="C250" s="27" t="n"/>
+      <c r="D250">
+        <f>IF($B250="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B250,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B250,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E250">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D250,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35087,6 +36020,10 @@
     <row r="251">
       <c r="A251" s="37" t="n"/>
       <c r="C251" s="27" t="n"/>
+      <c r="D251">
+        <f>IF($B251="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B251,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B251,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E251">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D251,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35103,6 +36040,10 @@
     <row r="252">
       <c r="A252" s="37" t="n"/>
       <c r="C252" s="27" t="n"/>
+      <c r="D252">
+        <f>IF($B252="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B252,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B252,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E252">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D252,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35119,6 +36060,10 @@
     <row r="253">
       <c r="A253" s="37" t="n"/>
       <c r="C253" s="27" t="n"/>
+      <c r="D253">
+        <f>IF($B253="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B253,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B253,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E253">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D253,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35135,6 +36080,10 @@
     <row r="254">
       <c r="A254" s="37" t="n"/>
       <c r="C254" s="27" t="n"/>
+      <c r="D254">
+        <f>IF($B254="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B254,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B254,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E254">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D254,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35151,6 +36100,10 @@
     <row r="255">
       <c r="A255" s="37" t="n"/>
       <c r="C255" s="27" t="n"/>
+      <c r="D255">
+        <f>IF($B255="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B255,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B255,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E255">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D255,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35167,6 +36120,10 @@
     <row r="256">
       <c r="A256" s="37" t="n"/>
       <c r="C256" s="27" t="n"/>
+      <c r="D256">
+        <f>IF($B256="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B256,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B256,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E256">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D256,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35183,6 +36140,10 @@
     <row r="257">
       <c r="A257" s="37" t="n"/>
       <c r="C257" s="27" t="n"/>
+      <c r="D257">
+        <f>IF($B257="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B257,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B257,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E257">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D257,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35199,6 +36160,10 @@
     <row r="258">
       <c r="A258" s="37" t="n"/>
       <c r="C258" s="27" t="n"/>
+      <c r="D258">
+        <f>IF($B258="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B258,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B258,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E258">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D258,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35215,6 +36180,10 @@
     <row r="259">
       <c r="A259" s="37" t="n"/>
       <c r="C259" s="27" t="n"/>
+      <c r="D259">
+        <f>IF($B259="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B259,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B259,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E259">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D259,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35231,6 +36200,10 @@
     <row r="260">
       <c r="A260" s="37" t="n"/>
       <c r="C260" s="27" t="n"/>
+      <c r="D260">
+        <f>IF($B260="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B260,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B260,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E260">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D260,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35247,6 +36220,10 @@
     <row r="261">
       <c r="A261" s="37" t="n"/>
       <c r="C261" s="27" t="n"/>
+      <c r="D261">
+        <f>IF($B261="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B261,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B261,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E261">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D261,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35263,6 +36240,10 @@
     <row r="262">
       <c r="A262" s="37" t="n"/>
       <c r="C262" s="27" t="n"/>
+      <c r="D262">
+        <f>IF($B262="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B262,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B262,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E262">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D262,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35279,6 +36260,10 @@
     <row r="263">
       <c r="A263" s="37" t="n"/>
       <c r="C263" s="27" t="n"/>
+      <c r="D263">
+        <f>IF($B263="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B263,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B263,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E263">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D263,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35295,6 +36280,10 @@
     <row r="264">
       <c r="A264" s="37" t="n"/>
       <c r="C264" s="27" t="n"/>
+      <c r="D264">
+        <f>IF($B264="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B264,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B264,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E264">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D264,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35311,6 +36300,10 @@
     <row r="265">
       <c r="A265" s="37" t="n"/>
       <c r="C265" s="27" t="n"/>
+      <c r="D265">
+        <f>IF($B265="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B265,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B265,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E265">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D265,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35327,6 +36320,10 @@
     <row r="266">
       <c r="A266" s="37" t="n"/>
       <c r="C266" s="27" t="n"/>
+      <c r="D266">
+        <f>IF($B266="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B266,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B266,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E266">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D266,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35343,6 +36340,10 @@
     <row r="267">
       <c r="A267" s="37" t="n"/>
       <c r="C267" s="27" t="n"/>
+      <c r="D267">
+        <f>IF($B267="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B267,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B267,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E267">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D267,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35359,6 +36360,10 @@
     <row r="268">
       <c r="A268" s="37" t="n"/>
       <c r="C268" s="27" t="n"/>
+      <c r="D268">
+        <f>IF($B268="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B268,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B268,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E268">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D268,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35375,6 +36380,10 @@
     <row r="269">
       <c r="A269" s="37" t="n"/>
       <c r="C269" s="27" t="n"/>
+      <c r="D269">
+        <f>IF($B269="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B269,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B269,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E269">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D269,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35391,6 +36400,10 @@
     <row r="270">
       <c r="A270" s="37" t="n"/>
       <c r="C270" s="27" t="n"/>
+      <c r="D270">
+        <f>IF($B270="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B270,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B270,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E270">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D270,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35407,6 +36420,10 @@
     <row r="271">
       <c r="A271" s="37" t="n"/>
       <c r="C271" s="27" t="n"/>
+      <c r="D271">
+        <f>IF($B271="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B271,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B271,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E271">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D271,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35423,6 +36440,10 @@
     <row r="272">
       <c r="A272" s="37" t="n"/>
       <c r="C272" s="27" t="n"/>
+      <c r="D272">
+        <f>IF($B272="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B272,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B272,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E272">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D272,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35439,6 +36460,10 @@
     <row r="273">
       <c r="A273" s="37" t="n"/>
       <c r="C273" s="27" t="n"/>
+      <c r="D273">
+        <f>IF($B273="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B273,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B273,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E273">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D273,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35455,6 +36480,10 @@
     <row r="274">
       <c r="A274" s="37" t="n"/>
       <c r="C274" s="27" t="n"/>
+      <c r="D274">
+        <f>IF($B274="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B274,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B274,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E274">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D274,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35471,6 +36500,10 @@
     <row r="275">
       <c r="A275" s="37" t="n"/>
       <c r="C275" s="27" t="n"/>
+      <c r="D275">
+        <f>IF($B275="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B275,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B275,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E275">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D275,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35487,6 +36520,10 @@
     <row r="276">
       <c r="A276" s="37" t="n"/>
       <c r="C276" s="27" t="n"/>
+      <c r="D276">
+        <f>IF($B276="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B276,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B276,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E276">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D276,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35503,6 +36540,10 @@
     <row r="277">
       <c r="A277" s="37" t="n"/>
       <c r="C277" s="27" t="n"/>
+      <c r="D277">
+        <f>IF($B277="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B277,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B277,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E277">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D277,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35519,6 +36560,10 @@
     <row r="278">
       <c r="A278" s="37" t="n"/>
       <c r="C278" s="27" t="n"/>
+      <c r="D278">
+        <f>IF($B278="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B278,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B278,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E278">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D278,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35535,6 +36580,10 @@
     <row r="279">
       <c r="A279" s="37" t="n"/>
       <c r="C279" s="27" t="n"/>
+      <c r="D279">
+        <f>IF($B279="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B279,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B279,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E279">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D279,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35551,6 +36600,10 @@
     <row r="280">
       <c r="A280" s="37" t="n"/>
       <c r="C280" s="27" t="n"/>
+      <c r="D280">
+        <f>IF($B280="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B280,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B280,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E280">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D280,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35567,6 +36620,10 @@
     <row r="281">
       <c r="A281" s="37" t="n"/>
       <c r="C281" s="27" t="n"/>
+      <c r="D281">
+        <f>IF($B281="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B281,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B281,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E281">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D281,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35583,6 +36640,10 @@
     <row r="282">
       <c r="A282" s="37" t="n"/>
       <c r="C282" s="27" t="n"/>
+      <c r="D282">
+        <f>IF($B282="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B282,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B282,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E282">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D282,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35599,6 +36660,10 @@
     <row r="283">
       <c r="A283" s="37" t="n"/>
       <c r="C283" s="27" t="n"/>
+      <c r="D283">
+        <f>IF($B283="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B283,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B283,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E283">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D283,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35615,6 +36680,10 @@
     <row r="284">
       <c r="A284" s="37" t="n"/>
       <c r="C284" s="27" t="n"/>
+      <c r="D284">
+        <f>IF($B284="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B284,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B284,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E284">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D284,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35631,6 +36700,10 @@
     <row r="285">
       <c r="A285" s="37" t="n"/>
       <c r="C285" s="27" t="n"/>
+      <c r="D285">
+        <f>IF($B285="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B285,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B285,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E285">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D285,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35647,6 +36720,10 @@
     <row r="286">
       <c r="A286" s="37" t="n"/>
       <c r="C286" s="27" t="n"/>
+      <c r="D286">
+        <f>IF($B286="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B286,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B286,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E286">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D286,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35663,6 +36740,10 @@
     <row r="287">
       <c r="A287" s="37" t="n"/>
       <c r="C287" s="27" t="n"/>
+      <c r="D287">
+        <f>IF($B287="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B287,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B287,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E287">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D287,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35679,6 +36760,10 @@
     <row r="288">
       <c r="A288" s="37" t="n"/>
       <c r="C288" s="27" t="n"/>
+      <c r="D288">
+        <f>IF($B288="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B288,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B288,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E288">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D288,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35695,6 +36780,10 @@
     <row r="289">
       <c r="A289" s="37" t="n"/>
       <c r="C289" s="27" t="n"/>
+      <c r="D289">
+        <f>IF($B289="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B289,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B289,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E289">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D289,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35711,6 +36800,10 @@
     <row r="290">
       <c r="A290" s="37" t="n"/>
       <c r="C290" s="27" t="n"/>
+      <c r="D290">
+        <f>IF($B290="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B290,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B290,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E290">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D290,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35727,6 +36820,10 @@
     <row r="291">
       <c r="A291" s="37" t="n"/>
       <c r="C291" s="27" t="n"/>
+      <c r="D291">
+        <f>IF($B291="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B291,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B291,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E291">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D291,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35743,6 +36840,10 @@
     <row r="292">
       <c r="A292" s="37" t="n"/>
       <c r="C292" s="27" t="n"/>
+      <c r="D292">
+        <f>IF($B292="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B292,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B292,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E292">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D292,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35759,6 +36860,10 @@
     <row r="293">
       <c r="A293" s="37" t="n"/>
       <c r="C293" s="27" t="n"/>
+      <c r="D293">
+        <f>IF($B293="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B293,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B293,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E293">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D293,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35775,6 +36880,10 @@
     <row r="294">
       <c r="A294" s="37" t="n"/>
       <c r="C294" s="27" t="n"/>
+      <c r="D294">
+        <f>IF($B294="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B294,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B294,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E294">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D294,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35791,6 +36900,10 @@
     <row r="295">
       <c r="A295" s="37" t="n"/>
       <c r="C295" s="27" t="n"/>
+      <c r="D295">
+        <f>IF($B295="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B295,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B295,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E295">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D295,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35807,6 +36920,10 @@
     <row r="296">
       <c r="A296" s="37" t="n"/>
       <c r="C296" s="27" t="n"/>
+      <c r="D296">
+        <f>IF($B296="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B296,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B296,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E296">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D296,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35823,6 +36940,10 @@
     <row r="297">
       <c r="A297" s="37" t="n"/>
       <c r="C297" s="27" t="n"/>
+      <c r="D297">
+        <f>IF($B297="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B297,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B297,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E297">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D297,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35839,6 +36960,10 @@
     <row r="298">
       <c r="A298" s="37" t="n"/>
       <c r="C298" s="27" t="n"/>
+      <c r="D298">
+        <f>IF($B298="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B298,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B298,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E298">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D298,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35855,6 +36980,10 @@
     <row r="299">
       <c r="A299" s="37" t="n"/>
       <c r="C299" s="27" t="n"/>
+      <c r="D299">
+        <f>IF($B299="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B299,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B299,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E299">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D299,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35871,6 +37000,10 @@
     <row r="300">
       <c r="A300" s="37" t="n"/>
       <c r="C300" s="27" t="n"/>
+      <c r="D300">
+        <f>IF($B300="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B300,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B300,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E300">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D300,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35887,6 +37020,10 @@
     <row r="301">
       <c r="A301" s="37" t="n"/>
       <c r="C301" s="27" t="n"/>
+      <c r="D301">
+        <f>IF($B301="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B301,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B301,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E301">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D301,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35903,6 +37040,10 @@
     <row r="302">
       <c r="A302" s="37" t="n"/>
       <c r="C302" s="27" t="n"/>
+      <c r="D302">
+        <f>IF($B302="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B302,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B302,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E302">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D302,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35919,6 +37060,10 @@
     <row r="303">
       <c r="A303" s="37" t="n"/>
       <c r="C303" s="27" t="n"/>
+      <c r="D303">
+        <f>IF($B303="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B303,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B303,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E303">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D303,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35935,6 +37080,10 @@
     <row r="304">
       <c r="A304" s="37" t="n"/>
       <c r="C304" s="27" t="n"/>
+      <c r="D304">
+        <f>IF($B304="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B304,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B304,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E304">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D304,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35951,6 +37100,10 @@
     <row r="305">
       <c r="A305" s="37" t="n"/>
       <c r="C305" s="27" t="n"/>
+      <c r="D305">
+        <f>IF($B305="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B305,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B305,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E305">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D305,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35967,6 +37120,10 @@
     <row r="306">
       <c r="A306" s="37" t="n"/>
       <c r="C306" s="27" t="n"/>
+      <c r="D306">
+        <f>IF($B306="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B306,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B306,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E306">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D306,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35983,6 +37140,10 @@
     <row r="307">
       <c r="A307" s="37" t="n"/>
       <c r="C307" s="27" t="n"/>
+      <c r="D307">
+        <f>IF($B307="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B307,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B307,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E307">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D307,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -35999,6 +37160,10 @@
     <row r="308">
       <c r="A308" s="37" t="n"/>
       <c r="C308" s="27" t="n"/>
+      <c r="D308">
+        <f>IF($B308="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B308,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B308,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E308">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D308,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36015,6 +37180,10 @@
     <row r="309">
       <c r="A309" s="37" t="n"/>
       <c r="C309" s="27" t="n"/>
+      <c r="D309">
+        <f>IF($B309="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B309,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B309,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E309">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D309,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36031,6 +37200,10 @@
     <row r="310">
       <c r="A310" s="37" t="n"/>
       <c r="C310" s="27" t="n"/>
+      <c r="D310">
+        <f>IF($B310="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B310,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B310,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E310">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D310,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36047,6 +37220,10 @@
     <row r="311">
       <c r="A311" s="37" t="n"/>
       <c r="C311" s="27" t="n"/>
+      <c r="D311">
+        <f>IF($B311="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B311,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B311,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E311">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D311,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36063,6 +37240,10 @@
     <row r="312">
       <c r="A312" s="37" t="n"/>
       <c r="C312" s="27" t="n"/>
+      <c r="D312">
+        <f>IF($B312="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B312,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B312,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E312">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D312,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36079,6 +37260,10 @@
     <row r="313">
       <c r="A313" s="37" t="n"/>
       <c r="C313" s="27" t="n"/>
+      <c r="D313">
+        <f>IF($B313="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B313,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B313,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E313">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D313,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36095,6 +37280,10 @@
     <row r="314">
       <c r="A314" s="37" t="n"/>
       <c r="C314" s="27" t="n"/>
+      <c r="D314">
+        <f>IF($B314="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B314,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B314,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E314">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D314,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36111,6 +37300,10 @@
     <row r="315">
       <c r="A315" s="37" t="n"/>
       <c r="C315" s="27" t="n"/>
+      <c r="D315">
+        <f>IF($B315="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B315,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B315,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E315">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D315,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36127,6 +37320,10 @@
     <row r="316">
       <c r="A316" s="37" t="n"/>
       <c r="C316" s="27" t="n"/>
+      <c r="D316">
+        <f>IF($B316="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B316,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B316,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E316">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D316,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36143,6 +37340,10 @@
     <row r="317">
       <c r="A317" s="37" t="n"/>
       <c r="C317" s="27" t="n"/>
+      <c r="D317">
+        <f>IF($B317="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B317,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B317,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E317">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D317,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36159,6 +37360,10 @@
     <row r="318">
       <c r="A318" s="37" t="n"/>
       <c r="C318" s="27" t="n"/>
+      <c r="D318">
+        <f>IF($B318="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B318,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B318,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E318">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D318,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36175,6 +37380,10 @@
     <row r="319">
       <c r="A319" s="37" t="n"/>
       <c r="C319" s="27" t="n"/>
+      <c r="D319">
+        <f>IF($B319="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B319,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B319,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E319">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D319,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36191,6 +37400,10 @@
     <row r="320">
       <c r="A320" s="37" t="n"/>
       <c r="C320" s="27" t="n"/>
+      <c r="D320">
+        <f>IF($B320="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B320,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B320,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E320">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D320,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36207,6 +37420,10 @@
     <row r="321">
       <c r="A321" s="37" t="n"/>
       <c r="C321" s="27" t="n"/>
+      <c r="D321">
+        <f>IF($B321="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B321,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B321,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E321">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D321,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36223,6 +37440,10 @@
     <row r="322">
       <c r="A322" s="37" t="n"/>
       <c r="C322" s="27" t="n"/>
+      <c r="D322">
+        <f>IF($B322="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B322,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B322,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E322">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D322,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36239,6 +37460,10 @@
     <row r="323">
       <c r="A323" s="37" t="n"/>
       <c r="C323" s="27" t="n"/>
+      <c r="D323">
+        <f>IF($B323="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B323,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B323,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E323">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D323,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36255,6 +37480,10 @@
     <row r="324">
       <c r="A324" s="37" t="n"/>
       <c r="C324" s="27" t="n"/>
+      <c r="D324">
+        <f>IF($B324="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B324,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B324,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E324">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D324,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36271,6 +37500,10 @@
     <row r="325">
       <c r="A325" s="37" t="n"/>
       <c r="C325" s="27" t="n"/>
+      <c r="D325">
+        <f>IF($B325="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B325,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B325,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E325">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D325,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36287,6 +37520,10 @@
     <row r="326">
       <c r="A326" s="37" t="n"/>
       <c r="C326" s="27" t="n"/>
+      <c r="D326">
+        <f>IF($B326="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B326,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B326,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E326">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D326,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36303,6 +37540,10 @@
     <row r="327">
       <c r="A327" s="37" t="n"/>
       <c r="C327" s="27" t="n"/>
+      <c r="D327">
+        <f>IF($B327="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B327,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B327,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E327">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D327,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36319,6 +37560,10 @@
     <row r="328">
       <c r="A328" s="37" t="n"/>
       <c r="C328" s="27" t="n"/>
+      <c r="D328">
+        <f>IF($B328="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B328,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B328,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E328">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D328,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36335,6 +37580,10 @@
     <row r="329">
       <c r="A329" s="37" t="n"/>
       <c r="C329" s="27" t="n"/>
+      <c r="D329">
+        <f>IF($B329="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B329,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B329,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E329">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D329,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36351,6 +37600,10 @@
     <row r="330">
       <c r="A330" s="37" t="n"/>
       <c r="C330" s="27" t="n"/>
+      <c r="D330">
+        <f>IF($B330="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B330,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B330,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E330">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D330,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36367,6 +37620,10 @@
     <row r="331">
       <c r="A331" s="37" t="n"/>
       <c r="C331" s="27" t="n"/>
+      <c r="D331">
+        <f>IF($B331="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B331,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B331,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E331">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D331,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36383,6 +37640,10 @@
     <row r="332">
       <c r="A332" s="37" t="n"/>
       <c r="C332" s="27" t="n"/>
+      <c r="D332">
+        <f>IF($B332="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B332,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B332,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E332">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D332,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36399,6 +37660,10 @@
     <row r="333">
       <c r="A333" s="37" t="n"/>
       <c r="C333" s="27" t="n"/>
+      <c r="D333">
+        <f>IF($B333="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B333,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B333,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E333">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D333,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36415,6 +37680,10 @@
     <row r="334">
       <c r="A334" s="37" t="n"/>
       <c r="C334" s="27" t="n"/>
+      <c r="D334">
+        <f>IF($B334="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B334,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B334,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E334">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D334,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36431,6 +37700,10 @@
     <row r="335">
       <c r="A335" s="37" t="n"/>
       <c r="C335" s="27" t="n"/>
+      <c r="D335">
+        <f>IF($B335="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B335,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B335,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E335">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D335,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36447,6 +37720,10 @@
     <row r="336">
       <c r="A336" s="37" t="n"/>
       <c r="C336" s="27" t="n"/>
+      <c r="D336">
+        <f>IF($B336="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B336,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B336,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E336">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D336,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36463,6 +37740,10 @@
     <row r="337">
       <c r="A337" s="37" t="n"/>
       <c r="C337" s="27" t="n"/>
+      <c r="D337">
+        <f>IF($B337="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B337,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B337,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E337">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D337,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36479,6 +37760,10 @@
     <row r="338">
       <c r="A338" s="37" t="n"/>
       <c r="C338" s="27" t="n"/>
+      <c r="D338">
+        <f>IF($B338="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B338,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B338,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E338">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D338,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36495,6 +37780,10 @@
     <row r="339">
       <c r="A339" s="37" t="n"/>
       <c r="C339" s="27" t="n"/>
+      <c r="D339">
+        <f>IF($B339="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B339,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B339,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E339">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D339,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36511,6 +37800,10 @@
     <row r="340">
       <c r="A340" s="37" t="n"/>
       <c r="C340" s="27" t="n"/>
+      <c r="D340">
+        <f>IF($B340="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B340,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B340,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E340">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D340,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36527,6 +37820,10 @@
     <row r="341">
       <c r="A341" s="37" t="n"/>
       <c r="C341" s="27" t="n"/>
+      <c r="D341">
+        <f>IF($B341="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B341,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B341,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E341">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D341,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36543,6 +37840,10 @@
     <row r="342">
       <c r="A342" s="37" t="n"/>
       <c r="C342" s="27" t="n"/>
+      <c r="D342">
+        <f>IF($B342="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B342,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B342,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E342">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D342,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36559,6 +37860,10 @@
     <row r="343">
       <c r="A343" s="37" t="n"/>
       <c r="C343" s="27" t="n"/>
+      <c r="D343">
+        <f>IF($B343="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B343,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B343,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E343">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D343,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36575,6 +37880,10 @@
     <row r="344">
       <c r="A344" s="37" t="n"/>
       <c r="C344" s="27" t="n"/>
+      <c r="D344">
+        <f>IF($B344="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B344,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B344,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E344">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D344,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36591,6 +37900,10 @@
     <row r="345">
       <c r="A345" s="37" t="n"/>
       <c r="C345" s="27" t="n"/>
+      <c r="D345">
+        <f>IF($B345="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B345,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B345,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E345">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D345,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36607,6 +37920,10 @@
     <row r="346">
       <c r="A346" s="37" t="n"/>
       <c r="C346" s="27" t="n"/>
+      <c r="D346">
+        <f>IF($B346="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B346,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B346,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E346">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D346,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36623,6 +37940,10 @@
     <row r="347">
       <c r="A347" s="37" t="n"/>
       <c r="C347" s="27" t="n"/>
+      <c r="D347">
+        <f>IF($B347="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B347,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B347,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E347">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D347,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36639,6 +37960,10 @@
     <row r="348">
       <c r="A348" s="37" t="n"/>
       <c r="C348" s="27" t="n"/>
+      <c r="D348">
+        <f>IF($B348="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B348,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B348,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E348">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D348,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36655,6 +37980,10 @@
     <row r="349">
       <c r="A349" s="37" t="n"/>
       <c r="C349" s="27" t="n"/>
+      <c r="D349">
+        <f>IF($B349="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B349,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B349,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E349">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D349,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36671,6 +38000,10 @@
     <row r="350">
       <c r="A350" s="37" t="n"/>
       <c r="C350" s="27" t="n"/>
+      <c r="D350">
+        <f>IF($B350="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B350,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B350,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E350">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D350,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36687,6 +38020,10 @@
     <row r="351">
       <c r="A351" s="37" t="n"/>
       <c r="C351" s="27" t="n"/>
+      <c r="D351">
+        <f>IF($B351="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B351,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B351,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E351">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D351,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36703,6 +38040,10 @@
     <row r="352">
       <c r="A352" s="37" t="n"/>
       <c r="C352" s="27" t="n"/>
+      <c r="D352">
+        <f>IF($B352="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B352,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B352,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E352">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D352,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36719,6 +38060,10 @@
     <row r="353">
       <c r="A353" s="37" t="n"/>
       <c r="C353" s="27" t="n"/>
+      <c r="D353">
+        <f>IF($B353="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B353,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B353,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E353">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D353,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36735,6 +38080,10 @@
     <row r="354">
       <c r="A354" s="37" t="n"/>
       <c r="C354" s="27" t="n"/>
+      <c r="D354">
+        <f>IF($B354="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B354,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B354,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E354">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D354,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36751,6 +38100,10 @@
     <row r="355">
       <c r="A355" s="37" t="n"/>
       <c r="C355" s="27" t="n"/>
+      <c r="D355">
+        <f>IF($B355="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B355,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B355,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E355">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D355,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36767,6 +38120,10 @@
     <row r="356">
       <c r="A356" s="37" t="n"/>
       <c r="C356" s="27" t="n"/>
+      <c r="D356">
+        <f>IF($B356="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B356,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B356,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E356">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D356,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36783,6 +38140,10 @@
     <row r="357">
       <c r="A357" s="37" t="n"/>
       <c r="C357" s="27" t="n"/>
+      <c r="D357">
+        <f>IF($B357="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B357,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B357,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E357">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D357,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36799,6 +38160,10 @@
     <row r="358">
       <c r="A358" s="37" t="n"/>
       <c r="C358" s="27" t="n"/>
+      <c r="D358">
+        <f>IF($B358="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B358,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B358,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E358">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D358,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36815,6 +38180,10 @@
     <row r="359">
       <c r="A359" s="37" t="n"/>
       <c r="C359" s="27" t="n"/>
+      <c r="D359">
+        <f>IF($B359="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B359,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B359,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E359">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D359,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36831,6 +38200,10 @@
     <row r="360">
       <c r="A360" s="37" t="n"/>
       <c r="C360" s="27" t="n"/>
+      <c r="D360">
+        <f>IF($B360="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B360,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B360,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E360">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D360,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36847,6 +38220,10 @@
     <row r="361">
       <c r="A361" s="37" t="n"/>
       <c r="C361" s="27" t="n"/>
+      <c r="D361">
+        <f>IF($B361="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B361,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B361,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E361">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D361,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36863,6 +38240,10 @@
     <row r="362">
       <c r="A362" s="37" t="n"/>
       <c r="C362" s="27" t="n"/>
+      <c r="D362">
+        <f>IF($B362="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B362,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B362,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E362">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D362,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36879,6 +38260,10 @@
     <row r="363">
       <c r="A363" s="37" t="n"/>
       <c r="C363" s="27" t="n"/>
+      <c r="D363">
+        <f>IF($B363="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B363,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B363,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E363">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D363,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36895,6 +38280,10 @@
     <row r="364">
       <c r="A364" s="37" t="n"/>
       <c r="C364" s="27" t="n"/>
+      <c r="D364">
+        <f>IF($B364="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B364,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B364,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E364">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D364,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36911,6 +38300,10 @@
     <row r="365">
       <c r="A365" s="37" t="n"/>
       <c r="C365" s="27" t="n"/>
+      <c r="D365">
+        <f>IF($B365="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B365,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B365,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E365">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D365,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36927,6 +38320,10 @@
     <row r="366">
       <c r="A366" s="37" t="n"/>
       <c r="C366" s="27" t="n"/>
+      <c r="D366">
+        <f>IF($B366="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B366,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B366,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E366">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D366,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36943,6 +38340,10 @@
     <row r="367">
       <c r="A367" s="37" t="n"/>
       <c r="C367" s="27" t="n"/>
+      <c r="D367">
+        <f>IF($B367="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B367,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B367,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E367">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D367,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36959,6 +38360,10 @@
     <row r="368">
       <c r="A368" s="37" t="n"/>
       <c r="C368" s="27" t="n"/>
+      <c r="D368">
+        <f>IF($B368="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B368,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B368,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E368">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D368,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36975,6 +38380,10 @@
     <row r="369">
       <c r="A369" s="37" t="n"/>
       <c r="C369" s="27" t="n"/>
+      <c r="D369">
+        <f>IF($B369="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B369,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B369,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E369">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D369,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -36991,6 +38400,10 @@
     <row r="370">
       <c r="A370" s="37" t="n"/>
       <c r="C370" s="27" t="n"/>
+      <c r="D370">
+        <f>IF($B370="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B370,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B370,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E370">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D370,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37007,6 +38420,10 @@
     <row r="371">
       <c r="A371" s="37" t="n"/>
       <c r="C371" s="27" t="n"/>
+      <c r="D371">
+        <f>IF($B371="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B371,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B371,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E371">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D371,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37023,6 +38440,10 @@
     <row r="372">
       <c r="A372" s="37" t="n"/>
       <c r="C372" s="27" t="n"/>
+      <c r="D372">
+        <f>IF($B372="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B372,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B372,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E372">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D372,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37039,6 +38460,10 @@
     <row r="373">
       <c r="A373" s="37" t="n"/>
       <c r="C373" s="27" t="n"/>
+      <c r="D373">
+        <f>IF($B373="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B373,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B373,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E373">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D373,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37055,6 +38480,10 @@
     <row r="374">
       <c r="A374" s="37" t="n"/>
       <c r="C374" s="27" t="n"/>
+      <c r="D374">
+        <f>IF($B374="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B374,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B374,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E374">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D374,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37071,6 +38500,10 @@
     <row r="375">
       <c r="A375" s="37" t="n"/>
       <c r="C375" s="27" t="n"/>
+      <c r="D375">
+        <f>IF($B375="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B375,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B375,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E375">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D375,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37087,6 +38520,10 @@
     <row r="376">
       <c r="A376" s="37" t="n"/>
       <c r="C376" s="27" t="n"/>
+      <c r="D376">
+        <f>IF($B376="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B376,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B376,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E376">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D376,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37103,6 +38540,10 @@
     <row r="377">
       <c r="A377" s="37" t="n"/>
       <c r="C377" s="27" t="n"/>
+      <c r="D377">
+        <f>IF($B377="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B377,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B377,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E377">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D377,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37119,6 +38560,10 @@
     <row r="378">
       <c r="A378" s="37" t="n"/>
       <c r="C378" s="27" t="n"/>
+      <c r="D378">
+        <f>IF($B378="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B378,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B378,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E378">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D378,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37135,6 +38580,10 @@
     <row r="379">
       <c r="A379" s="37" t="n"/>
       <c r="C379" s="27" t="n"/>
+      <c r="D379">
+        <f>IF($B379="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B379,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B379,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E379">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D379,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37151,6 +38600,10 @@
     <row r="380">
       <c r="A380" s="37" t="n"/>
       <c r="C380" s="27" t="n"/>
+      <c r="D380">
+        <f>IF($B380="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B380,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B380,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E380">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D380,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37167,6 +38620,10 @@
     <row r="381">
       <c r="A381" s="37" t="n"/>
       <c r="C381" s="27" t="n"/>
+      <c r="D381">
+        <f>IF($B381="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B381,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B381,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E381">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D381,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37183,6 +38640,10 @@
     <row r="382">
       <c r="A382" s="37" t="n"/>
       <c r="C382" s="27" t="n"/>
+      <c r="D382">
+        <f>IF($B382="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B382,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B382,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E382">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D382,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37199,6 +38660,10 @@
     <row r="383">
       <c r="A383" s="37" t="n"/>
       <c r="C383" s="27" t="n"/>
+      <c r="D383">
+        <f>IF($B383="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B383,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B383,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E383">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D383,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37215,6 +38680,10 @@
     <row r="384">
       <c r="A384" s="37" t="n"/>
       <c r="C384" s="27" t="n"/>
+      <c r="D384">
+        <f>IF($B384="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B384,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B384,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E384">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D384,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37231,6 +38700,10 @@
     <row r="385">
       <c r="A385" s="37" t="n"/>
       <c r="C385" s="27" t="n"/>
+      <c r="D385">
+        <f>IF($B385="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B385,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B385,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E385">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D385,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37247,6 +38720,10 @@
     <row r="386">
       <c r="A386" s="37" t="n"/>
       <c r="C386" s="27" t="n"/>
+      <c r="D386">
+        <f>IF($B386="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B386,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B386,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E386">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D386,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37263,6 +38740,10 @@
     <row r="387">
       <c r="A387" s="37" t="n"/>
       <c r="C387" s="27" t="n"/>
+      <c r="D387">
+        <f>IF($B387="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B387,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B387,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E387">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D387,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37279,6 +38760,10 @@
     <row r="388">
       <c r="A388" s="37" t="n"/>
       <c r="C388" s="27" t="n"/>
+      <c r="D388">
+        <f>IF($B388="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B388,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B388,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E388">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D388,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37295,6 +38780,10 @@
     <row r="389">
       <c r="A389" s="37" t="n"/>
       <c r="C389" s="27" t="n"/>
+      <c r="D389">
+        <f>IF($B389="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B389,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B389,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E389">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D389,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37311,6 +38800,10 @@
     <row r="390">
       <c r="A390" s="37" t="n"/>
       <c r="C390" s="27" t="n"/>
+      <c r="D390">
+        <f>IF($B390="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B390,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B390,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E390">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D390,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37327,6 +38820,10 @@
     <row r="391">
       <c r="A391" s="37" t="n"/>
       <c r="C391" s="27" t="n"/>
+      <c r="D391">
+        <f>IF($B391="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B391,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B391,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E391">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D391,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37343,6 +38840,10 @@
     <row r="392">
       <c r="A392" s="37" t="n"/>
       <c r="C392" s="27" t="n"/>
+      <c r="D392">
+        <f>IF($B392="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B392,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B392,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E392">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D392,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37359,6 +38860,10 @@
     <row r="393">
       <c r="A393" s="37" t="n"/>
       <c r="C393" s="27" t="n"/>
+      <c r="D393">
+        <f>IF($B393="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B393,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B393,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E393">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D393,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37375,6 +38880,10 @@
     <row r="394">
       <c r="A394" s="37" t="n"/>
       <c r="C394" s="27" t="n"/>
+      <c r="D394">
+        <f>IF($B394="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B394,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B394,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E394">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D394,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37391,6 +38900,10 @@
     <row r="395">
       <c r="A395" s="37" t="n"/>
       <c r="C395" s="27" t="n"/>
+      <c r="D395">
+        <f>IF($B395="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B395,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B395,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E395">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D395,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37407,6 +38920,10 @@
     <row r="396">
       <c r="A396" s="37" t="n"/>
       <c r="C396" s="27" t="n"/>
+      <c r="D396">
+        <f>IF($B396="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B396,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B396,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E396">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D396,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37423,6 +38940,10 @@
     <row r="397">
       <c r="A397" s="37" t="n"/>
       <c r="C397" s="27" t="n"/>
+      <c r="D397">
+        <f>IF($B397="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B397,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B397,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E397">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D397,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37439,6 +38960,10 @@
     <row r="398">
       <c r="A398" s="37" t="n"/>
       <c r="C398" s="27" t="n"/>
+      <c r="D398">
+        <f>IF($B398="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B398,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B398,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E398">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D398,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37455,6 +38980,10 @@
     <row r="399">
       <c r="A399" s="37" t="n"/>
       <c r="C399" s="27" t="n"/>
+      <c r="D399">
+        <f>IF($B399="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B399,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B399,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E399">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D399,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37471,6 +39000,10 @@
     <row r="400">
       <c r="A400" s="37" t="n"/>
       <c r="C400" s="27" t="n"/>
+      <c r="D400">
+        <f>IF($B400="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B400,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B400,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E400">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D400,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37487,6 +39020,10 @@
     <row r="401">
       <c r="A401" s="37" t="n"/>
       <c r="C401" s="27" t="n"/>
+      <c r="D401">
+        <f>IF($B401="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B401,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B401,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E401">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D401,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37503,6 +39040,10 @@
     <row r="402">
       <c r="A402" s="37" t="n"/>
       <c r="C402" s="27" t="n"/>
+      <c r="D402">
+        <f>IF($B402="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B402,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B402,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E402">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D402,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37519,6 +39060,10 @@
     <row r="403">
       <c r="A403" s="37" t="n"/>
       <c r="C403" s="27" t="n"/>
+      <c r="D403">
+        <f>IF($B403="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B403,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B403,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E403">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D403,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37535,6 +39080,10 @@
     <row r="404">
       <c r="A404" s="37" t="n"/>
       <c r="C404" s="27" t="n"/>
+      <c r="D404">
+        <f>IF($B404="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B404,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B404,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E404">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D404,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37551,6 +39100,10 @@
     <row r="405">
       <c r="A405" s="37" t="n"/>
       <c r="C405" s="27" t="n"/>
+      <c r="D405">
+        <f>IF($B405="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B405,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B405,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E405">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D405,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37567,6 +39120,10 @@
     <row r="406">
       <c r="A406" s="37" t="n"/>
       <c r="C406" s="27" t="n"/>
+      <c r="D406">
+        <f>IF($B406="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B406,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B406,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E406">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D406,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37583,6 +39140,10 @@
     <row r="407">
       <c r="A407" s="37" t="n"/>
       <c r="C407" s="27" t="n"/>
+      <c r="D407">
+        <f>IF($B407="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B407,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B407,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E407">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D407,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37599,6 +39160,10 @@
     <row r="408">
       <c r="A408" s="37" t="n"/>
       <c r="C408" s="27" t="n"/>
+      <c r="D408">
+        <f>IF($B408="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B408,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B408,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E408">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D408,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37615,6 +39180,10 @@
     <row r="409">
       <c r="A409" s="37" t="n"/>
       <c r="C409" s="27" t="n"/>
+      <c r="D409">
+        <f>IF($B409="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B409,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B409,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E409">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D409,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37631,6 +39200,10 @@
     <row r="410">
       <c r="A410" s="37" t="n"/>
       <c r="C410" s="27" t="n"/>
+      <c r="D410">
+        <f>IF($B410="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B410,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B410,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E410">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D410,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37647,6 +39220,10 @@
     <row r="411">
       <c r="A411" s="37" t="n"/>
       <c r="C411" s="27" t="n"/>
+      <c r="D411">
+        <f>IF($B411="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B411,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B411,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E411">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D411,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37663,6 +39240,10 @@
     <row r="412">
       <c r="A412" s="37" t="n"/>
       <c r="C412" s="27" t="n"/>
+      <c r="D412">
+        <f>IF($B412="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B412,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B412,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E412">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D412,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37679,6 +39260,10 @@
     <row r="413">
       <c r="A413" s="37" t="n"/>
       <c r="C413" s="27" t="n"/>
+      <c r="D413">
+        <f>IF($B413="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B413,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B413,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E413">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D413,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37695,6 +39280,10 @@
     <row r="414">
       <c r="A414" s="37" t="n"/>
       <c r="C414" s="27" t="n"/>
+      <c r="D414">
+        <f>IF($B414="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B414,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B414,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E414">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D414,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37711,6 +39300,10 @@
     <row r="415">
       <c r="A415" s="37" t="n"/>
       <c r="C415" s="27" t="n"/>
+      <c r="D415">
+        <f>IF($B415="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B415,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B415,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E415">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D415,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37727,6 +39320,10 @@
     <row r="416">
       <c r="A416" s="37" t="n"/>
       <c r="C416" s="27" t="n"/>
+      <c r="D416">
+        <f>IF($B416="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B416,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B416,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E416">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D416,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37743,6 +39340,10 @@
     <row r="417">
       <c r="A417" s="37" t="n"/>
       <c r="C417" s="27" t="n"/>
+      <c r="D417">
+        <f>IF($B417="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B417,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B417,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E417">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D417,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37759,6 +39360,10 @@
     <row r="418">
       <c r="A418" s="37" t="n"/>
       <c r="C418" s="27" t="n"/>
+      <c r="D418">
+        <f>IF($B418="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B418,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B418,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E418">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D418,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37775,6 +39380,10 @@
     <row r="419">
       <c r="A419" s="37" t="n"/>
       <c r="C419" s="27" t="n"/>
+      <c r="D419">
+        <f>IF($B419="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B419,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B419,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E419">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D419,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37791,6 +39400,10 @@
     <row r="420">
       <c r="A420" s="37" t="n"/>
       <c r="C420" s="27" t="n"/>
+      <c r="D420">
+        <f>IF($B420="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B420,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B420,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E420">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D420,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37807,6 +39420,10 @@
     <row r="421">
       <c r="A421" s="37" t="n"/>
       <c r="C421" s="27" t="n"/>
+      <c r="D421">
+        <f>IF($B421="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B421,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B421,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E421">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D421,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37823,6 +39440,10 @@
     <row r="422">
       <c r="A422" s="37" t="n"/>
       <c r="C422" s="27" t="n"/>
+      <c r="D422">
+        <f>IF($B422="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B422,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B422,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E422">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D422,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37839,6 +39460,10 @@
     <row r="423">
       <c r="A423" s="37" t="n"/>
       <c r="C423" s="27" t="n"/>
+      <c r="D423">
+        <f>IF($B423="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B423,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B423,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E423">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D423,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37855,6 +39480,10 @@
     <row r="424">
       <c r="A424" s="37" t="n"/>
       <c r="C424" s="27" t="n"/>
+      <c r="D424">
+        <f>IF($B424="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B424,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B424,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E424">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D424,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37871,6 +39500,10 @@
     <row r="425">
       <c r="A425" s="37" t="n"/>
       <c r="C425" s="27" t="n"/>
+      <c r="D425">
+        <f>IF($B425="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B425,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B425,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E425">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D425,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37887,6 +39520,10 @@
     <row r="426">
       <c r="A426" s="37" t="n"/>
       <c r="C426" s="27" t="n"/>
+      <c r="D426">
+        <f>IF($B426="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B426,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B426,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E426">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D426,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37903,6 +39540,10 @@
     <row r="427">
       <c r="A427" s="37" t="n"/>
       <c r="C427" s="27" t="n"/>
+      <c r="D427">
+        <f>IF($B427="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B427,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B427,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E427">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D427,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37919,6 +39560,10 @@
     <row r="428">
       <c r="A428" s="37" t="n"/>
       <c r="C428" s="27" t="n"/>
+      <c r="D428">
+        <f>IF($B428="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B428,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B428,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E428">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D428,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37935,6 +39580,10 @@
     <row r="429">
       <c r="A429" s="37" t="n"/>
       <c r="C429" s="27" t="n"/>
+      <c r="D429">
+        <f>IF($B429="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B429,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B429,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E429">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D429,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37951,6 +39600,10 @@
     <row r="430">
       <c r="A430" s="37" t="n"/>
       <c r="C430" s="27" t="n"/>
+      <c r="D430">
+        <f>IF($B430="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B430,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B430,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E430">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D430,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37967,6 +39620,10 @@
     <row r="431">
       <c r="A431" s="37" t="n"/>
       <c r="C431" s="27" t="n"/>
+      <c r="D431">
+        <f>IF($B431="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B431,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B431,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E431">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D431,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37983,6 +39640,10 @@
     <row r="432">
       <c r="A432" s="37" t="n"/>
       <c r="C432" s="27" t="n"/>
+      <c r="D432">
+        <f>IF($B432="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B432,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B432,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E432">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D432,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -37999,6 +39660,10 @@
     <row r="433">
       <c r="A433" s="37" t="n"/>
       <c r="C433" s="27" t="n"/>
+      <c r="D433">
+        <f>IF($B433="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B433,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B433,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E433">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D433,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38015,6 +39680,10 @@
     <row r="434">
       <c r="A434" s="37" t="n"/>
       <c r="C434" s="27" t="n"/>
+      <c r="D434">
+        <f>IF($B434="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B434,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B434,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E434">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D434,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38031,6 +39700,10 @@
     <row r="435">
       <c r="A435" s="37" t="n"/>
       <c r="C435" s="27" t="n"/>
+      <c r="D435">
+        <f>IF($B435="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B435,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B435,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E435">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D435,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38047,6 +39720,10 @@
     <row r="436">
       <c r="A436" s="37" t="n"/>
       <c r="C436" s="27" t="n"/>
+      <c r="D436">
+        <f>IF($B436="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B436,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B436,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E436">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D436,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38063,6 +39740,10 @@
     <row r="437">
       <c r="A437" s="37" t="n"/>
       <c r="C437" s="27" t="n"/>
+      <c r="D437">
+        <f>IF($B437="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B437,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B437,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E437">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D437,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38079,6 +39760,10 @@
     <row r="438">
       <c r="A438" s="37" t="n"/>
       <c r="C438" s="27" t="n"/>
+      <c r="D438">
+        <f>IF($B438="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B438,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B438,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E438">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D438,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38095,6 +39780,10 @@
     <row r="439">
       <c r="A439" s="37" t="n"/>
       <c r="C439" s="27" t="n"/>
+      <c r="D439">
+        <f>IF($B439="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B439,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B439,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E439">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D439,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38111,6 +39800,10 @@
     <row r="440">
       <c r="A440" s="37" t="n"/>
       <c r="C440" s="27" t="n"/>
+      <c r="D440">
+        <f>IF($B440="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B440,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B440,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E440">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D440,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38127,6 +39820,10 @@
     <row r="441">
       <c r="A441" s="37" t="n"/>
       <c r="C441" s="27" t="n"/>
+      <c r="D441">
+        <f>IF($B441="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B441,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B441,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E441">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D441,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38143,6 +39840,10 @@
     <row r="442">
       <c r="A442" s="37" t="n"/>
       <c r="C442" s="27" t="n"/>
+      <c r="D442">
+        <f>IF($B442="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B442,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B442,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E442">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D442,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38159,6 +39860,10 @@
     <row r="443">
       <c r="A443" s="37" t="n"/>
       <c r="C443" s="27" t="n"/>
+      <c r="D443">
+        <f>IF($B443="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B443,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B443,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E443">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D443,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38175,6 +39880,10 @@
     <row r="444">
       <c r="A444" s="37" t="n"/>
       <c r="C444" s="27" t="n"/>
+      <c r="D444">
+        <f>IF($B444="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B444,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B444,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E444">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D444,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38191,6 +39900,10 @@
     <row r="445">
       <c r="A445" s="37" t="n"/>
       <c r="C445" s="27" t="n"/>
+      <c r="D445">
+        <f>IF($B445="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B445,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B445,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E445">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D445,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38207,6 +39920,10 @@
     <row r="446">
       <c r="A446" s="37" t="n"/>
       <c r="C446" s="27" t="n"/>
+      <c r="D446">
+        <f>IF($B446="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B446,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B446,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E446">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D446,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38223,6 +39940,10 @@
     <row r="447">
       <c r="A447" s="37" t="n"/>
       <c r="C447" s="27" t="n"/>
+      <c r="D447">
+        <f>IF($B447="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B447,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B447,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E447">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D447,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38239,6 +39960,10 @@
     <row r="448">
       <c r="A448" s="37" t="n"/>
       <c r="C448" s="27" t="n"/>
+      <c r="D448">
+        <f>IF($B448="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B448,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B448,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E448">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D448,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38255,6 +39980,10 @@
     <row r="449">
       <c r="A449" s="37" t="n"/>
       <c r="C449" s="27" t="n"/>
+      <c r="D449">
+        <f>IF($B449="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B449,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B449,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E449">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D449,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38271,6 +40000,10 @@
     <row r="450">
       <c r="A450" s="37" t="n"/>
       <c r="C450" s="27" t="n"/>
+      <c r="D450">
+        <f>IF($B450="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B450,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B450,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E450">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D450,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38287,6 +40020,10 @@
     <row r="451">
       <c r="A451" s="37" t="n"/>
       <c r="C451" s="27" t="n"/>
+      <c r="D451">
+        <f>IF($B451="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B451,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B451,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E451">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D451,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38303,6 +40040,10 @@
     <row r="452">
       <c r="A452" s="37" t="n"/>
       <c r="C452" s="27" t="n"/>
+      <c r="D452">
+        <f>IF($B452="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B452,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B452,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E452">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D452,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38319,6 +40060,10 @@
     <row r="453">
       <c r="A453" s="37" t="n"/>
       <c r="C453" s="27" t="n"/>
+      <c r="D453">
+        <f>IF($B453="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B453,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B453,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E453">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D453,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38335,6 +40080,10 @@
     <row r="454">
       <c r="A454" s="37" t="n"/>
       <c r="C454" s="27" t="n"/>
+      <c r="D454">
+        <f>IF($B454="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B454,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B454,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E454">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D454,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38351,6 +40100,10 @@
     <row r="455">
       <c r="A455" s="37" t="n"/>
       <c r="C455" s="27" t="n"/>
+      <c r="D455">
+        <f>IF($B455="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B455,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B455,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E455">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D455,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38367,6 +40120,10 @@
     <row r="456">
       <c r="A456" s="37" t="n"/>
       <c r="C456" s="27" t="n"/>
+      <c r="D456">
+        <f>IF($B456="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B456,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B456,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E456">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D456,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38383,6 +40140,10 @@
     <row r="457">
       <c r="A457" s="37" t="n"/>
       <c r="C457" s="27" t="n"/>
+      <c r="D457">
+        <f>IF($B457="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B457,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B457,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E457">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D457,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38399,6 +40160,10 @@
     <row r="458">
       <c r="A458" s="37" t="n"/>
       <c r="C458" s="27" t="n"/>
+      <c r="D458">
+        <f>IF($B458="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B458,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B458,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E458">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D458,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38415,6 +40180,10 @@
     <row r="459">
       <c r="A459" s="37" t="n"/>
       <c r="C459" s="27" t="n"/>
+      <c r="D459">
+        <f>IF($B459="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B459,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B459,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E459">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D459,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38431,6 +40200,10 @@
     <row r="460">
       <c r="A460" s="37" t="n"/>
       <c r="C460" s="27" t="n"/>
+      <c r="D460">
+        <f>IF($B460="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B460,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B460,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E460">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D460,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38447,6 +40220,10 @@
     <row r="461">
       <c r="A461" s="37" t="n"/>
       <c r="C461" s="27" t="n"/>
+      <c r="D461">
+        <f>IF($B461="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B461,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B461,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E461">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D461,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38463,6 +40240,10 @@
     <row r="462">
       <c r="A462" s="37" t="n"/>
       <c r="C462" s="27" t="n"/>
+      <c r="D462">
+        <f>IF($B462="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B462,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B462,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E462">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D462,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38479,6 +40260,10 @@
     <row r="463">
       <c r="A463" s="37" t="n"/>
       <c r="C463" s="27" t="n"/>
+      <c r="D463">
+        <f>IF($B463="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B463,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B463,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E463">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D463,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38495,6 +40280,10 @@
     <row r="464">
       <c r="A464" s="37" t="n"/>
       <c r="C464" s="27" t="n"/>
+      <c r="D464">
+        <f>IF($B464="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B464,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B464,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E464">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D464,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38511,6 +40300,10 @@
     <row r="465">
       <c r="A465" s="37" t="n"/>
       <c r="C465" s="27" t="n"/>
+      <c r="D465">
+        <f>IF($B465="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B465,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B465,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E465">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D465,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38527,6 +40320,10 @@
     <row r="466">
       <c r="A466" s="37" t="n"/>
       <c r="C466" s="27" t="n"/>
+      <c r="D466">
+        <f>IF($B466="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B466,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B466,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E466">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D466,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38543,6 +40340,10 @@
     <row r="467">
       <c r="A467" s="37" t="n"/>
       <c r="C467" s="27" t="n"/>
+      <c r="D467">
+        <f>IF($B467="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B467,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B467,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E467">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D467,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38559,6 +40360,10 @@
     <row r="468">
       <c r="A468" s="37" t="n"/>
       <c r="C468" s="27" t="n"/>
+      <c r="D468">
+        <f>IF($B468="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B468,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B468,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E468">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D468,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38575,6 +40380,10 @@
     <row r="469">
       <c r="A469" s="37" t="n"/>
       <c r="C469" s="27" t="n"/>
+      <c r="D469">
+        <f>IF($B469="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B469,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B469,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E469">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D469,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38591,6 +40400,10 @@
     <row r="470">
       <c r="A470" s="37" t="n"/>
       <c r="C470" s="27" t="n"/>
+      <c r="D470">
+        <f>IF($B470="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B470,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B470,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E470">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D470,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38607,6 +40420,10 @@
     <row r="471">
       <c r="A471" s="37" t="n"/>
       <c r="C471" s="27" t="n"/>
+      <c r="D471">
+        <f>IF($B471="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B471,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B471,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E471">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D471,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38623,6 +40440,10 @@
     <row r="472">
       <c r="A472" s="37" t="n"/>
       <c r="C472" s="27" t="n"/>
+      <c r="D472">
+        <f>IF($B472="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B472,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B472,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E472">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D472,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38639,6 +40460,10 @@
     <row r="473">
       <c r="A473" s="37" t="n"/>
       <c r="C473" s="27" t="n"/>
+      <c r="D473">
+        <f>IF($B473="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B473,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B473,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E473">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D473,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38655,6 +40480,10 @@
     <row r="474">
       <c r="A474" s="37" t="n"/>
       <c r="C474" s="27" t="n"/>
+      <c r="D474">
+        <f>IF($B474="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B474,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B474,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E474">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D474,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38671,6 +40500,10 @@
     <row r="475">
       <c r="A475" s="37" t="n"/>
       <c r="C475" s="27" t="n"/>
+      <c r="D475">
+        <f>IF($B475="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B475,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B475,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E475">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D475,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38687,6 +40520,10 @@
     <row r="476">
       <c r="A476" s="37" t="n"/>
       <c r="C476" s="27" t="n"/>
+      <c r="D476">
+        <f>IF($B476="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B476,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B476,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E476">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D476,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38703,6 +40540,10 @@
     <row r="477">
       <c r="A477" s="37" t="n"/>
       <c r="C477" s="27" t="n"/>
+      <c r="D477">
+        <f>IF($B477="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B477,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B477,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E477">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D477,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38719,6 +40560,10 @@
     <row r="478">
       <c r="A478" s="37" t="n"/>
       <c r="C478" s="27" t="n"/>
+      <c r="D478">
+        <f>IF($B478="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B478,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B478,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E478">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D478,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38735,6 +40580,10 @@
     <row r="479">
       <c r="A479" s="37" t="n"/>
       <c r="C479" s="27" t="n"/>
+      <c r="D479">
+        <f>IF($B479="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B479,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B479,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E479">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D479,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38751,6 +40600,10 @@
     <row r="480">
       <c r="A480" s="37" t="n"/>
       <c r="C480" s="27" t="n"/>
+      <c r="D480">
+        <f>IF($B480="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B480,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B480,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E480">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D480,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38767,6 +40620,10 @@
     <row r="481">
       <c r="A481" s="37" t="n"/>
       <c r="C481" s="27" t="n"/>
+      <c r="D481">
+        <f>IF($B481="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B481,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B481,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E481">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D481,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38783,6 +40640,10 @@
     <row r="482">
       <c r="A482" s="37" t="n"/>
       <c r="C482" s="27" t="n"/>
+      <c r="D482">
+        <f>IF($B482="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B482,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B482,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E482">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D482,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38799,6 +40660,10 @@
     <row r="483">
       <c r="A483" s="37" t="n"/>
       <c r="C483" s="27" t="n"/>
+      <c r="D483">
+        <f>IF($B483="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B483,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B483,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E483">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D483,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38815,6 +40680,10 @@
     <row r="484">
       <c r="A484" s="37" t="n"/>
       <c r="C484" s="27" t="n"/>
+      <c r="D484">
+        <f>IF($B484="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B484,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B484,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E484">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D484,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38831,6 +40700,10 @@
     <row r="485">
       <c r="A485" s="37" t="n"/>
       <c r="C485" s="27" t="n"/>
+      <c r="D485">
+        <f>IF($B485="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B485,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B485,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E485">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D485,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38847,6 +40720,10 @@
     <row r="486">
       <c r="A486" s="37" t="n"/>
       <c r="C486" s="27" t="n"/>
+      <c r="D486">
+        <f>IF($B486="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B486,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B486,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E486">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D486,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38863,6 +40740,10 @@
     <row r="487">
       <c r="A487" s="37" t="n"/>
       <c r="C487" s="27" t="n"/>
+      <c r="D487">
+        <f>IF($B487="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B487,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B487,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E487">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D487,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38879,6 +40760,10 @@
     <row r="488">
       <c r="A488" s="37" t="n"/>
       <c r="C488" s="27" t="n"/>
+      <c r="D488">
+        <f>IF($B488="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B488,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B488,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E488">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D488,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38895,6 +40780,10 @@
     <row r="489">
       <c r="A489" s="37" t="n"/>
       <c r="C489" s="27" t="n"/>
+      <c r="D489">
+        <f>IF($B489="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B489,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B489,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E489">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D489,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38911,6 +40800,10 @@
     <row r="490">
       <c r="A490" s="37" t="n"/>
       <c r="C490" s="27" t="n"/>
+      <c r="D490">
+        <f>IF($B490="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B490,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B490,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E490">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D490,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38927,6 +40820,10 @@
     <row r="491">
       <c r="A491" s="37" t="n"/>
       <c r="C491" s="27" t="n"/>
+      <c r="D491">
+        <f>IF($B491="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B491,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B491,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E491">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D491,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38943,6 +40840,10 @@
     <row r="492">
       <c r="A492" s="37" t="n"/>
       <c r="C492" s="27" t="n"/>
+      <c r="D492">
+        <f>IF($B492="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B492,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B492,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E492">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D492,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38959,6 +40860,10 @@
     <row r="493">
       <c r="A493" s="37" t="n"/>
       <c r="C493" s="27" t="n"/>
+      <c r="D493">
+        <f>IF($B493="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B493,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B493,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E493">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D493,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38975,6 +40880,10 @@
     <row r="494">
       <c r="A494" s="37" t="n"/>
       <c r="C494" s="27" t="n"/>
+      <c r="D494">
+        <f>IF($B494="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B494,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B494,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E494">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D494,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -38991,6 +40900,10 @@
     <row r="495">
       <c r="A495" s="37" t="n"/>
       <c r="C495" s="27" t="n"/>
+      <c r="D495">
+        <f>IF($B495="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B495,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B495,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E495">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D495,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -39007,6 +40920,10 @@
     <row r="496">
       <c r="A496" s="37" t="n"/>
       <c r="C496" s="27" t="n"/>
+      <c r="D496">
+        <f>IF($B496="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B496,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B496,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E496">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D496,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -39023,6 +40940,10 @@
     <row r="497">
       <c r="A497" s="37" t="n"/>
       <c r="C497" s="27" t="n"/>
+      <c r="D497">
+        <f>IF($B497="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B497,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B497,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E497">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D497,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -39039,6 +40960,10 @@
     <row r="498">
       <c r="A498" s="37" t="n"/>
       <c r="C498" s="27" t="n"/>
+      <c r="D498">
+        <f>IF($B498="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B498,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B498,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E498">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D498,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -39055,6 +40980,10 @@
     <row r="499">
       <c r="A499" s="37" t="n"/>
       <c r="C499" s="27" t="n"/>
+      <c r="D499">
+        <f>IF($B499="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B499,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B499,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E499">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D499,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -39071,6 +41000,10 @@
     <row r="500">
       <c r="A500" s="37" t="n"/>
       <c r="C500" s="27" t="n"/>
+      <c r="D500">
+        <f>IF($B500="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B500,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B500,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E500">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D500,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -39087,6 +41020,10 @@
     <row r="501">
       <c r="A501" s="37" t="n"/>
       <c r="C501" s="27" t="n"/>
+      <c r="D501">
+        <f>IF($B501="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B501,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B501,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E501">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D501,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -39103,6 +41040,10 @@
     <row r="502">
       <c r="A502" s="37" t="n"/>
       <c r="C502" s="27" t="n"/>
+      <c r="D502">
+        <f>IF($B502="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B502,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B502,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E502">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D502,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -39119,6 +41060,10 @@
     <row r="503">
       <c r="A503" s="37" t="n"/>
       <c r="C503" s="27" t="n"/>
+      <c r="D503">
+        <f>IF($B503="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B503,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B503,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E503">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D503,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -39135,6 +41080,10 @@
     <row r="504">
       <c r="A504" s="37" t="n"/>
       <c r="C504" s="27" t="n"/>
+      <c r="D504">
+        <f>IF($B504="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B504,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B504,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E504">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D504,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -39151,6 +41100,10 @@
     <row r="505">
       <c r="A505" s="37" t="n"/>
       <c r="C505" s="27" t="n"/>
+      <c r="D505">
+        <f>IF($B505="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B505,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B505,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E505">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D505,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -39167,6 +41120,10 @@
     <row r="506">
       <c r="A506" s="37" t="n"/>
       <c r="C506" s="27" t="n"/>
+      <c r="D506">
+        <f>IF($B506="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B506,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B506,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E506">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D506,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -39183,6 +41140,10 @@
     <row r="507">
       <c r="A507" s="37" t="n"/>
       <c r="C507" s="27" t="n"/>
+      <c r="D507">
+        <f>IF($B507="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B507,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B507,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E507">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D507,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -39199,6 +41160,10 @@
     <row r="508">
       <c r="A508" s="37" t="n"/>
       <c r="C508" s="27" t="n"/>
+      <c r="D508">
+        <f>IF($B508="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B508,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B508,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E508">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D508,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -39215,6 +41180,10 @@
     <row r="509">
       <c r="A509" s="37" t="n"/>
       <c r="C509" s="27" t="n"/>
+      <c r="D509">
+        <f>IF($B509="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B509,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B509,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E509">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D509,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -39231,6 +41200,10 @@
     <row r="510">
       <c r="A510" s="37" t="n"/>
       <c r="C510" s="27" t="n"/>
+      <c r="D510">
+        <f>IF($B510="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B510,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B510,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E510">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D510,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -39247,6 +41220,10 @@
     <row r="511">
       <c r="A511" s="37" t="n"/>
       <c r="C511" s="27" t="n"/>
+      <c r="D511">
+        <f>IF($B511="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B511,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B511,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E511">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D511,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -39263,6 +41240,10 @@
     <row r="512">
       <c r="A512" s="37" t="n"/>
       <c r="C512" s="27" t="n"/>
+      <c r="D512">
+        <f>IF($B512="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B512,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B512,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E512">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D512,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -39279,6 +41260,10 @@
     <row r="513">
       <c r="A513" s="37" t="n"/>
       <c r="C513" s="27" t="n"/>
+      <c r="D513">
+        <f>IF($B513="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B513,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B513,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E513">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D513,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -39295,6 +41280,10 @@
     <row r="514">
       <c r="A514" s="37" t="n"/>
       <c r="C514" s="27" t="n"/>
+      <c r="D514">
+        <f>IF($B514="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B514,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B514,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
       <c r="E514">
         <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D514,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
         <v/>
@@ -39308,20 +41297,41 @@
         <v/>
       </c>
     </row>
+    <row r="515">
+      <c r="A515" s="37" t="n"/>
+      <c r="C515" s="27" t="n"/>
+      <c r="D515">
+        <f>IF($B515="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B515,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B515,Fact_Income[Description],0)),"")))</f>
+        <v/>
+      </c>
+      <c r="E515">
+        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D515,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <v/>
+      </c>
+      <c r="H515">
+        <f>IF($C515="","",IF(SignConvention="Negative = Expense",IF($C515&lt;0,"Expense","Income"),IF($C515&gt;0,"Expense","Income")))</f>
+        <v/>
+      </c>
+      <c r="I515" s="27">
+        <f>IF($C515="","",ABS($C515))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A6:K6"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="A9:K9"/>
-    <mergeCell ref="A11:C11"/>
     <mergeCell ref="A7:K7"/>
-    <mergeCell ref="E11:K11"/>
-    <mergeCell ref="A13:K13"/>
+    <mergeCell ref="E12:K12"/>
+    <mergeCell ref="A10:K10"/>
+    <mergeCell ref="A14:K14"/>
+    <mergeCell ref="A12:C12"/>
     <mergeCell ref="A5:K5"/>
     <mergeCell ref="A1:K2"/>
     <mergeCell ref="A8:K8"/>
   </mergeCells>
-  <conditionalFormatting sqref="H15:H514">
+  <conditionalFormatting sqref="H16:H515">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="3">
       <formula>"Expense"</formula>
     </cfRule>
@@ -39329,29 +41339,29 @@
       <formula>"Income"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D15:D514">
+  <conditionalFormatting sqref="D16:D515">
     <cfRule type="expression" priority="3" dxfId="5">
-      <formula>AND($C15&lt;&gt;"",$D15="")</formula>
+      <formula>AND($C16&lt;&gt;"",$D16="")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
-    <dataValidation sqref="D11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="D12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Negative = Expense,Positive = Expense"</formula1>
     </dataValidation>
-    <dataValidation sqref="D15:D514" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Please choose a value from the dropdown list." type="list">
-      <formula1>=VendorNameList</formula1>
+    <dataValidation sqref="D16:D515" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Please choose a value from the dropdown list." type="list">
+      <formula1>VendorNameList</formula1>
     </dataValidation>
-    <dataValidation sqref="E15:E514" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Please choose a value from the dropdown list." type="list">
-      <formula1>=ExpenseCategoryList</formula1>
+    <dataValidation sqref="E16:E515" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Please choose a value from the dropdown list." type="list">
+      <formula1>ExpenseCategoryList</formula1>
     </dataValidation>
-    <dataValidation sqref="F15:F514" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Please choose a value from the dropdown list." type="list">
-      <formula1>=AccountNameList</formula1>
+    <dataValidation sqref="F16:F515" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Please choose a value from the dropdown list." type="list">
+      <formula1>AccountNameList</formula1>
     </dataValidation>
-    <dataValidation sqref="G15:G514" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Please choose a value from the dropdown list." type="list">
-      <formula1>=PaymentMethodList</formula1>
+    <dataValidation sqref="G16:G515" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Please choose a value from the dropdown list." type="list">
+      <formula1>PaymentMethodList</formula1>
     </dataValidation>
-    <dataValidation sqref="J15:J514" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Please choose a value from the dropdown list." type="list">
-      <formula1>=List_NeedWant</formula1>
+    <dataValidation sqref="J16:J515" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Please choose a value from the dropdown list." type="list">
+      <formula1>List_NeedWant</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -39368,7 +41378,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:N37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -39384,6 +41394,7 @@
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
     <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -39401,6 +41412,10 @@
       <c r="H1" s="2" t="n"/>
       <c r="I1" s="2" t="n"/>
       <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="2" t="n"/>
+      <c r="N1" s="2" t="n"/>
     </row>
     <row r="2" ht="10" customHeight="1">
       <c r="A2" s="2" t="n"/>
@@ -39413,6 +41428,10 @@
       <c r="H2" s="2" t="n"/>
       <c r="I2" s="2" t="n"/>
       <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="26" t="inlineStr">
@@ -39472,6 +41491,7 @@
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="n"/>
       <c r="M10" s="2" t="n"/>
+      <c r="N10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="36" t="inlineStr">
@@ -39537,6 +41557,11 @@
       <c r="M11" s="36" t="inlineStr">
         <is>
           <t>Notes</t>
+        </is>
+      </c>
+      <c r="N11" s="36" t="inlineStr">
+        <is>
+          <t>Description</t>
         </is>
       </c>
     </row>
@@ -39595,6 +41620,7 @@
           <t>Semi-monthly payroll</t>
         </is>
       </c>
+      <c r="N12" s="38" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="38">
@@ -39651,6 +41677,7 @@
           <t>Semi-monthly payroll</t>
         </is>
       </c>
+      <c r="N13" s="38" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="38">
@@ -39707,6 +41734,7 @@
           <t>Semi-monthly payroll</t>
         </is>
       </c>
+      <c r="N14" s="38" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="38">
@@ -39763,6 +41791,7 @@
           <t>Semi-monthly payroll</t>
         </is>
       </c>
+      <c r="N15" s="38" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="38">
@@ -39819,6 +41848,7 @@
           <t>Semi-monthly payroll</t>
         </is>
       </c>
+      <c r="N16" s="38" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="38">
@@ -39875,6 +41905,7 @@
           <t>Semi-monthly payroll</t>
         </is>
       </c>
+      <c r="N17" s="38" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="38">
@@ -39931,6 +41962,7 @@
           <t>Semi-monthly payroll</t>
         </is>
       </c>
+      <c r="N18" s="38" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="38">
@@ -39987,6 +42019,7 @@
           <t>Semi-monthly payroll</t>
         </is>
       </c>
+      <c r="N19" s="38" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="38">
@@ -40043,6 +42076,7 @@
           <t>Semi-monthly payroll</t>
         </is>
       </c>
+      <c r="N20" s="38" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="38">
@@ -40099,6 +42133,7 @@
           <t>Semi-monthly payroll</t>
         </is>
       </c>
+      <c r="N21" s="38" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="38">
@@ -40155,6 +42190,7 @@
           <t>Semi-monthly payroll</t>
         </is>
       </c>
+      <c r="N22" s="38" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="38">
@@ -40211,6 +42247,7 @@
           <t>Semi-monthly payroll</t>
         </is>
       </c>
+      <c r="N23" s="38" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="38">
@@ -40267,6 +42304,7 @@
           <t>Semi-monthly payroll</t>
         </is>
       </c>
+      <c r="N24" s="38" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="38">
@@ -40323,6 +42361,7 @@
           <t>Semi-monthly payroll</t>
         </is>
       </c>
+      <c r="N25" s="38" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="38">
@@ -40379,6 +42418,7 @@
           <t>Semi-monthly payroll</t>
         </is>
       </c>
+      <c r="N26" s="38" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="38">
@@ -40435,6 +42475,7 @@
           <t>Semi-monthly payroll</t>
         </is>
       </c>
+      <c r="N27" s="38" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="38">
@@ -40491,6 +42532,7 @@
           <t>Semi-monthly payroll</t>
         </is>
       </c>
+      <c r="N28" s="38" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="38">
@@ -40547,6 +42589,7 @@
           <t>Semi-monthly payroll</t>
         </is>
       </c>
+      <c r="N29" s="38" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="38">
@@ -40603,6 +42646,7 @@
           <t>Semi-monthly payroll</t>
         </is>
       </c>
+      <c r="N30" s="38" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="38">
@@ -40659,6 +42703,7 @@
           <t>Semi-monthly payroll</t>
         </is>
       </c>
+      <c r="N31" s="38" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="38">
@@ -40715,6 +42760,7 @@
           <t>Semi-monthly payroll</t>
         </is>
       </c>
+      <c r="N32" s="38" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="38">
@@ -40771,6 +42817,7 @@
           <t>Semi-monthly payroll</t>
         </is>
       </c>
+      <c r="N33" s="38" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="38">
@@ -40827,6 +42874,7 @@
           <t>Semi-monthly payroll</t>
         </is>
       </c>
+      <c r="N34" s="38" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="38">
@@ -40883,6 +42931,7 @@
           <t>Semi-monthly payroll</t>
         </is>
       </c>
+      <c r="N35" s="38" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="38">
@@ -40939,6 +42988,7 @@
           <t>Semi-monthly payroll</t>
         </is>
       </c>
+      <c r="N36" s="38" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="38">
@@ -40995,25 +43045,26 @@
           <t>Semi-monthly payroll</t>
         </is>
       </c>
+      <c r="N37" s="38" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A1:J2"/>
-    <mergeCell ref="A10:M10"/>
+    <mergeCell ref="A1:N2"/>
+    <mergeCell ref="A10:N10"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation sqref="C12:C337" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Please choose a value from the dropdown list." type="list">
-      <formula1>=SourceNameList</formula1>
+      <formula1>SourceNameList</formula1>
     </dataValidation>
     <dataValidation sqref="E12:E337" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Please choose a value from the dropdown list." type="list">
-      <formula1>=ExpenseCategoryList</formula1>
+      <formula1>ExpenseCategoryList</formula1>
     </dataValidation>
     <dataValidation sqref="G12:G337" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Please choose a value from the dropdown list." type="list">
-      <formula1>=AccountNameList</formula1>
+      <formula1>AccountNameList</formula1>
     </dataValidation>
     <dataValidation sqref="L12:L337" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Please choose a value from the dropdown list." type="list">
-      <formula1>=List_YesNo</formula1>
+      <formula1>List_YesNo</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -41048,7 +43099,8 @@
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
-    <col hidden="1" width="13" customWidth="1" min="15" max="15"/>
+    <col width="30" customWidth="1" min="15" max="15"/>
+    <col hidden="1" width="13" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -41070,6 +43122,8 @@
       <c r="L1" s="2" t="n"/>
       <c r="M1" s="2" t="n"/>
       <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
+      <c r="P1" s="2" t="n"/>
     </row>
     <row r="2" ht="10" customHeight="1">
       <c r="A2" s="2" t="n"/>
@@ -41086,6 +43140,8 @@
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
+      <c r="P2" s="2" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="26" t="inlineStr">
@@ -41182,6 +43238,11 @@
       </c>
       <c r="O5" s="36" t="inlineStr">
         <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="P5" s="36" t="inlineStr">
+        <is>
           <t>CurMonthAmt</t>
         </is>
       </c>
@@ -41248,7 +43309,8 @@
           <t>Monthly mortgage payment</t>
         </is>
       </c>
-      <c r="O6" s="40">
+      <c r="O6" s="38" t="n"/>
+      <c r="P6" s="40">
         <f>IF(AND($B6&gt;=CurMonthStart,$B6&lt;=CurMonthEnd),$K6,0)</f>
         <v/>
       </c>
@@ -41311,7 +43373,8 @@
         </is>
       </c>
       <c r="N7" s="38" t="inlineStr"/>
-      <c r="O7" s="40">
+      <c r="O7" s="38" t="n"/>
+      <c r="P7" s="40">
         <f>IF(AND($B7&gt;=CurMonthStart,$B7&lt;=CurMonthEnd),$K7,0)</f>
         <v/>
       </c>
@@ -41378,7 +43441,8 @@
           <t>Bulk groceries</t>
         </is>
       </c>
-      <c r="O8" s="40">
+      <c r="O8" s="38" t="n"/>
+      <c r="P8" s="40">
         <f>IF(AND($B8&gt;=CurMonthStart,$B8&lt;=CurMonthEnd),$K8,0)</f>
         <v/>
       </c>
@@ -41445,7 +43509,8 @@
           <t>Gas</t>
         </is>
       </c>
-      <c r="O9" s="40">
+      <c r="O9" s="38" t="n"/>
+      <c r="P9" s="40">
         <f>IF(AND($B9&gt;=CurMonthStart,$B9&lt;=CurMonthEnd),$K9,0)</f>
         <v/>
       </c>
@@ -41512,7 +43577,8 @@
           <t>Wiper blades / oil</t>
         </is>
       </c>
-      <c r="O10" s="40">
+      <c r="O10" s="38" t="n"/>
+      <c r="P10" s="40">
         <f>IF(AND($B10&gt;=CurMonthStart,$B10&lt;=CurMonthEnd),$K10,0)</f>
         <v/>
       </c>
@@ -41575,7 +43641,8 @@
         </is>
       </c>
       <c r="N11" s="38" t="inlineStr"/>
-      <c r="O11" s="40">
+      <c r="O11" s="38" t="n"/>
+      <c r="P11" s="40">
         <f>IF(AND($B11&gt;=CurMonthStart,$B11&lt;=CurMonthEnd),$K11,0)</f>
         <v/>
       </c>
@@ -41642,7 +43709,8 @@
           <t>Internet</t>
         </is>
       </c>
-      <c r="O12" s="40">
+      <c r="O12" s="38" t="n"/>
+      <c r="P12" s="40">
         <f>IF(AND($B12&gt;=CurMonthStart,$B12&lt;=CurMonthEnd),$K12,0)</f>
         <v/>
       </c>
@@ -41709,7 +43777,8 @@
           <t>Mobile phone</t>
         </is>
       </c>
-      <c r="O13" s="40">
+      <c r="O13" s="38" t="n"/>
+      <c r="P13" s="40">
         <f>IF(AND($B13&gt;=CurMonthStart,$B13&lt;=CurMonthEnd),$K13,0)</f>
         <v/>
       </c>
@@ -41776,7 +43845,8 @@
           <t>Auto + home insurance</t>
         </is>
       </c>
-      <c r="O14" s="40">
+      <c r="O14" s="38" t="n"/>
+      <c r="P14" s="40">
         <f>IF(AND($B14&gt;=CurMonthStart,$B14&lt;=CurMonthEnd),$K14,0)</f>
         <v/>
       </c>
@@ -41843,7 +43913,8 @@
           <t>Copay</t>
         </is>
       </c>
-      <c r="O15" s="40">
+      <c r="O15" s="38" t="n"/>
+      <c r="P15" s="40">
         <f>IF(AND($B15&gt;=CurMonthStart,$B15&lt;=CurMonthEnd),$K15,0)</f>
         <v/>
       </c>
@@ -41906,7 +43977,8 @@
         </is>
       </c>
       <c r="N16" s="38" t="inlineStr"/>
-      <c r="O16" s="40">
+      <c r="O16" s="38" t="n"/>
+      <c r="P16" s="40">
         <f>IF(AND($B16&gt;=CurMonthStart,$B16&lt;=CurMonthEnd),$K16,0)</f>
         <v/>
       </c>
@@ -41973,7 +44045,8 @@
           <t>Streaming subscription</t>
         </is>
       </c>
-      <c r="O17" s="40">
+      <c r="O17" s="38" t="n"/>
+      <c r="P17" s="40">
         <f>IF(AND($B17&gt;=CurMonthStart,$B17&lt;=CurMonthEnd),$K17,0)</f>
         <v/>
       </c>
@@ -42036,7 +44109,8 @@
         </is>
       </c>
       <c r="N18" s="38" t="inlineStr"/>
-      <c r="O18" s="40">
+      <c r="O18" s="38" t="n"/>
+      <c r="P18" s="40">
         <f>IF(AND($B18&gt;=CurMonthStart,$B18&lt;=CurMonthEnd),$K18,0)</f>
         <v/>
       </c>
@@ -42103,7 +44177,8 @@
           <t>Gym membership</t>
         </is>
       </c>
-      <c r="O19" s="40">
+      <c r="O19" s="38" t="n"/>
+      <c r="P19" s="40">
         <f>IF(AND($B19&gt;=CurMonthStart,$B19&lt;=CurMonthEnd),$K19,0)</f>
         <v/>
       </c>
@@ -42166,7 +44241,8 @@
         </is>
       </c>
       <c r="N20" s="38" t="inlineStr"/>
-      <c r="O20" s="40">
+      <c r="O20" s="38" t="n"/>
+      <c r="P20" s="40">
         <f>IF(AND($B20&gt;=CurMonthStart,$B20&lt;=CurMonthEnd),$K20,0)</f>
         <v/>
       </c>
@@ -42229,7 +44305,8 @@
         </is>
       </c>
       <c r="N21" s="38" t="inlineStr"/>
-      <c r="O21" s="40">
+      <c r="O21" s="38" t="n"/>
+      <c r="P21" s="40">
         <f>IF(AND($B21&gt;=CurMonthStart,$B21&lt;=CurMonthEnd),$K21,0)</f>
         <v/>
       </c>
@@ -42296,7 +44373,8 @@
           <t>Monthly mortgage payment</t>
         </is>
       </c>
-      <c r="O22" s="40">
+      <c r="O22" s="38" t="n"/>
+      <c r="P22" s="40">
         <f>IF(AND($B22&gt;=CurMonthStart,$B22&lt;=CurMonthEnd),$K22,0)</f>
         <v/>
       </c>
@@ -42359,7 +44437,8 @@
         </is>
       </c>
       <c r="N23" s="38" t="inlineStr"/>
-      <c r="O23" s="40">
+      <c r="O23" s="38" t="n"/>
+      <c r="P23" s="40">
         <f>IF(AND($B23&gt;=CurMonthStart,$B23&lt;=CurMonthEnd),$K23,0)</f>
         <v/>
       </c>
@@ -42426,7 +44505,8 @@
           <t>Bulk groceries</t>
         </is>
       </c>
-      <c r="O24" s="40">
+      <c r="O24" s="38" t="n"/>
+      <c r="P24" s="40">
         <f>IF(AND($B24&gt;=CurMonthStart,$B24&lt;=CurMonthEnd),$K24,0)</f>
         <v/>
       </c>
@@ -42493,7 +44573,8 @@
           <t>Gas</t>
         </is>
       </c>
-      <c r="O25" s="40">
+      <c r="O25" s="38" t="n"/>
+      <c r="P25" s="40">
         <f>IF(AND($B25&gt;=CurMonthStart,$B25&lt;=CurMonthEnd),$K25,0)</f>
         <v/>
       </c>
@@ -42560,7 +44641,8 @@
           <t>Wiper blades / oil</t>
         </is>
       </c>
-      <c r="O26" s="40">
+      <c r="O26" s="38" t="n"/>
+      <c r="P26" s="40">
         <f>IF(AND($B26&gt;=CurMonthStart,$B26&lt;=CurMonthEnd),$K26,0)</f>
         <v/>
       </c>
@@ -42623,7 +44705,8 @@
         </is>
       </c>
       <c r="N27" s="38" t="inlineStr"/>
-      <c r="O27" s="40">
+      <c r="O27" s="38" t="n"/>
+      <c r="P27" s="40">
         <f>IF(AND($B27&gt;=CurMonthStart,$B27&lt;=CurMonthEnd),$K27,0)</f>
         <v/>
       </c>
@@ -42690,7 +44773,8 @@
           <t>Internet</t>
         </is>
       </c>
-      <c r="O28" s="40">
+      <c r="O28" s="38" t="n"/>
+      <c r="P28" s="40">
         <f>IF(AND($B28&gt;=CurMonthStart,$B28&lt;=CurMonthEnd),$K28,0)</f>
         <v/>
       </c>
@@ -42757,7 +44841,8 @@
           <t>Mobile phone</t>
         </is>
       </c>
-      <c r="O29" s="40">
+      <c r="O29" s="38" t="n"/>
+      <c r="P29" s="40">
         <f>IF(AND($B29&gt;=CurMonthStart,$B29&lt;=CurMonthEnd),$K29,0)</f>
         <v/>
       </c>
@@ -42824,7 +44909,8 @@
           <t>Auto + home insurance</t>
         </is>
       </c>
-      <c r="O30" s="40">
+      <c r="O30" s="38" t="n"/>
+      <c r="P30" s="40">
         <f>IF(AND($B30&gt;=CurMonthStart,$B30&lt;=CurMonthEnd),$K30,0)</f>
         <v/>
       </c>
@@ -42891,7 +44977,8 @@
           <t>Copay</t>
         </is>
       </c>
-      <c r="O31" s="40">
+      <c r="O31" s="38" t="n"/>
+      <c r="P31" s="40">
         <f>IF(AND($B31&gt;=CurMonthStart,$B31&lt;=CurMonthEnd),$K31,0)</f>
         <v/>
       </c>
@@ -42954,7 +45041,8 @@
         </is>
       </c>
       <c r="N32" s="38" t="inlineStr"/>
-      <c r="O32" s="40">
+      <c r="O32" s="38" t="n"/>
+      <c r="P32" s="40">
         <f>IF(AND($B32&gt;=CurMonthStart,$B32&lt;=CurMonthEnd),$K32,0)</f>
         <v/>
       </c>
@@ -43021,7 +45109,8 @@
           <t>Streaming subscription</t>
         </is>
       </c>
-      <c r="O33" s="40">
+      <c r="O33" s="38" t="n"/>
+      <c r="P33" s="40">
         <f>IF(AND($B33&gt;=CurMonthStart,$B33&lt;=CurMonthEnd),$K33,0)</f>
         <v/>
       </c>
@@ -43084,7 +45173,8 @@
         </is>
       </c>
       <c r="N34" s="38" t="inlineStr"/>
-      <c r="O34" s="40">
+      <c r="O34" s="38" t="n"/>
+      <c r="P34" s="40">
         <f>IF(AND($B34&gt;=CurMonthStart,$B34&lt;=CurMonthEnd),$K34,0)</f>
         <v/>
       </c>
@@ -43151,7 +45241,8 @@
           <t>Gym membership</t>
         </is>
       </c>
-      <c r="O35" s="40">
+      <c r="O35" s="38" t="n"/>
+      <c r="P35" s="40">
         <f>IF(AND($B35&gt;=CurMonthStart,$B35&lt;=CurMonthEnd),$K35,0)</f>
         <v/>
       </c>
@@ -43214,7 +45305,8 @@
         </is>
       </c>
       <c r="N36" s="38" t="inlineStr"/>
-      <c r="O36" s="40">
+      <c r="O36" s="38" t="n"/>
+      <c r="P36" s="40">
         <f>IF(AND($B36&gt;=CurMonthStart,$B36&lt;=CurMonthEnd),$K36,0)</f>
         <v/>
       </c>
@@ -43277,7 +45369,8 @@
         </is>
       </c>
       <c r="N37" s="38" t="inlineStr"/>
-      <c r="O37" s="40">
+      <c r="O37" s="38" t="n"/>
+      <c r="P37" s="40">
         <f>IF(AND($B37&gt;=CurMonthStart,$B37&lt;=CurMonthEnd),$K37,0)</f>
         <v/>
       </c>
@@ -43344,7 +45437,8 @@
           <t>Monthly mortgage payment</t>
         </is>
       </c>
-      <c r="O38" s="40">
+      <c r="O38" s="38" t="n"/>
+      <c r="P38" s="40">
         <f>IF(AND($B38&gt;=CurMonthStart,$B38&lt;=CurMonthEnd),$K38,0)</f>
         <v/>
       </c>
@@ -43407,7 +45501,8 @@
         </is>
       </c>
       <c r="N39" s="38" t="inlineStr"/>
-      <c r="O39" s="40">
+      <c r="O39" s="38" t="n"/>
+      <c r="P39" s="40">
         <f>IF(AND($B39&gt;=CurMonthStart,$B39&lt;=CurMonthEnd),$K39,0)</f>
         <v/>
       </c>
@@ -43474,7 +45569,8 @@
           <t>Bulk groceries</t>
         </is>
       </c>
-      <c r="O40" s="40">
+      <c r="O40" s="38" t="n"/>
+      <c r="P40" s="40">
         <f>IF(AND($B40&gt;=CurMonthStart,$B40&lt;=CurMonthEnd),$K40,0)</f>
         <v/>
       </c>
@@ -43541,7 +45637,8 @@
           <t>Gas</t>
         </is>
       </c>
-      <c r="O41" s="40">
+      <c r="O41" s="38" t="n"/>
+      <c r="P41" s="40">
         <f>IF(AND($B41&gt;=CurMonthStart,$B41&lt;=CurMonthEnd),$K41,0)</f>
         <v/>
       </c>
@@ -43608,7 +45705,8 @@
           <t>Wiper blades / oil</t>
         </is>
       </c>
-      <c r="O42" s="40">
+      <c r="O42" s="38" t="n"/>
+      <c r="P42" s="40">
         <f>IF(AND($B42&gt;=CurMonthStart,$B42&lt;=CurMonthEnd),$K42,0)</f>
         <v/>
       </c>
@@ -43671,7 +45769,8 @@
         </is>
       </c>
       <c r="N43" s="38" t="inlineStr"/>
-      <c r="O43" s="40">
+      <c r="O43" s="38" t="n"/>
+      <c r="P43" s="40">
         <f>IF(AND($B43&gt;=CurMonthStart,$B43&lt;=CurMonthEnd),$K43,0)</f>
         <v/>
       </c>
@@ -43738,7 +45837,8 @@
           <t>Internet</t>
         </is>
       </c>
-      <c r="O44" s="40">
+      <c r="O44" s="38" t="n"/>
+      <c r="P44" s="40">
         <f>IF(AND($B44&gt;=CurMonthStart,$B44&lt;=CurMonthEnd),$K44,0)</f>
         <v/>
       </c>
@@ -43805,7 +45905,8 @@
           <t>Mobile phone</t>
         </is>
       </c>
-      <c r="O45" s="40">
+      <c r="O45" s="38" t="n"/>
+      <c r="P45" s="40">
         <f>IF(AND($B45&gt;=CurMonthStart,$B45&lt;=CurMonthEnd),$K45,0)</f>
         <v/>
       </c>
@@ -43872,7 +45973,8 @@
           <t>Auto + home insurance</t>
         </is>
       </c>
-      <c r="O46" s="40">
+      <c r="O46" s="38" t="n"/>
+      <c r="P46" s="40">
         <f>IF(AND($B46&gt;=CurMonthStart,$B46&lt;=CurMonthEnd),$K46,0)</f>
         <v/>
       </c>
@@ -43939,7 +46041,8 @@
           <t>Copay</t>
         </is>
       </c>
-      <c r="O47" s="40">
+      <c r="O47" s="38" t="n"/>
+      <c r="P47" s="40">
         <f>IF(AND($B47&gt;=CurMonthStart,$B47&lt;=CurMonthEnd),$K47,0)</f>
         <v/>
       </c>
@@ -44002,7 +46105,8 @@
         </is>
       </c>
       <c r="N48" s="38" t="inlineStr"/>
-      <c r="O48" s="40">
+      <c r="O48" s="38" t="n"/>
+      <c r="P48" s="40">
         <f>IF(AND($B48&gt;=CurMonthStart,$B48&lt;=CurMonthEnd),$K48,0)</f>
         <v/>
       </c>
@@ -44069,7 +46173,8 @@
           <t>Streaming subscription</t>
         </is>
       </c>
-      <c r="O49" s="40">
+      <c r="O49" s="38" t="n"/>
+      <c r="P49" s="40">
         <f>IF(AND($B49&gt;=CurMonthStart,$B49&lt;=CurMonthEnd),$K49,0)</f>
         <v/>
       </c>
@@ -44132,7 +46237,8 @@
         </is>
       </c>
       <c r="N50" s="38" t="inlineStr"/>
-      <c r="O50" s="40">
+      <c r="O50" s="38" t="n"/>
+      <c r="P50" s="40">
         <f>IF(AND($B50&gt;=CurMonthStart,$B50&lt;=CurMonthEnd),$K50,0)</f>
         <v/>
       </c>
@@ -44199,7 +46305,8 @@
           <t>Gym membership</t>
         </is>
       </c>
-      <c r="O51" s="40">
+      <c r="O51" s="38" t="n"/>
+      <c r="P51" s="40">
         <f>IF(AND($B51&gt;=CurMonthStart,$B51&lt;=CurMonthEnd),$K51,0)</f>
         <v/>
       </c>
@@ -44262,7 +46369,8 @@
         </is>
       </c>
       <c r="N52" s="38" t="inlineStr"/>
-      <c r="O52" s="40">
+      <c r="O52" s="38" t="n"/>
+      <c r="P52" s="40">
         <f>IF(AND($B52&gt;=CurMonthStart,$B52&lt;=CurMonthEnd),$K52,0)</f>
         <v/>
       </c>
@@ -44325,7 +46433,8 @@
         </is>
       </c>
       <c r="N53" s="38" t="inlineStr"/>
-      <c r="O53" s="40">
+      <c r="O53" s="38" t="n"/>
+      <c r="P53" s="40">
         <f>IF(AND($B53&gt;=CurMonthStart,$B53&lt;=CurMonthEnd),$K53,0)</f>
         <v/>
       </c>
@@ -44392,7 +46501,8 @@
           <t>Monthly mortgage payment</t>
         </is>
       </c>
-      <c r="O54" s="40">
+      <c r="O54" s="38" t="n"/>
+      <c r="P54" s="40">
         <f>IF(AND($B54&gt;=CurMonthStart,$B54&lt;=CurMonthEnd),$K54,0)</f>
         <v/>
       </c>
@@ -44455,7 +46565,8 @@
         </is>
       </c>
       <c r="N55" s="38" t="inlineStr"/>
-      <c r="O55" s="40">
+      <c r="O55" s="38" t="n"/>
+      <c r="P55" s="40">
         <f>IF(AND($B55&gt;=CurMonthStart,$B55&lt;=CurMonthEnd),$K55,0)</f>
         <v/>
       </c>
@@ -44522,7 +46633,8 @@
           <t>Bulk groceries</t>
         </is>
       </c>
-      <c r="O56" s="40">
+      <c r="O56" s="38" t="n"/>
+      <c r="P56" s="40">
         <f>IF(AND($B56&gt;=CurMonthStart,$B56&lt;=CurMonthEnd),$K56,0)</f>
         <v/>
       </c>
@@ -44589,7 +46701,8 @@
           <t>Gas</t>
         </is>
       </c>
-      <c r="O57" s="40">
+      <c r="O57" s="38" t="n"/>
+      <c r="P57" s="40">
         <f>IF(AND($B57&gt;=CurMonthStart,$B57&lt;=CurMonthEnd),$K57,0)</f>
         <v/>
       </c>
@@ -44656,7 +46769,8 @@
           <t>Wiper blades / oil</t>
         </is>
       </c>
-      <c r="O58" s="40">
+      <c r="O58" s="38" t="n"/>
+      <c r="P58" s="40">
         <f>IF(AND($B58&gt;=CurMonthStart,$B58&lt;=CurMonthEnd),$K58,0)</f>
         <v/>
       </c>
@@ -44719,7 +46833,8 @@
         </is>
       </c>
       <c r="N59" s="38" t="inlineStr"/>
-      <c r="O59" s="40">
+      <c r="O59" s="38" t="n"/>
+      <c r="P59" s="40">
         <f>IF(AND($B59&gt;=CurMonthStart,$B59&lt;=CurMonthEnd),$K59,0)</f>
         <v/>
       </c>
@@ -44786,7 +46901,8 @@
           <t>Internet</t>
         </is>
       </c>
-      <c r="O60" s="40">
+      <c r="O60" s="38" t="n"/>
+      <c r="P60" s="40">
         <f>IF(AND($B60&gt;=CurMonthStart,$B60&lt;=CurMonthEnd),$K60,0)</f>
         <v/>
       </c>
@@ -44853,7 +46969,8 @@
           <t>Mobile phone</t>
         </is>
       </c>
-      <c r="O61" s="40">
+      <c r="O61" s="38" t="n"/>
+      <c r="P61" s="40">
         <f>IF(AND($B61&gt;=CurMonthStart,$B61&lt;=CurMonthEnd),$K61,0)</f>
         <v/>
       </c>
@@ -44920,7 +47037,8 @@
           <t>Auto + home insurance</t>
         </is>
       </c>
-      <c r="O62" s="40">
+      <c r="O62" s="38" t="n"/>
+      <c r="P62" s="40">
         <f>IF(AND($B62&gt;=CurMonthStart,$B62&lt;=CurMonthEnd),$K62,0)</f>
         <v/>
       </c>
@@ -44987,7 +47105,8 @@
           <t>Copay</t>
         </is>
       </c>
-      <c r="O63" s="40">
+      <c r="O63" s="38" t="n"/>
+      <c r="P63" s="40">
         <f>IF(AND($B63&gt;=CurMonthStart,$B63&lt;=CurMonthEnd),$K63,0)</f>
         <v/>
       </c>
@@ -45050,7 +47169,8 @@
         </is>
       </c>
       <c r="N64" s="38" t="inlineStr"/>
-      <c r="O64" s="40">
+      <c r="O64" s="38" t="n"/>
+      <c r="P64" s="40">
         <f>IF(AND($B64&gt;=CurMonthStart,$B64&lt;=CurMonthEnd),$K64,0)</f>
         <v/>
       </c>
@@ -45117,7 +47237,8 @@
           <t>Streaming subscription</t>
         </is>
       </c>
-      <c r="O65" s="40">
+      <c r="O65" s="38" t="n"/>
+      <c r="P65" s="40">
         <f>IF(AND($B65&gt;=CurMonthStart,$B65&lt;=CurMonthEnd),$K65,0)</f>
         <v/>
       </c>
@@ -45180,7 +47301,8 @@
         </is>
       </c>
       <c r="N66" s="38" t="inlineStr"/>
-      <c r="O66" s="40">
+      <c r="O66" s="38" t="n"/>
+      <c r="P66" s="40">
         <f>IF(AND($B66&gt;=CurMonthStart,$B66&lt;=CurMonthEnd),$K66,0)</f>
         <v/>
       </c>
@@ -45247,7 +47369,8 @@
           <t>Gym membership</t>
         </is>
       </c>
-      <c r="O67" s="40">
+      <c r="O67" s="38" t="n"/>
+      <c r="P67" s="40">
         <f>IF(AND($B67&gt;=CurMonthStart,$B67&lt;=CurMonthEnd),$K67,0)</f>
         <v/>
       </c>
@@ -45310,7 +47433,8 @@
         </is>
       </c>
       <c r="N68" s="38" t="inlineStr"/>
-      <c r="O68" s="40">
+      <c r="O68" s="38" t="n"/>
+      <c r="P68" s="40">
         <f>IF(AND($B68&gt;=CurMonthStart,$B68&lt;=CurMonthEnd),$K68,0)</f>
         <v/>
       </c>
@@ -45373,7 +47497,8 @@
         </is>
       </c>
       <c r="N69" s="38" t="inlineStr"/>
-      <c r="O69" s="40">
+      <c r="O69" s="38" t="n"/>
+      <c r="P69" s="40">
         <f>IF(AND($B69&gt;=CurMonthStart,$B69&lt;=CurMonthEnd),$K69,0)</f>
         <v/>
       </c>
@@ -45440,7 +47565,8 @@
           <t>Monthly mortgage payment</t>
         </is>
       </c>
-      <c r="O70" s="40">
+      <c r="O70" s="38" t="n"/>
+      <c r="P70" s="40">
         <f>IF(AND($B70&gt;=CurMonthStart,$B70&lt;=CurMonthEnd),$K70,0)</f>
         <v/>
       </c>
@@ -45503,7 +47629,8 @@
         </is>
       </c>
       <c r="N71" s="38" t="inlineStr"/>
-      <c r="O71" s="40">
+      <c r="O71" s="38" t="n"/>
+      <c r="P71" s="40">
         <f>IF(AND($B71&gt;=CurMonthStart,$B71&lt;=CurMonthEnd),$K71,0)</f>
         <v/>
       </c>
@@ -45570,7 +47697,8 @@
           <t>Bulk groceries</t>
         </is>
       </c>
-      <c r="O72" s="40">
+      <c r="O72" s="38" t="n"/>
+      <c r="P72" s="40">
         <f>IF(AND($B72&gt;=CurMonthStart,$B72&lt;=CurMonthEnd),$K72,0)</f>
         <v/>
       </c>
@@ -45637,7 +47765,8 @@
           <t>Gas</t>
         </is>
       </c>
-      <c r="O73" s="40">
+      <c r="O73" s="38" t="n"/>
+      <c r="P73" s="40">
         <f>IF(AND($B73&gt;=CurMonthStart,$B73&lt;=CurMonthEnd),$K73,0)</f>
         <v/>
       </c>
@@ -45704,7 +47833,8 @@
           <t>Wiper blades / oil</t>
         </is>
       </c>
-      <c r="O74" s="40">
+      <c r="O74" s="38" t="n"/>
+      <c r="P74" s="40">
         <f>IF(AND($B74&gt;=CurMonthStart,$B74&lt;=CurMonthEnd),$K74,0)</f>
         <v/>
       </c>
@@ -45767,7 +47897,8 @@
         </is>
       </c>
       <c r="N75" s="38" t="inlineStr"/>
-      <c r="O75" s="40">
+      <c r="O75" s="38" t="n"/>
+      <c r="P75" s="40">
         <f>IF(AND($B75&gt;=CurMonthStart,$B75&lt;=CurMonthEnd),$K75,0)</f>
         <v/>
       </c>
@@ -45834,7 +47965,8 @@
           <t>Internet</t>
         </is>
       </c>
-      <c r="O76" s="40">
+      <c r="O76" s="38" t="n"/>
+      <c r="P76" s="40">
         <f>IF(AND($B76&gt;=CurMonthStart,$B76&lt;=CurMonthEnd),$K76,0)</f>
         <v/>
       </c>
@@ -45901,7 +48033,8 @@
           <t>Mobile phone</t>
         </is>
       </c>
-      <c r="O77" s="40">
+      <c r="O77" s="38" t="n"/>
+      <c r="P77" s="40">
         <f>IF(AND($B77&gt;=CurMonthStart,$B77&lt;=CurMonthEnd),$K77,0)</f>
         <v/>
       </c>
@@ -45968,7 +48101,8 @@
           <t>Auto + home insurance</t>
         </is>
       </c>
-      <c r="O78" s="40">
+      <c r="O78" s="38" t="n"/>
+      <c r="P78" s="40">
         <f>IF(AND($B78&gt;=CurMonthStart,$B78&lt;=CurMonthEnd),$K78,0)</f>
         <v/>
       </c>
@@ -46035,7 +48169,8 @@
           <t>Copay</t>
         </is>
       </c>
-      <c r="O79" s="40">
+      <c r="O79" s="38" t="n"/>
+      <c r="P79" s="40">
         <f>IF(AND($B79&gt;=CurMonthStart,$B79&lt;=CurMonthEnd),$K79,0)</f>
         <v/>
       </c>
@@ -46098,7 +48233,8 @@
         </is>
       </c>
       <c r="N80" s="38" t="inlineStr"/>
-      <c r="O80" s="40">
+      <c r="O80" s="38" t="n"/>
+      <c r="P80" s="40">
         <f>IF(AND($B80&gt;=CurMonthStart,$B80&lt;=CurMonthEnd),$K80,0)</f>
         <v/>
       </c>
@@ -46165,7 +48301,8 @@
           <t>Streaming subscription</t>
         </is>
       </c>
-      <c r="O81" s="40">
+      <c r="O81" s="38" t="n"/>
+      <c r="P81" s="40">
         <f>IF(AND($B81&gt;=CurMonthStart,$B81&lt;=CurMonthEnd),$K81,0)</f>
         <v/>
       </c>
@@ -46228,7 +48365,8 @@
         </is>
       </c>
       <c r="N82" s="38" t="inlineStr"/>
-      <c r="O82" s="40">
+      <c r="O82" s="38" t="n"/>
+      <c r="P82" s="40">
         <f>IF(AND($B82&gt;=CurMonthStart,$B82&lt;=CurMonthEnd),$K82,0)</f>
         <v/>
       </c>
@@ -46295,7 +48433,8 @@
           <t>Gym membership</t>
         </is>
       </c>
-      <c r="O83" s="40">
+      <c r="O83" s="38" t="n"/>
+      <c r="P83" s="40">
         <f>IF(AND($B83&gt;=CurMonthStart,$B83&lt;=CurMonthEnd),$K83,0)</f>
         <v/>
       </c>
@@ -46358,7 +48497,8 @@
         </is>
       </c>
       <c r="N84" s="38" t="inlineStr"/>
-      <c r="O84" s="40">
+      <c r="O84" s="38" t="n"/>
+      <c r="P84" s="40">
         <f>IF(AND($B84&gt;=CurMonthStart,$B84&lt;=CurMonthEnd),$K84,0)</f>
         <v/>
       </c>
@@ -46421,7 +48561,8 @@
         </is>
       </c>
       <c r="N85" s="38" t="inlineStr"/>
-      <c r="O85" s="40">
+      <c r="O85" s="38" t="n"/>
+      <c r="P85" s="40">
         <f>IF(AND($B85&gt;=CurMonthStart,$B85&lt;=CurMonthEnd),$K85,0)</f>
         <v/>
       </c>
@@ -46488,7 +48629,8 @@
           <t>Monthly mortgage payment</t>
         </is>
       </c>
-      <c r="O86" s="40">
+      <c r="O86" s="38" t="n"/>
+      <c r="P86" s="40">
         <f>IF(AND($B86&gt;=CurMonthStart,$B86&lt;=CurMonthEnd),$K86,0)</f>
         <v/>
       </c>
@@ -46551,7 +48693,8 @@
         </is>
       </c>
       <c r="N87" s="38" t="inlineStr"/>
-      <c r="O87" s="40">
+      <c r="O87" s="38" t="n"/>
+      <c r="P87" s="40">
         <f>IF(AND($B87&gt;=CurMonthStart,$B87&lt;=CurMonthEnd),$K87,0)</f>
         <v/>
       </c>
@@ -46618,7 +48761,8 @@
           <t>Bulk groceries</t>
         </is>
       </c>
-      <c r="O88" s="40">
+      <c r="O88" s="38" t="n"/>
+      <c r="P88" s="40">
         <f>IF(AND($B88&gt;=CurMonthStart,$B88&lt;=CurMonthEnd),$K88,0)</f>
         <v/>
       </c>
@@ -46685,7 +48829,8 @@
           <t>Gas</t>
         </is>
       </c>
-      <c r="O89" s="40">
+      <c r="O89" s="38" t="n"/>
+      <c r="P89" s="40">
         <f>IF(AND($B89&gt;=CurMonthStart,$B89&lt;=CurMonthEnd),$K89,0)</f>
         <v/>
       </c>
@@ -46752,7 +48897,8 @@
           <t>Wiper blades / oil</t>
         </is>
       </c>
-      <c r="O90" s="40">
+      <c r="O90" s="38" t="n"/>
+      <c r="P90" s="40">
         <f>IF(AND($B90&gt;=CurMonthStart,$B90&lt;=CurMonthEnd),$K90,0)</f>
         <v/>
       </c>
@@ -46815,7 +48961,8 @@
         </is>
       </c>
       <c r="N91" s="38" t="inlineStr"/>
-      <c r="O91" s="40">
+      <c r="O91" s="38" t="n"/>
+      <c r="P91" s="40">
         <f>IF(AND($B91&gt;=CurMonthStart,$B91&lt;=CurMonthEnd),$K91,0)</f>
         <v/>
       </c>
@@ -46882,7 +49029,8 @@
           <t>Internet</t>
         </is>
       </c>
-      <c r="O92" s="40">
+      <c r="O92" s="38" t="n"/>
+      <c r="P92" s="40">
         <f>IF(AND($B92&gt;=CurMonthStart,$B92&lt;=CurMonthEnd),$K92,0)</f>
         <v/>
       </c>
@@ -46949,7 +49097,8 @@
           <t>Mobile phone</t>
         </is>
       </c>
-      <c r="O93" s="40">
+      <c r="O93" s="38" t="n"/>
+      <c r="P93" s="40">
         <f>IF(AND($B93&gt;=CurMonthStart,$B93&lt;=CurMonthEnd),$K93,0)</f>
         <v/>
       </c>
@@ -47016,7 +49165,8 @@
           <t>Auto + home insurance</t>
         </is>
       </c>
-      <c r="O94" s="40">
+      <c r="O94" s="38" t="n"/>
+      <c r="P94" s="40">
         <f>IF(AND($B94&gt;=CurMonthStart,$B94&lt;=CurMonthEnd),$K94,0)</f>
         <v/>
       </c>
@@ -47083,7 +49233,8 @@
           <t>Copay</t>
         </is>
       </c>
-      <c r="O95" s="40">
+      <c r="O95" s="38" t="n"/>
+      <c r="P95" s="40">
         <f>IF(AND($B95&gt;=CurMonthStart,$B95&lt;=CurMonthEnd),$K95,0)</f>
         <v/>
       </c>
@@ -47146,7 +49297,8 @@
         </is>
       </c>
       <c r="N96" s="38" t="inlineStr"/>
-      <c r="O96" s="40">
+      <c r="O96" s="38" t="n"/>
+      <c r="P96" s="40">
         <f>IF(AND($B96&gt;=CurMonthStart,$B96&lt;=CurMonthEnd),$K96,0)</f>
         <v/>
       </c>
@@ -47213,7 +49365,8 @@
           <t>Streaming subscription</t>
         </is>
       </c>
-      <c r="O97" s="40">
+      <c r="O97" s="38" t="n"/>
+      <c r="P97" s="40">
         <f>IF(AND($B97&gt;=CurMonthStart,$B97&lt;=CurMonthEnd),$K97,0)</f>
         <v/>
       </c>
@@ -47276,7 +49429,8 @@
         </is>
       </c>
       <c r="N98" s="38" t="inlineStr"/>
-      <c r="O98" s="40">
+      <c r="O98" s="38" t="n"/>
+      <c r="P98" s="40">
         <f>IF(AND($B98&gt;=CurMonthStart,$B98&lt;=CurMonthEnd),$K98,0)</f>
         <v/>
       </c>
@@ -47343,7 +49497,8 @@
           <t>Gym membership</t>
         </is>
       </c>
-      <c r="O99" s="40">
+      <c r="O99" s="38" t="n"/>
+      <c r="P99" s="40">
         <f>IF(AND($B99&gt;=CurMonthStart,$B99&lt;=CurMonthEnd),$K99,0)</f>
         <v/>
       </c>
@@ -47406,7 +49561,8 @@
         </is>
       </c>
       <c r="N100" s="38" t="inlineStr"/>
-      <c r="O100" s="40">
+      <c r="O100" s="38" t="n"/>
+      <c r="P100" s="40">
         <f>IF(AND($B100&gt;=CurMonthStart,$B100&lt;=CurMonthEnd),$K100,0)</f>
         <v/>
       </c>
@@ -47469,7 +49625,8 @@
         </is>
       </c>
       <c r="N101" s="38" t="inlineStr"/>
-      <c r="O101" s="40">
+      <c r="O101" s="38" t="n"/>
+      <c r="P101" s="40">
         <f>IF(AND($B101&gt;=CurMonthStart,$B101&lt;=CurMonthEnd),$K101,0)</f>
         <v/>
       </c>
@@ -47536,7 +49693,8 @@
           <t>Monthly mortgage payment</t>
         </is>
       </c>
-      <c r="O102" s="40">
+      <c r="O102" s="38" t="n"/>
+      <c r="P102" s="40">
         <f>IF(AND($B102&gt;=CurMonthStart,$B102&lt;=CurMonthEnd),$K102,0)</f>
         <v/>
       </c>
@@ -47599,7 +49757,8 @@
         </is>
       </c>
       <c r="N103" s="38" t="inlineStr"/>
-      <c r="O103" s="40">
+      <c r="O103" s="38" t="n"/>
+      <c r="P103" s="40">
         <f>IF(AND($B103&gt;=CurMonthStart,$B103&lt;=CurMonthEnd),$K103,0)</f>
         <v/>
       </c>
@@ -47666,7 +49825,8 @@
           <t>Bulk groceries</t>
         </is>
       </c>
-      <c r="O104" s="40">
+      <c r="O104" s="38" t="n"/>
+      <c r="P104" s="40">
         <f>IF(AND($B104&gt;=CurMonthStart,$B104&lt;=CurMonthEnd),$K104,0)</f>
         <v/>
       </c>
@@ -47733,7 +49893,8 @@
           <t>Gas</t>
         </is>
       </c>
-      <c r="O105" s="40">
+      <c r="O105" s="38" t="n"/>
+      <c r="P105" s="40">
         <f>IF(AND($B105&gt;=CurMonthStart,$B105&lt;=CurMonthEnd),$K105,0)</f>
         <v/>
       </c>
@@ -47800,7 +49961,8 @@
           <t>Wiper blades / oil</t>
         </is>
       </c>
-      <c r="O106" s="40">
+      <c r="O106" s="38" t="n"/>
+      <c r="P106" s="40">
         <f>IF(AND($B106&gt;=CurMonthStart,$B106&lt;=CurMonthEnd),$K106,0)</f>
         <v/>
       </c>
@@ -47863,7 +50025,8 @@
         </is>
       </c>
       <c r="N107" s="38" t="inlineStr"/>
-      <c r="O107" s="40">
+      <c r="O107" s="38" t="n"/>
+      <c r="P107" s="40">
         <f>IF(AND($B107&gt;=CurMonthStart,$B107&lt;=CurMonthEnd),$K107,0)</f>
         <v/>
       </c>
@@ -47930,7 +50093,8 @@
           <t>Internet</t>
         </is>
       </c>
-      <c r="O108" s="40">
+      <c r="O108" s="38" t="n"/>
+      <c r="P108" s="40">
         <f>IF(AND($B108&gt;=CurMonthStart,$B108&lt;=CurMonthEnd),$K108,0)</f>
         <v/>
       </c>
@@ -47997,7 +50161,8 @@
           <t>Mobile phone</t>
         </is>
       </c>
-      <c r="O109" s="40">
+      <c r="O109" s="38" t="n"/>
+      <c r="P109" s="40">
         <f>IF(AND($B109&gt;=CurMonthStart,$B109&lt;=CurMonthEnd),$K109,0)</f>
         <v/>
       </c>
@@ -48064,7 +50229,8 @@
           <t>Auto + home insurance</t>
         </is>
       </c>
-      <c r="O110" s="40">
+      <c r="O110" s="38" t="n"/>
+      <c r="P110" s="40">
         <f>IF(AND($B110&gt;=CurMonthStart,$B110&lt;=CurMonthEnd),$K110,0)</f>
         <v/>
       </c>
@@ -48131,7 +50297,8 @@
           <t>Copay</t>
         </is>
       </c>
-      <c r="O111" s="40">
+      <c r="O111" s="38" t="n"/>
+      <c r="P111" s="40">
         <f>IF(AND($B111&gt;=CurMonthStart,$B111&lt;=CurMonthEnd),$K111,0)</f>
         <v/>
       </c>
@@ -48194,7 +50361,8 @@
         </is>
       </c>
       <c r="N112" s="38" t="inlineStr"/>
-      <c r="O112" s="40">
+      <c r="O112" s="38" t="n"/>
+      <c r="P112" s="40">
         <f>IF(AND($B112&gt;=CurMonthStart,$B112&lt;=CurMonthEnd),$K112,0)</f>
         <v/>
       </c>
@@ -48261,7 +50429,8 @@
           <t>Streaming subscription</t>
         </is>
       </c>
-      <c r="O113" s="40">
+      <c r="O113" s="38" t="n"/>
+      <c r="P113" s="40">
         <f>IF(AND($B113&gt;=CurMonthStart,$B113&lt;=CurMonthEnd),$K113,0)</f>
         <v/>
       </c>
@@ -48324,7 +50493,8 @@
         </is>
       </c>
       <c r="N114" s="38" t="inlineStr"/>
-      <c r="O114" s="40">
+      <c r="O114" s="38" t="n"/>
+      <c r="P114" s="40">
         <f>IF(AND($B114&gt;=CurMonthStart,$B114&lt;=CurMonthEnd),$K114,0)</f>
         <v/>
       </c>
@@ -48391,7 +50561,8 @@
           <t>Gym membership</t>
         </is>
       </c>
-      <c r="O115" s="40">
+      <c r="O115" s="38" t="n"/>
+      <c r="P115" s="40">
         <f>IF(AND($B115&gt;=CurMonthStart,$B115&lt;=CurMonthEnd),$K115,0)</f>
         <v/>
       </c>
@@ -48454,7 +50625,8 @@
         </is>
       </c>
       <c r="N116" s="38" t="inlineStr"/>
-      <c r="O116" s="40">
+      <c r="O116" s="38" t="n"/>
+      <c r="P116" s="40">
         <f>IF(AND($B116&gt;=CurMonthStart,$B116&lt;=CurMonthEnd),$K116,0)</f>
         <v/>
       </c>
@@ -48517,7 +50689,8 @@
         </is>
       </c>
       <c r="N117" s="38" t="inlineStr"/>
-      <c r="O117" s="40">
+      <c r="O117" s="38" t="n"/>
+      <c r="P117" s="40">
         <f>IF(AND($B117&gt;=CurMonthStart,$B117&lt;=CurMonthEnd),$K117,0)</f>
         <v/>
       </c>
@@ -48584,7 +50757,8 @@
           <t>Monthly mortgage payment</t>
         </is>
       </c>
-      <c r="O118" s="40">
+      <c r="O118" s="38" t="n"/>
+      <c r="P118" s="40">
         <f>IF(AND($B118&gt;=CurMonthStart,$B118&lt;=CurMonthEnd),$K118,0)</f>
         <v/>
       </c>
@@ -48647,7 +50821,8 @@
         </is>
       </c>
       <c r="N119" s="38" t="inlineStr"/>
-      <c r="O119" s="40">
+      <c r="O119" s="38" t="n"/>
+      <c r="P119" s="40">
         <f>IF(AND($B119&gt;=CurMonthStart,$B119&lt;=CurMonthEnd),$K119,0)</f>
         <v/>
       </c>
@@ -48714,7 +50889,8 @@
           <t>Bulk groceries</t>
         </is>
       </c>
-      <c r="O120" s="40">
+      <c r="O120" s="38" t="n"/>
+      <c r="P120" s="40">
         <f>IF(AND($B120&gt;=CurMonthStart,$B120&lt;=CurMonthEnd),$K120,0)</f>
         <v/>
       </c>
@@ -48781,7 +50957,8 @@
           <t>Gas</t>
         </is>
       </c>
-      <c r="O121" s="40">
+      <c r="O121" s="38" t="n"/>
+      <c r="P121" s="40">
         <f>IF(AND($B121&gt;=CurMonthStart,$B121&lt;=CurMonthEnd),$K121,0)</f>
         <v/>
       </c>
@@ -48848,7 +51025,8 @@
           <t>Wiper blades / oil</t>
         </is>
       </c>
-      <c r="O122" s="40">
+      <c r="O122" s="38" t="n"/>
+      <c r="P122" s="40">
         <f>IF(AND($B122&gt;=CurMonthStart,$B122&lt;=CurMonthEnd),$K122,0)</f>
         <v/>
       </c>
@@ -48911,7 +51089,8 @@
         </is>
       </c>
       <c r="N123" s="38" t="inlineStr"/>
-      <c r="O123" s="40">
+      <c r="O123" s="38" t="n"/>
+      <c r="P123" s="40">
         <f>IF(AND($B123&gt;=CurMonthStart,$B123&lt;=CurMonthEnd),$K123,0)</f>
         <v/>
       </c>
@@ -48978,7 +51157,8 @@
           <t>Internet</t>
         </is>
       </c>
-      <c r="O124" s="40">
+      <c r="O124" s="38" t="n"/>
+      <c r="P124" s="40">
         <f>IF(AND($B124&gt;=CurMonthStart,$B124&lt;=CurMonthEnd),$K124,0)</f>
         <v/>
       </c>
@@ -49045,7 +51225,8 @@
           <t>Mobile phone</t>
         </is>
       </c>
-      <c r="O125" s="40">
+      <c r="O125" s="38" t="n"/>
+      <c r="P125" s="40">
         <f>IF(AND($B125&gt;=CurMonthStart,$B125&lt;=CurMonthEnd),$K125,0)</f>
         <v/>
       </c>
@@ -49112,7 +51293,8 @@
           <t>Auto + home insurance</t>
         </is>
       </c>
-      <c r="O126" s="40">
+      <c r="O126" s="38" t="n"/>
+      <c r="P126" s="40">
         <f>IF(AND($B126&gt;=CurMonthStart,$B126&lt;=CurMonthEnd),$K126,0)</f>
         <v/>
       </c>
@@ -49179,7 +51361,8 @@
           <t>Copay</t>
         </is>
       </c>
-      <c r="O127" s="40">
+      <c r="O127" s="38" t="n"/>
+      <c r="P127" s="40">
         <f>IF(AND($B127&gt;=CurMonthStart,$B127&lt;=CurMonthEnd),$K127,0)</f>
         <v/>
       </c>
@@ -49242,7 +51425,8 @@
         </is>
       </c>
       <c r="N128" s="38" t="inlineStr"/>
-      <c r="O128" s="40">
+      <c r="O128" s="38" t="n"/>
+      <c r="P128" s="40">
         <f>IF(AND($B128&gt;=CurMonthStart,$B128&lt;=CurMonthEnd),$K128,0)</f>
         <v/>
       </c>
@@ -49309,7 +51493,8 @@
           <t>Streaming subscription</t>
         </is>
       </c>
-      <c r="O129" s="40">
+      <c r="O129" s="38" t="n"/>
+      <c r="P129" s="40">
         <f>IF(AND($B129&gt;=CurMonthStart,$B129&lt;=CurMonthEnd),$K129,0)</f>
         <v/>
       </c>
@@ -49372,7 +51557,8 @@
         </is>
       </c>
       <c r="N130" s="38" t="inlineStr"/>
-      <c r="O130" s="40">
+      <c r="O130" s="38" t="n"/>
+      <c r="P130" s="40">
         <f>IF(AND($B130&gt;=CurMonthStart,$B130&lt;=CurMonthEnd),$K130,0)</f>
         <v/>
       </c>
@@ -49439,7 +51625,8 @@
           <t>Gym membership</t>
         </is>
       </c>
-      <c r="O131" s="40">
+      <c r="O131" s="38" t="n"/>
+      <c r="P131" s="40">
         <f>IF(AND($B131&gt;=CurMonthStart,$B131&lt;=CurMonthEnd),$K131,0)</f>
         <v/>
       </c>
@@ -49502,7 +51689,8 @@
         </is>
       </c>
       <c r="N132" s="38" t="inlineStr"/>
-      <c r="O132" s="40">
+      <c r="O132" s="38" t="n"/>
+      <c r="P132" s="40">
         <f>IF(AND($B132&gt;=CurMonthStart,$B132&lt;=CurMonthEnd),$K132,0)</f>
         <v/>
       </c>
@@ -49565,7 +51753,8 @@
         </is>
       </c>
       <c r="N133" s="38" t="inlineStr"/>
-      <c r="O133" s="40">
+      <c r="O133" s="38" t="n"/>
+      <c r="P133" s="40">
         <f>IF(AND($B133&gt;=CurMonthStart,$B133&lt;=CurMonthEnd),$K133,0)</f>
         <v/>
       </c>
@@ -49632,7 +51821,8 @@
           <t>Monthly mortgage payment</t>
         </is>
       </c>
-      <c r="O134" s="40">
+      <c r="O134" s="38" t="n"/>
+      <c r="P134" s="40">
         <f>IF(AND($B134&gt;=CurMonthStart,$B134&lt;=CurMonthEnd),$K134,0)</f>
         <v/>
       </c>
@@ -49695,7 +51885,8 @@
         </is>
       </c>
       <c r="N135" s="38" t="inlineStr"/>
-      <c r="O135" s="40">
+      <c r="O135" s="38" t="n"/>
+      <c r="P135" s="40">
         <f>IF(AND($B135&gt;=CurMonthStart,$B135&lt;=CurMonthEnd),$K135,0)</f>
         <v/>
       </c>
@@ -49762,7 +51953,8 @@
           <t>Bulk groceries</t>
         </is>
       </c>
-      <c r="O136" s="40">
+      <c r="O136" s="38" t="n"/>
+      <c r="P136" s="40">
         <f>IF(AND($B136&gt;=CurMonthStart,$B136&lt;=CurMonthEnd),$K136,0)</f>
         <v/>
       </c>
@@ -49829,7 +52021,8 @@
           <t>Gas</t>
         </is>
       </c>
-      <c r="O137" s="40">
+      <c r="O137" s="38" t="n"/>
+      <c r="P137" s="40">
         <f>IF(AND($B137&gt;=CurMonthStart,$B137&lt;=CurMonthEnd),$K137,0)</f>
         <v/>
       </c>
@@ -49896,7 +52089,8 @@
           <t>Wiper blades / oil</t>
         </is>
       </c>
-      <c r="O138" s="40">
+      <c r="O138" s="38" t="n"/>
+      <c r="P138" s="40">
         <f>IF(AND($B138&gt;=CurMonthStart,$B138&lt;=CurMonthEnd),$K138,0)</f>
         <v/>
       </c>
@@ -49959,7 +52153,8 @@
         </is>
       </c>
       <c r="N139" s="38" t="inlineStr"/>
-      <c r="O139" s="40">
+      <c r="O139" s="38" t="n"/>
+      <c r="P139" s="40">
         <f>IF(AND($B139&gt;=CurMonthStart,$B139&lt;=CurMonthEnd),$K139,0)</f>
         <v/>
       </c>
@@ -50026,7 +52221,8 @@
           <t>Internet</t>
         </is>
       </c>
-      <c r="O140" s="40">
+      <c r="O140" s="38" t="n"/>
+      <c r="P140" s="40">
         <f>IF(AND($B140&gt;=CurMonthStart,$B140&lt;=CurMonthEnd),$K140,0)</f>
         <v/>
       </c>
@@ -50093,7 +52289,8 @@
           <t>Mobile phone</t>
         </is>
       </c>
-      <c r="O141" s="40">
+      <c r="O141" s="38" t="n"/>
+      <c r="P141" s="40">
         <f>IF(AND($B141&gt;=CurMonthStart,$B141&lt;=CurMonthEnd),$K141,0)</f>
         <v/>
       </c>
@@ -50160,7 +52357,8 @@
           <t>Auto + home insurance</t>
         </is>
       </c>
-      <c r="O142" s="40">
+      <c r="O142" s="38" t="n"/>
+      <c r="P142" s="40">
         <f>IF(AND($B142&gt;=CurMonthStart,$B142&lt;=CurMonthEnd),$K142,0)</f>
         <v/>
       </c>
@@ -50227,7 +52425,8 @@
           <t>Copay</t>
         </is>
       </c>
-      <c r="O143" s="40">
+      <c r="O143" s="38" t="n"/>
+      <c r="P143" s="40">
         <f>IF(AND($B143&gt;=CurMonthStart,$B143&lt;=CurMonthEnd),$K143,0)</f>
         <v/>
       </c>
@@ -50290,7 +52489,8 @@
         </is>
       </c>
       <c r="N144" s="38" t="inlineStr"/>
-      <c r="O144" s="40">
+      <c r="O144" s="38" t="n"/>
+      <c r="P144" s="40">
         <f>IF(AND($B144&gt;=CurMonthStart,$B144&lt;=CurMonthEnd),$K144,0)</f>
         <v/>
       </c>
@@ -50357,7 +52557,8 @@
           <t>Streaming subscription</t>
         </is>
       </c>
-      <c r="O145" s="40">
+      <c r="O145" s="38" t="n"/>
+      <c r="P145" s="40">
         <f>IF(AND($B145&gt;=CurMonthStart,$B145&lt;=CurMonthEnd),$K145,0)</f>
         <v/>
       </c>
@@ -50420,7 +52621,8 @@
         </is>
       </c>
       <c r="N146" s="38" t="inlineStr"/>
-      <c r="O146" s="40">
+      <c r="O146" s="38" t="n"/>
+      <c r="P146" s="40">
         <f>IF(AND($B146&gt;=CurMonthStart,$B146&lt;=CurMonthEnd),$K146,0)</f>
         <v/>
       </c>
@@ -50487,7 +52689,8 @@
           <t>Gym membership</t>
         </is>
       </c>
-      <c r="O147" s="40">
+      <c r="O147" s="38" t="n"/>
+      <c r="P147" s="40">
         <f>IF(AND($B147&gt;=CurMonthStart,$B147&lt;=CurMonthEnd),$K147,0)</f>
         <v/>
       </c>
@@ -50550,7 +52753,8 @@
         </is>
       </c>
       <c r="N148" s="38" t="inlineStr"/>
-      <c r="O148" s="40">
+      <c r="O148" s="38" t="n"/>
+      <c r="P148" s="40">
         <f>IF(AND($B148&gt;=CurMonthStart,$B148&lt;=CurMonthEnd),$K148,0)</f>
         <v/>
       </c>
@@ -50613,7 +52817,8 @@
         </is>
       </c>
       <c r="N149" s="38" t="inlineStr"/>
-      <c r="O149" s="40">
+      <c r="O149" s="38" t="n"/>
+      <c r="P149" s="40">
         <f>IF(AND($B149&gt;=CurMonthStart,$B149&lt;=CurMonthEnd),$K149,0)</f>
         <v/>
       </c>
@@ -50680,7 +52885,8 @@
           <t>Monthly mortgage payment</t>
         </is>
       </c>
-      <c r="O150" s="40">
+      <c r="O150" s="38" t="n"/>
+      <c r="P150" s="40">
         <f>IF(AND($B150&gt;=CurMonthStart,$B150&lt;=CurMonthEnd),$K150,0)</f>
         <v/>
       </c>
@@ -50743,7 +52949,8 @@
         </is>
       </c>
       <c r="N151" s="38" t="inlineStr"/>
-      <c r="O151" s="40">
+      <c r="O151" s="38" t="n"/>
+      <c r="P151" s="40">
         <f>IF(AND($B151&gt;=CurMonthStart,$B151&lt;=CurMonthEnd),$K151,0)</f>
         <v/>
       </c>
@@ -50810,7 +53017,8 @@
           <t>Bulk groceries</t>
         </is>
       </c>
-      <c r="O152" s="40">
+      <c r="O152" s="38" t="n"/>
+      <c r="P152" s="40">
         <f>IF(AND($B152&gt;=CurMonthStart,$B152&lt;=CurMonthEnd),$K152,0)</f>
         <v/>
       </c>
@@ -50877,7 +53085,8 @@
           <t>Gas</t>
         </is>
       </c>
-      <c r="O153" s="40">
+      <c r="O153" s="38" t="n"/>
+      <c r="P153" s="40">
         <f>IF(AND($B153&gt;=CurMonthStart,$B153&lt;=CurMonthEnd),$K153,0)</f>
         <v/>
       </c>
@@ -50944,7 +53153,8 @@
           <t>Wiper blades / oil</t>
         </is>
       </c>
-      <c r="O154" s="40">
+      <c r="O154" s="38" t="n"/>
+      <c r="P154" s="40">
         <f>IF(AND($B154&gt;=CurMonthStart,$B154&lt;=CurMonthEnd),$K154,0)</f>
         <v/>
       </c>
@@ -51007,7 +53217,8 @@
         </is>
       </c>
       <c r="N155" s="38" t="inlineStr"/>
-      <c r="O155" s="40">
+      <c r="O155" s="38" t="n"/>
+      <c r="P155" s="40">
         <f>IF(AND($B155&gt;=CurMonthStart,$B155&lt;=CurMonthEnd),$K155,0)</f>
         <v/>
       </c>
@@ -51074,7 +53285,8 @@
           <t>Internet</t>
         </is>
       </c>
-      <c r="O156" s="40">
+      <c r="O156" s="38" t="n"/>
+      <c r="P156" s="40">
         <f>IF(AND($B156&gt;=CurMonthStart,$B156&lt;=CurMonthEnd),$K156,0)</f>
         <v/>
       </c>
@@ -51141,7 +53353,8 @@
           <t>Mobile phone</t>
         </is>
       </c>
-      <c r="O157" s="40">
+      <c r="O157" s="38" t="n"/>
+      <c r="P157" s="40">
         <f>IF(AND($B157&gt;=CurMonthStart,$B157&lt;=CurMonthEnd),$K157,0)</f>
         <v/>
       </c>
@@ -51208,7 +53421,8 @@
           <t>Auto + home insurance</t>
         </is>
       </c>
-      <c r="O158" s="40">
+      <c r="O158" s="38" t="n"/>
+      <c r="P158" s="40">
         <f>IF(AND($B158&gt;=CurMonthStart,$B158&lt;=CurMonthEnd),$K158,0)</f>
         <v/>
       </c>
@@ -51275,7 +53489,8 @@
           <t>Copay</t>
         </is>
       </c>
-      <c r="O159" s="40">
+      <c r="O159" s="38" t="n"/>
+      <c r="P159" s="40">
         <f>IF(AND($B159&gt;=CurMonthStart,$B159&lt;=CurMonthEnd),$K159,0)</f>
         <v/>
       </c>
@@ -51338,7 +53553,8 @@
         </is>
       </c>
       <c r="N160" s="38" t="inlineStr"/>
-      <c r="O160" s="40">
+      <c r="O160" s="38" t="n"/>
+      <c r="P160" s="40">
         <f>IF(AND($B160&gt;=CurMonthStart,$B160&lt;=CurMonthEnd),$K160,0)</f>
         <v/>
       </c>
@@ -51405,7 +53621,8 @@
           <t>Streaming subscription</t>
         </is>
       </c>
-      <c r="O161" s="40">
+      <c r="O161" s="38" t="n"/>
+      <c r="P161" s="40">
         <f>IF(AND($B161&gt;=CurMonthStart,$B161&lt;=CurMonthEnd),$K161,0)</f>
         <v/>
       </c>
@@ -51468,7 +53685,8 @@
         </is>
       </c>
       <c r="N162" s="38" t="inlineStr"/>
-      <c r="O162" s="40">
+      <c r="O162" s="38" t="n"/>
+      <c r="P162" s="40">
         <f>IF(AND($B162&gt;=CurMonthStart,$B162&lt;=CurMonthEnd),$K162,0)</f>
         <v/>
       </c>
@@ -51535,7 +53753,8 @@
           <t>Gym membership</t>
         </is>
       </c>
-      <c r="O163" s="40">
+      <c r="O163" s="38" t="n"/>
+      <c r="P163" s="40">
         <f>IF(AND($B163&gt;=CurMonthStart,$B163&lt;=CurMonthEnd),$K163,0)</f>
         <v/>
       </c>
@@ -51598,7 +53817,8 @@
         </is>
       </c>
       <c r="N164" s="38" t="inlineStr"/>
-      <c r="O164" s="40">
+      <c r="O164" s="38" t="n"/>
+      <c r="P164" s="40">
         <f>IF(AND($B164&gt;=CurMonthStart,$B164&lt;=CurMonthEnd),$K164,0)</f>
         <v/>
       </c>
@@ -51661,7 +53881,8 @@
         </is>
       </c>
       <c r="N165" s="38" t="inlineStr"/>
-      <c r="O165" s="40">
+      <c r="O165" s="38" t="n"/>
+      <c r="P165" s="40">
         <f>IF(AND($B165&gt;=CurMonthStart,$B165&lt;=CurMonthEnd),$K165,0)</f>
         <v/>
       </c>
@@ -51728,7 +53949,8 @@
           <t>Monthly mortgage payment</t>
         </is>
       </c>
-      <c r="O166" s="40">
+      <c r="O166" s="38" t="n"/>
+      <c r="P166" s="40">
         <f>IF(AND($B166&gt;=CurMonthStart,$B166&lt;=CurMonthEnd),$K166,0)</f>
         <v/>
       </c>
@@ -51791,7 +54013,8 @@
         </is>
       </c>
       <c r="N167" s="38" t="inlineStr"/>
-      <c r="O167" s="40">
+      <c r="O167" s="38" t="n"/>
+      <c r="P167" s="40">
         <f>IF(AND($B167&gt;=CurMonthStart,$B167&lt;=CurMonthEnd),$K167,0)</f>
         <v/>
       </c>
@@ -51858,7 +54081,8 @@
           <t>Bulk groceries</t>
         </is>
       </c>
-      <c r="O168" s="40">
+      <c r="O168" s="38" t="n"/>
+      <c r="P168" s="40">
         <f>IF(AND($B168&gt;=CurMonthStart,$B168&lt;=CurMonthEnd),$K168,0)</f>
         <v/>
       </c>
@@ -51925,7 +54149,8 @@
           <t>Gas</t>
         </is>
       </c>
-      <c r="O169" s="40">
+      <c r="O169" s="38" t="n"/>
+      <c r="P169" s="40">
         <f>IF(AND($B169&gt;=CurMonthStart,$B169&lt;=CurMonthEnd),$K169,0)</f>
         <v/>
       </c>
@@ -51992,7 +54217,8 @@
           <t>Wiper blades / oil</t>
         </is>
       </c>
-      <c r="O170" s="40">
+      <c r="O170" s="38" t="n"/>
+      <c r="P170" s="40">
         <f>IF(AND($B170&gt;=CurMonthStart,$B170&lt;=CurMonthEnd),$K170,0)</f>
         <v/>
       </c>
@@ -52055,7 +54281,8 @@
         </is>
       </c>
       <c r="N171" s="38" t="inlineStr"/>
-      <c r="O171" s="40">
+      <c r="O171" s="38" t="n"/>
+      <c r="P171" s="40">
         <f>IF(AND($B171&gt;=CurMonthStart,$B171&lt;=CurMonthEnd),$K171,0)</f>
         <v/>
       </c>
@@ -52122,7 +54349,8 @@
           <t>Internet</t>
         </is>
       </c>
-      <c r="O172" s="40">
+      <c r="O172" s="38" t="n"/>
+      <c r="P172" s="40">
         <f>IF(AND($B172&gt;=CurMonthStart,$B172&lt;=CurMonthEnd),$K172,0)</f>
         <v/>
       </c>
@@ -52189,7 +54417,8 @@
           <t>Mobile phone</t>
         </is>
       </c>
-      <c r="O173" s="40">
+      <c r="O173" s="38" t="n"/>
+      <c r="P173" s="40">
         <f>IF(AND($B173&gt;=CurMonthStart,$B173&lt;=CurMonthEnd),$K173,0)</f>
         <v/>
       </c>
@@ -52256,7 +54485,8 @@
           <t>Auto + home insurance</t>
         </is>
       </c>
-      <c r="O174" s="40">
+      <c r="O174" s="38" t="n"/>
+      <c r="P174" s="40">
         <f>IF(AND($B174&gt;=CurMonthStart,$B174&lt;=CurMonthEnd),$K174,0)</f>
         <v/>
       </c>
@@ -52323,7 +54553,8 @@
           <t>Copay</t>
         </is>
       </c>
-      <c r="O175" s="40">
+      <c r="O175" s="38" t="n"/>
+      <c r="P175" s="40">
         <f>IF(AND($B175&gt;=CurMonthStart,$B175&lt;=CurMonthEnd),$K175,0)</f>
         <v/>
       </c>
@@ -52386,7 +54617,8 @@
         </is>
       </c>
       <c r="N176" s="38" t="inlineStr"/>
-      <c r="O176" s="40">
+      <c r="O176" s="38" t="n"/>
+      <c r="P176" s="40">
         <f>IF(AND($B176&gt;=CurMonthStart,$B176&lt;=CurMonthEnd),$K176,0)</f>
         <v/>
       </c>
@@ -52453,7 +54685,8 @@
           <t>Streaming subscription</t>
         </is>
       </c>
-      <c r="O177" s="40">
+      <c r="O177" s="38" t="n"/>
+      <c r="P177" s="40">
         <f>IF(AND($B177&gt;=CurMonthStart,$B177&lt;=CurMonthEnd),$K177,0)</f>
         <v/>
       </c>
@@ -52516,7 +54749,8 @@
         </is>
       </c>
       <c r="N178" s="38" t="inlineStr"/>
-      <c r="O178" s="40">
+      <c r="O178" s="38" t="n"/>
+      <c r="P178" s="40">
         <f>IF(AND($B178&gt;=CurMonthStart,$B178&lt;=CurMonthEnd),$K178,0)</f>
         <v/>
       </c>
@@ -52583,7 +54817,8 @@
           <t>Gym membership</t>
         </is>
       </c>
-      <c r="O179" s="40">
+      <c r="O179" s="38" t="n"/>
+      <c r="P179" s="40">
         <f>IF(AND($B179&gt;=CurMonthStart,$B179&lt;=CurMonthEnd),$K179,0)</f>
         <v/>
       </c>
@@ -52646,7 +54881,8 @@
         </is>
       </c>
       <c r="N180" s="38" t="inlineStr"/>
-      <c r="O180" s="40">
+      <c r="O180" s="38" t="n"/>
+      <c r="P180" s="40">
         <f>IF(AND($B180&gt;=CurMonthStart,$B180&lt;=CurMonthEnd),$K180,0)</f>
         <v/>
       </c>
@@ -52709,7 +54945,8 @@
         </is>
       </c>
       <c r="N181" s="38" t="inlineStr"/>
-      <c r="O181" s="40">
+      <c r="O181" s="38" t="n"/>
+      <c r="P181" s="40">
         <f>IF(AND($B181&gt;=CurMonthStart,$B181&lt;=CurMonthEnd),$K181,0)</f>
         <v/>
       </c>
@@ -52776,7 +55013,8 @@
           <t>Monthly mortgage payment</t>
         </is>
       </c>
-      <c r="O182" s="40">
+      <c r="O182" s="38" t="n"/>
+      <c r="P182" s="40">
         <f>IF(AND($B182&gt;=CurMonthStart,$B182&lt;=CurMonthEnd),$K182,0)</f>
         <v/>
       </c>
@@ -52839,7 +55077,8 @@
         </is>
       </c>
       <c r="N183" s="38" t="inlineStr"/>
-      <c r="O183" s="40">
+      <c r="O183" s="38" t="n"/>
+      <c r="P183" s="40">
         <f>IF(AND($B183&gt;=CurMonthStart,$B183&lt;=CurMonthEnd),$K183,0)</f>
         <v/>
       </c>
@@ -52906,7 +55145,8 @@
           <t>Bulk groceries</t>
         </is>
       </c>
-      <c r="O184" s="40">
+      <c r="O184" s="38" t="n"/>
+      <c r="P184" s="40">
         <f>IF(AND($B184&gt;=CurMonthStart,$B184&lt;=CurMonthEnd),$K184,0)</f>
         <v/>
       </c>
@@ -52973,7 +55213,8 @@
           <t>Gas</t>
         </is>
       </c>
-      <c r="O185" s="40">
+      <c r="O185" s="38" t="n"/>
+      <c r="P185" s="40">
         <f>IF(AND($B185&gt;=CurMonthStart,$B185&lt;=CurMonthEnd),$K185,0)</f>
         <v/>
       </c>
@@ -53040,7 +55281,8 @@
           <t>Wiper blades / oil</t>
         </is>
       </c>
-      <c r="O186" s="40">
+      <c r="O186" s="38" t="n"/>
+      <c r="P186" s="40">
         <f>IF(AND($B186&gt;=CurMonthStart,$B186&lt;=CurMonthEnd),$K186,0)</f>
         <v/>
       </c>
@@ -53103,7 +55345,8 @@
         </is>
       </c>
       <c r="N187" s="38" t="inlineStr"/>
-      <c r="O187" s="40">
+      <c r="O187" s="38" t="n"/>
+      <c r="P187" s="40">
         <f>IF(AND($B187&gt;=CurMonthStart,$B187&lt;=CurMonthEnd),$K187,0)</f>
         <v/>
       </c>
@@ -53170,7 +55413,8 @@
           <t>Internet</t>
         </is>
       </c>
-      <c r="O188" s="40">
+      <c r="O188" s="38" t="n"/>
+      <c r="P188" s="40">
         <f>IF(AND($B188&gt;=CurMonthStart,$B188&lt;=CurMonthEnd),$K188,0)</f>
         <v/>
       </c>
@@ -53237,7 +55481,8 @@
           <t>Mobile phone</t>
         </is>
       </c>
-      <c r="O189" s="40">
+      <c r="O189" s="38" t="n"/>
+      <c r="P189" s="40">
         <f>IF(AND($B189&gt;=CurMonthStart,$B189&lt;=CurMonthEnd),$K189,0)</f>
         <v/>
       </c>
@@ -53304,7 +55549,8 @@
           <t>Auto + home insurance</t>
         </is>
       </c>
-      <c r="O190" s="40">
+      <c r="O190" s="38" t="n"/>
+      <c r="P190" s="40">
         <f>IF(AND($B190&gt;=CurMonthStart,$B190&lt;=CurMonthEnd),$K190,0)</f>
         <v/>
       </c>
@@ -53371,7 +55617,8 @@
           <t>Copay</t>
         </is>
       </c>
-      <c r="O191" s="40">
+      <c r="O191" s="38" t="n"/>
+      <c r="P191" s="40">
         <f>IF(AND($B191&gt;=CurMonthStart,$B191&lt;=CurMonthEnd),$K191,0)</f>
         <v/>
       </c>
@@ -53434,7 +55681,8 @@
         </is>
       </c>
       <c r="N192" s="38" t="inlineStr"/>
-      <c r="O192" s="40">
+      <c r="O192" s="38" t="n"/>
+      <c r="P192" s="40">
         <f>IF(AND($B192&gt;=CurMonthStart,$B192&lt;=CurMonthEnd),$K192,0)</f>
         <v/>
       </c>
@@ -53501,7 +55749,8 @@
           <t>Streaming subscription</t>
         </is>
       </c>
-      <c r="O193" s="40">
+      <c r="O193" s="38" t="n"/>
+      <c r="P193" s="40">
         <f>IF(AND($B193&gt;=CurMonthStart,$B193&lt;=CurMonthEnd),$K193,0)</f>
         <v/>
       </c>
@@ -53564,7 +55813,8 @@
         </is>
       </c>
       <c r="N194" s="38" t="inlineStr"/>
-      <c r="O194" s="40">
+      <c r="O194" s="38" t="n"/>
+      <c r="P194" s="40">
         <f>IF(AND($B194&gt;=CurMonthStart,$B194&lt;=CurMonthEnd),$K194,0)</f>
         <v/>
       </c>
@@ -53631,7 +55881,8 @@
           <t>Gym membership</t>
         </is>
       </c>
-      <c r="O195" s="40">
+      <c r="O195" s="38" t="n"/>
+      <c r="P195" s="40">
         <f>IF(AND($B195&gt;=CurMonthStart,$B195&lt;=CurMonthEnd),$K195,0)</f>
         <v/>
       </c>
@@ -53694,7 +55945,8 @@
         </is>
       </c>
       <c r="N196" s="38" t="inlineStr"/>
-      <c r="O196" s="40">
+      <c r="O196" s="38" t="n"/>
+      <c r="P196" s="40">
         <f>IF(AND($B196&gt;=CurMonthStart,$B196&lt;=CurMonthEnd),$K196,0)</f>
         <v/>
       </c>
@@ -53757,14 +56009,15 @@
         </is>
       </c>
       <c r="N197" s="38" t="inlineStr"/>
-      <c r="O197" s="40">
+      <c r="O197" s="38" t="n"/>
+      <c r="P197" s="40">
         <f>IF(AND($B197&gt;=CurMonthStart,$B197&lt;=CurMonthEnd),$K197,0)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:N2"/>
+    <mergeCell ref="A1:P2"/>
     <mergeCell ref="A4:P4"/>
   </mergeCells>
   <conditionalFormatting sqref="K6:K197">
@@ -53774,22 +56027,22 @@
   </conditionalFormatting>
   <dataValidations count="6">
     <dataValidation sqref="C6:C497" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Please choose a value from the dropdown list." type="list">
-      <formula1>=VendorNameList</formula1>
+      <formula1>VendorNameList</formula1>
     </dataValidation>
     <dataValidation sqref="E6:E497" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Please choose a value from the dropdown list." type="list">
-      <formula1>=ExpenseCategoryList</formula1>
+      <formula1>ExpenseCategoryList</formula1>
     </dataValidation>
     <dataValidation sqref="G6:G497" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Please choose a value from the dropdown list." type="list">
-      <formula1>=AccountNameList</formula1>
+      <formula1>AccountNameList</formula1>
     </dataValidation>
     <dataValidation sqref="I6:I497" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Please choose a value from the dropdown list." type="list">
-      <formula1>=PaymentMethodList</formula1>
+      <formula1>PaymentMethodList</formula1>
     </dataValidation>
     <dataValidation sqref="L6:L497" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Please choose a value from the dropdown list." type="list">
-      <formula1>=List_NeedWant</formula1>
+      <formula1>List_NeedWant</formula1>
     </dataValidation>
     <dataValidation sqref="M6:M497" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Please choose a value from the dropdown list." type="list">
-      <formula1>=List_YesNo</formula1>
+      <formula1>List_YesNo</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -54846,10 +57099,10 @@
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
     <dataValidation sqref="C18:C189" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Please choose a value from the dropdown list." type="list">
-      <formula1>=Dim_Goal[GoalName]</formula1>
+      <formula1>Dim_Goal[GoalName]</formula1>
     </dataValidation>
     <dataValidation sqref="E18:E189" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Please choose a value from the dropdown list." type="list">
-      <formula1>=AccountNameList</formula1>
+      <formula1>AccountNameList</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -55693,7 +57946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -56118,6 +58371,27 @@
         <v/>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="38" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" s="38" t="inlineStr">
+        <is>
+          <t>Other Income Source</t>
+        </is>
+      </c>
+      <c r="C23" s="38" t="n">
+        <v>12</v>
+      </c>
+      <c r="D23" s="40">
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B23,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <v/>
+      </c>
+      <c r="E23" s="40">
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B23,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A4:E4"/>

--- a/Personal Finance Dashboard/Personal Finance Intelligence Dashboard.xlsx
+++ b/Personal Finance Dashboard/Personal Finance Intelligence Dashboard.xlsx
@@ -37,7 +37,7 @@
     <definedName name="VendorNameList">Dim_Vendor[VendorName]</definedName>
     <definedName name="AccountNameList">Dim_Account[AccountName]</definedName>
     <definedName name="SourceNameList">Dim_Source[SourceName]</definedName>
-    <definedName name="SignConvention">'Bank Import'!$D$12</definedName>
+    <definedName name="SignConvention">'Bank Import'!$D$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1155,8 +1155,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BankImportRaw" displayName="BankImportRaw" ref="A15:K515" headerRowCount="1">
-  <autoFilter ref="A15:K515"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BankImportRaw" displayName="BankImportRaw" ref="A16:K516" headerRowCount="1">
+  <autoFilter ref="A16:K516"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="Description"/>
@@ -1742,14 +1742,14 @@
     </row>
     <row r="6">
       <c r="A6" s="7">
-        <f>SUMIFS(Fact_Income[NetAmount],Fact_Income[Date],"&gt;="&amp;CurMonthStart,Fact_Income[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Income[NetAmount],Fact_Income[Date],"&gt;="&amp;CurMonthStart,Fact_Income[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Income",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="B6" s="8" t="n"/>
       <c r="C6" s="8" t="n"/>
       <c r="D6" s="9" t="n"/>
       <c r="E6" s="10">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F6" s="8" t="n"/>
@@ -1931,7 +1931,7 @@
     <row r="69">
       <c r="A69" s="19" t="inlineStr">
         <is>
-          <t>Top Expenses (This Month)</t>
+          <t>Top Expenses (This Month, Expenses tab only)</t>
         </is>
       </c>
       <c r="E69" s="19" t="inlineStr">
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="M71" s="23">
-        <f>IFERROR(SUMIFS(Fact_Expenses[Amount],Fact_Expenses[NeedWantFlag],"Need")/SUM(Fact_Expenses[Amount]),0)</f>
+        <f>IFERROR((SUMIFS(Fact_Expenses[Amount],Fact_Expenses[NeedWantFlag],"Need")+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[NeedWantFlag],"Need",BankImportRaw[TransactionType],"Expense"))/(SUM(Fact_Expenses[Amount])+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Expense")),0)</f>
         <v/>
       </c>
     </row>
@@ -2057,7 +2057,7 @@
       </c>
       <c r="K72" s="21" t="inlineStr">
         <is>
-          <t>Recurring Spend / mo</t>
+          <t>Recurring Spend / mo (manual entries only)</t>
         </is>
       </c>
       <c r="M72" s="24">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="D78" s="19" t="inlineStr">
         <is>
-          <t>Recent Transactions</t>
+          <t>Recent Transactions (Expenses tab only)</t>
         </is>
       </c>
     </row>
@@ -2488,7 +2488,7 @@
         </is>
       </c>
       <c r="B93" s="27">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],"Dining &amp; Entertainment",Fact_Expenses[Date],"&gt;="&amp;EOMONTH(TodayDate,-2)+1,Fact_Expenses[Date],"&lt;="&amp;EOMONTH(TodayDate,-1))</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],"Dining &amp; Entertainment",Fact_Expenses[Date],"&gt;="&amp;EOMONTH(TodayDate,-2)+1,Fact_Expenses[Date],"&lt;="&amp;EOMONTH(TodayDate,-1))+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],"Dining &amp; Entertainment",BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;EOMONTH(TodayDate,-2)+1,BankImportRaw[Date],"&lt;="&amp;EOMONTH(TodayDate,-1))</f>
         <v/>
       </c>
       <c r="C93" s="27">
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="B94" s="27">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],"Shopping",Fact_Expenses[Date],"&gt;="&amp;EOMONTH(TodayDate,-2)+1,Fact_Expenses[Date],"&lt;="&amp;EOMONTH(TodayDate,-1))</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],"Shopping",Fact_Expenses[Date],"&gt;="&amp;EOMONTH(TodayDate,-2)+1,Fact_Expenses[Date],"&lt;="&amp;EOMONTH(TodayDate,-1))+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],"Shopping",BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;EOMONTH(TodayDate,-2)+1,BankImportRaw[Date],"&lt;="&amp;EOMONTH(TodayDate,-1))</f>
         <v/>
       </c>
       <c r="C94" s="27">
@@ -2542,7 +2542,7 @@
         </is>
       </c>
       <c r="B95" s="27">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],"Personal Care",Fact_Expenses[Date],"&gt;="&amp;EOMONTH(TodayDate,-2)+1,Fact_Expenses[Date],"&lt;="&amp;EOMONTH(TodayDate,-1))</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],"Personal Care",Fact_Expenses[Date],"&gt;="&amp;EOMONTH(TodayDate,-2)+1,Fact_Expenses[Date],"&lt;="&amp;EOMONTH(TodayDate,-1))+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],"Personal Care",BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;EOMONTH(TodayDate,-2)+1,BankImportRaw[Date],"&lt;="&amp;EOMONTH(TodayDate,-1))</f>
         <v/>
       </c>
       <c r="C95" s="27">
@@ -2569,7 +2569,7 @@
         </is>
       </c>
       <c r="B96" s="27">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[NeedWantFlag],"Want",Fact_Expenses[Date],"&gt;="&amp;EOMONTH(TodayDate,-2)+1,Fact_Expenses[Date],"&lt;="&amp;EOMONTH(TodayDate,-1))</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[NeedWantFlag],"Want",Fact_Expenses[Date],"&gt;="&amp;EOMONTH(TodayDate,-2)+1,Fact_Expenses[Date],"&lt;="&amp;EOMONTH(TodayDate,-1))+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[NeedWantFlag],"Want",BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;EOMONTH(TodayDate,-2)+1,BankImportRaw[Date],"&lt;="&amp;EOMONTH(TodayDate,-1))</f>
         <v/>
       </c>
       <c r="C96" s="27">
@@ -30522,11 +30522,11 @@
         <v/>
       </c>
       <c r="C2" s="48">
-        <f>SUMIFS(Fact_Income[NetAmount],Fact_Income[Date],"&gt;="&amp;EOMONTH(A2,-1)+1,Fact_Income[Date],"&lt;="&amp;B2)</f>
+        <f>SUMIFS(Fact_Income[NetAmount],Fact_Income[Date],"&gt;="&amp;EOMONTH(A2,-1)+1,Fact_Income[Date],"&lt;="&amp;B2)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Income",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A2,-1)+1,BankImportRaw[Date],"&lt;="&amp;B2)</f>
         <v/>
       </c>
       <c r="D2" s="48">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;EOMONTH(A2,-1)+1,Fact_Expenses[Date],"&lt;="&amp;B2)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;EOMONTH(A2,-1)+1,Fact_Expenses[Date],"&lt;="&amp;B2)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A2,-1)+1,BankImportRaw[Date],"&lt;="&amp;B2)</f>
         <v/>
       </c>
       <c r="E2" s="48">
@@ -30548,11 +30548,11 @@
         <v/>
       </c>
       <c r="C3" s="48">
-        <f>SUMIFS(Fact_Income[NetAmount],Fact_Income[Date],"&gt;="&amp;EOMONTH(A3,-1)+1,Fact_Income[Date],"&lt;="&amp;B3)</f>
+        <f>SUMIFS(Fact_Income[NetAmount],Fact_Income[Date],"&gt;="&amp;EOMONTH(A3,-1)+1,Fact_Income[Date],"&lt;="&amp;B3)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Income",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A3,-1)+1,BankImportRaw[Date],"&lt;="&amp;B3)</f>
         <v/>
       </c>
       <c r="D3" s="48">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;EOMONTH(A3,-1)+1,Fact_Expenses[Date],"&lt;="&amp;B3)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;EOMONTH(A3,-1)+1,Fact_Expenses[Date],"&lt;="&amp;B3)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A3,-1)+1,BankImportRaw[Date],"&lt;="&amp;B3)</f>
         <v/>
       </c>
       <c r="E3" s="48">
@@ -30574,11 +30574,11 @@
         <v/>
       </c>
       <c r="C4" s="48">
-        <f>SUMIFS(Fact_Income[NetAmount],Fact_Income[Date],"&gt;="&amp;EOMONTH(A4,-1)+1,Fact_Income[Date],"&lt;="&amp;B4)</f>
+        <f>SUMIFS(Fact_Income[NetAmount],Fact_Income[Date],"&gt;="&amp;EOMONTH(A4,-1)+1,Fact_Income[Date],"&lt;="&amp;B4)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Income",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A4,-1)+1,BankImportRaw[Date],"&lt;="&amp;B4)</f>
         <v/>
       </c>
       <c r="D4" s="48">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;EOMONTH(A4,-1)+1,Fact_Expenses[Date],"&lt;="&amp;B4)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;EOMONTH(A4,-1)+1,Fact_Expenses[Date],"&lt;="&amp;B4)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A4,-1)+1,BankImportRaw[Date],"&lt;="&amp;B4)</f>
         <v/>
       </c>
       <c r="E4" s="48">
@@ -30600,11 +30600,11 @@
         <v/>
       </c>
       <c r="C5" s="48">
-        <f>SUMIFS(Fact_Income[NetAmount],Fact_Income[Date],"&gt;="&amp;EOMONTH(A5,-1)+1,Fact_Income[Date],"&lt;="&amp;B5)</f>
+        <f>SUMIFS(Fact_Income[NetAmount],Fact_Income[Date],"&gt;="&amp;EOMONTH(A5,-1)+1,Fact_Income[Date],"&lt;="&amp;B5)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Income",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A5,-1)+1,BankImportRaw[Date],"&lt;="&amp;B5)</f>
         <v/>
       </c>
       <c r="D5" s="48">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;EOMONTH(A5,-1)+1,Fact_Expenses[Date],"&lt;="&amp;B5)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;EOMONTH(A5,-1)+1,Fact_Expenses[Date],"&lt;="&amp;B5)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A5,-1)+1,BankImportRaw[Date],"&lt;="&amp;B5)</f>
         <v/>
       </c>
       <c r="E5" s="48">
@@ -30626,11 +30626,11 @@
         <v/>
       </c>
       <c r="C6" s="48">
-        <f>SUMIFS(Fact_Income[NetAmount],Fact_Income[Date],"&gt;="&amp;EOMONTH(A6,-1)+1,Fact_Income[Date],"&lt;="&amp;B6)</f>
+        <f>SUMIFS(Fact_Income[NetAmount],Fact_Income[Date],"&gt;="&amp;EOMONTH(A6,-1)+1,Fact_Income[Date],"&lt;="&amp;B6)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Income",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A6,-1)+1,BankImportRaw[Date],"&lt;="&amp;B6)</f>
         <v/>
       </c>
       <c r="D6" s="48">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;EOMONTH(A6,-1)+1,Fact_Expenses[Date],"&lt;="&amp;B6)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;EOMONTH(A6,-1)+1,Fact_Expenses[Date],"&lt;="&amp;B6)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A6,-1)+1,BankImportRaw[Date],"&lt;="&amp;B6)</f>
         <v/>
       </c>
       <c r="E6" s="48">
@@ -30652,11 +30652,11 @@
         <v/>
       </c>
       <c r="C7" s="48">
-        <f>SUMIFS(Fact_Income[NetAmount],Fact_Income[Date],"&gt;="&amp;EOMONTH(A7,-1)+1,Fact_Income[Date],"&lt;="&amp;B7)</f>
+        <f>SUMIFS(Fact_Income[NetAmount],Fact_Income[Date],"&gt;="&amp;EOMONTH(A7,-1)+1,Fact_Income[Date],"&lt;="&amp;B7)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Income",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A7,-1)+1,BankImportRaw[Date],"&lt;="&amp;B7)</f>
         <v/>
       </c>
       <c r="D7" s="48">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;EOMONTH(A7,-1)+1,Fact_Expenses[Date],"&lt;="&amp;B7)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;EOMONTH(A7,-1)+1,Fact_Expenses[Date],"&lt;="&amp;B7)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A7,-1)+1,BankImportRaw[Date],"&lt;="&amp;B7)</f>
         <v/>
       </c>
       <c r="E7" s="48">
@@ -30678,11 +30678,11 @@
         <v/>
       </c>
       <c r="C8" s="48">
-        <f>SUMIFS(Fact_Income[NetAmount],Fact_Income[Date],"&gt;="&amp;EOMONTH(A8,-1)+1,Fact_Income[Date],"&lt;="&amp;B8)</f>
+        <f>SUMIFS(Fact_Income[NetAmount],Fact_Income[Date],"&gt;="&amp;EOMONTH(A8,-1)+1,Fact_Income[Date],"&lt;="&amp;B8)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Income",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A8,-1)+1,BankImportRaw[Date],"&lt;="&amp;B8)</f>
         <v/>
       </c>
       <c r="D8" s="48">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;EOMONTH(A8,-1)+1,Fact_Expenses[Date],"&lt;="&amp;B8)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;EOMONTH(A8,-1)+1,Fact_Expenses[Date],"&lt;="&amp;B8)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A8,-1)+1,BankImportRaw[Date],"&lt;="&amp;B8)</f>
         <v/>
       </c>
       <c r="E8" s="48">
@@ -30704,11 +30704,11 @@
         <v/>
       </c>
       <c r="C9" s="48">
-        <f>SUMIFS(Fact_Income[NetAmount],Fact_Income[Date],"&gt;="&amp;EOMONTH(A9,-1)+1,Fact_Income[Date],"&lt;="&amp;B9)</f>
+        <f>SUMIFS(Fact_Income[NetAmount],Fact_Income[Date],"&gt;="&amp;EOMONTH(A9,-1)+1,Fact_Income[Date],"&lt;="&amp;B9)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Income",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A9,-1)+1,BankImportRaw[Date],"&lt;="&amp;B9)</f>
         <v/>
       </c>
       <c r="D9" s="48">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;EOMONTH(A9,-1)+1,Fact_Expenses[Date],"&lt;="&amp;B9)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;EOMONTH(A9,-1)+1,Fact_Expenses[Date],"&lt;="&amp;B9)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A9,-1)+1,BankImportRaw[Date],"&lt;="&amp;B9)</f>
         <v/>
       </c>
       <c r="E9" s="48">
@@ -30730,11 +30730,11 @@
         <v/>
       </c>
       <c r="C10" s="48">
-        <f>SUMIFS(Fact_Income[NetAmount],Fact_Income[Date],"&gt;="&amp;EOMONTH(A10,-1)+1,Fact_Income[Date],"&lt;="&amp;B10)</f>
+        <f>SUMIFS(Fact_Income[NetAmount],Fact_Income[Date],"&gt;="&amp;EOMONTH(A10,-1)+1,Fact_Income[Date],"&lt;="&amp;B10)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Income",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A10,-1)+1,BankImportRaw[Date],"&lt;="&amp;B10)</f>
         <v/>
       </c>
       <c r="D10" s="48">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;EOMONTH(A10,-1)+1,Fact_Expenses[Date],"&lt;="&amp;B10)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;EOMONTH(A10,-1)+1,Fact_Expenses[Date],"&lt;="&amp;B10)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A10,-1)+1,BankImportRaw[Date],"&lt;="&amp;B10)</f>
         <v/>
       </c>
       <c r="E10" s="48">
@@ -30756,11 +30756,11 @@
         <v/>
       </c>
       <c r="C11" s="48">
-        <f>SUMIFS(Fact_Income[NetAmount],Fact_Income[Date],"&gt;="&amp;EOMONTH(A11,-1)+1,Fact_Income[Date],"&lt;="&amp;B11)</f>
+        <f>SUMIFS(Fact_Income[NetAmount],Fact_Income[Date],"&gt;="&amp;EOMONTH(A11,-1)+1,Fact_Income[Date],"&lt;="&amp;B11)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Income",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A11,-1)+1,BankImportRaw[Date],"&lt;="&amp;B11)</f>
         <v/>
       </c>
       <c r="D11" s="48">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;EOMONTH(A11,-1)+1,Fact_Expenses[Date],"&lt;="&amp;B11)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;EOMONTH(A11,-1)+1,Fact_Expenses[Date],"&lt;="&amp;B11)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A11,-1)+1,BankImportRaw[Date],"&lt;="&amp;B11)</f>
         <v/>
       </c>
       <c r="E11" s="48">
@@ -30782,11 +30782,11 @@
         <v/>
       </c>
       <c r="C12" s="48">
-        <f>SUMIFS(Fact_Income[NetAmount],Fact_Income[Date],"&gt;="&amp;EOMONTH(A12,-1)+1,Fact_Income[Date],"&lt;="&amp;B12)</f>
+        <f>SUMIFS(Fact_Income[NetAmount],Fact_Income[Date],"&gt;="&amp;EOMONTH(A12,-1)+1,Fact_Income[Date],"&lt;="&amp;B12)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Income",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A12,-1)+1,BankImportRaw[Date],"&lt;="&amp;B12)</f>
         <v/>
       </c>
       <c r="D12" s="48">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;EOMONTH(A12,-1)+1,Fact_Expenses[Date],"&lt;="&amp;B12)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;EOMONTH(A12,-1)+1,Fact_Expenses[Date],"&lt;="&amp;B12)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A12,-1)+1,BankImportRaw[Date],"&lt;="&amp;B12)</f>
         <v/>
       </c>
       <c r="E12" s="48">
@@ -30808,11 +30808,11 @@
         <v/>
       </c>
       <c r="C13" s="48">
-        <f>SUMIFS(Fact_Income[NetAmount],Fact_Income[Date],"&gt;="&amp;EOMONTH(A13,-1)+1,Fact_Income[Date],"&lt;="&amp;B13)</f>
+        <f>SUMIFS(Fact_Income[NetAmount],Fact_Income[Date],"&gt;="&amp;EOMONTH(A13,-1)+1,Fact_Income[Date],"&lt;="&amp;B13)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Income",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A13,-1)+1,BankImportRaw[Date],"&lt;="&amp;B13)</f>
         <v/>
       </c>
       <c r="D13" s="48">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;EOMONTH(A13,-1)+1,Fact_Expenses[Date],"&lt;="&amp;B13)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;EOMONTH(A13,-1)+1,Fact_Expenses[Date],"&lt;="&amp;B13)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A13,-1)+1,BankImportRaw[Date],"&lt;="&amp;B13)</f>
         <v/>
       </c>
       <c r="E13" s="48">
@@ -30834,11 +30834,11 @@
         <v/>
       </c>
       <c r="C14" s="48">
-        <f>SUMIFS(Fact_Income[NetAmount],Fact_Income[Date],"&gt;="&amp;EOMONTH(A14,-1)+1,Fact_Income[Date],"&lt;="&amp;B14)</f>
+        <f>SUMIFS(Fact_Income[NetAmount],Fact_Income[Date],"&gt;="&amp;EOMONTH(A14,-1)+1,Fact_Income[Date],"&lt;="&amp;B14)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Income",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A14,-1)+1,BankImportRaw[Date],"&lt;="&amp;B14)</f>
         <v/>
       </c>
       <c r="D14" s="48">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;EOMONTH(A14,-1)+1,Fact_Expenses[Date],"&lt;="&amp;B14)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;EOMONTH(A14,-1)+1,Fact_Expenses[Date],"&lt;="&amp;B14)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A14,-1)+1,BankImportRaw[Date],"&lt;="&amp;B14)</f>
         <v/>
       </c>
       <c r="E14" s="48">
@@ -31131,7 +31131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K515"/>
+  <dimension ref="A1:K516"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -31194,7 +31194,7 @@
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="31" t="inlineStr">
         <is>
-          <t>2. Open that CSV, copy its Date / Description / Amount columns, and paste them into columns A, B, C of the table below (the first blank row right under the header row) — paste values only (Home &gt; Paste &gt; Values) so formatting doesn't fight the table.</t>
+          <t>2. Open that CSV, copy its Date / Description / Amount columns, and paste them into columns A, B, C of the table below — into the first blank row, not over existing rows — paste values only (Home &gt; Paste &gt; Values) so formatting doesn't fight the table.</t>
         </is>
       </c>
     </row>
@@ -31208,14 +31208,14 @@
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="31" t="inlineStr">
         <is>
-          <t>4. Column D (Vendor) tries to auto-fill itself from any past import where you picked a vendor for that exact same bank description — if it's blank (new or slightly different wording), pick a Vendor from the dropdown. Category (E) then auto-fills from that vendor's default category; override it if needed.</t>
+          <t>4. Column D (Vendor) tries to auto-fill itself from any earlier row in this tab with the exact same bank description — if it's blank (new or slightly different wording), pick a Vendor from the dropdown. Category (E) then auto-fills from that vendor's default category; override it if needed.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="31" t="inlineStr">
         <is>
-          <t>5. Column H tells you Expense or Income and column I gives the positive amount to enter. Copy the finished rows — including column B (Description) — into the Expenses tab (or Income tab for deposits/paychecks), matching them to that tab's Description column: this is what lets column D recognize the same transaction next time. Then delete the pasted rows here so this stays a scratch area for the next import.</t>
+          <t>That's it — every row here counts immediately in the Dashboard KPIs, charts, Budget, and Vendor totals. There's no copy step: this tab IS the ledger for bank-derived transactions, the same way Expenses/Income are the ledger for anything you enter by hand. Don't delete rows after importing — deleting a row removes that transaction from every report.</t>
         </is>
       </c>
     </row>
@@ -31226,122 +31226,109 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="40" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>Note: the Dashboard's 'Top Expenses' and 'Recent Transactions' widgets only look at the Expenses tab (a limitation of ranking individual transactions across two separate tables) — everything else (KPIs, Budget, Vendor totals, charts, Cut-Back Analyzer) includes this tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>Sign Convention for this import:</t>
         </is>
       </c>
-      <c r="D12" s="34" t="inlineStr">
+      <c r="D13" s="34" t="inlineStr">
         <is>
           <t>Negative = Expense</t>
         </is>
       </c>
-      <c r="E12" s="35" t="inlineStr">
+      <c r="E13" s="35" t="inlineStr">
         <is>
           <t>Most bank/debit exports show purchases as negative numbers (“Negative = Expense”). Most credit-card exports show charges as positive numbers and payments as negative (“Positive = Expense”). Check one real row against your bank statement to confirm.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="26" t="inlineStr">
-        <is>
-          <t>Paste your CSV's Date / Description / Amount into columns A-C — Vendor (D) auto-fills from past imports when it recognizes the description</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n"/>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n"/>
-      <c r="E14" s="2" t="n"/>
-      <c r="F14" s="2" t="n"/>
-      <c r="G14" s="2" t="n"/>
-      <c r="H14" s="2" t="n"/>
-      <c r="I14" s="2" t="n"/>
-      <c r="J14" s="2" t="n"/>
-      <c r="K14" s="2" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="36" t="inlineStr">
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t>Paste your CSV's Date / Description / Amount into columns A-C — Vendor (D) auto-fills from earlier rows when it recognizes the description</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="2" t="n"/>
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2" t="n"/>
+      <c r="J15" s="2" t="n"/>
+      <c r="K15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B15" s="36" t="inlineStr">
+      <c r="B16" s="36" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C15" s="36" t="inlineStr">
+      <c r="C16" s="36" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="D15" s="36" t="inlineStr">
+      <c r="D16" s="36" t="inlineStr">
         <is>
           <t>VendorName</t>
         </is>
       </c>
-      <c r="E15" s="36" t="inlineStr">
+      <c r="E16" s="36" t="inlineStr">
         <is>
           <t>CategoryName</t>
         </is>
       </c>
-      <c r="F15" s="36" t="inlineStr">
+      <c r="F16" s="36" t="inlineStr">
         <is>
           <t>AccountName</t>
         </is>
       </c>
-      <c r="G15" s="36" t="inlineStr">
+      <c r="G16" s="36" t="inlineStr">
         <is>
           <t>PaymentMethod</t>
         </is>
       </c>
-      <c r="H15" s="36" t="inlineStr">
+      <c r="H16" s="36" t="inlineStr">
         <is>
           <t>TransactionType</t>
         </is>
       </c>
-      <c r="I15" s="36" t="inlineStr">
+      <c r="I16" s="36" t="inlineStr">
         <is>
           <t>AbsAmount</t>
         </is>
       </c>
-      <c r="J15" s="36" t="inlineStr">
+      <c r="J16" s="36" t="inlineStr">
         <is>
           <t>NeedWantFlag</t>
         </is>
       </c>
-      <c r="K15" s="36" t="inlineStr">
+      <c r="K16" s="36" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="37" t="n"/>
-      <c r="C16" s="27" t="n"/>
-      <c r="D16">
-        <f>IF($B16="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B16,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B16,Fact_Income[Description],0)),"")))</f>
-        <v/>
-      </c>
-      <c r="E16">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D16,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
-        <v/>
-      </c>
-      <c r="H16">
-        <f>IF($C16="","",IF(SignConvention="Negative = Expense",IF($C16&lt;0,"Expense","Income"),IF($C16&gt;0,"Expense","Income")))</f>
-        <v/>
-      </c>
-      <c r="I16" s="27">
-        <f>IF($C16="","",ABS($C16))</f>
-        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="37" t="n"/>
       <c r="C17" s="27" t="n"/>
       <c r="D17">
-        <f>IF($B17="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B17,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B17,Fact_Income[Description],0)),"")))</f>
+        <f>""</f>
         <v/>
       </c>
       <c r="E17">
@@ -31361,7 +31348,7 @@
       <c r="A18" s="37" t="n"/>
       <c r="C18" s="27" t="n"/>
       <c r="D18">
-        <f>IF($B18="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B18,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B18,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B18="","",IFERROR(INDEX($D$17:$D$17,MATCH($B18,$B$17:$B$17,0)),""))</f>
         <v/>
       </c>
       <c r="E18">
@@ -31381,7 +31368,7 @@
       <c r="A19" s="37" t="n"/>
       <c r="C19" s="27" t="n"/>
       <c r="D19">
-        <f>IF($B19="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B19,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B19,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B19="","",IFERROR(INDEX($D$17:$D$18,MATCH($B19,$B$17:$B$18,0)),""))</f>
         <v/>
       </c>
       <c r="E19">
@@ -31401,7 +31388,7 @@
       <c r="A20" s="37" t="n"/>
       <c r="C20" s="27" t="n"/>
       <c r="D20">
-        <f>IF($B20="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B20,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B20,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B20="","",IFERROR(INDEX($D$17:$D$19,MATCH($B20,$B$17:$B$19,0)),""))</f>
         <v/>
       </c>
       <c r="E20">
@@ -31421,7 +31408,7 @@
       <c r="A21" s="37" t="n"/>
       <c r="C21" s="27" t="n"/>
       <c r="D21">
-        <f>IF($B21="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B21,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B21,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B21="","",IFERROR(INDEX($D$17:$D$20,MATCH($B21,$B$17:$B$20,0)),""))</f>
         <v/>
       </c>
       <c r="E21">
@@ -31441,7 +31428,7 @@
       <c r="A22" s="37" t="n"/>
       <c r="C22" s="27" t="n"/>
       <c r="D22">
-        <f>IF($B22="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B22,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B22,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B22="","",IFERROR(INDEX($D$17:$D$21,MATCH($B22,$B$17:$B$21,0)),""))</f>
         <v/>
       </c>
       <c r="E22">
@@ -31461,7 +31448,7 @@
       <c r="A23" s="37" t="n"/>
       <c r="C23" s="27" t="n"/>
       <c r="D23">
-        <f>IF($B23="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B23,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B23,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B23="","",IFERROR(INDEX($D$17:$D$22,MATCH($B23,$B$17:$B$22,0)),""))</f>
         <v/>
       </c>
       <c r="E23">
@@ -31481,7 +31468,7 @@
       <c r="A24" s="37" t="n"/>
       <c r="C24" s="27" t="n"/>
       <c r="D24">
-        <f>IF($B24="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B24,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B24,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B24="","",IFERROR(INDEX($D$17:$D$23,MATCH($B24,$B$17:$B$23,0)),""))</f>
         <v/>
       </c>
       <c r="E24">
@@ -31501,7 +31488,7 @@
       <c r="A25" s="37" t="n"/>
       <c r="C25" s="27" t="n"/>
       <c r="D25">
-        <f>IF($B25="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B25,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B25,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B25="","",IFERROR(INDEX($D$17:$D$24,MATCH($B25,$B$17:$B$24,0)),""))</f>
         <v/>
       </c>
       <c r="E25">
@@ -31521,7 +31508,7 @@
       <c r="A26" s="37" t="n"/>
       <c r="C26" s="27" t="n"/>
       <c r="D26">
-        <f>IF($B26="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B26,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B26,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B26="","",IFERROR(INDEX($D$17:$D$25,MATCH($B26,$B$17:$B$25,0)),""))</f>
         <v/>
       </c>
       <c r="E26">
@@ -31541,7 +31528,7 @@
       <c r="A27" s="37" t="n"/>
       <c r="C27" s="27" t="n"/>
       <c r="D27">
-        <f>IF($B27="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B27,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B27,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B27="","",IFERROR(INDEX($D$17:$D$26,MATCH($B27,$B$17:$B$26,0)),""))</f>
         <v/>
       </c>
       <c r="E27">
@@ -31561,7 +31548,7 @@
       <c r="A28" s="37" t="n"/>
       <c r="C28" s="27" t="n"/>
       <c r="D28">
-        <f>IF($B28="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B28,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B28,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B28="","",IFERROR(INDEX($D$17:$D$27,MATCH($B28,$B$17:$B$27,0)),""))</f>
         <v/>
       </c>
       <c r="E28">
@@ -31581,7 +31568,7 @@
       <c r="A29" s="37" t="n"/>
       <c r="C29" s="27" t="n"/>
       <c r="D29">
-        <f>IF($B29="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B29,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B29,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B29="","",IFERROR(INDEX($D$17:$D$28,MATCH($B29,$B$17:$B$28,0)),""))</f>
         <v/>
       </c>
       <c r="E29">
@@ -31601,7 +31588,7 @@
       <c r="A30" s="37" t="n"/>
       <c r="C30" s="27" t="n"/>
       <c r="D30">
-        <f>IF($B30="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B30,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B30,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B30="","",IFERROR(INDEX($D$17:$D$29,MATCH($B30,$B$17:$B$29,0)),""))</f>
         <v/>
       </c>
       <c r="E30">
@@ -31621,7 +31608,7 @@
       <c r="A31" s="37" t="n"/>
       <c r="C31" s="27" t="n"/>
       <c r="D31">
-        <f>IF($B31="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B31,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B31,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B31="","",IFERROR(INDEX($D$17:$D$30,MATCH($B31,$B$17:$B$30,0)),""))</f>
         <v/>
       </c>
       <c r="E31">
@@ -31641,7 +31628,7 @@
       <c r="A32" s="37" t="n"/>
       <c r="C32" s="27" t="n"/>
       <c r="D32">
-        <f>IF($B32="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B32,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B32,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B32="","",IFERROR(INDEX($D$17:$D$31,MATCH($B32,$B$17:$B$31,0)),""))</f>
         <v/>
       </c>
       <c r="E32">
@@ -31661,7 +31648,7 @@
       <c r="A33" s="37" t="n"/>
       <c r="C33" s="27" t="n"/>
       <c r="D33">
-        <f>IF($B33="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B33,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B33,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B33="","",IFERROR(INDEX($D$17:$D$32,MATCH($B33,$B$17:$B$32,0)),""))</f>
         <v/>
       </c>
       <c r="E33">
@@ -31681,7 +31668,7 @@
       <c r="A34" s="37" t="n"/>
       <c r="C34" s="27" t="n"/>
       <c r="D34">
-        <f>IF($B34="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B34,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B34,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B34="","",IFERROR(INDEX($D$17:$D$33,MATCH($B34,$B$17:$B$33,0)),""))</f>
         <v/>
       </c>
       <c r="E34">
@@ -31701,7 +31688,7 @@
       <c r="A35" s="37" t="n"/>
       <c r="C35" s="27" t="n"/>
       <c r="D35">
-        <f>IF($B35="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B35,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B35,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B35="","",IFERROR(INDEX($D$17:$D$34,MATCH($B35,$B$17:$B$34,0)),""))</f>
         <v/>
       </c>
       <c r="E35">
@@ -31721,7 +31708,7 @@
       <c r="A36" s="37" t="n"/>
       <c r="C36" s="27" t="n"/>
       <c r="D36">
-        <f>IF($B36="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B36,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B36,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B36="","",IFERROR(INDEX($D$17:$D$35,MATCH($B36,$B$17:$B$35,0)),""))</f>
         <v/>
       </c>
       <c r="E36">
@@ -31741,7 +31728,7 @@
       <c r="A37" s="37" t="n"/>
       <c r="C37" s="27" t="n"/>
       <c r="D37">
-        <f>IF($B37="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B37,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B37,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B37="","",IFERROR(INDEX($D$17:$D$36,MATCH($B37,$B$17:$B$36,0)),""))</f>
         <v/>
       </c>
       <c r="E37">
@@ -31761,7 +31748,7 @@
       <c r="A38" s="37" t="n"/>
       <c r="C38" s="27" t="n"/>
       <c r="D38">
-        <f>IF($B38="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B38,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B38,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B38="","",IFERROR(INDEX($D$17:$D$37,MATCH($B38,$B$17:$B$37,0)),""))</f>
         <v/>
       </c>
       <c r="E38">
@@ -31781,7 +31768,7 @@
       <c r="A39" s="37" t="n"/>
       <c r="C39" s="27" t="n"/>
       <c r="D39">
-        <f>IF($B39="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B39,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B39,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B39="","",IFERROR(INDEX($D$17:$D$38,MATCH($B39,$B$17:$B$38,0)),""))</f>
         <v/>
       </c>
       <c r="E39">
@@ -31801,7 +31788,7 @@
       <c r="A40" s="37" t="n"/>
       <c r="C40" s="27" t="n"/>
       <c r="D40">
-        <f>IF($B40="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B40,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B40,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B40="","",IFERROR(INDEX($D$17:$D$39,MATCH($B40,$B$17:$B$39,0)),""))</f>
         <v/>
       </c>
       <c r="E40">
@@ -31821,7 +31808,7 @@
       <c r="A41" s="37" t="n"/>
       <c r="C41" s="27" t="n"/>
       <c r="D41">
-        <f>IF($B41="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B41,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B41,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B41="","",IFERROR(INDEX($D$17:$D$40,MATCH($B41,$B$17:$B$40,0)),""))</f>
         <v/>
       </c>
       <c r="E41">
@@ -31841,7 +31828,7 @@
       <c r="A42" s="37" t="n"/>
       <c r="C42" s="27" t="n"/>
       <c r="D42">
-        <f>IF($B42="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B42,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B42,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B42="","",IFERROR(INDEX($D$17:$D$41,MATCH($B42,$B$17:$B$41,0)),""))</f>
         <v/>
       </c>
       <c r="E42">
@@ -31861,7 +31848,7 @@
       <c r="A43" s="37" t="n"/>
       <c r="C43" s="27" t="n"/>
       <c r="D43">
-        <f>IF($B43="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B43,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B43,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B43="","",IFERROR(INDEX($D$17:$D$42,MATCH($B43,$B$17:$B$42,0)),""))</f>
         <v/>
       </c>
       <c r="E43">
@@ -31881,7 +31868,7 @@
       <c r="A44" s="37" t="n"/>
       <c r="C44" s="27" t="n"/>
       <c r="D44">
-        <f>IF($B44="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B44,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B44,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B44="","",IFERROR(INDEX($D$17:$D$43,MATCH($B44,$B$17:$B$43,0)),""))</f>
         <v/>
       </c>
       <c r="E44">
@@ -31901,7 +31888,7 @@
       <c r="A45" s="37" t="n"/>
       <c r="C45" s="27" t="n"/>
       <c r="D45">
-        <f>IF($B45="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B45,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B45,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B45="","",IFERROR(INDEX($D$17:$D$44,MATCH($B45,$B$17:$B$44,0)),""))</f>
         <v/>
       </c>
       <c r="E45">
@@ -31921,7 +31908,7 @@
       <c r="A46" s="37" t="n"/>
       <c r="C46" s="27" t="n"/>
       <c r="D46">
-        <f>IF($B46="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B46,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B46,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B46="","",IFERROR(INDEX($D$17:$D$45,MATCH($B46,$B$17:$B$45,0)),""))</f>
         <v/>
       </c>
       <c r="E46">
@@ -31941,7 +31928,7 @@
       <c r="A47" s="37" t="n"/>
       <c r="C47" s="27" t="n"/>
       <c r="D47">
-        <f>IF($B47="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B47,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B47,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B47="","",IFERROR(INDEX($D$17:$D$46,MATCH($B47,$B$17:$B$46,0)),""))</f>
         <v/>
       </c>
       <c r="E47">
@@ -31961,7 +31948,7 @@
       <c r="A48" s="37" t="n"/>
       <c r="C48" s="27" t="n"/>
       <c r="D48">
-        <f>IF($B48="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B48,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B48,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B48="","",IFERROR(INDEX($D$17:$D$47,MATCH($B48,$B$17:$B$47,0)),""))</f>
         <v/>
       </c>
       <c r="E48">
@@ -31981,7 +31968,7 @@
       <c r="A49" s="37" t="n"/>
       <c r="C49" s="27" t="n"/>
       <c r="D49">
-        <f>IF($B49="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B49,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B49,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B49="","",IFERROR(INDEX($D$17:$D$48,MATCH($B49,$B$17:$B$48,0)),""))</f>
         <v/>
       </c>
       <c r="E49">
@@ -32001,7 +31988,7 @@
       <c r="A50" s="37" t="n"/>
       <c r="C50" s="27" t="n"/>
       <c r="D50">
-        <f>IF($B50="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B50,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B50,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B50="","",IFERROR(INDEX($D$17:$D$49,MATCH($B50,$B$17:$B$49,0)),""))</f>
         <v/>
       </c>
       <c r="E50">
@@ -32021,7 +32008,7 @@
       <c r="A51" s="37" t="n"/>
       <c r="C51" s="27" t="n"/>
       <c r="D51">
-        <f>IF($B51="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B51,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B51,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B51="","",IFERROR(INDEX($D$17:$D$50,MATCH($B51,$B$17:$B$50,0)),""))</f>
         <v/>
       </c>
       <c r="E51">
@@ -32041,7 +32028,7 @@
       <c r="A52" s="37" t="n"/>
       <c r="C52" s="27" t="n"/>
       <c r="D52">
-        <f>IF($B52="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B52,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B52,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B52="","",IFERROR(INDEX($D$17:$D$51,MATCH($B52,$B$17:$B$51,0)),""))</f>
         <v/>
       </c>
       <c r="E52">
@@ -32061,7 +32048,7 @@
       <c r="A53" s="37" t="n"/>
       <c r="C53" s="27" t="n"/>
       <c r="D53">
-        <f>IF($B53="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B53,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B53,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B53="","",IFERROR(INDEX($D$17:$D$52,MATCH($B53,$B$17:$B$52,0)),""))</f>
         <v/>
       </c>
       <c r="E53">
@@ -32081,7 +32068,7 @@
       <c r="A54" s="37" t="n"/>
       <c r="C54" s="27" t="n"/>
       <c r="D54">
-        <f>IF($B54="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B54,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B54,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B54="","",IFERROR(INDEX($D$17:$D$53,MATCH($B54,$B$17:$B$53,0)),""))</f>
         <v/>
       </c>
       <c r="E54">
@@ -32101,7 +32088,7 @@
       <c r="A55" s="37" t="n"/>
       <c r="C55" s="27" t="n"/>
       <c r="D55">
-        <f>IF($B55="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B55,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B55,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B55="","",IFERROR(INDEX($D$17:$D$54,MATCH($B55,$B$17:$B$54,0)),""))</f>
         <v/>
       </c>
       <c r="E55">
@@ -32121,7 +32108,7 @@
       <c r="A56" s="37" t="n"/>
       <c r="C56" s="27" t="n"/>
       <c r="D56">
-        <f>IF($B56="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B56,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B56,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B56="","",IFERROR(INDEX($D$17:$D$55,MATCH($B56,$B$17:$B$55,0)),""))</f>
         <v/>
       </c>
       <c r="E56">
@@ -32141,7 +32128,7 @@
       <c r="A57" s="37" t="n"/>
       <c r="C57" s="27" t="n"/>
       <c r="D57">
-        <f>IF($B57="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B57,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B57,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B57="","",IFERROR(INDEX($D$17:$D$56,MATCH($B57,$B$17:$B$56,0)),""))</f>
         <v/>
       </c>
       <c r="E57">
@@ -32161,7 +32148,7 @@
       <c r="A58" s="37" t="n"/>
       <c r="C58" s="27" t="n"/>
       <c r="D58">
-        <f>IF($B58="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B58,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B58,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B58="","",IFERROR(INDEX($D$17:$D$57,MATCH($B58,$B$17:$B$57,0)),""))</f>
         <v/>
       </c>
       <c r="E58">
@@ -32181,7 +32168,7 @@
       <c r="A59" s="37" t="n"/>
       <c r="C59" s="27" t="n"/>
       <c r="D59">
-        <f>IF($B59="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B59,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B59,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B59="","",IFERROR(INDEX($D$17:$D$58,MATCH($B59,$B$17:$B$58,0)),""))</f>
         <v/>
       </c>
       <c r="E59">
@@ -32201,7 +32188,7 @@
       <c r="A60" s="37" t="n"/>
       <c r="C60" s="27" t="n"/>
       <c r="D60">
-        <f>IF($B60="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B60,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B60,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B60="","",IFERROR(INDEX($D$17:$D$59,MATCH($B60,$B$17:$B$59,0)),""))</f>
         <v/>
       </c>
       <c r="E60">
@@ -32221,7 +32208,7 @@
       <c r="A61" s="37" t="n"/>
       <c r="C61" s="27" t="n"/>
       <c r="D61">
-        <f>IF($B61="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B61,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B61,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B61="","",IFERROR(INDEX($D$17:$D$60,MATCH($B61,$B$17:$B$60,0)),""))</f>
         <v/>
       </c>
       <c r="E61">
@@ -32241,7 +32228,7 @@
       <c r="A62" s="37" t="n"/>
       <c r="C62" s="27" t="n"/>
       <c r="D62">
-        <f>IF($B62="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B62,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B62,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B62="","",IFERROR(INDEX($D$17:$D$61,MATCH($B62,$B$17:$B$61,0)),""))</f>
         <v/>
       </c>
       <c r="E62">
@@ -32261,7 +32248,7 @@
       <c r="A63" s="37" t="n"/>
       <c r="C63" s="27" t="n"/>
       <c r="D63">
-        <f>IF($B63="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B63,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B63,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B63="","",IFERROR(INDEX($D$17:$D$62,MATCH($B63,$B$17:$B$62,0)),""))</f>
         <v/>
       </c>
       <c r="E63">
@@ -32281,7 +32268,7 @@
       <c r="A64" s="37" t="n"/>
       <c r="C64" s="27" t="n"/>
       <c r="D64">
-        <f>IF($B64="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B64,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B64,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B64="","",IFERROR(INDEX($D$17:$D$63,MATCH($B64,$B$17:$B$63,0)),""))</f>
         <v/>
       </c>
       <c r="E64">
@@ -32301,7 +32288,7 @@
       <c r="A65" s="37" t="n"/>
       <c r="C65" s="27" t="n"/>
       <c r="D65">
-        <f>IF($B65="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B65,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B65,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B65="","",IFERROR(INDEX($D$17:$D$64,MATCH($B65,$B$17:$B$64,0)),""))</f>
         <v/>
       </c>
       <c r="E65">
@@ -32321,7 +32308,7 @@
       <c r="A66" s="37" t="n"/>
       <c r="C66" s="27" t="n"/>
       <c r="D66">
-        <f>IF($B66="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B66,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B66,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B66="","",IFERROR(INDEX($D$17:$D$65,MATCH($B66,$B$17:$B$65,0)),""))</f>
         <v/>
       </c>
       <c r="E66">
@@ -32341,7 +32328,7 @@
       <c r="A67" s="37" t="n"/>
       <c r="C67" s="27" t="n"/>
       <c r="D67">
-        <f>IF($B67="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B67,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B67,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B67="","",IFERROR(INDEX($D$17:$D$66,MATCH($B67,$B$17:$B$66,0)),""))</f>
         <v/>
       </c>
       <c r="E67">
@@ -32361,7 +32348,7 @@
       <c r="A68" s="37" t="n"/>
       <c r="C68" s="27" t="n"/>
       <c r="D68">
-        <f>IF($B68="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B68,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B68,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B68="","",IFERROR(INDEX($D$17:$D$67,MATCH($B68,$B$17:$B$67,0)),""))</f>
         <v/>
       </c>
       <c r="E68">
@@ -32381,7 +32368,7 @@
       <c r="A69" s="37" t="n"/>
       <c r="C69" s="27" t="n"/>
       <c r="D69">
-        <f>IF($B69="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B69,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B69,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B69="","",IFERROR(INDEX($D$17:$D$68,MATCH($B69,$B$17:$B$68,0)),""))</f>
         <v/>
       </c>
       <c r="E69">
@@ -32401,7 +32388,7 @@
       <c r="A70" s="37" t="n"/>
       <c r="C70" s="27" t="n"/>
       <c r="D70">
-        <f>IF($B70="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B70,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B70,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B70="","",IFERROR(INDEX($D$17:$D$69,MATCH($B70,$B$17:$B$69,0)),""))</f>
         <v/>
       </c>
       <c r="E70">
@@ -32421,7 +32408,7 @@
       <c r="A71" s="37" t="n"/>
       <c r="C71" s="27" t="n"/>
       <c r="D71">
-        <f>IF($B71="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B71,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B71,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B71="","",IFERROR(INDEX($D$17:$D$70,MATCH($B71,$B$17:$B$70,0)),""))</f>
         <v/>
       </c>
       <c r="E71">
@@ -32441,7 +32428,7 @@
       <c r="A72" s="37" t="n"/>
       <c r="C72" s="27" t="n"/>
       <c r="D72">
-        <f>IF($B72="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B72,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B72,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B72="","",IFERROR(INDEX($D$17:$D$71,MATCH($B72,$B$17:$B$71,0)),""))</f>
         <v/>
       </c>
       <c r="E72">
@@ -32461,7 +32448,7 @@
       <c r="A73" s="37" t="n"/>
       <c r="C73" s="27" t="n"/>
       <c r="D73">
-        <f>IF($B73="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B73,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B73,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B73="","",IFERROR(INDEX($D$17:$D$72,MATCH($B73,$B$17:$B$72,0)),""))</f>
         <v/>
       </c>
       <c r="E73">
@@ -32481,7 +32468,7 @@
       <c r="A74" s="37" t="n"/>
       <c r="C74" s="27" t="n"/>
       <c r="D74">
-        <f>IF($B74="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B74,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B74,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B74="","",IFERROR(INDEX($D$17:$D$73,MATCH($B74,$B$17:$B$73,0)),""))</f>
         <v/>
       </c>
       <c r="E74">
@@ -32501,7 +32488,7 @@
       <c r="A75" s="37" t="n"/>
       <c r="C75" s="27" t="n"/>
       <c r="D75">
-        <f>IF($B75="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B75,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B75,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B75="","",IFERROR(INDEX($D$17:$D$74,MATCH($B75,$B$17:$B$74,0)),""))</f>
         <v/>
       </c>
       <c r="E75">
@@ -32521,7 +32508,7 @@
       <c r="A76" s="37" t="n"/>
       <c r="C76" s="27" t="n"/>
       <c r="D76">
-        <f>IF($B76="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B76,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B76,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B76="","",IFERROR(INDEX($D$17:$D$75,MATCH($B76,$B$17:$B$75,0)),""))</f>
         <v/>
       </c>
       <c r="E76">
@@ -32541,7 +32528,7 @@
       <c r="A77" s="37" t="n"/>
       <c r="C77" s="27" t="n"/>
       <c r="D77">
-        <f>IF($B77="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B77,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B77,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B77="","",IFERROR(INDEX($D$17:$D$76,MATCH($B77,$B$17:$B$76,0)),""))</f>
         <v/>
       </c>
       <c r="E77">
@@ -32561,7 +32548,7 @@
       <c r="A78" s="37" t="n"/>
       <c r="C78" s="27" t="n"/>
       <c r="D78">
-        <f>IF($B78="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B78,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B78,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B78="","",IFERROR(INDEX($D$17:$D$77,MATCH($B78,$B$17:$B$77,0)),""))</f>
         <v/>
       </c>
       <c r="E78">
@@ -32581,7 +32568,7 @@
       <c r="A79" s="37" t="n"/>
       <c r="C79" s="27" t="n"/>
       <c r="D79">
-        <f>IF($B79="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B79,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B79,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B79="","",IFERROR(INDEX($D$17:$D$78,MATCH($B79,$B$17:$B$78,0)),""))</f>
         <v/>
       </c>
       <c r="E79">
@@ -32601,7 +32588,7 @@
       <c r="A80" s="37" t="n"/>
       <c r="C80" s="27" t="n"/>
       <c r="D80">
-        <f>IF($B80="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B80,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B80,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B80="","",IFERROR(INDEX($D$17:$D$79,MATCH($B80,$B$17:$B$79,0)),""))</f>
         <v/>
       </c>
       <c r="E80">
@@ -32621,7 +32608,7 @@
       <c r="A81" s="37" t="n"/>
       <c r="C81" s="27" t="n"/>
       <c r="D81">
-        <f>IF($B81="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B81,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B81,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B81="","",IFERROR(INDEX($D$17:$D$80,MATCH($B81,$B$17:$B$80,0)),""))</f>
         <v/>
       </c>
       <c r="E81">
@@ -32641,7 +32628,7 @@
       <c r="A82" s="37" t="n"/>
       <c r="C82" s="27" t="n"/>
       <c r="D82">
-        <f>IF($B82="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B82,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B82,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B82="","",IFERROR(INDEX($D$17:$D$81,MATCH($B82,$B$17:$B$81,0)),""))</f>
         <v/>
       </c>
       <c r="E82">
@@ -32661,7 +32648,7 @@
       <c r="A83" s="37" t="n"/>
       <c r="C83" s="27" t="n"/>
       <c r="D83">
-        <f>IF($B83="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B83,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B83,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B83="","",IFERROR(INDEX($D$17:$D$82,MATCH($B83,$B$17:$B$82,0)),""))</f>
         <v/>
       </c>
       <c r="E83">
@@ -32681,7 +32668,7 @@
       <c r="A84" s="37" t="n"/>
       <c r="C84" s="27" t="n"/>
       <c r="D84">
-        <f>IF($B84="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B84,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B84,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B84="","",IFERROR(INDEX($D$17:$D$83,MATCH($B84,$B$17:$B$83,0)),""))</f>
         <v/>
       </c>
       <c r="E84">
@@ -32701,7 +32688,7 @@
       <c r="A85" s="37" t="n"/>
       <c r="C85" s="27" t="n"/>
       <c r="D85">
-        <f>IF($B85="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B85,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B85,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B85="","",IFERROR(INDEX($D$17:$D$84,MATCH($B85,$B$17:$B$84,0)),""))</f>
         <v/>
       </c>
       <c r="E85">
@@ -32721,7 +32708,7 @@
       <c r="A86" s="37" t="n"/>
       <c r="C86" s="27" t="n"/>
       <c r="D86">
-        <f>IF($B86="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B86,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B86,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B86="","",IFERROR(INDEX($D$17:$D$85,MATCH($B86,$B$17:$B$85,0)),""))</f>
         <v/>
       </c>
       <c r="E86">
@@ -32741,7 +32728,7 @@
       <c r="A87" s="37" t="n"/>
       <c r="C87" s="27" t="n"/>
       <c r="D87">
-        <f>IF($B87="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B87,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B87,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B87="","",IFERROR(INDEX($D$17:$D$86,MATCH($B87,$B$17:$B$86,0)),""))</f>
         <v/>
       </c>
       <c r="E87">
@@ -32761,7 +32748,7 @@
       <c r="A88" s="37" t="n"/>
       <c r="C88" s="27" t="n"/>
       <c r="D88">
-        <f>IF($B88="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B88,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B88,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B88="","",IFERROR(INDEX($D$17:$D$87,MATCH($B88,$B$17:$B$87,0)),""))</f>
         <v/>
       </c>
       <c r="E88">
@@ -32781,7 +32768,7 @@
       <c r="A89" s="37" t="n"/>
       <c r="C89" s="27" t="n"/>
       <c r="D89">
-        <f>IF($B89="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B89,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B89,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B89="","",IFERROR(INDEX($D$17:$D$88,MATCH($B89,$B$17:$B$88,0)),""))</f>
         <v/>
       </c>
       <c r="E89">
@@ -32801,7 +32788,7 @@
       <c r="A90" s="37" t="n"/>
       <c r="C90" s="27" t="n"/>
       <c r="D90">
-        <f>IF($B90="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B90,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B90,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B90="","",IFERROR(INDEX($D$17:$D$89,MATCH($B90,$B$17:$B$89,0)),""))</f>
         <v/>
       </c>
       <c r="E90">
@@ -32821,7 +32808,7 @@
       <c r="A91" s="37" t="n"/>
       <c r="C91" s="27" t="n"/>
       <c r="D91">
-        <f>IF($B91="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B91,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B91,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B91="","",IFERROR(INDEX($D$17:$D$90,MATCH($B91,$B$17:$B$90,0)),""))</f>
         <v/>
       </c>
       <c r="E91">
@@ -32841,7 +32828,7 @@
       <c r="A92" s="37" t="n"/>
       <c r="C92" s="27" t="n"/>
       <c r="D92">
-        <f>IF($B92="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B92,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B92,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B92="","",IFERROR(INDEX($D$17:$D$91,MATCH($B92,$B$17:$B$91,0)),""))</f>
         <v/>
       </c>
       <c r="E92">
@@ -32861,7 +32848,7 @@
       <c r="A93" s="37" t="n"/>
       <c r="C93" s="27" t="n"/>
       <c r="D93">
-        <f>IF($B93="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B93,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B93,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B93="","",IFERROR(INDEX($D$17:$D$92,MATCH($B93,$B$17:$B$92,0)),""))</f>
         <v/>
       </c>
       <c r="E93">
@@ -32881,7 +32868,7 @@
       <c r="A94" s="37" t="n"/>
       <c r="C94" s="27" t="n"/>
       <c r="D94">
-        <f>IF($B94="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B94,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B94,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B94="","",IFERROR(INDEX($D$17:$D$93,MATCH($B94,$B$17:$B$93,0)),""))</f>
         <v/>
       </c>
       <c r="E94">
@@ -32901,7 +32888,7 @@
       <c r="A95" s="37" t="n"/>
       <c r="C95" s="27" t="n"/>
       <c r="D95">
-        <f>IF($B95="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B95,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B95,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B95="","",IFERROR(INDEX($D$17:$D$94,MATCH($B95,$B$17:$B$94,0)),""))</f>
         <v/>
       </c>
       <c r="E95">
@@ -32921,7 +32908,7 @@
       <c r="A96" s="37" t="n"/>
       <c r="C96" s="27" t="n"/>
       <c r="D96">
-        <f>IF($B96="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B96,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B96,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B96="","",IFERROR(INDEX($D$17:$D$95,MATCH($B96,$B$17:$B$95,0)),""))</f>
         <v/>
       </c>
       <c r="E96">
@@ -32941,7 +32928,7 @@
       <c r="A97" s="37" t="n"/>
       <c r="C97" s="27" t="n"/>
       <c r="D97">
-        <f>IF($B97="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B97,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B97,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B97="","",IFERROR(INDEX($D$17:$D$96,MATCH($B97,$B$17:$B$96,0)),""))</f>
         <v/>
       </c>
       <c r="E97">
@@ -32961,7 +32948,7 @@
       <c r="A98" s="37" t="n"/>
       <c r="C98" s="27" t="n"/>
       <c r="D98">
-        <f>IF($B98="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B98,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B98,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B98="","",IFERROR(INDEX($D$17:$D$97,MATCH($B98,$B$17:$B$97,0)),""))</f>
         <v/>
       </c>
       <c r="E98">
@@ -32981,7 +32968,7 @@
       <c r="A99" s="37" t="n"/>
       <c r="C99" s="27" t="n"/>
       <c r="D99">
-        <f>IF($B99="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B99,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B99,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B99="","",IFERROR(INDEX($D$17:$D$98,MATCH($B99,$B$17:$B$98,0)),""))</f>
         <v/>
       </c>
       <c r="E99">
@@ -33001,7 +32988,7 @@
       <c r="A100" s="37" t="n"/>
       <c r="C100" s="27" t="n"/>
       <c r="D100">
-        <f>IF($B100="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B100,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B100,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B100="","",IFERROR(INDEX($D$17:$D$99,MATCH($B100,$B$17:$B$99,0)),""))</f>
         <v/>
       </c>
       <c r="E100">
@@ -33021,7 +33008,7 @@
       <c r="A101" s="37" t="n"/>
       <c r="C101" s="27" t="n"/>
       <c r="D101">
-        <f>IF($B101="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B101,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B101,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B101="","",IFERROR(INDEX($D$17:$D$100,MATCH($B101,$B$17:$B$100,0)),""))</f>
         <v/>
       </c>
       <c r="E101">
@@ -33041,7 +33028,7 @@
       <c r="A102" s="37" t="n"/>
       <c r="C102" s="27" t="n"/>
       <c r="D102">
-        <f>IF($B102="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B102,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B102,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B102="","",IFERROR(INDEX($D$17:$D$101,MATCH($B102,$B$17:$B$101,0)),""))</f>
         <v/>
       </c>
       <c r="E102">
@@ -33061,7 +33048,7 @@
       <c r="A103" s="37" t="n"/>
       <c r="C103" s="27" t="n"/>
       <c r="D103">
-        <f>IF($B103="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B103,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B103,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B103="","",IFERROR(INDEX($D$17:$D$102,MATCH($B103,$B$17:$B$102,0)),""))</f>
         <v/>
       </c>
       <c r="E103">
@@ -33081,7 +33068,7 @@
       <c r="A104" s="37" t="n"/>
       <c r="C104" s="27" t="n"/>
       <c r="D104">
-        <f>IF($B104="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B104,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B104,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B104="","",IFERROR(INDEX($D$17:$D$103,MATCH($B104,$B$17:$B$103,0)),""))</f>
         <v/>
       </c>
       <c r="E104">
@@ -33101,7 +33088,7 @@
       <c r="A105" s="37" t="n"/>
       <c r="C105" s="27" t="n"/>
       <c r="D105">
-        <f>IF($B105="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B105,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B105,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B105="","",IFERROR(INDEX($D$17:$D$104,MATCH($B105,$B$17:$B$104,0)),""))</f>
         <v/>
       </c>
       <c r="E105">
@@ -33121,7 +33108,7 @@
       <c r="A106" s="37" t="n"/>
       <c r="C106" s="27" t="n"/>
       <c r="D106">
-        <f>IF($B106="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B106,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B106,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B106="","",IFERROR(INDEX($D$17:$D$105,MATCH($B106,$B$17:$B$105,0)),""))</f>
         <v/>
       </c>
       <c r="E106">
@@ -33141,7 +33128,7 @@
       <c r="A107" s="37" t="n"/>
       <c r="C107" s="27" t="n"/>
       <c r="D107">
-        <f>IF($B107="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B107,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B107,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B107="","",IFERROR(INDEX($D$17:$D$106,MATCH($B107,$B$17:$B$106,0)),""))</f>
         <v/>
       </c>
       <c r="E107">
@@ -33161,7 +33148,7 @@
       <c r="A108" s="37" t="n"/>
       <c r="C108" s="27" t="n"/>
       <c r="D108">
-        <f>IF($B108="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B108,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B108,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B108="","",IFERROR(INDEX($D$17:$D$107,MATCH($B108,$B$17:$B$107,0)),""))</f>
         <v/>
       </c>
       <c r="E108">
@@ -33181,7 +33168,7 @@
       <c r="A109" s="37" t="n"/>
       <c r="C109" s="27" t="n"/>
       <c r="D109">
-        <f>IF($B109="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B109,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B109,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B109="","",IFERROR(INDEX($D$17:$D$108,MATCH($B109,$B$17:$B$108,0)),""))</f>
         <v/>
       </c>
       <c r="E109">
@@ -33201,7 +33188,7 @@
       <c r="A110" s="37" t="n"/>
       <c r="C110" s="27" t="n"/>
       <c r="D110">
-        <f>IF($B110="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B110,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B110,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B110="","",IFERROR(INDEX($D$17:$D$109,MATCH($B110,$B$17:$B$109,0)),""))</f>
         <v/>
       </c>
       <c r="E110">
@@ -33221,7 +33208,7 @@
       <c r="A111" s="37" t="n"/>
       <c r="C111" s="27" t="n"/>
       <c r="D111">
-        <f>IF($B111="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B111,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B111,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B111="","",IFERROR(INDEX($D$17:$D$110,MATCH($B111,$B$17:$B$110,0)),""))</f>
         <v/>
       </c>
       <c r="E111">
@@ -33241,7 +33228,7 @@
       <c r="A112" s="37" t="n"/>
       <c r="C112" s="27" t="n"/>
       <c r="D112">
-        <f>IF($B112="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B112,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B112,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B112="","",IFERROR(INDEX($D$17:$D$111,MATCH($B112,$B$17:$B$111,0)),""))</f>
         <v/>
       </c>
       <c r="E112">
@@ -33261,7 +33248,7 @@
       <c r="A113" s="37" t="n"/>
       <c r="C113" s="27" t="n"/>
       <c r="D113">
-        <f>IF($B113="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B113,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B113,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B113="","",IFERROR(INDEX($D$17:$D$112,MATCH($B113,$B$17:$B$112,0)),""))</f>
         <v/>
       </c>
       <c r="E113">
@@ -33281,7 +33268,7 @@
       <c r="A114" s="37" t="n"/>
       <c r="C114" s="27" t="n"/>
       <c r="D114">
-        <f>IF($B114="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B114,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B114,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B114="","",IFERROR(INDEX($D$17:$D$113,MATCH($B114,$B$17:$B$113,0)),""))</f>
         <v/>
       </c>
       <c r="E114">
@@ -33301,7 +33288,7 @@
       <c r="A115" s="37" t="n"/>
       <c r="C115" s="27" t="n"/>
       <c r="D115">
-        <f>IF($B115="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B115,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B115,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B115="","",IFERROR(INDEX($D$17:$D$114,MATCH($B115,$B$17:$B$114,0)),""))</f>
         <v/>
       </c>
       <c r="E115">
@@ -33321,7 +33308,7 @@
       <c r="A116" s="37" t="n"/>
       <c r="C116" s="27" t="n"/>
       <c r="D116">
-        <f>IF($B116="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B116,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B116,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B116="","",IFERROR(INDEX($D$17:$D$115,MATCH($B116,$B$17:$B$115,0)),""))</f>
         <v/>
       </c>
       <c r="E116">
@@ -33341,7 +33328,7 @@
       <c r="A117" s="37" t="n"/>
       <c r="C117" s="27" t="n"/>
       <c r="D117">
-        <f>IF($B117="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B117,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B117,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B117="","",IFERROR(INDEX($D$17:$D$116,MATCH($B117,$B$17:$B$116,0)),""))</f>
         <v/>
       </c>
       <c r="E117">
@@ -33361,7 +33348,7 @@
       <c r="A118" s="37" t="n"/>
       <c r="C118" s="27" t="n"/>
       <c r="D118">
-        <f>IF($B118="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B118,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B118,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B118="","",IFERROR(INDEX($D$17:$D$117,MATCH($B118,$B$17:$B$117,0)),""))</f>
         <v/>
       </c>
       <c r="E118">
@@ -33381,7 +33368,7 @@
       <c r="A119" s="37" t="n"/>
       <c r="C119" s="27" t="n"/>
       <c r="D119">
-        <f>IF($B119="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B119,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B119,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B119="","",IFERROR(INDEX($D$17:$D$118,MATCH($B119,$B$17:$B$118,0)),""))</f>
         <v/>
       </c>
       <c r="E119">
@@ -33401,7 +33388,7 @@
       <c r="A120" s="37" t="n"/>
       <c r="C120" s="27" t="n"/>
       <c r="D120">
-        <f>IF($B120="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B120,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B120,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B120="","",IFERROR(INDEX($D$17:$D$119,MATCH($B120,$B$17:$B$119,0)),""))</f>
         <v/>
       </c>
       <c r="E120">
@@ -33421,7 +33408,7 @@
       <c r="A121" s="37" t="n"/>
       <c r="C121" s="27" t="n"/>
       <c r="D121">
-        <f>IF($B121="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B121,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B121,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B121="","",IFERROR(INDEX($D$17:$D$120,MATCH($B121,$B$17:$B$120,0)),""))</f>
         <v/>
       </c>
       <c r="E121">
@@ -33441,7 +33428,7 @@
       <c r="A122" s="37" t="n"/>
       <c r="C122" s="27" t="n"/>
       <c r="D122">
-        <f>IF($B122="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B122,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B122,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B122="","",IFERROR(INDEX($D$17:$D$121,MATCH($B122,$B$17:$B$121,0)),""))</f>
         <v/>
       </c>
       <c r="E122">
@@ -33461,7 +33448,7 @@
       <c r="A123" s="37" t="n"/>
       <c r="C123" s="27" t="n"/>
       <c r="D123">
-        <f>IF($B123="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B123,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B123,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B123="","",IFERROR(INDEX($D$17:$D$122,MATCH($B123,$B$17:$B$122,0)),""))</f>
         <v/>
       </c>
       <c r="E123">
@@ -33481,7 +33468,7 @@
       <c r="A124" s="37" t="n"/>
       <c r="C124" s="27" t="n"/>
       <c r="D124">
-        <f>IF($B124="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B124,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B124,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B124="","",IFERROR(INDEX($D$17:$D$123,MATCH($B124,$B$17:$B$123,0)),""))</f>
         <v/>
       </c>
       <c r="E124">
@@ -33501,7 +33488,7 @@
       <c r="A125" s="37" t="n"/>
       <c r="C125" s="27" t="n"/>
       <c r="D125">
-        <f>IF($B125="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B125,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B125,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B125="","",IFERROR(INDEX($D$17:$D$124,MATCH($B125,$B$17:$B$124,0)),""))</f>
         <v/>
       </c>
       <c r="E125">
@@ -33521,7 +33508,7 @@
       <c r="A126" s="37" t="n"/>
       <c r="C126" s="27" t="n"/>
       <c r="D126">
-        <f>IF($B126="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B126,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B126,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B126="","",IFERROR(INDEX($D$17:$D$125,MATCH($B126,$B$17:$B$125,0)),""))</f>
         <v/>
       </c>
       <c r="E126">
@@ -33541,7 +33528,7 @@
       <c r="A127" s="37" t="n"/>
       <c r="C127" s="27" t="n"/>
       <c r="D127">
-        <f>IF($B127="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B127,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B127,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B127="","",IFERROR(INDEX($D$17:$D$126,MATCH($B127,$B$17:$B$126,0)),""))</f>
         <v/>
       </c>
       <c r="E127">
@@ -33561,7 +33548,7 @@
       <c r="A128" s="37" t="n"/>
       <c r="C128" s="27" t="n"/>
       <c r="D128">
-        <f>IF($B128="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B128,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B128,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B128="","",IFERROR(INDEX($D$17:$D$127,MATCH($B128,$B$17:$B$127,0)),""))</f>
         <v/>
       </c>
       <c r="E128">
@@ -33581,7 +33568,7 @@
       <c r="A129" s="37" t="n"/>
       <c r="C129" s="27" t="n"/>
       <c r="D129">
-        <f>IF($B129="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B129,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B129,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B129="","",IFERROR(INDEX($D$17:$D$128,MATCH($B129,$B$17:$B$128,0)),""))</f>
         <v/>
       </c>
       <c r="E129">
@@ -33601,7 +33588,7 @@
       <c r="A130" s="37" t="n"/>
       <c r="C130" s="27" t="n"/>
       <c r="D130">
-        <f>IF($B130="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B130,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B130,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B130="","",IFERROR(INDEX($D$17:$D$129,MATCH($B130,$B$17:$B$129,0)),""))</f>
         <v/>
       </c>
       <c r="E130">
@@ -33621,7 +33608,7 @@
       <c r="A131" s="37" t="n"/>
       <c r="C131" s="27" t="n"/>
       <c r="D131">
-        <f>IF($B131="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B131,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B131,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B131="","",IFERROR(INDEX($D$17:$D$130,MATCH($B131,$B$17:$B$130,0)),""))</f>
         <v/>
       </c>
       <c r="E131">
@@ -33641,7 +33628,7 @@
       <c r="A132" s="37" t="n"/>
       <c r="C132" s="27" t="n"/>
       <c r="D132">
-        <f>IF($B132="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B132,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B132,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B132="","",IFERROR(INDEX($D$17:$D$131,MATCH($B132,$B$17:$B$131,0)),""))</f>
         <v/>
       </c>
       <c r="E132">
@@ -33661,7 +33648,7 @@
       <c r="A133" s="37" t="n"/>
       <c r="C133" s="27" t="n"/>
       <c r="D133">
-        <f>IF($B133="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B133,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B133,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B133="","",IFERROR(INDEX($D$17:$D$132,MATCH($B133,$B$17:$B$132,0)),""))</f>
         <v/>
       </c>
       <c r="E133">
@@ -33681,7 +33668,7 @@
       <c r="A134" s="37" t="n"/>
       <c r="C134" s="27" t="n"/>
       <c r="D134">
-        <f>IF($B134="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B134,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B134,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B134="","",IFERROR(INDEX($D$17:$D$133,MATCH($B134,$B$17:$B$133,0)),""))</f>
         <v/>
       </c>
       <c r="E134">
@@ -33701,7 +33688,7 @@
       <c r="A135" s="37" t="n"/>
       <c r="C135" s="27" t="n"/>
       <c r="D135">
-        <f>IF($B135="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B135,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B135,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B135="","",IFERROR(INDEX($D$17:$D$134,MATCH($B135,$B$17:$B$134,0)),""))</f>
         <v/>
       </c>
       <c r="E135">
@@ -33721,7 +33708,7 @@
       <c r="A136" s="37" t="n"/>
       <c r="C136" s="27" t="n"/>
       <c r="D136">
-        <f>IF($B136="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B136,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B136,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B136="","",IFERROR(INDEX($D$17:$D$135,MATCH($B136,$B$17:$B$135,0)),""))</f>
         <v/>
       </c>
       <c r="E136">
@@ -33741,7 +33728,7 @@
       <c r="A137" s="37" t="n"/>
       <c r="C137" s="27" t="n"/>
       <c r="D137">
-        <f>IF($B137="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B137,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B137,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B137="","",IFERROR(INDEX($D$17:$D$136,MATCH($B137,$B$17:$B$136,0)),""))</f>
         <v/>
       </c>
       <c r="E137">
@@ -33761,7 +33748,7 @@
       <c r="A138" s="37" t="n"/>
       <c r="C138" s="27" t="n"/>
       <c r="D138">
-        <f>IF($B138="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B138,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B138,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B138="","",IFERROR(INDEX($D$17:$D$137,MATCH($B138,$B$17:$B$137,0)),""))</f>
         <v/>
       </c>
       <c r="E138">
@@ -33781,7 +33768,7 @@
       <c r="A139" s="37" t="n"/>
       <c r="C139" s="27" t="n"/>
       <c r="D139">
-        <f>IF($B139="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B139,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B139,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B139="","",IFERROR(INDEX($D$17:$D$138,MATCH($B139,$B$17:$B$138,0)),""))</f>
         <v/>
       </c>
       <c r="E139">
@@ -33801,7 +33788,7 @@
       <c r="A140" s="37" t="n"/>
       <c r="C140" s="27" t="n"/>
       <c r="D140">
-        <f>IF($B140="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B140,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B140,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B140="","",IFERROR(INDEX($D$17:$D$139,MATCH($B140,$B$17:$B$139,0)),""))</f>
         <v/>
       </c>
       <c r="E140">
@@ -33821,7 +33808,7 @@
       <c r="A141" s="37" t="n"/>
       <c r="C141" s="27" t="n"/>
       <c r="D141">
-        <f>IF($B141="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B141,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B141,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B141="","",IFERROR(INDEX($D$17:$D$140,MATCH($B141,$B$17:$B$140,0)),""))</f>
         <v/>
       </c>
       <c r="E141">
@@ -33841,7 +33828,7 @@
       <c r="A142" s="37" t="n"/>
       <c r="C142" s="27" t="n"/>
       <c r="D142">
-        <f>IF($B142="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B142,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B142,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B142="","",IFERROR(INDEX($D$17:$D$141,MATCH($B142,$B$17:$B$141,0)),""))</f>
         <v/>
       </c>
       <c r="E142">
@@ -33861,7 +33848,7 @@
       <c r="A143" s="37" t="n"/>
       <c r="C143" s="27" t="n"/>
       <c r="D143">
-        <f>IF($B143="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B143,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B143,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B143="","",IFERROR(INDEX($D$17:$D$142,MATCH($B143,$B$17:$B$142,0)),""))</f>
         <v/>
       </c>
       <c r="E143">
@@ -33881,7 +33868,7 @@
       <c r="A144" s="37" t="n"/>
       <c r="C144" s="27" t="n"/>
       <c r="D144">
-        <f>IF($B144="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B144,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B144,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B144="","",IFERROR(INDEX($D$17:$D$143,MATCH($B144,$B$17:$B$143,0)),""))</f>
         <v/>
       </c>
       <c r="E144">
@@ -33901,7 +33888,7 @@
       <c r="A145" s="37" t="n"/>
       <c r="C145" s="27" t="n"/>
       <c r="D145">
-        <f>IF($B145="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B145,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B145,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B145="","",IFERROR(INDEX($D$17:$D$144,MATCH($B145,$B$17:$B$144,0)),""))</f>
         <v/>
       </c>
       <c r="E145">
@@ -33921,7 +33908,7 @@
       <c r="A146" s="37" t="n"/>
       <c r="C146" s="27" t="n"/>
       <c r="D146">
-        <f>IF($B146="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B146,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B146,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B146="","",IFERROR(INDEX($D$17:$D$145,MATCH($B146,$B$17:$B$145,0)),""))</f>
         <v/>
       </c>
       <c r="E146">
@@ -33941,7 +33928,7 @@
       <c r="A147" s="37" t="n"/>
       <c r="C147" s="27" t="n"/>
       <c r="D147">
-        <f>IF($B147="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B147,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B147,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B147="","",IFERROR(INDEX($D$17:$D$146,MATCH($B147,$B$17:$B$146,0)),""))</f>
         <v/>
       </c>
       <c r="E147">
@@ -33961,7 +33948,7 @@
       <c r="A148" s="37" t="n"/>
       <c r="C148" s="27" t="n"/>
       <c r="D148">
-        <f>IF($B148="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B148,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B148,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B148="","",IFERROR(INDEX($D$17:$D$147,MATCH($B148,$B$17:$B$147,0)),""))</f>
         <v/>
       </c>
       <c r="E148">
@@ -33981,7 +33968,7 @@
       <c r="A149" s="37" t="n"/>
       <c r="C149" s="27" t="n"/>
       <c r="D149">
-        <f>IF($B149="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B149,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B149,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B149="","",IFERROR(INDEX($D$17:$D$148,MATCH($B149,$B$17:$B$148,0)),""))</f>
         <v/>
       </c>
       <c r="E149">
@@ -34001,7 +33988,7 @@
       <c r="A150" s="37" t="n"/>
       <c r="C150" s="27" t="n"/>
       <c r="D150">
-        <f>IF($B150="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B150,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B150,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B150="","",IFERROR(INDEX($D$17:$D$149,MATCH($B150,$B$17:$B$149,0)),""))</f>
         <v/>
       </c>
       <c r="E150">
@@ -34021,7 +34008,7 @@
       <c r="A151" s="37" t="n"/>
       <c r="C151" s="27" t="n"/>
       <c r="D151">
-        <f>IF($B151="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B151,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B151,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B151="","",IFERROR(INDEX($D$17:$D$150,MATCH($B151,$B$17:$B$150,0)),""))</f>
         <v/>
       </c>
       <c r="E151">
@@ -34041,7 +34028,7 @@
       <c r="A152" s="37" t="n"/>
       <c r="C152" s="27" t="n"/>
       <c r="D152">
-        <f>IF($B152="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B152,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B152,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B152="","",IFERROR(INDEX($D$17:$D$151,MATCH($B152,$B$17:$B$151,0)),""))</f>
         <v/>
       </c>
       <c r="E152">
@@ -34061,7 +34048,7 @@
       <c r="A153" s="37" t="n"/>
       <c r="C153" s="27" t="n"/>
       <c r="D153">
-        <f>IF($B153="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B153,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B153,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B153="","",IFERROR(INDEX($D$17:$D$152,MATCH($B153,$B$17:$B$152,0)),""))</f>
         <v/>
       </c>
       <c r="E153">
@@ -34081,7 +34068,7 @@
       <c r="A154" s="37" t="n"/>
       <c r="C154" s="27" t="n"/>
       <c r="D154">
-        <f>IF($B154="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B154,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B154,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B154="","",IFERROR(INDEX($D$17:$D$153,MATCH($B154,$B$17:$B$153,0)),""))</f>
         <v/>
       </c>
       <c r="E154">
@@ -34101,7 +34088,7 @@
       <c r="A155" s="37" t="n"/>
       <c r="C155" s="27" t="n"/>
       <c r="D155">
-        <f>IF($B155="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B155,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B155,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B155="","",IFERROR(INDEX($D$17:$D$154,MATCH($B155,$B$17:$B$154,0)),""))</f>
         <v/>
       </c>
       <c r="E155">
@@ -34121,7 +34108,7 @@
       <c r="A156" s="37" t="n"/>
       <c r="C156" s="27" t="n"/>
       <c r="D156">
-        <f>IF($B156="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B156,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B156,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B156="","",IFERROR(INDEX($D$17:$D$155,MATCH($B156,$B$17:$B$155,0)),""))</f>
         <v/>
       </c>
       <c r="E156">
@@ -34141,7 +34128,7 @@
       <c r="A157" s="37" t="n"/>
       <c r="C157" s="27" t="n"/>
       <c r="D157">
-        <f>IF($B157="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B157,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B157,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B157="","",IFERROR(INDEX($D$17:$D$156,MATCH($B157,$B$17:$B$156,0)),""))</f>
         <v/>
       </c>
       <c r="E157">
@@ -34161,7 +34148,7 @@
       <c r="A158" s="37" t="n"/>
       <c r="C158" s="27" t="n"/>
       <c r="D158">
-        <f>IF($B158="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B158,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B158,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B158="","",IFERROR(INDEX($D$17:$D$157,MATCH($B158,$B$17:$B$157,0)),""))</f>
         <v/>
       </c>
       <c r="E158">
@@ -34181,7 +34168,7 @@
       <c r="A159" s="37" t="n"/>
       <c r="C159" s="27" t="n"/>
       <c r="D159">
-        <f>IF($B159="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B159,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B159,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B159="","",IFERROR(INDEX($D$17:$D$158,MATCH($B159,$B$17:$B$158,0)),""))</f>
         <v/>
       </c>
       <c r="E159">
@@ -34201,7 +34188,7 @@
       <c r="A160" s="37" t="n"/>
       <c r="C160" s="27" t="n"/>
       <c r="D160">
-        <f>IF($B160="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B160,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B160,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B160="","",IFERROR(INDEX($D$17:$D$159,MATCH($B160,$B$17:$B$159,0)),""))</f>
         <v/>
       </c>
       <c r="E160">
@@ -34221,7 +34208,7 @@
       <c r="A161" s="37" t="n"/>
       <c r="C161" s="27" t="n"/>
       <c r="D161">
-        <f>IF($B161="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B161,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B161,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B161="","",IFERROR(INDEX($D$17:$D$160,MATCH($B161,$B$17:$B$160,0)),""))</f>
         <v/>
       </c>
       <c r="E161">
@@ -34241,7 +34228,7 @@
       <c r="A162" s="37" t="n"/>
       <c r="C162" s="27" t="n"/>
       <c r="D162">
-        <f>IF($B162="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B162,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B162,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B162="","",IFERROR(INDEX($D$17:$D$161,MATCH($B162,$B$17:$B$161,0)),""))</f>
         <v/>
       </c>
       <c r="E162">
@@ -34261,7 +34248,7 @@
       <c r="A163" s="37" t="n"/>
       <c r="C163" s="27" t="n"/>
       <c r="D163">
-        <f>IF($B163="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B163,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B163,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B163="","",IFERROR(INDEX($D$17:$D$162,MATCH($B163,$B$17:$B$162,0)),""))</f>
         <v/>
       </c>
       <c r="E163">
@@ -34281,7 +34268,7 @@
       <c r="A164" s="37" t="n"/>
       <c r="C164" s="27" t="n"/>
       <c r="D164">
-        <f>IF($B164="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B164,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B164,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B164="","",IFERROR(INDEX($D$17:$D$163,MATCH($B164,$B$17:$B$163,0)),""))</f>
         <v/>
       </c>
       <c r="E164">
@@ -34301,7 +34288,7 @@
       <c r="A165" s="37" t="n"/>
       <c r="C165" s="27" t="n"/>
       <c r="D165">
-        <f>IF($B165="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B165,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B165,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B165="","",IFERROR(INDEX($D$17:$D$164,MATCH($B165,$B$17:$B$164,0)),""))</f>
         <v/>
       </c>
       <c r="E165">
@@ -34321,7 +34308,7 @@
       <c r="A166" s="37" t="n"/>
       <c r="C166" s="27" t="n"/>
       <c r="D166">
-        <f>IF($B166="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B166,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B166,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B166="","",IFERROR(INDEX($D$17:$D$165,MATCH($B166,$B$17:$B$165,0)),""))</f>
         <v/>
       </c>
       <c r="E166">
@@ -34341,7 +34328,7 @@
       <c r="A167" s="37" t="n"/>
       <c r="C167" s="27" t="n"/>
       <c r="D167">
-        <f>IF($B167="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B167,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B167,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B167="","",IFERROR(INDEX($D$17:$D$166,MATCH($B167,$B$17:$B$166,0)),""))</f>
         <v/>
       </c>
       <c r="E167">
@@ -34361,7 +34348,7 @@
       <c r="A168" s="37" t="n"/>
       <c r="C168" s="27" t="n"/>
       <c r="D168">
-        <f>IF($B168="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B168,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B168,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B168="","",IFERROR(INDEX($D$17:$D$167,MATCH($B168,$B$17:$B$167,0)),""))</f>
         <v/>
       </c>
       <c r="E168">
@@ -34381,7 +34368,7 @@
       <c r="A169" s="37" t="n"/>
       <c r="C169" s="27" t="n"/>
       <c r="D169">
-        <f>IF($B169="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B169,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B169,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B169="","",IFERROR(INDEX($D$17:$D$168,MATCH($B169,$B$17:$B$168,0)),""))</f>
         <v/>
       </c>
       <c r="E169">
@@ -34401,7 +34388,7 @@
       <c r="A170" s="37" t="n"/>
       <c r="C170" s="27" t="n"/>
       <c r="D170">
-        <f>IF($B170="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B170,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B170,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B170="","",IFERROR(INDEX($D$17:$D$169,MATCH($B170,$B$17:$B$169,0)),""))</f>
         <v/>
       </c>
       <c r="E170">
@@ -34421,7 +34408,7 @@
       <c r="A171" s="37" t="n"/>
       <c r="C171" s="27" t="n"/>
       <c r="D171">
-        <f>IF($B171="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B171,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B171,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B171="","",IFERROR(INDEX($D$17:$D$170,MATCH($B171,$B$17:$B$170,0)),""))</f>
         <v/>
       </c>
       <c r="E171">
@@ -34441,7 +34428,7 @@
       <c r="A172" s="37" t="n"/>
       <c r="C172" s="27" t="n"/>
       <c r="D172">
-        <f>IF($B172="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B172,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B172,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B172="","",IFERROR(INDEX($D$17:$D$171,MATCH($B172,$B$17:$B$171,0)),""))</f>
         <v/>
       </c>
       <c r="E172">
@@ -34461,7 +34448,7 @@
       <c r="A173" s="37" t="n"/>
       <c r="C173" s="27" t="n"/>
       <c r="D173">
-        <f>IF($B173="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B173,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B173,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B173="","",IFERROR(INDEX($D$17:$D$172,MATCH($B173,$B$17:$B$172,0)),""))</f>
         <v/>
       </c>
       <c r="E173">
@@ -34481,7 +34468,7 @@
       <c r="A174" s="37" t="n"/>
       <c r="C174" s="27" t="n"/>
       <c r="D174">
-        <f>IF($B174="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B174,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B174,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B174="","",IFERROR(INDEX($D$17:$D$173,MATCH($B174,$B$17:$B$173,0)),""))</f>
         <v/>
       </c>
       <c r="E174">
@@ -34501,7 +34488,7 @@
       <c r="A175" s="37" t="n"/>
       <c r="C175" s="27" t="n"/>
       <c r="D175">
-        <f>IF($B175="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B175,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B175,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B175="","",IFERROR(INDEX($D$17:$D$174,MATCH($B175,$B$17:$B$174,0)),""))</f>
         <v/>
       </c>
       <c r="E175">
@@ -34521,7 +34508,7 @@
       <c r="A176" s="37" t="n"/>
       <c r="C176" s="27" t="n"/>
       <c r="D176">
-        <f>IF($B176="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B176,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B176,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B176="","",IFERROR(INDEX($D$17:$D$175,MATCH($B176,$B$17:$B$175,0)),""))</f>
         <v/>
       </c>
       <c r="E176">
@@ -34541,7 +34528,7 @@
       <c r="A177" s="37" t="n"/>
       <c r="C177" s="27" t="n"/>
       <c r="D177">
-        <f>IF($B177="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B177,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B177,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B177="","",IFERROR(INDEX($D$17:$D$176,MATCH($B177,$B$17:$B$176,0)),""))</f>
         <v/>
       </c>
       <c r="E177">
@@ -34561,7 +34548,7 @@
       <c r="A178" s="37" t="n"/>
       <c r="C178" s="27" t="n"/>
       <c r="D178">
-        <f>IF($B178="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B178,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B178,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B178="","",IFERROR(INDEX($D$17:$D$177,MATCH($B178,$B$17:$B$177,0)),""))</f>
         <v/>
       </c>
       <c r="E178">
@@ -34581,7 +34568,7 @@
       <c r="A179" s="37" t="n"/>
       <c r="C179" s="27" t="n"/>
       <c r="D179">
-        <f>IF($B179="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B179,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B179,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B179="","",IFERROR(INDEX($D$17:$D$178,MATCH($B179,$B$17:$B$178,0)),""))</f>
         <v/>
       </c>
       <c r="E179">
@@ -34601,7 +34588,7 @@
       <c r="A180" s="37" t="n"/>
       <c r="C180" s="27" t="n"/>
       <c r="D180">
-        <f>IF($B180="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B180,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B180,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B180="","",IFERROR(INDEX($D$17:$D$179,MATCH($B180,$B$17:$B$179,0)),""))</f>
         <v/>
       </c>
       <c r="E180">
@@ -34621,7 +34608,7 @@
       <c r="A181" s="37" t="n"/>
       <c r="C181" s="27" t="n"/>
       <c r="D181">
-        <f>IF($B181="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B181,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B181,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B181="","",IFERROR(INDEX($D$17:$D$180,MATCH($B181,$B$17:$B$180,0)),""))</f>
         <v/>
       </c>
       <c r="E181">
@@ -34641,7 +34628,7 @@
       <c r="A182" s="37" t="n"/>
       <c r="C182" s="27" t="n"/>
       <c r="D182">
-        <f>IF($B182="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B182,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B182,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B182="","",IFERROR(INDEX($D$17:$D$181,MATCH($B182,$B$17:$B$181,0)),""))</f>
         <v/>
       </c>
       <c r="E182">
@@ -34661,7 +34648,7 @@
       <c r="A183" s="37" t="n"/>
       <c r="C183" s="27" t="n"/>
       <c r="D183">
-        <f>IF($B183="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B183,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B183,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B183="","",IFERROR(INDEX($D$17:$D$182,MATCH($B183,$B$17:$B$182,0)),""))</f>
         <v/>
       </c>
       <c r="E183">
@@ -34681,7 +34668,7 @@
       <c r="A184" s="37" t="n"/>
       <c r="C184" s="27" t="n"/>
       <c r="D184">
-        <f>IF($B184="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B184,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B184,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B184="","",IFERROR(INDEX($D$17:$D$183,MATCH($B184,$B$17:$B$183,0)),""))</f>
         <v/>
       </c>
       <c r="E184">
@@ -34701,7 +34688,7 @@
       <c r="A185" s="37" t="n"/>
       <c r="C185" s="27" t="n"/>
       <c r="D185">
-        <f>IF($B185="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B185,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B185,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B185="","",IFERROR(INDEX($D$17:$D$184,MATCH($B185,$B$17:$B$184,0)),""))</f>
         <v/>
       </c>
       <c r="E185">
@@ -34721,7 +34708,7 @@
       <c r="A186" s="37" t="n"/>
       <c r="C186" s="27" t="n"/>
       <c r="D186">
-        <f>IF($B186="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B186,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B186,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B186="","",IFERROR(INDEX($D$17:$D$185,MATCH($B186,$B$17:$B$185,0)),""))</f>
         <v/>
       </c>
       <c r="E186">
@@ -34741,7 +34728,7 @@
       <c r="A187" s="37" t="n"/>
       <c r="C187" s="27" t="n"/>
       <c r="D187">
-        <f>IF($B187="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B187,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B187,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B187="","",IFERROR(INDEX($D$17:$D$186,MATCH($B187,$B$17:$B$186,0)),""))</f>
         <v/>
       </c>
       <c r="E187">
@@ -34761,7 +34748,7 @@
       <c r="A188" s="37" t="n"/>
       <c r="C188" s="27" t="n"/>
       <c r="D188">
-        <f>IF($B188="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B188,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B188,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B188="","",IFERROR(INDEX($D$17:$D$187,MATCH($B188,$B$17:$B$187,0)),""))</f>
         <v/>
       </c>
       <c r="E188">
@@ -34781,7 +34768,7 @@
       <c r="A189" s="37" t="n"/>
       <c r="C189" s="27" t="n"/>
       <c r="D189">
-        <f>IF($B189="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B189,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B189,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B189="","",IFERROR(INDEX($D$17:$D$188,MATCH($B189,$B$17:$B$188,0)),""))</f>
         <v/>
       </c>
       <c r="E189">
@@ -34801,7 +34788,7 @@
       <c r="A190" s="37" t="n"/>
       <c r="C190" s="27" t="n"/>
       <c r="D190">
-        <f>IF($B190="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B190,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B190,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B190="","",IFERROR(INDEX($D$17:$D$189,MATCH($B190,$B$17:$B$189,0)),""))</f>
         <v/>
       </c>
       <c r="E190">
@@ -34821,7 +34808,7 @@
       <c r="A191" s="37" t="n"/>
       <c r="C191" s="27" t="n"/>
       <c r="D191">
-        <f>IF($B191="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B191,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B191,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B191="","",IFERROR(INDEX($D$17:$D$190,MATCH($B191,$B$17:$B$190,0)),""))</f>
         <v/>
       </c>
       <c r="E191">
@@ -34841,7 +34828,7 @@
       <c r="A192" s="37" t="n"/>
       <c r="C192" s="27" t="n"/>
       <c r="D192">
-        <f>IF($B192="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B192,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B192,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B192="","",IFERROR(INDEX($D$17:$D$191,MATCH($B192,$B$17:$B$191,0)),""))</f>
         <v/>
       </c>
       <c r="E192">
@@ -34861,7 +34848,7 @@
       <c r="A193" s="37" t="n"/>
       <c r="C193" s="27" t="n"/>
       <c r="D193">
-        <f>IF($B193="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B193,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B193,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B193="","",IFERROR(INDEX($D$17:$D$192,MATCH($B193,$B$17:$B$192,0)),""))</f>
         <v/>
       </c>
       <c r="E193">
@@ -34881,7 +34868,7 @@
       <c r="A194" s="37" t="n"/>
       <c r="C194" s="27" t="n"/>
       <c r="D194">
-        <f>IF($B194="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B194,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B194,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B194="","",IFERROR(INDEX($D$17:$D$193,MATCH($B194,$B$17:$B$193,0)),""))</f>
         <v/>
       </c>
       <c r="E194">
@@ -34901,7 +34888,7 @@
       <c r="A195" s="37" t="n"/>
       <c r="C195" s="27" t="n"/>
       <c r="D195">
-        <f>IF($B195="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B195,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B195,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B195="","",IFERROR(INDEX($D$17:$D$194,MATCH($B195,$B$17:$B$194,0)),""))</f>
         <v/>
       </c>
       <c r="E195">
@@ -34921,7 +34908,7 @@
       <c r="A196" s="37" t="n"/>
       <c r="C196" s="27" t="n"/>
       <c r="D196">
-        <f>IF($B196="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B196,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B196,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B196="","",IFERROR(INDEX($D$17:$D$195,MATCH($B196,$B$17:$B$195,0)),""))</f>
         <v/>
       </c>
       <c r="E196">
@@ -34941,7 +34928,7 @@
       <c r="A197" s="37" t="n"/>
       <c r="C197" s="27" t="n"/>
       <c r="D197">
-        <f>IF($B197="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B197,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B197,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B197="","",IFERROR(INDEX($D$17:$D$196,MATCH($B197,$B$17:$B$196,0)),""))</f>
         <v/>
       </c>
       <c r="E197">
@@ -34961,7 +34948,7 @@
       <c r="A198" s="37" t="n"/>
       <c r="C198" s="27" t="n"/>
       <c r="D198">
-        <f>IF($B198="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B198,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B198,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B198="","",IFERROR(INDEX($D$17:$D$197,MATCH($B198,$B$17:$B$197,0)),""))</f>
         <v/>
       </c>
       <c r="E198">
@@ -34981,7 +34968,7 @@
       <c r="A199" s="37" t="n"/>
       <c r="C199" s="27" t="n"/>
       <c r="D199">
-        <f>IF($B199="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B199,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B199,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B199="","",IFERROR(INDEX($D$17:$D$198,MATCH($B199,$B$17:$B$198,0)),""))</f>
         <v/>
       </c>
       <c r="E199">
@@ -35001,7 +34988,7 @@
       <c r="A200" s="37" t="n"/>
       <c r="C200" s="27" t="n"/>
       <c r="D200">
-        <f>IF($B200="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B200,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B200,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B200="","",IFERROR(INDEX($D$17:$D$199,MATCH($B200,$B$17:$B$199,0)),""))</f>
         <v/>
       </c>
       <c r="E200">
@@ -35021,7 +35008,7 @@
       <c r="A201" s="37" t="n"/>
       <c r="C201" s="27" t="n"/>
       <c r="D201">
-        <f>IF($B201="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B201,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B201,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B201="","",IFERROR(INDEX($D$17:$D$200,MATCH($B201,$B$17:$B$200,0)),""))</f>
         <v/>
       </c>
       <c r="E201">
@@ -35041,7 +35028,7 @@
       <c r="A202" s="37" t="n"/>
       <c r="C202" s="27" t="n"/>
       <c r="D202">
-        <f>IF($B202="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B202,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B202,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B202="","",IFERROR(INDEX($D$17:$D$201,MATCH($B202,$B$17:$B$201,0)),""))</f>
         <v/>
       </c>
       <c r="E202">
@@ -35061,7 +35048,7 @@
       <c r="A203" s="37" t="n"/>
       <c r="C203" s="27" t="n"/>
       <c r="D203">
-        <f>IF($B203="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B203,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B203,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B203="","",IFERROR(INDEX($D$17:$D$202,MATCH($B203,$B$17:$B$202,0)),""))</f>
         <v/>
       </c>
       <c r="E203">
@@ -35081,7 +35068,7 @@
       <c r="A204" s="37" t="n"/>
       <c r="C204" s="27" t="n"/>
       <c r="D204">
-        <f>IF($B204="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B204,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B204,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B204="","",IFERROR(INDEX($D$17:$D$203,MATCH($B204,$B$17:$B$203,0)),""))</f>
         <v/>
       </c>
       <c r="E204">
@@ -35101,7 +35088,7 @@
       <c r="A205" s="37" t="n"/>
       <c r="C205" s="27" t="n"/>
       <c r="D205">
-        <f>IF($B205="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B205,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B205,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B205="","",IFERROR(INDEX($D$17:$D$204,MATCH($B205,$B$17:$B$204,0)),""))</f>
         <v/>
       </c>
       <c r="E205">
@@ -35121,7 +35108,7 @@
       <c r="A206" s="37" t="n"/>
       <c r="C206" s="27" t="n"/>
       <c r="D206">
-        <f>IF($B206="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B206,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B206,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B206="","",IFERROR(INDEX($D$17:$D$205,MATCH($B206,$B$17:$B$205,0)),""))</f>
         <v/>
       </c>
       <c r="E206">
@@ -35141,7 +35128,7 @@
       <c r="A207" s="37" t="n"/>
       <c r="C207" s="27" t="n"/>
       <c r="D207">
-        <f>IF($B207="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B207,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B207,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B207="","",IFERROR(INDEX($D$17:$D$206,MATCH($B207,$B$17:$B$206,0)),""))</f>
         <v/>
       </c>
       <c r="E207">
@@ -35161,7 +35148,7 @@
       <c r="A208" s="37" t="n"/>
       <c r="C208" s="27" t="n"/>
       <c r="D208">
-        <f>IF($B208="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B208,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B208,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B208="","",IFERROR(INDEX($D$17:$D$207,MATCH($B208,$B$17:$B$207,0)),""))</f>
         <v/>
       </c>
       <c r="E208">
@@ -35181,7 +35168,7 @@
       <c r="A209" s="37" t="n"/>
       <c r="C209" s="27" t="n"/>
       <c r="D209">
-        <f>IF($B209="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B209,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B209,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B209="","",IFERROR(INDEX($D$17:$D$208,MATCH($B209,$B$17:$B$208,0)),""))</f>
         <v/>
       </c>
       <c r="E209">
@@ -35201,7 +35188,7 @@
       <c r="A210" s="37" t="n"/>
       <c r="C210" s="27" t="n"/>
       <c r="D210">
-        <f>IF($B210="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B210,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B210,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B210="","",IFERROR(INDEX($D$17:$D$209,MATCH($B210,$B$17:$B$209,0)),""))</f>
         <v/>
       </c>
       <c r="E210">
@@ -35221,7 +35208,7 @@
       <c r="A211" s="37" t="n"/>
       <c r="C211" s="27" t="n"/>
       <c r="D211">
-        <f>IF($B211="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B211,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B211,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B211="","",IFERROR(INDEX($D$17:$D$210,MATCH($B211,$B$17:$B$210,0)),""))</f>
         <v/>
       </c>
       <c r="E211">
@@ -35241,7 +35228,7 @@
       <c r="A212" s="37" t="n"/>
       <c r="C212" s="27" t="n"/>
       <c r="D212">
-        <f>IF($B212="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B212,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B212,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B212="","",IFERROR(INDEX($D$17:$D$211,MATCH($B212,$B$17:$B$211,0)),""))</f>
         <v/>
       </c>
       <c r="E212">
@@ -35261,7 +35248,7 @@
       <c r="A213" s="37" t="n"/>
       <c r="C213" s="27" t="n"/>
       <c r="D213">
-        <f>IF($B213="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B213,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B213,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B213="","",IFERROR(INDEX($D$17:$D$212,MATCH($B213,$B$17:$B$212,0)),""))</f>
         <v/>
       </c>
       <c r="E213">
@@ -35281,7 +35268,7 @@
       <c r="A214" s="37" t="n"/>
       <c r="C214" s="27" t="n"/>
       <c r="D214">
-        <f>IF($B214="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B214,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B214,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B214="","",IFERROR(INDEX($D$17:$D$213,MATCH($B214,$B$17:$B$213,0)),""))</f>
         <v/>
       </c>
       <c r="E214">
@@ -35301,7 +35288,7 @@
       <c r="A215" s="37" t="n"/>
       <c r="C215" s="27" t="n"/>
       <c r="D215">
-        <f>IF($B215="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B215,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B215,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B215="","",IFERROR(INDEX($D$17:$D$214,MATCH($B215,$B$17:$B$214,0)),""))</f>
         <v/>
       </c>
       <c r="E215">
@@ -35321,7 +35308,7 @@
       <c r="A216" s="37" t="n"/>
       <c r="C216" s="27" t="n"/>
       <c r="D216">
-        <f>IF($B216="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B216,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B216,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B216="","",IFERROR(INDEX($D$17:$D$215,MATCH($B216,$B$17:$B$215,0)),""))</f>
         <v/>
       </c>
       <c r="E216">
@@ -35341,7 +35328,7 @@
       <c r="A217" s="37" t="n"/>
       <c r="C217" s="27" t="n"/>
       <c r="D217">
-        <f>IF($B217="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B217,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B217,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B217="","",IFERROR(INDEX($D$17:$D$216,MATCH($B217,$B$17:$B$216,0)),""))</f>
         <v/>
       </c>
       <c r="E217">
@@ -35361,7 +35348,7 @@
       <c r="A218" s="37" t="n"/>
       <c r="C218" s="27" t="n"/>
       <c r="D218">
-        <f>IF($B218="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B218,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B218,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B218="","",IFERROR(INDEX($D$17:$D$217,MATCH($B218,$B$17:$B$217,0)),""))</f>
         <v/>
       </c>
       <c r="E218">
@@ -35381,7 +35368,7 @@
       <c r="A219" s="37" t="n"/>
       <c r="C219" s="27" t="n"/>
       <c r="D219">
-        <f>IF($B219="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B219,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B219,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B219="","",IFERROR(INDEX($D$17:$D$218,MATCH($B219,$B$17:$B$218,0)),""))</f>
         <v/>
       </c>
       <c r="E219">
@@ -35401,7 +35388,7 @@
       <c r="A220" s="37" t="n"/>
       <c r="C220" s="27" t="n"/>
       <c r="D220">
-        <f>IF($B220="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B220,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B220,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B220="","",IFERROR(INDEX($D$17:$D$219,MATCH($B220,$B$17:$B$219,0)),""))</f>
         <v/>
       </c>
       <c r="E220">
@@ -35421,7 +35408,7 @@
       <c r="A221" s="37" t="n"/>
       <c r="C221" s="27" t="n"/>
       <c r="D221">
-        <f>IF($B221="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B221,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B221,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B221="","",IFERROR(INDEX($D$17:$D$220,MATCH($B221,$B$17:$B$220,0)),""))</f>
         <v/>
       </c>
       <c r="E221">
@@ -35441,7 +35428,7 @@
       <c r="A222" s="37" t="n"/>
       <c r="C222" s="27" t="n"/>
       <c r="D222">
-        <f>IF($B222="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B222,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B222,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B222="","",IFERROR(INDEX($D$17:$D$221,MATCH($B222,$B$17:$B$221,0)),""))</f>
         <v/>
       </c>
       <c r="E222">
@@ -35461,7 +35448,7 @@
       <c r="A223" s="37" t="n"/>
       <c r="C223" s="27" t="n"/>
       <c r="D223">
-        <f>IF($B223="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B223,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B223,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B223="","",IFERROR(INDEX($D$17:$D$222,MATCH($B223,$B$17:$B$222,0)),""))</f>
         <v/>
       </c>
       <c r="E223">
@@ -35481,7 +35468,7 @@
       <c r="A224" s="37" t="n"/>
       <c r="C224" s="27" t="n"/>
       <c r="D224">
-        <f>IF($B224="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B224,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B224,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B224="","",IFERROR(INDEX($D$17:$D$223,MATCH($B224,$B$17:$B$223,0)),""))</f>
         <v/>
       </c>
       <c r="E224">
@@ -35501,7 +35488,7 @@
       <c r="A225" s="37" t="n"/>
       <c r="C225" s="27" t="n"/>
       <c r="D225">
-        <f>IF($B225="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B225,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B225,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B225="","",IFERROR(INDEX($D$17:$D$224,MATCH($B225,$B$17:$B$224,0)),""))</f>
         <v/>
       </c>
       <c r="E225">
@@ -35521,7 +35508,7 @@
       <c r="A226" s="37" t="n"/>
       <c r="C226" s="27" t="n"/>
       <c r="D226">
-        <f>IF($B226="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B226,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B226,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B226="","",IFERROR(INDEX($D$17:$D$225,MATCH($B226,$B$17:$B$225,0)),""))</f>
         <v/>
       </c>
       <c r="E226">
@@ -35541,7 +35528,7 @@
       <c r="A227" s="37" t="n"/>
       <c r="C227" s="27" t="n"/>
       <c r="D227">
-        <f>IF($B227="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B227,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B227,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B227="","",IFERROR(INDEX($D$17:$D$226,MATCH($B227,$B$17:$B$226,0)),""))</f>
         <v/>
       </c>
       <c r="E227">
@@ -35561,7 +35548,7 @@
       <c r="A228" s="37" t="n"/>
       <c r="C228" s="27" t="n"/>
       <c r="D228">
-        <f>IF($B228="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B228,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B228,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B228="","",IFERROR(INDEX($D$17:$D$227,MATCH($B228,$B$17:$B$227,0)),""))</f>
         <v/>
       </c>
       <c r="E228">
@@ -35581,7 +35568,7 @@
       <c r="A229" s="37" t="n"/>
       <c r="C229" s="27" t="n"/>
       <c r="D229">
-        <f>IF($B229="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B229,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B229,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B229="","",IFERROR(INDEX($D$17:$D$228,MATCH($B229,$B$17:$B$228,0)),""))</f>
         <v/>
       </c>
       <c r="E229">
@@ -35601,7 +35588,7 @@
       <c r="A230" s="37" t="n"/>
       <c r="C230" s="27" t="n"/>
       <c r="D230">
-        <f>IF($B230="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B230,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B230,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B230="","",IFERROR(INDEX($D$17:$D$229,MATCH($B230,$B$17:$B$229,0)),""))</f>
         <v/>
       </c>
       <c r="E230">
@@ -35621,7 +35608,7 @@
       <c r="A231" s="37" t="n"/>
       <c r="C231" s="27" t="n"/>
       <c r="D231">
-        <f>IF($B231="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B231,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B231,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B231="","",IFERROR(INDEX($D$17:$D$230,MATCH($B231,$B$17:$B$230,0)),""))</f>
         <v/>
       </c>
       <c r="E231">
@@ -35641,7 +35628,7 @@
       <c r="A232" s="37" t="n"/>
       <c r="C232" s="27" t="n"/>
       <c r="D232">
-        <f>IF($B232="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B232,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B232,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B232="","",IFERROR(INDEX($D$17:$D$231,MATCH($B232,$B$17:$B$231,0)),""))</f>
         <v/>
       </c>
       <c r="E232">
@@ -35661,7 +35648,7 @@
       <c r="A233" s="37" t="n"/>
       <c r="C233" s="27" t="n"/>
       <c r="D233">
-        <f>IF($B233="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B233,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B233,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B233="","",IFERROR(INDEX($D$17:$D$232,MATCH($B233,$B$17:$B$232,0)),""))</f>
         <v/>
       </c>
       <c r="E233">
@@ -35681,7 +35668,7 @@
       <c r="A234" s="37" t="n"/>
       <c r="C234" s="27" t="n"/>
       <c r="D234">
-        <f>IF($B234="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B234,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B234,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B234="","",IFERROR(INDEX($D$17:$D$233,MATCH($B234,$B$17:$B$233,0)),""))</f>
         <v/>
       </c>
       <c r="E234">
@@ -35701,7 +35688,7 @@
       <c r="A235" s="37" t="n"/>
       <c r="C235" s="27" t="n"/>
       <c r="D235">
-        <f>IF($B235="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B235,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B235,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B235="","",IFERROR(INDEX($D$17:$D$234,MATCH($B235,$B$17:$B$234,0)),""))</f>
         <v/>
       </c>
       <c r="E235">
@@ -35721,7 +35708,7 @@
       <c r="A236" s="37" t="n"/>
       <c r="C236" s="27" t="n"/>
       <c r="D236">
-        <f>IF($B236="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B236,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B236,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B236="","",IFERROR(INDEX($D$17:$D$235,MATCH($B236,$B$17:$B$235,0)),""))</f>
         <v/>
       </c>
       <c r="E236">
@@ -35741,7 +35728,7 @@
       <c r="A237" s="37" t="n"/>
       <c r="C237" s="27" t="n"/>
       <c r="D237">
-        <f>IF($B237="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B237,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B237,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B237="","",IFERROR(INDEX($D$17:$D$236,MATCH($B237,$B$17:$B$236,0)),""))</f>
         <v/>
       </c>
       <c r="E237">
@@ -35761,7 +35748,7 @@
       <c r="A238" s="37" t="n"/>
       <c r="C238" s="27" t="n"/>
       <c r="D238">
-        <f>IF($B238="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B238,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B238,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B238="","",IFERROR(INDEX($D$17:$D$237,MATCH($B238,$B$17:$B$237,0)),""))</f>
         <v/>
       </c>
       <c r="E238">
@@ -35781,7 +35768,7 @@
       <c r="A239" s="37" t="n"/>
       <c r="C239" s="27" t="n"/>
       <c r="D239">
-        <f>IF($B239="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B239,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B239,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B239="","",IFERROR(INDEX($D$17:$D$238,MATCH($B239,$B$17:$B$238,0)),""))</f>
         <v/>
       </c>
       <c r="E239">
@@ -35801,7 +35788,7 @@
       <c r="A240" s="37" t="n"/>
       <c r="C240" s="27" t="n"/>
       <c r="D240">
-        <f>IF($B240="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B240,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B240,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B240="","",IFERROR(INDEX($D$17:$D$239,MATCH($B240,$B$17:$B$239,0)),""))</f>
         <v/>
       </c>
       <c r="E240">
@@ -35821,7 +35808,7 @@
       <c r="A241" s="37" t="n"/>
       <c r="C241" s="27" t="n"/>
       <c r="D241">
-        <f>IF($B241="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B241,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B241,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B241="","",IFERROR(INDEX($D$17:$D$240,MATCH($B241,$B$17:$B$240,0)),""))</f>
         <v/>
       </c>
       <c r="E241">
@@ -35841,7 +35828,7 @@
       <c r="A242" s="37" t="n"/>
       <c r="C242" s="27" t="n"/>
       <c r="D242">
-        <f>IF($B242="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B242,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B242,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B242="","",IFERROR(INDEX($D$17:$D$241,MATCH($B242,$B$17:$B$241,0)),""))</f>
         <v/>
       </c>
       <c r="E242">
@@ -35861,7 +35848,7 @@
       <c r="A243" s="37" t="n"/>
       <c r="C243" s="27" t="n"/>
       <c r="D243">
-        <f>IF($B243="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B243,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B243,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B243="","",IFERROR(INDEX($D$17:$D$242,MATCH($B243,$B$17:$B$242,0)),""))</f>
         <v/>
       </c>
       <c r="E243">
@@ -35881,7 +35868,7 @@
       <c r="A244" s="37" t="n"/>
       <c r="C244" s="27" t="n"/>
       <c r="D244">
-        <f>IF($B244="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B244,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B244,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B244="","",IFERROR(INDEX($D$17:$D$243,MATCH($B244,$B$17:$B$243,0)),""))</f>
         <v/>
       </c>
       <c r="E244">
@@ -35901,7 +35888,7 @@
       <c r="A245" s="37" t="n"/>
       <c r="C245" s="27" t="n"/>
       <c r="D245">
-        <f>IF($B245="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B245,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B245,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B245="","",IFERROR(INDEX($D$17:$D$244,MATCH($B245,$B$17:$B$244,0)),""))</f>
         <v/>
       </c>
       <c r="E245">
@@ -35921,7 +35908,7 @@
       <c r="A246" s="37" t="n"/>
       <c r="C246" s="27" t="n"/>
       <c r="D246">
-        <f>IF($B246="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B246,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B246,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B246="","",IFERROR(INDEX($D$17:$D$245,MATCH($B246,$B$17:$B$245,0)),""))</f>
         <v/>
       </c>
       <c r="E246">
@@ -35941,7 +35928,7 @@
       <c r="A247" s="37" t="n"/>
       <c r="C247" s="27" t="n"/>
       <c r="D247">
-        <f>IF($B247="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B247,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B247,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B247="","",IFERROR(INDEX($D$17:$D$246,MATCH($B247,$B$17:$B$246,0)),""))</f>
         <v/>
       </c>
       <c r="E247">
@@ -35961,7 +35948,7 @@
       <c r="A248" s="37" t="n"/>
       <c r="C248" s="27" t="n"/>
       <c r="D248">
-        <f>IF($B248="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B248,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B248,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B248="","",IFERROR(INDEX($D$17:$D$247,MATCH($B248,$B$17:$B$247,0)),""))</f>
         <v/>
       </c>
       <c r="E248">
@@ -35981,7 +35968,7 @@
       <c r="A249" s="37" t="n"/>
       <c r="C249" s="27" t="n"/>
       <c r="D249">
-        <f>IF($B249="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B249,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B249,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B249="","",IFERROR(INDEX($D$17:$D$248,MATCH($B249,$B$17:$B$248,0)),""))</f>
         <v/>
       </c>
       <c r="E249">
@@ -36001,7 +35988,7 @@
       <c r="A250" s="37" t="n"/>
       <c r="C250" s="27" t="n"/>
       <c r="D250">
-        <f>IF($B250="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B250,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B250,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B250="","",IFERROR(INDEX($D$17:$D$249,MATCH($B250,$B$17:$B$249,0)),""))</f>
         <v/>
       </c>
       <c r="E250">
@@ -36021,7 +36008,7 @@
       <c r="A251" s="37" t="n"/>
       <c r="C251" s="27" t="n"/>
       <c r="D251">
-        <f>IF($B251="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B251,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B251,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B251="","",IFERROR(INDEX($D$17:$D$250,MATCH($B251,$B$17:$B$250,0)),""))</f>
         <v/>
       </c>
       <c r="E251">
@@ -36041,7 +36028,7 @@
       <c r="A252" s="37" t="n"/>
       <c r="C252" s="27" t="n"/>
       <c r="D252">
-        <f>IF($B252="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B252,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B252,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B252="","",IFERROR(INDEX($D$17:$D$251,MATCH($B252,$B$17:$B$251,0)),""))</f>
         <v/>
       </c>
       <c r="E252">
@@ -36061,7 +36048,7 @@
       <c r="A253" s="37" t="n"/>
       <c r="C253" s="27" t="n"/>
       <c r="D253">
-        <f>IF($B253="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B253,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B253,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B253="","",IFERROR(INDEX($D$17:$D$252,MATCH($B253,$B$17:$B$252,0)),""))</f>
         <v/>
       </c>
       <c r="E253">
@@ -36081,7 +36068,7 @@
       <c r="A254" s="37" t="n"/>
       <c r="C254" s="27" t="n"/>
       <c r="D254">
-        <f>IF($B254="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B254,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B254,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B254="","",IFERROR(INDEX($D$17:$D$253,MATCH($B254,$B$17:$B$253,0)),""))</f>
         <v/>
       </c>
       <c r="E254">
@@ -36101,7 +36088,7 @@
       <c r="A255" s="37" t="n"/>
       <c r="C255" s="27" t="n"/>
       <c r="D255">
-        <f>IF($B255="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B255,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B255,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B255="","",IFERROR(INDEX($D$17:$D$254,MATCH($B255,$B$17:$B$254,0)),""))</f>
         <v/>
       </c>
       <c r="E255">
@@ -36121,7 +36108,7 @@
       <c r="A256" s="37" t="n"/>
       <c r="C256" s="27" t="n"/>
       <c r="D256">
-        <f>IF($B256="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B256,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B256,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B256="","",IFERROR(INDEX($D$17:$D$255,MATCH($B256,$B$17:$B$255,0)),""))</f>
         <v/>
       </c>
       <c r="E256">
@@ -36141,7 +36128,7 @@
       <c r="A257" s="37" t="n"/>
       <c r="C257" s="27" t="n"/>
       <c r="D257">
-        <f>IF($B257="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B257,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B257,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B257="","",IFERROR(INDEX($D$17:$D$256,MATCH($B257,$B$17:$B$256,0)),""))</f>
         <v/>
       </c>
       <c r="E257">
@@ -36161,7 +36148,7 @@
       <c r="A258" s="37" t="n"/>
       <c r="C258" s="27" t="n"/>
       <c r="D258">
-        <f>IF($B258="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B258,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B258,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B258="","",IFERROR(INDEX($D$17:$D$257,MATCH($B258,$B$17:$B$257,0)),""))</f>
         <v/>
       </c>
       <c r="E258">
@@ -36181,7 +36168,7 @@
       <c r="A259" s="37" t="n"/>
       <c r="C259" s="27" t="n"/>
       <c r="D259">
-        <f>IF($B259="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B259,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B259,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B259="","",IFERROR(INDEX($D$17:$D$258,MATCH($B259,$B$17:$B$258,0)),""))</f>
         <v/>
       </c>
       <c r="E259">
@@ -36201,7 +36188,7 @@
       <c r="A260" s="37" t="n"/>
       <c r="C260" s="27" t="n"/>
       <c r="D260">
-        <f>IF($B260="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B260,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B260,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B260="","",IFERROR(INDEX($D$17:$D$259,MATCH($B260,$B$17:$B$259,0)),""))</f>
         <v/>
       </c>
       <c r="E260">
@@ -36221,7 +36208,7 @@
       <c r="A261" s="37" t="n"/>
       <c r="C261" s="27" t="n"/>
       <c r="D261">
-        <f>IF($B261="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B261,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B261,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B261="","",IFERROR(INDEX($D$17:$D$260,MATCH($B261,$B$17:$B$260,0)),""))</f>
         <v/>
       </c>
       <c r="E261">
@@ -36241,7 +36228,7 @@
       <c r="A262" s="37" t="n"/>
       <c r="C262" s="27" t="n"/>
       <c r="D262">
-        <f>IF($B262="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B262,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B262,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B262="","",IFERROR(INDEX($D$17:$D$261,MATCH($B262,$B$17:$B$261,0)),""))</f>
         <v/>
       </c>
       <c r="E262">
@@ -36261,7 +36248,7 @@
       <c r="A263" s="37" t="n"/>
       <c r="C263" s="27" t="n"/>
       <c r="D263">
-        <f>IF($B263="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B263,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B263,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B263="","",IFERROR(INDEX($D$17:$D$262,MATCH($B263,$B$17:$B$262,0)),""))</f>
         <v/>
       </c>
       <c r="E263">
@@ -36281,7 +36268,7 @@
       <c r="A264" s="37" t="n"/>
       <c r="C264" s="27" t="n"/>
       <c r="D264">
-        <f>IF($B264="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B264,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B264,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B264="","",IFERROR(INDEX($D$17:$D$263,MATCH($B264,$B$17:$B$263,0)),""))</f>
         <v/>
       </c>
       <c r="E264">
@@ -36301,7 +36288,7 @@
       <c r="A265" s="37" t="n"/>
       <c r="C265" s="27" t="n"/>
       <c r="D265">
-        <f>IF($B265="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B265,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B265,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B265="","",IFERROR(INDEX($D$17:$D$264,MATCH($B265,$B$17:$B$264,0)),""))</f>
         <v/>
       </c>
       <c r="E265">
@@ -36321,7 +36308,7 @@
       <c r="A266" s="37" t="n"/>
       <c r="C266" s="27" t="n"/>
       <c r="D266">
-        <f>IF($B266="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B266,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B266,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B266="","",IFERROR(INDEX($D$17:$D$265,MATCH($B266,$B$17:$B$265,0)),""))</f>
         <v/>
       </c>
       <c r="E266">
@@ -36341,7 +36328,7 @@
       <c r="A267" s="37" t="n"/>
       <c r="C267" s="27" t="n"/>
       <c r="D267">
-        <f>IF($B267="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B267,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B267,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B267="","",IFERROR(INDEX($D$17:$D$266,MATCH($B267,$B$17:$B$266,0)),""))</f>
         <v/>
       </c>
       <c r="E267">
@@ -36361,7 +36348,7 @@
       <c r="A268" s="37" t="n"/>
       <c r="C268" s="27" t="n"/>
       <c r="D268">
-        <f>IF($B268="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B268,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B268,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B268="","",IFERROR(INDEX($D$17:$D$267,MATCH($B268,$B$17:$B$267,0)),""))</f>
         <v/>
       </c>
       <c r="E268">
@@ -36381,7 +36368,7 @@
       <c r="A269" s="37" t="n"/>
       <c r="C269" s="27" t="n"/>
       <c r="D269">
-        <f>IF($B269="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B269,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B269,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B269="","",IFERROR(INDEX($D$17:$D$268,MATCH($B269,$B$17:$B$268,0)),""))</f>
         <v/>
       </c>
       <c r="E269">
@@ -36401,7 +36388,7 @@
       <c r="A270" s="37" t="n"/>
       <c r="C270" s="27" t="n"/>
       <c r="D270">
-        <f>IF($B270="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B270,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B270,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B270="","",IFERROR(INDEX($D$17:$D$269,MATCH($B270,$B$17:$B$269,0)),""))</f>
         <v/>
       </c>
       <c r="E270">
@@ -36421,7 +36408,7 @@
       <c r="A271" s="37" t="n"/>
       <c r="C271" s="27" t="n"/>
       <c r="D271">
-        <f>IF($B271="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B271,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B271,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B271="","",IFERROR(INDEX($D$17:$D$270,MATCH($B271,$B$17:$B$270,0)),""))</f>
         <v/>
       </c>
       <c r="E271">
@@ -36441,7 +36428,7 @@
       <c r="A272" s="37" t="n"/>
       <c r="C272" s="27" t="n"/>
       <c r="D272">
-        <f>IF($B272="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B272,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B272,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B272="","",IFERROR(INDEX($D$17:$D$271,MATCH($B272,$B$17:$B$271,0)),""))</f>
         <v/>
       </c>
       <c r="E272">
@@ -36461,7 +36448,7 @@
       <c r="A273" s="37" t="n"/>
       <c r="C273" s="27" t="n"/>
       <c r="D273">
-        <f>IF($B273="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B273,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B273,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B273="","",IFERROR(INDEX($D$17:$D$272,MATCH($B273,$B$17:$B$272,0)),""))</f>
         <v/>
       </c>
       <c r="E273">
@@ -36481,7 +36468,7 @@
       <c r="A274" s="37" t="n"/>
       <c r="C274" s="27" t="n"/>
       <c r="D274">
-        <f>IF($B274="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B274,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B274,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B274="","",IFERROR(INDEX($D$17:$D$273,MATCH($B274,$B$17:$B$273,0)),""))</f>
         <v/>
       </c>
       <c r="E274">
@@ -36501,7 +36488,7 @@
       <c r="A275" s="37" t="n"/>
       <c r="C275" s="27" t="n"/>
       <c r="D275">
-        <f>IF($B275="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B275,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B275,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B275="","",IFERROR(INDEX($D$17:$D$274,MATCH($B275,$B$17:$B$274,0)),""))</f>
         <v/>
       </c>
       <c r="E275">
@@ -36521,7 +36508,7 @@
       <c r="A276" s="37" t="n"/>
       <c r="C276" s="27" t="n"/>
       <c r="D276">
-        <f>IF($B276="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B276,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B276,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B276="","",IFERROR(INDEX($D$17:$D$275,MATCH($B276,$B$17:$B$275,0)),""))</f>
         <v/>
       </c>
       <c r="E276">
@@ -36541,7 +36528,7 @@
       <c r="A277" s="37" t="n"/>
       <c r="C277" s="27" t="n"/>
       <c r="D277">
-        <f>IF($B277="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B277,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B277,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B277="","",IFERROR(INDEX($D$17:$D$276,MATCH($B277,$B$17:$B$276,0)),""))</f>
         <v/>
       </c>
       <c r="E277">
@@ -36561,7 +36548,7 @@
       <c r="A278" s="37" t="n"/>
       <c r="C278" s="27" t="n"/>
       <c r="D278">
-        <f>IF($B278="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B278,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B278,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B278="","",IFERROR(INDEX($D$17:$D$277,MATCH($B278,$B$17:$B$277,0)),""))</f>
         <v/>
       </c>
       <c r="E278">
@@ -36581,7 +36568,7 @@
       <c r="A279" s="37" t="n"/>
       <c r="C279" s="27" t="n"/>
       <c r="D279">
-        <f>IF($B279="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B279,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B279,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B279="","",IFERROR(INDEX($D$17:$D$278,MATCH($B279,$B$17:$B$278,0)),""))</f>
         <v/>
       </c>
       <c r="E279">
@@ -36601,7 +36588,7 @@
       <c r="A280" s="37" t="n"/>
       <c r="C280" s="27" t="n"/>
       <c r="D280">
-        <f>IF($B280="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B280,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B280,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B280="","",IFERROR(INDEX($D$17:$D$279,MATCH($B280,$B$17:$B$279,0)),""))</f>
         <v/>
       </c>
       <c r="E280">
@@ -36621,7 +36608,7 @@
       <c r="A281" s="37" t="n"/>
       <c r="C281" s="27" t="n"/>
       <c r="D281">
-        <f>IF($B281="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B281,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B281,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B281="","",IFERROR(INDEX($D$17:$D$280,MATCH($B281,$B$17:$B$280,0)),""))</f>
         <v/>
       </c>
       <c r="E281">
@@ -36641,7 +36628,7 @@
       <c r="A282" s="37" t="n"/>
       <c r="C282" s="27" t="n"/>
       <c r="D282">
-        <f>IF($B282="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B282,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B282,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B282="","",IFERROR(INDEX($D$17:$D$281,MATCH($B282,$B$17:$B$281,0)),""))</f>
         <v/>
       </c>
       <c r="E282">
@@ -36661,7 +36648,7 @@
       <c r="A283" s="37" t="n"/>
       <c r="C283" s="27" t="n"/>
       <c r="D283">
-        <f>IF($B283="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B283,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B283,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B283="","",IFERROR(INDEX($D$17:$D$282,MATCH($B283,$B$17:$B$282,0)),""))</f>
         <v/>
       </c>
       <c r="E283">
@@ -36681,7 +36668,7 @@
       <c r="A284" s="37" t="n"/>
       <c r="C284" s="27" t="n"/>
       <c r="D284">
-        <f>IF($B284="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B284,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B284,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B284="","",IFERROR(INDEX($D$17:$D$283,MATCH($B284,$B$17:$B$283,0)),""))</f>
         <v/>
       </c>
       <c r="E284">
@@ -36701,7 +36688,7 @@
       <c r="A285" s="37" t="n"/>
       <c r="C285" s="27" t="n"/>
       <c r="D285">
-        <f>IF($B285="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B285,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B285,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B285="","",IFERROR(INDEX($D$17:$D$284,MATCH($B285,$B$17:$B$284,0)),""))</f>
         <v/>
       </c>
       <c r="E285">
@@ -36721,7 +36708,7 @@
       <c r="A286" s="37" t="n"/>
       <c r="C286" s="27" t="n"/>
       <c r="D286">
-        <f>IF($B286="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B286,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B286,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B286="","",IFERROR(INDEX($D$17:$D$285,MATCH($B286,$B$17:$B$285,0)),""))</f>
         <v/>
       </c>
       <c r="E286">
@@ -36741,7 +36728,7 @@
       <c r="A287" s="37" t="n"/>
       <c r="C287" s="27" t="n"/>
       <c r="D287">
-        <f>IF($B287="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B287,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B287,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B287="","",IFERROR(INDEX($D$17:$D$286,MATCH($B287,$B$17:$B$286,0)),""))</f>
         <v/>
       </c>
       <c r="E287">
@@ -36761,7 +36748,7 @@
       <c r="A288" s="37" t="n"/>
       <c r="C288" s="27" t="n"/>
       <c r="D288">
-        <f>IF($B288="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B288,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B288,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B288="","",IFERROR(INDEX($D$17:$D$287,MATCH($B288,$B$17:$B$287,0)),""))</f>
         <v/>
       </c>
       <c r="E288">
@@ -36781,7 +36768,7 @@
       <c r="A289" s="37" t="n"/>
       <c r="C289" s="27" t="n"/>
       <c r="D289">
-        <f>IF($B289="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B289,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B289,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B289="","",IFERROR(INDEX($D$17:$D$288,MATCH($B289,$B$17:$B$288,0)),""))</f>
         <v/>
       </c>
       <c r="E289">
@@ -36801,7 +36788,7 @@
       <c r="A290" s="37" t="n"/>
       <c r="C290" s="27" t="n"/>
       <c r="D290">
-        <f>IF($B290="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B290,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B290,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B290="","",IFERROR(INDEX($D$17:$D$289,MATCH($B290,$B$17:$B$289,0)),""))</f>
         <v/>
       </c>
       <c r="E290">
@@ -36821,7 +36808,7 @@
       <c r="A291" s="37" t="n"/>
       <c r="C291" s="27" t="n"/>
       <c r="D291">
-        <f>IF($B291="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B291,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B291,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B291="","",IFERROR(INDEX($D$17:$D$290,MATCH($B291,$B$17:$B$290,0)),""))</f>
         <v/>
       </c>
       <c r="E291">
@@ -36841,7 +36828,7 @@
       <c r="A292" s="37" t="n"/>
       <c r="C292" s="27" t="n"/>
       <c r="D292">
-        <f>IF($B292="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B292,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B292,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B292="","",IFERROR(INDEX($D$17:$D$291,MATCH($B292,$B$17:$B$291,0)),""))</f>
         <v/>
       </c>
       <c r="E292">
@@ -36861,7 +36848,7 @@
       <c r="A293" s="37" t="n"/>
       <c r="C293" s="27" t="n"/>
       <c r="D293">
-        <f>IF($B293="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B293,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B293,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B293="","",IFERROR(INDEX($D$17:$D$292,MATCH($B293,$B$17:$B$292,0)),""))</f>
         <v/>
       </c>
       <c r="E293">
@@ -36881,7 +36868,7 @@
       <c r="A294" s="37" t="n"/>
       <c r="C294" s="27" t="n"/>
       <c r="D294">
-        <f>IF($B294="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B294,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B294,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B294="","",IFERROR(INDEX($D$17:$D$293,MATCH($B294,$B$17:$B$293,0)),""))</f>
         <v/>
       </c>
       <c r="E294">
@@ -36901,7 +36888,7 @@
       <c r="A295" s="37" t="n"/>
       <c r="C295" s="27" t="n"/>
       <c r="D295">
-        <f>IF($B295="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B295,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B295,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B295="","",IFERROR(INDEX($D$17:$D$294,MATCH($B295,$B$17:$B$294,0)),""))</f>
         <v/>
       </c>
       <c r="E295">
@@ -36921,7 +36908,7 @@
       <c r="A296" s="37" t="n"/>
       <c r="C296" s="27" t="n"/>
       <c r="D296">
-        <f>IF($B296="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B296,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B296,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B296="","",IFERROR(INDEX($D$17:$D$295,MATCH($B296,$B$17:$B$295,0)),""))</f>
         <v/>
       </c>
       <c r="E296">
@@ -36941,7 +36928,7 @@
       <c r="A297" s="37" t="n"/>
       <c r="C297" s="27" t="n"/>
       <c r="D297">
-        <f>IF($B297="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B297,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B297,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B297="","",IFERROR(INDEX($D$17:$D$296,MATCH($B297,$B$17:$B$296,0)),""))</f>
         <v/>
       </c>
       <c r="E297">
@@ -36961,7 +36948,7 @@
       <c r="A298" s="37" t="n"/>
       <c r="C298" s="27" t="n"/>
       <c r="D298">
-        <f>IF($B298="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B298,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B298,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B298="","",IFERROR(INDEX($D$17:$D$297,MATCH($B298,$B$17:$B$297,0)),""))</f>
         <v/>
       </c>
       <c r="E298">
@@ -36981,7 +36968,7 @@
       <c r="A299" s="37" t="n"/>
       <c r="C299" s="27" t="n"/>
       <c r="D299">
-        <f>IF($B299="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B299,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B299,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B299="","",IFERROR(INDEX($D$17:$D$298,MATCH($B299,$B$17:$B$298,0)),""))</f>
         <v/>
       </c>
       <c r="E299">
@@ -37001,7 +36988,7 @@
       <c r="A300" s="37" t="n"/>
       <c r="C300" s="27" t="n"/>
       <c r="D300">
-        <f>IF($B300="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B300,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B300,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B300="","",IFERROR(INDEX($D$17:$D$299,MATCH($B300,$B$17:$B$299,0)),""))</f>
         <v/>
       </c>
       <c r="E300">
@@ -37021,7 +37008,7 @@
       <c r="A301" s="37" t="n"/>
       <c r="C301" s="27" t="n"/>
       <c r="D301">
-        <f>IF($B301="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B301,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B301,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B301="","",IFERROR(INDEX($D$17:$D$300,MATCH($B301,$B$17:$B$300,0)),""))</f>
         <v/>
       </c>
       <c r="E301">
@@ -37041,7 +37028,7 @@
       <c r="A302" s="37" t="n"/>
       <c r="C302" s="27" t="n"/>
       <c r="D302">
-        <f>IF($B302="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B302,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B302,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B302="","",IFERROR(INDEX($D$17:$D$301,MATCH($B302,$B$17:$B$301,0)),""))</f>
         <v/>
       </c>
       <c r="E302">
@@ -37061,7 +37048,7 @@
       <c r="A303" s="37" t="n"/>
       <c r="C303" s="27" t="n"/>
       <c r="D303">
-        <f>IF($B303="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B303,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B303,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B303="","",IFERROR(INDEX($D$17:$D$302,MATCH($B303,$B$17:$B$302,0)),""))</f>
         <v/>
       </c>
       <c r="E303">
@@ -37081,7 +37068,7 @@
       <c r="A304" s="37" t="n"/>
       <c r="C304" s="27" t="n"/>
       <c r="D304">
-        <f>IF($B304="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B304,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B304,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B304="","",IFERROR(INDEX($D$17:$D$303,MATCH($B304,$B$17:$B$303,0)),""))</f>
         <v/>
       </c>
       <c r="E304">
@@ -37101,7 +37088,7 @@
       <c r="A305" s="37" t="n"/>
       <c r="C305" s="27" t="n"/>
       <c r="D305">
-        <f>IF($B305="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B305,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B305,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B305="","",IFERROR(INDEX($D$17:$D$304,MATCH($B305,$B$17:$B$304,0)),""))</f>
         <v/>
       </c>
       <c r="E305">
@@ -37121,7 +37108,7 @@
       <c r="A306" s="37" t="n"/>
       <c r="C306" s="27" t="n"/>
       <c r="D306">
-        <f>IF($B306="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B306,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B306,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B306="","",IFERROR(INDEX($D$17:$D$305,MATCH($B306,$B$17:$B$305,0)),""))</f>
         <v/>
       </c>
       <c r="E306">
@@ -37141,7 +37128,7 @@
       <c r="A307" s="37" t="n"/>
       <c r="C307" s="27" t="n"/>
       <c r="D307">
-        <f>IF($B307="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B307,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B307,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B307="","",IFERROR(INDEX($D$17:$D$306,MATCH($B307,$B$17:$B$306,0)),""))</f>
         <v/>
       </c>
       <c r="E307">
@@ -37161,7 +37148,7 @@
       <c r="A308" s="37" t="n"/>
       <c r="C308" s="27" t="n"/>
       <c r="D308">
-        <f>IF($B308="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B308,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B308,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B308="","",IFERROR(INDEX($D$17:$D$307,MATCH($B308,$B$17:$B$307,0)),""))</f>
         <v/>
       </c>
       <c r="E308">
@@ -37181,7 +37168,7 @@
       <c r="A309" s="37" t="n"/>
       <c r="C309" s="27" t="n"/>
       <c r="D309">
-        <f>IF($B309="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B309,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B309,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B309="","",IFERROR(INDEX($D$17:$D$308,MATCH($B309,$B$17:$B$308,0)),""))</f>
         <v/>
       </c>
       <c r="E309">
@@ -37201,7 +37188,7 @@
       <c r="A310" s="37" t="n"/>
       <c r="C310" s="27" t="n"/>
       <c r="D310">
-        <f>IF($B310="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B310,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B310,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B310="","",IFERROR(INDEX($D$17:$D$309,MATCH($B310,$B$17:$B$309,0)),""))</f>
         <v/>
       </c>
       <c r="E310">
@@ -37221,7 +37208,7 @@
       <c r="A311" s="37" t="n"/>
       <c r="C311" s="27" t="n"/>
       <c r="D311">
-        <f>IF($B311="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B311,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B311,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B311="","",IFERROR(INDEX($D$17:$D$310,MATCH($B311,$B$17:$B$310,0)),""))</f>
         <v/>
       </c>
       <c r="E311">
@@ -37241,7 +37228,7 @@
       <c r="A312" s="37" t="n"/>
       <c r="C312" s="27" t="n"/>
       <c r="D312">
-        <f>IF($B312="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B312,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B312,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B312="","",IFERROR(INDEX($D$17:$D$311,MATCH($B312,$B$17:$B$311,0)),""))</f>
         <v/>
       </c>
       <c r="E312">
@@ -37261,7 +37248,7 @@
       <c r="A313" s="37" t="n"/>
       <c r="C313" s="27" t="n"/>
       <c r="D313">
-        <f>IF($B313="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B313,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B313,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B313="","",IFERROR(INDEX($D$17:$D$312,MATCH($B313,$B$17:$B$312,0)),""))</f>
         <v/>
       </c>
       <c r="E313">
@@ -37281,7 +37268,7 @@
       <c r="A314" s="37" t="n"/>
       <c r="C314" s="27" t="n"/>
       <c r="D314">
-        <f>IF($B314="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B314,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B314,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B314="","",IFERROR(INDEX($D$17:$D$313,MATCH($B314,$B$17:$B$313,0)),""))</f>
         <v/>
       </c>
       <c r="E314">
@@ -37301,7 +37288,7 @@
       <c r="A315" s="37" t="n"/>
       <c r="C315" s="27" t="n"/>
       <c r="D315">
-        <f>IF($B315="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B315,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B315,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B315="","",IFERROR(INDEX($D$17:$D$314,MATCH($B315,$B$17:$B$314,0)),""))</f>
         <v/>
       </c>
       <c r="E315">
@@ -37321,7 +37308,7 @@
       <c r="A316" s="37" t="n"/>
       <c r="C316" s="27" t="n"/>
       <c r="D316">
-        <f>IF($B316="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B316,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B316,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B316="","",IFERROR(INDEX($D$17:$D$315,MATCH($B316,$B$17:$B$315,0)),""))</f>
         <v/>
       </c>
       <c r="E316">
@@ -37341,7 +37328,7 @@
       <c r="A317" s="37" t="n"/>
       <c r="C317" s="27" t="n"/>
       <c r="D317">
-        <f>IF($B317="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B317,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B317,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B317="","",IFERROR(INDEX($D$17:$D$316,MATCH($B317,$B$17:$B$316,0)),""))</f>
         <v/>
       </c>
       <c r="E317">
@@ -37361,7 +37348,7 @@
       <c r="A318" s="37" t="n"/>
       <c r="C318" s="27" t="n"/>
       <c r="D318">
-        <f>IF($B318="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B318,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B318,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B318="","",IFERROR(INDEX($D$17:$D$317,MATCH($B318,$B$17:$B$317,0)),""))</f>
         <v/>
       </c>
       <c r="E318">
@@ -37381,7 +37368,7 @@
       <c r="A319" s="37" t="n"/>
       <c r="C319" s="27" t="n"/>
       <c r="D319">
-        <f>IF($B319="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B319,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B319,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B319="","",IFERROR(INDEX($D$17:$D$318,MATCH($B319,$B$17:$B$318,0)),""))</f>
         <v/>
       </c>
       <c r="E319">
@@ -37401,7 +37388,7 @@
       <c r="A320" s="37" t="n"/>
       <c r="C320" s="27" t="n"/>
       <c r="D320">
-        <f>IF($B320="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B320,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B320,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B320="","",IFERROR(INDEX($D$17:$D$319,MATCH($B320,$B$17:$B$319,0)),""))</f>
         <v/>
       </c>
       <c r="E320">
@@ -37421,7 +37408,7 @@
       <c r="A321" s="37" t="n"/>
       <c r="C321" s="27" t="n"/>
       <c r="D321">
-        <f>IF($B321="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B321,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B321,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B321="","",IFERROR(INDEX($D$17:$D$320,MATCH($B321,$B$17:$B$320,0)),""))</f>
         <v/>
       </c>
       <c r="E321">
@@ -37441,7 +37428,7 @@
       <c r="A322" s="37" t="n"/>
       <c r="C322" s="27" t="n"/>
       <c r="D322">
-        <f>IF($B322="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B322,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B322,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B322="","",IFERROR(INDEX($D$17:$D$321,MATCH($B322,$B$17:$B$321,0)),""))</f>
         <v/>
       </c>
       <c r="E322">
@@ -37461,7 +37448,7 @@
       <c r="A323" s="37" t="n"/>
       <c r="C323" s="27" t="n"/>
       <c r="D323">
-        <f>IF($B323="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B323,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B323,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B323="","",IFERROR(INDEX($D$17:$D$322,MATCH($B323,$B$17:$B$322,0)),""))</f>
         <v/>
       </c>
       <c r="E323">
@@ -37481,7 +37468,7 @@
       <c r="A324" s="37" t="n"/>
       <c r="C324" s="27" t="n"/>
       <c r="D324">
-        <f>IF($B324="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B324,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B324,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B324="","",IFERROR(INDEX($D$17:$D$323,MATCH($B324,$B$17:$B$323,0)),""))</f>
         <v/>
       </c>
       <c r="E324">
@@ -37501,7 +37488,7 @@
       <c r="A325" s="37" t="n"/>
       <c r="C325" s="27" t="n"/>
       <c r="D325">
-        <f>IF($B325="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B325,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B325,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B325="","",IFERROR(INDEX($D$17:$D$324,MATCH($B325,$B$17:$B$324,0)),""))</f>
         <v/>
       </c>
       <c r="E325">
@@ -37521,7 +37508,7 @@
       <c r="A326" s="37" t="n"/>
       <c r="C326" s="27" t="n"/>
       <c r="D326">
-        <f>IF($B326="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B326,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B326,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B326="","",IFERROR(INDEX($D$17:$D$325,MATCH($B326,$B$17:$B$325,0)),""))</f>
         <v/>
       </c>
       <c r="E326">
@@ -37541,7 +37528,7 @@
       <c r="A327" s="37" t="n"/>
       <c r="C327" s="27" t="n"/>
       <c r="D327">
-        <f>IF($B327="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B327,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B327,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B327="","",IFERROR(INDEX($D$17:$D$326,MATCH($B327,$B$17:$B$326,0)),""))</f>
         <v/>
       </c>
       <c r="E327">
@@ -37561,7 +37548,7 @@
       <c r="A328" s="37" t="n"/>
       <c r="C328" s="27" t="n"/>
       <c r="D328">
-        <f>IF($B328="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B328,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B328,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B328="","",IFERROR(INDEX($D$17:$D$327,MATCH($B328,$B$17:$B$327,0)),""))</f>
         <v/>
       </c>
       <c r="E328">
@@ -37581,7 +37568,7 @@
       <c r="A329" s="37" t="n"/>
       <c r="C329" s="27" t="n"/>
       <c r="D329">
-        <f>IF($B329="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B329,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B329,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B329="","",IFERROR(INDEX($D$17:$D$328,MATCH($B329,$B$17:$B$328,0)),""))</f>
         <v/>
       </c>
       <c r="E329">
@@ -37601,7 +37588,7 @@
       <c r="A330" s="37" t="n"/>
       <c r="C330" s="27" t="n"/>
       <c r="D330">
-        <f>IF($B330="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B330,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B330,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B330="","",IFERROR(INDEX($D$17:$D$329,MATCH($B330,$B$17:$B$329,0)),""))</f>
         <v/>
       </c>
       <c r="E330">
@@ -37621,7 +37608,7 @@
       <c r="A331" s="37" t="n"/>
       <c r="C331" s="27" t="n"/>
       <c r="D331">
-        <f>IF($B331="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B331,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B331,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B331="","",IFERROR(INDEX($D$17:$D$330,MATCH($B331,$B$17:$B$330,0)),""))</f>
         <v/>
       </c>
       <c r="E331">
@@ -37641,7 +37628,7 @@
       <c r="A332" s="37" t="n"/>
       <c r="C332" s="27" t="n"/>
       <c r="D332">
-        <f>IF($B332="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B332,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B332,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B332="","",IFERROR(INDEX($D$17:$D$331,MATCH($B332,$B$17:$B$331,0)),""))</f>
         <v/>
       </c>
       <c r="E332">
@@ -37661,7 +37648,7 @@
       <c r="A333" s="37" t="n"/>
       <c r="C333" s="27" t="n"/>
       <c r="D333">
-        <f>IF($B333="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B333,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B333,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B333="","",IFERROR(INDEX($D$17:$D$332,MATCH($B333,$B$17:$B$332,0)),""))</f>
         <v/>
       </c>
       <c r="E333">
@@ -37681,7 +37668,7 @@
       <c r="A334" s="37" t="n"/>
       <c r="C334" s="27" t="n"/>
       <c r="D334">
-        <f>IF($B334="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B334,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B334,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B334="","",IFERROR(INDEX($D$17:$D$333,MATCH($B334,$B$17:$B$333,0)),""))</f>
         <v/>
       </c>
       <c r="E334">
@@ -37701,7 +37688,7 @@
       <c r="A335" s="37" t="n"/>
       <c r="C335" s="27" t="n"/>
       <c r="D335">
-        <f>IF($B335="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B335,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B335,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B335="","",IFERROR(INDEX($D$17:$D$334,MATCH($B335,$B$17:$B$334,0)),""))</f>
         <v/>
       </c>
       <c r="E335">
@@ -37721,7 +37708,7 @@
       <c r="A336" s="37" t="n"/>
       <c r="C336" s="27" t="n"/>
       <c r="D336">
-        <f>IF($B336="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B336,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B336,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B336="","",IFERROR(INDEX($D$17:$D$335,MATCH($B336,$B$17:$B$335,0)),""))</f>
         <v/>
       </c>
       <c r="E336">
@@ -37741,7 +37728,7 @@
       <c r="A337" s="37" t="n"/>
       <c r="C337" s="27" t="n"/>
       <c r="D337">
-        <f>IF($B337="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B337,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B337,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B337="","",IFERROR(INDEX($D$17:$D$336,MATCH($B337,$B$17:$B$336,0)),""))</f>
         <v/>
       </c>
       <c r="E337">
@@ -37761,7 +37748,7 @@
       <c r="A338" s="37" t="n"/>
       <c r="C338" s="27" t="n"/>
       <c r="D338">
-        <f>IF($B338="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B338,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B338,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B338="","",IFERROR(INDEX($D$17:$D$337,MATCH($B338,$B$17:$B$337,0)),""))</f>
         <v/>
       </c>
       <c r="E338">
@@ -37781,7 +37768,7 @@
       <c r="A339" s="37" t="n"/>
       <c r="C339" s="27" t="n"/>
       <c r="D339">
-        <f>IF($B339="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B339,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B339,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B339="","",IFERROR(INDEX($D$17:$D$338,MATCH($B339,$B$17:$B$338,0)),""))</f>
         <v/>
       </c>
       <c r="E339">
@@ -37801,7 +37788,7 @@
       <c r="A340" s="37" t="n"/>
       <c r="C340" s="27" t="n"/>
       <c r="D340">
-        <f>IF($B340="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B340,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B340,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B340="","",IFERROR(INDEX($D$17:$D$339,MATCH($B340,$B$17:$B$339,0)),""))</f>
         <v/>
       </c>
       <c r="E340">
@@ -37821,7 +37808,7 @@
       <c r="A341" s="37" t="n"/>
       <c r="C341" s="27" t="n"/>
       <c r="D341">
-        <f>IF($B341="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B341,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B341,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B341="","",IFERROR(INDEX($D$17:$D$340,MATCH($B341,$B$17:$B$340,0)),""))</f>
         <v/>
       </c>
       <c r="E341">
@@ -37841,7 +37828,7 @@
       <c r="A342" s="37" t="n"/>
       <c r="C342" s="27" t="n"/>
       <c r="D342">
-        <f>IF($B342="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B342,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B342,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B342="","",IFERROR(INDEX($D$17:$D$341,MATCH($B342,$B$17:$B$341,0)),""))</f>
         <v/>
       </c>
       <c r="E342">
@@ -37861,7 +37848,7 @@
       <c r="A343" s="37" t="n"/>
       <c r="C343" s="27" t="n"/>
       <c r="D343">
-        <f>IF($B343="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B343,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B343,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B343="","",IFERROR(INDEX($D$17:$D$342,MATCH($B343,$B$17:$B$342,0)),""))</f>
         <v/>
       </c>
       <c r="E343">
@@ -37881,7 +37868,7 @@
       <c r="A344" s="37" t="n"/>
       <c r="C344" s="27" t="n"/>
       <c r="D344">
-        <f>IF($B344="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B344,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B344,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B344="","",IFERROR(INDEX($D$17:$D$343,MATCH($B344,$B$17:$B$343,0)),""))</f>
         <v/>
       </c>
       <c r="E344">
@@ -37901,7 +37888,7 @@
       <c r="A345" s="37" t="n"/>
       <c r="C345" s="27" t="n"/>
       <c r="D345">
-        <f>IF($B345="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B345,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B345,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B345="","",IFERROR(INDEX($D$17:$D$344,MATCH($B345,$B$17:$B$344,0)),""))</f>
         <v/>
       </c>
       <c r="E345">
@@ -37921,7 +37908,7 @@
       <c r="A346" s="37" t="n"/>
       <c r="C346" s="27" t="n"/>
       <c r="D346">
-        <f>IF($B346="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B346,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B346,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B346="","",IFERROR(INDEX($D$17:$D$345,MATCH($B346,$B$17:$B$345,0)),""))</f>
         <v/>
       </c>
       <c r="E346">
@@ -37941,7 +37928,7 @@
       <c r="A347" s="37" t="n"/>
       <c r="C347" s="27" t="n"/>
       <c r="D347">
-        <f>IF($B347="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B347,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B347,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B347="","",IFERROR(INDEX($D$17:$D$346,MATCH($B347,$B$17:$B$346,0)),""))</f>
         <v/>
       </c>
       <c r="E347">
@@ -37961,7 +37948,7 @@
       <c r="A348" s="37" t="n"/>
       <c r="C348" s="27" t="n"/>
       <c r="D348">
-        <f>IF($B348="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B348,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B348,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B348="","",IFERROR(INDEX($D$17:$D$347,MATCH($B348,$B$17:$B$347,0)),""))</f>
         <v/>
       </c>
       <c r="E348">
@@ -37981,7 +37968,7 @@
       <c r="A349" s="37" t="n"/>
       <c r="C349" s="27" t="n"/>
       <c r="D349">
-        <f>IF($B349="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B349,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B349,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B349="","",IFERROR(INDEX($D$17:$D$348,MATCH($B349,$B$17:$B$348,0)),""))</f>
         <v/>
       </c>
       <c r="E349">
@@ -38001,7 +37988,7 @@
       <c r="A350" s="37" t="n"/>
       <c r="C350" s="27" t="n"/>
       <c r="D350">
-        <f>IF($B350="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B350,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B350,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B350="","",IFERROR(INDEX($D$17:$D$349,MATCH($B350,$B$17:$B$349,0)),""))</f>
         <v/>
       </c>
       <c r="E350">
@@ -38021,7 +38008,7 @@
       <c r="A351" s="37" t="n"/>
       <c r="C351" s="27" t="n"/>
       <c r="D351">
-        <f>IF($B351="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B351,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B351,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B351="","",IFERROR(INDEX($D$17:$D$350,MATCH($B351,$B$17:$B$350,0)),""))</f>
         <v/>
       </c>
       <c r="E351">
@@ -38041,7 +38028,7 @@
       <c r="A352" s="37" t="n"/>
       <c r="C352" s="27" t="n"/>
       <c r="D352">
-        <f>IF($B352="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B352,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B352,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B352="","",IFERROR(INDEX($D$17:$D$351,MATCH($B352,$B$17:$B$351,0)),""))</f>
         <v/>
       </c>
       <c r="E352">
@@ -38061,7 +38048,7 @@
       <c r="A353" s="37" t="n"/>
       <c r="C353" s="27" t="n"/>
       <c r="D353">
-        <f>IF($B353="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B353,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B353,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B353="","",IFERROR(INDEX($D$17:$D$352,MATCH($B353,$B$17:$B$352,0)),""))</f>
         <v/>
       </c>
       <c r="E353">
@@ -38081,7 +38068,7 @@
       <c r="A354" s="37" t="n"/>
       <c r="C354" s="27" t="n"/>
       <c r="D354">
-        <f>IF($B354="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B354,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B354,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B354="","",IFERROR(INDEX($D$17:$D$353,MATCH($B354,$B$17:$B$353,0)),""))</f>
         <v/>
       </c>
       <c r="E354">
@@ -38101,7 +38088,7 @@
       <c r="A355" s="37" t="n"/>
       <c r="C355" s="27" t="n"/>
       <c r="D355">
-        <f>IF($B355="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B355,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B355,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B355="","",IFERROR(INDEX($D$17:$D$354,MATCH($B355,$B$17:$B$354,0)),""))</f>
         <v/>
       </c>
       <c r="E355">
@@ -38121,7 +38108,7 @@
       <c r="A356" s="37" t="n"/>
       <c r="C356" s="27" t="n"/>
       <c r="D356">
-        <f>IF($B356="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B356,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B356,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B356="","",IFERROR(INDEX($D$17:$D$355,MATCH($B356,$B$17:$B$355,0)),""))</f>
         <v/>
       </c>
       <c r="E356">
@@ -38141,7 +38128,7 @@
       <c r="A357" s="37" t="n"/>
       <c r="C357" s="27" t="n"/>
       <c r="D357">
-        <f>IF($B357="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B357,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B357,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B357="","",IFERROR(INDEX($D$17:$D$356,MATCH($B357,$B$17:$B$356,0)),""))</f>
         <v/>
       </c>
       <c r="E357">
@@ -38161,7 +38148,7 @@
       <c r="A358" s="37" t="n"/>
       <c r="C358" s="27" t="n"/>
       <c r="D358">
-        <f>IF($B358="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B358,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B358,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B358="","",IFERROR(INDEX($D$17:$D$357,MATCH($B358,$B$17:$B$357,0)),""))</f>
         <v/>
       </c>
       <c r="E358">
@@ -38181,7 +38168,7 @@
       <c r="A359" s="37" t="n"/>
       <c r="C359" s="27" t="n"/>
       <c r="D359">
-        <f>IF($B359="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B359,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B359,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B359="","",IFERROR(INDEX($D$17:$D$358,MATCH($B359,$B$17:$B$358,0)),""))</f>
         <v/>
       </c>
       <c r="E359">
@@ -38201,7 +38188,7 @@
       <c r="A360" s="37" t="n"/>
       <c r="C360" s="27" t="n"/>
       <c r="D360">
-        <f>IF($B360="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B360,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B360,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B360="","",IFERROR(INDEX($D$17:$D$359,MATCH($B360,$B$17:$B$359,0)),""))</f>
         <v/>
       </c>
       <c r="E360">
@@ -38221,7 +38208,7 @@
       <c r="A361" s="37" t="n"/>
       <c r="C361" s="27" t="n"/>
       <c r="D361">
-        <f>IF($B361="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B361,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B361,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B361="","",IFERROR(INDEX($D$17:$D$360,MATCH($B361,$B$17:$B$360,0)),""))</f>
         <v/>
       </c>
       <c r="E361">
@@ -38241,7 +38228,7 @@
       <c r="A362" s="37" t="n"/>
       <c r="C362" s="27" t="n"/>
       <c r="D362">
-        <f>IF($B362="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B362,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B362,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B362="","",IFERROR(INDEX($D$17:$D$361,MATCH($B362,$B$17:$B$361,0)),""))</f>
         <v/>
       </c>
       <c r="E362">
@@ -38261,7 +38248,7 @@
       <c r="A363" s="37" t="n"/>
       <c r="C363" s="27" t="n"/>
       <c r="D363">
-        <f>IF($B363="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B363,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B363,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B363="","",IFERROR(INDEX($D$17:$D$362,MATCH($B363,$B$17:$B$362,0)),""))</f>
         <v/>
       </c>
       <c r="E363">
@@ -38281,7 +38268,7 @@
       <c r="A364" s="37" t="n"/>
       <c r="C364" s="27" t="n"/>
       <c r="D364">
-        <f>IF($B364="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B364,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B364,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B364="","",IFERROR(INDEX($D$17:$D$363,MATCH($B364,$B$17:$B$363,0)),""))</f>
         <v/>
       </c>
       <c r="E364">
@@ -38301,7 +38288,7 @@
       <c r="A365" s="37" t="n"/>
       <c r="C365" s="27" t="n"/>
       <c r="D365">
-        <f>IF($B365="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B365,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B365,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B365="","",IFERROR(INDEX($D$17:$D$364,MATCH($B365,$B$17:$B$364,0)),""))</f>
         <v/>
       </c>
       <c r="E365">
@@ -38321,7 +38308,7 @@
       <c r="A366" s="37" t="n"/>
       <c r="C366" s="27" t="n"/>
       <c r="D366">
-        <f>IF($B366="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B366,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B366,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B366="","",IFERROR(INDEX($D$17:$D$365,MATCH($B366,$B$17:$B$365,0)),""))</f>
         <v/>
       </c>
       <c r="E366">
@@ -38341,7 +38328,7 @@
       <c r="A367" s="37" t="n"/>
       <c r="C367" s="27" t="n"/>
       <c r="D367">
-        <f>IF($B367="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B367,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B367,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B367="","",IFERROR(INDEX($D$17:$D$366,MATCH($B367,$B$17:$B$366,0)),""))</f>
         <v/>
       </c>
       <c r="E367">
@@ -38361,7 +38348,7 @@
       <c r="A368" s="37" t="n"/>
       <c r="C368" s="27" t="n"/>
       <c r="D368">
-        <f>IF($B368="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B368,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B368,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B368="","",IFERROR(INDEX($D$17:$D$367,MATCH($B368,$B$17:$B$367,0)),""))</f>
         <v/>
       </c>
       <c r="E368">
@@ -38381,7 +38368,7 @@
       <c r="A369" s="37" t="n"/>
       <c r="C369" s="27" t="n"/>
       <c r="D369">
-        <f>IF($B369="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B369,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B369,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B369="","",IFERROR(INDEX($D$17:$D$368,MATCH($B369,$B$17:$B$368,0)),""))</f>
         <v/>
       </c>
       <c r="E369">
@@ -38401,7 +38388,7 @@
       <c r="A370" s="37" t="n"/>
       <c r="C370" s="27" t="n"/>
       <c r="D370">
-        <f>IF($B370="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B370,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B370,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B370="","",IFERROR(INDEX($D$17:$D$369,MATCH($B370,$B$17:$B$369,0)),""))</f>
         <v/>
       </c>
       <c r="E370">
@@ -38421,7 +38408,7 @@
       <c r="A371" s="37" t="n"/>
       <c r="C371" s="27" t="n"/>
       <c r="D371">
-        <f>IF($B371="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B371,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B371,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B371="","",IFERROR(INDEX($D$17:$D$370,MATCH($B371,$B$17:$B$370,0)),""))</f>
         <v/>
       </c>
       <c r="E371">
@@ -38441,7 +38428,7 @@
       <c r="A372" s="37" t="n"/>
       <c r="C372" s="27" t="n"/>
       <c r="D372">
-        <f>IF($B372="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B372,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B372,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B372="","",IFERROR(INDEX($D$17:$D$371,MATCH($B372,$B$17:$B$371,0)),""))</f>
         <v/>
       </c>
       <c r="E372">
@@ -38461,7 +38448,7 @@
       <c r="A373" s="37" t="n"/>
       <c r="C373" s="27" t="n"/>
       <c r="D373">
-        <f>IF($B373="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B373,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B373,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B373="","",IFERROR(INDEX($D$17:$D$372,MATCH($B373,$B$17:$B$372,0)),""))</f>
         <v/>
       </c>
       <c r="E373">
@@ -38481,7 +38468,7 @@
       <c r="A374" s="37" t="n"/>
       <c r="C374" s="27" t="n"/>
       <c r="D374">
-        <f>IF($B374="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B374,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B374,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B374="","",IFERROR(INDEX($D$17:$D$373,MATCH($B374,$B$17:$B$373,0)),""))</f>
         <v/>
       </c>
       <c r="E374">
@@ -38501,7 +38488,7 @@
       <c r="A375" s="37" t="n"/>
       <c r="C375" s="27" t="n"/>
       <c r="D375">
-        <f>IF($B375="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B375,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B375,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B375="","",IFERROR(INDEX($D$17:$D$374,MATCH($B375,$B$17:$B$374,0)),""))</f>
         <v/>
       </c>
       <c r="E375">
@@ -38521,7 +38508,7 @@
       <c r="A376" s="37" t="n"/>
       <c r="C376" s="27" t="n"/>
       <c r="D376">
-        <f>IF($B376="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B376,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B376,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B376="","",IFERROR(INDEX($D$17:$D$375,MATCH($B376,$B$17:$B$375,0)),""))</f>
         <v/>
       </c>
       <c r="E376">
@@ -38541,7 +38528,7 @@
       <c r="A377" s="37" t="n"/>
       <c r="C377" s="27" t="n"/>
       <c r="D377">
-        <f>IF($B377="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B377,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B377,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B377="","",IFERROR(INDEX($D$17:$D$376,MATCH($B377,$B$17:$B$376,0)),""))</f>
         <v/>
       </c>
       <c r="E377">
@@ -38561,7 +38548,7 @@
       <c r="A378" s="37" t="n"/>
       <c r="C378" s="27" t="n"/>
       <c r="D378">
-        <f>IF($B378="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B378,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B378,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B378="","",IFERROR(INDEX($D$17:$D$377,MATCH($B378,$B$17:$B$377,0)),""))</f>
         <v/>
       </c>
       <c r="E378">
@@ -38581,7 +38568,7 @@
       <c r="A379" s="37" t="n"/>
       <c r="C379" s="27" t="n"/>
       <c r="D379">
-        <f>IF($B379="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B379,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B379,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B379="","",IFERROR(INDEX($D$17:$D$378,MATCH($B379,$B$17:$B$378,0)),""))</f>
         <v/>
       </c>
       <c r="E379">
@@ -38601,7 +38588,7 @@
       <c r="A380" s="37" t="n"/>
       <c r="C380" s="27" t="n"/>
       <c r="D380">
-        <f>IF($B380="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B380,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B380,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B380="","",IFERROR(INDEX($D$17:$D$379,MATCH($B380,$B$17:$B$379,0)),""))</f>
         <v/>
       </c>
       <c r="E380">
@@ -38621,7 +38608,7 @@
       <c r="A381" s="37" t="n"/>
       <c r="C381" s="27" t="n"/>
       <c r="D381">
-        <f>IF($B381="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B381,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B381,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B381="","",IFERROR(INDEX($D$17:$D$380,MATCH($B381,$B$17:$B$380,0)),""))</f>
         <v/>
       </c>
       <c r="E381">
@@ -38641,7 +38628,7 @@
       <c r="A382" s="37" t="n"/>
       <c r="C382" s="27" t="n"/>
       <c r="D382">
-        <f>IF($B382="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B382,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B382,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B382="","",IFERROR(INDEX($D$17:$D$381,MATCH($B382,$B$17:$B$381,0)),""))</f>
         <v/>
       </c>
       <c r="E382">
@@ -38661,7 +38648,7 @@
       <c r="A383" s="37" t="n"/>
       <c r="C383" s="27" t="n"/>
       <c r="D383">
-        <f>IF($B383="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B383,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B383,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B383="","",IFERROR(INDEX($D$17:$D$382,MATCH($B383,$B$17:$B$382,0)),""))</f>
         <v/>
       </c>
       <c r="E383">
@@ -38681,7 +38668,7 @@
       <c r="A384" s="37" t="n"/>
       <c r="C384" s="27" t="n"/>
       <c r="D384">
-        <f>IF($B384="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B384,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B384,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B384="","",IFERROR(INDEX($D$17:$D$383,MATCH($B384,$B$17:$B$383,0)),""))</f>
         <v/>
       </c>
       <c r="E384">
@@ -38701,7 +38688,7 @@
       <c r="A385" s="37" t="n"/>
       <c r="C385" s="27" t="n"/>
       <c r="D385">
-        <f>IF($B385="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B385,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B385,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B385="","",IFERROR(INDEX($D$17:$D$384,MATCH($B385,$B$17:$B$384,0)),""))</f>
         <v/>
       </c>
       <c r="E385">
@@ -38721,7 +38708,7 @@
       <c r="A386" s="37" t="n"/>
       <c r="C386" s="27" t="n"/>
       <c r="D386">
-        <f>IF($B386="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B386,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B386,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B386="","",IFERROR(INDEX($D$17:$D$385,MATCH($B386,$B$17:$B$385,0)),""))</f>
         <v/>
       </c>
       <c r="E386">
@@ -38741,7 +38728,7 @@
       <c r="A387" s="37" t="n"/>
       <c r="C387" s="27" t="n"/>
       <c r="D387">
-        <f>IF($B387="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B387,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B387,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B387="","",IFERROR(INDEX($D$17:$D$386,MATCH($B387,$B$17:$B$386,0)),""))</f>
         <v/>
       </c>
       <c r="E387">
@@ -38761,7 +38748,7 @@
       <c r="A388" s="37" t="n"/>
       <c r="C388" s="27" t="n"/>
       <c r="D388">
-        <f>IF($B388="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B388,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B388,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B388="","",IFERROR(INDEX($D$17:$D$387,MATCH($B388,$B$17:$B$387,0)),""))</f>
         <v/>
       </c>
       <c r="E388">
@@ -38781,7 +38768,7 @@
       <c r="A389" s="37" t="n"/>
       <c r="C389" s="27" t="n"/>
       <c r="D389">
-        <f>IF($B389="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B389,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B389,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B389="","",IFERROR(INDEX($D$17:$D$388,MATCH($B389,$B$17:$B$388,0)),""))</f>
         <v/>
       </c>
       <c r="E389">
@@ -38801,7 +38788,7 @@
       <c r="A390" s="37" t="n"/>
       <c r="C390" s="27" t="n"/>
       <c r="D390">
-        <f>IF($B390="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B390,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B390,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B390="","",IFERROR(INDEX($D$17:$D$389,MATCH($B390,$B$17:$B$389,0)),""))</f>
         <v/>
       </c>
       <c r="E390">
@@ -38821,7 +38808,7 @@
       <c r="A391" s="37" t="n"/>
       <c r="C391" s="27" t="n"/>
       <c r="D391">
-        <f>IF($B391="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B391,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B391,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B391="","",IFERROR(INDEX($D$17:$D$390,MATCH($B391,$B$17:$B$390,0)),""))</f>
         <v/>
       </c>
       <c r="E391">
@@ -38841,7 +38828,7 @@
       <c r="A392" s="37" t="n"/>
       <c r="C392" s="27" t="n"/>
       <c r="D392">
-        <f>IF($B392="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B392,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B392,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B392="","",IFERROR(INDEX($D$17:$D$391,MATCH($B392,$B$17:$B$391,0)),""))</f>
         <v/>
       </c>
       <c r="E392">
@@ -38861,7 +38848,7 @@
       <c r="A393" s="37" t="n"/>
       <c r="C393" s="27" t="n"/>
       <c r="D393">
-        <f>IF($B393="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B393,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B393,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B393="","",IFERROR(INDEX($D$17:$D$392,MATCH($B393,$B$17:$B$392,0)),""))</f>
         <v/>
       </c>
       <c r="E393">
@@ -38881,7 +38868,7 @@
       <c r="A394" s="37" t="n"/>
       <c r="C394" s="27" t="n"/>
       <c r="D394">
-        <f>IF($B394="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B394,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B394,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B394="","",IFERROR(INDEX($D$17:$D$393,MATCH($B394,$B$17:$B$393,0)),""))</f>
         <v/>
       </c>
       <c r="E394">
@@ -38901,7 +38888,7 @@
       <c r="A395" s="37" t="n"/>
       <c r="C395" s="27" t="n"/>
       <c r="D395">
-        <f>IF($B395="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B395,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B395,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B395="","",IFERROR(INDEX($D$17:$D$394,MATCH($B395,$B$17:$B$394,0)),""))</f>
         <v/>
       </c>
       <c r="E395">
@@ -38921,7 +38908,7 @@
       <c r="A396" s="37" t="n"/>
       <c r="C396" s="27" t="n"/>
       <c r="D396">
-        <f>IF($B396="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B396,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B396,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B396="","",IFERROR(INDEX($D$17:$D$395,MATCH($B396,$B$17:$B$395,0)),""))</f>
         <v/>
       </c>
       <c r="E396">
@@ -38941,7 +38928,7 @@
       <c r="A397" s="37" t="n"/>
       <c r="C397" s="27" t="n"/>
       <c r="D397">
-        <f>IF($B397="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B397,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B397,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B397="","",IFERROR(INDEX($D$17:$D$396,MATCH($B397,$B$17:$B$396,0)),""))</f>
         <v/>
       </c>
       <c r="E397">
@@ -38961,7 +38948,7 @@
       <c r="A398" s="37" t="n"/>
       <c r="C398" s="27" t="n"/>
       <c r="D398">
-        <f>IF($B398="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B398,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B398,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B398="","",IFERROR(INDEX($D$17:$D$397,MATCH($B398,$B$17:$B$397,0)),""))</f>
         <v/>
       </c>
       <c r="E398">
@@ -38981,7 +38968,7 @@
       <c r="A399" s="37" t="n"/>
       <c r="C399" s="27" t="n"/>
       <c r="D399">
-        <f>IF($B399="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B399,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B399,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B399="","",IFERROR(INDEX($D$17:$D$398,MATCH($B399,$B$17:$B$398,0)),""))</f>
         <v/>
       </c>
       <c r="E399">
@@ -39001,7 +38988,7 @@
       <c r="A400" s="37" t="n"/>
       <c r="C400" s="27" t="n"/>
       <c r="D400">
-        <f>IF($B400="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B400,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B400,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B400="","",IFERROR(INDEX($D$17:$D$399,MATCH($B400,$B$17:$B$399,0)),""))</f>
         <v/>
       </c>
       <c r="E400">
@@ -39021,7 +39008,7 @@
       <c r="A401" s="37" t="n"/>
       <c r="C401" s="27" t="n"/>
       <c r="D401">
-        <f>IF($B401="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B401,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B401,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B401="","",IFERROR(INDEX($D$17:$D$400,MATCH($B401,$B$17:$B$400,0)),""))</f>
         <v/>
       </c>
       <c r="E401">
@@ -39041,7 +39028,7 @@
       <c r="A402" s="37" t="n"/>
       <c r="C402" s="27" t="n"/>
       <c r="D402">
-        <f>IF($B402="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B402,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B402,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B402="","",IFERROR(INDEX($D$17:$D$401,MATCH($B402,$B$17:$B$401,0)),""))</f>
         <v/>
       </c>
       <c r="E402">
@@ -39061,7 +39048,7 @@
       <c r="A403" s="37" t="n"/>
       <c r="C403" s="27" t="n"/>
       <c r="D403">
-        <f>IF($B403="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B403,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B403,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B403="","",IFERROR(INDEX($D$17:$D$402,MATCH($B403,$B$17:$B$402,0)),""))</f>
         <v/>
       </c>
       <c r="E403">
@@ -39081,7 +39068,7 @@
       <c r="A404" s="37" t="n"/>
       <c r="C404" s="27" t="n"/>
       <c r="D404">
-        <f>IF($B404="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B404,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B404,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B404="","",IFERROR(INDEX($D$17:$D$403,MATCH($B404,$B$17:$B$403,0)),""))</f>
         <v/>
       </c>
       <c r="E404">
@@ -39101,7 +39088,7 @@
       <c r="A405" s="37" t="n"/>
       <c r="C405" s="27" t="n"/>
       <c r="D405">
-        <f>IF($B405="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B405,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B405,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B405="","",IFERROR(INDEX($D$17:$D$404,MATCH($B405,$B$17:$B$404,0)),""))</f>
         <v/>
       </c>
       <c r="E405">
@@ -39121,7 +39108,7 @@
       <c r="A406" s="37" t="n"/>
       <c r="C406" s="27" t="n"/>
       <c r="D406">
-        <f>IF($B406="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B406,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B406,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B406="","",IFERROR(INDEX($D$17:$D$405,MATCH($B406,$B$17:$B$405,0)),""))</f>
         <v/>
       </c>
       <c r="E406">
@@ -39141,7 +39128,7 @@
       <c r="A407" s="37" t="n"/>
       <c r="C407" s="27" t="n"/>
       <c r="D407">
-        <f>IF($B407="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B407,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B407,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B407="","",IFERROR(INDEX($D$17:$D$406,MATCH($B407,$B$17:$B$406,0)),""))</f>
         <v/>
       </c>
       <c r="E407">
@@ -39161,7 +39148,7 @@
       <c r="A408" s="37" t="n"/>
       <c r="C408" s="27" t="n"/>
       <c r="D408">
-        <f>IF($B408="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B408,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B408,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B408="","",IFERROR(INDEX($D$17:$D$407,MATCH($B408,$B$17:$B$407,0)),""))</f>
         <v/>
       </c>
       <c r="E408">
@@ -39181,7 +39168,7 @@
       <c r="A409" s="37" t="n"/>
       <c r="C409" s="27" t="n"/>
       <c r="D409">
-        <f>IF($B409="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B409,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B409,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B409="","",IFERROR(INDEX($D$17:$D$408,MATCH($B409,$B$17:$B$408,0)),""))</f>
         <v/>
       </c>
       <c r="E409">
@@ -39201,7 +39188,7 @@
       <c r="A410" s="37" t="n"/>
       <c r="C410" s="27" t="n"/>
       <c r="D410">
-        <f>IF($B410="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B410,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B410,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B410="","",IFERROR(INDEX($D$17:$D$409,MATCH($B410,$B$17:$B$409,0)),""))</f>
         <v/>
       </c>
       <c r="E410">
@@ -39221,7 +39208,7 @@
       <c r="A411" s="37" t="n"/>
       <c r="C411" s="27" t="n"/>
       <c r="D411">
-        <f>IF($B411="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B411,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B411,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B411="","",IFERROR(INDEX($D$17:$D$410,MATCH($B411,$B$17:$B$410,0)),""))</f>
         <v/>
       </c>
       <c r="E411">
@@ -39241,7 +39228,7 @@
       <c r="A412" s="37" t="n"/>
       <c r="C412" s="27" t="n"/>
       <c r="D412">
-        <f>IF($B412="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B412,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B412,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B412="","",IFERROR(INDEX($D$17:$D$411,MATCH($B412,$B$17:$B$411,0)),""))</f>
         <v/>
       </c>
       <c r="E412">
@@ -39261,7 +39248,7 @@
       <c r="A413" s="37" t="n"/>
       <c r="C413" s="27" t="n"/>
       <c r="D413">
-        <f>IF($B413="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B413,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B413,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B413="","",IFERROR(INDEX($D$17:$D$412,MATCH($B413,$B$17:$B$412,0)),""))</f>
         <v/>
       </c>
       <c r="E413">
@@ -39281,7 +39268,7 @@
       <c r="A414" s="37" t="n"/>
       <c r="C414" s="27" t="n"/>
       <c r="D414">
-        <f>IF($B414="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B414,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B414,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B414="","",IFERROR(INDEX($D$17:$D$413,MATCH($B414,$B$17:$B$413,0)),""))</f>
         <v/>
       </c>
       <c r="E414">
@@ -39301,7 +39288,7 @@
       <c r="A415" s="37" t="n"/>
       <c r="C415" s="27" t="n"/>
       <c r="D415">
-        <f>IF($B415="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B415,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B415,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B415="","",IFERROR(INDEX($D$17:$D$414,MATCH($B415,$B$17:$B$414,0)),""))</f>
         <v/>
       </c>
       <c r="E415">
@@ -39321,7 +39308,7 @@
       <c r="A416" s="37" t="n"/>
       <c r="C416" s="27" t="n"/>
       <c r="D416">
-        <f>IF($B416="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B416,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B416,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B416="","",IFERROR(INDEX($D$17:$D$415,MATCH($B416,$B$17:$B$415,0)),""))</f>
         <v/>
       </c>
       <c r="E416">
@@ -39341,7 +39328,7 @@
       <c r="A417" s="37" t="n"/>
       <c r="C417" s="27" t="n"/>
       <c r="D417">
-        <f>IF($B417="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B417,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B417,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B417="","",IFERROR(INDEX($D$17:$D$416,MATCH($B417,$B$17:$B$416,0)),""))</f>
         <v/>
       </c>
       <c r="E417">
@@ -39361,7 +39348,7 @@
       <c r="A418" s="37" t="n"/>
       <c r="C418" s="27" t="n"/>
       <c r="D418">
-        <f>IF($B418="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B418,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B418,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B418="","",IFERROR(INDEX($D$17:$D$417,MATCH($B418,$B$17:$B$417,0)),""))</f>
         <v/>
       </c>
       <c r="E418">
@@ -39381,7 +39368,7 @@
       <c r="A419" s="37" t="n"/>
       <c r="C419" s="27" t="n"/>
       <c r="D419">
-        <f>IF($B419="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B419,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B419,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B419="","",IFERROR(INDEX($D$17:$D$418,MATCH($B419,$B$17:$B$418,0)),""))</f>
         <v/>
       </c>
       <c r="E419">
@@ -39401,7 +39388,7 @@
       <c r="A420" s="37" t="n"/>
       <c r="C420" s="27" t="n"/>
       <c r="D420">
-        <f>IF($B420="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B420,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B420,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B420="","",IFERROR(INDEX($D$17:$D$419,MATCH($B420,$B$17:$B$419,0)),""))</f>
         <v/>
       </c>
       <c r="E420">
@@ -39421,7 +39408,7 @@
       <c r="A421" s="37" t="n"/>
       <c r="C421" s="27" t="n"/>
       <c r="D421">
-        <f>IF($B421="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B421,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B421,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B421="","",IFERROR(INDEX($D$17:$D$420,MATCH($B421,$B$17:$B$420,0)),""))</f>
         <v/>
       </c>
       <c r="E421">
@@ -39441,7 +39428,7 @@
       <c r="A422" s="37" t="n"/>
       <c r="C422" s="27" t="n"/>
       <c r="D422">
-        <f>IF($B422="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B422,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B422,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B422="","",IFERROR(INDEX($D$17:$D$421,MATCH($B422,$B$17:$B$421,0)),""))</f>
         <v/>
       </c>
       <c r="E422">
@@ -39461,7 +39448,7 @@
       <c r="A423" s="37" t="n"/>
       <c r="C423" s="27" t="n"/>
       <c r="D423">
-        <f>IF($B423="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B423,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B423,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B423="","",IFERROR(INDEX($D$17:$D$422,MATCH($B423,$B$17:$B$422,0)),""))</f>
         <v/>
       </c>
       <c r="E423">
@@ -39481,7 +39468,7 @@
       <c r="A424" s="37" t="n"/>
       <c r="C424" s="27" t="n"/>
       <c r="D424">
-        <f>IF($B424="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B424,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B424,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B424="","",IFERROR(INDEX($D$17:$D$423,MATCH($B424,$B$17:$B$423,0)),""))</f>
         <v/>
       </c>
       <c r="E424">
@@ -39501,7 +39488,7 @@
       <c r="A425" s="37" t="n"/>
       <c r="C425" s="27" t="n"/>
       <c r="D425">
-        <f>IF($B425="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B425,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B425,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B425="","",IFERROR(INDEX($D$17:$D$424,MATCH($B425,$B$17:$B$424,0)),""))</f>
         <v/>
       </c>
       <c r="E425">
@@ -39521,7 +39508,7 @@
       <c r="A426" s="37" t="n"/>
       <c r="C426" s="27" t="n"/>
       <c r="D426">
-        <f>IF($B426="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B426,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B426,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B426="","",IFERROR(INDEX($D$17:$D$425,MATCH($B426,$B$17:$B$425,0)),""))</f>
         <v/>
       </c>
       <c r="E426">
@@ -39541,7 +39528,7 @@
       <c r="A427" s="37" t="n"/>
       <c r="C427" s="27" t="n"/>
       <c r="D427">
-        <f>IF($B427="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B427,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B427,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B427="","",IFERROR(INDEX($D$17:$D$426,MATCH($B427,$B$17:$B$426,0)),""))</f>
         <v/>
       </c>
       <c r="E427">
@@ -39561,7 +39548,7 @@
       <c r="A428" s="37" t="n"/>
       <c r="C428" s="27" t="n"/>
       <c r="D428">
-        <f>IF($B428="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B428,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B428,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B428="","",IFERROR(INDEX($D$17:$D$427,MATCH($B428,$B$17:$B$427,0)),""))</f>
         <v/>
       </c>
       <c r="E428">
@@ -39581,7 +39568,7 @@
       <c r="A429" s="37" t="n"/>
       <c r="C429" s="27" t="n"/>
       <c r="D429">
-        <f>IF($B429="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B429,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B429,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B429="","",IFERROR(INDEX($D$17:$D$428,MATCH($B429,$B$17:$B$428,0)),""))</f>
         <v/>
       </c>
       <c r="E429">
@@ -39601,7 +39588,7 @@
       <c r="A430" s="37" t="n"/>
       <c r="C430" s="27" t="n"/>
       <c r="D430">
-        <f>IF($B430="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B430,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B430,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B430="","",IFERROR(INDEX($D$17:$D$429,MATCH($B430,$B$17:$B$429,0)),""))</f>
         <v/>
       </c>
       <c r="E430">
@@ -39621,7 +39608,7 @@
       <c r="A431" s="37" t="n"/>
       <c r="C431" s="27" t="n"/>
       <c r="D431">
-        <f>IF($B431="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B431,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B431,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B431="","",IFERROR(INDEX($D$17:$D$430,MATCH($B431,$B$17:$B$430,0)),""))</f>
         <v/>
       </c>
       <c r="E431">
@@ -39641,7 +39628,7 @@
       <c r="A432" s="37" t="n"/>
       <c r="C432" s="27" t="n"/>
       <c r="D432">
-        <f>IF($B432="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B432,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B432,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B432="","",IFERROR(INDEX($D$17:$D$431,MATCH($B432,$B$17:$B$431,0)),""))</f>
         <v/>
       </c>
       <c r="E432">
@@ -39661,7 +39648,7 @@
       <c r="A433" s="37" t="n"/>
       <c r="C433" s="27" t="n"/>
       <c r="D433">
-        <f>IF($B433="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B433,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B433,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B433="","",IFERROR(INDEX($D$17:$D$432,MATCH($B433,$B$17:$B$432,0)),""))</f>
         <v/>
       </c>
       <c r="E433">
@@ -39681,7 +39668,7 @@
       <c r="A434" s="37" t="n"/>
       <c r="C434" s="27" t="n"/>
       <c r="D434">
-        <f>IF($B434="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B434,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B434,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B434="","",IFERROR(INDEX($D$17:$D$433,MATCH($B434,$B$17:$B$433,0)),""))</f>
         <v/>
       </c>
       <c r="E434">
@@ -39701,7 +39688,7 @@
       <c r="A435" s="37" t="n"/>
       <c r="C435" s="27" t="n"/>
       <c r="D435">
-        <f>IF($B435="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B435,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B435,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B435="","",IFERROR(INDEX($D$17:$D$434,MATCH($B435,$B$17:$B$434,0)),""))</f>
         <v/>
       </c>
       <c r="E435">
@@ -39721,7 +39708,7 @@
       <c r="A436" s="37" t="n"/>
       <c r="C436" s="27" t="n"/>
       <c r="D436">
-        <f>IF($B436="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B436,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B436,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B436="","",IFERROR(INDEX($D$17:$D$435,MATCH($B436,$B$17:$B$435,0)),""))</f>
         <v/>
       </c>
       <c r="E436">
@@ -39741,7 +39728,7 @@
       <c r="A437" s="37" t="n"/>
       <c r="C437" s="27" t="n"/>
       <c r="D437">
-        <f>IF($B437="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B437,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B437,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B437="","",IFERROR(INDEX($D$17:$D$436,MATCH($B437,$B$17:$B$436,0)),""))</f>
         <v/>
       </c>
       <c r="E437">
@@ -39761,7 +39748,7 @@
       <c r="A438" s="37" t="n"/>
       <c r="C438" s="27" t="n"/>
       <c r="D438">
-        <f>IF($B438="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B438,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B438,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B438="","",IFERROR(INDEX($D$17:$D$437,MATCH($B438,$B$17:$B$437,0)),""))</f>
         <v/>
       </c>
       <c r="E438">
@@ -39781,7 +39768,7 @@
       <c r="A439" s="37" t="n"/>
       <c r="C439" s="27" t="n"/>
       <c r="D439">
-        <f>IF($B439="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B439,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B439,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B439="","",IFERROR(INDEX($D$17:$D$438,MATCH($B439,$B$17:$B$438,0)),""))</f>
         <v/>
       </c>
       <c r="E439">
@@ -39801,7 +39788,7 @@
       <c r="A440" s="37" t="n"/>
       <c r="C440" s="27" t="n"/>
       <c r="D440">
-        <f>IF($B440="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B440,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B440,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B440="","",IFERROR(INDEX($D$17:$D$439,MATCH($B440,$B$17:$B$439,0)),""))</f>
         <v/>
       </c>
       <c r="E440">
@@ -39821,7 +39808,7 @@
       <c r="A441" s="37" t="n"/>
       <c r="C441" s="27" t="n"/>
       <c r="D441">
-        <f>IF($B441="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B441,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B441,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B441="","",IFERROR(INDEX($D$17:$D$440,MATCH($B441,$B$17:$B$440,0)),""))</f>
         <v/>
       </c>
       <c r="E441">
@@ -39841,7 +39828,7 @@
       <c r="A442" s="37" t="n"/>
       <c r="C442" s="27" t="n"/>
       <c r="D442">
-        <f>IF($B442="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B442,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B442,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B442="","",IFERROR(INDEX($D$17:$D$441,MATCH($B442,$B$17:$B$441,0)),""))</f>
         <v/>
       </c>
       <c r="E442">
@@ -39861,7 +39848,7 @@
       <c r="A443" s="37" t="n"/>
       <c r="C443" s="27" t="n"/>
       <c r="D443">
-        <f>IF($B443="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B443,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B443,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B443="","",IFERROR(INDEX($D$17:$D$442,MATCH($B443,$B$17:$B$442,0)),""))</f>
         <v/>
       </c>
       <c r="E443">
@@ -39881,7 +39868,7 @@
       <c r="A444" s="37" t="n"/>
       <c r="C444" s="27" t="n"/>
       <c r="D444">
-        <f>IF($B444="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B444,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B444,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B444="","",IFERROR(INDEX($D$17:$D$443,MATCH($B444,$B$17:$B$443,0)),""))</f>
         <v/>
       </c>
       <c r="E444">
@@ -39901,7 +39888,7 @@
       <c r="A445" s="37" t="n"/>
       <c r="C445" s="27" t="n"/>
       <c r="D445">
-        <f>IF($B445="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B445,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B445,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B445="","",IFERROR(INDEX($D$17:$D$444,MATCH($B445,$B$17:$B$444,0)),""))</f>
         <v/>
       </c>
       <c r="E445">
@@ -39921,7 +39908,7 @@
       <c r="A446" s="37" t="n"/>
       <c r="C446" s="27" t="n"/>
       <c r="D446">
-        <f>IF($B446="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B446,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B446,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B446="","",IFERROR(INDEX($D$17:$D$445,MATCH($B446,$B$17:$B$445,0)),""))</f>
         <v/>
       </c>
       <c r="E446">
@@ -39941,7 +39928,7 @@
       <c r="A447" s="37" t="n"/>
       <c r="C447" s="27" t="n"/>
       <c r="D447">
-        <f>IF($B447="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B447,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B447,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B447="","",IFERROR(INDEX($D$17:$D$446,MATCH($B447,$B$17:$B$446,0)),""))</f>
         <v/>
       </c>
       <c r="E447">
@@ -39961,7 +39948,7 @@
       <c r="A448" s="37" t="n"/>
       <c r="C448" s="27" t="n"/>
       <c r="D448">
-        <f>IF($B448="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B448,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B448,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B448="","",IFERROR(INDEX($D$17:$D$447,MATCH($B448,$B$17:$B$447,0)),""))</f>
         <v/>
       </c>
       <c r="E448">
@@ -39981,7 +39968,7 @@
       <c r="A449" s="37" t="n"/>
       <c r="C449" s="27" t="n"/>
       <c r="D449">
-        <f>IF($B449="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B449,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B449,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B449="","",IFERROR(INDEX($D$17:$D$448,MATCH($B449,$B$17:$B$448,0)),""))</f>
         <v/>
       </c>
       <c r="E449">
@@ -40001,7 +39988,7 @@
       <c r="A450" s="37" t="n"/>
       <c r="C450" s="27" t="n"/>
       <c r="D450">
-        <f>IF($B450="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B450,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B450,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B450="","",IFERROR(INDEX($D$17:$D$449,MATCH($B450,$B$17:$B$449,0)),""))</f>
         <v/>
       </c>
       <c r="E450">
@@ -40021,7 +40008,7 @@
       <c r="A451" s="37" t="n"/>
       <c r="C451" s="27" t="n"/>
       <c r="D451">
-        <f>IF($B451="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B451,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B451,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B451="","",IFERROR(INDEX($D$17:$D$450,MATCH($B451,$B$17:$B$450,0)),""))</f>
         <v/>
       </c>
       <c r="E451">
@@ -40041,7 +40028,7 @@
       <c r="A452" s="37" t="n"/>
       <c r="C452" s="27" t="n"/>
       <c r="D452">
-        <f>IF($B452="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B452,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B452,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B452="","",IFERROR(INDEX($D$17:$D$451,MATCH($B452,$B$17:$B$451,0)),""))</f>
         <v/>
       </c>
       <c r="E452">
@@ -40061,7 +40048,7 @@
       <c r="A453" s="37" t="n"/>
       <c r="C453" s="27" t="n"/>
       <c r="D453">
-        <f>IF($B453="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B453,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B453,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B453="","",IFERROR(INDEX($D$17:$D$452,MATCH($B453,$B$17:$B$452,0)),""))</f>
         <v/>
       </c>
       <c r="E453">
@@ -40081,7 +40068,7 @@
       <c r="A454" s="37" t="n"/>
       <c r="C454" s="27" t="n"/>
       <c r="D454">
-        <f>IF($B454="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B454,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B454,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B454="","",IFERROR(INDEX($D$17:$D$453,MATCH($B454,$B$17:$B$453,0)),""))</f>
         <v/>
       </c>
       <c r="E454">
@@ -40101,7 +40088,7 @@
       <c r="A455" s="37" t="n"/>
       <c r="C455" s="27" t="n"/>
       <c r="D455">
-        <f>IF($B455="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B455,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B455,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B455="","",IFERROR(INDEX($D$17:$D$454,MATCH($B455,$B$17:$B$454,0)),""))</f>
         <v/>
       </c>
       <c r="E455">
@@ -40121,7 +40108,7 @@
       <c r="A456" s="37" t="n"/>
       <c r="C456" s="27" t="n"/>
       <c r="D456">
-        <f>IF($B456="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B456,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B456,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B456="","",IFERROR(INDEX($D$17:$D$455,MATCH($B456,$B$17:$B$455,0)),""))</f>
         <v/>
       </c>
       <c r="E456">
@@ -40141,7 +40128,7 @@
       <c r="A457" s="37" t="n"/>
       <c r="C457" s="27" t="n"/>
       <c r="D457">
-        <f>IF($B457="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B457,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B457,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B457="","",IFERROR(INDEX($D$17:$D$456,MATCH($B457,$B$17:$B$456,0)),""))</f>
         <v/>
       </c>
       <c r="E457">
@@ -40161,7 +40148,7 @@
       <c r="A458" s="37" t="n"/>
       <c r="C458" s="27" t="n"/>
       <c r="D458">
-        <f>IF($B458="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B458,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B458,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B458="","",IFERROR(INDEX($D$17:$D$457,MATCH($B458,$B$17:$B$457,0)),""))</f>
         <v/>
       </c>
       <c r="E458">
@@ -40181,7 +40168,7 @@
       <c r="A459" s="37" t="n"/>
       <c r="C459" s="27" t="n"/>
       <c r="D459">
-        <f>IF($B459="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B459,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B459,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B459="","",IFERROR(INDEX($D$17:$D$458,MATCH($B459,$B$17:$B$458,0)),""))</f>
         <v/>
       </c>
       <c r="E459">
@@ -40201,7 +40188,7 @@
       <c r="A460" s="37" t="n"/>
       <c r="C460" s="27" t="n"/>
       <c r="D460">
-        <f>IF($B460="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B460,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B460,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B460="","",IFERROR(INDEX($D$17:$D$459,MATCH($B460,$B$17:$B$459,0)),""))</f>
         <v/>
       </c>
       <c r="E460">
@@ -40221,7 +40208,7 @@
       <c r="A461" s="37" t="n"/>
       <c r="C461" s="27" t="n"/>
       <c r="D461">
-        <f>IF($B461="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B461,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B461,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B461="","",IFERROR(INDEX($D$17:$D$460,MATCH($B461,$B$17:$B$460,0)),""))</f>
         <v/>
       </c>
       <c r="E461">
@@ -40241,7 +40228,7 @@
       <c r="A462" s="37" t="n"/>
       <c r="C462" s="27" t="n"/>
       <c r="D462">
-        <f>IF($B462="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B462,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B462,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B462="","",IFERROR(INDEX($D$17:$D$461,MATCH($B462,$B$17:$B$461,0)),""))</f>
         <v/>
       </c>
       <c r="E462">
@@ -40261,7 +40248,7 @@
       <c r="A463" s="37" t="n"/>
       <c r="C463" s="27" t="n"/>
       <c r="D463">
-        <f>IF($B463="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B463,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B463,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B463="","",IFERROR(INDEX($D$17:$D$462,MATCH($B463,$B$17:$B$462,0)),""))</f>
         <v/>
       </c>
       <c r="E463">
@@ -40281,7 +40268,7 @@
       <c r="A464" s="37" t="n"/>
       <c r="C464" s="27" t="n"/>
       <c r="D464">
-        <f>IF($B464="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B464,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B464,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B464="","",IFERROR(INDEX($D$17:$D$463,MATCH($B464,$B$17:$B$463,0)),""))</f>
         <v/>
       </c>
       <c r="E464">
@@ -40301,7 +40288,7 @@
       <c r="A465" s="37" t="n"/>
       <c r="C465" s="27" t="n"/>
       <c r="D465">
-        <f>IF($B465="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B465,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B465,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B465="","",IFERROR(INDEX($D$17:$D$464,MATCH($B465,$B$17:$B$464,0)),""))</f>
         <v/>
       </c>
       <c r="E465">
@@ -40321,7 +40308,7 @@
       <c r="A466" s="37" t="n"/>
       <c r="C466" s="27" t="n"/>
       <c r="D466">
-        <f>IF($B466="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B466,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B466,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B466="","",IFERROR(INDEX($D$17:$D$465,MATCH($B466,$B$17:$B$465,0)),""))</f>
         <v/>
       </c>
       <c r="E466">
@@ -40341,7 +40328,7 @@
       <c r="A467" s="37" t="n"/>
       <c r="C467" s="27" t="n"/>
       <c r="D467">
-        <f>IF($B467="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B467,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B467,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B467="","",IFERROR(INDEX($D$17:$D$466,MATCH($B467,$B$17:$B$466,0)),""))</f>
         <v/>
       </c>
       <c r="E467">
@@ -40361,7 +40348,7 @@
       <c r="A468" s="37" t="n"/>
       <c r="C468" s="27" t="n"/>
       <c r="D468">
-        <f>IF($B468="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B468,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B468,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B468="","",IFERROR(INDEX($D$17:$D$467,MATCH($B468,$B$17:$B$467,0)),""))</f>
         <v/>
       </c>
       <c r="E468">
@@ -40381,7 +40368,7 @@
       <c r="A469" s="37" t="n"/>
       <c r="C469" s="27" t="n"/>
       <c r="D469">
-        <f>IF($B469="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B469,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B469,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B469="","",IFERROR(INDEX($D$17:$D$468,MATCH($B469,$B$17:$B$468,0)),""))</f>
         <v/>
       </c>
       <c r="E469">
@@ -40401,7 +40388,7 @@
       <c r="A470" s="37" t="n"/>
       <c r="C470" s="27" t="n"/>
       <c r="D470">
-        <f>IF($B470="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B470,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B470,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B470="","",IFERROR(INDEX($D$17:$D$469,MATCH($B470,$B$17:$B$469,0)),""))</f>
         <v/>
       </c>
       <c r="E470">
@@ -40421,7 +40408,7 @@
       <c r="A471" s="37" t="n"/>
       <c r="C471" s="27" t="n"/>
       <c r="D471">
-        <f>IF($B471="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B471,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B471,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B471="","",IFERROR(INDEX($D$17:$D$470,MATCH($B471,$B$17:$B$470,0)),""))</f>
         <v/>
       </c>
       <c r="E471">
@@ -40441,7 +40428,7 @@
       <c r="A472" s="37" t="n"/>
       <c r="C472" s="27" t="n"/>
       <c r="D472">
-        <f>IF($B472="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B472,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B472,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B472="","",IFERROR(INDEX($D$17:$D$471,MATCH($B472,$B$17:$B$471,0)),""))</f>
         <v/>
       </c>
       <c r="E472">
@@ -40461,7 +40448,7 @@
       <c r="A473" s="37" t="n"/>
       <c r="C473" s="27" t="n"/>
       <c r="D473">
-        <f>IF($B473="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B473,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B473,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B473="","",IFERROR(INDEX($D$17:$D$472,MATCH($B473,$B$17:$B$472,0)),""))</f>
         <v/>
       </c>
       <c r="E473">
@@ -40481,7 +40468,7 @@
       <c r="A474" s="37" t="n"/>
       <c r="C474" s="27" t="n"/>
       <c r="D474">
-        <f>IF($B474="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B474,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B474,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B474="","",IFERROR(INDEX($D$17:$D$473,MATCH($B474,$B$17:$B$473,0)),""))</f>
         <v/>
       </c>
       <c r="E474">
@@ -40501,7 +40488,7 @@
       <c r="A475" s="37" t="n"/>
       <c r="C475" s="27" t="n"/>
       <c r="D475">
-        <f>IF($B475="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B475,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B475,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B475="","",IFERROR(INDEX($D$17:$D$474,MATCH($B475,$B$17:$B$474,0)),""))</f>
         <v/>
       </c>
       <c r="E475">
@@ -40521,7 +40508,7 @@
       <c r="A476" s="37" t="n"/>
       <c r="C476" s="27" t="n"/>
       <c r="D476">
-        <f>IF($B476="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B476,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B476,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B476="","",IFERROR(INDEX($D$17:$D$475,MATCH($B476,$B$17:$B$475,0)),""))</f>
         <v/>
       </c>
       <c r="E476">
@@ -40541,7 +40528,7 @@
       <c r="A477" s="37" t="n"/>
       <c r="C477" s="27" t="n"/>
       <c r="D477">
-        <f>IF($B477="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B477,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B477,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B477="","",IFERROR(INDEX($D$17:$D$476,MATCH($B477,$B$17:$B$476,0)),""))</f>
         <v/>
       </c>
       <c r="E477">
@@ -40561,7 +40548,7 @@
       <c r="A478" s="37" t="n"/>
       <c r="C478" s="27" t="n"/>
       <c r="D478">
-        <f>IF($B478="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B478,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B478,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B478="","",IFERROR(INDEX($D$17:$D$477,MATCH($B478,$B$17:$B$477,0)),""))</f>
         <v/>
       </c>
       <c r="E478">
@@ -40581,7 +40568,7 @@
       <c r="A479" s="37" t="n"/>
       <c r="C479" s="27" t="n"/>
       <c r="D479">
-        <f>IF($B479="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B479,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B479,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B479="","",IFERROR(INDEX($D$17:$D$478,MATCH($B479,$B$17:$B$478,0)),""))</f>
         <v/>
       </c>
       <c r="E479">
@@ -40601,7 +40588,7 @@
       <c r="A480" s="37" t="n"/>
       <c r="C480" s="27" t="n"/>
       <c r="D480">
-        <f>IF($B480="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B480,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B480,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B480="","",IFERROR(INDEX($D$17:$D$479,MATCH($B480,$B$17:$B$479,0)),""))</f>
         <v/>
       </c>
       <c r="E480">
@@ -40621,7 +40608,7 @@
       <c r="A481" s="37" t="n"/>
       <c r="C481" s="27" t="n"/>
       <c r="D481">
-        <f>IF($B481="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B481,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B481,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B481="","",IFERROR(INDEX($D$17:$D$480,MATCH($B481,$B$17:$B$480,0)),""))</f>
         <v/>
       </c>
       <c r="E481">
@@ -40641,7 +40628,7 @@
       <c r="A482" s="37" t="n"/>
       <c r="C482" s="27" t="n"/>
       <c r="D482">
-        <f>IF($B482="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B482,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B482,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B482="","",IFERROR(INDEX($D$17:$D$481,MATCH($B482,$B$17:$B$481,0)),""))</f>
         <v/>
       </c>
       <c r="E482">
@@ -40661,7 +40648,7 @@
       <c r="A483" s="37" t="n"/>
       <c r="C483" s="27" t="n"/>
       <c r="D483">
-        <f>IF($B483="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B483,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B483,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B483="","",IFERROR(INDEX($D$17:$D$482,MATCH($B483,$B$17:$B$482,0)),""))</f>
         <v/>
       </c>
       <c r="E483">
@@ -40681,7 +40668,7 @@
       <c r="A484" s="37" t="n"/>
       <c r="C484" s="27" t="n"/>
       <c r="D484">
-        <f>IF($B484="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B484,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B484,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B484="","",IFERROR(INDEX($D$17:$D$483,MATCH($B484,$B$17:$B$483,0)),""))</f>
         <v/>
       </c>
       <c r="E484">
@@ -40701,7 +40688,7 @@
       <c r="A485" s="37" t="n"/>
       <c r="C485" s="27" t="n"/>
       <c r="D485">
-        <f>IF($B485="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B485,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B485,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B485="","",IFERROR(INDEX($D$17:$D$484,MATCH($B485,$B$17:$B$484,0)),""))</f>
         <v/>
       </c>
       <c r="E485">
@@ -40721,7 +40708,7 @@
       <c r="A486" s="37" t="n"/>
       <c r="C486" s="27" t="n"/>
       <c r="D486">
-        <f>IF($B486="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B486,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B486,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B486="","",IFERROR(INDEX($D$17:$D$485,MATCH($B486,$B$17:$B$485,0)),""))</f>
         <v/>
       </c>
       <c r="E486">
@@ -40741,7 +40728,7 @@
       <c r="A487" s="37" t="n"/>
       <c r="C487" s="27" t="n"/>
       <c r="D487">
-        <f>IF($B487="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B487,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B487,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B487="","",IFERROR(INDEX($D$17:$D$486,MATCH($B487,$B$17:$B$486,0)),""))</f>
         <v/>
       </c>
       <c r="E487">
@@ -40761,7 +40748,7 @@
       <c r="A488" s="37" t="n"/>
       <c r="C488" s="27" t="n"/>
       <c r="D488">
-        <f>IF($B488="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B488,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B488,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B488="","",IFERROR(INDEX($D$17:$D$487,MATCH($B488,$B$17:$B$487,0)),""))</f>
         <v/>
       </c>
       <c r="E488">
@@ -40781,7 +40768,7 @@
       <c r="A489" s="37" t="n"/>
       <c r="C489" s="27" t="n"/>
       <c r="D489">
-        <f>IF($B489="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B489,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B489,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B489="","",IFERROR(INDEX($D$17:$D$488,MATCH($B489,$B$17:$B$488,0)),""))</f>
         <v/>
       </c>
       <c r="E489">
@@ -40801,7 +40788,7 @@
       <c r="A490" s="37" t="n"/>
       <c r="C490" s="27" t="n"/>
       <c r="D490">
-        <f>IF($B490="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B490,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B490,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B490="","",IFERROR(INDEX($D$17:$D$489,MATCH($B490,$B$17:$B$489,0)),""))</f>
         <v/>
       </c>
       <c r="E490">
@@ -40821,7 +40808,7 @@
       <c r="A491" s="37" t="n"/>
       <c r="C491" s="27" t="n"/>
       <c r="D491">
-        <f>IF($B491="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B491,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B491,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B491="","",IFERROR(INDEX($D$17:$D$490,MATCH($B491,$B$17:$B$490,0)),""))</f>
         <v/>
       </c>
       <c r="E491">
@@ -40841,7 +40828,7 @@
       <c r="A492" s="37" t="n"/>
       <c r="C492" s="27" t="n"/>
       <c r="D492">
-        <f>IF($B492="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B492,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B492,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B492="","",IFERROR(INDEX($D$17:$D$491,MATCH($B492,$B$17:$B$491,0)),""))</f>
         <v/>
       </c>
       <c r="E492">
@@ -40861,7 +40848,7 @@
       <c r="A493" s="37" t="n"/>
       <c r="C493" s="27" t="n"/>
       <c r="D493">
-        <f>IF($B493="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B493,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B493,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B493="","",IFERROR(INDEX($D$17:$D$492,MATCH($B493,$B$17:$B$492,0)),""))</f>
         <v/>
       </c>
       <c r="E493">
@@ -40881,7 +40868,7 @@
       <c r="A494" s="37" t="n"/>
       <c r="C494" s="27" t="n"/>
       <c r="D494">
-        <f>IF($B494="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B494,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B494,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B494="","",IFERROR(INDEX($D$17:$D$493,MATCH($B494,$B$17:$B$493,0)),""))</f>
         <v/>
       </c>
       <c r="E494">
@@ -40901,7 +40888,7 @@
       <c r="A495" s="37" t="n"/>
       <c r="C495" s="27" t="n"/>
       <c r="D495">
-        <f>IF($B495="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B495,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B495,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B495="","",IFERROR(INDEX($D$17:$D$494,MATCH($B495,$B$17:$B$494,0)),""))</f>
         <v/>
       </c>
       <c r="E495">
@@ -40921,7 +40908,7 @@
       <c r="A496" s="37" t="n"/>
       <c r="C496" s="27" t="n"/>
       <c r="D496">
-        <f>IF($B496="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B496,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B496,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B496="","",IFERROR(INDEX($D$17:$D$495,MATCH($B496,$B$17:$B$495,0)),""))</f>
         <v/>
       </c>
       <c r="E496">
@@ -40941,7 +40928,7 @@
       <c r="A497" s="37" t="n"/>
       <c r="C497" s="27" t="n"/>
       <c r="D497">
-        <f>IF($B497="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B497,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B497,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B497="","",IFERROR(INDEX($D$17:$D$496,MATCH($B497,$B$17:$B$496,0)),""))</f>
         <v/>
       </c>
       <c r="E497">
@@ -40961,7 +40948,7 @@
       <c r="A498" s="37" t="n"/>
       <c r="C498" s="27" t="n"/>
       <c r="D498">
-        <f>IF($B498="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B498,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B498,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B498="","",IFERROR(INDEX($D$17:$D$497,MATCH($B498,$B$17:$B$497,0)),""))</f>
         <v/>
       </c>
       <c r="E498">
@@ -40981,7 +40968,7 @@
       <c r="A499" s="37" t="n"/>
       <c r="C499" s="27" t="n"/>
       <c r="D499">
-        <f>IF($B499="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B499,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B499,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B499="","",IFERROR(INDEX($D$17:$D$498,MATCH($B499,$B$17:$B$498,0)),""))</f>
         <v/>
       </c>
       <c r="E499">
@@ -41001,7 +40988,7 @@
       <c r="A500" s="37" t="n"/>
       <c r="C500" s="27" t="n"/>
       <c r="D500">
-        <f>IF($B500="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B500,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B500,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B500="","",IFERROR(INDEX($D$17:$D$499,MATCH($B500,$B$17:$B$499,0)),""))</f>
         <v/>
       </c>
       <c r="E500">
@@ -41021,7 +41008,7 @@
       <c r="A501" s="37" t="n"/>
       <c r="C501" s="27" t="n"/>
       <c r="D501">
-        <f>IF($B501="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B501,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B501,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B501="","",IFERROR(INDEX($D$17:$D$500,MATCH($B501,$B$17:$B$500,0)),""))</f>
         <v/>
       </c>
       <c r="E501">
@@ -41041,7 +41028,7 @@
       <c r="A502" s="37" t="n"/>
       <c r="C502" s="27" t="n"/>
       <c r="D502">
-        <f>IF($B502="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B502,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B502,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B502="","",IFERROR(INDEX($D$17:$D$501,MATCH($B502,$B$17:$B$501,0)),""))</f>
         <v/>
       </c>
       <c r="E502">
@@ -41061,7 +41048,7 @@
       <c r="A503" s="37" t="n"/>
       <c r="C503" s="27" t="n"/>
       <c r="D503">
-        <f>IF($B503="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B503,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B503,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B503="","",IFERROR(INDEX($D$17:$D$502,MATCH($B503,$B$17:$B$502,0)),""))</f>
         <v/>
       </c>
       <c r="E503">
@@ -41081,7 +41068,7 @@
       <c r="A504" s="37" t="n"/>
       <c r="C504" s="27" t="n"/>
       <c r="D504">
-        <f>IF($B504="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B504,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B504,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B504="","",IFERROR(INDEX($D$17:$D$503,MATCH($B504,$B$17:$B$503,0)),""))</f>
         <v/>
       </c>
       <c r="E504">
@@ -41101,7 +41088,7 @@
       <c r="A505" s="37" t="n"/>
       <c r="C505" s="27" t="n"/>
       <c r="D505">
-        <f>IF($B505="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B505,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B505,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B505="","",IFERROR(INDEX($D$17:$D$504,MATCH($B505,$B$17:$B$504,0)),""))</f>
         <v/>
       </c>
       <c r="E505">
@@ -41121,7 +41108,7 @@
       <c r="A506" s="37" t="n"/>
       <c r="C506" s="27" t="n"/>
       <c r="D506">
-        <f>IF($B506="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B506,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B506,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B506="","",IFERROR(INDEX($D$17:$D$505,MATCH($B506,$B$17:$B$505,0)),""))</f>
         <v/>
       </c>
       <c r="E506">
@@ -41141,7 +41128,7 @@
       <c r="A507" s="37" t="n"/>
       <c r="C507" s="27" t="n"/>
       <c r="D507">
-        <f>IF($B507="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B507,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B507,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B507="","",IFERROR(INDEX($D$17:$D$506,MATCH($B507,$B$17:$B$506,0)),""))</f>
         <v/>
       </c>
       <c r="E507">
@@ -41161,7 +41148,7 @@
       <c r="A508" s="37" t="n"/>
       <c r="C508" s="27" t="n"/>
       <c r="D508">
-        <f>IF($B508="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B508,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B508,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B508="","",IFERROR(INDEX($D$17:$D$507,MATCH($B508,$B$17:$B$507,0)),""))</f>
         <v/>
       </c>
       <c r="E508">
@@ -41181,7 +41168,7 @@
       <c r="A509" s="37" t="n"/>
       <c r="C509" s="27" t="n"/>
       <c r="D509">
-        <f>IF($B509="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B509,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B509,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B509="","",IFERROR(INDEX($D$17:$D$508,MATCH($B509,$B$17:$B$508,0)),""))</f>
         <v/>
       </c>
       <c r="E509">
@@ -41201,7 +41188,7 @@
       <c r="A510" s="37" t="n"/>
       <c r="C510" s="27" t="n"/>
       <c r="D510">
-        <f>IF($B510="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B510,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B510,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B510="","",IFERROR(INDEX($D$17:$D$509,MATCH($B510,$B$17:$B$509,0)),""))</f>
         <v/>
       </c>
       <c r="E510">
@@ -41221,7 +41208,7 @@
       <c r="A511" s="37" t="n"/>
       <c r="C511" s="27" t="n"/>
       <c r="D511">
-        <f>IF($B511="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B511,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B511,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B511="","",IFERROR(INDEX($D$17:$D$510,MATCH($B511,$B$17:$B$510,0)),""))</f>
         <v/>
       </c>
       <c r="E511">
@@ -41241,7 +41228,7 @@
       <c r="A512" s="37" t="n"/>
       <c r="C512" s="27" t="n"/>
       <c r="D512">
-        <f>IF($B512="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B512,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B512,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B512="","",IFERROR(INDEX($D$17:$D$511,MATCH($B512,$B$17:$B$511,0)),""))</f>
         <v/>
       </c>
       <c r="E512">
@@ -41261,7 +41248,7 @@
       <c r="A513" s="37" t="n"/>
       <c r="C513" s="27" t="n"/>
       <c r="D513">
-        <f>IF($B513="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B513,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B513,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B513="","",IFERROR(INDEX($D$17:$D$512,MATCH($B513,$B$17:$B$512,0)),""))</f>
         <v/>
       </c>
       <c r="E513">
@@ -41281,7 +41268,7 @@
       <c r="A514" s="37" t="n"/>
       <c r="C514" s="27" t="n"/>
       <c r="D514">
-        <f>IF($B514="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B514,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B514,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B514="","",IFERROR(INDEX($D$17:$D$513,MATCH($B514,$B$17:$B$513,0)),""))</f>
         <v/>
       </c>
       <c r="E514">
@@ -41301,7 +41288,7 @@
       <c r="A515" s="37" t="n"/>
       <c r="C515" s="27" t="n"/>
       <c r="D515">
-        <f>IF($B515="","",IFERROR(INDEX(Fact_Expenses[VendorName],MATCH($B515,Fact_Expenses[Description],0)),IFERROR(INDEX(Fact_Income[SourceName],MATCH($B515,Fact_Income[Description],0)),"")))</f>
+        <f>IF($B515="","",IFERROR(INDEX($D$17:$D$514,MATCH($B515,$B$17:$B$514,0)),""))</f>
         <v/>
       </c>
       <c r="E515">
@@ -41317,21 +41304,42 @@
         <v/>
       </c>
     </row>
+    <row r="516">
+      <c r="A516" s="37" t="n"/>
+      <c r="C516" s="27" t="n"/>
+      <c r="D516">
+        <f>IF($B516="","",IFERROR(INDEX($D$17:$D$515,MATCH($B516,$B$17:$B$515,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E516">
+        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D516,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <v/>
+      </c>
+      <c r="H516">
+        <f>IF($C516="","",IF(SignConvention="Negative = Expense",IF($C516&lt;0,"Expense","Income"),IF($C516&gt;0,"Expense","Income")))</f>
+        <v/>
+      </c>
+      <c r="I516" s="27">
+        <f>IF($C516="","",ABS($C516))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="A6:K6"/>
+    <mergeCell ref="E13:K13"/>
+    <mergeCell ref="A13:C13"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="A9:K9"/>
+    <mergeCell ref="A15:K15"/>
     <mergeCell ref="A7:K7"/>
-    <mergeCell ref="E12:K12"/>
+    <mergeCell ref="A11:K11"/>
     <mergeCell ref="A10:K10"/>
-    <mergeCell ref="A14:K14"/>
-    <mergeCell ref="A12:C12"/>
     <mergeCell ref="A5:K5"/>
     <mergeCell ref="A1:K2"/>
     <mergeCell ref="A8:K8"/>
   </mergeCells>
-  <conditionalFormatting sqref="H16:H515">
+  <conditionalFormatting sqref="H17:H516">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="3">
       <formula>"Expense"</formula>
     </cfRule>
@@ -41339,28 +41347,28 @@
       <formula>"Income"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D16:D515">
+  <conditionalFormatting sqref="D17:D516">
     <cfRule type="expression" priority="3" dxfId="5">
-      <formula>AND($C16&lt;&gt;"",$D16="")</formula>
+      <formula>AND($C17&lt;&gt;"",$D17="")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
-    <dataValidation sqref="D12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="D13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Negative = Expense,Positive = Expense"</formula1>
     </dataValidation>
-    <dataValidation sqref="D16:D515" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Please choose a value from the dropdown list." type="list">
+    <dataValidation sqref="D17:D516" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Please choose a value from the dropdown list." type="list">
       <formula1>VendorNameList</formula1>
     </dataValidation>
-    <dataValidation sqref="E16:E515" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Please choose a value from the dropdown list." type="list">
+    <dataValidation sqref="E17:E516" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Please choose a value from the dropdown list." type="list">
       <formula1>ExpenseCategoryList</formula1>
     </dataValidation>
-    <dataValidation sqref="F16:F515" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Please choose a value from the dropdown list." type="list">
+    <dataValidation sqref="F17:F516" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Please choose a value from the dropdown list." type="list">
       <formula1>AccountNameList</formula1>
     </dataValidation>
-    <dataValidation sqref="G16:G515" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Please choose a value from the dropdown list." type="list">
+    <dataValidation sqref="G17:G516" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Please choose a value from the dropdown list." type="list">
       <formula1>PaymentMethodList</formula1>
     </dataValidation>
-    <dataValidation sqref="J16:J515" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Please choose a value from the dropdown list." type="list">
+    <dataValidation sqref="J17:J516" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Please choose a value from the dropdown list." type="list">
       <formula1>List_NeedWant</formula1>
     </dataValidation>
   </dataValidations>
@@ -57231,7 +57239,7 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="26" t="inlineStr">
         <is>
-          <t>Category Budgets  —  set MonthlyBudget per category; Actual pulls live from Expenses this month</t>
+          <t>Category Budgets  —  set MonthlyBudget per category; Actual pulls live from Expenses + Bank Import this month</t>
         </is>
       </c>
       <c r="B9" s="2" t="n"/>
@@ -57289,7 +57297,7 @@
         <v>2200</v>
       </c>
       <c r="C11" s="40">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A11,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A11,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A11,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="D11" s="40">
@@ -57319,7 +57327,7 @@
         <v>320</v>
       </c>
       <c r="C12" s="40">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A12,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A12,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A12,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="D12" s="40">
@@ -57349,7 +57357,7 @@
         <v>250</v>
       </c>
       <c r="C13" s="40">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A13,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A13,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A13,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="D13" s="40">
@@ -57379,7 +57387,7 @@
         <v>650</v>
       </c>
       <c r="C14" s="40">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A14,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A14,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A14,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="D14" s="40">
@@ -57409,7 +57417,7 @@
         <v>300</v>
       </c>
       <c r="C15" s="40">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A15,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A15,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A15,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="D15" s="40">
@@ -57439,7 +57447,7 @@
         <v>150</v>
       </c>
       <c r="C16" s="40">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A16,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A16,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A16,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="D16" s="40">
@@ -57469,7 +57477,7 @@
         <v>200</v>
       </c>
       <c r="C17" s="40">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A17,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A17,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A17,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="D17" s="40">
@@ -57499,7 +57507,7 @@
         <v>80</v>
       </c>
       <c r="C18" s="40">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A18,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A18,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A18,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="D18" s="40">
@@ -57529,7 +57537,7 @@
         <v>200</v>
       </c>
       <c r="C19" s="40">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A19,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A19,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A19,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="D19" s="40">
@@ -57559,7 +57567,7 @@
         <v>100</v>
       </c>
       <c r="C20" s="40">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A20,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A20,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A20,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="D20" s="40">
@@ -58027,11 +58035,11 @@
         <v>1</v>
       </c>
       <c r="D6" s="40">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B6,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B6,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B6,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="E6" s="40">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B6,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B6,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B6,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -58048,11 +58056,11 @@
         <v>2</v>
       </c>
       <c r="D7" s="40">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B7,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B7,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B7,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="E7" s="40">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B7,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B7,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B7,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -58069,11 +58077,11 @@
         <v>2</v>
       </c>
       <c r="D8" s="40">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B8,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B8,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B8,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="E8" s="40">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B8,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B8,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B8,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -58090,11 +58098,11 @@
         <v>2</v>
       </c>
       <c r="D9" s="40">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B9,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B9,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B9,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="E9" s="40">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B9,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B9,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B9,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -58111,11 +58119,11 @@
         <v>3</v>
       </c>
       <c r="D10" s="40">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B10,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B10,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B10,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="E10" s="40">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B10,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B10,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B10,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -58132,11 +58140,11 @@
         <v>3</v>
       </c>
       <c r="D11" s="40">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B11,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B11,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B11,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="E11" s="40">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B11,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B11,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B11,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -58153,11 +58161,11 @@
         <v>4</v>
       </c>
       <c r="D12" s="40">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B12,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B12,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B12,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="E12" s="40">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B12,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B12,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B12,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -58174,11 +58182,11 @@
         <v>4</v>
       </c>
       <c r="D13" s="40">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B13,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B13,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B13,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="E13" s="40">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B13,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B13,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B13,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -58195,11 +58203,11 @@
         <v>5</v>
       </c>
       <c r="D14" s="40">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B14,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B14,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B14,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="E14" s="40">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B14,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B14,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B14,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -58216,11 +58224,11 @@
         <v>6</v>
       </c>
       <c r="D15" s="40">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B15,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B15,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B15,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="E15" s="40">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B15,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B15,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B15,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -58237,11 +58245,11 @@
         <v>7</v>
       </c>
       <c r="D16" s="40">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B16,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B16,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B16,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="E16" s="40">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B16,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B16,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B16,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -58258,11 +58266,11 @@
         <v>7</v>
       </c>
       <c r="D17" s="40">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B17,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B17,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B17,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="E17" s="40">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B17,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B17,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B17,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -58279,11 +58287,11 @@
         <v>7</v>
       </c>
       <c r="D18" s="40">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B18,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B18,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B18,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="E18" s="40">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B18,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B18,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B18,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -58300,11 +58308,11 @@
         <v>8</v>
       </c>
       <c r="D19" s="40">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B19,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B19,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B19,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="E19" s="40">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B19,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B19,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B19,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -58321,11 +58329,11 @@
         <v>9</v>
       </c>
       <c r="D20" s="40">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B20,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B20,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B20,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="E20" s="40">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B20,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B20,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B20,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -58342,11 +58350,11 @@
         <v>9</v>
       </c>
       <c r="D21" s="40">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B21,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B21,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B21,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="E21" s="40">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B21,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B21,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B21,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -58363,11 +58371,11 @@
         <v>11</v>
       </c>
       <c r="D22" s="40">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B22,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B22,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B22,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="E22" s="40">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B22,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B22,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B22,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -58384,11 +58392,11 @@
         <v>12</v>
       </c>
       <c r="D23" s="40">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B23,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B23,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B23,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="E23" s="40">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B23,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B23,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B23,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>

--- a/Personal Finance Dashboard/Personal Finance Intelligence Dashboard.xlsx
+++ b/Personal Finance Dashboard/Personal Finance Intelligence Dashboard.xlsx
@@ -1337,14 +1337,15 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Dim_Vendor" displayName="Dim_Vendor" ref="A5:E156" headerRowCount="1">
-  <autoFilter ref="A5:E156"/>
-  <tableColumns count="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Dim_Vendor" displayName="Dim_Vendor" ref="A5:F156" headerRowCount="1">
+  <autoFilter ref="A5:F156"/>
+  <tableColumns count="6">
     <tableColumn id="1" name="VendorID"/>
     <tableColumn id="2" name="VendorName"/>
-    <tableColumn id="3" name="DefaultCategoryID"/>
-    <tableColumn id="4" name="CurMonthSpend"/>
-    <tableColumn id="5" name="YTDSpend"/>
+    <tableColumn id="3" name="DefaultCategory"/>
+    <tableColumn id="4" name="DefaultCategoryID"/>
+    <tableColumn id="5" name="CurMonthSpend"/>
+    <tableColumn id="6" name="YTDSpend"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showRowStripes="1"/>
 </table>
@@ -31518,7 +31519,7 @@
         <v/>
       </c>
       <c r="E17">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D17,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D17,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H17">
@@ -31538,7 +31539,7 @@
         <v/>
       </c>
       <c r="E18">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D18,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D18,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H18">
@@ -31558,7 +31559,7 @@
         <v/>
       </c>
       <c r="E19">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D19,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D19,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H19">
@@ -31578,7 +31579,7 @@
         <v/>
       </c>
       <c r="E20">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D20,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D20,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H20">
@@ -31598,7 +31599,7 @@
         <v/>
       </c>
       <c r="E21">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D21,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D21,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H21">
@@ -31618,7 +31619,7 @@
         <v/>
       </c>
       <c r="E22">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D22,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D22,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H22">
@@ -31638,7 +31639,7 @@
         <v/>
       </c>
       <c r="E23">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D23,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D23,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H23">
@@ -31658,7 +31659,7 @@
         <v/>
       </c>
       <c r="E24">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D24,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D24,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H24">
@@ -31678,7 +31679,7 @@
         <v/>
       </c>
       <c r="E25">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D25,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D25,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H25">
@@ -31698,7 +31699,7 @@
         <v/>
       </c>
       <c r="E26">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D26,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D26,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H26">
@@ -31718,7 +31719,7 @@
         <v/>
       </c>
       <c r="E27">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D27,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D27,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H27">
@@ -31738,7 +31739,7 @@
         <v/>
       </c>
       <c r="E28">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D28,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D28,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H28">
@@ -31758,7 +31759,7 @@
         <v/>
       </c>
       <c r="E29">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D29,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D29,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H29">
@@ -31778,7 +31779,7 @@
         <v/>
       </c>
       <c r="E30">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D30,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D30,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H30">
@@ -31798,7 +31799,7 @@
         <v/>
       </c>
       <c r="E31">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D31,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D31,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H31">
@@ -31818,7 +31819,7 @@
         <v/>
       </c>
       <c r="E32">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D32,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D32,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H32">
@@ -31838,7 +31839,7 @@
         <v/>
       </c>
       <c r="E33">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D33,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D33,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H33">
@@ -31858,7 +31859,7 @@
         <v/>
       </c>
       <c r="E34">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D34,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D34,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H34">
@@ -31878,7 +31879,7 @@
         <v/>
       </c>
       <c r="E35">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D35,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D35,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H35">
@@ -31898,7 +31899,7 @@
         <v/>
       </c>
       <c r="E36">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D36,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D36,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H36">
@@ -31918,7 +31919,7 @@
         <v/>
       </c>
       <c r="E37">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D37,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D37,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H37">
@@ -31938,7 +31939,7 @@
         <v/>
       </c>
       <c r="E38">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D38,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D38,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H38">
@@ -31958,7 +31959,7 @@
         <v/>
       </c>
       <c r="E39">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D39,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D39,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H39">
@@ -31978,7 +31979,7 @@
         <v/>
       </c>
       <c r="E40">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D40,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D40,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H40">
@@ -31998,7 +31999,7 @@
         <v/>
       </c>
       <c r="E41">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D41,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D41,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H41">
@@ -32018,7 +32019,7 @@
         <v/>
       </c>
       <c r="E42">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D42,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D42,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H42">
@@ -32038,7 +32039,7 @@
         <v/>
       </c>
       <c r="E43">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D43,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D43,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H43">
@@ -32058,7 +32059,7 @@
         <v/>
       </c>
       <c r="E44">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D44,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D44,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H44">
@@ -32078,7 +32079,7 @@
         <v/>
       </c>
       <c r="E45">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D45,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D45,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H45">
@@ -32098,7 +32099,7 @@
         <v/>
       </c>
       <c r="E46">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D46,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D46,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H46">
@@ -32118,7 +32119,7 @@
         <v/>
       </c>
       <c r="E47">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D47,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D47,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H47">
@@ -32138,7 +32139,7 @@
         <v/>
       </c>
       <c r="E48">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D48,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D48,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H48">
@@ -32158,7 +32159,7 @@
         <v/>
       </c>
       <c r="E49">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D49,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D49,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H49">
@@ -32178,7 +32179,7 @@
         <v/>
       </c>
       <c r="E50">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D50,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D50,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H50">
@@ -32198,7 +32199,7 @@
         <v/>
       </c>
       <c r="E51">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D51,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D51,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H51">
@@ -32218,7 +32219,7 @@
         <v/>
       </c>
       <c r="E52">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D52,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D52,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H52">
@@ -32238,7 +32239,7 @@
         <v/>
       </c>
       <c r="E53">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D53,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D53,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H53">
@@ -32258,7 +32259,7 @@
         <v/>
       </c>
       <c r="E54">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D54,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D54,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H54">
@@ -32278,7 +32279,7 @@
         <v/>
       </c>
       <c r="E55">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D55,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D55,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H55">
@@ -32298,7 +32299,7 @@
         <v/>
       </c>
       <c r="E56">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D56,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D56,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H56">
@@ -32318,7 +32319,7 @@
         <v/>
       </c>
       <c r="E57">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D57,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D57,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H57">
@@ -32338,7 +32339,7 @@
         <v/>
       </c>
       <c r="E58">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D58,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D58,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H58">
@@ -32358,7 +32359,7 @@
         <v/>
       </c>
       <c r="E59">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D59,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D59,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H59">
@@ -32378,7 +32379,7 @@
         <v/>
       </c>
       <c r="E60">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D60,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D60,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H60">
@@ -32398,7 +32399,7 @@
         <v/>
       </c>
       <c r="E61">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D61,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D61,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H61">
@@ -32418,7 +32419,7 @@
         <v/>
       </c>
       <c r="E62">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D62,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D62,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H62">
@@ -32438,7 +32439,7 @@
         <v/>
       </c>
       <c r="E63">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D63,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D63,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H63">
@@ -32458,7 +32459,7 @@
         <v/>
       </c>
       <c r="E64">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D64,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D64,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H64">
@@ -32478,7 +32479,7 @@
         <v/>
       </c>
       <c r="E65">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D65,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D65,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H65">
@@ -32498,7 +32499,7 @@
         <v/>
       </c>
       <c r="E66">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D66,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D66,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H66">
@@ -32518,7 +32519,7 @@
         <v/>
       </c>
       <c r="E67">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D67,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D67,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H67">
@@ -32538,7 +32539,7 @@
         <v/>
       </c>
       <c r="E68">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D68,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D68,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H68">
@@ -32558,7 +32559,7 @@
         <v/>
       </c>
       <c r="E69">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D69,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D69,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H69">
@@ -32578,7 +32579,7 @@
         <v/>
       </c>
       <c r="E70">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D70,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D70,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H70">
@@ -32598,7 +32599,7 @@
         <v/>
       </c>
       <c r="E71">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D71,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D71,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H71">
@@ -32618,7 +32619,7 @@
         <v/>
       </c>
       <c r="E72">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D72,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D72,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H72">
@@ -32638,7 +32639,7 @@
         <v/>
       </c>
       <c r="E73">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D73,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D73,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H73">
@@ -32658,7 +32659,7 @@
         <v/>
       </c>
       <c r="E74">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D74,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D74,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H74">
@@ -32678,7 +32679,7 @@
         <v/>
       </c>
       <c r="E75">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D75,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D75,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H75">
@@ -32698,7 +32699,7 @@
         <v/>
       </c>
       <c r="E76">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D76,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D76,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H76">
@@ -32718,7 +32719,7 @@
         <v/>
       </c>
       <c r="E77">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D77,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D77,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H77">
@@ -32738,7 +32739,7 @@
         <v/>
       </c>
       <c r="E78">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D78,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D78,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H78">
@@ -32758,7 +32759,7 @@
         <v/>
       </c>
       <c r="E79">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D79,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D79,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H79">
@@ -32778,7 +32779,7 @@
         <v/>
       </c>
       <c r="E80">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D80,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D80,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H80">
@@ -32798,7 +32799,7 @@
         <v/>
       </c>
       <c r="E81">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D81,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D81,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H81">
@@ -32818,7 +32819,7 @@
         <v/>
       </c>
       <c r="E82">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D82,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D82,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H82">
@@ -32838,7 +32839,7 @@
         <v/>
       </c>
       <c r="E83">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D83,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D83,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H83">
@@ -32858,7 +32859,7 @@
         <v/>
       </c>
       <c r="E84">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D84,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D84,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H84">
@@ -32878,7 +32879,7 @@
         <v/>
       </c>
       <c r="E85">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D85,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D85,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H85">
@@ -32898,7 +32899,7 @@
         <v/>
       </c>
       <c r="E86">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D86,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D86,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H86">
@@ -32918,7 +32919,7 @@
         <v/>
       </c>
       <c r="E87">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D87,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D87,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H87">
@@ -32938,7 +32939,7 @@
         <v/>
       </c>
       <c r="E88">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D88,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D88,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H88">
@@ -32958,7 +32959,7 @@
         <v/>
       </c>
       <c r="E89">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D89,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D89,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H89">
@@ -32978,7 +32979,7 @@
         <v/>
       </c>
       <c r="E90">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D90,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D90,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H90">
@@ -32998,7 +32999,7 @@
         <v/>
       </c>
       <c r="E91">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D91,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D91,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H91">
@@ -33018,7 +33019,7 @@
         <v/>
       </c>
       <c r="E92">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D92,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D92,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H92">
@@ -33038,7 +33039,7 @@
         <v/>
       </c>
       <c r="E93">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D93,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D93,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H93">
@@ -33058,7 +33059,7 @@
         <v/>
       </c>
       <c r="E94">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D94,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D94,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H94">
@@ -33078,7 +33079,7 @@
         <v/>
       </c>
       <c r="E95">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D95,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D95,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H95">
@@ -33098,7 +33099,7 @@
         <v/>
       </c>
       <c r="E96">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D96,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D96,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H96">
@@ -33118,7 +33119,7 @@
         <v/>
       </c>
       <c r="E97">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D97,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D97,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H97">
@@ -33138,7 +33139,7 @@
         <v/>
       </c>
       <c r="E98">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D98,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D98,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H98">
@@ -33158,7 +33159,7 @@
         <v/>
       </c>
       <c r="E99">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D99,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D99,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H99">
@@ -33178,7 +33179,7 @@
         <v/>
       </c>
       <c r="E100">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D100,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D100,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H100">
@@ -33198,7 +33199,7 @@
         <v/>
       </c>
       <c r="E101">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D101,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D101,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H101">
@@ -33218,7 +33219,7 @@
         <v/>
       </c>
       <c r="E102">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D102,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D102,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H102">
@@ -33238,7 +33239,7 @@
         <v/>
       </c>
       <c r="E103">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D103,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D103,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H103">
@@ -33258,7 +33259,7 @@
         <v/>
       </c>
       <c r="E104">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D104,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D104,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H104">
@@ -33278,7 +33279,7 @@
         <v/>
       </c>
       <c r="E105">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D105,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D105,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H105">
@@ -33298,7 +33299,7 @@
         <v/>
       </c>
       <c r="E106">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D106,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D106,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H106">
@@ -33318,7 +33319,7 @@
         <v/>
       </c>
       <c r="E107">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D107,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D107,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H107">
@@ -33338,7 +33339,7 @@
         <v/>
       </c>
       <c r="E108">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D108,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D108,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H108">
@@ -33358,7 +33359,7 @@
         <v/>
       </c>
       <c r="E109">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D109,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D109,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H109">
@@ -33378,7 +33379,7 @@
         <v/>
       </c>
       <c r="E110">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D110,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D110,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H110">
@@ -33398,7 +33399,7 @@
         <v/>
       </c>
       <c r="E111">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D111,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D111,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H111">
@@ -33418,7 +33419,7 @@
         <v/>
       </c>
       <c r="E112">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D112,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D112,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H112">
@@ -33438,7 +33439,7 @@
         <v/>
       </c>
       <c r="E113">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D113,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D113,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H113">
@@ -33458,7 +33459,7 @@
         <v/>
       </c>
       <c r="E114">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D114,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D114,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H114">
@@ -33478,7 +33479,7 @@
         <v/>
       </c>
       <c r="E115">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D115,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D115,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H115">
@@ -33498,7 +33499,7 @@
         <v/>
       </c>
       <c r="E116">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D116,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D116,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H116">
@@ -33518,7 +33519,7 @@
         <v/>
       </c>
       <c r="E117">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D117,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D117,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H117">
@@ -33538,7 +33539,7 @@
         <v/>
       </c>
       <c r="E118">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D118,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D118,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H118">
@@ -33558,7 +33559,7 @@
         <v/>
       </c>
       <c r="E119">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D119,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D119,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H119">
@@ -33578,7 +33579,7 @@
         <v/>
       </c>
       <c r="E120">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D120,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D120,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H120">
@@ -33598,7 +33599,7 @@
         <v/>
       </c>
       <c r="E121">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D121,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D121,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H121">
@@ -33618,7 +33619,7 @@
         <v/>
       </c>
       <c r="E122">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D122,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D122,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H122">
@@ -33638,7 +33639,7 @@
         <v/>
       </c>
       <c r="E123">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D123,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D123,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H123">
@@ -33658,7 +33659,7 @@
         <v/>
       </c>
       <c r="E124">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D124,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D124,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H124">
@@ -33678,7 +33679,7 @@
         <v/>
       </c>
       <c r="E125">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D125,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D125,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H125">
@@ -33698,7 +33699,7 @@
         <v/>
       </c>
       <c r="E126">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D126,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D126,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H126">
@@ -33718,7 +33719,7 @@
         <v/>
       </c>
       <c r="E127">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D127,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D127,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H127">
@@ -33738,7 +33739,7 @@
         <v/>
       </c>
       <c r="E128">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D128,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D128,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H128">
@@ -33758,7 +33759,7 @@
         <v/>
       </c>
       <c r="E129">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D129,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D129,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H129">
@@ -33778,7 +33779,7 @@
         <v/>
       </c>
       <c r="E130">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D130,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D130,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H130">
@@ -33798,7 +33799,7 @@
         <v/>
       </c>
       <c r="E131">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D131,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D131,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H131">
@@ -33818,7 +33819,7 @@
         <v/>
       </c>
       <c r="E132">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D132,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D132,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H132">
@@ -33838,7 +33839,7 @@
         <v/>
       </c>
       <c r="E133">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D133,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D133,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H133">
@@ -33858,7 +33859,7 @@
         <v/>
       </c>
       <c r="E134">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D134,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D134,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H134">
@@ -33878,7 +33879,7 @@
         <v/>
       </c>
       <c r="E135">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D135,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D135,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H135">
@@ -33898,7 +33899,7 @@
         <v/>
       </c>
       <c r="E136">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D136,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D136,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H136">
@@ -33918,7 +33919,7 @@
         <v/>
       </c>
       <c r="E137">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D137,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D137,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H137">
@@ -33938,7 +33939,7 @@
         <v/>
       </c>
       <c r="E138">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D138,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D138,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H138">
@@ -33958,7 +33959,7 @@
         <v/>
       </c>
       <c r="E139">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D139,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D139,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H139">
@@ -33978,7 +33979,7 @@
         <v/>
       </c>
       <c r="E140">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D140,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D140,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H140">
@@ -33998,7 +33999,7 @@
         <v/>
       </c>
       <c r="E141">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D141,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D141,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H141">
@@ -34018,7 +34019,7 @@
         <v/>
       </c>
       <c r="E142">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D142,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D142,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H142">
@@ -34038,7 +34039,7 @@
         <v/>
       </c>
       <c r="E143">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D143,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D143,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H143">
@@ -34058,7 +34059,7 @@
         <v/>
       </c>
       <c r="E144">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D144,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D144,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H144">
@@ -34078,7 +34079,7 @@
         <v/>
       </c>
       <c r="E145">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D145,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D145,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H145">
@@ -34098,7 +34099,7 @@
         <v/>
       </c>
       <c r="E146">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D146,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D146,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H146">
@@ -34118,7 +34119,7 @@
         <v/>
       </c>
       <c r="E147">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D147,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D147,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H147">
@@ -34138,7 +34139,7 @@
         <v/>
       </c>
       <c r="E148">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D148,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D148,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H148">
@@ -34158,7 +34159,7 @@
         <v/>
       </c>
       <c r="E149">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D149,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D149,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H149">
@@ -34178,7 +34179,7 @@
         <v/>
       </c>
       <c r="E150">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D150,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D150,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H150">
@@ -34198,7 +34199,7 @@
         <v/>
       </c>
       <c r="E151">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D151,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D151,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H151">
@@ -34218,7 +34219,7 @@
         <v/>
       </c>
       <c r="E152">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D152,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D152,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H152">
@@ -34238,7 +34239,7 @@
         <v/>
       </c>
       <c r="E153">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D153,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D153,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H153">
@@ -34258,7 +34259,7 @@
         <v/>
       </c>
       <c r="E154">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D154,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D154,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H154">
@@ -34278,7 +34279,7 @@
         <v/>
       </c>
       <c r="E155">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D155,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D155,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H155">
@@ -34298,7 +34299,7 @@
         <v/>
       </c>
       <c r="E156">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D156,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D156,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H156">
@@ -34318,7 +34319,7 @@
         <v/>
       </c>
       <c r="E157">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D157,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D157,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H157">
@@ -34338,7 +34339,7 @@
         <v/>
       </c>
       <c r="E158">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D158,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D158,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H158">
@@ -34358,7 +34359,7 @@
         <v/>
       </c>
       <c r="E159">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D159,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D159,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H159">
@@ -34378,7 +34379,7 @@
         <v/>
       </c>
       <c r="E160">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D160,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D160,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H160">
@@ -34398,7 +34399,7 @@
         <v/>
       </c>
       <c r="E161">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D161,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D161,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H161">
@@ -34418,7 +34419,7 @@
         <v/>
       </c>
       <c r="E162">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D162,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D162,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H162">
@@ -34438,7 +34439,7 @@
         <v/>
       </c>
       <c r="E163">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D163,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D163,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H163">
@@ -34458,7 +34459,7 @@
         <v/>
       </c>
       <c r="E164">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D164,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D164,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H164">
@@ -34478,7 +34479,7 @@
         <v/>
       </c>
       <c r="E165">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D165,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D165,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H165">
@@ -34498,7 +34499,7 @@
         <v/>
       </c>
       <c r="E166">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D166,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D166,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H166">
@@ -34518,7 +34519,7 @@
         <v/>
       </c>
       <c r="E167">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D167,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D167,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H167">
@@ -34538,7 +34539,7 @@
         <v/>
       </c>
       <c r="E168">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D168,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D168,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H168">
@@ -34558,7 +34559,7 @@
         <v/>
       </c>
       <c r="E169">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D169,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D169,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H169">
@@ -34578,7 +34579,7 @@
         <v/>
       </c>
       <c r="E170">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D170,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D170,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H170">
@@ -34598,7 +34599,7 @@
         <v/>
       </c>
       <c r="E171">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D171,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D171,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H171">
@@ -34618,7 +34619,7 @@
         <v/>
       </c>
       <c r="E172">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D172,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D172,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H172">
@@ -34638,7 +34639,7 @@
         <v/>
       </c>
       <c r="E173">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D173,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D173,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H173">
@@ -34658,7 +34659,7 @@
         <v/>
       </c>
       <c r="E174">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D174,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D174,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H174">
@@ -34678,7 +34679,7 @@
         <v/>
       </c>
       <c r="E175">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D175,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D175,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H175">
@@ -34698,7 +34699,7 @@
         <v/>
       </c>
       <c r="E176">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D176,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D176,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H176">
@@ -34718,7 +34719,7 @@
         <v/>
       </c>
       <c r="E177">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D177,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D177,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H177">
@@ -34738,7 +34739,7 @@
         <v/>
       </c>
       <c r="E178">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D178,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D178,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H178">
@@ -34758,7 +34759,7 @@
         <v/>
       </c>
       <c r="E179">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D179,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D179,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H179">
@@ -34778,7 +34779,7 @@
         <v/>
       </c>
       <c r="E180">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D180,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D180,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H180">
@@ -34798,7 +34799,7 @@
         <v/>
       </c>
       <c r="E181">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D181,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D181,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H181">
@@ -34818,7 +34819,7 @@
         <v/>
       </c>
       <c r="E182">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D182,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D182,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H182">
@@ -34838,7 +34839,7 @@
         <v/>
       </c>
       <c r="E183">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D183,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D183,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H183">
@@ -34858,7 +34859,7 @@
         <v/>
       </c>
       <c r="E184">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D184,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D184,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H184">
@@ -34878,7 +34879,7 @@
         <v/>
       </c>
       <c r="E185">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D185,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D185,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H185">
@@ -34898,7 +34899,7 @@
         <v/>
       </c>
       <c r="E186">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D186,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D186,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H186">
@@ -34918,7 +34919,7 @@
         <v/>
       </c>
       <c r="E187">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D187,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D187,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H187">
@@ -34938,7 +34939,7 @@
         <v/>
       </c>
       <c r="E188">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D188,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D188,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H188">
@@ -34958,7 +34959,7 @@
         <v/>
       </c>
       <c r="E189">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D189,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D189,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H189">
@@ -34978,7 +34979,7 @@
         <v/>
       </c>
       <c r="E190">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D190,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D190,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H190">
@@ -34998,7 +34999,7 @@
         <v/>
       </c>
       <c r="E191">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D191,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D191,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H191">
@@ -35018,7 +35019,7 @@
         <v/>
       </c>
       <c r="E192">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D192,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D192,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H192">
@@ -35038,7 +35039,7 @@
         <v/>
       </c>
       <c r="E193">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D193,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D193,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H193">
@@ -35058,7 +35059,7 @@
         <v/>
       </c>
       <c r="E194">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D194,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D194,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H194">
@@ -35078,7 +35079,7 @@
         <v/>
       </c>
       <c r="E195">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D195,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D195,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H195">
@@ -35098,7 +35099,7 @@
         <v/>
       </c>
       <c r="E196">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D196,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D196,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H196">
@@ -35118,7 +35119,7 @@
         <v/>
       </c>
       <c r="E197">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D197,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D197,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H197">
@@ -35138,7 +35139,7 @@
         <v/>
       </c>
       <c r="E198">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D198,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D198,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H198">
@@ -35158,7 +35159,7 @@
         <v/>
       </c>
       <c r="E199">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D199,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D199,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H199">
@@ -35178,7 +35179,7 @@
         <v/>
       </c>
       <c r="E200">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D200,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D200,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H200">
@@ -35198,7 +35199,7 @@
         <v/>
       </c>
       <c r="E201">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D201,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D201,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H201">
@@ -35218,7 +35219,7 @@
         <v/>
       </c>
       <c r="E202">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D202,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D202,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H202">
@@ -35238,7 +35239,7 @@
         <v/>
       </c>
       <c r="E203">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D203,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D203,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H203">
@@ -35258,7 +35259,7 @@
         <v/>
       </c>
       <c r="E204">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D204,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D204,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H204">
@@ -35278,7 +35279,7 @@
         <v/>
       </c>
       <c r="E205">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D205,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D205,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H205">
@@ -35298,7 +35299,7 @@
         <v/>
       </c>
       <c r="E206">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D206,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D206,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H206">
@@ -35318,7 +35319,7 @@
         <v/>
       </c>
       <c r="E207">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D207,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D207,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H207">
@@ -35338,7 +35339,7 @@
         <v/>
       </c>
       <c r="E208">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D208,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D208,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H208">
@@ -35358,7 +35359,7 @@
         <v/>
       </c>
       <c r="E209">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D209,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D209,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H209">
@@ -35378,7 +35379,7 @@
         <v/>
       </c>
       <c r="E210">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D210,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D210,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H210">
@@ -35398,7 +35399,7 @@
         <v/>
       </c>
       <c r="E211">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D211,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D211,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H211">
@@ -35418,7 +35419,7 @@
         <v/>
       </c>
       <c r="E212">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D212,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D212,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H212">
@@ -35438,7 +35439,7 @@
         <v/>
       </c>
       <c r="E213">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D213,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D213,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H213">
@@ -35458,7 +35459,7 @@
         <v/>
       </c>
       <c r="E214">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D214,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D214,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H214">
@@ -35478,7 +35479,7 @@
         <v/>
       </c>
       <c r="E215">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D215,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D215,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H215">
@@ -35498,7 +35499,7 @@
         <v/>
       </c>
       <c r="E216">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D216,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D216,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H216">
@@ -35518,7 +35519,7 @@
         <v/>
       </c>
       <c r="E217">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D217,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D217,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H217">
@@ -35538,7 +35539,7 @@
         <v/>
       </c>
       <c r="E218">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D218,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D218,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H218">
@@ -35558,7 +35559,7 @@
         <v/>
       </c>
       <c r="E219">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D219,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D219,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H219">
@@ -35578,7 +35579,7 @@
         <v/>
       </c>
       <c r="E220">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D220,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D220,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H220">
@@ -35598,7 +35599,7 @@
         <v/>
       </c>
       <c r="E221">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D221,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D221,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H221">
@@ -35618,7 +35619,7 @@
         <v/>
       </c>
       <c r="E222">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D222,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D222,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H222">
@@ -35638,7 +35639,7 @@
         <v/>
       </c>
       <c r="E223">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D223,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D223,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H223">
@@ -35658,7 +35659,7 @@
         <v/>
       </c>
       <c r="E224">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D224,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D224,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H224">
@@ -35678,7 +35679,7 @@
         <v/>
       </c>
       <c r="E225">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D225,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D225,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H225">
@@ -35698,7 +35699,7 @@
         <v/>
       </c>
       <c r="E226">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D226,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D226,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H226">
@@ -35718,7 +35719,7 @@
         <v/>
       </c>
       <c r="E227">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D227,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D227,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H227">
@@ -35738,7 +35739,7 @@
         <v/>
       </c>
       <c r="E228">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D228,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D228,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H228">
@@ -35758,7 +35759,7 @@
         <v/>
       </c>
       <c r="E229">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D229,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D229,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H229">
@@ -35778,7 +35779,7 @@
         <v/>
       </c>
       <c r="E230">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D230,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D230,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H230">
@@ -35798,7 +35799,7 @@
         <v/>
       </c>
       <c r="E231">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D231,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D231,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H231">
@@ -35818,7 +35819,7 @@
         <v/>
       </c>
       <c r="E232">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D232,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D232,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H232">
@@ -35838,7 +35839,7 @@
         <v/>
       </c>
       <c r="E233">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D233,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D233,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H233">
@@ -35858,7 +35859,7 @@
         <v/>
       </c>
       <c r="E234">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D234,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D234,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H234">
@@ -35878,7 +35879,7 @@
         <v/>
       </c>
       <c r="E235">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D235,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D235,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H235">
@@ -35898,7 +35899,7 @@
         <v/>
       </c>
       <c r="E236">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D236,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D236,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H236">
@@ -35918,7 +35919,7 @@
         <v/>
       </c>
       <c r="E237">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D237,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D237,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H237">
@@ -35938,7 +35939,7 @@
         <v/>
       </c>
       <c r="E238">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D238,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D238,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H238">
@@ -35958,7 +35959,7 @@
         <v/>
       </c>
       <c r="E239">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D239,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D239,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H239">
@@ -35978,7 +35979,7 @@
         <v/>
       </c>
       <c r="E240">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D240,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D240,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H240">
@@ -35998,7 +35999,7 @@
         <v/>
       </c>
       <c r="E241">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D241,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D241,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H241">
@@ -36018,7 +36019,7 @@
         <v/>
       </c>
       <c r="E242">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D242,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D242,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H242">
@@ -36038,7 +36039,7 @@
         <v/>
       </c>
       <c r="E243">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D243,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D243,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H243">
@@ -36058,7 +36059,7 @@
         <v/>
       </c>
       <c r="E244">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D244,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D244,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H244">
@@ -36078,7 +36079,7 @@
         <v/>
       </c>
       <c r="E245">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D245,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D245,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H245">
@@ -36098,7 +36099,7 @@
         <v/>
       </c>
       <c r="E246">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D246,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D246,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H246">
@@ -36118,7 +36119,7 @@
         <v/>
       </c>
       <c r="E247">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D247,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D247,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H247">
@@ -36138,7 +36139,7 @@
         <v/>
       </c>
       <c r="E248">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D248,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D248,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H248">
@@ -36158,7 +36159,7 @@
         <v/>
       </c>
       <c r="E249">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D249,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D249,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H249">
@@ -36178,7 +36179,7 @@
         <v/>
       </c>
       <c r="E250">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D250,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D250,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H250">
@@ -36198,7 +36199,7 @@
         <v/>
       </c>
       <c r="E251">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D251,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D251,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H251">
@@ -36218,7 +36219,7 @@
         <v/>
       </c>
       <c r="E252">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D252,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D252,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H252">
@@ -36238,7 +36239,7 @@
         <v/>
       </c>
       <c r="E253">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D253,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D253,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H253">
@@ -36258,7 +36259,7 @@
         <v/>
       </c>
       <c r="E254">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D254,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D254,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H254">
@@ -36278,7 +36279,7 @@
         <v/>
       </c>
       <c r="E255">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D255,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D255,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H255">
@@ -36298,7 +36299,7 @@
         <v/>
       </c>
       <c r="E256">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D256,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D256,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H256">
@@ -36318,7 +36319,7 @@
         <v/>
       </c>
       <c r="E257">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D257,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D257,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H257">
@@ -36338,7 +36339,7 @@
         <v/>
       </c>
       <c r="E258">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D258,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D258,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H258">
@@ -36358,7 +36359,7 @@
         <v/>
       </c>
       <c r="E259">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D259,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D259,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H259">
@@ -36378,7 +36379,7 @@
         <v/>
       </c>
       <c r="E260">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D260,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D260,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H260">
@@ -36398,7 +36399,7 @@
         <v/>
       </c>
       <c r="E261">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D261,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D261,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H261">
@@ -36418,7 +36419,7 @@
         <v/>
       </c>
       <c r="E262">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D262,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D262,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H262">
@@ -36438,7 +36439,7 @@
         <v/>
       </c>
       <c r="E263">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D263,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D263,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H263">
@@ -36458,7 +36459,7 @@
         <v/>
       </c>
       <c r="E264">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D264,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D264,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H264">
@@ -36478,7 +36479,7 @@
         <v/>
       </c>
       <c r="E265">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D265,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D265,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H265">
@@ -36498,7 +36499,7 @@
         <v/>
       </c>
       <c r="E266">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D266,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D266,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H266">
@@ -36518,7 +36519,7 @@
         <v/>
       </c>
       <c r="E267">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D267,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D267,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H267">
@@ -36538,7 +36539,7 @@
         <v/>
       </c>
       <c r="E268">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D268,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D268,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H268">
@@ -36558,7 +36559,7 @@
         <v/>
       </c>
       <c r="E269">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D269,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D269,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H269">
@@ -36578,7 +36579,7 @@
         <v/>
       </c>
       <c r="E270">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D270,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D270,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H270">
@@ -36598,7 +36599,7 @@
         <v/>
       </c>
       <c r="E271">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D271,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D271,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H271">
@@ -36618,7 +36619,7 @@
         <v/>
       </c>
       <c r="E272">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D272,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D272,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H272">
@@ -36638,7 +36639,7 @@
         <v/>
       </c>
       <c r="E273">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D273,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D273,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H273">
@@ -36658,7 +36659,7 @@
         <v/>
       </c>
       <c r="E274">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D274,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D274,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H274">
@@ -36678,7 +36679,7 @@
         <v/>
       </c>
       <c r="E275">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D275,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D275,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H275">
@@ -36698,7 +36699,7 @@
         <v/>
       </c>
       <c r="E276">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D276,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D276,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H276">
@@ -36718,7 +36719,7 @@
         <v/>
       </c>
       <c r="E277">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D277,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D277,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H277">
@@ -36738,7 +36739,7 @@
         <v/>
       </c>
       <c r="E278">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D278,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D278,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H278">
@@ -36758,7 +36759,7 @@
         <v/>
       </c>
       <c r="E279">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D279,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D279,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H279">
@@ -36778,7 +36779,7 @@
         <v/>
       </c>
       <c r="E280">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D280,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D280,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H280">
@@ -36798,7 +36799,7 @@
         <v/>
       </c>
       <c r="E281">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D281,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D281,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H281">
@@ -36818,7 +36819,7 @@
         <v/>
       </c>
       <c r="E282">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D282,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D282,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H282">
@@ -36838,7 +36839,7 @@
         <v/>
       </c>
       <c r="E283">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D283,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D283,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H283">
@@ -36858,7 +36859,7 @@
         <v/>
       </c>
       <c r="E284">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D284,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D284,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H284">
@@ -36878,7 +36879,7 @@
         <v/>
       </c>
       <c r="E285">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D285,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D285,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H285">
@@ -36898,7 +36899,7 @@
         <v/>
       </c>
       <c r="E286">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D286,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D286,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H286">
@@ -36918,7 +36919,7 @@
         <v/>
       </c>
       <c r="E287">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D287,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D287,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H287">
@@ -36938,7 +36939,7 @@
         <v/>
       </c>
       <c r="E288">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D288,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D288,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H288">
@@ -36958,7 +36959,7 @@
         <v/>
       </c>
       <c r="E289">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D289,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D289,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H289">
@@ -36978,7 +36979,7 @@
         <v/>
       </c>
       <c r="E290">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D290,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D290,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H290">
@@ -36998,7 +36999,7 @@
         <v/>
       </c>
       <c r="E291">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D291,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D291,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H291">
@@ -37018,7 +37019,7 @@
         <v/>
       </c>
       <c r="E292">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D292,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D292,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H292">
@@ -37038,7 +37039,7 @@
         <v/>
       </c>
       <c r="E293">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D293,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D293,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H293">
@@ -37058,7 +37059,7 @@
         <v/>
       </c>
       <c r="E294">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D294,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D294,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H294">
@@ -37078,7 +37079,7 @@
         <v/>
       </c>
       <c r="E295">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D295,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D295,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H295">
@@ -37098,7 +37099,7 @@
         <v/>
       </c>
       <c r="E296">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D296,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D296,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H296">
@@ -37118,7 +37119,7 @@
         <v/>
       </c>
       <c r="E297">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D297,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D297,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H297">
@@ -37138,7 +37139,7 @@
         <v/>
       </c>
       <c r="E298">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D298,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D298,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H298">
@@ -37158,7 +37159,7 @@
         <v/>
       </c>
       <c r="E299">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D299,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D299,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H299">
@@ -37178,7 +37179,7 @@
         <v/>
       </c>
       <c r="E300">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D300,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D300,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H300">
@@ -37198,7 +37199,7 @@
         <v/>
       </c>
       <c r="E301">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D301,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D301,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H301">
@@ -37218,7 +37219,7 @@
         <v/>
       </c>
       <c r="E302">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D302,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D302,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H302">
@@ -37238,7 +37239,7 @@
         <v/>
       </c>
       <c r="E303">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D303,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D303,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H303">
@@ -37258,7 +37259,7 @@
         <v/>
       </c>
       <c r="E304">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D304,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D304,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H304">
@@ -37278,7 +37279,7 @@
         <v/>
       </c>
       <c r="E305">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D305,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D305,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H305">
@@ -37298,7 +37299,7 @@
         <v/>
       </c>
       <c r="E306">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D306,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D306,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H306">
@@ -37318,7 +37319,7 @@
         <v/>
       </c>
       <c r="E307">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D307,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D307,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H307">
@@ -37338,7 +37339,7 @@
         <v/>
       </c>
       <c r="E308">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D308,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D308,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H308">
@@ -37358,7 +37359,7 @@
         <v/>
       </c>
       <c r="E309">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D309,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D309,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H309">
@@ -37378,7 +37379,7 @@
         <v/>
       </c>
       <c r="E310">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D310,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D310,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H310">
@@ -37398,7 +37399,7 @@
         <v/>
       </c>
       <c r="E311">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D311,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D311,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H311">
@@ -37418,7 +37419,7 @@
         <v/>
       </c>
       <c r="E312">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D312,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D312,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H312">
@@ -37438,7 +37439,7 @@
         <v/>
       </c>
       <c r="E313">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D313,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D313,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H313">
@@ -37458,7 +37459,7 @@
         <v/>
       </c>
       <c r="E314">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D314,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D314,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H314">
@@ -37478,7 +37479,7 @@
         <v/>
       </c>
       <c r="E315">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D315,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D315,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H315">
@@ -37498,7 +37499,7 @@
         <v/>
       </c>
       <c r="E316">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D316,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D316,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H316">
@@ -37518,7 +37519,7 @@
         <v/>
       </c>
       <c r="E317">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D317,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D317,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H317">
@@ -37538,7 +37539,7 @@
         <v/>
       </c>
       <c r="E318">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D318,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D318,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H318">
@@ -37558,7 +37559,7 @@
         <v/>
       </c>
       <c r="E319">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D319,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D319,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H319">
@@ -37578,7 +37579,7 @@
         <v/>
       </c>
       <c r="E320">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D320,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D320,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H320">
@@ -37598,7 +37599,7 @@
         <v/>
       </c>
       <c r="E321">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D321,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D321,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H321">
@@ -37618,7 +37619,7 @@
         <v/>
       </c>
       <c r="E322">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D322,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D322,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H322">
@@ -37638,7 +37639,7 @@
         <v/>
       </c>
       <c r="E323">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D323,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D323,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H323">
@@ -37658,7 +37659,7 @@
         <v/>
       </c>
       <c r="E324">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D324,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D324,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H324">
@@ -37678,7 +37679,7 @@
         <v/>
       </c>
       <c r="E325">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D325,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D325,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H325">
@@ -37698,7 +37699,7 @@
         <v/>
       </c>
       <c r="E326">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D326,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D326,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H326">
@@ -37718,7 +37719,7 @@
         <v/>
       </c>
       <c r="E327">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D327,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D327,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H327">
@@ -37738,7 +37739,7 @@
         <v/>
       </c>
       <c r="E328">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D328,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D328,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H328">
@@ -37758,7 +37759,7 @@
         <v/>
       </c>
       <c r="E329">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D329,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D329,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H329">
@@ -37778,7 +37779,7 @@
         <v/>
       </c>
       <c r="E330">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D330,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D330,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H330">
@@ -37798,7 +37799,7 @@
         <v/>
       </c>
       <c r="E331">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D331,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D331,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H331">
@@ -37818,7 +37819,7 @@
         <v/>
       </c>
       <c r="E332">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D332,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D332,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H332">
@@ -37838,7 +37839,7 @@
         <v/>
       </c>
       <c r="E333">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D333,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D333,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H333">
@@ -37858,7 +37859,7 @@
         <v/>
       </c>
       <c r="E334">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D334,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D334,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H334">
@@ -37878,7 +37879,7 @@
         <v/>
       </c>
       <c r="E335">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D335,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D335,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H335">
@@ -37898,7 +37899,7 @@
         <v/>
       </c>
       <c r="E336">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D336,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D336,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H336">
@@ -37918,7 +37919,7 @@
         <v/>
       </c>
       <c r="E337">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D337,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D337,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H337">
@@ -37938,7 +37939,7 @@
         <v/>
       </c>
       <c r="E338">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D338,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D338,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H338">
@@ -37958,7 +37959,7 @@
         <v/>
       </c>
       <c r="E339">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D339,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D339,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H339">
@@ -37978,7 +37979,7 @@
         <v/>
       </c>
       <c r="E340">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D340,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D340,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H340">
@@ -37998,7 +37999,7 @@
         <v/>
       </c>
       <c r="E341">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D341,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D341,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H341">
@@ -38018,7 +38019,7 @@
         <v/>
       </c>
       <c r="E342">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D342,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D342,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H342">
@@ -38038,7 +38039,7 @@
         <v/>
       </c>
       <c r="E343">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D343,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D343,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H343">
@@ -38058,7 +38059,7 @@
         <v/>
       </c>
       <c r="E344">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D344,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D344,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H344">
@@ -38078,7 +38079,7 @@
         <v/>
       </c>
       <c r="E345">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D345,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D345,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H345">
@@ -38098,7 +38099,7 @@
         <v/>
       </c>
       <c r="E346">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D346,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D346,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H346">
@@ -38118,7 +38119,7 @@
         <v/>
       </c>
       <c r="E347">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D347,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D347,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H347">
@@ -38138,7 +38139,7 @@
         <v/>
       </c>
       <c r="E348">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D348,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D348,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H348">
@@ -38158,7 +38159,7 @@
         <v/>
       </c>
       <c r="E349">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D349,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D349,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H349">
@@ -38178,7 +38179,7 @@
         <v/>
       </c>
       <c r="E350">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D350,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D350,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H350">
@@ -38198,7 +38199,7 @@
         <v/>
       </c>
       <c r="E351">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D351,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D351,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H351">
@@ -38218,7 +38219,7 @@
         <v/>
       </c>
       <c r="E352">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D352,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D352,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H352">
@@ -38238,7 +38239,7 @@
         <v/>
       </c>
       <c r="E353">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D353,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D353,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H353">
@@ -38258,7 +38259,7 @@
         <v/>
       </c>
       <c r="E354">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D354,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D354,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H354">
@@ -38278,7 +38279,7 @@
         <v/>
       </c>
       <c r="E355">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D355,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D355,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H355">
@@ -38298,7 +38299,7 @@
         <v/>
       </c>
       <c r="E356">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D356,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D356,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H356">
@@ -38318,7 +38319,7 @@
         <v/>
       </c>
       <c r="E357">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D357,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D357,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H357">
@@ -38338,7 +38339,7 @@
         <v/>
       </c>
       <c r="E358">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D358,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D358,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H358">
@@ -38358,7 +38359,7 @@
         <v/>
       </c>
       <c r="E359">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D359,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D359,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H359">
@@ -38378,7 +38379,7 @@
         <v/>
       </c>
       <c r="E360">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D360,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D360,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H360">
@@ -38398,7 +38399,7 @@
         <v/>
       </c>
       <c r="E361">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D361,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D361,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H361">
@@ -38418,7 +38419,7 @@
         <v/>
       </c>
       <c r="E362">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D362,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D362,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H362">
@@ -38438,7 +38439,7 @@
         <v/>
       </c>
       <c r="E363">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D363,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D363,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H363">
@@ -38458,7 +38459,7 @@
         <v/>
       </c>
       <c r="E364">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D364,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D364,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H364">
@@ -38478,7 +38479,7 @@
         <v/>
       </c>
       <c r="E365">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D365,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D365,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H365">
@@ -38498,7 +38499,7 @@
         <v/>
       </c>
       <c r="E366">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D366,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D366,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H366">
@@ -38518,7 +38519,7 @@
         <v/>
       </c>
       <c r="E367">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D367,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D367,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H367">
@@ -38538,7 +38539,7 @@
         <v/>
       </c>
       <c r="E368">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D368,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D368,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H368">
@@ -38558,7 +38559,7 @@
         <v/>
       </c>
       <c r="E369">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D369,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D369,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H369">
@@ -38578,7 +38579,7 @@
         <v/>
       </c>
       <c r="E370">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D370,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D370,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H370">
@@ -38598,7 +38599,7 @@
         <v/>
       </c>
       <c r="E371">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D371,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D371,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H371">
@@ -38618,7 +38619,7 @@
         <v/>
       </c>
       <c r="E372">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D372,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D372,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H372">
@@ -38638,7 +38639,7 @@
         <v/>
       </c>
       <c r="E373">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D373,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D373,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H373">
@@ -38658,7 +38659,7 @@
         <v/>
       </c>
       <c r="E374">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D374,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D374,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H374">
@@ -38678,7 +38679,7 @@
         <v/>
       </c>
       <c r="E375">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D375,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D375,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H375">
@@ -38698,7 +38699,7 @@
         <v/>
       </c>
       <c r="E376">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D376,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D376,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H376">
@@ -38718,7 +38719,7 @@
         <v/>
       </c>
       <c r="E377">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D377,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D377,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H377">
@@ -38738,7 +38739,7 @@
         <v/>
       </c>
       <c r="E378">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D378,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D378,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H378">
@@ -38758,7 +38759,7 @@
         <v/>
       </c>
       <c r="E379">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D379,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D379,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H379">
@@ -38778,7 +38779,7 @@
         <v/>
       </c>
       <c r="E380">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D380,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D380,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H380">
@@ -38798,7 +38799,7 @@
         <v/>
       </c>
       <c r="E381">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D381,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D381,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H381">
@@ -38818,7 +38819,7 @@
         <v/>
       </c>
       <c r="E382">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D382,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D382,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H382">
@@ -38838,7 +38839,7 @@
         <v/>
       </c>
       <c r="E383">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D383,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D383,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H383">
@@ -38858,7 +38859,7 @@
         <v/>
       </c>
       <c r="E384">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D384,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D384,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H384">
@@ -38878,7 +38879,7 @@
         <v/>
       </c>
       <c r="E385">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D385,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D385,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H385">
@@ -38898,7 +38899,7 @@
         <v/>
       </c>
       <c r="E386">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D386,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D386,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H386">
@@ -38918,7 +38919,7 @@
         <v/>
       </c>
       <c r="E387">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D387,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D387,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H387">
@@ -38938,7 +38939,7 @@
         <v/>
       </c>
       <c r="E388">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D388,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D388,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H388">
@@ -38958,7 +38959,7 @@
         <v/>
       </c>
       <c r="E389">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D389,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D389,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H389">
@@ -38978,7 +38979,7 @@
         <v/>
       </c>
       <c r="E390">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D390,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D390,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H390">
@@ -38998,7 +38999,7 @@
         <v/>
       </c>
       <c r="E391">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D391,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D391,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H391">
@@ -39018,7 +39019,7 @@
         <v/>
       </c>
       <c r="E392">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D392,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D392,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H392">
@@ -39038,7 +39039,7 @@
         <v/>
       </c>
       <c r="E393">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D393,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D393,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H393">
@@ -39058,7 +39059,7 @@
         <v/>
       </c>
       <c r="E394">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D394,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D394,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H394">
@@ -39078,7 +39079,7 @@
         <v/>
       </c>
       <c r="E395">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D395,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D395,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H395">
@@ -39098,7 +39099,7 @@
         <v/>
       </c>
       <c r="E396">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D396,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D396,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H396">
@@ -39118,7 +39119,7 @@
         <v/>
       </c>
       <c r="E397">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D397,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D397,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H397">
@@ -39138,7 +39139,7 @@
         <v/>
       </c>
       <c r="E398">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D398,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D398,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H398">
@@ -39158,7 +39159,7 @@
         <v/>
       </c>
       <c r="E399">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D399,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D399,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H399">
@@ -39178,7 +39179,7 @@
         <v/>
       </c>
       <c r="E400">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D400,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D400,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H400">
@@ -39198,7 +39199,7 @@
         <v/>
       </c>
       <c r="E401">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D401,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D401,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H401">
@@ -39218,7 +39219,7 @@
         <v/>
       </c>
       <c r="E402">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D402,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D402,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H402">
@@ -39238,7 +39239,7 @@
         <v/>
       </c>
       <c r="E403">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D403,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D403,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H403">
@@ -39258,7 +39259,7 @@
         <v/>
       </c>
       <c r="E404">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D404,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D404,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H404">
@@ -39278,7 +39279,7 @@
         <v/>
       </c>
       <c r="E405">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D405,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D405,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H405">
@@ -39298,7 +39299,7 @@
         <v/>
       </c>
       <c r="E406">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D406,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D406,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H406">
@@ -39318,7 +39319,7 @@
         <v/>
       </c>
       <c r="E407">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D407,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D407,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H407">
@@ -39338,7 +39339,7 @@
         <v/>
       </c>
       <c r="E408">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D408,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D408,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H408">
@@ -39358,7 +39359,7 @@
         <v/>
       </c>
       <c r="E409">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D409,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D409,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H409">
@@ -39378,7 +39379,7 @@
         <v/>
       </c>
       <c r="E410">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D410,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D410,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H410">
@@ -39398,7 +39399,7 @@
         <v/>
       </c>
       <c r="E411">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D411,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D411,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H411">
@@ -39418,7 +39419,7 @@
         <v/>
       </c>
       <c r="E412">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D412,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D412,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H412">
@@ -39438,7 +39439,7 @@
         <v/>
       </c>
       <c r="E413">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D413,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D413,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H413">
@@ -39458,7 +39459,7 @@
         <v/>
       </c>
       <c r="E414">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D414,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D414,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H414">
@@ -39478,7 +39479,7 @@
         <v/>
       </c>
       <c r="E415">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D415,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D415,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H415">
@@ -39498,7 +39499,7 @@
         <v/>
       </c>
       <c r="E416">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D416,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D416,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H416">
@@ -39518,7 +39519,7 @@
         <v/>
       </c>
       <c r="E417">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D417,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D417,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H417">
@@ -39538,7 +39539,7 @@
         <v/>
       </c>
       <c r="E418">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D418,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D418,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H418">
@@ -39558,7 +39559,7 @@
         <v/>
       </c>
       <c r="E419">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D419,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D419,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H419">
@@ -39578,7 +39579,7 @@
         <v/>
       </c>
       <c r="E420">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D420,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D420,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H420">
@@ -39598,7 +39599,7 @@
         <v/>
       </c>
       <c r="E421">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D421,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D421,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H421">
@@ -39618,7 +39619,7 @@
         <v/>
       </c>
       <c r="E422">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D422,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D422,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H422">
@@ -39638,7 +39639,7 @@
         <v/>
       </c>
       <c r="E423">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D423,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D423,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H423">
@@ -39658,7 +39659,7 @@
         <v/>
       </c>
       <c r="E424">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D424,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D424,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H424">
@@ -39678,7 +39679,7 @@
         <v/>
       </c>
       <c r="E425">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D425,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D425,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H425">
@@ -39698,7 +39699,7 @@
         <v/>
       </c>
       <c r="E426">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D426,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D426,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H426">
@@ -39718,7 +39719,7 @@
         <v/>
       </c>
       <c r="E427">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D427,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D427,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H427">
@@ -39738,7 +39739,7 @@
         <v/>
       </c>
       <c r="E428">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D428,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D428,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H428">
@@ -39758,7 +39759,7 @@
         <v/>
       </c>
       <c r="E429">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D429,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D429,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H429">
@@ -39778,7 +39779,7 @@
         <v/>
       </c>
       <c r="E430">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D430,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D430,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H430">
@@ -39798,7 +39799,7 @@
         <v/>
       </c>
       <c r="E431">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D431,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D431,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H431">
@@ -39818,7 +39819,7 @@
         <v/>
       </c>
       <c r="E432">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D432,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D432,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H432">
@@ -39838,7 +39839,7 @@
         <v/>
       </c>
       <c r="E433">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D433,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D433,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H433">
@@ -39858,7 +39859,7 @@
         <v/>
       </c>
       <c r="E434">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D434,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D434,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H434">
@@ -39878,7 +39879,7 @@
         <v/>
       </c>
       <c r="E435">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D435,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D435,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H435">
@@ -39898,7 +39899,7 @@
         <v/>
       </c>
       <c r="E436">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D436,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D436,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H436">
@@ -39918,7 +39919,7 @@
         <v/>
       </c>
       <c r="E437">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D437,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D437,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H437">
@@ -39938,7 +39939,7 @@
         <v/>
       </c>
       <c r="E438">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D438,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D438,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H438">
@@ -39958,7 +39959,7 @@
         <v/>
       </c>
       <c r="E439">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D439,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D439,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H439">
@@ -39978,7 +39979,7 @@
         <v/>
       </c>
       <c r="E440">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D440,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D440,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H440">
@@ -39998,7 +39999,7 @@
         <v/>
       </c>
       <c r="E441">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D441,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D441,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H441">
@@ -40018,7 +40019,7 @@
         <v/>
       </c>
       <c r="E442">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D442,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D442,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H442">
@@ -40038,7 +40039,7 @@
         <v/>
       </c>
       <c r="E443">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D443,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D443,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H443">
@@ -40058,7 +40059,7 @@
         <v/>
       </c>
       <c r="E444">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D444,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D444,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H444">
@@ -40078,7 +40079,7 @@
         <v/>
       </c>
       <c r="E445">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D445,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D445,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H445">
@@ -40098,7 +40099,7 @@
         <v/>
       </c>
       <c r="E446">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D446,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D446,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H446">
@@ -40118,7 +40119,7 @@
         <v/>
       </c>
       <c r="E447">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D447,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D447,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H447">
@@ -40138,7 +40139,7 @@
         <v/>
       </c>
       <c r="E448">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D448,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D448,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H448">
@@ -40158,7 +40159,7 @@
         <v/>
       </c>
       <c r="E449">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D449,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D449,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H449">
@@ -40178,7 +40179,7 @@
         <v/>
       </c>
       <c r="E450">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D450,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D450,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H450">
@@ -40198,7 +40199,7 @@
         <v/>
       </c>
       <c r="E451">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D451,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D451,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H451">
@@ -40218,7 +40219,7 @@
         <v/>
       </c>
       <c r="E452">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D452,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D452,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H452">
@@ -40238,7 +40239,7 @@
         <v/>
       </c>
       <c r="E453">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D453,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D453,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H453">
@@ -40258,7 +40259,7 @@
         <v/>
       </c>
       <c r="E454">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D454,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D454,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H454">
@@ -40278,7 +40279,7 @@
         <v/>
       </c>
       <c r="E455">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D455,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D455,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H455">
@@ -40298,7 +40299,7 @@
         <v/>
       </c>
       <c r="E456">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D456,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D456,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H456">
@@ -40318,7 +40319,7 @@
         <v/>
       </c>
       <c r="E457">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D457,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D457,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H457">
@@ -40338,7 +40339,7 @@
         <v/>
       </c>
       <c r="E458">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D458,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D458,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H458">
@@ -40358,7 +40359,7 @@
         <v/>
       </c>
       <c r="E459">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D459,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D459,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H459">
@@ -40378,7 +40379,7 @@
         <v/>
       </c>
       <c r="E460">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D460,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D460,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H460">
@@ -40398,7 +40399,7 @@
         <v/>
       </c>
       <c r="E461">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D461,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D461,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H461">
@@ -40418,7 +40419,7 @@
         <v/>
       </c>
       <c r="E462">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D462,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D462,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H462">
@@ -40438,7 +40439,7 @@
         <v/>
       </c>
       <c r="E463">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D463,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D463,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H463">
@@ -40458,7 +40459,7 @@
         <v/>
       </c>
       <c r="E464">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D464,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D464,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H464">
@@ -40478,7 +40479,7 @@
         <v/>
       </c>
       <c r="E465">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D465,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D465,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H465">
@@ -40498,7 +40499,7 @@
         <v/>
       </c>
       <c r="E466">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D466,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D466,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H466">
@@ -40518,7 +40519,7 @@
         <v/>
       </c>
       <c r="E467">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D467,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D467,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H467">
@@ -40538,7 +40539,7 @@
         <v/>
       </c>
       <c r="E468">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D468,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D468,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H468">
@@ -40558,7 +40559,7 @@
         <v/>
       </c>
       <c r="E469">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D469,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D469,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H469">
@@ -40578,7 +40579,7 @@
         <v/>
       </c>
       <c r="E470">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D470,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D470,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H470">
@@ -40598,7 +40599,7 @@
         <v/>
       </c>
       <c r="E471">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D471,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D471,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H471">
@@ -40618,7 +40619,7 @@
         <v/>
       </c>
       <c r="E472">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D472,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D472,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H472">
@@ -40638,7 +40639,7 @@
         <v/>
       </c>
       <c r="E473">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D473,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D473,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H473">
@@ -40658,7 +40659,7 @@
         <v/>
       </c>
       <c r="E474">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D474,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D474,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H474">
@@ -40678,7 +40679,7 @@
         <v/>
       </c>
       <c r="E475">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D475,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D475,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H475">
@@ -40698,7 +40699,7 @@
         <v/>
       </c>
       <c r="E476">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D476,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D476,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H476">
@@ -40718,7 +40719,7 @@
         <v/>
       </c>
       <c r="E477">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D477,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D477,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H477">
@@ -40738,7 +40739,7 @@
         <v/>
       </c>
       <c r="E478">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D478,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D478,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H478">
@@ -40758,7 +40759,7 @@
         <v/>
       </c>
       <c r="E479">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D479,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D479,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H479">
@@ -40778,7 +40779,7 @@
         <v/>
       </c>
       <c r="E480">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D480,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D480,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H480">
@@ -40798,7 +40799,7 @@
         <v/>
       </c>
       <c r="E481">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D481,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D481,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H481">
@@ -40818,7 +40819,7 @@
         <v/>
       </c>
       <c r="E482">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D482,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D482,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H482">
@@ -40838,7 +40839,7 @@
         <v/>
       </c>
       <c r="E483">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D483,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D483,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H483">
@@ -40858,7 +40859,7 @@
         <v/>
       </c>
       <c r="E484">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D484,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D484,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H484">
@@ -40878,7 +40879,7 @@
         <v/>
       </c>
       <c r="E485">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D485,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D485,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H485">
@@ -40898,7 +40899,7 @@
         <v/>
       </c>
       <c r="E486">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D486,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D486,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H486">
@@ -40918,7 +40919,7 @@
         <v/>
       </c>
       <c r="E487">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D487,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D487,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H487">
@@ -40938,7 +40939,7 @@
         <v/>
       </c>
       <c r="E488">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D488,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D488,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H488">
@@ -40958,7 +40959,7 @@
         <v/>
       </c>
       <c r="E489">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D489,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D489,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H489">
@@ -40978,7 +40979,7 @@
         <v/>
       </c>
       <c r="E490">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D490,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D490,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H490">
@@ -40998,7 +40999,7 @@
         <v/>
       </c>
       <c r="E491">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D491,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D491,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H491">
@@ -41018,7 +41019,7 @@
         <v/>
       </c>
       <c r="E492">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D492,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D492,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H492">
@@ -41038,7 +41039,7 @@
         <v/>
       </c>
       <c r="E493">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D493,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D493,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H493">
@@ -41058,7 +41059,7 @@
         <v/>
       </c>
       <c r="E494">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D494,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D494,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H494">
@@ -41078,7 +41079,7 @@
         <v/>
       </c>
       <c r="E495">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D495,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D495,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H495">
@@ -41098,7 +41099,7 @@
         <v/>
       </c>
       <c r="E496">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D496,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D496,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H496">
@@ -41118,7 +41119,7 @@
         <v/>
       </c>
       <c r="E497">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D497,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D497,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H497">
@@ -41138,7 +41139,7 @@
         <v/>
       </c>
       <c r="E498">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D498,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D498,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H498">
@@ -41158,7 +41159,7 @@
         <v/>
       </c>
       <c r="E499">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D499,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D499,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H499">
@@ -41178,7 +41179,7 @@
         <v/>
       </c>
       <c r="E500">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D500,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D500,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H500">
@@ -41198,7 +41199,7 @@
         <v/>
       </c>
       <c r="E501">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D501,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D501,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H501">
@@ -41218,7 +41219,7 @@
         <v/>
       </c>
       <c r="E502">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D502,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D502,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H502">
@@ -41238,7 +41239,7 @@
         <v/>
       </c>
       <c r="E503">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D503,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D503,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H503">
@@ -41258,7 +41259,7 @@
         <v/>
       </c>
       <c r="E504">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D504,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D504,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H504">
@@ -41278,7 +41279,7 @@
         <v/>
       </c>
       <c r="E505">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D505,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D505,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H505">
@@ -41298,7 +41299,7 @@
         <v/>
       </c>
       <c r="E506">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D506,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D506,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H506">
@@ -41318,7 +41319,7 @@
         <v/>
       </c>
       <c r="E507">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D507,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D507,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H507">
@@ -41338,7 +41339,7 @@
         <v/>
       </c>
       <c r="E508">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D508,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D508,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H508">
@@ -41358,7 +41359,7 @@
         <v/>
       </c>
       <c r="E509">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D509,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D509,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H509">
@@ -41378,7 +41379,7 @@
         <v/>
       </c>
       <c r="E510">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D510,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D510,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H510">
@@ -41398,7 +41399,7 @@
         <v/>
       </c>
       <c r="E511">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D511,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D511,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H511">
@@ -41418,7 +41419,7 @@
         <v/>
       </c>
       <c r="E512">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D512,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D512,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H512">
@@ -41438,7 +41439,7 @@
         <v/>
       </c>
       <c r="E513">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D513,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D513,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H513">
@@ -41458,7 +41459,7 @@
         <v/>
       </c>
       <c r="E514">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D514,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D514,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H514">
@@ -41478,7 +41479,7 @@
         <v/>
       </c>
       <c r="E515">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D515,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D515,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H515">
@@ -41498,7 +41499,7 @@
         <v/>
       </c>
       <c r="E516">
-        <f>IFERROR(INDEX(Dim_Category[CategoryName],MATCH(INDEX(Dim_Vendor[DefaultCategoryID],MATCH($D516,Dim_Vendor[VendorName],0)),Dim_Category[CategoryID],0)),"")</f>
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D516,Dim_Vendor[VendorName],0)),"")</f>
         <v/>
       </c>
       <c r="H516">
@@ -43992,9 +43993,10 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col hidden="1" width="18" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col hidden="1" width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -44020,13 +44022,14 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>Dim_Vendor  —  add a row here to make a new vendor available in Expenses</t>
+          <t>Dim_Vendor  —  add a row to make a new vendor available in Expenses; set/edit DefaultCategory (dropdown) so Bank Import can auto-suggest a category</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
       <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="36" t="inlineStr">
@@ -44041,15 +44044,20 @@
       </c>
       <c r="C5" s="36" t="inlineStr">
         <is>
+          <t>DefaultCategory</t>
+        </is>
+      </c>
+      <c r="D5" s="36" t="inlineStr">
+        <is>
           <t>DefaultCategoryID</t>
         </is>
       </c>
-      <c r="D5" s="36" t="inlineStr">
+      <c r="E5" s="36" t="inlineStr">
         <is>
           <t>CurMonthSpend</t>
         </is>
       </c>
-      <c r="E5" s="36" t="inlineStr">
+      <c r="F5" s="36" t="inlineStr">
         <is>
           <t>YTDSpend</t>
         </is>
@@ -44065,11 +44073,15 @@
         </is>
       </c>
       <c r="C6" s="38" t="n"/>
-      <c r="D6" s="39">
+      <c r="D6" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C6,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E6" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B6,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B6,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E6" s="39">
+      <c r="F6" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B6,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B6,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -44084,11 +44096,15 @@
         </is>
       </c>
       <c r="C7" s="38" t="n"/>
-      <c r="D7" s="39">
+      <c r="D7" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C7,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B7,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B7,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E7" s="39">
+      <c r="F7" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B7,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B7,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -44103,11 +44119,15 @@
         </is>
       </c>
       <c r="C8" s="38" t="n"/>
-      <c r="D8" s="39">
+      <c r="D8" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C8,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E8" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B8,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B8,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E8" s="39">
+      <c r="F8" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B8,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B8,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -44121,14 +44141,20 @@
           <t>AMAZON</t>
         </is>
       </c>
-      <c r="C9" s="38" t="n">
-        <v>20</v>
-      </c>
-      <c r="D9" s="39">
+      <c r="C9" s="38" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="D9" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C9,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E9" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B9,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B9,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E9" s="39">
+      <c r="F9" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B9,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B9,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -44142,14 +44168,20 @@
           <t>AMAZON PRIME</t>
         </is>
       </c>
-      <c r="C10" s="38" t="n">
-        <v>20</v>
-      </c>
-      <c r="D10" s="39">
+      <c r="C10" s="38" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="D10" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C10,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B10,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B10,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E10" s="39">
+      <c r="F10" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B10,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B10,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -44163,14 +44195,20 @@
           <t>ASI / PROGRESSIVE INSURANCE</t>
         </is>
       </c>
-      <c r="C11" s="38" t="n">
-        <v>6</v>
-      </c>
-      <c r="D11" s="39">
+      <c r="C11" s="38" t="inlineStr">
+        <is>
+          <t>Insurance Car</t>
+        </is>
+      </c>
+      <c r="D11" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C11,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E11" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B11,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B11,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E11" s="39">
+      <c r="F11" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B11,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B11,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -44184,14 +44222,20 @@
           <t>BABY DREAMS</t>
         </is>
       </c>
-      <c r="C12" s="38" t="n">
-        <v>16</v>
-      </c>
-      <c r="D12" s="39">
+      <c r="C12" s="38" t="inlineStr">
+        <is>
+          <t>Kid's Accessories</t>
+        </is>
+      </c>
+      <c r="D12" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C12,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B12,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B12,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E12" s="39">
+      <c r="F12" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B12,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B12,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -44205,14 +44249,20 @@
           <t>BAIS HASFORIM</t>
         </is>
       </c>
-      <c r="C13" s="38" t="n">
-        <v>23</v>
-      </c>
-      <c r="D13" s="39">
+      <c r="C13" s="38" t="inlineStr">
+        <is>
+          <t>Books</t>
+        </is>
+      </c>
+      <c r="D13" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C13,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E13" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B13,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B13,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E13" s="39">
+      <c r="F13" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B13,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B13,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -44227,11 +44277,15 @@
         </is>
       </c>
       <c r="C14" s="38" t="n"/>
-      <c r="D14" s="39">
+      <c r="D14" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C14,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B14,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B14,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E14" s="39">
+      <c r="F14" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B14,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B14,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -44245,14 +44299,20 @@
           <t>BINGO WHOLESALE</t>
         </is>
       </c>
-      <c r="C15" s="38" t="n">
-        <v>8</v>
-      </c>
-      <c r="D15" s="39">
+      <c r="C15" s="38" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="D15" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C15,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E15" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B15,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B15,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E15" s="39">
+      <c r="F15" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B15,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B15,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -44267,11 +44327,15 @@
         </is>
       </c>
       <c r="C16" s="38" t="n"/>
-      <c r="D16" s="39">
+      <c r="D16" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C16,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B16,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B16,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E16" s="39">
+      <c r="F16" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B16,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B16,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -44285,14 +44349,20 @@
           <t>CAFE CHOCOLAT</t>
         </is>
       </c>
-      <c r="C17" s="38" t="n">
-        <v>9</v>
-      </c>
-      <c r="D17" s="39">
+      <c r="C17" s="38" t="inlineStr">
+        <is>
+          <t>Dining &amp; Restaurants</t>
+        </is>
+      </c>
+      <c r="D17" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C17,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E17" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B17,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B17,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E17" s="39">
+      <c r="F17" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B17,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B17,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -44306,14 +44376,20 @@
           <t>CAFE CORNER</t>
         </is>
       </c>
-      <c r="C18" s="38" t="n">
-        <v>9</v>
-      </c>
-      <c r="D18" s="39">
+      <c r="C18" s="38" t="inlineStr">
+        <is>
+          <t>Dining &amp; Restaurants</t>
+        </is>
+      </c>
+      <c r="D18" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C18,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E18" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B18,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B18,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E18" s="39">
+      <c r="F18" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B18,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B18,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -44327,14 +44403,20 @@
           <t>CELL 2 GET</t>
         </is>
       </c>
-      <c r="C19" s="38" t="n">
-        <v>2</v>
-      </c>
-      <c r="D19" s="39">
+      <c r="C19" s="38" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="D19" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C19,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E19" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B19,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B19,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E19" s="39">
+      <c r="F19" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B19,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B19,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -44349,11 +44431,15 @@
         </is>
       </c>
       <c r="C20" s="38" t="n"/>
-      <c r="D20" s="39">
+      <c r="D20" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C20,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E20" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B20,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B20,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E20" s="39">
+      <c r="F20" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B20,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B20,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -44367,14 +44453,20 @@
           <t>CHURRASKO GRILL</t>
         </is>
       </c>
-      <c r="C21" s="38" t="n">
-        <v>9</v>
-      </c>
-      <c r="D21" s="39">
+      <c r="C21" s="38" t="inlineStr">
+        <is>
+          <t>Dining &amp; Restaurants</t>
+        </is>
+      </c>
+      <c r="D21" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C21,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E21" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B21,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B21,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E21" s="39">
+      <c r="F21" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B21,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B21,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -44388,14 +44480,20 @@
           <t>CLAIRE'S</t>
         </is>
       </c>
-      <c r="C22" s="38" t="n">
-        <v>16</v>
-      </c>
-      <c r="D22" s="39">
+      <c r="C22" s="38" t="inlineStr">
+        <is>
+          <t>Kid's Accessories</t>
+        </is>
+      </c>
+      <c r="D22" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C22,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E22" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B22,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B22,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E22" s="39">
+      <c r="F22" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B22,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B22,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -44410,11 +44508,15 @@
         </is>
       </c>
       <c r="C23" s="38" t="n"/>
-      <c r="D23" s="39">
+      <c r="D23" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C23,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E23" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B23,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B23,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E23" s="39">
+      <c r="F23" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B23,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B23,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -44429,11 +44531,15 @@
         </is>
       </c>
       <c r="C24" s="38" t="n"/>
-      <c r="D24" s="39">
+      <c r="D24" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C24,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E24" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B24,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B24,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E24" s="39">
+      <c r="F24" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B24,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B24,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -44448,11 +44554,15 @@
         </is>
       </c>
       <c r="C25" s="38" t="n"/>
-      <c r="D25" s="39">
+      <c r="D25" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C25,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E25" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B25,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B25,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E25" s="39">
+      <c r="F25" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B25,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B25,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -44467,11 +44577,15 @@
         </is>
       </c>
       <c r="C26" s="38" t="n"/>
-      <c r="D26" s="39">
+      <c r="D26" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C26,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E26" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B26,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B26,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E26" s="39">
+      <c r="F26" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B26,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B26,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -44486,11 +44600,15 @@
         </is>
       </c>
       <c r="C27" s="38" t="n"/>
-      <c r="D27" s="39">
+      <c r="D27" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C27,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E27" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B27,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B27,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E27" s="39">
+      <c r="F27" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B27,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B27,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -44505,11 +44623,15 @@
         </is>
       </c>
       <c r="C28" s="38" t="n"/>
-      <c r="D28" s="39">
+      <c r="D28" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C28,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E28" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B28,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B28,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E28" s="39">
+      <c r="F28" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B28,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B28,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -44524,11 +44646,15 @@
         </is>
       </c>
       <c r="C29" s="38" t="n"/>
-      <c r="D29" s="39">
+      <c r="D29" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C29,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E29" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B29,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B29,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E29" s="39">
+      <c r="F29" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B29,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B29,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -44542,14 +44668,20 @@
           <t>COSTUME CENTRAL</t>
         </is>
       </c>
-      <c r="C30" s="38" t="n">
-        <v>18</v>
-      </c>
-      <c r="D30" s="39">
+      <c r="C30" s="38" t="inlineStr">
+        <is>
+          <t>Toys</t>
+        </is>
+      </c>
+      <c r="D30" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C30,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E30" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B30,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B30,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E30" s="39">
+      <c r="F30" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B30,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B30,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -44563,14 +44695,20 @@
           <t>CROSSROADS WINE &amp; SPIRITS</t>
         </is>
       </c>
-      <c r="C31" s="38" t="n">
-        <v>11</v>
-      </c>
-      <c r="D31" s="39">
+      <c r="C31" s="38" t="inlineStr">
+        <is>
+          <t>Entertainment</t>
+        </is>
+      </c>
+      <c r="D31" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C31,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E31" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B31,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B31,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E31" s="39">
+      <c r="F31" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B31,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B31,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -44584,14 +44722,20 @@
           <t>CVS PHARMACY</t>
         </is>
       </c>
-      <c r="C32" s="38" t="n">
-        <v>10</v>
-      </c>
-      <c r="D32" s="39">
+      <c r="C32" s="38" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D32" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C32,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E32" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B32,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B32,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E32" s="39">
+      <c r="F32" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B32,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B32,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -44605,14 +44749,20 @@
           <t>DAVE &amp; BUSTERS</t>
         </is>
       </c>
-      <c r="C33" s="38" t="n">
-        <v>11</v>
-      </c>
-      <c r="D33" s="39">
+      <c r="C33" s="38" t="inlineStr">
+        <is>
+          <t>Entertainment</t>
+        </is>
+      </c>
+      <c r="D33" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C33,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E33" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B33,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B33,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E33" s="39">
+      <c r="F33" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B33,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B33,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -44627,11 +44777,15 @@
         </is>
       </c>
       <c r="C34" s="38" t="n"/>
-      <c r="D34" s="39">
+      <c r="D34" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C34,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E34" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B34,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B34,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E34" s="39">
+      <c r="F34" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B34,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B34,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -44646,11 +44800,15 @@
         </is>
       </c>
       <c r="C35" s="38" t="n"/>
-      <c r="D35" s="39">
+      <c r="D35" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C35,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E35" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B35,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B35,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E35" s="39">
+      <c r="F35" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B35,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B35,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -44664,14 +44822,20 @@
           <t>DSW</t>
         </is>
       </c>
-      <c r="C36" s="38" t="n">
-        <v>14</v>
-      </c>
-      <c r="D36" s="39">
+      <c r="C36" s="38" t="inlineStr">
+        <is>
+          <t>Women's Clothing</t>
+        </is>
+      </c>
+      <c r="D36" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C36,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E36" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B36,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B36,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E36" s="39">
+      <c r="F36" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B36,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B36,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -44686,11 +44850,15 @@
         </is>
       </c>
       <c r="C37" s="38" t="n"/>
-      <c r="D37" s="39">
+      <c r="D37" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C37,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E37" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B37,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B37,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E37" s="39">
+      <c r="F37" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B37,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B37,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -44705,11 +44873,15 @@
         </is>
       </c>
       <c r="C38" s="38" t="n"/>
-      <c r="D38" s="39">
+      <c r="D38" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C38,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E38" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B38,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B38,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E38" s="39">
+      <c r="F38" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B38,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B38,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -44723,14 +44895,20 @@
           <t>EVERGREEN KOSHER MARKET</t>
         </is>
       </c>
-      <c r="C39" s="38" t="n">
-        <v>8</v>
-      </c>
-      <c r="D39" s="39">
+      <c r="C39" s="38" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="D39" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C39,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E39" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B39,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B39,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E39" s="39">
+      <c r="F39" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B39,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B39,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -44744,14 +44922,20 @@
           <t>EXXON GAS</t>
         </is>
       </c>
-      <c r="C40" s="38" t="n">
-        <v>7</v>
-      </c>
-      <c r="D40" s="39">
+      <c r="C40" s="38" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="D40" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C40,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E40" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B40,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B40,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E40" s="39">
+      <c r="F40" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B40,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B40,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -44765,14 +44949,20 @@
           <t>E-Z PASS</t>
         </is>
       </c>
-      <c r="C41" s="38" t="n">
-        <v>5</v>
-      </c>
-      <c r="D41" s="39">
+      <c r="C41" s="38" t="inlineStr">
+        <is>
+          <t>Car Expenses</t>
+        </is>
+      </c>
+      <c r="D41" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C41,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E41" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B41,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B41,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E41" s="39">
+      <c r="F41" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B41,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B41,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -44787,11 +44977,15 @@
         </is>
       </c>
       <c r="C42" s="38" t="n"/>
-      <c r="D42" s="39">
+      <c r="D42" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C42,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E42" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B42,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B42,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E42" s="39">
+      <c r="F42" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B42,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B42,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -44806,11 +45000,15 @@
         </is>
       </c>
       <c r="C43" s="38" t="n"/>
-      <c r="D43" s="39">
+      <c r="D43" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C43,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E43" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B43,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B43,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E43" s="39">
+      <c r="F43" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B43,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B43,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -44824,14 +45022,20 @@
           <t>FIVE BELOW</t>
         </is>
       </c>
-      <c r="C44" s="38" t="n">
-        <v>18</v>
-      </c>
-      <c r="D44" s="39">
+      <c r="C44" s="38" t="inlineStr">
+        <is>
+          <t>Toys</t>
+        </is>
+      </c>
+      <c r="D44" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C44,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E44" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B44,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B44,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E44" s="39">
+      <c r="F44" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B44,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B44,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -44846,11 +45050,15 @@
         </is>
       </c>
       <c r="C45" s="38" t="n"/>
-      <c r="D45" s="39">
+      <c r="D45" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C45,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E45" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B45,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B45,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E45" s="39">
+      <c r="F45" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B45,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B45,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -44864,14 +45072,20 @@
           <t>FRANKEL'S DESIGNER SHOES</t>
         </is>
       </c>
-      <c r="C46" s="38" t="n">
-        <v>14</v>
-      </c>
-      <c r="D46" s="39">
+      <c r="C46" s="38" t="inlineStr">
+        <is>
+          <t>Women's Clothing</t>
+        </is>
+      </c>
+      <c r="D46" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C46,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E46" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B46,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B46,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E46" s="39">
+      <c r="F46" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B46,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B46,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -44885,14 +45099,20 @@
           <t>GEICO</t>
         </is>
       </c>
-      <c r="C47" s="38" t="n">
-        <v>6</v>
-      </c>
-      <c r="D47" s="39">
+      <c r="C47" s="38" t="inlineStr">
+        <is>
+          <t>Insurance Car</t>
+        </is>
+      </c>
+      <c r="D47" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C47,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E47" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B47,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B47,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E47" s="39">
+      <c r="F47" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B47,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B47,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -44907,11 +45127,15 @@
         </is>
       </c>
       <c r="C48" s="38" t="n"/>
-      <c r="D48" s="39">
+      <c r="D48" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C48,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E48" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B48,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B48,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E48" s="39">
+      <c r="F48" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B48,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B48,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -44925,14 +45149,20 @@
           <t>GRAPE WINE &amp; SPIRIT</t>
         </is>
       </c>
-      <c r="C49" s="38" t="n">
-        <v>11</v>
-      </c>
-      <c r="D49" s="39">
+      <c r="C49" s="38" t="inlineStr">
+        <is>
+          <t>Entertainment</t>
+        </is>
+      </c>
+      <c r="D49" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C49,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E49" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B49,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B49,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E49" s="39">
+      <c r="F49" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B49,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B49,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -44946,14 +45176,20 @@
           <t>H&amp;M</t>
         </is>
       </c>
-      <c r="C50" s="38" t="n">
-        <v>14</v>
-      </c>
-      <c r="D50" s="39">
+      <c r="C50" s="38" t="inlineStr">
+        <is>
+          <t>Women's Clothing</t>
+        </is>
+      </c>
+      <c r="D50" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C50,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E50" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B50,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B50,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E50" s="39">
+      <c r="F50" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B50,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B50,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -44967,14 +45203,20 @@
           <t>HAVA JAVA</t>
         </is>
       </c>
-      <c r="C51" s="38" t="n">
-        <v>9</v>
-      </c>
-      <c r="D51" s="39">
+      <c r="C51" s="38" t="inlineStr">
+        <is>
+          <t>Dining &amp; Restaurants</t>
+        </is>
+      </c>
+      <c r="D51" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C51,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E51" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B51,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B51,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E51" s="39">
+      <c r="F51" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B51,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B51,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -44988,14 +45230,20 @@
           <t>HEAVEN SCENT</t>
         </is>
       </c>
-      <c r="C52" s="38" t="n">
-        <v>17</v>
-      </c>
-      <c r="D52" s="39">
+      <c r="C52" s="38" t="inlineStr">
+        <is>
+          <t>Gifts</t>
+        </is>
+      </c>
+      <c r="D52" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C52,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E52" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B52,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B52,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E52" s="39">
+      <c r="F52" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B52,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B52,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -45010,11 +45258,15 @@
         </is>
       </c>
       <c r="C53" s="38" t="n"/>
-      <c r="D53" s="39">
+      <c r="D53" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C53,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E53" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B53,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B53,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E53" s="39">
+      <c r="F53" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B53,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B53,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -45029,11 +45281,15 @@
         </is>
       </c>
       <c r="C54" s="38" t="n"/>
-      <c r="D54" s="39">
+      <c r="D54" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C54,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E54" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B54,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B54,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E54" s="39">
+      <c r="F54" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B54,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B54,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -45048,11 +45304,15 @@
         </is>
       </c>
       <c r="C55" s="38" t="n"/>
-      <c r="D55" s="39">
+      <c r="D55" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C55,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E55" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B55,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B55,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E55" s="39">
+      <c r="F55" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B55,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B55,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -45066,14 +45326,20 @@
           <t>INVITE WITH CLASS</t>
         </is>
       </c>
-      <c r="C56" s="38" t="n">
-        <v>17</v>
-      </c>
-      <c r="D56" s="39">
+      <c r="C56" s="38" t="inlineStr">
+        <is>
+          <t>Gifts</t>
+        </is>
+      </c>
+      <c r="D56" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C56,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E56" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B56,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B56,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E56" s="39">
+      <c r="F56" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B56,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B56,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -45087,14 +45353,20 @@
           <t>IRS</t>
         </is>
       </c>
-      <c r="C57" s="38" t="n">
-        <v>25</v>
-      </c>
-      <c r="D57" s="39">
+      <c r="C57" s="38" t="inlineStr">
+        <is>
+          <t>Taxes</t>
+        </is>
+      </c>
+      <c r="D57" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C57,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E57" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B57,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B57,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E57" s="39">
+      <c r="F57" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B57,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B57,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -45108,14 +45380,20 @@
           <t>JOSEPH DANITTI - CUFF &amp; CO</t>
         </is>
       </c>
-      <c r="C58" s="38" t="n">
-        <v>17</v>
-      </c>
-      <c r="D58" s="39">
+      <c r="C58" s="38" t="inlineStr">
+        <is>
+          <t>Gifts</t>
+        </is>
+      </c>
+      <c r="D58" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C58,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E58" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B58,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B58,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E58" s="39">
+      <c r="F58" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B58,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B58,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -45130,11 +45408,15 @@
         </is>
       </c>
       <c r="C59" s="38" t="n"/>
-      <c r="D59" s="39">
+      <c r="D59" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C59,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E59" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B59,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B59,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E59" s="39">
+      <c r="F59" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B59,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B59,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -45149,11 +45431,15 @@
         </is>
       </c>
       <c r="C60" s="38" t="n"/>
-      <c r="D60" s="39">
+      <c r="D60" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C60,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E60" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B60,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B60,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E60" s="39">
+      <c r="F60" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B60,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B60,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -45167,14 +45453,20 @@
           <t>KIDICHIC</t>
         </is>
       </c>
-      <c r="C61" s="38" t="n">
-        <v>15</v>
-      </c>
-      <c r="D61" s="39">
+      <c r="C61" s="38" t="inlineStr">
+        <is>
+          <t>Kid's Clothing</t>
+        </is>
+      </c>
+      <c r="D61" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C61,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E61" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B61,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B61,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E61" s="39">
+      <c r="F61" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B61,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B61,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -45188,14 +45480,20 @@
           <t>KIDS FIRST PEO</t>
         </is>
       </c>
-      <c r="C62" s="38" t="n">
-        <v>10</v>
-      </c>
-      <c r="D62" s="39">
+      <c r="C62" s="38" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D62" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C62,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E62" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B62,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B62,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E62" s="39">
+      <c r="F62" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B62,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B62,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -45209,14 +45507,20 @@
           <t>KRISPY BY GG</t>
         </is>
       </c>
-      <c r="C63" s="38" t="n">
-        <v>9</v>
-      </c>
-      <c r="D63" s="39">
+      <c r="C63" s="38" t="inlineStr">
+        <is>
+          <t>Dining &amp; Restaurants</t>
+        </is>
+      </c>
+      <c r="D63" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C63,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E63" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B63,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B63,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E63" s="39">
+      <c r="F63" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B63,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B63,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -45231,11 +45535,15 @@
         </is>
       </c>
       <c r="C64" s="38" t="n"/>
-      <c r="D64" s="39">
+      <c r="D64" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C64,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E64" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B64,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B64,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E64" s="39">
+      <c r="F64" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B64,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B64,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -45250,11 +45558,15 @@
         </is>
       </c>
       <c r="C65" s="38" t="n"/>
-      <c r="D65" s="39">
+      <c r="D65" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C65,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E65" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B65,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B65,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E65" s="39">
+      <c r="F65" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B65,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B65,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -45268,14 +45580,20 @@
           <t>LILY &amp; TODD</t>
         </is>
       </c>
-      <c r="C66" s="38" t="n">
-        <v>15</v>
-      </c>
-      <c r="D66" s="39">
+      <c r="C66" s="38" t="inlineStr">
+        <is>
+          <t>Kid's Clothing</t>
+        </is>
+      </c>
+      <c r="D66" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C66,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E66" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B66,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B66,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E66" s="39">
+      <c r="F66" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B66,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B66,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -45289,14 +45607,20 @@
           <t>LILY AND TODD</t>
         </is>
       </c>
-      <c r="C67" s="38" t="n">
-        <v>15</v>
-      </c>
-      <c r="D67" s="39">
+      <c r="C67" s="38" t="inlineStr">
+        <is>
+          <t>Kid's Clothing</t>
+        </is>
+      </c>
+      <c r="D67" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C67,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E67" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B67,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B67,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E67" s="39">
+      <c r="F67" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B67,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B67,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -45311,11 +45635,15 @@
         </is>
       </c>
       <c r="C68" s="38" t="n"/>
-      <c r="D68" s="39">
+      <c r="D68" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C68,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E68" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B68,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B68,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E68" s="39">
+      <c r="F68" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B68,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B68,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -45329,14 +45657,20 @@
           <t>LUIBELLE</t>
         </is>
       </c>
-      <c r="C69" s="38" t="n">
-        <v>14</v>
-      </c>
-      <c r="D69" s="39">
+      <c r="C69" s="38" t="inlineStr">
+        <is>
+          <t>Women's Clothing</t>
+        </is>
+      </c>
+      <c r="D69" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C69,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E69" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B69,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B69,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E69" s="39">
+      <c r="F69" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B69,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B69,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -45350,14 +45684,20 @@
           <t>LUKOIL</t>
         </is>
       </c>
-      <c r="C70" s="38" t="n">
-        <v>7</v>
-      </c>
-      <c r="D70" s="39">
+      <c r="C70" s="38" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="D70" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C70,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E70" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B70,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B70,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E70" s="39">
+      <c r="F70" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B70,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B70,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -45371,14 +45711,20 @@
           <t>LULU KIDS CLOTHING</t>
         </is>
       </c>
-      <c r="C71" s="38" t="n">
-        <v>15</v>
-      </c>
-      <c r="D71" s="39">
+      <c r="C71" s="38" t="inlineStr">
+        <is>
+          <t>Kid's Clothing</t>
+        </is>
+      </c>
+      <c r="D71" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C71,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E71" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B71,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B71,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E71" s="39">
+      <c r="F71" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B71,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B71,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -45392,14 +45738,20 @@
           <t>MACY'S</t>
         </is>
       </c>
-      <c r="C72" s="38" t="n">
-        <v>14</v>
-      </c>
-      <c r="D72" s="39">
+      <c r="C72" s="38" t="inlineStr">
+        <is>
+          <t>Women's Clothing</t>
+        </is>
+      </c>
+      <c r="D72" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C72,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E72" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B72,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B72,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E72" s="39">
+      <c r="F72" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B72,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B72,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -45414,11 +45766,15 @@
         </is>
       </c>
       <c r="C73" s="38" t="n"/>
-      <c r="D73" s="39">
+      <c r="D73" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C73,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E73" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B73,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B73,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E73" s="39">
+      <c r="F73" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B73,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B73,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -45432,14 +45788,20 @@
           <t>MELT</t>
         </is>
       </c>
-      <c r="C74" s="38" t="n">
-        <v>9</v>
-      </c>
-      <c r="D74" s="39">
+      <c r="C74" s="38" t="inlineStr">
+        <is>
+          <t>Dining &amp; Restaurants</t>
+        </is>
+      </c>
+      <c r="D74" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C74,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E74" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B74,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B74,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E74" s="39">
+      <c r="F74" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B74,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B74,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -45453,14 +45815,20 @@
           <t>MERKAZ SEFORIM</t>
         </is>
       </c>
-      <c r="C75" s="38" t="n">
-        <v>23</v>
-      </c>
-      <c r="D75" s="39">
+      <c r="C75" s="38" t="inlineStr">
+        <is>
+          <t>Books</t>
+        </is>
+      </c>
+      <c r="D75" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C75,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E75" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B75,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B75,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E75" s="39">
+      <c r="F75" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B75,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B75,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -45474,14 +45842,20 @@
           <t>METRO BY T-MOBILE</t>
         </is>
       </c>
-      <c r="C76" s="38" t="n">
-        <v>2</v>
-      </c>
-      <c r="D76" s="39">
+      <c r="C76" s="38" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="D76" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C76,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E76" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B76,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B76,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E76" s="39">
+      <c r="F76" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B76,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B76,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -45495,14 +45869,20 @@
           <t>MIDAS - MONSEY</t>
         </is>
       </c>
-      <c r="C77" s="38" t="n">
-        <v>5</v>
-      </c>
-      <c r="D77" s="39">
+      <c r="C77" s="38" t="inlineStr">
+        <is>
+          <t>Car Expenses</t>
+        </is>
+      </c>
+      <c r="D77" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C77,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E77" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B77,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B77,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E77" s="39">
+      <c r="F77" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B77,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B77,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -45516,14 +45896,20 @@
           <t>Mikes Burger</t>
         </is>
       </c>
-      <c r="C78" s="38" t="n">
-        <v>9</v>
-      </c>
-      <c r="D78" s="39">
+      <c r="C78" s="38" t="inlineStr">
+        <is>
+          <t>Dining &amp; Restaurants</t>
+        </is>
+      </c>
+      <c r="D78" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C78,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E78" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B78,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B78,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E78" s="39">
+      <c r="F78" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B78,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B78,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -45537,14 +45923,20 @@
           <t>MONSEY GLATT</t>
         </is>
       </c>
-      <c r="C79" s="38" t="n">
-        <v>8</v>
-      </c>
-      <c r="D79" s="39">
+      <c r="C79" s="38" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="D79" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C79,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E79" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B79,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B79,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E79" s="39">
+      <c r="F79" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B79,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B79,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -45558,14 +45950,20 @@
           <t>MONSEY URGENT CARE</t>
         </is>
       </c>
-      <c r="C80" s="38" t="n">
-        <v>10</v>
-      </c>
-      <c r="D80" s="39">
+      <c r="C80" s="38" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D80" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C80,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E80" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B80,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B80,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E80" s="39">
+      <c r="F80" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B80,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B80,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -45579,14 +45977,20 @@
           <t>MONSEY WINE &amp; LIQUOR</t>
         </is>
       </c>
-      <c r="C81" s="38" t="n">
-        <v>11</v>
-      </c>
-      <c r="D81" s="39">
+      <c r="C81" s="38" t="inlineStr">
+        <is>
+          <t>Entertainment</t>
+        </is>
+      </c>
+      <c r="D81" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C81,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E81" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B81,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B81,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E81" s="39">
+      <c r="F81" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B81,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B81,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -45601,11 +46005,15 @@
         </is>
       </c>
       <c r="C82" s="38" t="n"/>
-      <c r="D82" s="39">
+      <c r="D82" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C82,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E82" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B82,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B82,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E82" s="39">
+      <c r="F82" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B82,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B82,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -45619,14 +46027,20 @@
           <t>MONTVALE WINE LIQUOR</t>
         </is>
       </c>
-      <c r="C83" s="38" t="n">
-        <v>11</v>
-      </c>
-      <c r="D83" s="39">
+      <c r="C83" s="38" t="inlineStr">
+        <is>
+          <t>Entertainment</t>
+        </is>
+      </c>
+      <c r="D83" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C83,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E83" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B83,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B83,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E83" s="39">
+      <c r="F83" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B83,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B83,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -45641,11 +46055,15 @@
         </is>
       </c>
       <c r="C84" s="38" t="n"/>
-      <c r="D84" s="39">
+      <c r="D84" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C84,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E84" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B84,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B84,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E84" s="39">
+      <c r="F84" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B84,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B84,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -45659,14 +46077,20 @@
           <t>MUNCH HEARTY</t>
         </is>
       </c>
-      <c r="C85" s="38" t="n">
-        <v>9</v>
-      </c>
-      <c r="D85" s="39">
+      <c r="C85" s="38" t="inlineStr">
+        <is>
+          <t>Dining &amp; Restaurants</t>
+        </is>
+      </c>
+      <c r="D85" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C85,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E85" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B85,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B85,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E85" s="39">
+      <c r="F85" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B85,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B85,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -45681,11 +46105,15 @@
         </is>
       </c>
       <c r="C86" s="38" t="n"/>
-      <c r="D86" s="39">
+      <c r="D86" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C86,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E86" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B86,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B86,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E86" s="39">
+      <c r="F86" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B86,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B86,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -45699,14 +46127,20 @@
           <t>NEW YORK STATE DMV</t>
         </is>
       </c>
-      <c r="C87" s="38" t="n">
-        <v>5</v>
-      </c>
-      <c r="D87" s="39">
+      <c r="C87" s="38" t="inlineStr">
+        <is>
+          <t>Car Expenses</t>
+        </is>
+      </c>
+      <c r="D87" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C87,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E87" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B87,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B87,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E87" s="39">
+      <c r="F87" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B87,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B87,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -45721,11 +46155,15 @@
         </is>
       </c>
       <c r="C88" s="38" t="n"/>
-      <c r="D88" s="39">
+      <c r="D88" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C88,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E88" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B88,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B88,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E88" s="39">
+      <c r="F88" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B88,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B88,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -45739,14 +46177,20 @@
           <t>Nissan Auto Lease</t>
         </is>
       </c>
-      <c r="C89" s="38" t="n">
-        <v>4</v>
-      </c>
-      <c r="D89" s="39">
+      <c r="C89" s="38" t="inlineStr">
+        <is>
+          <t>Car Lease/Finance</t>
+        </is>
+      </c>
+      <c r="D89" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C89,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E89" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B89,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B89,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E89" s="39">
+      <c r="F89" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B89,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B89,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -45761,11 +46205,15 @@
         </is>
       </c>
       <c r="C90" s="38" t="n"/>
-      <c r="D90" s="39">
+      <c r="D90" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C90,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E90" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B90,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B90,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E90" s="39">
+      <c r="F90" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B90,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B90,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -45779,14 +46227,20 @@
           <t>NORDSTROM RACK</t>
         </is>
       </c>
-      <c r="C91" s="38" t="n">
-        <v>14</v>
-      </c>
-      <c r="D91" s="39">
+      <c r="C91" s="38" t="inlineStr">
+        <is>
+          <t>Women's Clothing</t>
+        </is>
+      </c>
+      <c r="D91" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C91,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E91" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B91,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B91,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E91" s="39">
+      <c r="F91" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B91,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B91,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -45801,11 +46255,15 @@
         </is>
       </c>
       <c r="C92" s="38" t="n"/>
-      <c r="D92" s="39">
+      <c r="D92" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C92,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E92" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B92,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B92,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E92" s="39">
+      <c r="F92" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B92,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B92,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -45819,14 +46277,20 @@
           <t>NU TREND CLEANERS</t>
         </is>
       </c>
-      <c r="C93" s="38" t="n">
-        <v>12</v>
-      </c>
-      <c r="D93" s="39">
+      <c r="C93" s="38" t="inlineStr">
+        <is>
+          <t>Personal Care</t>
+        </is>
+      </c>
+      <c r="D93" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C93,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E93" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B93,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B93,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E93" s="39">
+      <c r="F93" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B93,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B93,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -45840,14 +46304,20 @@
           <t>NUMBER BARN</t>
         </is>
       </c>
-      <c r="C94" s="38" t="n">
-        <v>2</v>
-      </c>
-      <c r="D94" s="39">
+      <c r="C94" s="38" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="D94" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C94,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E94" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B94,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B94,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E94" s="39">
+      <c r="F94" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B94,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B94,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -45861,14 +46331,20 @@
           <t>NY STATE TAX</t>
         </is>
       </c>
-      <c r="C95" s="38" t="n">
-        <v>25</v>
-      </c>
-      <c r="D95" s="39">
+      <c r="C95" s="38" t="inlineStr">
+        <is>
+          <t>Taxes</t>
+        </is>
+      </c>
+      <c r="D95" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C95,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E95" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B95,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B95,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E95" s="39">
+      <c r="F95" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B95,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B95,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -45882,14 +46358,20 @@
           <t>NYS TAX</t>
         </is>
       </c>
-      <c r="C96" s="38" t="n">
-        <v>25</v>
-      </c>
-      <c r="D96" s="39">
+      <c r="C96" s="38" t="inlineStr">
+        <is>
+          <t>Taxes</t>
+        </is>
+      </c>
+      <c r="D96" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C96,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E96" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B96,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B96,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E96" s="39">
+      <c r="F96" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B96,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B96,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -45904,11 +46386,15 @@
         </is>
       </c>
       <c r="C97" s="38" t="n"/>
-      <c r="D97" s="39">
+      <c r="D97" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C97,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E97" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B97,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B97,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E97" s="39">
+      <c r="F97" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B97,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B97,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -45923,11 +46409,15 @@
         </is>
       </c>
       <c r="C98" s="38" t="n"/>
-      <c r="D98" s="39">
+      <c r="D98" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C98,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E98" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B98,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B98,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E98" s="39">
+      <c r="F98" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B98,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B98,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -45941,14 +46431,20 @@
           <t>OLYMPIA PITA</t>
         </is>
       </c>
-      <c r="C99" s="38" t="n">
-        <v>9</v>
-      </c>
-      <c r="D99" s="39">
+      <c r="C99" s="38" t="inlineStr">
+        <is>
+          <t>Dining &amp; Restaurants</t>
+        </is>
+      </c>
+      <c r="D99" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C99,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E99" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B99,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B99,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E99" s="39">
+      <c r="F99" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B99,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B99,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -45963,11 +46459,15 @@
         </is>
       </c>
       <c r="C100" s="38" t="n"/>
-      <c r="D100" s="39">
+      <c r="D100" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C100,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E100" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B100,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B100,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E100" s="39">
+      <c r="F100" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B100,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B100,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -45981,14 +46481,20 @@
           <t>ORANGE &amp; ROCKLAND</t>
         </is>
       </c>
-      <c r="C101" s="38" t="n">
-        <v>2</v>
-      </c>
-      <c r="D101" s="39">
+      <c r="C101" s="38" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="D101" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C101,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E101" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B101,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B101,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E101" s="39">
+      <c r="F101" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B101,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B101,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -46003,11 +46509,15 @@
         </is>
       </c>
       <c r="C102" s="38" t="n"/>
-      <c r="D102" s="39">
+      <c r="D102" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C102,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E102" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B102,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B102,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E102" s="39">
+      <c r="F102" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B102,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B102,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -46021,14 +46531,20 @@
           <t>PHARMACY PLUS</t>
         </is>
       </c>
-      <c r="C103" s="38" t="n">
-        <v>10</v>
-      </c>
-      <c r="D103" s="39">
+      <c r="C103" s="38" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D103" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C103,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E103" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B103,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B103,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E103" s="39">
+      <c r="F103" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B103,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B103,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -46042,14 +46558,20 @@
           <t>PIES N FRIES</t>
         </is>
       </c>
-      <c r="C104" s="38" t="n">
-        <v>9</v>
-      </c>
-      <c r="D104" s="39">
+      <c r="C104" s="38" t="inlineStr">
+        <is>
+          <t>Dining &amp; Restaurants</t>
+        </is>
+      </c>
+      <c r="D104" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C104,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E104" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B104,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B104,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E104" s="39">
+      <c r="F104" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B104,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B104,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -46063,14 +46585,20 @@
           <t>PITA LAND</t>
         </is>
       </c>
-      <c r="C105" s="38" t="n">
-        <v>9</v>
-      </c>
-      <c r="D105" s="39">
+      <c r="C105" s="38" t="inlineStr">
+        <is>
+          <t>Dining &amp; Restaurants</t>
+        </is>
+      </c>
+      <c r="D105" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C105,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E105" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B105,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B105,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E105" s="39">
+      <c r="F105" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B105,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B105,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -46085,11 +46613,15 @@
         </is>
       </c>
       <c r="C106" s="38" t="n"/>
-      <c r="D106" s="39">
+      <c r="D106" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C106,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E106" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B106,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B106,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E106" s="39">
+      <c r="F106" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B106,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B106,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -46103,14 +46635,20 @@
           <t>Prime Video</t>
         </is>
       </c>
-      <c r="C107" s="38" t="n">
-        <v>11</v>
-      </c>
-      <c r="D107" s="39">
+      <c r="C107" s="38" t="inlineStr">
+        <is>
+          <t>Entertainment</t>
+        </is>
+      </c>
+      <c r="D107" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C107,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E107" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B107,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B107,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E107" s="39">
+      <c r="F107" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B107,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B107,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -46125,11 +46663,15 @@
         </is>
       </c>
       <c r="C108" s="38" t="n"/>
-      <c r="D108" s="39">
+      <c r="D108" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C108,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E108" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B108,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B108,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E108" s="39">
+      <c r="F108" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B108,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B108,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -46144,11 +46686,15 @@
         </is>
       </c>
       <c r="C109" s="38" t="n"/>
-      <c r="D109" s="39">
+      <c r="D109" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C109,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E109" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B109,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B109,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E109" s="39">
+      <c r="F109" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B109,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B109,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -46163,11 +46709,15 @@
         </is>
       </c>
       <c r="C110" s="38" t="n"/>
-      <c r="D110" s="39">
+      <c r="D110" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C110,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E110" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B110,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B110,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E110" s="39">
+      <c r="F110" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B110,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B110,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -46181,14 +46731,20 @@
           <t>ROCKET MORTGAGE</t>
         </is>
       </c>
-      <c r="C111" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D111" s="39">
+      <c r="C111" s="38" t="inlineStr">
+        <is>
+          <t>Mortgage</t>
+        </is>
+      </c>
+      <c r="D111" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C111,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E111" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B111,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B111,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E111" s="39">
+      <c r="F111" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B111,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B111,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -46202,14 +46758,20 @@
           <t>ROCKLAND KOSHER</t>
         </is>
       </c>
-      <c r="C112" s="38" t="n">
-        <v>8</v>
-      </c>
-      <c r="D112" s="39">
+      <c r="C112" s="38" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="D112" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C112,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E112" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B112,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B112,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E112" s="39">
+      <c r="F112" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B112,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B112,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -46223,14 +46785,20 @@
           <t>SANDERS BAKERY</t>
         </is>
       </c>
-      <c r="C113" s="38" t="n">
-        <v>9</v>
-      </c>
-      <c r="D113" s="39">
+      <c r="C113" s="38" t="inlineStr">
+        <is>
+          <t>Dining &amp; Restaurants</t>
+        </is>
+      </c>
+      <c r="D113" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C113,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E113" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B113,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B113,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E113" s="39">
+      <c r="F113" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B113,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B113,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -46244,14 +46812,20 @@
           <t>SEASONS EXPRESS</t>
         </is>
       </c>
-      <c r="C114" s="38" t="n">
-        <v>8</v>
-      </c>
-      <c r="D114" s="39">
+      <c r="C114" s="38" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="D114" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C114,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E114" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B114,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B114,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E114" s="39">
+      <c r="F114" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B114,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B114,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -46265,14 +46839,20 @@
           <t>SEPHORA</t>
         </is>
       </c>
-      <c r="C115" s="38" t="n">
-        <v>12</v>
-      </c>
-      <c r="D115" s="39">
+      <c r="C115" s="38" t="inlineStr">
+        <is>
+          <t>Personal Care</t>
+        </is>
+      </c>
+      <c r="D115" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C115,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E115" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B115,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B115,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E115" s="39">
+      <c r="F115" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B115,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B115,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -46286,14 +46866,20 @@
           <t>SHAWARMA DELIGHT</t>
         </is>
       </c>
-      <c r="C116" s="38" t="n">
-        <v>9</v>
-      </c>
-      <c r="D116" s="39">
+      <c r="C116" s="38" t="inlineStr">
+        <is>
+          <t>Dining &amp; Restaurants</t>
+        </is>
+      </c>
+      <c r="D116" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C116,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E116" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B116,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B116,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E116" s="39">
+      <c r="F116" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B116,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B116,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -46307,14 +46893,20 @@
           <t>SHELIS IN TOWN SQ</t>
         </is>
       </c>
-      <c r="C117" s="38" t="n">
-        <v>9</v>
-      </c>
-      <c r="D117" s="39">
+      <c r="C117" s="38" t="inlineStr">
+        <is>
+          <t>Dining &amp; Restaurants</t>
+        </is>
+      </c>
+      <c r="D117" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C117,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E117" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B117,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B117,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E117" s="39">
+      <c r="F117" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B117,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B117,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -46328,14 +46920,20 @@
           <t>SHELL OIL</t>
         </is>
       </c>
-      <c r="C118" s="38" t="n">
-        <v>7</v>
-      </c>
-      <c r="D118" s="39">
+      <c r="C118" s="38" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="D118" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C118,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E118" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B118,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B118,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E118" s="39">
+      <c r="F118" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B118,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B118,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -46349,14 +46947,20 @@
           <t>SHOPRITE</t>
         </is>
       </c>
-      <c r="C119" s="38" t="n">
-        <v>8</v>
-      </c>
-      <c r="D119" s="39">
+      <c r="C119" s="38" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="D119" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C119,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E119" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B119,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B119,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E119" s="39">
+      <c r="F119" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B119,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B119,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -46371,11 +46975,15 @@
         </is>
       </c>
       <c r="C120" s="38" t="n"/>
-      <c r="D120" s="39">
+      <c r="D120" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C120,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E120" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B120,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B120,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E120" s="39">
+      <c r="F120" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B120,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B120,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -46390,11 +46998,15 @@
         </is>
       </c>
       <c r="C121" s="38" t="n"/>
-      <c r="D121" s="39">
+      <c r="D121" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C121,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E121" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B121,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B121,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E121" s="39">
+      <c r="F121" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B121,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B121,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -46408,14 +47020,20 @@
           <t>SPARK CAR WASH</t>
         </is>
       </c>
-      <c r="C122" s="38" t="n">
-        <v>5</v>
-      </c>
-      <c r="D122" s="39">
+      <c r="C122" s="38" t="inlineStr">
+        <is>
+          <t>Car Expenses</t>
+        </is>
+      </c>
+      <c r="D122" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C122,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E122" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B122,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B122,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E122" s="39">
+      <c r="F122" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B122,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B122,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -46429,14 +47047,20 @@
           <t>SPRINKLES</t>
         </is>
       </c>
-      <c r="C123" s="38" t="n">
-        <v>9</v>
-      </c>
-      <c r="D123" s="39">
+      <c r="C123" s="38" t="inlineStr">
+        <is>
+          <t>Dining &amp; Restaurants</t>
+        </is>
+      </c>
+      <c r="D123" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C123,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E123" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B123,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B123,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E123" s="39">
+      <c r="F123" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B123,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B123,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -46450,14 +47074,20 @@
           <t>SW DESIGNER SHOES</t>
         </is>
       </c>
-      <c r="C124" s="38" t="n">
-        <v>14</v>
-      </c>
-      <c r="D124" s="39">
+      <c r="C124" s="38" t="inlineStr">
+        <is>
+          <t>Women's Clothing</t>
+        </is>
+      </c>
+      <c r="D124" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C124,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E124" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B124,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B124,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E124" s="39">
+      <c r="F124" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B124,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B124,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -46471,14 +47101,20 @@
           <t>SWADDLES BABY</t>
         </is>
       </c>
-      <c r="C125" s="38" t="n">
-        <v>16</v>
-      </c>
-      <c r="D125" s="39">
+      <c r="C125" s="38" t="inlineStr">
+        <is>
+          <t>Kid's Accessories</t>
+        </is>
+      </c>
+      <c r="D125" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C125,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E125" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B125,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B125,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E125" s="39">
+      <c r="F125" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B125,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B125,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -46492,14 +47128,20 @@
           <t>SWEET EXPRESSIONS</t>
         </is>
       </c>
-      <c r="C126" s="38" t="n">
-        <v>17</v>
-      </c>
-      <c r="D126" s="39">
+      <c r="C126" s="38" t="inlineStr">
+        <is>
+          <t>Gifts</t>
+        </is>
+      </c>
+      <c r="D126" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C126,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E126" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B126,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B126,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E126" s="39">
+      <c r="F126" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B126,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B126,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -46514,11 +47156,15 @@
         </is>
       </c>
       <c r="C127" s="38" t="n"/>
-      <c r="D127" s="39">
+      <c r="D127" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C127,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E127" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B127,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B127,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E127" s="39">
+      <c r="F127" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B127,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B127,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -46533,11 +47179,15 @@
         </is>
       </c>
       <c r="C128" s="38" t="n"/>
-      <c r="D128" s="39">
+      <c r="D128" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C128,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E128" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B128,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B128,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E128" s="39">
+      <c r="F128" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B128,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B128,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -46551,14 +47201,20 @@
           <t>TARGET</t>
         </is>
       </c>
-      <c r="C129" s="38" t="n">
-        <v>22</v>
-      </c>
-      <c r="D129" s="39">
+      <c r="C129" s="38" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="D129" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C129,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E129" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B129,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B129,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E129" s="39">
+      <c r="F129" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B129,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B129,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -46573,11 +47229,15 @@
         </is>
       </c>
       <c r="C130" s="38" t="n"/>
-      <c r="D130" s="39">
+      <c r="D130" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C130,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E130" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B130,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B130,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E130" s="39">
+      <c r="F130" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B130,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B130,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -46591,14 +47251,20 @@
           <t>THE CHILDRENS PLACE</t>
         </is>
       </c>
-      <c r="C131" s="38" t="n">
-        <v>15</v>
-      </c>
-      <c r="D131" s="39">
+      <c r="C131" s="38" t="inlineStr">
+        <is>
+          <t>Kid's Clothing</t>
+        </is>
+      </c>
+      <c r="D131" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C131,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E131" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B131,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B131,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E131" s="39">
+      <c r="F131" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B131,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B131,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -46613,11 +47279,15 @@
         </is>
       </c>
       <c r="C132" s="38" t="n"/>
-      <c r="D132" s="39">
+      <c r="D132" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C132,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E132" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B132,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B132,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E132" s="39">
+      <c r="F132" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B132,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B132,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -46632,11 +47302,15 @@
         </is>
       </c>
       <c r="C133" s="38" t="n"/>
-      <c r="D133" s="39">
+      <c r="D133" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C133,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E133" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B133,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B133,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E133" s="39">
+      <c r="F133" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B133,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B133,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -46650,14 +47324,20 @@
           <t>TOTTINI</t>
         </is>
       </c>
-      <c r="C134" s="38" t="n">
-        <v>16</v>
-      </c>
-      <c r="D134" s="39">
+      <c r="C134" s="38" t="inlineStr">
+        <is>
+          <t>Kid's Accessories</t>
+        </is>
+      </c>
+      <c r="D134" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C134,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E134" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B134,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B134,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E134" s="39">
+      <c r="F134" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B134,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B134,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -46671,14 +47351,20 @@
           <t>TOYOTA</t>
         </is>
       </c>
-      <c r="C135" s="38" t="n">
-        <v>4</v>
-      </c>
-      <c r="D135" s="39">
+      <c r="C135" s="38" t="inlineStr">
+        <is>
+          <t>Car Lease/Finance</t>
+        </is>
+      </c>
+      <c r="D135" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C135,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E135" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B135,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B135,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E135" s="39">
+      <c r="F135" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B135,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B135,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -46692,14 +47378,20 @@
           <t>TOYS 4 U</t>
         </is>
       </c>
-      <c r="C136" s="38" t="n">
-        <v>18</v>
-      </c>
-      <c r="D136" s="39">
+      <c r="C136" s="38" t="inlineStr">
+        <is>
+          <t>Toys</t>
+        </is>
+      </c>
+      <c r="D136" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C136,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E136" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B136,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B136,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E136" s="39">
+      <c r="F136" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B136,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B136,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -46713,14 +47405,20 @@
           <t>TURTLE BACK ZOO</t>
         </is>
       </c>
-      <c r="C137" s="38" t="n">
-        <v>11</v>
-      </c>
-      <c r="D137" s="39">
+      <c r="C137" s="38" t="inlineStr">
+        <is>
+          <t>Entertainment</t>
+        </is>
+      </c>
+      <c r="D137" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C137,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E137" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B137,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B137,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E137" s="39">
+      <c r="F137" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B137,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B137,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -46735,11 +47433,15 @@
         </is>
       </c>
       <c r="C138" s="38" t="n"/>
-      <c r="D138" s="39">
+      <c r="D138" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C138,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E138" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B138,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B138,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E138" s="39">
+      <c r="F138" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B138,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B138,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -46753,14 +47455,20 @@
           <t>UBER EATS</t>
         </is>
       </c>
-      <c r="C139" s="38" t="n">
-        <v>9</v>
-      </c>
-      <c r="D139" s="39">
+      <c r="C139" s="38" t="inlineStr">
+        <is>
+          <t>Dining &amp; Restaurants</t>
+        </is>
+      </c>
+      <c r="D139" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C139,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E139" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B139,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B139,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E139" s="39">
+      <c r="F139" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B139,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B139,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -46774,14 +47482,20 @@
           <t>ULTA</t>
         </is>
       </c>
-      <c r="C140" s="38" t="n">
-        <v>12</v>
-      </c>
-      <c r="D140" s="39">
+      <c r="C140" s="38" t="inlineStr">
+        <is>
+          <t>Personal Care</t>
+        </is>
+      </c>
+      <c r="D140" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C140,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E140" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B140,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B140,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E140" s="39">
+      <c r="F140" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B140,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B140,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -46795,14 +47509,20 @@
           <t>US MOBILE</t>
         </is>
       </c>
-      <c r="C141" s="38" t="n">
-        <v>2</v>
-      </c>
-      <c r="D141" s="39">
+      <c r="C141" s="38" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="D141" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C141,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E141" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B141,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B141,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E141" s="39">
+      <c r="F141" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B141,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B141,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -46816,14 +47536,20 @@
           <t>VEOLIA</t>
         </is>
       </c>
-      <c r="C142" s="38" t="n">
-        <v>2</v>
-      </c>
-      <c r="D142" s="39">
+      <c r="C142" s="38" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="D142" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C142,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E142" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B142,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B142,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E142" s="39">
+      <c r="F142" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B142,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B142,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -46837,14 +47563,20 @@
           <t>WAL-MART</t>
         </is>
       </c>
-      <c r="C143" s="38" t="n">
-        <v>21</v>
-      </c>
-      <c r="D143" s="39">
+      <c r="C143" s="38" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D143" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C143,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E143" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B143,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B143,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E143" s="39">
+      <c r="F143" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B143,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B143,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -46858,14 +47590,20 @@
           <t>Walmart+ Membership</t>
         </is>
       </c>
-      <c r="C144" s="38" t="n">
-        <v>21</v>
-      </c>
-      <c r="D144" s="39">
+      <c r="C144" s="38" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D144" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C144,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E144" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B144,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B144,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E144" s="39">
+      <c r="F144" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B144,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B144,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -46879,14 +47617,20 @@
           <t>WEGMANS MONTVALE</t>
         </is>
       </c>
-      <c r="C145" s="38" t="n">
-        <v>8</v>
-      </c>
-      <c r="D145" s="39">
+      <c r="C145" s="38" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="D145" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C145,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E145" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B145,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B145,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E145" s="39">
+      <c r="F145" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B145,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B145,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -46900,14 +47644,20 @@
           <t>WESLEY KOSHER</t>
         </is>
       </c>
-      <c r="C146" s="38" t="n">
-        <v>8</v>
-      </c>
-      <c r="D146" s="39">
+      <c r="C146" s="38" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="D146" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C146,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E146" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B146,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B146,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E146" s="39">
+      <c r="F146" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B146,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B146,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -46921,14 +47671,20 @@
           <t>WESTCHESTER MEDICAL CENTER</t>
         </is>
       </c>
-      <c r="C147" s="38" t="n">
-        <v>10</v>
-      </c>
-      <c r="D147" s="39">
+      <c r="C147" s="38" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D147" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C147,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E147" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B147,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B147,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E147" s="39">
+      <c r="F147" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B147,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B147,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -46942,14 +47698,20 @@
           <t>WINE ON 59</t>
         </is>
       </c>
-      <c r="C148" s="38" t="n">
-        <v>11</v>
-      </c>
-      <c r="D148" s="39">
+      <c r="C148" s="38" t="inlineStr">
+        <is>
+          <t>Entertainment</t>
+        </is>
+      </c>
+      <c r="D148" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C148,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E148" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B148,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B148,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E148" s="39">
+      <c r="F148" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B148,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B148,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -46963,14 +47725,20 @@
           <t>YOFFEE COFFEE</t>
         </is>
       </c>
-      <c r="C149" s="38" t="n">
-        <v>9</v>
-      </c>
-      <c r="D149" s="39">
+      <c r="C149" s="38" t="inlineStr">
+        <is>
+          <t>Dining &amp; Restaurants</t>
+        </is>
+      </c>
+      <c r="D149" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C149,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E149" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B149,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B149,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E149" s="39">
+      <c r="F149" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B149,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B149,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -46984,14 +47752,20 @@
           <t>Zadarma</t>
         </is>
       </c>
-      <c r="C150" s="38" t="n">
-        <v>2</v>
-      </c>
-      <c r="D150" s="39">
+      <c r="C150" s="38" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="D150" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C150,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E150" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B150,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B150,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E150" s="39">
+      <c r="F150" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B150,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B150,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -47005,14 +47779,20 @@
           <t>Zara</t>
         </is>
       </c>
-      <c r="C151" s="38" t="n">
-        <v>14</v>
-      </c>
-      <c r="D151" s="39">
+      <c r="C151" s="38" t="inlineStr">
+        <is>
+          <t>Women's Clothing</t>
+        </is>
+      </c>
+      <c r="D151" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C151,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E151" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B151,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B151,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E151" s="39">
+      <c r="F151" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B151,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B151,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -47027,11 +47807,15 @@
         </is>
       </c>
       <c r="C152" s="38" t="n"/>
-      <c r="D152" s="39">
+      <c r="D152" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C152,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E152" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B152,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B152,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E152" s="39">
+      <c r="F152" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B152,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B152,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -47046,11 +47830,15 @@
         </is>
       </c>
       <c r="C153" s="38" t="n"/>
-      <c r="D153" s="39">
+      <c r="D153" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C153,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E153" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B153,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B153,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E153" s="39">
+      <c r="F153" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B153,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B153,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -47064,14 +47852,20 @@
           <t>Payroll Direct DB</t>
         </is>
       </c>
-      <c r="C154" s="38" t="n">
-        <v>26</v>
-      </c>
-      <c r="D154" s="39">
+      <c r="C154" s="38" t="inlineStr">
+        <is>
+          <t>Payroll Direct DB</t>
+        </is>
+      </c>
+      <c r="D154" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C154,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E154" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B154,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B154,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E154" s="39">
+      <c r="F154" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B154,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B154,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -47085,14 +47879,20 @@
           <t>Payroll Cash RB</t>
         </is>
       </c>
-      <c r="C155" s="38" t="n">
-        <v>27</v>
-      </c>
-      <c r="D155" s="39">
+      <c r="C155" s="38" t="inlineStr">
+        <is>
+          <t>Payroll Cash RB</t>
+        </is>
+      </c>
+      <c r="D155" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C155,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E155" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B155,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B155,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E155" s="39">
+      <c r="F155" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B155,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B155,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
@@ -47106,23 +47906,34 @@
           <t>Payroll Direct RB</t>
         </is>
       </c>
-      <c r="C156" s="38" t="n">
-        <v>28</v>
-      </c>
-      <c r="D156" s="39">
+      <c r="C156" s="38" t="inlineStr">
+        <is>
+          <t>Payroll Direct RB</t>
+        </is>
+      </c>
+      <c r="D156" s="38">
+        <f>IFERROR(INDEX(Dim_Category[CategoryID],MATCH($C156,Dim_Category[CategoryName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="E156" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B156,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B156,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
-      <c r="E156" s="39">
+      <c r="F156" s="39">
         <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B156,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B156,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A4:F4"/>
     <mergeCell ref="A1:F2"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="C6:C206" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Please choose a value from the dropdown list." type="list">
+      <formula1>CategoryNameList</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Personal Finance Dashboard/Personal Finance Intelligence Dashboard.xlsx
+++ b/Personal Finance Dashboard/Personal Finance Intelligence Dashboard.xlsx
@@ -37,7 +37,7 @@
     <definedName name="VendorNameList">Dim_Vendor[VendorName]</definedName>
     <definedName name="AccountNameList">Dim_Account[AccountName]</definedName>
     <definedName name="SourceNameList">Dim_Source[SourceName]</definedName>
-    <definedName name="SignConvention">'Bank Import'!$D$13</definedName>
+    <definedName name="SignConvention">'Bank Import'!$D$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -403,7 +403,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="10">
     <dxf>
       <font>
         <b val="1"/>
@@ -446,6 +446,11 @@
     <dxf>
       <font>
         <color rgb="0015803D"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="002563EB"/>
       </font>
     </dxf>
     <dxf>
@@ -1155,8 +1160,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BankImportRaw" displayName="BankImportRaw" ref="A16:K516" headerRowCount="1">
-  <autoFilter ref="A16:K516"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BankImportRaw" displayName="BankImportRaw" ref="A17:K517" headerRowCount="1">
+  <autoFilter ref="A17:K517"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="Description"/>
@@ -1750,7 +1755,7 @@
       <c r="C6" s="8" t="n"/>
       <c r="D6" s="9" t="n"/>
       <c r="E6" s="10">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F6" s="8" t="n"/>
@@ -2023,7 +2028,7 @@
         </is>
       </c>
       <c r="M71" s="23">
-        <f>IFERROR((SUMIFS(Fact_Expenses[Amount],Fact_Expenses[NeedWantFlag],"Need")+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[NeedWantFlag],"Need",BankImportRaw[TransactionType],"Expense"))/(SUM(Fact_Expenses[Amount])+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Expense")),0)</f>
+        <f>IFERROR((SUMIFS(Fact_Expenses[Amount],Fact_Expenses[NeedWantFlag],"Need")+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[NeedWantFlag],"Need",BankImportRaw[TransactionType],"Expense")-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[NeedWantFlag],"Need",BankImportRaw[TransactionType],"Return"))/(SUM(Fact_Expenses[Amount])+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Expense")-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Return")),0)</f>
         <v/>
       </c>
     </row>
@@ -2639,7 +2644,7 @@
         </is>
       </c>
       <c r="B108" s="27">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],"Dining &amp; Restaurants",Fact_Expenses[Date],"&gt;="&amp;EOMONTH(TodayDate,-2)+1,Fact_Expenses[Date],"&lt;="&amp;EOMONTH(TodayDate,-1))+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],"Dining &amp; Restaurants",BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;EOMONTH(TodayDate,-2)+1,BankImportRaw[Date],"&lt;="&amp;EOMONTH(TodayDate,-1))</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],"Dining &amp; Restaurants",Fact_Expenses[Date],"&gt;="&amp;EOMONTH(TodayDate,-2)+1,Fact_Expenses[Date],"&lt;="&amp;EOMONTH(TodayDate,-1))+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],"Dining &amp; Restaurants",BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;EOMONTH(TodayDate,-2)+1,BankImportRaw[Date],"&lt;="&amp;EOMONTH(TodayDate,-1))-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],"Dining &amp; Restaurants",BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;EOMONTH(TodayDate,-2)+1,BankImportRaw[Date],"&lt;="&amp;EOMONTH(TodayDate,-1))</f>
         <v/>
       </c>
       <c r="C108" s="27">
@@ -2666,7 +2671,7 @@
         </is>
       </c>
       <c r="B109" s="27">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],"Entertainment",Fact_Expenses[Date],"&gt;="&amp;EOMONTH(TodayDate,-2)+1,Fact_Expenses[Date],"&lt;="&amp;EOMONTH(TodayDate,-1))+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],"Entertainment",BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;EOMONTH(TodayDate,-2)+1,BankImportRaw[Date],"&lt;="&amp;EOMONTH(TodayDate,-1))</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],"Entertainment",Fact_Expenses[Date],"&gt;="&amp;EOMONTH(TodayDate,-2)+1,Fact_Expenses[Date],"&lt;="&amp;EOMONTH(TodayDate,-1))+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],"Entertainment",BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;EOMONTH(TodayDate,-2)+1,BankImportRaw[Date],"&lt;="&amp;EOMONTH(TodayDate,-1))-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],"Entertainment",BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;EOMONTH(TodayDate,-2)+1,BankImportRaw[Date],"&lt;="&amp;EOMONTH(TodayDate,-1))</f>
         <v/>
       </c>
       <c r="C109" s="27">
@@ -2693,7 +2698,7 @@
         </is>
       </c>
       <c r="B110" s="27">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],"Personal Care",Fact_Expenses[Date],"&gt;="&amp;EOMONTH(TodayDate,-2)+1,Fact_Expenses[Date],"&lt;="&amp;EOMONTH(TodayDate,-1))+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],"Personal Care",BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;EOMONTH(TodayDate,-2)+1,BankImportRaw[Date],"&lt;="&amp;EOMONTH(TodayDate,-1))</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],"Personal Care",Fact_Expenses[Date],"&gt;="&amp;EOMONTH(TodayDate,-2)+1,Fact_Expenses[Date],"&lt;="&amp;EOMONTH(TodayDate,-1))+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],"Personal Care",BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;EOMONTH(TodayDate,-2)+1,BankImportRaw[Date],"&lt;="&amp;EOMONTH(TodayDate,-1))-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],"Personal Care",BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;EOMONTH(TodayDate,-2)+1,BankImportRaw[Date],"&lt;="&amp;EOMONTH(TodayDate,-1))</f>
         <v/>
       </c>
       <c r="C110" s="27">
@@ -2720,7 +2725,7 @@
         </is>
       </c>
       <c r="B111" s="27">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[NeedWantFlag],"Want",Fact_Expenses[Date],"&gt;="&amp;EOMONTH(TodayDate,-2)+1,Fact_Expenses[Date],"&lt;="&amp;EOMONTH(TodayDate,-1))+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[NeedWantFlag],"Want",BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;EOMONTH(TodayDate,-2)+1,BankImportRaw[Date],"&lt;="&amp;EOMONTH(TodayDate,-1))</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[NeedWantFlag],"Want",Fact_Expenses[Date],"&gt;="&amp;EOMONTH(TodayDate,-2)+1,Fact_Expenses[Date],"&lt;="&amp;EOMONTH(TodayDate,-1))+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[NeedWantFlag],"Want",BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;EOMONTH(TodayDate,-2)+1,BankImportRaw[Date],"&lt;="&amp;EOMONTH(TodayDate,-1))-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[NeedWantFlag],"Want",BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;EOMONTH(TodayDate,-2)+1,BankImportRaw[Date],"&lt;="&amp;EOMONTH(TodayDate,-1))</f>
         <v/>
       </c>
       <c r="C111" s="27">
@@ -30713,7 +30718,7 @@
         <v/>
       </c>
       <c r="D2" s="48">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;EOMONTH(A2,-1)+1,Fact_Expenses[Date],"&lt;="&amp;B2)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A2,-1)+1,BankImportRaw[Date],"&lt;="&amp;B2)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;EOMONTH(A2,-1)+1,Fact_Expenses[Date],"&lt;="&amp;B2)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A2,-1)+1,BankImportRaw[Date],"&lt;="&amp;B2)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A2,-1)+1,BankImportRaw[Date],"&lt;="&amp;B2)</f>
         <v/>
       </c>
       <c r="E2" s="48">
@@ -30739,7 +30744,7 @@
         <v/>
       </c>
       <c r="D3" s="48">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;EOMONTH(A3,-1)+1,Fact_Expenses[Date],"&lt;="&amp;B3)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A3,-1)+1,BankImportRaw[Date],"&lt;="&amp;B3)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;EOMONTH(A3,-1)+1,Fact_Expenses[Date],"&lt;="&amp;B3)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A3,-1)+1,BankImportRaw[Date],"&lt;="&amp;B3)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A3,-1)+1,BankImportRaw[Date],"&lt;="&amp;B3)</f>
         <v/>
       </c>
       <c r="E3" s="48">
@@ -30765,7 +30770,7 @@
         <v/>
       </c>
       <c r="D4" s="48">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;EOMONTH(A4,-1)+1,Fact_Expenses[Date],"&lt;="&amp;B4)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A4,-1)+1,BankImportRaw[Date],"&lt;="&amp;B4)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;EOMONTH(A4,-1)+1,Fact_Expenses[Date],"&lt;="&amp;B4)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A4,-1)+1,BankImportRaw[Date],"&lt;="&amp;B4)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A4,-1)+1,BankImportRaw[Date],"&lt;="&amp;B4)</f>
         <v/>
       </c>
       <c r="E4" s="48">
@@ -30791,7 +30796,7 @@
         <v/>
       </c>
       <c r="D5" s="48">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;EOMONTH(A5,-1)+1,Fact_Expenses[Date],"&lt;="&amp;B5)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A5,-1)+1,BankImportRaw[Date],"&lt;="&amp;B5)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;EOMONTH(A5,-1)+1,Fact_Expenses[Date],"&lt;="&amp;B5)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A5,-1)+1,BankImportRaw[Date],"&lt;="&amp;B5)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A5,-1)+1,BankImportRaw[Date],"&lt;="&amp;B5)</f>
         <v/>
       </c>
       <c r="E5" s="48">
@@ -30817,7 +30822,7 @@
         <v/>
       </c>
       <c r="D6" s="48">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;EOMONTH(A6,-1)+1,Fact_Expenses[Date],"&lt;="&amp;B6)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A6,-1)+1,BankImportRaw[Date],"&lt;="&amp;B6)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;EOMONTH(A6,-1)+1,Fact_Expenses[Date],"&lt;="&amp;B6)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A6,-1)+1,BankImportRaw[Date],"&lt;="&amp;B6)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A6,-1)+1,BankImportRaw[Date],"&lt;="&amp;B6)</f>
         <v/>
       </c>
       <c r="E6" s="48">
@@ -30843,7 +30848,7 @@
         <v/>
       </c>
       <c r="D7" s="48">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;EOMONTH(A7,-1)+1,Fact_Expenses[Date],"&lt;="&amp;B7)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A7,-1)+1,BankImportRaw[Date],"&lt;="&amp;B7)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;EOMONTH(A7,-1)+1,Fact_Expenses[Date],"&lt;="&amp;B7)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A7,-1)+1,BankImportRaw[Date],"&lt;="&amp;B7)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A7,-1)+1,BankImportRaw[Date],"&lt;="&amp;B7)</f>
         <v/>
       </c>
       <c r="E7" s="48">
@@ -30869,7 +30874,7 @@
         <v/>
       </c>
       <c r="D8" s="48">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;EOMONTH(A8,-1)+1,Fact_Expenses[Date],"&lt;="&amp;B8)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A8,-1)+1,BankImportRaw[Date],"&lt;="&amp;B8)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;EOMONTH(A8,-1)+1,Fact_Expenses[Date],"&lt;="&amp;B8)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A8,-1)+1,BankImportRaw[Date],"&lt;="&amp;B8)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A8,-1)+1,BankImportRaw[Date],"&lt;="&amp;B8)</f>
         <v/>
       </c>
       <c r="E8" s="48">
@@ -30895,7 +30900,7 @@
         <v/>
       </c>
       <c r="D9" s="48">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;EOMONTH(A9,-1)+1,Fact_Expenses[Date],"&lt;="&amp;B9)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A9,-1)+1,BankImportRaw[Date],"&lt;="&amp;B9)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;EOMONTH(A9,-1)+1,Fact_Expenses[Date],"&lt;="&amp;B9)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A9,-1)+1,BankImportRaw[Date],"&lt;="&amp;B9)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A9,-1)+1,BankImportRaw[Date],"&lt;="&amp;B9)</f>
         <v/>
       </c>
       <c r="E9" s="48">
@@ -30921,7 +30926,7 @@
         <v/>
       </c>
       <c r="D10" s="48">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;EOMONTH(A10,-1)+1,Fact_Expenses[Date],"&lt;="&amp;B10)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A10,-1)+1,BankImportRaw[Date],"&lt;="&amp;B10)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;EOMONTH(A10,-1)+1,Fact_Expenses[Date],"&lt;="&amp;B10)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A10,-1)+1,BankImportRaw[Date],"&lt;="&amp;B10)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A10,-1)+1,BankImportRaw[Date],"&lt;="&amp;B10)</f>
         <v/>
       </c>
       <c r="E10" s="48">
@@ -30947,7 +30952,7 @@
         <v/>
       </c>
       <c r="D11" s="48">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;EOMONTH(A11,-1)+1,Fact_Expenses[Date],"&lt;="&amp;B11)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A11,-1)+1,BankImportRaw[Date],"&lt;="&amp;B11)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;EOMONTH(A11,-1)+1,Fact_Expenses[Date],"&lt;="&amp;B11)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A11,-1)+1,BankImportRaw[Date],"&lt;="&amp;B11)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A11,-1)+1,BankImportRaw[Date],"&lt;="&amp;B11)</f>
         <v/>
       </c>
       <c r="E11" s="48">
@@ -30973,7 +30978,7 @@
         <v/>
       </c>
       <c r="D12" s="48">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;EOMONTH(A12,-1)+1,Fact_Expenses[Date],"&lt;="&amp;B12)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A12,-1)+1,BankImportRaw[Date],"&lt;="&amp;B12)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;EOMONTH(A12,-1)+1,Fact_Expenses[Date],"&lt;="&amp;B12)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A12,-1)+1,BankImportRaw[Date],"&lt;="&amp;B12)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A12,-1)+1,BankImportRaw[Date],"&lt;="&amp;B12)</f>
         <v/>
       </c>
       <c r="E12" s="48">
@@ -30999,7 +31004,7 @@
         <v/>
       </c>
       <c r="D13" s="48">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;EOMONTH(A13,-1)+1,Fact_Expenses[Date],"&lt;="&amp;B13)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A13,-1)+1,BankImportRaw[Date],"&lt;="&amp;B13)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;EOMONTH(A13,-1)+1,Fact_Expenses[Date],"&lt;="&amp;B13)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A13,-1)+1,BankImportRaw[Date],"&lt;="&amp;B13)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A13,-1)+1,BankImportRaw[Date],"&lt;="&amp;B13)</f>
         <v/>
       </c>
       <c r="E13" s="48">
@@ -31025,7 +31030,7 @@
         <v/>
       </c>
       <c r="D14" s="48">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;EOMONTH(A14,-1)+1,Fact_Expenses[Date],"&lt;="&amp;B14)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A14,-1)+1,BankImportRaw[Date],"&lt;="&amp;B14)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[Date],"&gt;="&amp;EOMONTH(A14,-1)+1,Fact_Expenses[Date],"&lt;="&amp;B14)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A14,-1)+1,BankImportRaw[Date],"&lt;="&amp;B14)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;EOMONTH(A14,-1)+1,BankImportRaw[Date],"&lt;="&amp;B14)</f>
         <v/>
       </c>
       <c r="E14" s="48">
@@ -31318,7 +31323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K516"/>
+  <dimension ref="A1:K517"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -31402,140 +31407,127 @@
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="31" t="inlineStr">
         <is>
-          <t>That's it — every row here counts immediately in the Dashboard KPIs, charts, Budget, and Vendor totals. There's no copy step: this tab IS the ledger for bank-derived transactions, the same way Expenses/Income are the ledger for anything you enter by hand. Don't delete rows after importing — deleting a row removes that transaction from every report.</t>
+          <t>5. Column H (TransactionType) guesses Expense or Income from the amount's sign — for a refund/return on a purchase, change it to Return using the dropdown. A Return reduces that category's and vendor's spend (it does NOT count as income), so refunds don't inflate your income or savings rate.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="31" t="inlineStr">
         <is>
-          <t>Note: the auto-fill in step 4 only recognizes an EXACT repeat of a description string. Recurring bills and subscriptions usually post with identical text every time, so those learn fast. If your bank appends a unique date or reference number to every line, matching won't catch it — you'll just pick the vendor again, same as the first time.</t>
+          <t>That's it — every row here counts immediately in the Dashboard KPIs, charts, Budget, and Vendor totals. There's no copy step: this tab IS the ledger for bank-derived transactions, the same way Expenses/Income are the ledger for anything you enter by hand. Don't delete rows after importing — deleting a row removes that transaction from every report.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="31" t="inlineStr">
         <is>
+          <t>Note: the auto-fill in step 4 only recognizes an EXACT repeat of a description string. Recurring bills and subscriptions usually post with identical text every time, so those learn fast. If your bank appends a unique date or reference number to every line, matching won't catch it — you'll just pick the vendor again, same as the first time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
           <t>Note: the Dashboard's 'Top Expenses' and 'Recent Transactions' widgets only look at the Expenses tab (a limitation of ranking individual transactions across two separate tables) — everything else (KPIs, Budget, Vendor totals, charts, Cut-Back Analyzer) includes this tab.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="40" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
+    <row r="14" ht="40" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>Sign Convention for this import:</t>
         </is>
       </c>
-      <c r="D13" s="34" t="inlineStr">
+      <c r="D14" s="34" t="inlineStr">
         <is>
           <t>Negative = Expense</t>
         </is>
       </c>
-      <c r="E13" s="35" t="inlineStr">
+      <c r="E14" s="35" t="inlineStr">
         <is>
           <t>Most bank/debit exports show purchases as negative numbers (“Negative = Expense”). Most credit-card exports show charges as positive numbers and payments as negative (“Positive = Expense”). Check one real row against your bank statement to confirm.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="26" t="inlineStr">
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="26" t="inlineStr">
         <is>
           <t>Paste your CSV's Date / Description / Amount into columns A-C — Vendor (D) auto-fills from earlier rows when it recognizes the description</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n"/>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="n"/>
-      <c r="E15" s="2" t="n"/>
-      <c r="F15" s="2" t="n"/>
-      <c r="G15" s="2" t="n"/>
-      <c r="H15" s="2" t="n"/>
-      <c r="I15" s="2" t="n"/>
-      <c r="J15" s="2" t="n"/>
-      <c r="K15" s="2" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="36" t="inlineStr">
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="36" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B16" s="36" t="inlineStr">
+      <c r="B17" s="36" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C16" s="36" t="inlineStr">
+      <c r="C17" s="36" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="D16" s="36" t="inlineStr">
+      <c r="D17" s="36" t="inlineStr">
         <is>
           <t>VendorName</t>
         </is>
       </c>
-      <c r="E16" s="36" t="inlineStr">
+      <c r="E17" s="36" t="inlineStr">
         <is>
           <t>CategoryName</t>
         </is>
       </c>
-      <c r="F16" s="36" t="inlineStr">
+      <c r="F17" s="36" t="inlineStr">
         <is>
           <t>AccountName</t>
         </is>
       </c>
-      <c r="G16" s="36" t="inlineStr">
+      <c r="G17" s="36" t="inlineStr">
         <is>
           <t>PaymentMethod</t>
         </is>
       </c>
-      <c r="H16" s="36" t="inlineStr">
+      <c r="H17" s="36" t="inlineStr">
         <is>
           <t>TransactionType</t>
         </is>
       </c>
-      <c r="I16" s="36" t="inlineStr">
+      <c r="I17" s="36" t="inlineStr">
         <is>
           <t>AbsAmount</t>
         </is>
       </c>
-      <c r="J16" s="36" t="inlineStr">
+      <c r="J17" s="36" t="inlineStr">
         <is>
           <t>NeedWantFlag</t>
         </is>
       </c>
-      <c r="K16" s="36" t="inlineStr">
+      <c r="K17" s="36" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="37" t="n"/>
-      <c r="C17" s="27" t="n"/>
-      <c r="D17">
-        <f>""</f>
-        <v/>
-      </c>
-      <c r="E17">
-        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D17,Dim_Vendor[VendorName],0)),"")</f>
-        <v/>
-      </c>
-      <c r="H17">
-        <f>IF($C17="","",IF(SignConvention="Negative = Expense",IF($C17&lt;0,"Expense","Income"),IF($C17&gt;0,"Expense","Income")))</f>
-        <v/>
-      </c>
-      <c r="I17" s="27">
-        <f>IF($C17="","",ABS($C17))</f>
-        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="37" t="n"/>
       <c r="C18" s="27" t="n"/>
       <c r="D18">
-        <f>IF($B18="","",IFERROR(INDEX($D$17:$D$17,MATCH($B18,$B$17:$B$17,0)),""))</f>
+        <f>""</f>
         <v/>
       </c>
       <c r="E18">
@@ -31555,7 +31547,7 @@
       <c r="A19" s="37" t="n"/>
       <c r="C19" s="27" t="n"/>
       <c r="D19">
-        <f>IF($B19="","",IFERROR(INDEX($D$17:$D$18,MATCH($B19,$B$17:$B$18,0)),""))</f>
+        <f>IF($B19="","",IFERROR(INDEX($D$18:$D$18,MATCH($B19,$B$18:$B$18,0)),""))</f>
         <v/>
       </c>
       <c r="E19">
@@ -31575,7 +31567,7 @@
       <c r="A20" s="37" t="n"/>
       <c r="C20" s="27" t="n"/>
       <c r="D20">
-        <f>IF($B20="","",IFERROR(INDEX($D$17:$D$19,MATCH($B20,$B$17:$B$19,0)),""))</f>
+        <f>IF($B20="","",IFERROR(INDEX($D$18:$D$19,MATCH($B20,$B$18:$B$19,0)),""))</f>
         <v/>
       </c>
       <c r="E20">
@@ -31595,7 +31587,7 @@
       <c r="A21" s="37" t="n"/>
       <c r="C21" s="27" t="n"/>
       <c r="D21">
-        <f>IF($B21="","",IFERROR(INDEX($D$17:$D$20,MATCH($B21,$B$17:$B$20,0)),""))</f>
+        <f>IF($B21="","",IFERROR(INDEX($D$18:$D$20,MATCH($B21,$B$18:$B$20,0)),""))</f>
         <v/>
       </c>
       <c r="E21">
@@ -31615,7 +31607,7 @@
       <c r="A22" s="37" t="n"/>
       <c r="C22" s="27" t="n"/>
       <c r="D22">
-        <f>IF($B22="","",IFERROR(INDEX($D$17:$D$21,MATCH($B22,$B$17:$B$21,0)),""))</f>
+        <f>IF($B22="","",IFERROR(INDEX($D$18:$D$21,MATCH($B22,$B$18:$B$21,0)),""))</f>
         <v/>
       </c>
       <c r="E22">
@@ -31635,7 +31627,7 @@
       <c r="A23" s="37" t="n"/>
       <c r="C23" s="27" t="n"/>
       <c r="D23">
-        <f>IF($B23="","",IFERROR(INDEX($D$17:$D$22,MATCH($B23,$B$17:$B$22,0)),""))</f>
+        <f>IF($B23="","",IFERROR(INDEX($D$18:$D$22,MATCH($B23,$B$18:$B$22,0)),""))</f>
         <v/>
       </c>
       <c r="E23">
@@ -31655,7 +31647,7 @@
       <c r="A24" s="37" t="n"/>
       <c r="C24" s="27" t="n"/>
       <c r="D24">
-        <f>IF($B24="","",IFERROR(INDEX($D$17:$D$23,MATCH($B24,$B$17:$B$23,0)),""))</f>
+        <f>IF($B24="","",IFERROR(INDEX($D$18:$D$23,MATCH($B24,$B$18:$B$23,0)),""))</f>
         <v/>
       </c>
       <c r="E24">
@@ -31675,7 +31667,7 @@
       <c r="A25" s="37" t="n"/>
       <c r="C25" s="27" t="n"/>
       <c r="D25">
-        <f>IF($B25="","",IFERROR(INDEX($D$17:$D$24,MATCH($B25,$B$17:$B$24,0)),""))</f>
+        <f>IF($B25="","",IFERROR(INDEX($D$18:$D$24,MATCH($B25,$B$18:$B$24,0)),""))</f>
         <v/>
       </c>
       <c r="E25">
@@ -31695,7 +31687,7 @@
       <c r="A26" s="37" t="n"/>
       <c r="C26" s="27" t="n"/>
       <c r="D26">
-        <f>IF($B26="","",IFERROR(INDEX($D$17:$D$25,MATCH($B26,$B$17:$B$25,0)),""))</f>
+        <f>IF($B26="","",IFERROR(INDEX($D$18:$D$25,MATCH($B26,$B$18:$B$25,0)),""))</f>
         <v/>
       </c>
       <c r="E26">
@@ -31715,7 +31707,7 @@
       <c r="A27" s="37" t="n"/>
       <c r="C27" s="27" t="n"/>
       <c r="D27">
-        <f>IF($B27="","",IFERROR(INDEX($D$17:$D$26,MATCH($B27,$B$17:$B$26,0)),""))</f>
+        <f>IF($B27="","",IFERROR(INDEX($D$18:$D$26,MATCH($B27,$B$18:$B$26,0)),""))</f>
         <v/>
       </c>
       <c r="E27">
@@ -31735,7 +31727,7 @@
       <c r="A28" s="37" t="n"/>
       <c r="C28" s="27" t="n"/>
       <c r="D28">
-        <f>IF($B28="","",IFERROR(INDEX($D$17:$D$27,MATCH($B28,$B$17:$B$27,0)),""))</f>
+        <f>IF($B28="","",IFERROR(INDEX($D$18:$D$27,MATCH($B28,$B$18:$B$27,0)),""))</f>
         <v/>
       </c>
       <c r="E28">
@@ -31755,7 +31747,7 @@
       <c r="A29" s="37" t="n"/>
       <c r="C29" s="27" t="n"/>
       <c r="D29">
-        <f>IF($B29="","",IFERROR(INDEX($D$17:$D$28,MATCH($B29,$B$17:$B$28,0)),""))</f>
+        <f>IF($B29="","",IFERROR(INDEX($D$18:$D$28,MATCH($B29,$B$18:$B$28,0)),""))</f>
         <v/>
       </c>
       <c r="E29">
@@ -31775,7 +31767,7 @@
       <c r="A30" s="37" t="n"/>
       <c r="C30" s="27" t="n"/>
       <c r="D30">
-        <f>IF($B30="","",IFERROR(INDEX($D$17:$D$29,MATCH($B30,$B$17:$B$29,0)),""))</f>
+        <f>IF($B30="","",IFERROR(INDEX($D$18:$D$29,MATCH($B30,$B$18:$B$29,0)),""))</f>
         <v/>
       </c>
       <c r="E30">
@@ -31795,7 +31787,7 @@
       <c r="A31" s="37" t="n"/>
       <c r="C31" s="27" t="n"/>
       <c r="D31">
-        <f>IF($B31="","",IFERROR(INDEX($D$17:$D$30,MATCH($B31,$B$17:$B$30,0)),""))</f>
+        <f>IF($B31="","",IFERROR(INDEX($D$18:$D$30,MATCH($B31,$B$18:$B$30,0)),""))</f>
         <v/>
       </c>
       <c r="E31">
@@ -31815,7 +31807,7 @@
       <c r="A32" s="37" t="n"/>
       <c r="C32" s="27" t="n"/>
       <c r="D32">
-        <f>IF($B32="","",IFERROR(INDEX($D$17:$D$31,MATCH($B32,$B$17:$B$31,0)),""))</f>
+        <f>IF($B32="","",IFERROR(INDEX($D$18:$D$31,MATCH($B32,$B$18:$B$31,0)),""))</f>
         <v/>
       </c>
       <c r="E32">
@@ -31835,7 +31827,7 @@
       <c r="A33" s="37" t="n"/>
       <c r="C33" s="27" t="n"/>
       <c r="D33">
-        <f>IF($B33="","",IFERROR(INDEX($D$17:$D$32,MATCH($B33,$B$17:$B$32,0)),""))</f>
+        <f>IF($B33="","",IFERROR(INDEX($D$18:$D$32,MATCH($B33,$B$18:$B$32,0)),""))</f>
         <v/>
       </c>
       <c r="E33">
@@ -31855,7 +31847,7 @@
       <c r="A34" s="37" t="n"/>
       <c r="C34" s="27" t="n"/>
       <c r="D34">
-        <f>IF($B34="","",IFERROR(INDEX($D$17:$D$33,MATCH($B34,$B$17:$B$33,0)),""))</f>
+        <f>IF($B34="","",IFERROR(INDEX($D$18:$D$33,MATCH($B34,$B$18:$B$33,0)),""))</f>
         <v/>
       </c>
       <c r="E34">
@@ -31875,7 +31867,7 @@
       <c r="A35" s="37" t="n"/>
       <c r="C35" s="27" t="n"/>
       <c r="D35">
-        <f>IF($B35="","",IFERROR(INDEX($D$17:$D$34,MATCH($B35,$B$17:$B$34,0)),""))</f>
+        <f>IF($B35="","",IFERROR(INDEX($D$18:$D$34,MATCH($B35,$B$18:$B$34,0)),""))</f>
         <v/>
       </c>
       <c r="E35">
@@ -31895,7 +31887,7 @@
       <c r="A36" s="37" t="n"/>
       <c r="C36" s="27" t="n"/>
       <c r="D36">
-        <f>IF($B36="","",IFERROR(INDEX($D$17:$D$35,MATCH($B36,$B$17:$B$35,0)),""))</f>
+        <f>IF($B36="","",IFERROR(INDEX($D$18:$D$35,MATCH($B36,$B$18:$B$35,0)),""))</f>
         <v/>
       </c>
       <c r="E36">
@@ -31915,7 +31907,7 @@
       <c r="A37" s="37" t="n"/>
       <c r="C37" s="27" t="n"/>
       <c r="D37">
-        <f>IF($B37="","",IFERROR(INDEX($D$17:$D$36,MATCH($B37,$B$17:$B$36,0)),""))</f>
+        <f>IF($B37="","",IFERROR(INDEX($D$18:$D$36,MATCH($B37,$B$18:$B$36,0)),""))</f>
         <v/>
       </c>
       <c r="E37">
@@ -31935,7 +31927,7 @@
       <c r="A38" s="37" t="n"/>
       <c r="C38" s="27" t="n"/>
       <c r="D38">
-        <f>IF($B38="","",IFERROR(INDEX($D$17:$D$37,MATCH($B38,$B$17:$B$37,0)),""))</f>
+        <f>IF($B38="","",IFERROR(INDEX($D$18:$D$37,MATCH($B38,$B$18:$B$37,0)),""))</f>
         <v/>
       </c>
       <c r="E38">
@@ -31955,7 +31947,7 @@
       <c r="A39" s="37" t="n"/>
       <c r="C39" s="27" t="n"/>
       <c r="D39">
-        <f>IF($B39="","",IFERROR(INDEX($D$17:$D$38,MATCH($B39,$B$17:$B$38,0)),""))</f>
+        <f>IF($B39="","",IFERROR(INDEX($D$18:$D$38,MATCH($B39,$B$18:$B$38,0)),""))</f>
         <v/>
       </c>
       <c r="E39">
@@ -31975,7 +31967,7 @@
       <c r="A40" s="37" t="n"/>
       <c r="C40" s="27" t="n"/>
       <c r="D40">
-        <f>IF($B40="","",IFERROR(INDEX($D$17:$D$39,MATCH($B40,$B$17:$B$39,0)),""))</f>
+        <f>IF($B40="","",IFERROR(INDEX($D$18:$D$39,MATCH($B40,$B$18:$B$39,0)),""))</f>
         <v/>
       </c>
       <c r="E40">
@@ -31995,7 +31987,7 @@
       <c r="A41" s="37" t="n"/>
       <c r="C41" s="27" t="n"/>
       <c r="D41">
-        <f>IF($B41="","",IFERROR(INDEX($D$17:$D$40,MATCH($B41,$B$17:$B$40,0)),""))</f>
+        <f>IF($B41="","",IFERROR(INDEX($D$18:$D$40,MATCH($B41,$B$18:$B$40,0)),""))</f>
         <v/>
       </c>
       <c r="E41">
@@ -32015,7 +32007,7 @@
       <c r="A42" s="37" t="n"/>
       <c r="C42" s="27" t="n"/>
       <c r="D42">
-        <f>IF($B42="","",IFERROR(INDEX($D$17:$D$41,MATCH($B42,$B$17:$B$41,0)),""))</f>
+        <f>IF($B42="","",IFERROR(INDEX($D$18:$D$41,MATCH($B42,$B$18:$B$41,0)),""))</f>
         <v/>
       </c>
       <c r="E42">
@@ -32035,7 +32027,7 @@
       <c r="A43" s="37" t="n"/>
       <c r="C43" s="27" t="n"/>
       <c r="D43">
-        <f>IF($B43="","",IFERROR(INDEX($D$17:$D$42,MATCH($B43,$B$17:$B$42,0)),""))</f>
+        <f>IF($B43="","",IFERROR(INDEX($D$18:$D$42,MATCH($B43,$B$18:$B$42,0)),""))</f>
         <v/>
       </c>
       <c r="E43">
@@ -32055,7 +32047,7 @@
       <c r="A44" s="37" t="n"/>
       <c r="C44" s="27" t="n"/>
       <c r="D44">
-        <f>IF($B44="","",IFERROR(INDEX($D$17:$D$43,MATCH($B44,$B$17:$B$43,0)),""))</f>
+        <f>IF($B44="","",IFERROR(INDEX($D$18:$D$43,MATCH($B44,$B$18:$B$43,0)),""))</f>
         <v/>
       </c>
       <c r="E44">
@@ -32075,7 +32067,7 @@
       <c r="A45" s="37" t="n"/>
       <c r="C45" s="27" t="n"/>
       <c r="D45">
-        <f>IF($B45="","",IFERROR(INDEX($D$17:$D$44,MATCH($B45,$B$17:$B$44,0)),""))</f>
+        <f>IF($B45="","",IFERROR(INDEX($D$18:$D$44,MATCH($B45,$B$18:$B$44,0)),""))</f>
         <v/>
       </c>
       <c r="E45">
@@ -32095,7 +32087,7 @@
       <c r="A46" s="37" t="n"/>
       <c r="C46" s="27" t="n"/>
       <c r="D46">
-        <f>IF($B46="","",IFERROR(INDEX($D$17:$D$45,MATCH($B46,$B$17:$B$45,0)),""))</f>
+        <f>IF($B46="","",IFERROR(INDEX($D$18:$D$45,MATCH($B46,$B$18:$B$45,0)),""))</f>
         <v/>
       </c>
       <c r="E46">
@@ -32115,7 +32107,7 @@
       <c r="A47" s="37" t="n"/>
       <c r="C47" s="27" t="n"/>
       <c r="D47">
-        <f>IF($B47="","",IFERROR(INDEX($D$17:$D$46,MATCH($B47,$B$17:$B$46,0)),""))</f>
+        <f>IF($B47="","",IFERROR(INDEX($D$18:$D$46,MATCH($B47,$B$18:$B$46,0)),""))</f>
         <v/>
       </c>
       <c r="E47">
@@ -32135,7 +32127,7 @@
       <c r="A48" s="37" t="n"/>
       <c r="C48" s="27" t="n"/>
       <c r="D48">
-        <f>IF($B48="","",IFERROR(INDEX($D$17:$D$47,MATCH($B48,$B$17:$B$47,0)),""))</f>
+        <f>IF($B48="","",IFERROR(INDEX($D$18:$D$47,MATCH($B48,$B$18:$B$47,0)),""))</f>
         <v/>
       </c>
       <c r="E48">
@@ -32155,7 +32147,7 @@
       <c r="A49" s="37" t="n"/>
       <c r="C49" s="27" t="n"/>
       <c r="D49">
-        <f>IF($B49="","",IFERROR(INDEX($D$17:$D$48,MATCH($B49,$B$17:$B$48,0)),""))</f>
+        <f>IF($B49="","",IFERROR(INDEX($D$18:$D$48,MATCH($B49,$B$18:$B$48,0)),""))</f>
         <v/>
       </c>
       <c r="E49">
@@ -32175,7 +32167,7 @@
       <c r="A50" s="37" t="n"/>
       <c r="C50" s="27" t="n"/>
       <c r="D50">
-        <f>IF($B50="","",IFERROR(INDEX($D$17:$D$49,MATCH($B50,$B$17:$B$49,0)),""))</f>
+        <f>IF($B50="","",IFERROR(INDEX($D$18:$D$49,MATCH($B50,$B$18:$B$49,0)),""))</f>
         <v/>
       </c>
       <c r="E50">
@@ -32195,7 +32187,7 @@
       <c r="A51" s="37" t="n"/>
       <c r="C51" s="27" t="n"/>
       <c r="D51">
-        <f>IF($B51="","",IFERROR(INDEX($D$17:$D$50,MATCH($B51,$B$17:$B$50,0)),""))</f>
+        <f>IF($B51="","",IFERROR(INDEX($D$18:$D$50,MATCH($B51,$B$18:$B$50,0)),""))</f>
         <v/>
       </c>
       <c r="E51">
@@ -32215,7 +32207,7 @@
       <c r="A52" s="37" t="n"/>
       <c r="C52" s="27" t="n"/>
       <c r="D52">
-        <f>IF($B52="","",IFERROR(INDEX($D$17:$D$51,MATCH($B52,$B$17:$B$51,0)),""))</f>
+        <f>IF($B52="","",IFERROR(INDEX($D$18:$D$51,MATCH($B52,$B$18:$B$51,0)),""))</f>
         <v/>
       </c>
       <c r="E52">
@@ -32235,7 +32227,7 @@
       <c r="A53" s="37" t="n"/>
       <c r="C53" s="27" t="n"/>
       <c r="D53">
-        <f>IF($B53="","",IFERROR(INDEX($D$17:$D$52,MATCH($B53,$B$17:$B$52,0)),""))</f>
+        <f>IF($B53="","",IFERROR(INDEX($D$18:$D$52,MATCH($B53,$B$18:$B$52,0)),""))</f>
         <v/>
       </c>
       <c r="E53">
@@ -32255,7 +32247,7 @@
       <c r="A54" s="37" t="n"/>
       <c r="C54" s="27" t="n"/>
       <c r="D54">
-        <f>IF($B54="","",IFERROR(INDEX($D$17:$D$53,MATCH($B54,$B$17:$B$53,0)),""))</f>
+        <f>IF($B54="","",IFERROR(INDEX($D$18:$D$53,MATCH($B54,$B$18:$B$53,0)),""))</f>
         <v/>
       </c>
       <c r="E54">
@@ -32275,7 +32267,7 @@
       <c r="A55" s="37" t="n"/>
       <c r="C55" s="27" t="n"/>
       <c r="D55">
-        <f>IF($B55="","",IFERROR(INDEX($D$17:$D$54,MATCH($B55,$B$17:$B$54,0)),""))</f>
+        <f>IF($B55="","",IFERROR(INDEX($D$18:$D$54,MATCH($B55,$B$18:$B$54,0)),""))</f>
         <v/>
       </c>
       <c r="E55">
@@ -32295,7 +32287,7 @@
       <c r="A56" s="37" t="n"/>
       <c r="C56" s="27" t="n"/>
       <c r="D56">
-        <f>IF($B56="","",IFERROR(INDEX($D$17:$D$55,MATCH($B56,$B$17:$B$55,0)),""))</f>
+        <f>IF($B56="","",IFERROR(INDEX($D$18:$D$55,MATCH($B56,$B$18:$B$55,0)),""))</f>
         <v/>
       </c>
       <c r="E56">
@@ -32315,7 +32307,7 @@
       <c r="A57" s="37" t="n"/>
       <c r="C57" s="27" t="n"/>
       <c r="D57">
-        <f>IF($B57="","",IFERROR(INDEX($D$17:$D$56,MATCH($B57,$B$17:$B$56,0)),""))</f>
+        <f>IF($B57="","",IFERROR(INDEX($D$18:$D$56,MATCH($B57,$B$18:$B$56,0)),""))</f>
         <v/>
       </c>
       <c r="E57">
@@ -32335,7 +32327,7 @@
       <c r="A58" s="37" t="n"/>
       <c r="C58" s="27" t="n"/>
       <c r="D58">
-        <f>IF($B58="","",IFERROR(INDEX($D$17:$D$57,MATCH($B58,$B$17:$B$57,0)),""))</f>
+        <f>IF($B58="","",IFERROR(INDEX($D$18:$D$57,MATCH($B58,$B$18:$B$57,0)),""))</f>
         <v/>
       </c>
       <c r="E58">
@@ -32355,7 +32347,7 @@
       <c r="A59" s="37" t="n"/>
       <c r="C59" s="27" t="n"/>
       <c r="D59">
-        <f>IF($B59="","",IFERROR(INDEX($D$17:$D$58,MATCH($B59,$B$17:$B$58,0)),""))</f>
+        <f>IF($B59="","",IFERROR(INDEX($D$18:$D$58,MATCH($B59,$B$18:$B$58,0)),""))</f>
         <v/>
       </c>
       <c r="E59">
@@ -32375,7 +32367,7 @@
       <c r="A60" s="37" t="n"/>
       <c r="C60" s="27" t="n"/>
       <c r="D60">
-        <f>IF($B60="","",IFERROR(INDEX($D$17:$D$59,MATCH($B60,$B$17:$B$59,0)),""))</f>
+        <f>IF($B60="","",IFERROR(INDEX($D$18:$D$59,MATCH($B60,$B$18:$B$59,0)),""))</f>
         <v/>
       </c>
       <c r="E60">
@@ -32395,7 +32387,7 @@
       <c r="A61" s="37" t="n"/>
       <c r="C61" s="27" t="n"/>
       <c r="D61">
-        <f>IF($B61="","",IFERROR(INDEX($D$17:$D$60,MATCH($B61,$B$17:$B$60,0)),""))</f>
+        <f>IF($B61="","",IFERROR(INDEX($D$18:$D$60,MATCH($B61,$B$18:$B$60,0)),""))</f>
         <v/>
       </c>
       <c r="E61">
@@ -32415,7 +32407,7 @@
       <c r="A62" s="37" t="n"/>
       <c r="C62" s="27" t="n"/>
       <c r="D62">
-        <f>IF($B62="","",IFERROR(INDEX($D$17:$D$61,MATCH($B62,$B$17:$B$61,0)),""))</f>
+        <f>IF($B62="","",IFERROR(INDEX($D$18:$D$61,MATCH($B62,$B$18:$B$61,0)),""))</f>
         <v/>
       </c>
       <c r="E62">
@@ -32435,7 +32427,7 @@
       <c r="A63" s="37" t="n"/>
       <c r="C63" s="27" t="n"/>
       <c r="D63">
-        <f>IF($B63="","",IFERROR(INDEX($D$17:$D$62,MATCH($B63,$B$17:$B$62,0)),""))</f>
+        <f>IF($B63="","",IFERROR(INDEX($D$18:$D$62,MATCH($B63,$B$18:$B$62,0)),""))</f>
         <v/>
       </c>
       <c r="E63">
@@ -32455,7 +32447,7 @@
       <c r="A64" s="37" t="n"/>
       <c r="C64" s="27" t="n"/>
       <c r="D64">
-        <f>IF($B64="","",IFERROR(INDEX($D$17:$D$63,MATCH($B64,$B$17:$B$63,0)),""))</f>
+        <f>IF($B64="","",IFERROR(INDEX($D$18:$D$63,MATCH($B64,$B$18:$B$63,0)),""))</f>
         <v/>
       </c>
       <c r="E64">
@@ -32475,7 +32467,7 @@
       <c r="A65" s="37" t="n"/>
       <c r="C65" s="27" t="n"/>
       <c r="D65">
-        <f>IF($B65="","",IFERROR(INDEX($D$17:$D$64,MATCH($B65,$B$17:$B$64,0)),""))</f>
+        <f>IF($B65="","",IFERROR(INDEX($D$18:$D$64,MATCH($B65,$B$18:$B$64,0)),""))</f>
         <v/>
       </c>
       <c r="E65">
@@ -32495,7 +32487,7 @@
       <c r="A66" s="37" t="n"/>
       <c r="C66" s="27" t="n"/>
       <c r="D66">
-        <f>IF($B66="","",IFERROR(INDEX($D$17:$D$65,MATCH($B66,$B$17:$B$65,0)),""))</f>
+        <f>IF($B66="","",IFERROR(INDEX($D$18:$D$65,MATCH($B66,$B$18:$B$65,0)),""))</f>
         <v/>
       </c>
       <c r="E66">
@@ -32515,7 +32507,7 @@
       <c r="A67" s="37" t="n"/>
       <c r="C67" s="27" t="n"/>
       <c r="D67">
-        <f>IF($B67="","",IFERROR(INDEX($D$17:$D$66,MATCH($B67,$B$17:$B$66,0)),""))</f>
+        <f>IF($B67="","",IFERROR(INDEX($D$18:$D$66,MATCH($B67,$B$18:$B$66,0)),""))</f>
         <v/>
       </c>
       <c r="E67">
@@ -32535,7 +32527,7 @@
       <c r="A68" s="37" t="n"/>
       <c r="C68" s="27" t="n"/>
       <c r="D68">
-        <f>IF($B68="","",IFERROR(INDEX($D$17:$D$67,MATCH($B68,$B$17:$B$67,0)),""))</f>
+        <f>IF($B68="","",IFERROR(INDEX($D$18:$D$67,MATCH($B68,$B$18:$B$67,0)),""))</f>
         <v/>
       </c>
       <c r="E68">
@@ -32555,7 +32547,7 @@
       <c r="A69" s="37" t="n"/>
       <c r="C69" s="27" t="n"/>
       <c r="D69">
-        <f>IF($B69="","",IFERROR(INDEX($D$17:$D$68,MATCH($B69,$B$17:$B$68,0)),""))</f>
+        <f>IF($B69="","",IFERROR(INDEX($D$18:$D$68,MATCH($B69,$B$18:$B$68,0)),""))</f>
         <v/>
       </c>
       <c r="E69">
@@ -32575,7 +32567,7 @@
       <c r="A70" s="37" t="n"/>
       <c r="C70" s="27" t="n"/>
       <c r="D70">
-        <f>IF($B70="","",IFERROR(INDEX($D$17:$D$69,MATCH($B70,$B$17:$B$69,0)),""))</f>
+        <f>IF($B70="","",IFERROR(INDEX($D$18:$D$69,MATCH($B70,$B$18:$B$69,0)),""))</f>
         <v/>
       </c>
       <c r="E70">
@@ -32595,7 +32587,7 @@
       <c r="A71" s="37" t="n"/>
       <c r="C71" s="27" t="n"/>
       <c r="D71">
-        <f>IF($B71="","",IFERROR(INDEX($D$17:$D$70,MATCH($B71,$B$17:$B$70,0)),""))</f>
+        <f>IF($B71="","",IFERROR(INDEX($D$18:$D$70,MATCH($B71,$B$18:$B$70,0)),""))</f>
         <v/>
       </c>
       <c r="E71">
@@ -32615,7 +32607,7 @@
       <c r="A72" s="37" t="n"/>
       <c r="C72" s="27" t="n"/>
       <c r="D72">
-        <f>IF($B72="","",IFERROR(INDEX($D$17:$D$71,MATCH($B72,$B$17:$B$71,0)),""))</f>
+        <f>IF($B72="","",IFERROR(INDEX($D$18:$D$71,MATCH($B72,$B$18:$B$71,0)),""))</f>
         <v/>
       </c>
       <c r="E72">
@@ -32635,7 +32627,7 @@
       <c r="A73" s="37" t="n"/>
       <c r="C73" s="27" t="n"/>
       <c r="D73">
-        <f>IF($B73="","",IFERROR(INDEX($D$17:$D$72,MATCH($B73,$B$17:$B$72,0)),""))</f>
+        <f>IF($B73="","",IFERROR(INDEX($D$18:$D$72,MATCH($B73,$B$18:$B$72,0)),""))</f>
         <v/>
       </c>
       <c r="E73">
@@ -32655,7 +32647,7 @@
       <c r="A74" s="37" t="n"/>
       <c r="C74" s="27" t="n"/>
       <c r="D74">
-        <f>IF($B74="","",IFERROR(INDEX($D$17:$D$73,MATCH($B74,$B$17:$B$73,0)),""))</f>
+        <f>IF($B74="","",IFERROR(INDEX($D$18:$D$73,MATCH($B74,$B$18:$B$73,0)),""))</f>
         <v/>
       </c>
       <c r="E74">
@@ -32675,7 +32667,7 @@
       <c r="A75" s="37" t="n"/>
       <c r="C75" s="27" t="n"/>
       <c r="D75">
-        <f>IF($B75="","",IFERROR(INDEX($D$17:$D$74,MATCH($B75,$B$17:$B$74,0)),""))</f>
+        <f>IF($B75="","",IFERROR(INDEX($D$18:$D$74,MATCH($B75,$B$18:$B$74,0)),""))</f>
         <v/>
       </c>
       <c r="E75">
@@ -32695,7 +32687,7 @@
       <c r="A76" s="37" t="n"/>
       <c r="C76" s="27" t="n"/>
       <c r="D76">
-        <f>IF($B76="","",IFERROR(INDEX($D$17:$D$75,MATCH($B76,$B$17:$B$75,0)),""))</f>
+        <f>IF($B76="","",IFERROR(INDEX($D$18:$D$75,MATCH($B76,$B$18:$B$75,0)),""))</f>
         <v/>
       </c>
       <c r="E76">
@@ -32715,7 +32707,7 @@
       <c r="A77" s="37" t="n"/>
       <c r="C77" s="27" t="n"/>
       <c r="D77">
-        <f>IF($B77="","",IFERROR(INDEX($D$17:$D$76,MATCH($B77,$B$17:$B$76,0)),""))</f>
+        <f>IF($B77="","",IFERROR(INDEX($D$18:$D$76,MATCH($B77,$B$18:$B$76,0)),""))</f>
         <v/>
       </c>
       <c r="E77">
@@ -32735,7 +32727,7 @@
       <c r="A78" s="37" t="n"/>
       <c r="C78" s="27" t="n"/>
       <c r="D78">
-        <f>IF($B78="","",IFERROR(INDEX($D$17:$D$77,MATCH($B78,$B$17:$B$77,0)),""))</f>
+        <f>IF($B78="","",IFERROR(INDEX($D$18:$D$77,MATCH($B78,$B$18:$B$77,0)),""))</f>
         <v/>
       </c>
       <c r="E78">
@@ -32755,7 +32747,7 @@
       <c r="A79" s="37" t="n"/>
       <c r="C79" s="27" t="n"/>
       <c r="D79">
-        <f>IF($B79="","",IFERROR(INDEX($D$17:$D$78,MATCH($B79,$B$17:$B$78,0)),""))</f>
+        <f>IF($B79="","",IFERROR(INDEX($D$18:$D$78,MATCH($B79,$B$18:$B$78,0)),""))</f>
         <v/>
       </c>
       <c r="E79">
@@ -32775,7 +32767,7 @@
       <c r="A80" s="37" t="n"/>
       <c r="C80" s="27" t="n"/>
       <c r="D80">
-        <f>IF($B80="","",IFERROR(INDEX($D$17:$D$79,MATCH($B80,$B$17:$B$79,0)),""))</f>
+        <f>IF($B80="","",IFERROR(INDEX($D$18:$D$79,MATCH($B80,$B$18:$B$79,0)),""))</f>
         <v/>
       </c>
       <c r="E80">
@@ -32795,7 +32787,7 @@
       <c r="A81" s="37" t="n"/>
       <c r="C81" s="27" t="n"/>
       <c r="D81">
-        <f>IF($B81="","",IFERROR(INDEX($D$17:$D$80,MATCH($B81,$B$17:$B$80,0)),""))</f>
+        <f>IF($B81="","",IFERROR(INDEX($D$18:$D$80,MATCH($B81,$B$18:$B$80,0)),""))</f>
         <v/>
       </c>
       <c r="E81">
@@ -32815,7 +32807,7 @@
       <c r="A82" s="37" t="n"/>
       <c r="C82" s="27" t="n"/>
       <c r="D82">
-        <f>IF($B82="","",IFERROR(INDEX($D$17:$D$81,MATCH($B82,$B$17:$B$81,0)),""))</f>
+        <f>IF($B82="","",IFERROR(INDEX($D$18:$D$81,MATCH($B82,$B$18:$B$81,0)),""))</f>
         <v/>
       </c>
       <c r="E82">
@@ -32835,7 +32827,7 @@
       <c r="A83" s="37" t="n"/>
       <c r="C83" s="27" t="n"/>
       <c r="D83">
-        <f>IF($B83="","",IFERROR(INDEX($D$17:$D$82,MATCH($B83,$B$17:$B$82,0)),""))</f>
+        <f>IF($B83="","",IFERROR(INDEX($D$18:$D$82,MATCH($B83,$B$18:$B$82,0)),""))</f>
         <v/>
       </c>
       <c r="E83">
@@ -32855,7 +32847,7 @@
       <c r="A84" s="37" t="n"/>
       <c r="C84" s="27" t="n"/>
       <c r="D84">
-        <f>IF($B84="","",IFERROR(INDEX($D$17:$D$83,MATCH($B84,$B$17:$B$83,0)),""))</f>
+        <f>IF($B84="","",IFERROR(INDEX($D$18:$D$83,MATCH($B84,$B$18:$B$83,0)),""))</f>
         <v/>
       </c>
       <c r="E84">
@@ -32875,7 +32867,7 @@
       <c r="A85" s="37" t="n"/>
       <c r="C85" s="27" t="n"/>
       <c r="D85">
-        <f>IF($B85="","",IFERROR(INDEX($D$17:$D$84,MATCH($B85,$B$17:$B$84,0)),""))</f>
+        <f>IF($B85="","",IFERROR(INDEX($D$18:$D$84,MATCH($B85,$B$18:$B$84,0)),""))</f>
         <v/>
       </c>
       <c r="E85">
@@ -32895,7 +32887,7 @@
       <c r="A86" s="37" t="n"/>
       <c r="C86" s="27" t="n"/>
       <c r="D86">
-        <f>IF($B86="","",IFERROR(INDEX($D$17:$D$85,MATCH($B86,$B$17:$B$85,0)),""))</f>
+        <f>IF($B86="","",IFERROR(INDEX($D$18:$D$85,MATCH($B86,$B$18:$B$85,0)),""))</f>
         <v/>
       </c>
       <c r="E86">
@@ -32915,7 +32907,7 @@
       <c r="A87" s="37" t="n"/>
       <c r="C87" s="27" t="n"/>
       <c r="D87">
-        <f>IF($B87="","",IFERROR(INDEX($D$17:$D$86,MATCH($B87,$B$17:$B$86,0)),""))</f>
+        <f>IF($B87="","",IFERROR(INDEX($D$18:$D$86,MATCH($B87,$B$18:$B$86,0)),""))</f>
         <v/>
       </c>
       <c r="E87">
@@ -32935,7 +32927,7 @@
       <c r="A88" s="37" t="n"/>
       <c r="C88" s="27" t="n"/>
       <c r="D88">
-        <f>IF($B88="","",IFERROR(INDEX($D$17:$D$87,MATCH($B88,$B$17:$B$87,0)),""))</f>
+        <f>IF($B88="","",IFERROR(INDEX($D$18:$D$87,MATCH($B88,$B$18:$B$87,0)),""))</f>
         <v/>
       </c>
       <c r="E88">
@@ -32955,7 +32947,7 @@
       <c r="A89" s="37" t="n"/>
       <c r="C89" s="27" t="n"/>
       <c r="D89">
-        <f>IF($B89="","",IFERROR(INDEX($D$17:$D$88,MATCH($B89,$B$17:$B$88,0)),""))</f>
+        <f>IF($B89="","",IFERROR(INDEX($D$18:$D$88,MATCH($B89,$B$18:$B$88,0)),""))</f>
         <v/>
       </c>
       <c r="E89">
@@ -32975,7 +32967,7 @@
       <c r="A90" s="37" t="n"/>
       <c r="C90" s="27" t="n"/>
       <c r="D90">
-        <f>IF($B90="","",IFERROR(INDEX($D$17:$D$89,MATCH($B90,$B$17:$B$89,0)),""))</f>
+        <f>IF($B90="","",IFERROR(INDEX($D$18:$D$89,MATCH($B90,$B$18:$B$89,0)),""))</f>
         <v/>
       </c>
       <c r="E90">
@@ -32995,7 +32987,7 @@
       <c r="A91" s="37" t="n"/>
       <c r="C91" s="27" t="n"/>
       <c r="D91">
-        <f>IF($B91="","",IFERROR(INDEX($D$17:$D$90,MATCH($B91,$B$17:$B$90,0)),""))</f>
+        <f>IF($B91="","",IFERROR(INDEX($D$18:$D$90,MATCH($B91,$B$18:$B$90,0)),""))</f>
         <v/>
       </c>
       <c r="E91">
@@ -33015,7 +33007,7 @@
       <c r="A92" s="37" t="n"/>
       <c r="C92" s="27" t="n"/>
       <c r="D92">
-        <f>IF($B92="","",IFERROR(INDEX($D$17:$D$91,MATCH($B92,$B$17:$B$91,0)),""))</f>
+        <f>IF($B92="","",IFERROR(INDEX($D$18:$D$91,MATCH($B92,$B$18:$B$91,0)),""))</f>
         <v/>
       </c>
       <c r="E92">
@@ -33035,7 +33027,7 @@
       <c r="A93" s="37" t="n"/>
       <c r="C93" s="27" t="n"/>
       <c r="D93">
-        <f>IF($B93="","",IFERROR(INDEX($D$17:$D$92,MATCH($B93,$B$17:$B$92,0)),""))</f>
+        <f>IF($B93="","",IFERROR(INDEX($D$18:$D$92,MATCH($B93,$B$18:$B$92,0)),""))</f>
         <v/>
       </c>
       <c r="E93">
@@ -33055,7 +33047,7 @@
       <c r="A94" s="37" t="n"/>
       <c r="C94" s="27" t="n"/>
       <c r="D94">
-        <f>IF($B94="","",IFERROR(INDEX($D$17:$D$93,MATCH($B94,$B$17:$B$93,0)),""))</f>
+        <f>IF($B94="","",IFERROR(INDEX($D$18:$D$93,MATCH($B94,$B$18:$B$93,0)),""))</f>
         <v/>
       </c>
       <c r="E94">
@@ -33075,7 +33067,7 @@
       <c r="A95" s="37" t="n"/>
       <c r="C95" s="27" t="n"/>
       <c r="D95">
-        <f>IF($B95="","",IFERROR(INDEX($D$17:$D$94,MATCH($B95,$B$17:$B$94,0)),""))</f>
+        <f>IF($B95="","",IFERROR(INDEX($D$18:$D$94,MATCH($B95,$B$18:$B$94,0)),""))</f>
         <v/>
       </c>
       <c r="E95">
@@ -33095,7 +33087,7 @@
       <c r="A96" s="37" t="n"/>
       <c r="C96" s="27" t="n"/>
       <c r="D96">
-        <f>IF($B96="","",IFERROR(INDEX($D$17:$D$95,MATCH($B96,$B$17:$B$95,0)),""))</f>
+        <f>IF($B96="","",IFERROR(INDEX($D$18:$D$95,MATCH($B96,$B$18:$B$95,0)),""))</f>
         <v/>
       </c>
       <c r="E96">
@@ -33115,7 +33107,7 @@
       <c r="A97" s="37" t="n"/>
       <c r="C97" s="27" t="n"/>
       <c r="D97">
-        <f>IF($B97="","",IFERROR(INDEX($D$17:$D$96,MATCH($B97,$B$17:$B$96,0)),""))</f>
+        <f>IF($B97="","",IFERROR(INDEX($D$18:$D$96,MATCH($B97,$B$18:$B$96,0)),""))</f>
         <v/>
       </c>
       <c r="E97">
@@ -33135,7 +33127,7 @@
       <c r="A98" s="37" t="n"/>
       <c r="C98" s="27" t="n"/>
       <c r="D98">
-        <f>IF($B98="","",IFERROR(INDEX($D$17:$D$97,MATCH($B98,$B$17:$B$97,0)),""))</f>
+        <f>IF($B98="","",IFERROR(INDEX($D$18:$D$97,MATCH($B98,$B$18:$B$97,0)),""))</f>
         <v/>
       </c>
       <c r="E98">
@@ -33155,7 +33147,7 @@
       <c r="A99" s="37" t="n"/>
       <c r="C99" s="27" t="n"/>
       <c r="D99">
-        <f>IF($B99="","",IFERROR(INDEX($D$17:$D$98,MATCH($B99,$B$17:$B$98,0)),""))</f>
+        <f>IF($B99="","",IFERROR(INDEX($D$18:$D$98,MATCH($B99,$B$18:$B$98,0)),""))</f>
         <v/>
       </c>
       <c r="E99">
@@ -33175,7 +33167,7 @@
       <c r="A100" s="37" t="n"/>
       <c r="C100" s="27" t="n"/>
       <c r="D100">
-        <f>IF($B100="","",IFERROR(INDEX($D$17:$D$99,MATCH($B100,$B$17:$B$99,0)),""))</f>
+        <f>IF($B100="","",IFERROR(INDEX($D$18:$D$99,MATCH($B100,$B$18:$B$99,0)),""))</f>
         <v/>
       </c>
       <c r="E100">
@@ -33195,7 +33187,7 @@
       <c r="A101" s="37" t="n"/>
       <c r="C101" s="27" t="n"/>
       <c r="D101">
-        <f>IF($B101="","",IFERROR(INDEX($D$17:$D$100,MATCH($B101,$B$17:$B$100,0)),""))</f>
+        <f>IF($B101="","",IFERROR(INDEX($D$18:$D$100,MATCH($B101,$B$18:$B$100,0)),""))</f>
         <v/>
       </c>
       <c r="E101">
@@ -33215,7 +33207,7 @@
       <c r="A102" s="37" t="n"/>
       <c r="C102" s="27" t="n"/>
       <c r="D102">
-        <f>IF($B102="","",IFERROR(INDEX($D$17:$D$101,MATCH($B102,$B$17:$B$101,0)),""))</f>
+        <f>IF($B102="","",IFERROR(INDEX($D$18:$D$101,MATCH($B102,$B$18:$B$101,0)),""))</f>
         <v/>
       </c>
       <c r="E102">
@@ -33235,7 +33227,7 @@
       <c r="A103" s="37" t="n"/>
       <c r="C103" s="27" t="n"/>
       <c r="D103">
-        <f>IF($B103="","",IFERROR(INDEX($D$17:$D$102,MATCH($B103,$B$17:$B$102,0)),""))</f>
+        <f>IF($B103="","",IFERROR(INDEX($D$18:$D$102,MATCH($B103,$B$18:$B$102,0)),""))</f>
         <v/>
       </c>
       <c r="E103">
@@ -33255,7 +33247,7 @@
       <c r="A104" s="37" t="n"/>
       <c r="C104" s="27" t="n"/>
       <c r="D104">
-        <f>IF($B104="","",IFERROR(INDEX($D$17:$D$103,MATCH($B104,$B$17:$B$103,0)),""))</f>
+        <f>IF($B104="","",IFERROR(INDEX($D$18:$D$103,MATCH($B104,$B$18:$B$103,0)),""))</f>
         <v/>
       </c>
       <c r="E104">
@@ -33275,7 +33267,7 @@
       <c r="A105" s="37" t="n"/>
       <c r="C105" s="27" t="n"/>
       <c r="D105">
-        <f>IF($B105="","",IFERROR(INDEX($D$17:$D$104,MATCH($B105,$B$17:$B$104,0)),""))</f>
+        <f>IF($B105="","",IFERROR(INDEX($D$18:$D$104,MATCH($B105,$B$18:$B$104,0)),""))</f>
         <v/>
       </c>
       <c r="E105">
@@ -33295,7 +33287,7 @@
       <c r="A106" s="37" t="n"/>
       <c r="C106" s="27" t="n"/>
       <c r="D106">
-        <f>IF($B106="","",IFERROR(INDEX($D$17:$D$105,MATCH($B106,$B$17:$B$105,0)),""))</f>
+        <f>IF($B106="","",IFERROR(INDEX($D$18:$D$105,MATCH($B106,$B$18:$B$105,0)),""))</f>
         <v/>
       </c>
       <c r="E106">
@@ -33315,7 +33307,7 @@
       <c r="A107" s="37" t="n"/>
       <c r="C107" s="27" t="n"/>
       <c r="D107">
-        <f>IF($B107="","",IFERROR(INDEX($D$17:$D$106,MATCH($B107,$B$17:$B$106,0)),""))</f>
+        <f>IF($B107="","",IFERROR(INDEX($D$18:$D$106,MATCH($B107,$B$18:$B$106,0)),""))</f>
         <v/>
       </c>
       <c r="E107">
@@ -33335,7 +33327,7 @@
       <c r="A108" s="37" t="n"/>
       <c r="C108" s="27" t="n"/>
       <c r="D108">
-        <f>IF($B108="","",IFERROR(INDEX($D$17:$D$107,MATCH($B108,$B$17:$B$107,0)),""))</f>
+        <f>IF($B108="","",IFERROR(INDEX($D$18:$D$107,MATCH($B108,$B$18:$B$107,0)),""))</f>
         <v/>
       </c>
       <c r="E108">
@@ -33355,7 +33347,7 @@
       <c r="A109" s="37" t="n"/>
       <c r="C109" s="27" t="n"/>
       <c r="D109">
-        <f>IF($B109="","",IFERROR(INDEX($D$17:$D$108,MATCH($B109,$B$17:$B$108,0)),""))</f>
+        <f>IF($B109="","",IFERROR(INDEX($D$18:$D$108,MATCH($B109,$B$18:$B$108,0)),""))</f>
         <v/>
       </c>
       <c r="E109">
@@ -33375,7 +33367,7 @@
       <c r="A110" s="37" t="n"/>
       <c r="C110" s="27" t="n"/>
       <c r="D110">
-        <f>IF($B110="","",IFERROR(INDEX($D$17:$D$109,MATCH($B110,$B$17:$B$109,0)),""))</f>
+        <f>IF($B110="","",IFERROR(INDEX($D$18:$D$109,MATCH($B110,$B$18:$B$109,0)),""))</f>
         <v/>
       </c>
       <c r="E110">
@@ -33395,7 +33387,7 @@
       <c r="A111" s="37" t="n"/>
       <c r="C111" s="27" t="n"/>
       <c r="D111">
-        <f>IF($B111="","",IFERROR(INDEX($D$17:$D$110,MATCH($B111,$B$17:$B$110,0)),""))</f>
+        <f>IF($B111="","",IFERROR(INDEX($D$18:$D$110,MATCH($B111,$B$18:$B$110,0)),""))</f>
         <v/>
       </c>
       <c r="E111">
@@ -33415,7 +33407,7 @@
       <c r="A112" s="37" t="n"/>
       <c r="C112" s="27" t="n"/>
       <c r="D112">
-        <f>IF($B112="","",IFERROR(INDEX($D$17:$D$111,MATCH($B112,$B$17:$B$111,0)),""))</f>
+        <f>IF($B112="","",IFERROR(INDEX($D$18:$D$111,MATCH($B112,$B$18:$B$111,0)),""))</f>
         <v/>
       </c>
       <c r="E112">
@@ -33435,7 +33427,7 @@
       <c r="A113" s="37" t="n"/>
       <c r="C113" s="27" t="n"/>
       <c r="D113">
-        <f>IF($B113="","",IFERROR(INDEX($D$17:$D$112,MATCH($B113,$B$17:$B$112,0)),""))</f>
+        <f>IF($B113="","",IFERROR(INDEX($D$18:$D$112,MATCH($B113,$B$18:$B$112,0)),""))</f>
         <v/>
       </c>
       <c r="E113">
@@ -33455,7 +33447,7 @@
       <c r="A114" s="37" t="n"/>
       <c r="C114" s="27" t="n"/>
       <c r="D114">
-        <f>IF($B114="","",IFERROR(INDEX($D$17:$D$113,MATCH($B114,$B$17:$B$113,0)),""))</f>
+        <f>IF($B114="","",IFERROR(INDEX($D$18:$D$113,MATCH($B114,$B$18:$B$113,0)),""))</f>
         <v/>
       </c>
       <c r="E114">
@@ -33475,7 +33467,7 @@
       <c r="A115" s="37" t="n"/>
       <c r="C115" s="27" t="n"/>
       <c r="D115">
-        <f>IF($B115="","",IFERROR(INDEX($D$17:$D$114,MATCH($B115,$B$17:$B$114,0)),""))</f>
+        <f>IF($B115="","",IFERROR(INDEX($D$18:$D$114,MATCH($B115,$B$18:$B$114,0)),""))</f>
         <v/>
       </c>
       <c r="E115">
@@ -33495,7 +33487,7 @@
       <c r="A116" s="37" t="n"/>
       <c r="C116" s="27" t="n"/>
       <c r="D116">
-        <f>IF($B116="","",IFERROR(INDEX($D$17:$D$115,MATCH($B116,$B$17:$B$115,0)),""))</f>
+        <f>IF($B116="","",IFERROR(INDEX($D$18:$D$115,MATCH($B116,$B$18:$B$115,0)),""))</f>
         <v/>
       </c>
       <c r="E116">
@@ -33515,7 +33507,7 @@
       <c r="A117" s="37" t="n"/>
       <c r="C117" s="27" t="n"/>
       <c r="D117">
-        <f>IF($B117="","",IFERROR(INDEX($D$17:$D$116,MATCH($B117,$B$17:$B$116,0)),""))</f>
+        <f>IF($B117="","",IFERROR(INDEX($D$18:$D$116,MATCH($B117,$B$18:$B$116,0)),""))</f>
         <v/>
       </c>
       <c r="E117">
@@ -33535,7 +33527,7 @@
       <c r="A118" s="37" t="n"/>
       <c r="C118" s="27" t="n"/>
       <c r="D118">
-        <f>IF($B118="","",IFERROR(INDEX($D$17:$D$117,MATCH($B118,$B$17:$B$117,0)),""))</f>
+        <f>IF($B118="","",IFERROR(INDEX($D$18:$D$117,MATCH($B118,$B$18:$B$117,0)),""))</f>
         <v/>
       </c>
       <c r="E118">
@@ -33555,7 +33547,7 @@
       <c r="A119" s="37" t="n"/>
       <c r="C119" s="27" t="n"/>
       <c r="D119">
-        <f>IF($B119="","",IFERROR(INDEX($D$17:$D$118,MATCH($B119,$B$17:$B$118,0)),""))</f>
+        <f>IF($B119="","",IFERROR(INDEX($D$18:$D$118,MATCH($B119,$B$18:$B$118,0)),""))</f>
         <v/>
       </c>
       <c r="E119">
@@ -33575,7 +33567,7 @@
       <c r="A120" s="37" t="n"/>
       <c r="C120" s="27" t="n"/>
       <c r="D120">
-        <f>IF($B120="","",IFERROR(INDEX($D$17:$D$119,MATCH($B120,$B$17:$B$119,0)),""))</f>
+        <f>IF($B120="","",IFERROR(INDEX($D$18:$D$119,MATCH($B120,$B$18:$B$119,0)),""))</f>
         <v/>
       </c>
       <c r="E120">
@@ -33595,7 +33587,7 @@
       <c r="A121" s="37" t="n"/>
       <c r="C121" s="27" t="n"/>
       <c r="D121">
-        <f>IF($B121="","",IFERROR(INDEX($D$17:$D$120,MATCH($B121,$B$17:$B$120,0)),""))</f>
+        <f>IF($B121="","",IFERROR(INDEX($D$18:$D$120,MATCH($B121,$B$18:$B$120,0)),""))</f>
         <v/>
       </c>
       <c r="E121">
@@ -33615,7 +33607,7 @@
       <c r="A122" s="37" t="n"/>
       <c r="C122" s="27" t="n"/>
       <c r="D122">
-        <f>IF($B122="","",IFERROR(INDEX($D$17:$D$121,MATCH($B122,$B$17:$B$121,0)),""))</f>
+        <f>IF($B122="","",IFERROR(INDEX($D$18:$D$121,MATCH($B122,$B$18:$B$121,0)),""))</f>
         <v/>
       </c>
       <c r="E122">
@@ -33635,7 +33627,7 @@
       <c r="A123" s="37" t="n"/>
       <c r="C123" s="27" t="n"/>
       <c r="D123">
-        <f>IF($B123="","",IFERROR(INDEX($D$17:$D$122,MATCH($B123,$B$17:$B$122,0)),""))</f>
+        <f>IF($B123="","",IFERROR(INDEX($D$18:$D$122,MATCH($B123,$B$18:$B$122,0)),""))</f>
         <v/>
       </c>
       <c r="E123">
@@ -33655,7 +33647,7 @@
       <c r="A124" s="37" t="n"/>
       <c r="C124" s="27" t="n"/>
       <c r="D124">
-        <f>IF($B124="","",IFERROR(INDEX($D$17:$D$123,MATCH($B124,$B$17:$B$123,0)),""))</f>
+        <f>IF($B124="","",IFERROR(INDEX($D$18:$D$123,MATCH($B124,$B$18:$B$123,0)),""))</f>
         <v/>
       </c>
       <c r="E124">
@@ -33675,7 +33667,7 @@
       <c r="A125" s="37" t="n"/>
       <c r="C125" s="27" t="n"/>
       <c r="D125">
-        <f>IF($B125="","",IFERROR(INDEX($D$17:$D$124,MATCH($B125,$B$17:$B$124,0)),""))</f>
+        <f>IF($B125="","",IFERROR(INDEX($D$18:$D$124,MATCH($B125,$B$18:$B$124,0)),""))</f>
         <v/>
       </c>
       <c r="E125">
@@ -33695,7 +33687,7 @@
       <c r="A126" s="37" t="n"/>
       <c r="C126" s="27" t="n"/>
       <c r="D126">
-        <f>IF($B126="","",IFERROR(INDEX($D$17:$D$125,MATCH($B126,$B$17:$B$125,0)),""))</f>
+        <f>IF($B126="","",IFERROR(INDEX($D$18:$D$125,MATCH($B126,$B$18:$B$125,0)),""))</f>
         <v/>
       </c>
       <c r="E126">
@@ -33715,7 +33707,7 @@
       <c r="A127" s="37" t="n"/>
       <c r="C127" s="27" t="n"/>
       <c r="D127">
-        <f>IF($B127="","",IFERROR(INDEX($D$17:$D$126,MATCH($B127,$B$17:$B$126,0)),""))</f>
+        <f>IF($B127="","",IFERROR(INDEX($D$18:$D$126,MATCH($B127,$B$18:$B$126,0)),""))</f>
         <v/>
       </c>
       <c r="E127">
@@ -33735,7 +33727,7 @@
       <c r="A128" s="37" t="n"/>
       <c r="C128" s="27" t="n"/>
       <c r="D128">
-        <f>IF($B128="","",IFERROR(INDEX($D$17:$D$127,MATCH($B128,$B$17:$B$127,0)),""))</f>
+        <f>IF($B128="","",IFERROR(INDEX($D$18:$D$127,MATCH($B128,$B$18:$B$127,0)),""))</f>
         <v/>
       </c>
       <c r="E128">
@@ -33755,7 +33747,7 @@
       <c r="A129" s="37" t="n"/>
       <c r="C129" s="27" t="n"/>
       <c r="D129">
-        <f>IF($B129="","",IFERROR(INDEX($D$17:$D$128,MATCH($B129,$B$17:$B$128,0)),""))</f>
+        <f>IF($B129="","",IFERROR(INDEX($D$18:$D$128,MATCH($B129,$B$18:$B$128,0)),""))</f>
         <v/>
       </c>
       <c r="E129">
@@ -33775,7 +33767,7 @@
       <c r="A130" s="37" t="n"/>
       <c r="C130" s="27" t="n"/>
       <c r="D130">
-        <f>IF($B130="","",IFERROR(INDEX($D$17:$D$129,MATCH($B130,$B$17:$B$129,0)),""))</f>
+        <f>IF($B130="","",IFERROR(INDEX($D$18:$D$129,MATCH($B130,$B$18:$B$129,0)),""))</f>
         <v/>
       </c>
       <c r="E130">
@@ -33795,7 +33787,7 @@
       <c r="A131" s="37" t="n"/>
       <c r="C131" s="27" t="n"/>
       <c r="D131">
-        <f>IF($B131="","",IFERROR(INDEX($D$17:$D$130,MATCH($B131,$B$17:$B$130,0)),""))</f>
+        <f>IF($B131="","",IFERROR(INDEX($D$18:$D$130,MATCH($B131,$B$18:$B$130,0)),""))</f>
         <v/>
       </c>
       <c r="E131">
@@ -33815,7 +33807,7 @@
       <c r="A132" s="37" t="n"/>
       <c r="C132" s="27" t="n"/>
       <c r="D132">
-        <f>IF($B132="","",IFERROR(INDEX($D$17:$D$131,MATCH($B132,$B$17:$B$131,0)),""))</f>
+        <f>IF($B132="","",IFERROR(INDEX($D$18:$D$131,MATCH($B132,$B$18:$B$131,0)),""))</f>
         <v/>
       </c>
       <c r="E132">
@@ -33835,7 +33827,7 @@
       <c r="A133" s="37" t="n"/>
       <c r="C133" s="27" t="n"/>
       <c r="D133">
-        <f>IF($B133="","",IFERROR(INDEX($D$17:$D$132,MATCH($B133,$B$17:$B$132,0)),""))</f>
+        <f>IF($B133="","",IFERROR(INDEX($D$18:$D$132,MATCH($B133,$B$18:$B$132,0)),""))</f>
         <v/>
       </c>
       <c r="E133">
@@ -33855,7 +33847,7 @@
       <c r="A134" s="37" t="n"/>
       <c r="C134" s="27" t="n"/>
       <c r="D134">
-        <f>IF($B134="","",IFERROR(INDEX($D$17:$D$133,MATCH($B134,$B$17:$B$133,0)),""))</f>
+        <f>IF($B134="","",IFERROR(INDEX($D$18:$D$133,MATCH($B134,$B$18:$B$133,0)),""))</f>
         <v/>
       </c>
       <c r="E134">
@@ -33875,7 +33867,7 @@
       <c r="A135" s="37" t="n"/>
       <c r="C135" s="27" t="n"/>
       <c r="D135">
-        <f>IF($B135="","",IFERROR(INDEX($D$17:$D$134,MATCH($B135,$B$17:$B$134,0)),""))</f>
+        <f>IF($B135="","",IFERROR(INDEX($D$18:$D$134,MATCH($B135,$B$18:$B$134,0)),""))</f>
         <v/>
       </c>
       <c r="E135">
@@ -33895,7 +33887,7 @@
       <c r="A136" s="37" t="n"/>
       <c r="C136" s="27" t="n"/>
       <c r="D136">
-        <f>IF($B136="","",IFERROR(INDEX($D$17:$D$135,MATCH($B136,$B$17:$B$135,0)),""))</f>
+        <f>IF($B136="","",IFERROR(INDEX($D$18:$D$135,MATCH($B136,$B$18:$B$135,0)),""))</f>
         <v/>
       </c>
       <c r="E136">
@@ -33915,7 +33907,7 @@
       <c r="A137" s="37" t="n"/>
       <c r="C137" s="27" t="n"/>
       <c r="D137">
-        <f>IF($B137="","",IFERROR(INDEX($D$17:$D$136,MATCH($B137,$B$17:$B$136,0)),""))</f>
+        <f>IF($B137="","",IFERROR(INDEX($D$18:$D$136,MATCH($B137,$B$18:$B$136,0)),""))</f>
         <v/>
       </c>
       <c r="E137">
@@ -33935,7 +33927,7 @@
       <c r="A138" s="37" t="n"/>
       <c r="C138" s="27" t="n"/>
       <c r="D138">
-        <f>IF($B138="","",IFERROR(INDEX($D$17:$D$137,MATCH($B138,$B$17:$B$137,0)),""))</f>
+        <f>IF($B138="","",IFERROR(INDEX($D$18:$D$137,MATCH($B138,$B$18:$B$137,0)),""))</f>
         <v/>
       </c>
       <c r="E138">
@@ -33955,7 +33947,7 @@
       <c r="A139" s="37" t="n"/>
       <c r="C139" s="27" t="n"/>
       <c r="D139">
-        <f>IF($B139="","",IFERROR(INDEX($D$17:$D$138,MATCH($B139,$B$17:$B$138,0)),""))</f>
+        <f>IF($B139="","",IFERROR(INDEX($D$18:$D$138,MATCH($B139,$B$18:$B$138,0)),""))</f>
         <v/>
       </c>
       <c r="E139">
@@ -33975,7 +33967,7 @@
       <c r="A140" s="37" t="n"/>
       <c r="C140" s="27" t="n"/>
       <c r="D140">
-        <f>IF($B140="","",IFERROR(INDEX($D$17:$D$139,MATCH($B140,$B$17:$B$139,0)),""))</f>
+        <f>IF($B140="","",IFERROR(INDEX($D$18:$D$139,MATCH($B140,$B$18:$B$139,0)),""))</f>
         <v/>
       </c>
       <c r="E140">
@@ -33995,7 +33987,7 @@
       <c r="A141" s="37" t="n"/>
       <c r="C141" s="27" t="n"/>
       <c r="D141">
-        <f>IF($B141="","",IFERROR(INDEX($D$17:$D$140,MATCH($B141,$B$17:$B$140,0)),""))</f>
+        <f>IF($B141="","",IFERROR(INDEX($D$18:$D$140,MATCH($B141,$B$18:$B$140,0)),""))</f>
         <v/>
       </c>
       <c r="E141">
@@ -34015,7 +34007,7 @@
       <c r="A142" s="37" t="n"/>
       <c r="C142" s="27" t="n"/>
       <c r="D142">
-        <f>IF($B142="","",IFERROR(INDEX($D$17:$D$141,MATCH($B142,$B$17:$B$141,0)),""))</f>
+        <f>IF($B142="","",IFERROR(INDEX($D$18:$D$141,MATCH($B142,$B$18:$B$141,0)),""))</f>
         <v/>
       </c>
       <c r="E142">
@@ -34035,7 +34027,7 @@
       <c r="A143" s="37" t="n"/>
       <c r="C143" s="27" t="n"/>
       <c r="D143">
-        <f>IF($B143="","",IFERROR(INDEX($D$17:$D$142,MATCH($B143,$B$17:$B$142,0)),""))</f>
+        <f>IF($B143="","",IFERROR(INDEX($D$18:$D$142,MATCH($B143,$B$18:$B$142,0)),""))</f>
         <v/>
       </c>
       <c r="E143">
@@ -34055,7 +34047,7 @@
       <c r="A144" s="37" t="n"/>
       <c r="C144" s="27" t="n"/>
       <c r="D144">
-        <f>IF($B144="","",IFERROR(INDEX($D$17:$D$143,MATCH($B144,$B$17:$B$143,0)),""))</f>
+        <f>IF($B144="","",IFERROR(INDEX($D$18:$D$143,MATCH($B144,$B$18:$B$143,0)),""))</f>
         <v/>
       </c>
       <c r="E144">
@@ -34075,7 +34067,7 @@
       <c r="A145" s="37" t="n"/>
       <c r="C145" s="27" t="n"/>
       <c r="D145">
-        <f>IF($B145="","",IFERROR(INDEX($D$17:$D$144,MATCH($B145,$B$17:$B$144,0)),""))</f>
+        <f>IF($B145="","",IFERROR(INDEX($D$18:$D$144,MATCH($B145,$B$18:$B$144,0)),""))</f>
         <v/>
       </c>
       <c r="E145">
@@ -34095,7 +34087,7 @@
       <c r="A146" s="37" t="n"/>
       <c r="C146" s="27" t="n"/>
       <c r="D146">
-        <f>IF($B146="","",IFERROR(INDEX($D$17:$D$145,MATCH($B146,$B$17:$B$145,0)),""))</f>
+        <f>IF($B146="","",IFERROR(INDEX($D$18:$D$145,MATCH($B146,$B$18:$B$145,0)),""))</f>
         <v/>
       </c>
       <c r="E146">
@@ -34115,7 +34107,7 @@
       <c r="A147" s="37" t="n"/>
       <c r="C147" s="27" t="n"/>
       <c r="D147">
-        <f>IF($B147="","",IFERROR(INDEX($D$17:$D$146,MATCH($B147,$B$17:$B$146,0)),""))</f>
+        <f>IF($B147="","",IFERROR(INDEX($D$18:$D$146,MATCH($B147,$B$18:$B$146,0)),""))</f>
         <v/>
       </c>
       <c r="E147">
@@ -34135,7 +34127,7 @@
       <c r="A148" s="37" t="n"/>
       <c r="C148" s="27" t="n"/>
       <c r="D148">
-        <f>IF($B148="","",IFERROR(INDEX($D$17:$D$147,MATCH($B148,$B$17:$B$147,0)),""))</f>
+        <f>IF($B148="","",IFERROR(INDEX($D$18:$D$147,MATCH($B148,$B$18:$B$147,0)),""))</f>
         <v/>
       </c>
       <c r="E148">
@@ -34155,7 +34147,7 @@
       <c r="A149" s="37" t="n"/>
       <c r="C149" s="27" t="n"/>
       <c r="D149">
-        <f>IF($B149="","",IFERROR(INDEX($D$17:$D$148,MATCH($B149,$B$17:$B$148,0)),""))</f>
+        <f>IF($B149="","",IFERROR(INDEX($D$18:$D$148,MATCH($B149,$B$18:$B$148,0)),""))</f>
         <v/>
       </c>
       <c r="E149">
@@ -34175,7 +34167,7 @@
       <c r="A150" s="37" t="n"/>
       <c r="C150" s="27" t="n"/>
       <c r="D150">
-        <f>IF($B150="","",IFERROR(INDEX($D$17:$D$149,MATCH($B150,$B$17:$B$149,0)),""))</f>
+        <f>IF($B150="","",IFERROR(INDEX($D$18:$D$149,MATCH($B150,$B$18:$B$149,0)),""))</f>
         <v/>
       </c>
       <c r="E150">
@@ -34195,7 +34187,7 @@
       <c r="A151" s="37" t="n"/>
       <c r="C151" s="27" t="n"/>
       <c r="D151">
-        <f>IF($B151="","",IFERROR(INDEX($D$17:$D$150,MATCH($B151,$B$17:$B$150,0)),""))</f>
+        <f>IF($B151="","",IFERROR(INDEX($D$18:$D$150,MATCH($B151,$B$18:$B$150,0)),""))</f>
         <v/>
       </c>
       <c r="E151">
@@ -34215,7 +34207,7 @@
       <c r="A152" s="37" t="n"/>
       <c r="C152" s="27" t="n"/>
       <c r="D152">
-        <f>IF($B152="","",IFERROR(INDEX($D$17:$D$151,MATCH($B152,$B$17:$B$151,0)),""))</f>
+        <f>IF($B152="","",IFERROR(INDEX($D$18:$D$151,MATCH($B152,$B$18:$B$151,0)),""))</f>
         <v/>
       </c>
       <c r="E152">
@@ -34235,7 +34227,7 @@
       <c r="A153" s="37" t="n"/>
       <c r="C153" s="27" t="n"/>
       <c r="D153">
-        <f>IF($B153="","",IFERROR(INDEX($D$17:$D$152,MATCH($B153,$B$17:$B$152,0)),""))</f>
+        <f>IF($B153="","",IFERROR(INDEX($D$18:$D$152,MATCH($B153,$B$18:$B$152,0)),""))</f>
         <v/>
       </c>
       <c r="E153">
@@ -34255,7 +34247,7 @@
       <c r="A154" s="37" t="n"/>
       <c r="C154" s="27" t="n"/>
       <c r="D154">
-        <f>IF($B154="","",IFERROR(INDEX($D$17:$D$153,MATCH($B154,$B$17:$B$153,0)),""))</f>
+        <f>IF($B154="","",IFERROR(INDEX($D$18:$D$153,MATCH($B154,$B$18:$B$153,0)),""))</f>
         <v/>
       </c>
       <c r="E154">
@@ -34275,7 +34267,7 @@
       <c r="A155" s="37" t="n"/>
       <c r="C155" s="27" t="n"/>
       <c r="D155">
-        <f>IF($B155="","",IFERROR(INDEX($D$17:$D$154,MATCH($B155,$B$17:$B$154,0)),""))</f>
+        <f>IF($B155="","",IFERROR(INDEX($D$18:$D$154,MATCH($B155,$B$18:$B$154,0)),""))</f>
         <v/>
       </c>
       <c r="E155">
@@ -34295,7 +34287,7 @@
       <c r="A156" s="37" t="n"/>
       <c r="C156" s="27" t="n"/>
       <c r="D156">
-        <f>IF($B156="","",IFERROR(INDEX($D$17:$D$155,MATCH($B156,$B$17:$B$155,0)),""))</f>
+        <f>IF($B156="","",IFERROR(INDEX($D$18:$D$155,MATCH($B156,$B$18:$B$155,0)),""))</f>
         <v/>
       </c>
       <c r="E156">
@@ -34315,7 +34307,7 @@
       <c r="A157" s="37" t="n"/>
       <c r="C157" s="27" t="n"/>
       <c r="D157">
-        <f>IF($B157="","",IFERROR(INDEX($D$17:$D$156,MATCH($B157,$B$17:$B$156,0)),""))</f>
+        <f>IF($B157="","",IFERROR(INDEX($D$18:$D$156,MATCH($B157,$B$18:$B$156,0)),""))</f>
         <v/>
       </c>
       <c r="E157">
@@ -34335,7 +34327,7 @@
       <c r="A158" s="37" t="n"/>
       <c r="C158" s="27" t="n"/>
       <c r="D158">
-        <f>IF($B158="","",IFERROR(INDEX($D$17:$D$157,MATCH($B158,$B$17:$B$157,0)),""))</f>
+        <f>IF($B158="","",IFERROR(INDEX($D$18:$D$157,MATCH($B158,$B$18:$B$157,0)),""))</f>
         <v/>
       </c>
       <c r="E158">
@@ -34355,7 +34347,7 @@
       <c r="A159" s="37" t="n"/>
       <c r="C159" s="27" t="n"/>
       <c r="D159">
-        <f>IF($B159="","",IFERROR(INDEX($D$17:$D$158,MATCH($B159,$B$17:$B$158,0)),""))</f>
+        <f>IF($B159="","",IFERROR(INDEX($D$18:$D$158,MATCH($B159,$B$18:$B$158,0)),""))</f>
         <v/>
       </c>
       <c r="E159">
@@ -34375,7 +34367,7 @@
       <c r="A160" s="37" t="n"/>
       <c r="C160" s="27" t="n"/>
       <c r="D160">
-        <f>IF($B160="","",IFERROR(INDEX($D$17:$D$159,MATCH($B160,$B$17:$B$159,0)),""))</f>
+        <f>IF($B160="","",IFERROR(INDEX($D$18:$D$159,MATCH($B160,$B$18:$B$159,0)),""))</f>
         <v/>
       </c>
       <c r="E160">
@@ -34395,7 +34387,7 @@
       <c r="A161" s="37" t="n"/>
       <c r="C161" s="27" t="n"/>
       <c r="D161">
-        <f>IF($B161="","",IFERROR(INDEX($D$17:$D$160,MATCH($B161,$B$17:$B$160,0)),""))</f>
+        <f>IF($B161="","",IFERROR(INDEX($D$18:$D$160,MATCH($B161,$B$18:$B$160,0)),""))</f>
         <v/>
       </c>
       <c r="E161">
@@ -34415,7 +34407,7 @@
       <c r="A162" s="37" t="n"/>
       <c r="C162" s="27" t="n"/>
       <c r="D162">
-        <f>IF($B162="","",IFERROR(INDEX($D$17:$D$161,MATCH($B162,$B$17:$B$161,0)),""))</f>
+        <f>IF($B162="","",IFERROR(INDEX($D$18:$D$161,MATCH($B162,$B$18:$B$161,0)),""))</f>
         <v/>
       </c>
       <c r="E162">
@@ -34435,7 +34427,7 @@
       <c r="A163" s="37" t="n"/>
       <c r="C163" s="27" t="n"/>
       <c r="D163">
-        <f>IF($B163="","",IFERROR(INDEX($D$17:$D$162,MATCH($B163,$B$17:$B$162,0)),""))</f>
+        <f>IF($B163="","",IFERROR(INDEX($D$18:$D$162,MATCH($B163,$B$18:$B$162,0)),""))</f>
         <v/>
       </c>
       <c r="E163">
@@ -34455,7 +34447,7 @@
       <c r="A164" s="37" t="n"/>
       <c r="C164" s="27" t="n"/>
       <c r="D164">
-        <f>IF($B164="","",IFERROR(INDEX($D$17:$D$163,MATCH($B164,$B$17:$B$163,0)),""))</f>
+        <f>IF($B164="","",IFERROR(INDEX($D$18:$D$163,MATCH($B164,$B$18:$B$163,0)),""))</f>
         <v/>
       </c>
       <c r="E164">
@@ -34475,7 +34467,7 @@
       <c r="A165" s="37" t="n"/>
       <c r="C165" s="27" t="n"/>
       <c r="D165">
-        <f>IF($B165="","",IFERROR(INDEX($D$17:$D$164,MATCH($B165,$B$17:$B$164,0)),""))</f>
+        <f>IF($B165="","",IFERROR(INDEX($D$18:$D$164,MATCH($B165,$B$18:$B$164,0)),""))</f>
         <v/>
       </c>
       <c r="E165">
@@ -34495,7 +34487,7 @@
       <c r="A166" s="37" t="n"/>
       <c r="C166" s="27" t="n"/>
       <c r="D166">
-        <f>IF($B166="","",IFERROR(INDEX($D$17:$D$165,MATCH($B166,$B$17:$B$165,0)),""))</f>
+        <f>IF($B166="","",IFERROR(INDEX($D$18:$D$165,MATCH($B166,$B$18:$B$165,0)),""))</f>
         <v/>
       </c>
       <c r="E166">
@@ -34515,7 +34507,7 @@
       <c r="A167" s="37" t="n"/>
       <c r="C167" s="27" t="n"/>
       <c r="D167">
-        <f>IF($B167="","",IFERROR(INDEX($D$17:$D$166,MATCH($B167,$B$17:$B$166,0)),""))</f>
+        <f>IF($B167="","",IFERROR(INDEX($D$18:$D$166,MATCH($B167,$B$18:$B$166,0)),""))</f>
         <v/>
       </c>
       <c r="E167">
@@ -34535,7 +34527,7 @@
       <c r="A168" s="37" t="n"/>
       <c r="C168" s="27" t="n"/>
       <c r="D168">
-        <f>IF($B168="","",IFERROR(INDEX($D$17:$D$167,MATCH($B168,$B$17:$B$167,0)),""))</f>
+        <f>IF($B168="","",IFERROR(INDEX($D$18:$D$167,MATCH($B168,$B$18:$B$167,0)),""))</f>
         <v/>
       </c>
       <c r="E168">
@@ -34555,7 +34547,7 @@
       <c r="A169" s="37" t="n"/>
       <c r="C169" s="27" t="n"/>
       <c r="D169">
-        <f>IF($B169="","",IFERROR(INDEX($D$17:$D$168,MATCH($B169,$B$17:$B$168,0)),""))</f>
+        <f>IF($B169="","",IFERROR(INDEX($D$18:$D$168,MATCH($B169,$B$18:$B$168,0)),""))</f>
         <v/>
       </c>
       <c r="E169">
@@ -34575,7 +34567,7 @@
       <c r="A170" s="37" t="n"/>
       <c r="C170" s="27" t="n"/>
       <c r="D170">
-        <f>IF($B170="","",IFERROR(INDEX($D$17:$D$169,MATCH($B170,$B$17:$B$169,0)),""))</f>
+        <f>IF($B170="","",IFERROR(INDEX($D$18:$D$169,MATCH($B170,$B$18:$B$169,0)),""))</f>
         <v/>
       </c>
       <c r="E170">
@@ -34595,7 +34587,7 @@
       <c r="A171" s="37" t="n"/>
       <c r="C171" s="27" t="n"/>
       <c r="D171">
-        <f>IF($B171="","",IFERROR(INDEX($D$17:$D$170,MATCH($B171,$B$17:$B$170,0)),""))</f>
+        <f>IF($B171="","",IFERROR(INDEX($D$18:$D$170,MATCH($B171,$B$18:$B$170,0)),""))</f>
         <v/>
       </c>
       <c r="E171">
@@ -34615,7 +34607,7 @@
       <c r="A172" s="37" t="n"/>
       <c r="C172" s="27" t="n"/>
       <c r="D172">
-        <f>IF($B172="","",IFERROR(INDEX($D$17:$D$171,MATCH($B172,$B$17:$B$171,0)),""))</f>
+        <f>IF($B172="","",IFERROR(INDEX($D$18:$D$171,MATCH($B172,$B$18:$B$171,0)),""))</f>
         <v/>
       </c>
       <c r="E172">
@@ -34635,7 +34627,7 @@
       <c r="A173" s="37" t="n"/>
       <c r="C173" s="27" t="n"/>
       <c r="D173">
-        <f>IF($B173="","",IFERROR(INDEX($D$17:$D$172,MATCH($B173,$B$17:$B$172,0)),""))</f>
+        <f>IF($B173="","",IFERROR(INDEX($D$18:$D$172,MATCH($B173,$B$18:$B$172,0)),""))</f>
         <v/>
       </c>
       <c r="E173">
@@ -34655,7 +34647,7 @@
       <c r="A174" s="37" t="n"/>
       <c r="C174" s="27" t="n"/>
       <c r="D174">
-        <f>IF($B174="","",IFERROR(INDEX($D$17:$D$173,MATCH($B174,$B$17:$B$173,0)),""))</f>
+        <f>IF($B174="","",IFERROR(INDEX($D$18:$D$173,MATCH($B174,$B$18:$B$173,0)),""))</f>
         <v/>
       </c>
       <c r="E174">
@@ -34675,7 +34667,7 @@
       <c r="A175" s="37" t="n"/>
       <c r="C175" s="27" t="n"/>
       <c r="D175">
-        <f>IF($B175="","",IFERROR(INDEX($D$17:$D$174,MATCH($B175,$B$17:$B$174,0)),""))</f>
+        <f>IF($B175="","",IFERROR(INDEX($D$18:$D$174,MATCH($B175,$B$18:$B$174,0)),""))</f>
         <v/>
       </c>
       <c r="E175">
@@ -34695,7 +34687,7 @@
       <c r="A176" s="37" t="n"/>
       <c r="C176" s="27" t="n"/>
       <c r="D176">
-        <f>IF($B176="","",IFERROR(INDEX($D$17:$D$175,MATCH($B176,$B$17:$B$175,0)),""))</f>
+        <f>IF($B176="","",IFERROR(INDEX($D$18:$D$175,MATCH($B176,$B$18:$B$175,0)),""))</f>
         <v/>
       </c>
       <c r="E176">
@@ -34715,7 +34707,7 @@
       <c r="A177" s="37" t="n"/>
       <c r="C177" s="27" t="n"/>
       <c r="D177">
-        <f>IF($B177="","",IFERROR(INDEX($D$17:$D$176,MATCH($B177,$B$17:$B$176,0)),""))</f>
+        <f>IF($B177="","",IFERROR(INDEX($D$18:$D$176,MATCH($B177,$B$18:$B$176,0)),""))</f>
         <v/>
       </c>
       <c r="E177">
@@ -34735,7 +34727,7 @@
       <c r="A178" s="37" t="n"/>
       <c r="C178" s="27" t="n"/>
       <c r="D178">
-        <f>IF($B178="","",IFERROR(INDEX($D$17:$D$177,MATCH($B178,$B$17:$B$177,0)),""))</f>
+        <f>IF($B178="","",IFERROR(INDEX($D$18:$D$177,MATCH($B178,$B$18:$B$177,0)),""))</f>
         <v/>
       </c>
       <c r="E178">
@@ -34755,7 +34747,7 @@
       <c r="A179" s="37" t="n"/>
       <c r="C179" s="27" t="n"/>
       <c r="D179">
-        <f>IF($B179="","",IFERROR(INDEX($D$17:$D$178,MATCH($B179,$B$17:$B$178,0)),""))</f>
+        <f>IF($B179="","",IFERROR(INDEX($D$18:$D$178,MATCH($B179,$B$18:$B$178,0)),""))</f>
         <v/>
       </c>
       <c r="E179">
@@ -34775,7 +34767,7 @@
       <c r="A180" s="37" t="n"/>
       <c r="C180" s="27" t="n"/>
       <c r="D180">
-        <f>IF($B180="","",IFERROR(INDEX($D$17:$D$179,MATCH($B180,$B$17:$B$179,0)),""))</f>
+        <f>IF($B180="","",IFERROR(INDEX($D$18:$D$179,MATCH($B180,$B$18:$B$179,0)),""))</f>
         <v/>
       </c>
       <c r="E180">
@@ -34795,7 +34787,7 @@
       <c r="A181" s="37" t="n"/>
       <c r="C181" s="27" t="n"/>
       <c r="D181">
-        <f>IF($B181="","",IFERROR(INDEX($D$17:$D$180,MATCH($B181,$B$17:$B$180,0)),""))</f>
+        <f>IF($B181="","",IFERROR(INDEX($D$18:$D$180,MATCH($B181,$B$18:$B$180,0)),""))</f>
         <v/>
       </c>
       <c r="E181">
@@ -34815,7 +34807,7 @@
       <c r="A182" s="37" t="n"/>
       <c r="C182" s="27" t="n"/>
       <c r="D182">
-        <f>IF($B182="","",IFERROR(INDEX($D$17:$D$181,MATCH($B182,$B$17:$B$181,0)),""))</f>
+        <f>IF($B182="","",IFERROR(INDEX($D$18:$D$181,MATCH($B182,$B$18:$B$181,0)),""))</f>
         <v/>
       </c>
       <c r="E182">
@@ -34835,7 +34827,7 @@
       <c r="A183" s="37" t="n"/>
       <c r="C183" s="27" t="n"/>
       <c r="D183">
-        <f>IF($B183="","",IFERROR(INDEX($D$17:$D$182,MATCH($B183,$B$17:$B$182,0)),""))</f>
+        <f>IF($B183="","",IFERROR(INDEX($D$18:$D$182,MATCH($B183,$B$18:$B$182,0)),""))</f>
         <v/>
       </c>
       <c r="E183">
@@ -34855,7 +34847,7 @@
       <c r="A184" s="37" t="n"/>
       <c r="C184" s="27" t="n"/>
       <c r="D184">
-        <f>IF($B184="","",IFERROR(INDEX($D$17:$D$183,MATCH($B184,$B$17:$B$183,0)),""))</f>
+        <f>IF($B184="","",IFERROR(INDEX($D$18:$D$183,MATCH($B184,$B$18:$B$183,0)),""))</f>
         <v/>
       </c>
       <c r="E184">
@@ -34875,7 +34867,7 @@
       <c r="A185" s="37" t="n"/>
       <c r="C185" s="27" t="n"/>
       <c r="D185">
-        <f>IF($B185="","",IFERROR(INDEX($D$17:$D$184,MATCH($B185,$B$17:$B$184,0)),""))</f>
+        <f>IF($B185="","",IFERROR(INDEX($D$18:$D$184,MATCH($B185,$B$18:$B$184,0)),""))</f>
         <v/>
       </c>
       <c r="E185">
@@ -34895,7 +34887,7 @@
       <c r="A186" s="37" t="n"/>
       <c r="C186" s="27" t="n"/>
       <c r="D186">
-        <f>IF($B186="","",IFERROR(INDEX($D$17:$D$185,MATCH($B186,$B$17:$B$185,0)),""))</f>
+        <f>IF($B186="","",IFERROR(INDEX($D$18:$D$185,MATCH($B186,$B$18:$B$185,0)),""))</f>
         <v/>
       </c>
       <c r="E186">
@@ -34915,7 +34907,7 @@
       <c r="A187" s="37" t="n"/>
       <c r="C187" s="27" t="n"/>
       <c r="D187">
-        <f>IF($B187="","",IFERROR(INDEX($D$17:$D$186,MATCH($B187,$B$17:$B$186,0)),""))</f>
+        <f>IF($B187="","",IFERROR(INDEX($D$18:$D$186,MATCH($B187,$B$18:$B$186,0)),""))</f>
         <v/>
       </c>
       <c r="E187">
@@ -34935,7 +34927,7 @@
       <c r="A188" s="37" t="n"/>
       <c r="C188" s="27" t="n"/>
       <c r="D188">
-        <f>IF($B188="","",IFERROR(INDEX($D$17:$D$187,MATCH($B188,$B$17:$B$187,0)),""))</f>
+        <f>IF($B188="","",IFERROR(INDEX($D$18:$D$187,MATCH($B188,$B$18:$B$187,0)),""))</f>
         <v/>
       </c>
       <c r="E188">
@@ -34955,7 +34947,7 @@
       <c r="A189" s="37" t="n"/>
       <c r="C189" s="27" t="n"/>
       <c r="D189">
-        <f>IF($B189="","",IFERROR(INDEX($D$17:$D$188,MATCH($B189,$B$17:$B$188,0)),""))</f>
+        <f>IF($B189="","",IFERROR(INDEX($D$18:$D$188,MATCH($B189,$B$18:$B$188,0)),""))</f>
         <v/>
       </c>
       <c r="E189">
@@ -34975,7 +34967,7 @@
       <c r="A190" s="37" t="n"/>
       <c r="C190" s="27" t="n"/>
       <c r="D190">
-        <f>IF($B190="","",IFERROR(INDEX($D$17:$D$189,MATCH($B190,$B$17:$B$189,0)),""))</f>
+        <f>IF($B190="","",IFERROR(INDEX($D$18:$D$189,MATCH($B190,$B$18:$B$189,0)),""))</f>
         <v/>
       </c>
       <c r="E190">
@@ -34995,7 +34987,7 @@
       <c r="A191" s="37" t="n"/>
       <c r="C191" s="27" t="n"/>
       <c r="D191">
-        <f>IF($B191="","",IFERROR(INDEX($D$17:$D$190,MATCH($B191,$B$17:$B$190,0)),""))</f>
+        <f>IF($B191="","",IFERROR(INDEX($D$18:$D$190,MATCH($B191,$B$18:$B$190,0)),""))</f>
         <v/>
       </c>
       <c r="E191">
@@ -35015,7 +35007,7 @@
       <c r="A192" s="37" t="n"/>
       <c r="C192" s="27" t="n"/>
       <c r="D192">
-        <f>IF($B192="","",IFERROR(INDEX($D$17:$D$191,MATCH($B192,$B$17:$B$191,0)),""))</f>
+        <f>IF($B192="","",IFERROR(INDEX($D$18:$D$191,MATCH($B192,$B$18:$B$191,0)),""))</f>
         <v/>
       </c>
       <c r="E192">
@@ -35035,7 +35027,7 @@
       <c r="A193" s="37" t="n"/>
       <c r="C193" s="27" t="n"/>
       <c r="D193">
-        <f>IF($B193="","",IFERROR(INDEX($D$17:$D$192,MATCH($B193,$B$17:$B$192,0)),""))</f>
+        <f>IF($B193="","",IFERROR(INDEX($D$18:$D$192,MATCH($B193,$B$18:$B$192,0)),""))</f>
         <v/>
       </c>
       <c r="E193">
@@ -35055,7 +35047,7 @@
       <c r="A194" s="37" t="n"/>
       <c r="C194" s="27" t="n"/>
       <c r="D194">
-        <f>IF($B194="","",IFERROR(INDEX($D$17:$D$193,MATCH($B194,$B$17:$B$193,0)),""))</f>
+        <f>IF($B194="","",IFERROR(INDEX($D$18:$D$193,MATCH($B194,$B$18:$B$193,0)),""))</f>
         <v/>
       </c>
       <c r="E194">
@@ -35075,7 +35067,7 @@
       <c r="A195" s="37" t="n"/>
       <c r="C195" s="27" t="n"/>
       <c r="D195">
-        <f>IF($B195="","",IFERROR(INDEX($D$17:$D$194,MATCH($B195,$B$17:$B$194,0)),""))</f>
+        <f>IF($B195="","",IFERROR(INDEX($D$18:$D$194,MATCH($B195,$B$18:$B$194,0)),""))</f>
         <v/>
       </c>
       <c r="E195">
@@ -35095,7 +35087,7 @@
       <c r="A196" s="37" t="n"/>
       <c r="C196" s="27" t="n"/>
       <c r="D196">
-        <f>IF($B196="","",IFERROR(INDEX($D$17:$D$195,MATCH($B196,$B$17:$B$195,0)),""))</f>
+        <f>IF($B196="","",IFERROR(INDEX($D$18:$D$195,MATCH($B196,$B$18:$B$195,0)),""))</f>
         <v/>
       </c>
       <c r="E196">
@@ -35115,7 +35107,7 @@
       <c r="A197" s="37" t="n"/>
       <c r="C197" s="27" t="n"/>
       <c r="D197">
-        <f>IF($B197="","",IFERROR(INDEX($D$17:$D$196,MATCH($B197,$B$17:$B$196,0)),""))</f>
+        <f>IF($B197="","",IFERROR(INDEX($D$18:$D$196,MATCH($B197,$B$18:$B$196,0)),""))</f>
         <v/>
       </c>
       <c r="E197">
@@ -35135,7 +35127,7 @@
       <c r="A198" s="37" t="n"/>
       <c r="C198" s="27" t="n"/>
       <c r="D198">
-        <f>IF($B198="","",IFERROR(INDEX($D$17:$D$197,MATCH($B198,$B$17:$B$197,0)),""))</f>
+        <f>IF($B198="","",IFERROR(INDEX($D$18:$D$197,MATCH($B198,$B$18:$B$197,0)),""))</f>
         <v/>
       </c>
       <c r="E198">
@@ -35155,7 +35147,7 @@
       <c r="A199" s="37" t="n"/>
       <c r="C199" s="27" t="n"/>
       <c r="D199">
-        <f>IF($B199="","",IFERROR(INDEX($D$17:$D$198,MATCH($B199,$B$17:$B$198,0)),""))</f>
+        <f>IF($B199="","",IFERROR(INDEX($D$18:$D$198,MATCH($B199,$B$18:$B$198,0)),""))</f>
         <v/>
       </c>
       <c r="E199">
@@ -35175,7 +35167,7 @@
       <c r="A200" s="37" t="n"/>
       <c r="C200" s="27" t="n"/>
       <c r="D200">
-        <f>IF($B200="","",IFERROR(INDEX($D$17:$D$199,MATCH($B200,$B$17:$B$199,0)),""))</f>
+        <f>IF($B200="","",IFERROR(INDEX($D$18:$D$199,MATCH($B200,$B$18:$B$199,0)),""))</f>
         <v/>
       </c>
       <c r="E200">
@@ -35195,7 +35187,7 @@
       <c r="A201" s="37" t="n"/>
       <c r="C201" s="27" t="n"/>
       <c r="D201">
-        <f>IF($B201="","",IFERROR(INDEX($D$17:$D$200,MATCH($B201,$B$17:$B$200,0)),""))</f>
+        <f>IF($B201="","",IFERROR(INDEX($D$18:$D$200,MATCH($B201,$B$18:$B$200,0)),""))</f>
         <v/>
       </c>
       <c r="E201">
@@ -35215,7 +35207,7 @@
       <c r="A202" s="37" t="n"/>
       <c r="C202" s="27" t="n"/>
       <c r="D202">
-        <f>IF($B202="","",IFERROR(INDEX($D$17:$D$201,MATCH($B202,$B$17:$B$201,0)),""))</f>
+        <f>IF($B202="","",IFERROR(INDEX($D$18:$D$201,MATCH($B202,$B$18:$B$201,0)),""))</f>
         <v/>
       </c>
       <c r="E202">
@@ -35235,7 +35227,7 @@
       <c r="A203" s="37" t="n"/>
       <c r="C203" s="27" t="n"/>
       <c r="D203">
-        <f>IF($B203="","",IFERROR(INDEX($D$17:$D$202,MATCH($B203,$B$17:$B$202,0)),""))</f>
+        <f>IF($B203="","",IFERROR(INDEX($D$18:$D$202,MATCH($B203,$B$18:$B$202,0)),""))</f>
         <v/>
       </c>
       <c r="E203">
@@ -35255,7 +35247,7 @@
       <c r="A204" s="37" t="n"/>
       <c r="C204" s="27" t="n"/>
       <c r="D204">
-        <f>IF($B204="","",IFERROR(INDEX($D$17:$D$203,MATCH($B204,$B$17:$B$203,0)),""))</f>
+        <f>IF($B204="","",IFERROR(INDEX($D$18:$D$203,MATCH($B204,$B$18:$B$203,0)),""))</f>
         <v/>
       </c>
       <c r="E204">
@@ -35275,7 +35267,7 @@
       <c r="A205" s="37" t="n"/>
       <c r="C205" s="27" t="n"/>
       <c r="D205">
-        <f>IF($B205="","",IFERROR(INDEX($D$17:$D$204,MATCH($B205,$B$17:$B$204,0)),""))</f>
+        <f>IF($B205="","",IFERROR(INDEX($D$18:$D$204,MATCH($B205,$B$18:$B$204,0)),""))</f>
         <v/>
       </c>
       <c r="E205">
@@ -35295,7 +35287,7 @@
       <c r="A206" s="37" t="n"/>
       <c r="C206" s="27" t="n"/>
       <c r="D206">
-        <f>IF($B206="","",IFERROR(INDEX($D$17:$D$205,MATCH($B206,$B$17:$B$205,0)),""))</f>
+        <f>IF($B206="","",IFERROR(INDEX($D$18:$D$205,MATCH($B206,$B$18:$B$205,0)),""))</f>
         <v/>
       </c>
       <c r="E206">
@@ -35315,7 +35307,7 @@
       <c r="A207" s="37" t="n"/>
       <c r="C207" s="27" t="n"/>
       <c r="D207">
-        <f>IF($B207="","",IFERROR(INDEX($D$17:$D$206,MATCH($B207,$B$17:$B$206,0)),""))</f>
+        <f>IF($B207="","",IFERROR(INDEX($D$18:$D$206,MATCH($B207,$B$18:$B$206,0)),""))</f>
         <v/>
       </c>
       <c r="E207">
@@ -35335,7 +35327,7 @@
       <c r="A208" s="37" t="n"/>
       <c r="C208" s="27" t="n"/>
       <c r="D208">
-        <f>IF($B208="","",IFERROR(INDEX($D$17:$D$207,MATCH($B208,$B$17:$B$207,0)),""))</f>
+        <f>IF($B208="","",IFERROR(INDEX($D$18:$D$207,MATCH($B208,$B$18:$B$207,0)),""))</f>
         <v/>
       </c>
       <c r="E208">
@@ -35355,7 +35347,7 @@
       <c r="A209" s="37" t="n"/>
       <c r="C209" s="27" t="n"/>
       <c r="D209">
-        <f>IF($B209="","",IFERROR(INDEX($D$17:$D$208,MATCH($B209,$B$17:$B$208,0)),""))</f>
+        <f>IF($B209="","",IFERROR(INDEX($D$18:$D$208,MATCH($B209,$B$18:$B$208,0)),""))</f>
         <v/>
       </c>
       <c r="E209">
@@ -35375,7 +35367,7 @@
       <c r="A210" s="37" t="n"/>
       <c r="C210" s="27" t="n"/>
       <c r="D210">
-        <f>IF($B210="","",IFERROR(INDEX($D$17:$D$209,MATCH($B210,$B$17:$B$209,0)),""))</f>
+        <f>IF($B210="","",IFERROR(INDEX($D$18:$D$209,MATCH($B210,$B$18:$B$209,0)),""))</f>
         <v/>
       </c>
       <c r="E210">
@@ -35395,7 +35387,7 @@
       <c r="A211" s="37" t="n"/>
       <c r="C211" s="27" t="n"/>
       <c r="D211">
-        <f>IF($B211="","",IFERROR(INDEX($D$17:$D$210,MATCH($B211,$B$17:$B$210,0)),""))</f>
+        <f>IF($B211="","",IFERROR(INDEX($D$18:$D$210,MATCH($B211,$B$18:$B$210,0)),""))</f>
         <v/>
       </c>
       <c r="E211">
@@ -35415,7 +35407,7 @@
       <c r="A212" s="37" t="n"/>
       <c r="C212" s="27" t="n"/>
       <c r="D212">
-        <f>IF($B212="","",IFERROR(INDEX($D$17:$D$211,MATCH($B212,$B$17:$B$211,0)),""))</f>
+        <f>IF($B212="","",IFERROR(INDEX($D$18:$D$211,MATCH($B212,$B$18:$B$211,0)),""))</f>
         <v/>
       </c>
       <c r="E212">
@@ -35435,7 +35427,7 @@
       <c r="A213" s="37" t="n"/>
       <c r="C213" s="27" t="n"/>
       <c r="D213">
-        <f>IF($B213="","",IFERROR(INDEX($D$17:$D$212,MATCH($B213,$B$17:$B$212,0)),""))</f>
+        <f>IF($B213="","",IFERROR(INDEX($D$18:$D$212,MATCH($B213,$B$18:$B$212,0)),""))</f>
         <v/>
       </c>
       <c r="E213">
@@ -35455,7 +35447,7 @@
       <c r="A214" s="37" t="n"/>
       <c r="C214" s="27" t="n"/>
       <c r="D214">
-        <f>IF($B214="","",IFERROR(INDEX($D$17:$D$213,MATCH($B214,$B$17:$B$213,0)),""))</f>
+        <f>IF($B214="","",IFERROR(INDEX($D$18:$D$213,MATCH($B214,$B$18:$B$213,0)),""))</f>
         <v/>
       </c>
       <c r="E214">
@@ -35475,7 +35467,7 @@
       <c r="A215" s="37" t="n"/>
       <c r="C215" s="27" t="n"/>
       <c r="D215">
-        <f>IF($B215="","",IFERROR(INDEX($D$17:$D$214,MATCH($B215,$B$17:$B$214,0)),""))</f>
+        <f>IF($B215="","",IFERROR(INDEX($D$18:$D$214,MATCH($B215,$B$18:$B$214,0)),""))</f>
         <v/>
       </c>
       <c r="E215">
@@ -35495,7 +35487,7 @@
       <c r="A216" s="37" t="n"/>
       <c r="C216" s="27" t="n"/>
       <c r="D216">
-        <f>IF($B216="","",IFERROR(INDEX($D$17:$D$215,MATCH($B216,$B$17:$B$215,0)),""))</f>
+        <f>IF($B216="","",IFERROR(INDEX($D$18:$D$215,MATCH($B216,$B$18:$B$215,0)),""))</f>
         <v/>
       </c>
       <c r="E216">
@@ -35515,7 +35507,7 @@
       <c r="A217" s="37" t="n"/>
       <c r="C217" s="27" t="n"/>
       <c r="D217">
-        <f>IF($B217="","",IFERROR(INDEX($D$17:$D$216,MATCH($B217,$B$17:$B$216,0)),""))</f>
+        <f>IF($B217="","",IFERROR(INDEX($D$18:$D$216,MATCH($B217,$B$18:$B$216,0)),""))</f>
         <v/>
       </c>
       <c r="E217">
@@ -35535,7 +35527,7 @@
       <c r="A218" s="37" t="n"/>
       <c r="C218" s="27" t="n"/>
       <c r="D218">
-        <f>IF($B218="","",IFERROR(INDEX($D$17:$D$217,MATCH($B218,$B$17:$B$217,0)),""))</f>
+        <f>IF($B218="","",IFERROR(INDEX($D$18:$D$217,MATCH($B218,$B$18:$B$217,0)),""))</f>
         <v/>
       </c>
       <c r="E218">
@@ -35555,7 +35547,7 @@
       <c r="A219" s="37" t="n"/>
       <c r="C219" s="27" t="n"/>
       <c r="D219">
-        <f>IF($B219="","",IFERROR(INDEX($D$17:$D$218,MATCH($B219,$B$17:$B$218,0)),""))</f>
+        <f>IF($B219="","",IFERROR(INDEX($D$18:$D$218,MATCH($B219,$B$18:$B$218,0)),""))</f>
         <v/>
       </c>
       <c r="E219">
@@ -35575,7 +35567,7 @@
       <c r="A220" s="37" t="n"/>
       <c r="C220" s="27" t="n"/>
       <c r="D220">
-        <f>IF($B220="","",IFERROR(INDEX($D$17:$D$219,MATCH($B220,$B$17:$B$219,0)),""))</f>
+        <f>IF($B220="","",IFERROR(INDEX($D$18:$D$219,MATCH($B220,$B$18:$B$219,0)),""))</f>
         <v/>
       </c>
       <c r="E220">
@@ -35595,7 +35587,7 @@
       <c r="A221" s="37" t="n"/>
       <c r="C221" s="27" t="n"/>
       <c r="D221">
-        <f>IF($B221="","",IFERROR(INDEX($D$17:$D$220,MATCH($B221,$B$17:$B$220,0)),""))</f>
+        <f>IF($B221="","",IFERROR(INDEX($D$18:$D$220,MATCH($B221,$B$18:$B$220,0)),""))</f>
         <v/>
       </c>
       <c r="E221">
@@ -35615,7 +35607,7 @@
       <c r="A222" s="37" t="n"/>
       <c r="C222" s="27" t="n"/>
       <c r="D222">
-        <f>IF($B222="","",IFERROR(INDEX($D$17:$D$221,MATCH($B222,$B$17:$B$221,0)),""))</f>
+        <f>IF($B222="","",IFERROR(INDEX($D$18:$D$221,MATCH($B222,$B$18:$B$221,0)),""))</f>
         <v/>
       </c>
       <c r="E222">
@@ -35635,7 +35627,7 @@
       <c r="A223" s="37" t="n"/>
       <c r="C223" s="27" t="n"/>
       <c r="D223">
-        <f>IF($B223="","",IFERROR(INDEX($D$17:$D$222,MATCH($B223,$B$17:$B$222,0)),""))</f>
+        <f>IF($B223="","",IFERROR(INDEX($D$18:$D$222,MATCH($B223,$B$18:$B$222,0)),""))</f>
         <v/>
       </c>
       <c r="E223">
@@ -35655,7 +35647,7 @@
       <c r="A224" s="37" t="n"/>
       <c r="C224" s="27" t="n"/>
       <c r="D224">
-        <f>IF($B224="","",IFERROR(INDEX($D$17:$D$223,MATCH($B224,$B$17:$B$223,0)),""))</f>
+        <f>IF($B224="","",IFERROR(INDEX($D$18:$D$223,MATCH($B224,$B$18:$B$223,0)),""))</f>
         <v/>
       </c>
       <c r="E224">
@@ -35675,7 +35667,7 @@
       <c r="A225" s="37" t="n"/>
       <c r="C225" s="27" t="n"/>
       <c r="D225">
-        <f>IF($B225="","",IFERROR(INDEX($D$17:$D$224,MATCH($B225,$B$17:$B$224,0)),""))</f>
+        <f>IF($B225="","",IFERROR(INDEX($D$18:$D$224,MATCH($B225,$B$18:$B$224,0)),""))</f>
         <v/>
       </c>
       <c r="E225">
@@ -35695,7 +35687,7 @@
       <c r="A226" s="37" t="n"/>
       <c r="C226" s="27" t="n"/>
       <c r="D226">
-        <f>IF($B226="","",IFERROR(INDEX($D$17:$D$225,MATCH($B226,$B$17:$B$225,0)),""))</f>
+        <f>IF($B226="","",IFERROR(INDEX($D$18:$D$225,MATCH($B226,$B$18:$B$225,0)),""))</f>
         <v/>
       </c>
       <c r="E226">
@@ -35715,7 +35707,7 @@
       <c r="A227" s="37" t="n"/>
       <c r="C227" s="27" t="n"/>
       <c r="D227">
-        <f>IF($B227="","",IFERROR(INDEX($D$17:$D$226,MATCH($B227,$B$17:$B$226,0)),""))</f>
+        <f>IF($B227="","",IFERROR(INDEX($D$18:$D$226,MATCH($B227,$B$18:$B$226,0)),""))</f>
         <v/>
       </c>
       <c r="E227">
@@ -35735,7 +35727,7 @@
       <c r="A228" s="37" t="n"/>
       <c r="C228" s="27" t="n"/>
       <c r="D228">
-        <f>IF($B228="","",IFERROR(INDEX($D$17:$D$227,MATCH($B228,$B$17:$B$227,0)),""))</f>
+        <f>IF($B228="","",IFERROR(INDEX($D$18:$D$227,MATCH($B228,$B$18:$B$227,0)),""))</f>
         <v/>
       </c>
       <c r="E228">
@@ -35755,7 +35747,7 @@
       <c r="A229" s="37" t="n"/>
       <c r="C229" s="27" t="n"/>
       <c r="D229">
-        <f>IF($B229="","",IFERROR(INDEX($D$17:$D$228,MATCH($B229,$B$17:$B$228,0)),""))</f>
+        <f>IF($B229="","",IFERROR(INDEX($D$18:$D$228,MATCH($B229,$B$18:$B$228,0)),""))</f>
         <v/>
       </c>
       <c r="E229">
@@ -35775,7 +35767,7 @@
       <c r="A230" s="37" t="n"/>
       <c r="C230" s="27" t="n"/>
       <c r="D230">
-        <f>IF($B230="","",IFERROR(INDEX($D$17:$D$229,MATCH($B230,$B$17:$B$229,0)),""))</f>
+        <f>IF($B230="","",IFERROR(INDEX($D$18:$D$229,MATCH($B230,$B$18:$B$229,0)),""))</f>
         <v/>
       </c>
       <c r="E230">
@@ -35795,7 +35787,7 @@
       <c r="A231" s="37" t="n"/>
       <c r="C231" s="27" t="n"/>
       <c r="D231">
-        <f>IF($B231="","",IFERROR(INDEX($D$17:$D$230,MATCH($B231,$B$17:$B$230,0)),""))</f>
+        <f>IF($B231="","",IFERROR(INDEX($D$18:$D$230,MATCH($B231,$B$18:$B$230,0)),""))</f>
         <v/>
       </c>
       <c r="E231">
@@ -35815,7 +35807,7 @@
       <c r="A232" s="37" t="n"/>
       <c r="C232" s="27" t="n"/>
       <c r="D232">
-        <f>IF($B232="","",IFERROR(INDEX($D$17:$D$231,MATCH($B232,$B$17:$B$231,0)),""))</f>
+        <f>IF($B232="","",IFERROR(INDEX($D$18:$D$231,MATCH($B232,$B$18:$B$231,0)),""))</f>
         <v/>
       </c>
       <c r="E232">
@@ -35835,7 +35827,7 @@
       <c r="A233" s="37" t="n"/>
       <c r="C233" s="27" t="n"/>
       <c r="D233">
-        <f>IF($B233="","",IFERROR(INDEX($D$17:$D$232,MATCH($B233,$B$17:$B$232,0)),""))</f>
+        <f>IF($B233="","",IFERROR(INDEX($D$18:$D$232,MATCH($B233,$B$18:$B$232,0)),""))</f>
         <v/>
       </c>
       <c r="E233">
@@ -35855,7 +35847,7 @@
       <c r="A234" s="37" t="n"/>
       <c r="C234" s="27" t="n"/>
       <c r="D234">
-        <f>IF($B234="","",IFERROR(INDEX($D$17:$D$233,MATCH($B234,$B$17:$B$233,0)),""))</f>
+        <f>IF($B234="","",IFERROR(INDEX($D$18:$D$233,MATCH($B234,$B$18:$B$233,0)),""))</f>
         <v/>
       </c>
       <c r="E234">
@@ -35875,7 +35867,7 @@
       <c r="A235" s="37" t="n"/>
       <c r="C235" s="27" t="n"/>
       <c r="D235">
-        <f>IF($B235="","",IFERROR(INDEX($D$17:$D$234,MATCH($B235,$B$17:$B$234,0)),""))</f>
+        <f>IF($B235="","",IFERROR(INDEX($D$18:$D$234,MATCH($B235,$B$18:$B$234,0)),""))</f>
         <v/>
       </c>
       <c r="E235">
@@ -35895,7 +35887,7 @@
       <c r="A236" s="37" t="n"/>
       <c r="C236" s="27" t="n"/>
       <c r="D236">
-        <f>IF($B236="","",IFERROR(INDEX($D$17:$D$235,MATCH($B236,$B$17:$B$235,0)),""))</f>
+        <f>IF($B236="","",IFERROR(INDEX($D$18:$D$235,MATCH($B236,$B$18:$B$235,0)),""))</f>
         <v/>
       </c>
       <c r="E236">
@@ -35915,7 +35907,7 @@
       <c r="A237" s="37" t="n"/>
       <c r="C237" s="27" t="n"/>
       <c r="D237">
-        <f>IF($B237="","",IFERROR(INDEX($D$17:$D$236,MATCH($B237,$B$17:$B$236,0)),""))</f>
+        <f>IF($B237="","",IFERROR(INDEX($D$18:$D$236,MATCH($B237,$B$18:$B$236,0)),""))</f>
         <v/>
       </c>
       <c r="E237">
@@ -35935,7 +35927,7 @@
       <c r="A238" s="37" t="n"/>
       <c r="C238" s="27" t="n"/>
       <c r="D238">
-        <f>IF($B238="","",IFERROR(INDEX($D$17:$D$237,MATCH($B238,$B$17:$B$237,0)),""))</f>
+        <f>IF($B238="","",IFERROR(INDEX($D$18:$D$237,MATCH($B238,$B$18:$B$237,0)),""))</f>
         <v/>
       </c>
       <c r="E238">
@@ -35955,7 +35947,7 @@
       <c r="A239" s="37" t="n"/>
       <c r="C239" s="27" t="n"/>
       <c r="D239">
-        <f>IF($B239="","",IFERROR(INDEX($D$17:$D$238,MATCH($B239,$B$17:$B$238,0)),""))</f>
+        <f>IF($B239="","",IFERROR(INDEX($D$18:$D$238,MATCH($B239,$B$18:$B$238,0)),""))</f>
         <v/>
       </c>
       <c r="E239">
@@ -35975,7 +35967,7 @@
       <c r="A240" s="37" t="n"/>
       <c r="C240" s="27" t="n"/>
       <c r="D240">
-        <f>IF($B240="","",IFERROR(INDEX($D$17:$D$239,MATCH($B240,$B$17:$B$239,0)),""))</f>
+        <f>IF($B240="","",IFERROR(INDEX($D$18:$D$239,MATCH($B240,$B$18:$B$239,0)),""))</f>
         <v/>
       </c>
       <c r="E240">
@@ -35995,7 +35987,7 @@
       <c r="A241" s="37" t="n"/>
       <c r="C241" s="27" t="n"/>
       <c r="D241">
-        <f>IF($B241="","",IFERROR(INDEX($D$17:$D$240,MATCH($B241,$B$17:$B$240,0)),""))</f>
+        <f>IF($B241="","",IFERROR(INDEX($D$18:$D$240,MATCH($B241,$B$18:$B$240,0)),""))</f>
         <v/>
       </c>
       <c r="E241">
@@ -36015,7 +36007,7 @@
       <c r="A242" s="37" t="n"/>
       <c r="C242" s="27" t="n"/>
       <c r="D242">
-        <f>IF($B242="","",IFERROR(INDEX($D$17:$D$241,MATCH($B242,$B$17:$B$241,0)),""))</f>
+        <f>IF($B242="","",IFERROR(INDEX($D$18:$D$241,MATCH($B242,$B$18:$B$241,0)),""))</f>
         <v/>
       </c>
       <c r="E242">
@@ -36035,7 +36027,7 @@
       <c r="A243" s="37" t="n"/>
       <c r="C243" s="27" t="n"/>
       <c r="D243">
-        <f>IF($B243="","",IFERROR(INDEX($D$17:$D$242,MATCH($B243,$B$17:$B$242,0)),""))</f>
+        <f>IF($B243="","",IFERROR(INDEX($D$18:$D$242,MATCH($B243,$B$18:$B$242,0)),""))</f>
         <v/>
       </c>
       <c r="E243">
@@ -36055,7 +36047,7 @@
       <c r="A244" s="37" t="n"/>
       <c r="C244" s="27" t="n"/>
       <c r="D244">
-        <f>IF($B244="","",IFERROR(INDEX($D$17:$D$243,MATCH($B244,$B$17:$B$243,0)),""))</f>
+        <f>IF($B244="","",IFERROR(INDEX($D$18:$D$243,MATCH($B244,$B$18:$B$243,0)),""))</f>
         <v/>
       </c>
       <c r="E244">
@@ -36075,7 +36067,7 @@
       <c r="A245" s="37" t="n"/>
       <c r="C245" s="27" t="n"/>
       <c r="D245">
-        <f>IF($B245="","",IFERROR(INDEX($D$17:$D$244,MATCH($B245,$B$17:$B$244,0)),""))</f>
+        <f>IF($B245="","",IFERROR(INDEX($D$18:$D$244,MATCH($B245,$B$18:$B$244,0)),""))</f>
         <v/>
       </c>
       <c r="E245">
@@ -36095,7 +36087,7 @@
       <c r="A246" s="37" t="n"/>
       <c r="C246" s="27" t="n"/>
       <c r="D246">
-        <f>IF($B246="","",IFERROR(INDEX($D$17:$D$245,MATCH($B246,$B$17:$B$245,0)),""))</f>
+        <f>IF($B246="","",IFERROR(INDEX($D$18:$D$245,MATCH($B246,$B$18:$B$245,0)),""))</f>
         <v/>
       </c>
       <c r="E246">
@@ -36115,7 +36107,7 @@
       <c r="A247" s="37" t="n"/>
       <c r="C247" s="27" t="n"/>
       <c r="D247">
-        <f>IF($B247="","",IFERROR(INDEX($D$17:$D$246,MATCH($B247,$B$17:$B$246,0)),""))</f>
+        <f>IF($B247="","",IFERROR(INDEX($D$18:$D$246,MATCH($B247,$B$18:$B$246,0)),""))</f>
         <v/>
       </c>
       <c r="E247">
@@ -36135,7 +36127,7 @@
       <c r="A248" s="37" t="n"/>
       <c r="C248" s="27" t="n"/>
       <c r="D248">
-        <f>IF($B248="","",IFERROR(INDEX($D$17:$D$247,MATCH($B248,$B$17:$B$247,0)),""))</f>
+        <f>IF($B248="","",IFERROR(INDEX($D$18:$D$247,MATCH($B248,$B$18:$B$247,0)),""))</f>
         <v/>
       </c>
       <c r="E248">
@@ -36155,7 +36147,7 @@
       <c r="A249" s="37" t="n"/>
       <c r="C249" s="27" t="n"/>
       <c r="D249">
-        <f>IF($B249="","",IFERROR(INDEX($D$17:$D$248,MATCH($B249,$B$17:$B$248,0)),""))</f>
+        <f>IF($B249="","",IFERROR(INDEX($D$18:$D$248,MATCH($B249,$B$18:$B$248,0)),""))</f>
         <v/>
       </c>
       <c r="E249">
@@ -36175,7 +36167,7 @@
       <c r="A250" s="37" t="n"/>
       <c r="C250" s="27" t="n"/>
       <c r="D250">
-        <f>IF($B250="","",IFERROR(INDEX($D$17:$D$249,MATCH($B250,$B$17:$B$249,0)),""))</f>
+        <f>IF($B250="","",IFERROR(INDEX($D$18:$D$249,MATCH($B250,$B$18:$B$249,0)),""))</f>
         <v/>
       </c>
       <c r="E250">
@@ -36195,7 +36187,7 @@
       <c r="A251" s="37" t="n"/>
       <c r="C251" s="27" t="n"/>
       <c r="D251">
-        <f>IF($B251="","",IFERROR(INDEX($D$17:$D$250,MATCH($B251,$B$17:$B$250,0)),""))</f>
+        <f>IF($B251="","",IFERROR(INDEX($D$18:$D$250,MATCH($B251,$B$18:$B$250,0)),""))</f>
         <v/>
       </c>
       <c r="E251">
@@ -36215,7 +36207,7 @@
       <c r="A252" s="37" t="n"/>
       <c r="C252" s="27" t="n"/>
       <c r="D252">
-        <f>IF($B252="","",IFERROR(INDEX($D$17:$D$251,MATCH($B252,$B$17:$B$251,0)),""))</f>
+        <f>IF($B252="","",IFERROR(INDEX($D$18:$D$251,MATCH($B252,$B$18:$B$251,0)),""))</f>
         <v/>
       </c>
       <c r="E252">
@@ -36235,7 +36227,7 @@
       <c r="A253" s="37" t="n"/>
       <c r="C253" s="27" t="n"/>
       <c r="D253">
-        <f>IF($B253="","",IFERROR(INDEX($D$17:$D$252,MATCH($B253,$B$17:$B$252,0)),""))</f>
+        <f>IF($B253="","",IFERROR(INDEX($D$18:$D$252,MATCH($B253,$B$18:$B$252,0)),""))</f>
         <v/>
       </c>
       <c r="E253">
@@ -36255,7 +36247,7 @@
       <c r="A254" s="37" t="n"/>
       <c r="C254" s="27" t="n"/>
       <c r="D254">
-        <f>IF($B254="","",IFERROR(INDEX($D$17:$D$253,MATCH($B254,$B$17:$B$253,0)),""))</f>
+        <f>IF($B254="","",IFERROR(INDEX($D$18:$D$253,MATCH($B254,$B$18:$B$253,0)),""))</f>
         <v/>
       </c>
       <c r="E254">
@@ -36275,7 +36267,7 @@
       <c r="A255" s="37" t="n"/>
       <c r="C255" s="27" t="n"/>
       <c r="D255">
-        <f>IF($B255="","",IFERROR(INDEX($D$17:$D$254,MATCH($B255,$B$17:$B$254,0)),""))</f>
+        <f>IF($B255="","",IFERROR(INDEX($D$18:$D$254,MATCH($B255,$B$18:$B$254,0)),""))</f>
         <v/>
       </c>
       <c r="E255">
@@ -36295,7 +36287,7 @@
       <c r="A256" s="37" t="n"/>
       <c r="C256" s="27" t="n"/>
       <c r="D256">
-        <f>IF($B256="","",IFERROR(INDEX($D$17:$D$255,MATCH($B256,$B$17:$B$255,0)),""))</f>
+        <f>IF($B256="","",IFERROR(INDEX($D$18:$D$255,MATCH($B256,$B$18:$B$255,0)),""))</f>
         <v/>
       </c>
       <c r="E256">
@@ -36315,7 +36307,7 @@
       <c r="A257" s="37" t="n"/>
       <c r="C257" s="27" t="n"/>
       <c r="D257">
-        <f>IF($B257="","",IFERROR(INDEX($D$17:$D$256,MATCH($B257,$B$17:$B$256,0)),""))</f>
+        <f>IF($B257="","",IFERROR(INDEX($D$18:$D$256,MATCH($B257,$B$18:$B$256,0)),""))</f>
         <v/>
       </c>
       <c r="E257">
@@ -36335,7 +36327,7 @@
       <c r="A258" s="37" t="n"/>
       <c r="C258" s="27" t="n"/>
       <c r="D258">
-        <f>IF($B258="","",IFERROR(INDEX($D$17:$D$257,MATCH($B258,$B$17:$B$257,0)),""))</f>
+        <f>IF($B258="","",IFERROR(INDEX($D$18:$D$257,MATCH($B258,$B$18:$B$257,0)),""))</f>
         <v/>
       </c>
       <c r="E258">
@@ -36355,7 +36347,7 @@
       <c r="A259" s="37" t="n"/>
       <c r="C259" s="27" t="n"/>
       <c r="D259">
-        <f>IF($B259="","",IFERROR(INDEX($D$17:$D$258,MATCH($B259,$B$17:$B$258,0)),""))</f>
+        <f>IF($B259="","",IFERROR(INDEX($D$18:$D$258,MATCH($B259,$B$18:$B$258,0)),""))</f>
         <v/>
       </c>
       <c r="E259">
@@ -36375,7 +36367,7 @@
       <c r="A260" s="37" t="n"/>
       <c r="C260" s="27" t="n"/>
       <c r="D260">
-        <f>IF($B260="","",IFERROR(INDEX($D$17:$D$259,MATCH($B260,$B$17:$B$259,0)),""))</f>
+        <f>IF($B260="","",IFERROR(INDEX($D$18:$D$259,MATCH($B260,$B$18:$B$259,0)),""))</f>
         <v/>
       </c>
       <c r="E260">
@@ -36395,7 +36387,7 @@
       <c r="A261" s="37" t="n"/>
       <c r="C261" s="27" t="n"/>
       <c r="D261">
-        <f>IF($B261="","",IFERROR(INDEX($D$17:$D$260,MATCH($B261,$B$17:$B$260,0)),""))</f>
+        <f>IF($B261="","",IFERROR(INDEX($D$18:$D$260,MATCH($B261,$B$18:$B$260,0)),""))</f>
         <v/>
       </c>
       <c r="E261">
@@ -36415,7 +36407,7 @@
       <c r="A262" s="37" t="n"/>
       <c r="C262" s="27" t="n"/>
       <c r="D262">
-        <f>IF($B262="","",IFERROR(INDEX($D$17:$D$261,MATCH($B262,$B$17:$B$261,0)),""))</f>
+        <f>IF($B262="","",IFERROR(INDEX($D$18:$D$261,MATCH($B262,$B$18:$B$261,0)),""))</f>
         <v/>
       </c>
       <c r="E262">
@@ -36435,7 +36427,7 @@
       <c r="A263" s="37" t="n"/>
       <c r="C263" s="27" t="n"/>
       <c r="D263">
-        <f>IF($B263="","",IFERROR(INDEX($D$17:$D$262,MATCH($B263,$B$17:$B$262,0)),""))</f>
+        <f>IF($B263="","",IFERROR(INDEX($D$18:$D$262,MATCH($B263,$B$18:$B$262,0)),""))</f>
         <v/>
       </c>
       <c r="E263">
@@ -36455,7 +36447,7 @@
       <c r="A264" s="37" t="n"/>
       <c r="C264" s="27" t="n"/>
       <c r="D264">
-        <f>IF($B264="","",IFERROR(INDEX($D$17:$D$263,MATCH($B264,$B$17:$B$263,0)),""))</f>
+        <f>IF($B264="","",IFERROR(INDEX($D$18:$D$263,MATCH($B264,$B$18:$B$263,0)),""))</f>
         <v/>
       </c>
       <c r="E264">
@@ -36475,7 +36467,7 @@
       <c r="A265" s="37" t="n"/>
       <c r="C265" s="27" t="n"/>
       <c r="D265">
-        <f>IF($B265="","",IFERROR(INDEX($D$17:$D$264,MATCH($B265,$B$17:$B$264,0)),""))</f>
+        <f>IF($B265="","",IFERROR(INDEX($D$18:$D$264,MATCH($B265,$B$18:$B$264,0)),""))</f>
         <v/>
       </c>
       <c r="E265">
@@ -36495,7 +36487,7 @@
       <c r="A266" s="37" t="n"/>
       <c r="C266" s="27" t="n"/>
       <c r="D266">
-        <f>IF($B266="","",IFERROR(INDEX($D$17:$D$265,MATCH($B266,$B$17:$B$265,0)),""))</f>
+        <f>IF($B266="","",IFERROR(INDEX($D$18:$D$265,MATCH($B266,$B$18:$B$265,0)),""))</f>
         <v/>
       </c>
       <c r="E266">
@@ -36515,7 +36507,7 @@
       <c r="A267" s="37" t="n"/>
       <c r="C267" s="27" t="n"/>
       <c r="D267">
-        <f>IF($B267="","",IFERROR(INDEX($D$17:$D$266,MATCH($B267,$B$17:$B$266,0)),""))</f>
+        <f>IF($B267="","",IFERROR(INDEX($D$18:$D$266,MATCH($B267,$B$18:$B$266,0)),""))</f>
         <v/>
       </c>
       <c r="E267">
@@ -36535,7 +36527,7 @@
       <c r="A268" s="37" t="n"/>
       <c r="C268" s="27" t="n"/>
       <c r="D268">
-        <f>IF($B268="","",IFERROR(INDEX($D$17:$D$267,MATCH($B268,$B$17:$B$267,0)),""))</f>
+        <f>IF($B268="","",IFERROR(INDEX($D$18:$D$267,MATCH($B268,$B$18:$B$267,0)),""))</f>
         <v/>
       </c>
       <c r="E268">
@@ -36555,7 +36547,7 @@
       <c r="A269" s="37" t="n"/>
       <c r="C269" s="27" t="n"/>
       <c r="D269">
-        <f>IF($B269="","",IFERROR(INDEX($D$17:$D$268,MATCH($B269,$B$17:$B$268,0)),""))</f>
+        <f>IF($B269="","",IFERROR(INDEX($D$18:$D$268,MATCH($B269,$B$18:$B$268,0)),""))</f>
         <v/>
       </c>
       <c r="E269">
@@ -36575,7 +36567,7 @@
       <c r="A270" s="37" t="n"/>
       <c r="C270" s="27" t="n"/>
       <c r="D270">
-        <f>IF($B270="","",IFERROR(INDEX($D$17:$D$269,MATCH($B270,$B$17:$B$269,0)),""))</f>
+        <f>IF($B270="","",IFERROR(INDEX($D$18:$D$269,MATCH($B270,$B$18:$B$269,0)),""))</f>
         <v/>
       </c>
       <c r="E270">
@@ -36595,7 +36587,7 @@
       <c r="A271" s="37" t="n"/>
       <c r="C271" s="27" t="n"/>
       <c r="D271">
-        <f>IF($B271="","",IFERROR(INDEX($D$17:$D$270,MATCH($B271,$B$17:$B$270,0)),""))</f>
+        <f>IF($B271="","",IFERROR(INDEX($D$18:$D$270,MATCH($B271,$B$18:$B$270,0)),""))</f>
         <v/>
       </c>
       <c r="E271">
@@ -36615,7 +36607,7 @@
       <c r="A272" s="37" t="n"/>
       <c r="C272" s="27" t="n"/>
       <c r="D272">
-        <f>IF($B272="","",IFERROR(INDEX($D$17:$D$271,MATCH($B272,$B$17:$B$271,0)),""))</f>
+        <f>IF($B272="","",IFERROR(INDEX($D$18:$D$271,MATCH($B272,$B$18:$B$271,0)),""))</f>
         <v/>
       </c>
       <c r="E272">
@@ -36635,7 +36627,7 @@
       <c r="A273" s="37" t="n"/>
       <c r="C273" s="27" t="n"/>
       <c r="D273">
-        <f>IF($B273="","",IFERROR(INDEX($D$17:$D$272,MATCH($B273,$B$17:$B$272,0)),""))</f>
+        <f>IF($B273="","",IFERROR(INDEX($D$18:$D$272,MATCH($B273,$B$18:$B$272,0)),""))</f>
         <v/>
       </c>
       <c r="E273">
@@ -36655,7 +36647,7 @@
       <c r="A274" s="37" t="n"/>
       <c r="C274" s="27" t="n"/>
       <c r="D274">
-        <f>IF($B274="","",IFERROR(INDEX($D$17:$D$273,MATCH($B274,$B$17:$B$273,0)),""))</f>
+        <f>IF($B274="","",IFERROR(INDEX($D$18:$D$273,MATCH($B274,$B$18:$B$273,0)),""))</f>
         <v/>
       </c>
       <c r="E274">
@@ -36675,7 +36667,7 @@
       <c r="A275" s="37" t="n"/>
       <c r="C275" s="27" t="n"/>
       <c r="D275">
-        <f>IF($B275="","",IFERROR(INDEX($D$17:$D$274,MATCH($B275,$B$17:$B$274,0)),""))</f>
+        <f>IF($B275="","",IFERROR(INDEX($D$18:$D$274,MATCH($B275,$B$18:$B$274,0)),""))</f>
         <v/>
       </c>
       <c r="E275">
@@ -36695,7 +36687,7 @@
       <c r="A276" s="37" t="n"/>
       <c r="C276" s="27" t="n"/>
       <c r="D276">
-        <f>IF($B276="","",IFERROR(INDEX($D$17:$D$275,MATCH($B276,$B$17:$B$275,0)),""))</f>
+        <f>IF($B276="","",IFERROR(INDEX($D$18:$D$275,MATCH($B276,$B$18:$B$275,0)),""))</f>
         <v/>
       </c>
       <c r="E276">
@@ -36715,7 +36707,7 @@
       <c r="A277" s="37" t="n"/>
       <c r="C277" s="27" t="n"/>
       <c r="D277">
-        <f>IF($B277="","",IFERROR(INDEX($D$17:$D$276,MATCH($B277,$B$17:$B$276,0)),""))</f>
+        <f>IF($B277="","",IFERROR(INDEX($D$18:$D$276,MATCH($B277,$B$18:$B$276,0)),""))</f>
         <v/>
       </c>
       <c r="E277">
@@ -36735,7 +36727,7 @@
       <c r="A278" s="37" t="n"/>
       <c r="C278" s="27" t="n"/>
       <c r="D278">
-        <f>IF($B278="","",IFERROR(INDEX($D$17:$D$277,MATCH($B278,$B$17:$B$277,0)),""))</f>
+        <f>IF($B278="","",IFERROR(INDEX($D$18:$D$277,MATCH($B278,$B$18:$B$277,0)),""))</f>
         <v/>
       </c>
       <c r="E278">
@@ -36755,7 +36747,7 @@
       <c r="A279" s="37" t="n"/>
       <c r="C279" s="27" t="n"/>
       <c r="D279">
-        <f>IF($B279="","",IFERROR(INDEX($D$17:$D$278,MATCH($B279,$B$17:$B$278,0)),""))</f>
+        <f>IF($B279="","",IFERROR(INDEX($D$18:$D$278,MATCH($B279,$B$18:$B$278,0)),""))</f>
         <v/>
       </c>
       <c r="E279">
@@ -36775,7 +36767,7 @@
       <c r="A280" s="37" t="n"/>
       <c r="C280" s="27" t="n"/>
       <c r="D280">
-        <f>IF($B280="","",IFERROR(INDEX($D$17:$D$279,MATCH($B280,$B$17:$B$279,0)),""))</f>
+        <f>IF($B280="","",IFERROR(INDEX($D$18:$D$279,MATCH($B280,$B$18:$B$279,0)),""))</f>
         <v/>
       </c>
       <c r="E280">
@@ -36795,7 +36787,7 @@
       <c r="A281" s="37" t="n"/>
       <c r="C281" s="27" t="n"/>
       <c r="D281">
-        <f>IF($B281="","",IFERROR(INDEX($D$17:$D$280,MATCH($B281,$B$17:$B$280,0)),""))</f>
+        <f>IF($B281="","",IFERROR(INDEX($D$18:$D$280,MATCH($B281,$B$18:$B$280,0)),""))</f>
         <v/>
       </c>
       <c r="E281">
@@ -36815,7 +36807,7 @@
       <c r="A282" s="37" t="n"/>
       <c r="C282" s="27" t="n"/>
       <c r="D282">
-        <f>IF($B282="","",IFERROR(INDEX($D$17:$D$281,MATCH($B282,$B$17:$B$281,0)),""))</f>
+        <f>IF($B282="","",IFERROR(INDEX($D$18:$D$281,MATCH($B282,$B$18:$B$281,0)),""))</f>
         <v/>
       </c>
       <c r="E282">
@@ -36835,7 +36827,7 @@
       <c r="A283" s="37" t="n"/>
       <c r="C283" s="27" t="n"/>
       <c r="D283">
-        <f>IF($B283="","",IFERROR(INDEX($D$17:$D$282,MATCH($B283,$B$17:$B$282,0)),""))</f>
+        <f>IF($B283="","",IFERROR(INDEX($D$18:$D$282,MATCH($B283,$B$18:$B$282,0)),""))</f>
         <v/>
       </c>
       <c r="E283">
@@ -36855,7 +36847,7 @@
       <c r="A284" s="37" t="n"/>
       <c r="C284" s="27" t="n"/>
       <c r="D284">
-        <f>IF($B284="","",IFERROR(INDEX($D$17:$D$283,MATCH($B284,$B$17:$B$283,0)),""))</f>
+        <f>IF($B284="","",IFERROR(INDEX($D$18:$D$283,MATCH($B284,$B$18:$B$283,0)),""))</f>
         <v/>
       </c>
       <c r="E284">
@@ -36875,7 +36867,7 @@
       <c r="A285" s="37" t="n"/>
       <c r="C285" s="27" t="n"/>
       <c r="D285">
-        <f>IF($B285="","",IFERROR(INDEX($D$17:$D$284,MATCH($B285,$B$17:$B$284,0)),""))</f>
+        <f>IF($B285="","",IFERROR(INDEX($D$18:$D$284,MATCH($B285,$B$18:$B$284,0)),""))</f>
         <v/>
       </c>
       <c r="E285">
@@ -36895,7 +36887,7 @@
       <c r="A286" s="37" t="n"/>
       <c r="C286" s="27" t="n"/>
       <c r="D286">
-        <f>IF($B286="","",IFERROR(INDEX($D$17:$D$285,MATCH($B286,$B$17:$B$285,0)),""))</f>
+        <f>IF($B286="","",IFERROR(INDEX($D$18:$D$285,MATCH($B286,$B$18:$B$285,0)),""))</f>
         <v/>
       </c>
       <c r="E286">
@@ -36915,7 +36907,7 @@
       <c r="A287" s="37" t="n"/>
       <c r="C287" s="27" t="n"/>
       <c r="D287">
-        <f>IF($B287="","",IFERROR(INDEX($D$17:$D$286,MATCH($B287,$B$17:$B$286,0)),""))</f>
+        <f>IF($B287="","",IFERROR(INDEX($D$18:$D$286,MATCH($B287,$B$18:$B$286,0)),""))</f>
         <v/>
       </c>
       <c r="E287">
@@ -36935,7 +36927,7 @@
       <c r="A288" s="37" t="n"/>
       <c r="C288" s="27" t="n"/>
       <c r="D288">
-        <f>IF($B288="","",IFERROR(INDEX($D$17:$D$287,MATCH($B288,$B$17:$B$287,0)),""))</f>
+        <f>IF($B288="","",IFERROR(INDEX($D$18:$D$287,MATCH($B288,$B$18:$B$287,0)),""))</f>
         <v/>
       </c>
       <c r="E288">
@@ -36955,7 +36947,7 @@
       <c r="A289" s="37" t="n"/>
       <c r="C289" s="27" t="n"/>
       <c r="D289">
-        <f>IF($B289="","",IFERROR(INDEX($D$17:$D$288,MATCH($B289,$B$17:$B$288,0)),""))</f>
+        <f>IF($B289="","",IFERROR(INDEX($D$18:$D$288,MATCH($B289,$B$18:$B$288,0)),""))</f>
         <v/>
       </c>
       <c r="E289">
@@ -36975,7 +36967,7 @@
       <c r="A290" s="37" t="n"/>
       <c r="C290" s="27" t="n"/>
       <c r="D290">
-        <f>IF($B290="","",IFERROR(INDEX($D$17:$D$289,MATCH($B290,$B$17:$B$289,0)),""))</f>
+        <f>IF($B290="","",IFERROR(INDEX($D$18:$D$289,MATCH($B290,$B$18:$B$289,0)),""))</f>
         <v/>
       </c>
       <c r="E290">
@@ -36995,7 +36987,7 @@
       <c r="A291" s="37" t="n"/>
       <c r="C291" s="27" t="n"/>
       <c r="D291">
-        <f>IF($B291="","",IFERROR(INDEX($D$17:$D$290,MATCH($B291,$B$17:$B$290,0)),""))</f>
+        <f>IF($B291="","",IFERROR(INDEX($D$18:$D$290,MATCH($B291,$B$18:$B$290,0)),""))</f>
         <v/>
       </c>
       <c r="E291">
@@ -37015,7 +37007,7 @@
       <c r="A292" s="37" t="n"/>
       <c r="C292" s="27" t="n"/>
       <c r="D292">
-        <f>IF($B292="","",IFERROR(INDEX($D$17:$D$291,MATCH($B292,$B$17:$B$291,0)),""))</f>
+        <f>IF($B292="","",IFERROR(INDEX($D$18:$D$291,MATCH($B292,$B$18:$B$291,0)),""))</f>
         <v/>
       </c>
       <c r="E292">
@@ -37035,7 +37027,7 @@
       <c r="A293" s="37" t="n"/>
       <c r="C293" s="27" t="n"/>
       <c r="D293">
-        <f>IF($B293="","",IFERROR(INDEX($D$17:$D$292,MATCH($B293,$B$17:$B$292,0)),""))</f>
+        <f>IF($B293="","",IFERROR(INDEX($D$18:$D$292,MATCH($B293,$B$18:$B$292,0)),""))</f>
         <v/>
       </c>
       <c r="E293">
@@ -37055,7 +37047,7 @@
       <c r="A294" s="37" t="n"/>
       <c r="C294" s="27" t="n"/>
       <c r="D294">
-        <f>IF($B294="","",IFERROR(INDEX($D$17:$D$293,MATCH($B294,$B$17:$B$293,0)),""))</f>
+        <f>IF($B294="","",IFERROR(INDEX($D$18:$D$293,MATCH($B294,$B$18:$B$293,0)),""))</f>
         <v/>
       </c>
       <c r="E294">
@@ -37075,7 +37067,7 @@
       <c r="A295" s="37" t="n"/>
       <c r="C295" s="27" t="n"/>
       <c r="D295">
-        <f>IF($B295="","",IFERROR(INDEX($D$17:$D$294,MATCH($B295,$B$17:$B$294,0)),""))</f>
+        <f>IF($B295="","",IFERROR(INDEX($D$18:$D$294,MATCH($B295,$B$18:$B$294,0)),""))</f>
         <v/>
       </c>
       <c r="E295">
@@ -37095,7 +37087,7 @@
       <c r="A296" s="37" t="n"/>
       <c r="C296" s="27" t="n"/>
       <c r="D296">
-        <f>IF($B296="","",IFERROR(INDEX($D$17:$D$295,MATCH($B296,$B$17:$B$295,0)),""))</f>
+        <f>IF($B296="","",IFERROR(INDEX($D$18:$D$295,MATCH($B296,$B$18:$B$295,0)),""))</f>
         <v/>
       </c>
       <c r="E296">
@@ -37115,7 +37107,7 @@
       <c r="A297" s="37" t="n"/>
       <c r="C297" s="27" t="n"/>
       <c r="D297">
-        <f>IF($B297="","",IFERROR(INDEX($D$17:$D$296,MATCH($B297,$B$17:$B$296,0)),""))</f>
+        <f>IF($B297="","",IFERROR(INDEX($D$18:$D$296,MATCH($B297,$B$18:$B$296,0)),""))</f>
         <v/>
       </c>
       <c r="E297">
@@ -37135,7 +37127,7 @@
       <c r="A298" s="37" t="n"/>
       <c r="C298" s="27" t="n"/>
       <c r="D298">
-        <f>IF($B298="","",IFERROR(INDEX($D$17:$D$297,MATCH($B298,$B$17:$B$297,0)),""))</f>
+        <f>IF($B298="","",IFERROR(INDEX($D$18:$D$297,MATCH($B298,$B$18:$B$297,0)),""))</f>
         <v/>
       </c>
       <c r="E298">
@@ -37155,7 +37147,7 @@
       <c r="A299" s="37" t="n"/>
       <c r="C299" s="27" t="n"/>
       <c r="D299">
-        <f>IF($B299="","",IFERROR(INDEX($D$17:$D$298,MATCH($B299,$B$17:$B$298,0)),""))</f>
+        <f>IF($B299="","",IFERROR(INDEX($D$18:$D$298,MATCH($B299,$B$18:$B$298,0)),""))</f>
         <v/>
       </c>
       <c r="E299">
@@ -37175,7 +37167,7 @@
       <c r="A300" s="37" t="n"/>
       <c r="C300" s="27" t="n"/>
       <c r="D300">
-        <f>IF($B300="","",IFERROR(INDEX($D$17:$D$299,MATCH($B300,$B$17:$B$299,0)),""))</f>
+        <f>IF($B300="","",IFERROR(INDEX($D$18:$D$299,MATCH($B300,$B$18:$B$299,0)),""))</f>
         <v/>
       </c>
       <c r="E300">
@@ -37195,7 +37187,7 @@
       <c r="A301" s="37" t="n"/>
       <c r="C301" s="27" t="n"/>
       <c r="D301">
-        <f>IF($B301="","",IFERROR(INDEX($D$17:$D$300,MATCH($B301,$B$17:$B$300,0)),""))</f>
+        <f>IF($B301="","",IFERROR(INDEX($D$18:$D$300,MATCH($B301,$B$18:$B$300,0)),""))</f>
         <v/>
       </c>
       <c r="E301">
@@ -37215,7 +37207,7 @@
       <c r="A302" s="37" t="n"/>
       <c r="C302" s="27" t="n"/>
       <c r="D302">
-        <f>IF($B302="","",IFERROR(INDEX($D$17:$D$301,MATCH($B302,$B$17:$B$301,0)),""))</f>
+        <f>IF($B302="","",IFERROR(INDEX($D$18:$D$301,MATCH($B302,$B$18:$B$301,0)),""))</f>
         <v/>
       </c>
       <c r="E302">
@@ -37235,7 +37227,7 @@
       <c r="A303" s="37" t="n"/>
       <c r="C303" s="27" t="n"/>
       <c r="D303">
-        <f>IF($B303="","",IFERROR(INDEX($D$17:$D$302,MATCH($B303,$B$17:$B$302,0)),""))</f>
+        <f>IF($B303="","",IFERROR(INDEX($D$18:$D$302,MATCH($B303,$B$18:$B$302,0)),""))</f>
         <v/>
       </c>
       <c r="E303">
@@ -37255,7 +37247,7 @@
       <c r="A304" s="37" t="n"/>
       <c r="C304" s="27" t="n"/>
       <c r="D304">
-        <f>IF($B304="","",IFERROR(INDEX($D$17:$D$303,MATCH($B304,$B$17:$B$303,0)),""))</f>
+        <f>IF($B304="","",IFERROR(INDEX($D$18:$D$303,MATCH($B304,$B$18:$B$303,0)),""))</f>
         <v/>
       </c>
       <c r="E304">
@@ -37275,7 +37267,7 @@
       <c r="A305" s="37" t="n"/>
       <c r="C305" s="27" t="n"/>
       <c r="D305">
-        <f>IF($B305="","",IFERROR(INDEX($D$17:$D$304,MATCH($B305,$B$17:$B$304,0)),""))</f>
+        <f>IF($B305="","",IFERROR(INDEX($D$18:$D$304,MATCH($B305,$B$18:$B$304,0)),""))</f>
         <v/>
       </c>
       <c r="E305">
@@ -37295,7 +37287,7 @@
       <c r="A306" s="37" t="n"/>
       <c r="C306" s="27" t="n"/>
       <c r="D306">
-        <f>IF($B306="","",IFERROR(INDEX($D$17:$D$305,MATCH($B306,$B$17:$B$305,0)),""))</f>
+        <f>IF($B306="","",IFERROR(INDEX($D$18:$D$305,MATCH($B306,$B$18:$B$305,0)),""))</f>
         <v/>
       </c>
       <c r="E306">
@@ -37315,7 +37307,7 @@
       <c r="A307" s="37" t="n"/>
       <c r="C307" s="27" t="n"/>
       <c r="D307">
-        <f>IF($B307="","",IFERROR(INDEX($D$17:$D$306,MATCH($B307,$B$17:$B$306,0)),""))</f>
+        <f>IF($B307="","",IFERROR(INDEX($D$18:$D$306,MATCH($B307,$B$18:$B$306,0)),""))</f>
         <v/>
       </c>
       <c r="E307">
@@ -37335,7 +37327,7 @@
       <c r="A308" s="37" t="n"/>
       <c r="C308" s="27" t="n"/>
       <c r="D308">
-        <f>IF($B308="","",IFERROR(INDEX($D$17:$D$307,MATCH($B308,$B$17:$B$307,0)),""))</f>
+        <f>IF($B308="","",IFERROR(INDEX($D$18:$D$307,MATCH($B308,$B$18:$B$307,0)),""))</f>
         <v/>
       </c>
       <c r="E308">
@@ -37355,7 +37347,7 @@
       <c r="A309" s="37" t="n"/>
       <c r="C309" s="27" t="n"/>
       <c r="D309">
-        <f>IF($B309="","",IFERROR(INDEX($D$17:$D$308,MATCH($B309,$B$17:$B$308,0)),""))</f>
+        <f>IF($B309="","",IFERROR(INDEX($D$18:$D$308,MATCH($B309,$B$18:$B$308,0)),""))</f>
         <v/>
       </c>
       <c r="E309">
@@ -37375,7 +37367,7 @@
       <c r="A310" s="37" t="n"/>
       <c r="C310" s="27" t="n"/>
       <c r="D310">
-        <f>IF($B310="","",IFERROR(INDEX($D$17:$D$309,MATCH($B310,$B$17:$B$309,0)),""))</f>
+        <f>IF($B310="","",IFERROR(INDEX($D$18:$D$309,MATCH($B310,$B$18:$B$309,0)),""))</f>
         <v/>
       </c>
       <c r="E310">
@@ -37395,7 +37387,7 @@
       <c r="A311" s="37" t="n"/>
       <c r="C311" s="27" t="n"/>
       <c r="D311">
-        <f>IF($B311="","",IFERROR(INDEX($D$17:$D$310,MATCH($B311,$B$17:$B$310,0)),""))</f>
+        <f>IF($B311="","",IFERROR(INDEX($D$18:$D$310,MATCH($B311,$B$18:$B$310,0)),""))</f>
         <v/>
       </c>
       <c r="E311">
@@ -37415,7 +37407,7 @@
       <c r="A312" s="37" t="n"/>
       <c r="C312" s="27" t="n"/>
       <c r="D312">
-        <f>IF($B312="","",IFERROR(INDEX($D$17:$D$311,MATCH($B312,$B$17:$B$311,0)),""))</f>
+        <f>IF($B312="","",IFERROR(INDEX($D$18:$D$311,MATCH($B312,$B$18:$B$311,0)),""))</f>
         <v/>
       </c>
       <c r="E312">
@@ -37435,7 +37427,7 @@
       <c r="A313" s="37" t="n"/>
       <c r="C313" s="27" t="n"/>
       <c r="D313">
-        <f>IF($B313="","",IFERROR(INDEX($D$17:$D$312,MATCH($B313,$B$17:$B$312,0)),""))</f>
+        <f>IF($B313="","",IFERROR(INDEX($D$18:$D$312,MATCH($B313,$B$18:$B$312,0)),""))</f>
         <v/>
       </c>
       <c r="E313">
@@ -37455,7 +37447,7 @@
       <c r="A314" s="37" t="n"/>
       <c r="C314" s="27" t="n"/>
       <c r="D314">
-        <f>IF($B314="","",IFERROR(INDEX($D$17:$D$313,MATCH($B314,$B$17:$B$313,0)),""))</f>
+        <f>IF($B314="","",IFERROR(INDEX($D$18:$D$313,MATCH($B314,$B$18:$B$313,0)),""))</f>
         <v/>
       </c>
       <c r="E314">
@@ -37475,7 +37467,7 @@
       <c r="A315" s="37" t="n"/>
       <c r="C315" s="27" t="n"/>
       <c r="D315">
-        <f>IF($B315="","",IFERROR(INDEX($D$17:$D$314,MATCH($B315,$B$17:$B$314,0)),""))</f>
+        <f>IF($B315="","",IFERROR(INDEX($D$18:$D$314,MATCH($B315,$B$18:$B$314,0)),""))</f>
         <v/>
       </c>
       <c r="E315">
@@ -37495,7 +37487,7 @@
       <c r="A316" s="37" t="n"/>
       <c r="C316" s="27" t="n"/>
       <c r="D316">
-        <f>IF($B316="","",IFERROR(INDEX($D$17:$D$315,MATCH($B316,$B$17:$B$315,0)),""))</f>
+        <f>IF($B316="","",IFERROR(INDEX($D$18:$D$315,MATCH($B316,$B$18:$B$315,0)),""))</f>
         <v/>
       </c>
       <c r="E316">
@@ -37515,7 +37507,7 @@
       <c r="A317" s="37" t="n"/>
       <c r="C317" s="27" t="n"/>
       <c r="D317">
-        <f>IF($B317="","",IFERROR(INDEX($D$17:$D$316,MATCH($B317,$B$17:$B$316,0)),""))</f>
+        <f>IF($B317="","",IFERROR(INDEX($D$18:$D$316,MATCH($B317,$B$18:$B$316,0)),""))</f>
         <v/>
       </c>
       <c r="E317">
@@ -37535,7 +37527,7 @@
       <c r="A318" s="37" t="n"/>
       <c r="C318" s="27" t="n"/>
       <c r="D318">
-        <f>IF($B318="","",IFERROR(INDEX($D$17:$D$317,MATCH($B318,$B$17:$B$317,0)),""))</f>
+        <f>IF($B318="","",IFERROR(INDEX($D$18:$D$317,MATCH($B318,$B$18:$B$317,0)),""))</f>
         <v/>
       </c>
       <c r="E318">
@@ -37555,7 +37547,7 @@
       <c r="A319" s="37" t="n"/>
       <c r="C319" s="27" t="n"/>
       <c r="D319">
-        <f>IF($B319="","",IFERROR(INDEX($D$17:$D$318,MATCH($B319,$B$17:$B$318,0)),""))</f>
+        <f>IF($B319="","",IFERROR(INDEX($D$18:$D$318,MATCH($B319,$B$18:$B$318,0)),""))</f>
         <v/>
       </c>
       <c r="E319">
@@ -37575,7 +37567,7 @@
       <c r="A320" s="37" t="n"/>
       <c r="C320" s="27" t="n"/>
       <c r="D320">
-        <f>IF($B320="","",IFERROR(INDEX($D$17:$D$319,MATCH($B320,$B$17:$B$319,0)),""))</f>
+        <f>IF($B320="","",IFERROR(INDEX($D$18:$D$319,MATCH($B320,$B$18:$B$319,0)),""))</f>
         <v/>
       </c>
       <c r="E320">
@@ -37595,7 +37587,7 @@
       <c r="A321" s="37" t="n"/>
       <c r="C321" s="27" t="n"/>
       <c r="D321">
-        <f>IF($B321="","",IFERROR(INDEX($D$17:$D$320,MATCH($B321,$B$17:$B$320,0)),""))</f>
+        <f>IF($B321="","",IFERROR(INDEX($D$18:$D$320,MATCH($B321,$B$18:$B$320,0)),""))</f>
         <v/>
       </c>
       <c r="E321">
@@ -37615,7 +37607,7 @@
       <c r="A322" s="37" t="n"/>
       <c r="C322" s="27" t="n"/>
       <c r="D322">
-        <f>IF($B322="","",IFERROR(INDEX($D$17:$D$321,MATCH($B322,$B$17:$B$321,0)),""))</f>
+        <f>IF($B322="","",IFERROR(INDEX($D$18:$D$321,MATCH($B322,$B$18:$B$321,0)),""))</f>
         <v/>
       </c>
       <c r="E322">
@@ -37635,7 +37627,7 @@
       <c r="A323" s="37" t="n"/>
       <c r="C323" s="27" t="n"/>
       <c r="D323">
-        <f>IF($B323="","",IFERROR(INDEX($D$17:$D$322,MATCH($B323,$B$17:$B$322,0)),""))</f>
+        <f>IF($B323="","",IFERROR(INDEX($D$18:$D$322,MATCH($B323,$B$18:$B$322,0)),""))</f>
         <v/>
       </c>
       <c r="E323">
@@ -37655,7 +37647,7 @@
       <c r="A324" s="37" t="n"/>
       <c r="C324" s="27" t="n"/>
       <c r="D324">
-        <f>IF($B324="","",IFERROR(INDEX($D$17:$D$323,MATCH($B324,$B$17:$B$323,0)),""))</f>
+        <f>IF($B324="","",IFERROR(INDEX($D$18:$D$323,MATCH($B324,$B$18:$B$323,0)),""))</f>
         <v/>
       </c>
       <c r="E324">
@@ -37675,7 +37667,7 @@
       <c r="A325" s="37" t="n"/>
       <c r="C325" s="27" t="n"/>
       <c r="D325">
-        <f>IF($B325="","",IFERROR(INDEX($D$17:$D$324,MATCH($B325,$B$17:$B$324,0)),""))</f>
+        <f>IF($B325="","",IFERROR(INDEX($D$18:$D$324,MATCH($B325,$B$18:$B$324,0)),""))</f>
         <v/>
       </c>
       <c r="E325">
@@ -37695,7 +37687,7 @@
       <c r="A326" s="37" t="n"/>
       <c r="C326" s="27" t="n"/>
       <c r="D326">
-        <f>IF($B326="","",IFERROR(INDEX($D$17:$D$325,MATCH($B326,$B$17:$B$325,0)),""))</f>
+        <f>IF($B326="","",IFERROR(INDEX($D$18:$D$325,MATCH($B326,$B$18:$B$325,0)),""))</f>
         <v/>
       </c>
       <c r="E326">
@@ -37715,7 +37707,7 @@
       <c r="A327" s="37" t="n"/>
       <c r="C327" s="27" t="n"/>
       <c r="D327">
-        <f>IF($B327="","",IFERROR(INDEX($D$17:$D$326,MATCH($B327,$B$17:$B$326,0)),""))</f>
+        <f>IF($B327="","",IFERROR(INDEX($D$18:$D$326,MATCH($B327,$B$18:$B$326,0)),""))</f>
         <v/>
       </c>
       <c r="E327">
@@ -37735,7 +37727,7 @@
       <c r="A328" s="37" t="n"/>
       <c r="C328" s="27" t="n"/>
       <c r="D328">
-        <f>IF($B328="","",IFERROR(INDEX($D$17:$D$327,MATCH($B328,$B$17:$B$327,0)),""))</f>
+        <f>IF($B328="","",IFERROR(INDEX($D$18:$D$327,MATCH($B328,$B$18:$B$327,0)),""))</f>
         <v/>
       </c>
       <c r="E328">
@@ -37755,7 +37747,7 @@
       <c r="A329" s="37" t="n"/>
       <c r="C329" s="27" t="n"/>
       <c r="D329">
-        <f>IF($B329="","",IFERROR(INDEX($D$17:$D$328,MATCH($B329,$B$17:$B$328,0)),""))</f>
+        <f>IF($B329="","",IFERROR(INDEX($D$18:$D$328,MATCH($B329,$B$18:$B$328,0)),""))</f>
         <v/>
       </c>
       <c r="E329">
@@ -37775,7 +37767,7 @@
       <c r="A330" s="37" t="n"/>
       <c r="C330" s="27" t="n"/>
       <c r="D330">
-        <f>IF($B330="","",IFERROR(INDEX($D$17:$D$329,MATCH($B330,$B$17:$B$329,0)),""))</f>
+        <f>IF($B330="","",IFERROR(INDEX($D$18:$D$329,MATCH($B330,$B$18:$B$329,0)),""))</f>
         <v/>
       </c>
       <c r="E330">
@@ -37795,7 +37787,7 @@
       <c r="A331" s="37" t="n"/>
       <c r="C331" s="27" t="n"/>
       <c r="D331">
-        <f>IF($B331="","",IFERROR(INDEX($D$17:$D$330,MATCH($B331,$B$17:$B$330,0)),""))</f>
+        <f>IF($B331="","",IFERROR(INDEX($D$18:$D$330,MATCH($B331,$B$18:$B$330,0)),""))</f>
         <v/>
       </c>
       <c r="E331">
@@ -37815,7 +37807,7 @@
       <c r="A332" s="37" t="n"/>
       <c r="C332" s="27" t="n"/>
       <c r="D332">
-        <f>IF($B332="","",IFERROR(INDEX($D$17:$D$331,MATCH($B332,$B$17:$B$331,0)),""))</f>
+        <f>IF($B332="","",IFERROR(INDEX($D$18:$D$331,MATCH($B332,$B$18:$B$331,0)),""))</f>
         <v/>
       </c>
       <c r="E332">
@@ -37835,7 +37827,7 @@
       <c r="A333" s="37" t="n"/>
       <c r="C333" s="27" t="n"/>
       <c r="D333">
-        <f>IF($B333="","",IFERROR(INDEX($D$17:$D$332,MATCH($B333,$B$17:$B$332,0)),""))</f>
+        <f>IF($B333="","",IFERROR(INDEX($D$18:$D$332,MATCH($B333,$B$18:$B$332,0)),""))</f>
         <v/>
       </c>
       <c r="E333">
@@ -37855,7 +37847,7 @@
       <c r="A334" s="37" t="n"/>
       <c r="C334" s="27" t="n"/>
       <c r="D334">
-        <f>IF($B334="","",IFERROR(INDEX($D$17:$D$333,MATCH($B334,$B$17:$B$333,0)),""))</f>
+        <f>IF($B334="","",IFERROR(INDEX($D$18:$D$333,MATCH($B334,$B$18:$B$333,0)),""))</f>
         <v/>
       </c>
       <c r="E334">
@@ -37875,7 +37867,7 @@
       <c r="A335" s="37" t="n"/>
       <c r="C335" s="27" t="n"/>
       <c r="D335">
-        <f>IF($B335="","",IFERROR(INDEX($D$17:$D$334,MATCH($B335,$B$17:$B$334,0)),""))</f>
+        <f>IF($B335="","",IFERROR(INDEX($D$18:$D$334,MATCH($B335,$B$18:$B$334,0)),""))</f>
         <v/>
       </c>
       <c r="E335">
@@ -37895,7 +37887,7 @@
       <c r="A336" s="37" t="n"/>
       <c r="C336" s="27" t="n"/>
       <c r="D336">
-        <f>IF($B336="","",IFERROR(INDEX($D$17:$D$335,MATCH($B336,$B$17:$B$335,0)),""))</f>
+        <f>IF($B336="","",IFERROR(INDEX($D$18:$D$335,MATCH($B336,$B$18:$B$335,0)),""))</f>
         <v/>
       </c>
       <c r="E336">
@@ -37915,7 +37907,7 @@
       <c r="A337" s="37" t="n"/>
       <c r="C337" s="27" t="n"/>
       <c r="D337">
-        <f>IF($B337="","",IFERROR(INDEX($D$17:$D$336,MATCH($B337,$B$17:$B$336,0)),""))</f>
+        <f>IF($B337="","",IFERROR(INDEX($D$18:$D$336,MATCH($B337,$B$18:$B$336,0)),""))</f>
         <v/>
       </c>
       <c r="E337">
@@ -37935,7 +37927,7 @@
       <c r="A338" s="37" t="n"/>
       <c r="C338" s="27" t="n"/>
       <c r="D338">
-        <f>IF($B338="","",IFERROR(INDEX($D$17:$D$337,MATCH($B338,$B$17:$B$337,0)),""))</f>
+        <f>IF($B338="","",IFERROR(INDEX($D$18:$D$337,MATCH($B338,$B$18:$B$337,0)),""))</f>
         <v/>
       </c>
       <c r="E338">
@@ -37955,7 +37947,7 @@
       <c r="A339" s="37" t="n"/>
       <c r="C339" s="27" t="n"/>
       <c r="D339">
-        <f>IF($B339="","",IFERROR(INDEX($D$17:$D$338,MATCH($B339,$B$17:$B$338,0)),""))</f>
+        <f>IF($B339="","",IFERROR(INDEX($D$18:$D$338,MATCH($B339,$B$18:$B$338,0)),""))</f>
         <v/>
       </c>
       <c r="E339">
@@ -37975,7 +37967,7 @@
       <c r="A340" s="37" t="n"/>
       <c r="C340" s="27" t="n"/>
       <c r="D340">
-        <f>IF($B340="","",IFERROR(INDEX($D$17:$D$339,MATCH($B340,$B$17:$B$339,0)),""))</f>
+        <f>IF($B340="","",IFERROR(INDEX($D$18:$D$339,MATCH($B340,$B$18:$B$339,0)),""))</f>
         <v/>
       </c>
       <c r="E340">
@@ -37995,7 +37987,7 @@
       <c r="A341" s="37" t="n"/>
       <c r="C341" s="27" t="n"/>
       <c r="D341">
-        <f>IF($B341="","",IFERROR(INDEX($D$17:$D$340,MATCH($B341,$B$17:$B$340,0)),""))</f>
+        <f>IF($B341="","",IFERROR(INDEX($D$18:$D$340,MATCH($B341,$B$18:$B$340,0)),""))</f>
         <v/>
       </c>
       <c r="E341">
@@ -38015,7 +38007,7 @@
       <c r="A342" s="37" t="n"/>
       <c r="C342" s="27" t="n"/>
       <c r="D342">
-        <f>IF($B342="","",IFERROR(INDEX($D$17:$D$341,MATCH($B342,$B$17:$B$341,0)),""))</f>
+        <f>IF($B342="","",IFERROR(INDEX($D$18:$D$341,MATCH($B342,$B$18:$B$341,0)),""))</f>
         <v/>
       </c>
       <c r="E342">
@@ -38035,7 +38027,7 @@
       <c r="A343" s="37" t="n"/>
       <c r="C343" s="27" t="n"/>
       <c r="D343">
-        <f>IF($B343="","",IFERROR(INDEX($D$17:$D$342,MATCH($B343,$B$17:$B$342,0)),""))</f>
+        <f>IF($B343="","",IFERROR(INDEX($D$18:$D$342,MATCH($B343,$B$18:$B$342,0)),""))</f>
         <v/>
       </c>
       <c r="E343">
@@ -38055,7 +38047,7 @@
       <c r="A344" s="37" t="n"/>
       <c r="C344" s="27" t="n"/>
       <c r="D344">
-        <f>IF($B344="","",IFERROR(INDEX($D$17:$D$343,MATCH($B344,$B$17:$B$343,0)),""))</f>
+        <f>IF($B344="","",IFERROR(INDEX($D$18:$D$343,MATCH($B344,$B$18:$B$343,0)),""))</f>
         <v/>
       </c>
       <c r="E344">
@@ -38075,7 +38067,7 @@
       <c r="A345" s="37" t="n"/>
       <c r="C345" s="27" t="n"/>
       <c r="D345">
-        <f>IF($B345="","",IFERROR(INDEX($D$17:$D$344,MATCH($B345,$B$17:$B$344,0)),""))</f>
+        <f>IF($B345="","",IFERROR(INDEX($D$18:$D$344,MATCH($B345,$B$18:$B$344,0)),""))</f>
         <v/>
       </c>
       <c r="E345">
@@ -38095,7 +38087,7 @@
       <c r="A346" s="37" t="n"/>
       <c r="C346" s="27" t="n"/>
       <c r="D346">
-        <f>IF($B346="","",IFERROR(INDEX($D$17:$D$345,MATCH($B346,$B$17:$B$345,0)),""))</f>
+        <f>IF($B346="","",IFERROR(INDEX($D$18:$D$345,MATCH($B346,$B$18:$B$345,0)),""))</f>
         <v/>
       </c>
       <c r="E346">
@@ -38115,7 +38107,7 @@
       <c r="A347" s="37" t="n"/>
       <c r="C347" s="27" t="n"/>
       <c r="D347">
-        <f>IF($B347="","",IFERROR(INDEX($D$17:$D$346,MATCH($B347,$B$17:$B$346,0)),""))</f>
+        <f>IF($B347="","",IFERROR(INDEX($D$18:$D$346,MATCH($B347,$B$18:$B$346,0)),""))</f>
         <v/>
       </c>
       <c r="E347">
@@ -38135,7 +38127,7 @@
       <c r="A348" s="37" t="n"/>
       <c r="C348" s="27" t="n"/>
       <c r="D348">
-        <f>IF($B348="","",IFERROR(INDEX($D$17:$D$347,MATCH($B348,$B$17:$B$347,0)),""))</f>
+        <f>IF($B348="","",IFERROR(INDEX($D$18:$D$347,MATCH($B348,$B$18:$B$347,0)),""))</f>
         <v/>
       </c>
       <c r="E348">
@@ -38155,7 +38147,7 @@
       <c r="A349" s="37" t="n"/>
       <c r="C349" s="27" t="n"/>
       <c r="D349">
-        <f>IF($B349="","",IFERROR(INDEX($D$17:$D$348,MATCH($B349,$B$17:$B$348,0)),""))</f>
+        <f>IF($B349="","",IFERROR(INDEX($D$18:$D$348,MATCH($B349,$B$18:$B$348,0)),""))</f>
         <v/>
       </c>
       <c r="E349">
@@ -38175,7 +38167,7 @@
       <c r="A350" s="37" t="n"/>
       <c r="C350" s="27" t="n"/>
       <c r="D350">
-        <f>IF($B350="","",IFERROR(INDEX($D$17:$D$349,MATCH($B350,$B$17:$B$349,0)),""))</f>
+        <f>IF($B350="","",IFERROR(INDEX($D$18:$D$349,MATCH($B350,$B$18:$B$349,0)),""))</f>
         <v/>
       </c>
       <c r="E350">
@@ -38195,7 +38187,7 @@
       <c r="A351" s="37" t="n"/>
       <c r="C351" s="27" t="n"/>
       <c r="D351">
-        <f>IF($B351="","",IFERROR(INDEX($D$17:$D$350,MATCH($B351,$B$17:$B$350,0)),""))</f>
+        <f>IF($B351="","",IFERROR(INDEX($D$18:$D$350,MATCH($B351,$B$18:$B$350,0)),""))</f>
         <v/>
       </c>
       <c r="E351">
@@ -38215,7 +38207,7 @@
       <c r="A352" s="37" t="n"/>
       <c r="C352" s="27" t="n"/>
       <c r="D352">
-        <f>IF($B352="","",IFERROR(INDEX($D$17:$D$351,MATCH($B352,$B$17:$B$351,0)),""))</f>
+        <f>IF($B352="","",IFERROR(INDEX($D$18:$D$351,MATCH($B352,$B$18:$B$351,0)),""))</f>
         <v/>
       </c>
       <c r="E352">
@@ -38235,7 +38227,7 @@
       <c r="A353" s="37" t="n"/>
       <c r="C353" s="27" t="n"/>
       <c r="D353">
-        <f>IF($B353="","",IFERROR(INDEX($D$17:$D$352,MATCH($B353,$B$17:$B$352,0)),""))</f>
+        <f>IF($B353="","",IFERROR(INDEX($D$18:$D$352,MATCH($B353,$B$18:$B$352,0)),""))</f>
         <v/>
       </c>
       <c r="E353">
@@ -38255,7 +38247,7 @@
       <c r="A354" s="37" t="n"/>
       <c r="C354" s="27" t="n"/>
       <c r="D354">
-        <f>IF($B354="","",IFERROR(INDEX($D$17:$D$353,MATCH($B354,$B$17:$B$353,0)),""))</f>
+        <f>IF($B354="","",IFERROR(INDEX($D$18:$D$353,MATCH($B354,$B$18:$B$353,0)),""))</f>
         <v/>
       </c>
       <c r="E354">
@@ -38275,7 +38267,7 @@
       <c r="A355" s="37" t="n"/>
       <c r="C355" s="27" t="n"/>
       <c r="D355">
-        <f>IF($B355="","",IFERROR(INDEX($D$17:$D$354,MATCH($B355,$B$17:$B$354,0)),""))</f>
+        <f>IF($B355="","",IFERROR(INDEX($D$18:$D$354,MATCH($B355,$B$18:$B$354,0)),""))</f>
         <v/>
       </c>
       <c r="E355">
@@ -38295,7 +38287,7 @@
       <c r="A356" s="37" t="n"/>
       <c r="C356" s="27" t="n"/>
       <c r="D356">
-        <f>IF($B356="","",IFERROR(INDEX($D$17:$D$355,MATCH($B356,$B$17:$B$355,0)),""))</f>
+        <f>IF($B356="","",IFERROR(INDEX($D$18:$D$355,MATCH($B356,$B$18:$B$355,0)),""))</f>
         <v/>
       </c>
       <c r="E356">
@@ -38315,7 +38307,7 @@
       <c r="A357" s="37" t="n"/>
       <c r="C357" s="27" t="n"/>
       <c r="D357">
-        <f>IF($B357="","",IFERROR(INDEX($D$17:$D$356,MATCH($B357,$B$17:$B$356,0)),""))</f>
+        <f>IF($B357="","",IFERROR(INDEX($D$18:$D$356,MATCH($B357,$B$18:$B$356,0)),""))</f>
         <v/>
       </c>
       <c r="E357">
@@ -38335,7 +38327,7 @@
       <c r="A358" s="37" t="n"/>
       <c r="C358" s="27" t="n"/>
       <c r="D358">
-        <f>IF($B358="","",IFERROR(INDEX($D$17:$D$357,MATCH($B358,$B$17:$B$357,0)),""))</f>
+        <f>IF($B358="","",IFERROR(INDEX($D$18:$D$357,MATCH($B358,$B$18:$B$357,0)),""))</f>
         <v/>
       </c>
       <c r="E358">
@@ -38355,7 +38347,7 @@
       <c r="A359" s="37" t="n"/>
       <c r="C359" s="27" t="n"/>
       <c r="D359">
-        <f>IF($B359="","",IFERROR(INDEX($D$17:$D$358,MATCH($B359,$B$17:$B$358,0)),""))</f>
+        <f>IF($B359="","",IFERROR(INDEX($D$18:$D$358,MATCH($B359,$B$18:$B$358,0)),""))</f>
         <v/>
       </c>
       <c r="E359">
@@ -38375,7 +38367,7 @@
       <c r="A360" s="37" t="n"/>
       <c r="C360" s="27" t="n"/>
       <c r="D360">
-        <f>IF($B360="","",IFERROR(INDEX($D$17:$D$359,MATCH($B360,$B$17:$B$359,0)),""))</f>
+        <f>IF($B360="","",IFERROR(INDEX($D$18:$D$359,MATCH($B360,$B$18:$B$359,0)),""))</f>
         <v/>
       </c>
       <c r="E360">
@@ -38395,7 +38387,7 @@
       <c r="A361" s="37" t="n"/>
       <c r="C361" s="27" t="n"/>
       <c r="D361">
-        <f>IF($B361="","",IFERROR(INDEX($D$17:$D$360,MATCH($B361,$B$17:$B$360,0)),""))</f>
+        <f>IF($B361="","",IFERROR(INDEX($D$18:$D$360,MATCH($B361,$B$18:$B$360,0)),""))</f>
         <v/>
       </c>
       <c r="E361">
@@ -38415,7 +38407,7 @@
       <c r="A362" s="37" t="n"/>
       <c r="C362" s="27" t="n"/>
       <c r="D362">
-        <f>IF($B362="","",IFERROR(INDEX($D$17:$D$361,MATCH($B362,$B$17:$B$361,0)),""))</f>
+        <f>IF($B362="","",IFERROR(INDEX($D$18:$D$361,MATCH($B362,$B$18:$B$361,0)),""))</f>
         <v/>
       </c>
       <c r="E362">
@@ -38435,7 +38427,7 @@
       <c r="A363" s="37" t="n"/>
       <c r="C363" s="27" t="n"/>
       <c r="D363">
-        <f>IF($B363="","",IFERROR(INDEX($D$17:$D$362,MATCH($B363,$B$17:$B$362,0)),""))</f>
+        <f>IF($B363="","",IFERROR(INDEX($D$18:$D$362,MATCH($B363,$B$18:$B$362,0)),""))</f>
         <v/>
       </c>
       <c r="E363">
@@ -38455,7 +38447,7 @@
       <c r="A364" s="37" t="n"/>
       <c r="C364" s="27" t="n"/>
       <c r="D364">
-        <f>IF($B364="","",IFERROR(INDEX($D$17:$D$363,MATCH($B364,$B$17:$B$363,0)),""))</f>
+        <f>IF($B364="","",IFERROR(INDEX($D$18:$D$363,MATCH($B364,$B$18:$B$363,0)),""))</f>
         <v/>
       </c>
       <c r="E364">
@@ -38475,7 +38467,7 @@
       <c r="A365" s="37" t="n"/>
       <c r="C365" s="27" t="n"/>
       <c r="D365">
-        <f>IF($B365="","",IFERROR(INDEX($D$17:$D$364,MATCH($B365,$B$17:$B$364,0)),""))</f>
+        <f>IF($B365="","",IFERROR(INDEX($D$18:$D$364,MATCH($B365,$B$18:$B$364,0)),""))</f>
         <v/>
       </c>
       <c r="E365">
@@ -38495,7 +38487,7 @@
       <c r="A366" s="37" t="n"/>
       <c r="C366" s="27" t="n"/>
       <c r="D366">
-        <f>IF($B366="","",IFERROR(INDEX($D$17:$D$365,MATCH($B366,$B$17:$B$365,0)),""))</f>
+        <f>IF($B366="","",IFERROR(INDEX($D$18:$D$365,MATCH($B366,$B$18:$B$365,0)),""))</f>
         <v/>
       </c>
       <c r="E366">
@@ -38515,7 +38507,7 @@
       <c r="A367" s="37" t="n"/>
       <c r="C367" s="27" t="n"/>
       <c r="D367">
-        <f>IF($B367="","",IFERROR(INDEX($D$17:$D$366,MATCH($B367,$B$17:$B$366,0)),""))</f>
+        <f>IF($B367="","",IFERROR(INDEX($D$18:$D$366,MATCH($B367,$B$18:$B$366,0)),""))</f>
         <v/>
       </c>
       <c r="E367">
@@ -38535,7 +38527,7 @@
       <c r="A368" s="37" t="n"/>
       <c r="C368" s="27" t="n"/>
       <c r="D368">
-        <f>IF($B368="","",IFERROR(INDEX($D$17:$D$367,MATCH($B368,$B$17:$B$367,0)),""))</f>
+        <f>IF($B368="","",IFERROR(INDEX($D$18:$D$367,MATCH($B368,$B$18:$B$367,0)),""))</f>
         <v/>
       </c>
       <c r="E368">
@@ -38555,7 +38547,7 @@
       <c r="A369" s="37" t="n"/>
       <c r="C369" s="27" t="n"/>
       <c r="D369">
-        <f>IF($B369="","",IFERROR(INDEX($D$17:$D$368,MATCH($B369,$B$17:$B$368,0)),""))</f>
+        <f>IF($B369="","",IFERROR(INDEX($D$18:$D$368,MATCH($B369,$B$18:$B$368,0)),""))</f>
         <v/>
       </c>
       <c r="E369">
@@ -38575,7 +38567,7 @@
       <c r="A370" s="37" t="n"/>
       <c r="C370" s="27" t="n"/>
       <c r="D370">
-        <f>IF($B370="","",IFERROR(INDEX($D$17:$D$369,MATCH($B370,$B$17:$B$369,0)),""))</f>
+        <f>IF($B370="","",IFERROR(INDEX($D$18:$D$369,MATCH($B370,$B$18:$B$369,0)),""))</f>
         <v/>
       </c>
       <c r="E370">
@@ -38595,7 +38587,7 @@
       <c r="A371" s="37" t="n"/>
       <c r="C371" s="27" t="n"/>
       <c r="D371">
-        <f>IF($B371="","",IFERROR(INDEX($D$17:$D$370,MATCH($B371,$B$17:$B$370,0)),""))</f>
+        <f>IF($B371="","",IFERROR(INDEX($D$18:$D$370,MATCH($B371,$B$18:$B$370,0)),""))</f>
         <v/>
       </c>
       <c r="E371">
@@ -38615,7 +38607,7 @@
       <c r="A372" s="37" t="n"/>
       <c r="C372" s="27" t="n"/>
       <c r="D372">
-        <f>IF($B372="","",IFERROR(INDEX($D$17:$D$371,MATCH($B372,$B$17:$B$371,0)),""))</f>
+        <f>IF($B372="","",IFERROR(INDEX($D$18:$D$371,MATCH($B372,$B$18:$B$371,0)),""))</f>
         <v/>
       </c>
       <c r="E372">
@@ -38635,7 +38627,7 @@
       <c r="A373" s="37" t="n"/>
       <c r="C373" s="27" t="n"/>
       <c r="D373">
-        <f>IF($B373="","",IFERROR(INDEX($D$17:$D$372,MATCH($B373,$B$17:$B$372,0)),""))</f>
+        <f>IF($B373="","",IFERROR(INDEX($D$18:$D$372,MATCH($B373,$B$18:$B$372,0)),""))</f>
         <v/>
       </c>
       <c r="E373">
@@ -38655,7 +38647,7 @@
       <c r="A374" s="37" t="n"/>
       <c r="C374" s="27" t="n"/>
       <c r="D374">
-        <f>IF($B374="","",IFERROR(INDEX($D$17:$D$373,MATCH($B374,$B$17:$B$373,0)),""))</f>
+        <f>IF($B374="","",IFERROR(INDEX($D$18:$D$373,MATCH($B374,$B$18:$B$373,0)),""))</f>
         <v/>
       </c>
       <c r="E374">
@@ -38675,7 +38667,7 @@
       <c r="A375" s="37" t="n"/>
       <c r="C375" s="27" t="n"/>
       <c r="D375">
-        <f>IF($B375="","",IFERROR(INDEX($D$17:$D$374,MATCH($B375,$B$17:$B$374,0)),""))</f>
+        <f>IF($B375="","",IFERROR(INDEX($D$18:$D$374,MATCH($B375,$B$18:$B$374,0)),""))</f>
         <v/>
       </c>
       <c r="E375">
@@ -38695,7 +38687,7 @@
       <c r="A376" s="37" t="n"/>
       <c r="C376" s="27" t="n"/>
       <c r="D376">
-        <f>IF($B376="","",IFERROR(INDEX($D$17:$D$375,MATCH($B376,$B$17:$B$375,0)),""))</f>
+        <f>IF($B376="","",IFERROR(INDEX($D$18:$D$375,MATCH($B376,$B$18:$B$375,0)),""))</f>
         <v/>
       </c>
       <c r="E376">
@@ -38715,7 +38707,7 @@
       <c r="A377" s="37" t="n"/>
       <c r="C377" s="27" t="n"/>
       <c r="D377">
-        <f>IF($B377="","",IFERROR(INDEX($D$17:$D$376,MATCH($B377,$B$17:$B$376,0)),""))</f>
+        <f>IF($B377="","",IFERROR(INDEX($D$18:$D$376,MATCH($B377,$B$18:$B$376,0)),""))</f>
         <v/>
       </c>
       <c r="E377">
@@ -38735,7 +38727,7 @@
       <c r="A378" s="37" t="n"/>
       <c r="C378" s="27" t="n"/>
       <c r="D378">
-        <f>IF($B378="","",IFERROR(INDEX($D$17:$D$377,MATCH($B378,$B$17:$B$377,0)),""))</f>
+        <f>IF($B378="","",IFERROR(INDEX($D$18:$D$377,MATCH($B378,$B$18:$B$377,0)),""))</f>
         <v/>
       </c>
       <c r="E378">
@@ -38755,7 +38747,7 @@
       <c r="A379" s="37" t="n"/>
       <c r="C379" s="27" t="n"/>
       <c r="D379">
-        <f>IF($B379="","",IFERROR(INDEX($D$17:$D$378,MATCH($B379,$B$17:$B$378,0)),""))</f>
+        <f>IF($B379="","",IFERROR(INDEX($D$18:$D$378,MATCH($B379,$B$18:$B$378,0)),""))</f>
         <v/>
       </c>
       <c r="E379">
@@ -38775,7 +38767,7 @@
       <c r="A380" s="37" t="n"/>
       <c r="C380" s="27" t="n"/>
       <c r="D380">
-        <f>IF($B380="","",IFERROR(INDEX($D$17:$D$379,MATCH($B380,$B$17:$B$379,0)),""))</f>
+        <f>IF($B380="","",IFERROR(INDEX($D$18:$D$379,MATCH($B380,$B$18:$B$379,0)),""))</f>
         <v/>
       </c>
       <c r="E380">
@@ -38795,7 +38787,7 @@
       <c r="A381" s="37" t="n"/>
       <c r="C381" s="27" t="n"/>
       <c r="D381">
-        <f>IF($B381="","",IFERROR(INDEX($D$17:$D$380,MATCH($B381,$B$17:$B$380,0)),""))</f>
+        <f>IF($B381="","",IFERROR(INDEX($D$18:$D$380,MATCH($B381,$B$18:$B$380,0)),""))</f>
         <v/>
       </c>
       <c r="E381">
@@ -38815,7 +38807,7 @@
       <c r="A382" s="37" t="n"/>
       <c r="C382" s="27" t="n"/>
       <c r="D382">
-        <f>IF($B382="","",IFERROR(INDEX($D$17:$D$381,MATCH($B382,$B$17:$B$381,0)),""))</f>
+        <f>IF($B382="","",IFERROR(INDEX($D$18:$D$381,MATCH($B382,$B$18:$B$381,0)),""))</f>
         <v/>
       </c>
       <c r="E382">
@@ -38835,7 +38827,7 @@
       <c r="A383" s="37" t="n"/>
       <c r="C383" s="27" t="n"/>
       <c r="D383">
-        <f>IF($B383="","",IFERROR(INDEX($D$17:$D$382,MATCH($B383,$B$17:$B$382,0)),""))</f>
+        <f>IF($B383="","",IFERROR(INDEX($D$18:$D$382,MATCH($B383,$B$18:$B$382,0)),""))</f>
         <v/>
       </c>
       <c r="E383">
@@ -38855,7 +38847,7 @@
       <c r="A384" s="37" t="n"/>
       <c r="C384" s="27" t="n"/>
       <c r="D384">
-        <f>IF($B384="","",IFERROR(INDEX($D$17:$D$383,MATCH($B384,$B$17:$B$383,0)),""))</f>
+        <f>IF($B384="","",IFERROR(INDEX($D$18:$D$383,MATCH($B384,$B$18:$B$383,0)),""))</f>
         <v/>
       </c>
       <c r="E384">
@@ -38875,7 +38867,7 @@
       <c r="A385" s="37" t="n"/>
       <c r="C385" s="27" t="n"/>
       <c r="D385">
-        <f>IF($B385="","",IFERROR(INDEX($D$17:$D$384,MATCH($B385,$B$17:$B$384,0)),""))</f>
+        <f>IF($B385="","",IFERROR(INDEX($D$18:$D$384,MATCH($B385,$B$18:$B$384,0)),""))</f>
         <v/>
       </c>
       <c r="E385">
@@ -38895,7 +38887,7 @@
       <c r="A386" s="37" t="n"/>
       <c r="C386" s="27" t="n"/>
       <c r="D386">
-        <f>IF($B386="","",IFERROR(INDEX($D$17:$D$385,MATCH($B386,$B$17:$B$385,0)),""))</f>
+        <f>IF($B386="","",IFERROR(INDEX($D$18:$D$385,MATCH($B386,$B$18:$B$385,0)),""))</f>
         <v/>
       </c>
       <c r="E386">
@@ -38915,7 +38907,7 @@
       <c r="A387" s="37" t="n"/>
       <c r="C387" s="27" t="n"/>
       <c r="D387">
-        <f>IF($B387="","",IFERROR(INDEX($D$17:$D$386,MATCH($B387,$B$17:$B$386,0)),""))</f>
+        <f>IF($B387="","",IFERROR(INDEX($D$18:$D$386,MATCH($B387,$B$18:$B$386,0)),""))</f>
         <v/>
       </c>
       <c r="E387">
@@ -38935,7 +38927,7 @@
       <c r="A388" s="37" t="n"/>
       <c r="C388" s="27" t="n"/>
       <c r="D388">
-        <f>IF($B388="","",IFERROR(INDEX($D$17:$D$387,MATCH($B388,$B$17:$B$387,0)),""))</f>
+        <f>IF($B388="","",IFERROR(INDEX($D$18:$D$387,MATCH($B388,$B$18:$B$387,0)),""))</f>
         <v/>
       </c>
       <c r="E388">
@@ -38955,7 +38947,7 @@
       <c r="A389" s="37" t="n"/>
       <c r="C389" s="27" t="n"/>
       <c r="D389">
-        <f>IF($B389="","",IFERROR(INDEX($D$17:$D$388,MATCH($B389,$B$17:$B$388,0)),""))</f>
+        <f>IF($B389="","",IFERROR(INDEX($D$18:$D$388,MATCH($B389,$B$18:$B$388,0)),""))</f>
         <v/>
       </c>
       <c r="E389">
@@ -38975,7 +38967,7 @@
       <c r="A390" s="37" t="n"/>
       <c r="C390" s="27" t="n"/>
       <c r="D390">
-        <f>IF($B390="","",IFERROR(INDEX($D$17:$D$389,MATCH($B390,$B$17:$B$389,0)),""))</f>
+        <f>IF($B390="","",IFERROR(INDEX($D$18:$D$389,MATCH($B390,$B$18:$B$389,0)),""))</f>
         <v/>
       </c>
       <c r="E390">
@@ -38995,7 +38987,7 @@
       <c r="A391" s="37" t="n"/>
       <c r="C391" s="27" t="n"/>
       <c r="D391">
-        <f>IF($B391="","",IFERROR(INDEX($D$17:$D$390,MATCH($B391,$B$17:$B$390,0)),""))</f>
+        <f>IF($B391="","",IFERROR(INDEX($D$18:$D$390,MATCH($B391,$B$18:$B$390,0)),""))</f>
         <v/>
       </c>
       <c r="E391">
@@ -39015,7 +39007,7 @@
       <c r="A392" s="37" t="n"/>
       <c r="C392" s="27" t="n"/>
       <c r="D392">
-        <f>IF($B392="","",IFERROR(INDEX($D$17:$D$391,MATCH($B392,$B$17:$B$391,0)),""))</f>
+        <f>IF($B392="","",IFERROR(INDEX($D$18:$D$391,MATCH($B392,$B$18:$B$391,0)),""))</f>
         <v/>
       </c>
       <c r="E392">
@@ -39035,7 +39027,7 @@
       <c r="A393" s="37" t="n"/>
       <c r="C393" s="27" t="n"/>
       <c r="D393">
-        <f>IF($B393="","",IFERROR(INDEX($D$17:$D$392,MATCH($B393,$B$17:$B$392,0)),""))</f>
+        <f>IF($B393="","",IFERROR(INDEX($D$18:$D$392,MATCH($B393,$B$18:$B$392,0)),""))</f>
         <v/>
       </c>
       <c r="E393">
@@ -39055,7 +39047,7 @@
       <c r="A394" s="37" t="n"/>
       <c r="C394" s="27" t="n"/>
       <c r="D394">
-        <f>IF($B394="","",IFERROR(INDEX($D$17:$D$393,MATCH($B394,$B$17:$B$393,0)),""))</f>
+        <f>IF($B394="","",IFERROR(INDEX($D$18:$D$393,MATCH($B394,$B$18:$B$393,0)),""))</f>
         <v/>
       </c>
       <c r="E394">
@@ -39075,7 +39067,7 @@
       <c r="A395" s="37" t="n"/>
       <c r="C395" s="27" t="n"/>
       <c r="D395">
-        <f>IF($B395="","",IFERROR(INDEX($D$17:$D$394,MATCH($B395,$B$17:$B$394,0)),""))</f>
+        <f>IF($B395="","",IFERROR(INDEX($D$18:$D$394,MATCH($B395,$B$18:$B$394,0)),""))</f>
         <v/>
       </c>
       <c r="E395">
@@ -39095,7 +39087,7 @@
       <c r="A396" s="37" t="n"/>
       <c r="C396" s="27" t="n"/>
       <c r="D396">
-        <f>IF($B396="","",IFERROR(INDEX($D$17:$D$395,MATCH($B396,$B$17:$B$395,0)),""))</f>
+        <f>IF($B396="","",IFERROR(INDEX($D$18:$D$395,MATCH($B396,$B$18:$B$395,0)),""))</f>
         <v/>
       </c>
       <c r="E396">
@@ -39115,7 +39107,7 @@
       <c r="A397" s="37" t="n"/>
       <c r="C397" s="27" t="n"/>
       <c r="D397">
-        <f>IF($B397="","",IFERROR(INDEX($D$17:$D$396,MATCH($B397,$B$17:$B$396,0)),""))</f>
+        <f>IF($B397="","",IFERROR(INDEX($D$18:$D$396,MATCH($B397,$B$18:$B$396,0)),""))</f>
         <v/>
       </c>
       <c r="E397">
@@ -39135,7 +39127,7 @@
       <c r="A398" s="37" t="n"/>
       <c r="C398" s="27" t="n"/>
       <c r="D398">
-        <f>IF($B398="","",IFERROR(INDEX($D$17:$D$397,MATCH($B398,$B$17:$B$397,0)),""))</f>
+        <f>IF($B398="","",IFERROR(INDEX($D$18:$D$397,MATCH($B398,$B$18:$B$397,0)),""))</f>
         <v/>
       </c>
       <c r="E398">
@@ -39155,7 +39147,7 @@
       <c r="A399" s="37" t="n"/>
       <c r="C399" s="27" t="n"/>
       <c r="D399">
-        <f>IF($B399="","",IFERROR(INDEX($D$17:$D$398,MATCH($B399,$B$17:$B$398,0)),""))</f>
+        <f>IF($B399="","",IFERROR(INDEX($D$18:$D$398,MATCH($B399,$B$18:$B$398,0)),""))</f>
         <v/>
       </c>
       <c r="E399">
@@ -39175,7 +39167,7 @@
       <c r="A400" s="37" t="n"/>
       <c r="C400" s="27" t="n"/>
       <c r="D400">
-        <f>IF($B400="","",IFERROR(INDEX($D$17:$D$399,MATCH($B400,$B$17:$B$399,0)),""))</f>
+        <f>IF($B400="","",IFERROR(INDEX($D$18:$D$399,MATCH($B400,$B$18:$B$399,0)),""))</f>
         <v/>
       </c>
       <c r="E400">
@@ -39195,7 +39187,7 @@
       <c r="A401" s="37" t="n"/>
       <c r="C401" s="27" t="n"/>
       <c r="D401">
-        <f>IF($B401="","",IFERROR(INDEX($D$17:$D$400,MATCH($B401,$B$17:$B$400,0)),""))</f>
+        <f>IF($B401="","",IFERROR(INDEX($D$18:$D$400,MATCH($B401,$B$18:$B$400,0)),""))</f>
         <v/>
       </c>
       <c r="E401">
@@ -39215,7 +39207,7 @@
       <c r="A402" s="37" t="n"/>
       <c r="C402" s="27" t="n"/>
       <c r="D402">
-        <f>IF($B402="","",IFERROR(INDEX($D$17:$D$401,MATCH($B402,$B$17:$B$401,0)),""))</f>
+        <f>IF($B402="","",IFERROR(INDEX($D$18:$D$401,MATCH($B402,$B$18:$B$401,0)),""))</f>
         <v/>
       </c>
       <c r="E402">
@@ -39235,7 +39227,7 @@
       <c r="A403" s="37" t="n"/>
       <c r="C403" s="27" t="n"/>
       <c r="D403">
-        <f>IF($B403="","",IFERROR(INDEX($D$17:$D$402,MATCH($B403,$B$17:$B$402,0)),""))</f>
+        <f>IF($B403="","",IFERROR(INDEX($D$18:$D$402,MATCH($B403,$B$18:$B$402,0)),""))</f>
         <v/>
       </c>
       <c r="E403">
@@ -39255,7 +39247,7 @@
       <c r="A404" s="37" t="n"/>
       <c r="C404" s="27" t="n"/>
       <c r="D404">
-        <f>IF($B404="","",IFERROR(INDEX($D$17:$D$403,MATCH($B404,$B$17:$B$403,0)),""))</f>
+        <f>IF($B404="","",IFERROR(INDEX($D$18:$D$403,MATCH($B404,$B$18:$B$403,0)),""))</f>
         <v/>
       </c>
       <c r="E404">
@@ -39275,7 +39267,7 @@
       <c r="A405" s="37" t="n"/>
       <c r="C405" s="27" t="n"/>
       <c r="D405">
-        <f>IF($B405="","",IFERROR(INDEX($D$17:$D$404,MATCH($B405,$B$17:$B$404,0)),""))</f>
+        <f>IF($B405="","",IFERROR(INDEX($D$18:$D$404,MATCH($B405,$B$18:$B$404,0)),""))</f>
         <v/>
       </c>
       <c r="E405">
@@ -39295,7 +39287,7 @@
       <c r="A406" s="37" t="n"/>
       <c r="C406" s="27" t="n"/>
       <c r="D406">
-        <f>IF($B406="","",IFERROR(INDEX($D$17:$D$405,MATCH($B406,$B$17:$B$405,0)),""))</f>
+        <f>IF($B406="","",IFERROR(INDEX($D$18:$D$405,MATCH($B406,$B$18:$B$405,0)),""))</f>
         <v/>
       </c>
       <c r="E406">
@@ -39315,7 +39307,7 @@
       <c r="A407" s="37" t="n"/>
       <c r="C407" s="27" t="n"/>
       <c r="D407">
-        <f>IF($B407="","",IFERROR(INDEX($D$17:$D$406,MATCH($B407,$B$17:$B$406,0)),""))</f>
+        <f>IF($B407="","",IFERROR(INDEX($D$18:$D$406,MATCH($B407,$B$18:$B$406,0)),""))</f>
         <v/>
       </c>
       <c r="E407">
@@ -39335,7 +39327,7 @@
       <c r="A408" s="37" t="n"/>
       <c r="C408" s="27" t="n"/>
       <c r="D408">
-        <f>IF($B408="","",IFERROR(INDEX($D$17:$D$407,MATCH($B408,$B$17:$B$407,0)),""))</f>
+        <f>IF($B408="","",IFERROR(INDEX($D$18:$D$407,MATCH($B408,$B$18:$B$407,0)),""))</f>
         <v/>
       </c>
       <c r="E408">
@@ -39355,7 +39347,7 @@
       <c r="A409" s="37" t="n"/>
       <c r="C409" s="27" t="n"/>
       <c r="D409">
-        <f>IF($B409="","",IFERROR(INDEX($D$17:$D$408,MATCH($B409,$B$17:$B$408,0)),""))</f>
+        <f>IF($B409="","",IFERROR(INDEX($D$18:$D$408,MATCH($B409,$B$18:$B$408,0)),""))</f>
         <v/>
       </c>
       <c r="E409">
@@ -39375,7 +39367,7 @@
       <c r="A410" s="37" t="n"/>
       <c r="C410" s="27" t="n"/>
       <c r="D410">
-        <f>IF($B410="","",IFERROR(INDEX($D$17:$D$409,MATCH($B410,$B$17:$B$409,0)),""))</f>
+        <f>IF($B410="","",IFERROR(INDEX($D$18:$D$409,MATCH($B410,$B$18:$B$409,0)),""))</f>
         <v/>
       </c>
       <c r="E410">
@@ -39395,7 +39387,7 @@
       <c r="A411" s="37" t="n"/>
       <c r="C411" s="27" t="n"/>
       <c r="D411">
-        <f>IF($B411="","",IFERROR(INDEX($D$17:$D$410,MATCH($B411,$B$17:$B$410,0)),""))</f>
+        <f>IF($B411="","",IFERROR(INDEX($D$18:$D$410,MATCH($B411,$B$18:$B$410,0)),""))</f>
         <v/>
       </c>
       <c r="E411">
@@ -39415,7 +39407,7 @@
       <c r="A412" s="37" t="n"/>
       <c r="C412" s="27" t="n"/>
       <c r="D412">
-        <f>IF($B412="","",IFERROR(INDEX($D$17:$D$411,MATCH($B412,$B$17:$B$411,0)),""))</f>
+        <f>IF($B412="","",IFERROR(INDEX($D$18:$D$411,MATCH($B412,$B$18:$B$411,0)),""))</f>
         <v/>
       </c>
       <c r="E412">
@@ -39435,7 +39427,7 @@
       <c r="A413" s="37" t="n"/>
       <c r="C413" s="27" t="n"/>
       <c r="D413">
-        <f>IF($B413="","",IFERROR(INDEX($D$17:$D$412,MATCH($B413,$B$17:$B$412,0)),""))</f>
+        <f>IF($B413="","",IFERROR(INDEX($D$18:$D$412,MATCH($B413,$B$18:$B$412,0)),""))</f>
         <v/>
       </c>
       <c r="E413">
@@ -39455,7 +39447,7 @@
       <c r="A414" s="37" t="n"/>
       <c r="C414" s="27" t="n"/>
       <c r="D414">
-        <f>IF($B414="","",IFERROR(INDEX($D$17:$D$413,MATCH($B414,$B$17:$B$413,0)),""))</f>
+        <f>IF($B414="","",IFERROR(INDEX($D$18:$D$413,MATCH($B414,$B$18:$B$413,0)),""))</f>
         <v/>
       </c>
       <c r="E414">
@@ -39475,7 +39467,7 @@
       <c r="A415" s="37" t="n"/>
       <c r="C415" s="27" t="n"/>
       <c r="D415">
-        <f>IF($B415="","",IFERROR(INDEX($D$17:$D$414,MATCH($B415,$B$17:$B$414,0)),""))</f>
+        <f>IF($B415="","",IFERROR(INDEX($D$18:$D$414,MATCH($B415,$B$18:$B$414,0)),""))</f>
         <v/>
       </c>
       <c r="E415">
@@ -39495,7 +39487,7 @@
       <c r="A416" s="37" t="n"/>
       <c r="C416" s="27" t="n"/>
       <c r="D416">
-        <f>IF($B416="","",IFERROR(INDEX($D$17:$D$415,MATCH($B416,$B$17:$B$415,0)),""))</f>
+        <f>IF($B416="","",IFERROR(INDEX($D$18:$D$415,MATCH($B416,$B$18:$B$415,0)),""))</f>
         <v/>
       </c>
       <c r="E416">
@@ -39515,7 +39507,7 @@
       <c r="A417" s="37" t="n"/>
       <c r="C417" s="27" t="n"/>
       <c r="D417">
-        <f>IF($B417="","",IFERROR(INDEX($D$17:$D$416,MATCH($B417,$B$17:$B$416,0)),""))</f>
+        <f>IF($B417="","",IFERROR(INDEX($D$18:$D$416,MATCH($B417,$B$18:$B$416,0)),""))</f>
         <v/>
       </c>
       <c r="E417">
@@ -39535,7 +39527,7 @@
       <c r="A418" s="37" t="n"/>
       <c r="C418" s="27" t="n"/>
       <c r="D418">
-        <f>IF($B418="","",IFERROR(INDEX($D$17:$D$417,MATCH($B418,$B$17:$B$417,0)),""))</f>
+        <f>IF($B418="","",IFERROR(INDEX($D$18:$D$417,MATCH($B418,$B$18:$B$417,0)),""))</f>
         <v/>
       </c>
       <c r="E418">
@@ -39555,7 +39547,7 @@
       <c r="A419" s="37" t="n"/>
       <c r="C419" s="27" t="n"/>
       <c r="D419">
-        <f>IF($B419="","",IFERROR(INDEX($D$17:$D$418,MATCH($B419,$B$17:$B$418,0)),""))</f>
+        <f>IF($B419="","",IFERROR(INDEX($D$18:$D$418,MATCH($B419,$B$18:$B$418,0)),""))</f>
         <v/>
       </c>
       <c r="E419">
@@ -39575,7 +39567,7 @@
       <c r="A420" s="37" t="n"/>
       <c r="C420" s="27" t="n"/>
       <c r="D420">
-        <f>IF($B420="","",IFERROR(INDEX($D$17:$D$419,MATCH($B420,$B$17:$B$419,0)),""))</f>
+        <f>IF($B420="","",IFERROR(INDEX($D$18:$D$419,MATCH($B420,$B$18:$B$419,0)),""))</f>
         <v/>
       </c>
       <c r="E420">
@@ -39595,7 +39587,7 @@
       <c r="A421" s="37" t="n"/>
       <c r="C421" s="27" t="n"/>
       <c r="D421">
-        <f>IF($B421="","",IFERROR(INDEX($D$17:$D$420,MATCH($B421,$B$17:$B$420,0)),""))</f>
+        <f>IF($B421="","",IFERROR(INDEX($D$18:$D$420,MATCH($B421,$B$18:$B$420,0)),""))</f>
         <v/>
       </c>
       <c r="E421">
@@ -39615,7 +39607,7 @@
       <c r="A422" s="37" t="n"/>
       <c r="C422" s="27" t="n"/>
       <c r="D422">
-        <f>IF($B422="","",IFERROR(INDEX($D$17:$D$421,MATCH($B422,$B$17:$B$421,0)),""))</f>
+        <f>IF($B422="","",IFERROR(INDEX($D$18:$D$421,MATCH($B422,$B$18:$B$421,0)),""))</f>
         <v/>
       </c>
       <c r="E422">
@@ -39635,7 +39627,7 @@
       <c r="A423" s="37" t="n"/>
       <c r="C423" s="27" t="n"/>
       <c r="D423">
-        <f>IF($B423="","",IFERROR(INDEX($D$17:$D$422,MATCH($B423,$B$17:$B$422,0)),""))</f>
+        <f>IF($B423="","",IFERROR(INDEX($D$18:$D$422,MATCH($B423,$B$18:$B$422,0)),""))</f>
         <v/>
       </c>
       <c r="E423">
@@ -39655,7 +39647,7 @@
       <c r="A424" s="37" t="n"/>
       <c r="C424" s="27" t="n"/>
       <c r="D424">
-        <f>IF($B424="","",IFERROR(INDEX($D$17:$D$423,MATCH($B424,$B$17:$B$423,0)),""))</f>
+        <f>IF($B424="","",IFERROR(INDEX($D$18:$D$423,MATCH($B424,$B$18:$B$423,0)),""))</f>
         <v/>
       </c>
       <c r="E424">
@@ -39675,7 +39667,7 @@
       <c r="A425" s="37" t="n"/>
       <c r="C425" s="27" t="n"/>
       <c r="D425">
-        <f>IF($B425="","",IFERROR(INDEX($D$17:$D$424,MATCH($B425,$B$17:$B$424,0)),""))</f>
+        <f>IF($B425="","",IFERROR(INDEX($D$18:$D$424,MATCH($B425,$B$18:$B$424,0)),""))</f>
         <v/>
       </c>
       <c r="E425">
@@ -39695,7 +39687,7 @@
       <c r="A426" s="37" t="n"/>
       <c r="C426" s="27" t="n"/>
       <c r="D426">
-        <f>IF($B426="","",IFERROR(INDEX($D$17:$D$425,MATCH($B426,$B$17:$B$425,0)),""))</f>
+        <f>IF($B426="","",IFERROR(INDEX($D$18:$D$425,MATCH($B426,$B$18:$B$425,0)),""))</f>
         <v/>
       </c>
       <c r="E426">
@@ -39715,7 +39707,7 @@
       <c r="A427" s="37" t="n"/>
       <c r="C427" s="27" t="n"/>
       <c r="D427">
-        <f>IF($B427="","",IFERROR(INDEX($D$17:$D$426,MATCH($B427,$B$17:$B$426,0)),""))</f>
+        <f>IF($B427="","",IFERROR(INDEX($D$18:$D$426,MATCH($B427,$B$18:$B$426,0)),""))</f>
         <v/>
       </c>
       <c r="E427">
@@ -39735,7 +39727,7 @@
       <c r="A428" s="37" t="n"/>
       <c r="C428" s="27" t="n"/>
       <c r="D428">
-        <f>IF($B428="","",IFERROR(INDEX($D$17:$D$427,MATCH($B428,$B$17:$B$427,0)),""))</f>
+        <f>IF($B428="","",IFERROR(INDEX($D$18:$D$427,MATCH($B428,$B$18:$B$427,0)),""))</f>
         <v/>
       </c>
       <c r="E428">
@@ -39755,7 +39747,7 @@
       <c r="A429" s="37" t="n"/>
       <c r="C429" s="27" t="n"/>
       <c r="D429">
-        <f>IF($B429="","",IFERROR(INDEX($D$17:$D$428,MATCH($B429,$B$17:$B$428,0)),""))</f>
+        <f>IF($B429="","",IFERROR(INDEX($D$18:$D$428,MATCH($B429,$B$18:$B$428,0)),""))</f>
         <v/>
       </c>
       <c r="E429">
@@ -39775,7 +39767,7 @@
       <c r="A430" s="37" t="n"/>
       <c r="C430" s="27" t="n"/>
       <c r="D430">
-        <f>IF($B430="","",IFERROR(INDEX($D$17:$D$429,MATCH($B430,$B$17:$B$429,0)),""))</f>
+        <f>IF($B430="","",IFERROR(INDEX($D$18:$D$429,MATCH($B430,$B$18:$B$429,0)),""))</f>
         <v/>
       </c>
       <c r="E430">
@@ -39795,7 +39787,7 @@
       <c r="A431" s="37" t="n"/>
       <c r="C431" s="27" t="n"/>
       <c r="D431">
-        <f>IF($B431="","",IFERROR(INDEX($D$17:$D$430,MATCH($B431,$B$17:$B$430,0)),""))</f>
+        <f>IF($B431="","",IFERROR(INDEX($D$18:$D$430,MATCH($B431,$B$18:$B$430,0)),""))</f>
         <v/>
       </c>
       <c r="E431">
@@ -39815,7 +39807,7 @@
       <c r="A432" s="37" t="n"/>
       <c r="C432" s="27" t="n"/>
       <c r="D432">
-        <f>IF($B432="","",IFERROR(INDEX($D$17:$D$431,MATCH($B432,$B$17:$B$431,0)),""))</f>
+        <f>IF($B432="","",IFERROR(INDEX($D$18:$D$431,MATCH($B432,$B$18:$B$431,0)),""))</f>
         <v/>
       </c>
       <c r="E432">
@@ -39835,7 +39827,7 @@
       <c r="A433" s="37" t="n"/>
       <c r="C433" s="27" t="n"/>
       <c r="D433">
-        <f>IF($B433="","",IFERROR(INDEX($D$17:$D$432,MATCH($B433,$B$17:$B$432,0)),""))</f>
+        <f>IF($B433="","",IFERROR(INDEX($D$18:$D$432,MATCH($B433,$B$18:$B$432,0)),""))</f>
         <v/>
       </c>
       <c r="E433">
@@ -39855,7 +39847,7 @@
       <c r="A434" s="37" t="n"/>
       <c r="C434" s="27" t="n"/>
       <c r="D434">
-        <f>IF($B434="","",IFERROR(INDEX($D$17:$D$433,MATCH($B434,$B$17:$B$433,0)),""))</f>
+        <f>IF($B434="","",IFERROR(INDEX($D$18:$D$433,MATCH($B434,$B$18:$B$433,0)),""))</f>
         <v/>
       </c>
       <c r="E434">
@@ -39875,7 +39867,7 @@
       <c r="A435" s="37" t="n"/>
       <c r="C435" s="27" t="n"/>
       <c r="D435">
-        <f>IF($B435="","",IFERROR(INDEX($D$17:$D$434,MATCH($B435,$B$17:$B$434,0)),""))</f>
+        <f>IF($B435="","",IFERROR(INDEX($D$18:$D$434,MATCH($B435,$B$18:$B$434,0)),""))</f>
         <v/>
       </c>
       <c r="E435">
@@ -39895,7 +39887,7 @@
       <c r="A436" s="37" t="n"/>
       <c r="C436" s="27" t="n"/>
       <c r="D436">
-        <f>IF($B436="","",IFERROR(INDEX($D$17:$D$435,MATCH($B436,$B$17:$B$435,0)),""))</f>
+        <f>IF($B436="","",IFERROR(INDEX($D$18:$D$435,MATCH($B436,$B$18:$B$435,0)),""))</f>
         <v/>
       </c>
       <c r="E436">
@@ -39915,7 +39907,7 @@
       <c r="A437" s="37" t="n"/>
       <c r="C437" s="27" t="n"/>
       <c r="D437">
-        <f>IF($B437="","",IFERROR(INDEX($D$17:$D$436,MATCH($B437,$B$17:$B$436,0)),""))</f>
+        <f>IF($B437="","",IFERROR(INDEX($D$18:$D$436,MATCH($B437,$B$18:$B$436,0)),""))</f>
         <v/>
       </c>
       <c r="E437">
@@ -39935,7 +39927,7 @@
       <c r="A438" s="37" t="n"/>
       <c r="C438" s="27" t="n"/>
       <c r="D438">
-        <f>IF($B438="","",IFERROR(INDEX($D$17:$D$437,MATCH($B438,$B$17:$B$437,0)),""))</f>
+        <f>IF($B438="","",IFERROR(INDEX($D$18:$D$437,MATCH($B438,$B$18:$B$437,0)),""))</f>
         <v/>
       </c>
       <c r="E438">
@@ -39955,7 +39947,7 @@
       <c r="A439" s="37" t="n"/>
       <c r="C439" s="27" t="n"/>
       <c r="D439">
-        <f>IF($B439="","",IFERROR(INDEX($D$17:$D$438,MATCH($B439,$B$17:$B$438,0)),""))</f>
+        <f>IF($B439="","",IFERROR(INDEX($D$18:$D$438,MATCH($B439,$B$18:$B$438,0)),""))</f>
         <v/>
       </c>
       <c r="E439">
@@ -39975,7 +39967,7 @@
       <c r="A440" s="37" t="n"/>
       <c r="C440" s="27" t="n"/>
       <c r="D440">
-        <f>IF($B440="","",IFERROR(INDEX($D$17:$D$439,MATCH($B440,$B$17:$B$439,0)),""))</f>
+        <f>IF($B440="","",IFERROR(INDEX($D$18:$D$439,MATCH($B440,$B$18:$B$439,0)),""))</f>
         <v/>
       </c>
       <c r="E440">
@@ -39995,7 +39987,7 @@
       <c r="A441" s="37" t="n"/>
       <c r="C441" s="27" t="n"/>
       <c r="D441">
-        <f>IF($B441="","",IFERROR(INDEX($D$17:$D$440,MATCH($B441,$B$17:$B$440,0)),""))</f>
+        <f>IF($B441="","",IFERROR(INDEX($D$18:$D$440,MATCH($B441,$B$18:$B$440,0)),""))</f>
         <v/>
       </c>
       <c r="E441">
@@ -40015,7 +40007,7 @@
       <c r="A442" s="37" t="n"/>
       <c r="C442" s="27" t="n"/>
       <c r="D442">
-        <f>IF($B442="","",IFERROR(INDEX($D$17:$D$441,MATCH($B442,$B$17:$B$441,0)),""))</f>
+        <f>IF($B442="","",IFERROR(INDEX($D$18:$D$441,MATCH($B442,$B$18:$B$441,0)),""))</f>
         <v/>
       </c>
       <c r="E442">
@@ -40035,7 +40027,7 @@
       <c r="A443" s="37" t="n"/>
       <c r="C443" s="27" t="n"/>
       <c r="D443">
-        <f>IF($B443="","",IFERROR(INDEX($D$17:$D$442,MATCH($B443,$B$17:$B$442,0)),""))</f>
+        <f>IF($B443="","",IFERROR(INDEX($D$18:$D$442,MATCH($B443,$B$18:$B$442,0)),""))</f>
         <v/>
       </c>
       <c r="E443">
@@ -40055,7 +40047,7 @@
       <c r="A444" s="37" t="n"/>
       <c r="C444" s="27" t="n"/>
       <c r="D444">
-        <f>IF($B444="","",IFERROR(INDEX($D$17:$D$443,MATCH($B444,$B$17:$B$443,0)),""))</f>
+        <f>IF($B444="","",IFERROR(INDEX($D$18:$D$443,MATCH($B444,$B$18:$B$443,0)),""))</f>
         <v/>
       </c>
       <c r="E444">
@@ -40075,7 +40067,7 @@
       <c r="A445" s="37" t="n"/>
       <c r="C445" s="27" t="n"/>
       <c r="D445">
-        <f>IF($B445="","",IFERROR(INDEX($D$17:$D$444,MATCH($B445,$B$17:$B$444,0)),""))</f>
+        <f>IF($B445="","",IFERROR(INDEX($D$18:$D$444,MATCH($B445,$B$18:$B$444,0)),""))</f>
         <v/>
       </c>
       <c r="E445">
@@ -40095,7 +40087,7 @@
       <c r="A446" s="37" t="n"/>
       <c r="C446" s="27" t="n"/>
       <c r="D446">
-        <f>IF($B446="","",IFERROR(INDEX($D$17:$D$445,MATCH($B446,$B$17:$B$445,0)),""))</f>
+        <f>IF($B446="","",IFERROR(INDEX($D$18:$D$445,MATCH($B446,$B$18:$B$445,0)),""))</f>
         <v/>
       </c>
       <c r="E446">
@@ -40115,7 +40107,7 @@
       <c r="A447" s="37" t="n"/>
       <c r="C447" s="27" t="n"/>
       <c r="D447">
-        <f>IF($B447="","",IFERROR(INDEX($D$17:$D$446,MATCH($B447,$B$17:$B$446,0)),""))</f>
+        <f>IF($B447="","",IFERROR(INDEX($D$18:$D$446,MATCH($B447,$B$18:$B$446,0)),""))</f>
         <v/>
       </c>
       <c r="E447">
@@ -40135,7 +40127,7 @@
       <c r="A448" s="37" t="n"/>
       <c r="C448" s="27" t="n"/>
       <c r="D448">
-        <f>IF($B448="","",IFERROR(INDEX($D$17:$D$447,MATCH($B448,$B$17:$B$447,0)),""))</f>
+        <f>IF($B448="","",IFERROR(INDEX($D$18:$D$447,MATCH($B448,$B$18:$B$447,0)),""))</f>
         <v/>
       </c>
       <c r="E448">
@@ -40155,7 +40147,7 @@
       <c r="A449" s="37" t="n"/>
       <c r="C449" s="27" t="n"/>
       <c r="D449">
-        <f>IF($B449="","",IFERROR(INDEX($D$17:$D$448,MATCH($B449,$B$17:$B$448,0)),""))</f>
+        <f>IF($B449="","",IFERROR(INDEX($D$18:$D$448,MATCH($B449,$B$18:$B$448,0)),""))</f>
         <v/>
       </c>
       <c r="E449">
@@ -40175,7 +40167,7 @@
       <c r="A450" s="37" t="n"/>
       <c r="C450" s="27" t="n"/>
       <c r="D450">
-        <f>IF($B450="","",IFERROR(INDEX($D$17:$D$449,MATCH($B450,$B$17:$B$449,0)),""))</f>
+        <f>IF($B450="","",IFERROR(INDEX($D$18:$D$449,MATCH($B450,$B$18:$B$449,0)),""))</f>
         <v/>
       </c>
       <c r="E450">
@@ -40195,7 +40187,7 @@
       <c r="A451" s="37" t="n"/>
       <c r="C451" s="27" t="n"/>
       <c r="D451">
-        <f>IF($B451="","",IFERROR(INDEX($D$17:$D$450,MATCH($B451,$B$17:$B$450,0)),""))</f>
+        <f>IF($B451="","",IFERROR(INDEX($D$18:$D$450,MATCH($B451,$B$18:$B$450,0)),""))</f>
         <v/>
       </c>
       <c r="E451">
@@ -40215,7 +40207,7 @@
       <c r="A452" s="37" t="n"/>
       <c r="C452" s="27" t="n"/>
       <c r="D452">
-        <f>IF($B452="","",IFERROR(INDEX($D$17:$D$451,MATCH($B452,$B$17:$B$451,0)),""))</f>
+        <f>IF($B452="","",IFERROR(INDEX($D$18:$D$451,MATCH($B452,$B$18:$B$451,0)),""))</f>
         <v/>
       </c>
       <c r="E452">
@@ -40235,7 +40227,7 @@
       <c r="A453" s="37" t="n"/>
       <c r="C453" s="27" t="n"/>
       <c r="D453">
-        <f>IF($B453="","",IFERROR(INDEX($D$17:$D$452,MATCH($B453,$B$17:$B$452,0)),""))</f>
+        <f>IF($B453="","",IFERROR(INDEX($D$18:$D$452,MATCH($B453,$B$18:$B$452,0)),""))</f>
         <v/>
       </c>
       <c r="E453">
@@ -40255,7 +40247,7 @@
       <c r="A454" s="37" t="n"/>
       <c r="C454" s="27" t="n"/>
       <c r="D454">
-        <f>IF($B454="","",IFERROR(INDEX($D$17:$D$453,MATCH($B454,$B$17:$B$453,0)),""))</f>
+        <f>IF($B454="","",IFERROR(INDEX($D$18:$D$453,MATCH($B454,$B$18:$B$453,0)),""))</f>
         <v/>
       </c>
       <c r="E454">
@@ -40275,7 +40267,7 @@
       <c r="A455" s="37" t="n"/>
       <c r="C455" s="27" t="n"/>
       <c r="D455">
-        <f>IF($B455="","",IFERROR(INDEX($D$17:$D$454,MATCH($B455,$B$17:$B$454,0)),""))</f>
+        <f>IF($B455="","",IFERROR(INDEX($D$18:$D$454,MATCH($B455,$B$18:$B$454,0)),""))</f>
         <v/>
       </c>
       <c r="E455">
@@ -40295,7 +40287,7 @@
       <c r="A456" s="37" t="n"/>
       <c r="C456" s="27" t="n"/>
       <c r="D456">
-        <f>IF($B456="","",IFERROR(INDEX($D$17:$D$455,MATCH($B456,$B$17:$B$455,0)),""))</f>
+        <f>IF($B456="","",IFERROR(INDEX($D$18:$D$455,MATCH($B456,$B$18:$B$455,0)),""))</f>
         <v/>
       </c>
       <c r="E456">
@@ -40315,7 +40307,7 @@
       <c r="A457" s="37" t="n"/>
       <c r="C457" s="27" t="n"/>
       <c r="D457">
-        <f>IF($B457="","",IFERROR(INDEX($D$17:$D$456,MATCH($B457,$B$17:$B$456,0)),""))</f>
+        <f>IF($B457="","",IFERROR(INDEX($D$18:$D$456,MATCH($B457,$B$18:$B$456,0)),""))</f>
         <v/>
       </c>
       <c r="E457">
@@ -40335,7 +40327,7 @@
       <c r="A458" s="37" t="n"/>
       <c r="C458" s="27" t="n"/>
       <c r="D458">
-        <f>IF($B458="","",IFERROR(INDEX($D$17:$D$457,MATCH($B458,$B$17:$B$457,0)),""))</f>
+        <f>IF($B458="","",IFERROR(INDEX($D$18:$D$457,MATCH($B458,$B$18:$B$457,0)),""))</f>
         <v/>
       </c>
       <c r="E458">
@@ -40355,7 +40347,7 @@
       <c r="A459" s="37" t="n"/>
       <c r="C459" s="27" t="n"/>
       <c r="D459">
-        <f>IF($B459="","",IFERROR(INDEX($D$17:$D$458,MATCH($B459,$B$17:$B$458,0)),""))</f>
+        <f>IF($B459="","",IFERROR(INDEX($D$18:$D$458,MATCH($B459,$B$18:$B$458,0)),""))</f>
         <v/>
       </c>
       <c r="E459">
@@ -40375,7 +40367,7 @@
       <c r="A460" s="37" t="n"/>
       <c r="C460" s="27" t="n"/>
       <c r="D460">
-        <f>IF($B460="","",IFERROR(INDEX($D$17:$D$459,MATCH($B460,$B$17:$B$459,0)),""))</f>
+        <f>IF($B460="","",IFERROR(INDEX($D$18:$D$459,MATCH($B460,$B$18:$B$459,0)),""))</f>
         <v/>
       </c>
       <c r="E460">
@@ -40395,7 +40387,7 @@
       <c r="A461" s="37" t="n"/>
       <c r="C461" s="27" t="n"/>
       <c r="D461">
-        <f>IF($B461="","",IFERROR(INDEX($D$17:$D$460,MATCH($B461,$B$17:$B$460,0)),""))</f>
+        <f>IF($B461="","",IFERROR(INDEX($D$18:$D$460,MATCH($B461,$B$18:$B$460,0)),""))</f>
         <v/>
       </c>
       <c r="E461">
@@ -40415,7 +40407,7 @@
       <c r="A462" s="37" t="n"/>
       <c r="C462" s="27" t="n"/>
       <c r="D462">
-        <f>IF($B462="","",IFERROR(INDEX($D$17:$D$461,MATCH($B462,$B$17:$B$461,0)),""))</f>
+        <f>IF($B462="","",IFERROR(INDEX($D$18:$D$461,MATCH($B462,$B$18:$B$461,0)),""))</f>
         <v/>
       </c>
       <c r="E462">
@@ -40435,7 +40427,7 @@
       <c r="A463" s="37" t="n"/>
       <c r="C463" s="27" t="n"/>
       <c r="D463">
-        <f>IF($B463="","",IFERROR(INDEX($D$17:$D$462,MATCH($B463,$B$17:$B$462,0)),""))</f>
+        <f>IF($B463="","",IFERROR(INDEX($D$18:$D$462,MATCH($B463,$B$18:$B$462,0)),""))</f>
         <v/>
       </c>
       <c r="E463">
@@ -40455,7 +40447,7 @@
       <c r="A464" s="37" t="n"/>
       <c r="C464" s="27" t="n"/>
       <c r="D464">
-        <f>IF($B464="","",IFERROR(INDEX($D$17:$D$463,MATCH($B464,$B$17:$B$463,0)),""))</f>
+        <f>IF($B464="","",IFERROR(INDEX($D$18:$D$463,MATCH($B464,$B$18:$B$463,0)),""))</f>
         <v/>
       </c>
       <c r="E464">
@@ -40475,7 +40467,7 @@
       <c r="A465" s="37" t="n"/>
       <c r="C465" s="27" t="n"/>
       <c r="D465">
-        <f>IF($B465="","",IFERROR(INDEX($D$17:$D$464,MATCH($B465,$B$17:$B$464,0)),""))</f>
+        <f>IF($B465="","",IFERROR(INDEX($D$18:$D$464,MATCH($B465,$B$18:$B$464,0)),""))</f>
         <v/>
       </c>
       <c r="E465">
@@ -40495,7 +40487,7 @@
       <c r="A466" s="37" t="n"/>
       <c r="C466" s="27" t="n"/>
       <c r="D466">
-        <f>IF($B466="","",IFERROR(INDEX($D$17:$D$465,MATCH($B466,$B$17:$B$465,0)),""))</f>
+        <f>IF($B466="","",IFERROR(INDEX($D$18:$D$465,MATCH($B466,$B$18:$B$465,0)),""))</f>
         <v/>
       </c>
       <c r="E466">
@@ -40515,7 +40507,7 @@
       <c r="A467" s="37" t="n"/>
       <c r="C467" s="27" t="n"/>
       <c r="D467">
-        <f>IF($B467="","",IFERROR(INDEX($D$17:$D$466,MATCH($B467,$B$17:$B$466,0)),""))</f>
+        <f>IF($B467="","",IFERROR(INDEX($D$18:$D$466,MATCH($B467,$B$18:$B$466,0)),""))</f>
         <v/>
       </c>
       <c r="E467">
@@ -40535,7 +40527,7 @@
       <c r="A468" s="37" t="n"/>
       <c r="C468" s="27" t="n"/>
       <c r="D468">
-        <f>IF($B468="","",IFERROR(INDEX($D$17:$D$467,MATCH($B468,$B$17:$B$467,0)),""))</f>
+        <f>IF($B468="","",IFERROR(INDEX($D$18:$D$467,MATCH($B468,$B$18:$B$467,0)),""))</f>
         <v/>
       </c>
       <c r="E468">
@@ -40555,7 +40547,7 @@
       <c r="A469" s="37" t="n"/>
       <c r="C469" s="27" t="n"/>
       <c r="D469">
-        <f>IF($B469="","",IFERROR(INDEX($D$17:$D$468,MATCH($B469,$B$17:$B$468,0)),""))</f>
+        <f>IF($B469="","",IFERROR(INDEX($D$18:$D$468,MATCH($B469,$B$18:$B$468,0)),""))</f>
         <v/>
       </c>
       <c r="E469">
@@ -40575,7 +40567,7 @@
       <c r="A470" s="37" t="n"/>
       <c r="C470" s="27" t="n"/>
       <c r="D470">
-        <f>IF($B470="","",IFERROR(INDEX($D$17:$D$469,MATCH($B470,$B$17:$B$469,0)),""))</f>
+        <f>IF($B470="","",IFERROR(INDEX($D$18:$D$469,MATCH($B470,$B$18:$B$469,0)),""))</f>
         <v/>
       </c>
       <c r="E470">
@@ -40595,7 +40587,7 @@
       <c r="A471" s="37" t="n"/>
       <c r="C471" s="27" t="n"/>
       <c r="D471">
-        <f>IF($B471="","",IFERROR(INDEX($D$17:$D$470,MATCH($B471,$B$17:$B$470,0)),""))</f>
+        <f>IF($B471="","",IFERROR(INDEX($D$18:$D$470,MATCH($B471,$B$18:$B$470,0)),""))</f>
         <v/>
       </c>
       <c r="E471">
@@ -40615,7 +40607,7 @@
       <c r="A472" s="37" t="n"/>
       <c r="C472" s="27" t="n"/>
       <c r="D472">
-        <f>IF($B472="","",IFERROR(INDEX($D$17:$D$471,MATCH($B472,$B$17:$B$471,0)),""))</f>
+        <f>IF($B472="","",IFERROR(INDEX($D$18:$D$471,MATCH($B472,$B$18:$B$471,0)),""))</f>
         <v/>
       </c>
       <c r="E472">
@@ -40635,7 +40627,7 @@
       <c r="A473" s="37" t="n"/>
       <c r="C473" s="27" t="n"/>
       <c r="D473">
-        <f>IF($B473="","",IFERROR(INDEX($D$17:$D$472,MATCH($B473,$B$17:$B$472,0)),""))</f>
+        <f>IF($B473="","",IFERROR(INDEX($D$18:$D$472,MATCH($B473,$B$18:$B$472,0)),""))</f>
         <v/>
       </c>
       <c r="E473">
@@ -40655,7 +40647,7 @@
       <c r="A474" s="37" t="n"/>
       <c r="C474" s="27" t="n"/>
       <c r="D474">
-        <f>IF($B474="","",IFERROR(INDEX($D$17:$D$473,MATCH($B474,$B$17:$B$473,0)),""))</f>
+        <f>IF($B474="","",IFERROR(INDEX($D$18:$D$473,MATCH($B474,$B$18:$B$473,0)),""))</f>
         <v/>
       </c>
       <c r="E474">
@@ -40675,7 +40667,7 @@
       <c r="A475" s="37" t="n"/>
       <c r="C475" s="27" t="n"/>
       <c r="D475">
-        <f>IF($B475="","",IFERROR(INDEX($D$17:$D$474,MATCH($B475,$B$17:$B$474,0)),""))</f>
+        <f>IF($B475="","",IFERROR(INDEX($D$18:$D$474,MATCH($B475,$B$18:$B$474,0)),""))</f>
         <v/>
       </c>
       <c r="E475">
@@ -40695,7 +40687,7 @@
       <c r="A476" s="37" t="n"/>
       <c r="C476" s="27" t="n"/>
       <c r="D476">
-        <f>IF($B476="","",IFERROR(INDEX($D$17:$D$475,MATCH($B476,$B$17:$B$475,0)),""))</f>
+        <f>IF($B476="","",IFERROR(INDEX($D$18:$D$475,MATCH($B476,$B$18:$B$475,0)),""))</f>
         <v/>
       </c>
       <c r="E476">
@@ -40715,7 +40707,7 @@
       <c r="A477" s="37" t="n"/>
       <c r="C477" s="27" t="n"/>
       <c r="D477">
-        <f>IF($B477="","",IFERROR(INDEX($D$17:$D$476,MATCH($B477,$B$17:$B$476,0)),""))</f>
+        <f>IF($B477="","",IFERROR(INDEX($D$18:$D$476,MATCH($B477,$B$18:$B$476,0)),""))</f>
         <v/>
       </c>
       <c r="E477">
@@ -40735,7 +40727,7 @@
       <c r="A478" s="37" t="n"/>
       <c r="C478" s="27" t="n"/>
       <c r="D478">
-        <f>IF($B478="","",IFERROR(INDEX($D$17:$D$477,MATCH($B478,$B$17:$B$477,0)),""))</f>
+        <f>IF($B478="","",IFERROR(INDEX($D$18:$D$477,MATCH($B478,$B$18:$B$477,0)),""))</f>
         <v/>
       </c>
       <c r="E478">
@@ -40755,7 +40747,7 @@
       <c r="A479" s="37" t="n"/>
       <c r="C479" s="27" t="n"/>
       <c r="D479">
-        <f>IF($B479="","",IFERROR(INDEX($D$17:$D$478,MATCH($B479,$B$17:$B$478,0)),""))</f>
+        <f>IF($B479="","",IFERROR(INDEX($D$18:$D$478,MATCH($B479,$B$18:$B$478,0)),""))</f>
         <v/>
       </c>
       <c r="E479">
@@ -40775,7 +40767,7 @@
       <c r="A480" s="37" t="n"/>
       <c r="C480" s="27" t="n"/>
       <c r="D480">
-        <f>IF($B480="","",IFERROR(INDEX($D$17:$D$479,MATCH($B480,$B$17:$B$479,0)),""))</f>
+        <f>IF($B480="","",IFERROR(INDEX($D$18:$D$479,MATCH($B480,$B$18:$B$479,0)),""))</f>
         <v/>
       </c>
       <c r="E480">
@@ -40795,7 +40787,7 @@
       <c r="A481" s="37" t="n"/>
       <c r="C481" s="27" t="n"/>
       <c r="D481">
-        <f>IF($B481="","",IFERROR(INDEX($D$17:$D$480,MATCH($B481,$B$17:$B$480,0)),""))</f>
+        <f>IF($B481="","",IFERROR(INDEX($D$18:$D$480,MATCH($B481,$B$18:$B$480,0)),""))</f>
         <v/>
       </c>
       <c r="E481">
@@ -40815,7 +40807,7 @@
       <c r="A482" s="37" t="n"/>
       <c r="C482" s="27" t="n"/>
       <c r="D482">
-        <f>IF($B482="","",IFERROR(INDEX($D$17:$D$481,MATCH($B482,$B$17:$B$481,0)),""))</f>
+        <f>IF($B482="","",IFERROR(INDEX($D$18:$D$481,MATCH($B482,$B$18:$B$481,0)),""))</f>
         <v/>
       </c>
       <c r="E482">
@@ -40835,7 +40827,7 @@
       <c r="A483" s="37" t="n"/>
       <c r="C483" s="27" t="n"/>
       <c r="D483">
-        <f>IF($B483="","",IFERROR(INDEX($D$17:$D$482,MATCH($B483,$B$17:$B$482,0)),""))</f>
+        <f>IF($B483="","",IFERROR(INDEX($D$18:$D$482,MATCH($B483,$B$18:$B$482,0)),""))</f>
         <v/>
       </c>
       <c r="E483">
@@ -40855,7 +40847,7 @@
       <c r="A484" s="37" t="n"/>
       <c r="C484" s="27" t="n"/>
       <c r="D484">
-        <f>IF($B484="","",IFERROR(INDEX($D$17:$D$483,MATCH($B484,$B$17:$B$483,0)),""))</f>
+        <f>IF($B484="","",IFERROR(INDEX($D$18:$D$483,MATCH($B484,$B$18:$B$483,0)),""))</f>
         <v/>
       </c>
       <c r="E484">
@@ -40875,7 +40867,7 @@
       <c r="A485" s="37" t="n"/>
       <c r="C485" s="27" t="n"/>
       <c r="D485">
-        <f>IF($B485="","",IFERROR(INDEX($D$17:$D$484,MATCH($B485,$B$17:$B$484,0)),""))</f>
+        <f>IF($B485="","",IFERROR(INDEX($D$18:$D$484,MATCH($B485,$B$18:$B$484,0)),""))</f>
         <v/>
       </c>
       <c r="E485">
@@ -40895,7 +40887,7 @@
       <c r="A486" s="37" t="n"/>
       <c r="C486" s="27" t="n"/>
       <c r="D486">
-        <f>IF($B486="","",IFERROR(INDEX($D$17:$D$485,MATCH($B486,$B$17:$B$485,0)),""))</f>
+        <f>IF($B486="","",IFERROR(INDEX($D$18:$D$485,MATCH($B486,$B$18:$B$485,0)),""))</f>
         <v/>
       </c>
       <c r="E486">
@@ -40915,7 +40907,7 @@
       <c r="A487" s="37" t="n"/>
       <c r="C487" s="27" t="n"/>
       <c r="D487">
-        <f>IF($B487="","",IFERROR(INDEX($D$17:$D$486,MATCH($B487,$B$17:$B$486,0)),""))</f>
+        <f>IF($B487="","",IFERROR(INDEX($D$18:$D$486,MATCH($B487,$B$18:$B$486,0)),""))</f>
         <v/>
       </c>
       <c r="E487">
@@ -40935,7 +40927,7 @@
       <c r="A488" s="37" t="n"/>
       <c r="C488" s="27" t="n"/>
       <c r="D488">
-        <f>IF($B488="","",IFERROR(INDEX($D$17:$D$487,MATCH($B488,$B$17:$B$487,0)),""))</f>
+        <f>IF($B488="","",IFERROR(INDEX($D$18:$D$487,MATCH($B488,$B$18:$B$487,0)),""))</f>
         <v/>
       </c>
       <c r="E488">
@@ -40955,7 +40947,7 @@
       <c r="A489" s="37" t="n"/>
       <c r="C489" s="27" t="n"/>
       <c r="D489">
-        <f>IF($B489="","",IFERROR(INDEX($D$17:$D$488,MATCH($B489,$B$17:$B$488,0)),""))</f>
+        <f>IF($B489="","",IFERROR(INDEX($D$18:$D$488,MATCH($B489,$B$18:$B$488,0)),""))</f>
         <v/>
       </c>
       <c r="E489">
@@ -40975,7 +40967,7 @@
       <c r="A490" s="37" t="n"/>
       <c r="C490" s="27" t="n"/>
       <c r="D490">
-        <f>IF($B490="","",IFERROR(INDEX($D$17:$D$489,MATCH($B490,$B$17:$B$489,0)),""))</f>
+        <f>IF($B490="","",IFERROR(INDEX($D$18:$D$489,MATCH($B490,$B$18:$B$489,0)),""))</f>
         <v/>
       </c>
       <c r="E490">
@@ -40995,7 +40987,7 @@
       <c r="A491" s="37" t="n"/>
       <c r="C491" s="27" t="n"/>
       <c r="D491">
-        <f>IF($B491="","",IFERROR(INDEX($D$17:$D$490,MATCH($B491,$B$17:$B$490,0)),""))</f>
+        <f>IF($B491="","",IFERROR(INDEX($D$18:$D$490,MATCH($B491,$B$18:$B$490,0)),""))</f>
         <v/>
       </c>
       <c r="E491">
@@ -41015,7 +41007,7 @@
       <c r="A492" s="37" t="n"/>
       <c r="C492" s="27" t="n"/>
       <c r="D492">
-        <f>IF($B492="","",IFERROR(INDEX($D$17:$D$491,MATCH($B492,$B$17:$B$491,0)),""))</f>
+        <f>IF($B492="","",IFERROR(INDEX($D$18:$D$491,MATCH($B492,$B$18:$B$491,0)),""))</f>
         <v/>
       </c>
       <c r="E492">
@@ -41035,7 +41027,7 @@
       <c r="A493" s="37" t="n"/>
       <c r="C493" s="27" t="n"/>
       <c r="D493">
-        <f>IF($B493="","",IFERROR(INDEX($D$17:$D$492,MATCH($B493,$B$17:$B$492,0)),""))</f>
+        <f>IF($B493="","",IFERROR(INDEX($D$18:$D$492,MATCH($B493,$B$18:$B$492,0)),""))</f>
         <v/>
       </c>
       <c r="E493">
@@ -41055,7 +41047,7 @@
       <c r="A494" s="37" t="n"/>
       <c r="C494" s="27" t="n"/>
       <c r="D494">
-        <f>IF($B494="","",IFERROR(INDEX($D$17:$D$493,MATCH($B494,$B$17:$B$493,0)),""))</f>
+        <f>IF($B494="","",IFERROR(INDEX($D$18:$D$493,MATCH($B494,$B$18:$B$493,0)),""))</f>
         <v/>
       </c>
       <c r="E494">
@@ -41075,7 +41067,7 @@
       <c r="A495" s="37" t="n"/>
       <c r="C495" s="27" t="n"/>
       <c r="D495">
-        <f>IF($B495="","",IFERROR(INDEX($D$17:$D$494,MATCH($B495,$B$17:$B$494,0)),""))</f>
+        <f>IF($B495="","",IFERROR(INDEX($D$18:$D$494,MATCH($B495,$B$18:$B$494,0)),""))</f>
         <v/>
       </c>
       <c r="E495">
@@ -41095,7 +41087,7 @@
       <c r="A496" s="37" t="n"/>
       <c r="C496" s="27" t="n"/>
       <c r="D496">
-        <f>IF($B496="","",IFERROR(INDEX($D$17:$D$495,MATCH($B496,$B$17:$B$495,0)),""))</f>
+        <f>IF($B496="","",IFERROR(INDEX($D$18:$D$495,MATCH($B496,$B$18:$B$495,0)),""))</f>
         <v/>
       </c>
       <c r="E496">
@@ -41115,7 +41107,7 @@
       <c r="A497" s="37" t="n"/>
       <c r="C497" s="27" t="n"/>
       <c r="D497">
-        <f>IF($B497="","",IFERROR(INDEX($D$17:$D$496,MATCH($B497,$B$17:$B$496,0)),""))</f>
+        <f>IF($B497="","",IFERROR(INDEX($D$18:$D$496,MATCH($B497,$B$18:$B$496,0)),""))</f>
         <v/>
       </c>
       <c r="E497">
@@ -41135,7 +41127,7 @@
       <c r="A498" s="37" t="n"/>
       <c r="C498" s="27" t="n"/>
       <c r="D498">
-        <f>IF($B498="","",IFERROR(INDEX($D$17:$D$497,MATCH($B498,$B$17:$B$497,0)),""))</f>
+        <f>IF($B498="","",IFERROR(INDEX($D$18:$D$497,MATCH($B498,$B$18:$B$497,0)),""))</f>
         <v/>
       </c>
       <c r="E498">
@@ -41155,7 +41147,7 @@
       <c r="A499" s="37" t="n"/>
       <c r="C499" s="27" t="n"/>
       <c r="D499">
-        <f>IF($B499="","",IFERROR(INDEX($D$17:$D$498,MATCH($B499,$B$17:$B$498,0)),""))</f>
+        <f>IF($B499="","",IFERROR(INDEX($D$18:$D$498,MATCH($B499,$B$18:$B$498,0)),""))</f>
         <v/>
       </c>
       <c r="E499">
@@ -41175,7 +41167,7 @@
       <c r="A500" s="37" t="n"/>
       <c r="C500" s="27" t="n"/>
       <c r="D500">
-        <f>IF($B500="","",IFERROR(INDEX($D$17:$D$499,MATCH($B500,$B$17:$B$499,0)),""))</f>
+        <f>IF($B500="","",IFERROR(INDEX($D$18:$D$499,MATCH($B500,$B$18:$B$499,0)),""))</f>
         <v/>
       </c>
       <c r="E500">
@@ -41195,7 +41187,7 @@
       <c r="A501" s="37" t="n"/>
       <c r="C501" s="27" t="n"/>
       <c r="D501">
-        <f>IF($B501="","",IFERROR(INDEX($D$17:$D$500,MATCH($B501,$B$17:$B$500,0)),""))</f>
+        <f>IF($B501="","",IFERROR(INDEX($D$18:$D$500,MATCH($B501,$B$18:$B$500,0)),""))</f>
         <v/>
       </c>
       <c r="E501">
@@ -41215,7 +41207,7 @@
       <c r="A502" s="37" t="n"/>
       <c r="C502" s="27" t="n"/>
       <c r="D502">
-        <f>IF($B502="","",IFERROR(INDEX($D$17:$D$501,MATCH($B502,$B$17:$B$501,0)),""))</f>
+        <f>IF($B502="","",IFERROR(INDEX($D$18:$D$501,MATCH($B502,$B$18:$B$501,0)),""))</f>
         <v/>
       </c>
       <c r="E502">
@@ -41235,7 +41227,7 @@
       <c r="A503" s="37" t="n"/>
       <c r="C503" s="27" t="n"/>
       <c r="D503">
-        <f>IF($B503="","",IFERROR(INDEX($D$17:$D$502,MATCH($B503,$B$17:$B$502,0)),""))</f>
+        <f>IF($B503="","",IFERROR(INDEX($D$18:$D$502,MATCH($B503,$B$18:$B$502,0)),""))</f>
         <v/>
       </c>
       <c r="E503">
@@ -41255,7 +41247,7 @@
       <c r="A504" s="37" t="n"/>
       <c r="C504" s="27" t="n"/>
       <c r="D504">
-        <f>IF($B504="","",IFERROR(INDEX($D$17:$D$503,MATCH($B504,$B$17:$B$503,0)),""))</f>
+        <f>IF($B504="","",IFERROR(INDEX($D$18:$D$503,MATCH($B504,$B$18:$B$503,0)),""))</f>
         <v/>
       </c>
       <c r="E504">
@@ -41275,7 +41267,7 @@
       <c r="A505" s="37" t="n"/>
       <c r="C505" s="27" t="n"/>
       <c r="D505">
-        <f>IF($B505="","",IFERROR(INDEX($D$17:$D$504,MATCH($B505,$B$17:$B$504,0)),""))</f>
+        <f>IF($B505="","",IFERROR(INDEX($D$18:$D$504,MATCH($B505,$B$18:$B$504,0)),""))</f>
         <v/>
       </c>
       <c r="E505">
@@ -41295,7 +41287,7 @@
       <c r="A506" s="37" t="n"/>
       <c r="C506" s="27" t="n"/>
       <c r="D506">
-        <f>IF($B506="","",IFERROR(INDEX($D$17:$D$505,MATCH($B506,$B$17:$B$505,0)),""))</f>
+        <f>IF($B506="","",IFERROR(INDEX($D$18:$D$505,MATCH($B506,$B$18:$B$505,0)),""))</f>
         <v/>
       </c>
       <c r="E506">
@@ -41315,7 +41307,7 @@
       <c r="A507" s="37" t="n"/>
       <c r="C507" s="27" t="n"/>
       <c r="D507">
-        <f>IF($B507="","",IFERROR(INDEX($D$17:$D$506,MATCH($B507,$B$17:$B$506,0)),""))</f>
+        <f>IF($B507="","",IFERROR(INDEX($D$18:$D$506,MATCH($B507,$B$18:$B$506,0)),""))</f>
         <v/>
       </c>
       <c r="E507">
@@ -41335,7 +41327,7 @@
       <c r="A508" s="37" t="n"/>
       <c r="C508" s="27" t="n"/>
       <c r="D508">
-        <f>IF($B508="","",IFERROR(INDEX($D$17:$D$507,MATCH($B508,$B$17:$B$507,0)),""))</f>
+        <f>IF($B508="","",IFERROR(INDEX($D$18:$D$507,MATCH($B508,$B$18:$B$507,0)),""))</f>
         <v/>
       </c>
       <c r="E508">
@@ -41355,7 +41347,7 @@
       <c r="A509" s="37" t="n"/>
       <c r="C509" s="27" t="n"/>
       <c r="D509">
-        <f>IF($B509="","",IFERROR(INDEX($D$17:$D$508,MATCH($B509,$B$17:$B$508,0)),""))</f>
+        <f>IF($B509="","",IFERROR(INDEX($D$18:$D$508,MATCH($B509,$B$18:$B$508,0)),""))</f>
         <v/>
       </c>
       <c r="E509">
@@ -41375,7 +41367,7 @@
       <c r="A510" s="37" t="n"/>
       <c r="C510" s="27" t="n"/>
       <c r="D510">
-        <f>IF($B510="","",IFERROR(INDEX($D$17:$D$509,MATCH($B510,$B$17:$B$509,0)),""))</f>
+        <f>IF($B510="","",IFERROR(INDEX($D$18:$D$509,MATCH($B510,$B$18:$B$509,0)),""))</f>
         <v/>
       </c>
       <c r="E510">
@@ -41395,7 +41387,7 @@
       <c r="A511" s="37" t="n"/>
       <c r="C511" s="27" t="n"/>
       <c r="D511">
-        <f>IF($B511="","",IFERROR(INDEX($D$17:$D$510,MATCH($B511,$B$17:$B$510,0)),""))</f>
+        <f>IF($B511="","",IFERROR(INDEX($D$18:$D$510,MATCH($B511,$B$18:$B$510,0)),""))</f>
         <v/>
       </c>
       <c r="E511">
@@ -41415,7 +41407,7 @@
       <c r="A512" s="37" t="n"/>
       <c r="C512" s="27" t="n"/>
       <c r="D512">
-        <f>IF($B512="","",IFERROR(INDEX($D$17:$D$511,MATCH($B512,$B$17:$B$511,0)),""))</f>
+        <f>IF($B512="","",IFERROR(INDEX($D$18:$D$511,MATCH($B512,$B$18:$B$511,0)),""))</f>
         <v/>
       </c>
       <c r="E512">
@@ -41435,7 +41427,7 @@
       <c r="A513" s="37" t="n"/>
       <c r="C513" s="27" t="n"/>
       <c r="D513">
-        <f>IF($B513="","",IFERROR(INDEX($D$17:$D$512,MATCH($B513,$B$17:$B$512,0)),""))</f>
+        <f>IF($B513="","",IFERROR(INDEX($D$18:$D$512,MATCH($B513,$B$18:$B$512,0)),""))</f>
         <v/>
       </c>
       <c r="E513">
@@ -41455,7 +41447,7 @@
       <c r="A514" s="37" t="n"/>
       <c r="C514" s="27" t="n"/>
       <c r="D514">
-        <f>IF($B514="","",IFERROR(INDEX($D$17:$D$513,MATCH($B514,$B$17:$B$513,0)),""))</f>
+        <f>IF($B514="","",IFERROR(INDEX($D$18:$D$513,MATCH($B514,$B$18:$B$513,0)),""))</f>
         <v/>
       </c>
       <c r="E514">
@@ -41475,7 +41467,7 @@
       <c r="A515" s="37" t="n"/>
       <c r="C515" s="27" t="n"/>
       <c r="D515">
-        <f>IF($B515="","",IFERROR(INDEX($D$17:$D$514,MATCH($B515,$B$17:$B$514,0)),""))</f>
+        <f>IF($B515="","",IFERROR(INDEX($D$18:$D$514,MATCH($B515,$B$18:$B$514,0)),""))</f>
         <v/>
       </c>
       <c r="E515">
@@ -41495,7 +41487,7 @@
       <c r="A516" s="37" t="n"/>
       <c r="C516" s="27" t="n"/>
       <c r="D516">
-        <f>IF($B516="","",IFERROR(INDEX($D$17:$D$515,MATCH($B516,$B$17:$B$515,0)),""))</f>
+        <f>IF($B516="","",IFERROR(INDEX($D$18:$D$515,MATCH($B516,$B$18:$B$515,0)),""))</f>
         <v/>
       </c>
       <c r="E516">
@@ -41511,51 +41503,78 @@
         <v/>
       </c>
     </row>
+    <row r="517">
+      <c r="A517" s="37" t="n"/>
+      <c r="C517" s="27" t="n"/>
+      <c r="D517">
+        <f>IF($B517="","",IFERROR(INDEX($D$18:$D$516,MATCH($B517,$B$18:$B$516,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E517">
+        <f>IFERROR(INDEX(Dim_Vendor[DefaultCategory],MATCH($D517,Dim_Vendor[VendorName],0)),"")</f>
+        <v/>
+      </c>
+      <c r="H517">
+        <f>IF($C517="","",IF(SignConvention="Negative = Expense",IF($C517&lt;0,"Expense","Income"),IF($C517&gt;0,"Expense","Income")))</f>
+        <v/>
+      </c>
+      <c r="I517" s="27">
+        <f>IF($C517="","",ABS($C517))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="13">
     <mergeCell ref="A6:K6"/>
-    <mergeCell ref="E13:K13"/>
-    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A12:K12"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="A9:K9"/>
-    <mergeCell ref="A15:K15"/>
+    <mergeCell ref="E14:K14"/>
     <mergeCell ref="A7:K7"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A16:K16"/>
     <mergeCell ref="A11:K11"/>
     <mergeCell ref="A10:K10"/>
     <mergeCell ref="A5:K5"/>
     <mergeCell ref="A1:K2"/>
     <mergeCell ref="A8:K8"/>
   </mergeCells>
-  <conditionalFormatting sqref="H17:H516">
+  <conditionalFormatting sqref="H18:H517">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="3">
       <formula>"Expense"</formula>
     </cfRule>
     <cfRule type="cellIs" priority="2" operator="equal" dxfId="4">
       <formula>"Income"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D17:D516">
-    <cfRule type="expression" priority="3" dxfId="5">
-      <formula>AND($C17&lt;&gt;"",$D17="")</formula>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="5">
+      <formula>"Return"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="6">
-    <dataValidation sqref="D13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+  <conditionalFormatting sqref="D18:D517">
+    <cfRule type="expression" priority="4" dxfId="6">
+      <formula>AND($C18&lt;&gt;"",$D18="")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="7">
+    <dataValidation sqref="D14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Negative = Expense,Positive = Expense"</formula1>
     </dataValidation>
-    <dataValidation sqref="D17:D516" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Please choose a value from the dropdown list." type="list">
+    <dataValidation sqref="D18:D517" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Please choose a value from the dropdown list." type="list">
       <formula1>VendorNameList</formula1>
     </dataValidation>
-    <dataValidation sqref="E17:E516" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Please choose a value from the dropdown list." type="list">
+    <dataValidation sqref="E18:E517" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Please choose a value from the dropdown list." type="list">
       <formula1>ExpenseCategoryList</formula1>
     </dataValidation>
-    <dataValidation sqref="F17:F516" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Please choose a value from the dropdown list." type="list">
+    <dataValidation sqref="F18:F517" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Please choose a value from the dropdown list." type="list">
       <formula1>AccountNameList</formula1>
     </dataValidation>
-    <dataValidation sqref="G17:G516" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Please choose a value from the dropdown list." type="list">
+    <dataValidation sqref="G18:G517" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Please choose a value from the dropdown list." type="list">
       <formula1>PaymentMethodList</formula1>
     </dataValidation>
-    <dataValidation sqref="J17:J516" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Please choose a value from the dropdown list." type="list">
+    <dataValidation sqref="H18:H517" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Please choose a value from the dropdown list." type="list">
+      <formula1>"Expense,Income,Return"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J18:J517" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Please choose a value from the dropdown list." type="list">
       <formula1>List_NeedWant</formula1>
     </dataValidation>
   </dataValidations>
@@ -42019,7 +42038,7 @@
     <mergeCell ref="A4:P4"/>
   </mergeCells>
   <conditionalFormatting sqref="K6">
-    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="5">
+    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="6">
       <formula>200</formula>
     </cfRule>
   </conditionalFormatting>
@@ -42362,7 +42381,7 @@
         <color rgb="002563EB"/>
       </dataBar>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="greaterThanOrEqual" dxfId="6">
+    <cfRule type="cellIs" priority="2" operator="greaterThanOrEqual" dxfId="7">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -42561,7 +42580,7 @@
         <v>2200</v>
       </c>
       <c r="C11" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A11,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A11,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A11,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A11,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A11,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="D11" s="39">
@@ -42591,7 +42610,7 @@
         <v>300</v>
       </c>
       <c r="C12" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A12,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A12,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A12,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A12,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A12,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="D12" s="39">
@@ -42621,7 +42640,7 @@
         <v>150</v>
       </c>
       <c r="C13" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A13,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A13,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A13,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A13,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A13,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="D13" s="39">
@@ -42651,7 +42670,7 @@
         <v>450</v>
       </c>
       <c r="C14" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A14,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A14,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A14,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A14,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A14,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="D14" s="39">
@@ -42681,7 +42700,7 @@
         <v>150</v>
       </c>
       <c r="C15" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A15,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A15,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A15,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A15,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A15,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="D15" s="39">
@@ -42711,7 +42730,7 @@
         <v>200</v>
       </c>
       <c r="C16" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A16,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A16,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A16,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A16,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A16,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="D16" s="39">
@@ -42741,7 +42760,7 @@
         <v>200</v>
       </c>
       <c r="C17" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A17,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A17,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A17,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A17,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A17,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="D17" s="39">
@@ -42771,7 +42790,7 @@
         <v>900</v>
       </c>
       <c r="C18" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A18,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A18,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A18,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A18,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A18,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="D18" s="39">
@@ -42801,7 +42820,7 @@
         <v>250</v>
       </c>
       <c r="C19" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A19,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A19,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A19,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A19,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A19,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="D19" s="39">
@@ -42831,7 +42850,7 @@
         <v>200</v>
       </c>
       <c r="C20" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A20,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A20,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A20,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A20,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A20,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="D20" s="39">
@@ -42861,7 +42880,7 @@
         <v>150</v>
       </c>
       <c r="C21" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A21,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A21,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A21,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A21,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A21,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="D21" s="39">
@@ -42891,7 +42910,7 @@
         <v>100</v>
       </c>
       <c r="C22" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A22,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A22,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A22,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A22,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A22,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="D22" s="39">
@@ -42921,7 +42940,7 @@
         <v>75</v>
       </c>
       <c r="C23" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A23,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A23,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A23,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A23,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A23,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="D23" s="39">
@@ -42951,7 +42970,7 @@
         <v>100</v>
       </c>
       <c r="C24" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A24,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A24,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A24,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A24,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A24,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="D24" s="39">
@@ -42981,7 +43000,7 @@
         <v>100</v>
       </c>
       <c r="C25" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A25,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A25,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A25,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A25,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A25,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="D25" s="39">
@@ -43011,7 +43030,7 @@
         <v>75</v>
       </c>
       <c r="C26" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A26,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A26,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A26,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A26,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A26,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="D26" s="39">
@@ -43041,7 +43060,7 @@
         <v>100</v>
       </c>
       <c r="C27" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A27,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A27,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A27,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A27,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A27,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="D27" s="39">
@@ -43071,7 +43090,7 @@
         <v>75</v>
       </c>
       <c r="C28" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A28,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A28,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A28,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A28,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A28,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="D28" s="39">
@@ -43101,7 +43120,7 @@
         <v>50</v>
       </c>
       <c r="C29" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A29,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A29,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A29,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A29,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A29,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="D29" s="39">
@@ -43131,7 +43150,7 @@
         <v>150</v>
       </c>
       <c r="C30" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A30,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A30,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A30,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A30,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A30,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="D30" s="39">
@@ -43161,7 +43180,7 @@
         <v>100</v>
       </c>
       <c r="C31" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A31,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A31,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A31,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A31,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A31,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="D31" s="39">
@@ -43191,7 +43210,7 @@
         <v>100</v>
       </c>
       <c r="C32" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A32,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A32,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A32,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A32,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A32,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="D32" s="39">
@@ -43221,7 +43240,7 @@
         <v>50</v>
       </c>
       <c r="C33" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A33,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A33,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A33,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A33,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A33,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="D33" s="39">
@@ -43251,7 +43270,7 @@
         <v>100</v>
       </c>
       <c r="C34" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A34,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A34,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A34,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A34,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A34,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="D34" s="39">
@@ -43281,7 +43300,7 @@
         <v>200</v>
       </c>
       <c r="C35" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A35,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A35,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[CategoryName],$A35,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A35,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[CategoryName],$A35,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="D35" s="39">
@@ -43318,10 +43337,10 @@
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Over Budget"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="7">
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="8">
       <formula>"Near Limit"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="8">
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="9">
       <formula>"Under Budget"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -44078,11 +44097,11 @@
         <v/>
       </c>
       <c r="E6" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B6,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B6,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B6,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B6,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B6,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F6" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B6,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B6,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B6,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B6,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B6,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -44101,11 +44120,11 @@
         <v/>
       </c>
       <c r="E7" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B7,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B7,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B7,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B7,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B7,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F7" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B7,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B7,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B7,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B7,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B7,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -44124,11 +44143,11 @@
         <v/>
       </c>
       <c r="E8" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B8,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B8,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B8,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B8,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B8,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F8" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B8,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B8,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B8,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B8,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B8,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -44151,11 +44170,11 @@
         <v/>
       </c>
       <c r="E9" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B9,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B9,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B9,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B9,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B9,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F9" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B9,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B9,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B9,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B9,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B9,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -44178,11 +44197,11 @@
         <v/>
       </c>
       <c r="E10" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B10,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B10,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B10,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B10,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B10,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F10" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B10,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B10,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B10,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B10,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B10,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -44205,11 +44224,11 @@
         <v/>
       </c>
       <c r="E11" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B11,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B11,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B11,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B11,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B11,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F11" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B11,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B11,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B11,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B11,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B11,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -44232,11 +44251,11 @@
         <v/>
       </c>
       <c r="E12" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B12,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B12,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B12,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B12,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B12,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F12" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B12,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B12,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B12,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B12,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B12,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -44259,11 +44278,11 @@
         <v/>
       </c>
       <c r="E13" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B13,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B13,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B13,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B13,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B13,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F13" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B13,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B13,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B13,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B13,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B13,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -44282,11 +44301,11 @@
         <v/>
       </c>
       <c r="E14" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B14,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B14,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B14,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B14,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B14,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F14" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B14,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B14,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B14,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B14,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B14,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -44309,11 +44328,11 @@
         <v/>
       </c>
       <c r="E15" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B15,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B15,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B15,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B15,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B15,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F15" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B15,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B15,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B15,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B15,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B15,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -44332,11 +44351,11 @@
         <v/>
       </c>
       <c r="E16" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B16,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B16,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B16,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B16,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B16,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F16" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B16,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B16,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B16,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B16,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B16,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -44359,11 +44378,11 @@
         <v/>
       </c>
       <c r="E17" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B17,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B17,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B17,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B17,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B17,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F17" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B17,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B17,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B17,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B17,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B17,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -44386,11 +44405,11 @@
         <v/>
       </c>
       <c r="E18" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B18,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B18,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B18,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B18,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B18,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F18" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B18,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B18,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B18,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B18,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B18,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -44413,11 +44432,11 @@
         <v/>
       </c>
       <c r="E19" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B19,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B19,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B19,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B19,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B19,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F19" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B19,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B19,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B19,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B19,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B19,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -44436,11 +44455,11 @@
         <v/>
       </c>
       <c r="E20" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B20,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B20,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B20,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B20,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B20,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F20" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B20,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B20,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B20,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B20,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B20,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -44463,11 +44482,11 @@
         <v/>
       </c>
       <c r="E21" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B21,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B21,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B21,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B21,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B21,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F21" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B21,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B21,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B21,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B21,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B21,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -44490,11 +44509,11 @@
         <v/>
       </c>
       <c r="E22" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B22,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B22,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B22,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B22,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B22,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F22" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B22,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B22,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B22,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B22,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B22,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -44513,11 +44532,11 @@
         <v/>
       </c>
       <c r="E23" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B23,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B23,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B23,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B23,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B23,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F23" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B23,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B23,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B23,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B23,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B23,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -44536,11 +44555,11 @@
         <v/>
       </c>
       <c r="E24" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B24,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B24,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B24,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B24,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B24,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F24" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B24,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B24,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B24,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B24,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B24,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -44559,11 +44578,11 @@
         <v/>
       </c>
       <c r="E25" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B25,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B25,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B25,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B25,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B25,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F25" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B25,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B25,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B25,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B25,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B25,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -44582,11 +44601,11 @@
         <v/>
       </c>
       <c r="E26" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B26,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B26,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B26,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B26,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B26,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F26" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B26,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B26,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B26,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B26,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B26,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -44605,11 +44624,11 @@
         <v/>
       </c>
       <c r="E27" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B27,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B27,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B27,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B27,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B27,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F27" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B27,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B27,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B27,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B27,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B27,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -44628,11 +44647,11 @@
         <v/>
       </c>
       <c r="E28" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B28,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B28,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B28,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B28,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B28,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F28" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B28,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B28,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B28,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B28,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B28,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -44651,11 +44670,11 @@
         <v/>
       </c>
       <c r="E29" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B29,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B29,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B29,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B29,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B29,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F29" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B29,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B29,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B29,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B29,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B29,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -44678,11 +44697,11 @@
         <v/>
       </c>
       <c r="E30" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B30,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B30,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B30,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B30,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B30,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F30" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B30,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B30,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B30,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B30,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B30,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -44705,11 +44724,11 @@
         <v/>
       </c>
       <c r="E31" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B31,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B31,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B31,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B31,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B31,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F31" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B31,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B31,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B31,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B31,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B31,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -44732,11 +44751,11 @@
         <v/>
       </c>
       <c r="E32" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B32,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B32,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B32,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B32,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B32,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F32" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B32,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B32,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B32,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B32,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B32,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -44759,11 +44778,11 @@
         <v/>
       </c>
       <c r="E33" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B33,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B33,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B33,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B33,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B33,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F33" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B33,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B33,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B33,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B33,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B33,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -44782,11 +44801,11 @@
         <v/>
       </c>
       <c r="E34" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B34,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B34,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B34,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B34,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B34,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F34" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B34,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B34,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B34,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B34,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B34,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -44805,11 +44824,11 @@
         <v/>
       </c>
       <c r="E35" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B35,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B35,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B35,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B35,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B35,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F35" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B35,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B35,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B35,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B35,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B35,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -44832,11 +44851,11 @@
         <v/>
       </c>
       <c r="E36" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B36,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B36,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B36,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B36,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B36,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F36" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B36,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B36,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B36,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B36,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B36,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -44855,11 +44874,11 @@
         <v/>
       </c>
       <c r="E37" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B37,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B37,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B37,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B37,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B37,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F37" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B37,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B37,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B37,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B37,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B37,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -44878,11 +44897,11 @@
         <v/>
       </c>
       <c r="E38" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B38,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B38,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B38,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B38,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B38,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F38" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B38,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B38,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B38,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B38,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B38,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -44905,11 +44924,11 @@
         <v/>
       </c>
       <c r="E39" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B39,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B39,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B39,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B39,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B39,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F39" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B39,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B39,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B39,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B39,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B39,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -44932,11 +44951,11 @@
         <v/>
       </c>
       <c r="E40" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B40,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B40,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B40,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B40,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B40,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F40" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B40,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B40,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B40,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B40,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B40,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -44959,11 +44978,11 @@
         <v/>
       </c>
       <c r="E41" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B41,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B41,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B41,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B41,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B41,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F41" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B41,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B41,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B41,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B41,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B41,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -44982,11 +45001,11 @@
         <v/>
       </c>
       <c r="E42" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B42,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B42,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B42,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B42,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B42,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F42" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B42,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B42,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B42,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B42,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B42,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -45005,11 +45024,11 @@
         <v/>
       </c>
       <c r="E43" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B43,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B43,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B43,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B43,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B43,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F43" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B43,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B43,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B43,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B43,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B43,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -45032,11 +45051,11 @@
         <v/>
       </c>
       <c r="E44" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B44,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B44,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B44,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B44,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B44,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F44" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B44,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B44,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B44,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B44,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B44,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -45055,11 +45074,11 @@
         <v/>
       </c>
       <c r="E45" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B45,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B45,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B45,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B45,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B45,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F45" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B45,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B45,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B45,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B45,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B45,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -45082,11 +45101,11 @@
         <v/>
       </c>
       <c r="E46" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B46,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B46,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B46,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B46,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B46,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F46" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B46,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B46,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B46,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B46,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B46,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -45109,11 +45128,11 @@
         <v/>
       </c>
       <c r="E47" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B47,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B47,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B47,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B47,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B47,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F47" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B47,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B47,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B47,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B47,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B47,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -45132,11 +45151,11 @@
         <v/>
       </c>
       <c r="E48" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B48,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B48,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B48,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B48,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B48,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F48" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B48,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B48,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B48,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B48,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B48,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -45159,11 +45178,11 @@
         <v/>
       </c>
       <c r="E49" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B49,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B49,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B49,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B49,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B49,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F49" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B49,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B49,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B49,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B49,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B49,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -45186,11 +45205,11 @@
         <v/>
       </c>
       <c r="E50" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B50,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B50,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B50,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B50,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B50,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F50" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B50,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B50,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B50,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B50,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B50,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -45213,11 +45232,11 @@
         <v/>
       </c>
       <c r="E51" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B51,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B51,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B51,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B51,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B51,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F51" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B51,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B51,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B51,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B51,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B51,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -45240,11 +45259,11 @@
         <v/>
       </c>
       <c r="E52" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B52,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B52,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B52,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B52,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B52,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F52" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B52,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B52,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B52,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B52,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B52,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -45263,11 +45282,11 @@
         <v/>
       </c>
       <c r="E53" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B53,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B53,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B53,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B53,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B53,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F53" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B53,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B53,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B53,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B53,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B53,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -45286,11 +45305,11 @@
         <v/>
       </c>
       <c r="E54" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B54,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B54,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B54,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B54,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B54,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F54" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B54,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B54,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B54,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B54,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B54,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -45309,11 +45328,11 @@
         <v/>
       </c>
       <c r="E55" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B55,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B55,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B55,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B55,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B55,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F55" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B55,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B55,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B55,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B55,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B55,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -45336,11 +45355,11 @@
         <v/>
       </c>
       <c r="E56" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B56,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B56,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B56,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B56,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B56,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F56" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B56,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B56,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B56,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B56,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B56,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -45363,11 +45382,11 @@
         <v/>
       </c>
       <c r="E57" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B57,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B57,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B57,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B57,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B57,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F57" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B57,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B57,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B57,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B57,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B57,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -45390,11 +45409,11 @@
         <v/>
       </c>
       <c r="E58" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B58,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B58,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B58,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B58,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B58,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F58" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B58,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B58,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B58,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B58,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B58,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -45413,11 +45432,11 @@
         <v/>
       </c>
       <c r="E59" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B59,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B59,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B59,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B59,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B59,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F59" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B59,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B59,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B59,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B59,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B59,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -45436,11 +45455,11 @@
         <v/>
       </c>
       <c r="E60" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B60,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B60,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B60,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B60,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B60,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F60" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B60,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B60,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B60,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B60,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B60,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -45463,11 +45482,11 @@
         <v/>
       </c>
       <c r="E61" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B61,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B61,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B61,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B61,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B61,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F61" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B61,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B61,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B61,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B61,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B61,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -45490,11 +45509,11 @@
         <v/>
       </c>
       <c r="E62" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B62,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B62,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B62,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B62,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B62,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F62" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B62,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B62,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B62,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B62,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B62,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -45517,11 +45536,11 @@
         <v/>
       </c>
       <c r="E63" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B63,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B63,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B63,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B63,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B63,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F63" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B63,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B63,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B63,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B63,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B63,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -45540,11 +45559,11 @@
         <v/>
       </c>
       <c r="E64" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B64,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B64,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B64,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B64,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B64,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F64" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B64,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B64,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B64,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B64,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B64,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -45563,11 +45582,11 @@
         <v/>
       </c>
       <c r="E65" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B65,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B65,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B65,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B65,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B65,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F65" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B65,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B65,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B65,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B65,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B65,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -45590,11 +45609,11 @@
         <v/>
       </c>
       <c r="E66" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B66,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B66,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B66,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B66,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B66,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F66" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B66,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B66,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B66,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B66,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B66,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -45617,11 +45636,11 @@
         <v/>
       </c>
       <c r="E67" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B67,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B67,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B67,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B67,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B67,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F67" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B67,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B67,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B67,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B67,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B67,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -45640,11 +45659,11 @@
         <v/>
       </c>
       <c r="E68" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B68,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B68,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B68,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B68,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B68,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F68" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B68,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B68,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B68,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B68,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B68,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -45667,11 +45686,11 @@
         <v/>
       </c>
       <c r="E69" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B69,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B69,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B69,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B69,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B69,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F69" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B69,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B69,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B69,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B69,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B69,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -45694,11 +45713,11 @@
         <v/>
       </c>
       <c r="E70" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B70,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B70,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B70,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B70,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B70,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F70" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B70,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B70,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B70,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B70,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B70,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -45721,11 +45740,11 @@
         <v/>
       </c>
       <c r="E71" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B71,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B71,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B71,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B71,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B71,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F71" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B71,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B71,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B71,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B71,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B71,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -45748,11 +45767,11 @@
         <v/>
       </c>
       <c r="E72" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B72,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B72,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B72,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B72,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B72,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F72" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B72,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B72,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B72,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B72,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B72,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -45771,11 +45790,11 @@
         <v/>
       </c>
       <c r="E73" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B73,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B73,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B73,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B73,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B73,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F73" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B73,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B73,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B73,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B73,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B73,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -45798,11 +45817,11 @@
         <v/>
       </c>
       <c r="E74" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B74,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B74,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B74,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B74,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B74,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F74" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B74,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B74,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B74,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B74,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B74,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -45825,11 +45844,11 @@
         <v/>
       </c>
       <c r="E75" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B75,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B75,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B75,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B75,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B75,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F75" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B75,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B75,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B75,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B75,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B75,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -45852,11 +45871,11 @@
         <v/>
       </c>
       <c r="E76" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B76,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B76,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B76,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B76,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B76,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F76" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B76,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B76,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B76,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B76,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B76,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -45879,11 +45898,11 @@
         <v/>
       </c>
       <c r="E77" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B77,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B77,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B77,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B77,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B77,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F77" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B77,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B77,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B77,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B77,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B77,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -45906,11 +45925,11 @@
         <v/>
       </c>
       <c r="E78" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B78,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B78,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B78,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B78,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B78,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F78" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B78,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B78,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B78,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B78,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B78,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -45933,11 +45952,11 @@
         <v/>
       </c>
       <c r="E79" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B79,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B79,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B79,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B79,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B79,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F79" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B79,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B79,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B79,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B79,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B79,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -45960,11 +45979,11 @@
         <v/>
       </c>
       <c r="E80" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B80,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B80,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B80,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B80,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B80,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F80" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B80,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B80,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B80,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B80,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B80,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -45987,11 +46006,11 @@
         <v/>
       </c>
       <c r="E81" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B81,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B81,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B81,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B81,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B81,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F81" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B81,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B81,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B81,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B81,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B81,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -46010,11 +46029,11 @@
         <v/>
       </c>
       <c r="E82" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B82,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B82,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B82,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B82,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B82,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F82" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B82,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B82,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B82,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B82,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B82,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -46037,11 +46056,11 @@
         <v/>
       </c>
       <c r="E83" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B83,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B83,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B83,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B83,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B83,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F83" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B83,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B83,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B83,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B83,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B83,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -46060,11 +46079,11 @@
         <v/>
       </c>
       <c r="E84" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B84,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B84,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B84,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B84,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B84,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F84" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B84,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B84,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B84,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B84,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B84,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -46087,11 +46106,11 @@
         <v/>
       </c>
       <c r="E85" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B85,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B85,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B85,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B85,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B85,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F85" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B85,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B85,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B85,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B85,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B85,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -46110,11 +46129,11 @@
         <v/>
       </c>
       <c r="E86" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B86,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B86,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B86,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B86,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B86,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F86" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B86,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B86,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B86,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B86,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B86,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -46137,11 +46156,11 @@
         <v/>
       </c>
       <c r="E87" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B87,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B87,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B87,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B87,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B87,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F87" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B87,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B87,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B87,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B87,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B87,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -46160,11 +46179,11 @@
         <v/>
       </c>
       <c r="E88" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B88,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B88,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B88,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B88,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B88,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F88" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B88,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B88,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B88,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B88,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B88,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -46187,11 +46206,11 @@
         <v/>
       </c>
       <c r="E89" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B89,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B89,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B89,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B89,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B89,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F89" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B89,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B89,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B89,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B89,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B89,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -46210,11 +46229,11 @@
         <v/>
       </c>
       <c r="E90" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B90,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B90,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B90,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B90,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B90,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F90" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B90,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B90,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B90,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B90,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B90,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -46237,11 +46256,11 @@
         <v/>
       </c>
       <c r="E91" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B91,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B91,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B91,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B91,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B91,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F91" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B91,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B91,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B91,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B91,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B91,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -46260,11 +46279,11 @@
         <v/>
       </c>
       <c r="E92" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B92,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B92,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B92,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B92,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B92,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F92" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B92,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B92,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B92,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B92,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B92,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -46287,11 +46306,11 @@
         <v/>
       </c>
       <c r="E93" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B93,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B93,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B93,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B93,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B93,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F93" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B93,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B93,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B93,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B93,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B93,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -46314,11 +46333,11 @@
         <v/>
       </c>
       <c r="E94" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B94,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B94,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B94,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B94,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B94,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F94" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B94,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B94,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B94,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B94,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B94,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -46341,11 +46360,11 @@
         <v/>
       </c>
       <c r="E95" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B95,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B95,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B95,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B95,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B95,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F95" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B95,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B95,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B95,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B95,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B95,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -46368,11 +46387,11 @@
         <v/>
       </c>
       <c r="E96" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B96,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B96,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B96,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B96,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B96,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F96" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B96,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B96,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B96,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B96,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B96,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -46391,11 +46410,11 @@
         <v/>
       </c>
       <c r="E97" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B97,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B97,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B97,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B97,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B97,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F97" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B97,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B97,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B97,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B97,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B97,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -46414,11 +46433,11 @@
         <v/>
       </c>
       <c r="E98" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B98,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B98,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B98,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B98,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B98,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F98" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B98,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B98,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B98,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B98,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B98,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -46441,11 +46460,11 @@
         <v/>
       </c>
       <c r="E99" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B99,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B99,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B99,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B99,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B99,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F99" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B99,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B99,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B99,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B99,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B99,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -46464,11 +46483,11 @@
         <v/>
       </c>
       <c r="E100" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B100,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B100,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B100,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B100,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B100,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F100" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B100,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B100,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B100,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B100,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B100,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -46491,11 +46510,11 @@
         <v/>
       </c>
       <c r="E101" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B101,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B101,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B101,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B101,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B101,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F101" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B101,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B101,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B101,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B101,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B101,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -46514,11 +46533,11 @@
         <v/>
       </c>
       <c r="E102" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B102,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B102,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B102,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B102,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B102,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F102" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B102,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B102,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B102,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B102,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B102,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -46541,11 +46560,11 @@
         <v/>
       </c>
       <c r="E103" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B103,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B103,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B103,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B103,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B103,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F103" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B103,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B103,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B103,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B103,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B103,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -46568,11 +46587,11 @@
         <v/>
       </c>
       <c r="E104" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B104,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B104,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B104,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B104,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B104,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F104" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B104,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B104,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B104,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B104,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B104,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -46595,11 +46614,11 @@
         <v/>
       </c>
       <c r="E105" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B105,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B105,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B105,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B105,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B105,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F105" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B105,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B105,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B105,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B105,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B105,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -46618,11 +46637,11 @@
         <v/>
       </c>
       <c r="E106" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B106,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B106,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B106,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B106,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B106,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F106" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B106,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B106,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B106,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B106,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B106,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -46645,11 +46664,11 @@
         <v/>
       </c>
       <c r="E107" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B107,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B107,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B107,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B107,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B107,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F107" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B107,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B107,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B107,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B107,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B107,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -46668,11 +46687,11 @@
         <v/>
       </c>
       <c r="E108" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B108,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B108,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B108,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B108,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B108,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F108" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B108,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B108,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B108,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B108,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B108,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -46691,11 +46710,11 @@
         <v/>
       </c>
       <c r="E109" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B109,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B109,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B109,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B109,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B109,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F109" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B109,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B109,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B109,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B109,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B109,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -46714,11 +46733,11 @@
         <v/>
       </c>
       <c r="E110" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B110,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B110,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B110,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B110,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B110,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F110" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B110,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B110,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B110,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B110,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B110,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -46741,11 +46760,11 @@
         <v/>
       </c>
       <c r="E111" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B111,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B111,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B111,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B111,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B111,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F111" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B111,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B111,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B111,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B111,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B111,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -46768,11 +46787,11 @@
         <v/>
       </c>
       <c r="E112" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B112,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B112,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B112,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B112,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B112,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F112" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B112,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B112,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B112,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B112,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B112,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -46795,11 +46814,11 @@
         <v/>
       </c>
       <c r="E113" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B113,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B113,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B113,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B113,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B113,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F113" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B113,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B113,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B113,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B113,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B113,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -46822,11 +46841,11 @@
         <v/>
       </c>
       <c r="E114" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B114,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B114,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B114,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B114,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B114,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F114" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B114,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B114,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B114,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B114,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B114,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -46849,11 +46868,11 @@
         <v/>
       </c>
       <c r="E115" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B115,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B115,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B115,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B115,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B115,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F115" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B115,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B115,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B115,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B115,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B115,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -46876,11 +46895,11 @@
         <v/>
       </c>
       <c r="E116" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B116,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B116,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B116,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B116,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B116,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F116" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B116,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B116,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B116,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B116,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B116,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -46903,11 +46922,11 @@
         <v/>
       </c>
       <c r="E117" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B117,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B117,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B117,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B117,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B117,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F117" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B117,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B117,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B117,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B117,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B117,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -46930,11 +46949,11 @@
         <v/>
       </c>
       <c r="E118" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B118,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B118,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B118,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B118,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B118,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F118" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B118,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B118,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B118,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B118,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B118,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -46957,11 +46976,11 @@
         <v/>
       </c>
       <c r="E119" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B119,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B119,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B119,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B119,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B119,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F119" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B119,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B119,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B119,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B119,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B119,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -46980,11 +46999,11 @@
         <v/>
       </c>
       <c r="E120" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B120,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B120,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B120,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B120,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B120,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F120" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B120,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B120,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B120,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B120,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B120,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -47003,11 +47022,11 @@
         <v/>
       </c>
       <c r="E121" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B121,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B121,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B121,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B121,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B121,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F121" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B121,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B121,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B121,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B121,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B121,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -47030,11 +47049,11 @@
         <v/>
       </c>
       <c r="E122" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B122,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B122,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B122,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B122,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B122,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F122" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B122,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B122,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B122,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B122,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B122,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -47057,11 +47076,11 @@
         <v/>
       </c>
       <c r="E123" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B123,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B123,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B123,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B123,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B123,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F123" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B123,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B123,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B123,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B123,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B123,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -47084,11 +47103,11 @@
         <v/>
       </c>
       <c r="E124" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B124,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B124,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B124,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B124,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B124,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F124" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B124,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B124,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B124,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B124,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B124,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -47111,11 +47130,11 @@
         <v/>
       </c>
       <c r="E125" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B125,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B125,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B125,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B125,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B125,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F125" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B125,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B125,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B125,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B125,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B125,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -47138,11 +47157,11 @@
         <v/>
       </c>
       <c r="E126" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B126,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B126,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B126,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B126,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B126,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F126" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B126,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B126,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B126,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B126,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B126,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -47161,11 +47180,11 @@
         <v/>
       </c>
       <c r="E127" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B127,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B127,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B127,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B127,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B127,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F127" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B127,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B127,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B127,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B127,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B127,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -47184,11 +47203,11 @@
         <v/>
       </c>
       <c r="E128" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B128,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B128,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B128,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B128,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B128,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F128" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B128,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B128,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B128,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B128,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B128,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -47211,11 +47230,11 @@
         <v/>
       </c>
       <c r="E129" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B129,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B129,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B129,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B129,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B129,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F129" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B129,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B129,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B129,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B129,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B129,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -47234,11 +47253,11 @@
         <v/>
       </c>
       <c r="E130" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B130,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B130,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B130,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B130,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B130,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F130" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B130,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B130,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B130,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B130,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B130,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -47261,11 +47280,11 @@
         <v/>
       </c>
       <c r="E131" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B131,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B131,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B131,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B131,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B131,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F131" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B131,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B131,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B131,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B131,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B131,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -47284,11 +47303,11 @@
         <v/>
       </c>
       <c r="E132" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B132,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B132,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B132,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B132,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B132,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F132" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B132,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B132,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B132,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B132,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B132,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -47307,11 +47326,11 @@
         <v/>
       </c>
       <c r="E133" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B133,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B133,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B133,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B133,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B133,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F133" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B133,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B133,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B133,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B133,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B133,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -47334,11 +47353,11 @@
         <v/>
       </c>
       <c r="E134" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B134,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B134,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B134,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B134,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B134,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F134" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B134,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B134,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B134,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B134,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B134,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -47361,11 +47380,11 @@
         <v/>
       </c>
       <c r="E135" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B135,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B135,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B135,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B135,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B135,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F135" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B135,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B135,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B135,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B135,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B135,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -47388,11 +47407,11 @@
         <v/>
       </c>
       <c r="E136" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B136,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B136,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B136,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B136,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B136,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F136" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B136,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B136,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B136,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B136,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B136,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -47415,11 +47434,11 @@
         <v/>
       </c>
       <c r="E137" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B137,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B137,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B137,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B137,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B137,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F137" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B137,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B137,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B137,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B137,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B137,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -47438,11 +47457,11 @@
         <v/>
       </c>
       <c r="E138" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B138,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B138,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B138,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B138,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B138,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F138" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B138,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B138,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B138,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B138,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B138,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -47465,11 +47484,11 @@
         <v/>
       </c>
       <c r="E139" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B139,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B139,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B139,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B139,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B139,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F139" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B139,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B139,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B139,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B139,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B139,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -47492,11 +47511,11 @@
         <v/>
       </c>
       <c r="E140" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B140,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B140,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B140,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B140,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B140,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F140" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B140,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B140,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B140,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B140,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B140,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -47519,11 +47538,11 @@
         <v/>
       </c>
       <c r="E141" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B141,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B141,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B141,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B141,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B141,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F141" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B141,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B141,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B141,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B141,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B141,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -47546,11 +47565,11 @@
         <v/>
       </c>
       <c r="E142" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B142,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B142,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B142,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B142,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B142,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F142" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B142,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B142,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B142,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B142,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B142,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -47573,11 +47592,11 @@
         <v/>
       </c>
       <c r="E143" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B143,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B143,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B143,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B143,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B143,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F143" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B143,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B143,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B143,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B143,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B143,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -47600,11 +47619,11 @@
         <v/>
       </c>
       <c r="E144" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B144,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B144,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B144,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B144,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B144,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F144" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B144,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B144,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B144,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B144,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B144,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -47627,11 +47646,11 @@
         <v/>
       </c>
       <c r="E145" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B145,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B145,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B145,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B145,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B145,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F145" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B145,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B145,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B145,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B145,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B145,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -47654,11 +47673,11 @@
         <v/>
       </c>
       <c r="E146" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B146,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B146,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B146,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B146,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B146,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F146" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B146,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B146,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B146,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B146,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B146,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -47681,11 +47700,11 @@
         <v/>
       </c>
       <c r="E147" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B147,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B147,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B147,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B147,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B147,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F147" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B147,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B147,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B147,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B147,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B147,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -47708,11 +47727,11 @@
         <v/>
       </c>
       <c r="E148" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B148,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B148,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B148,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B148,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B148,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F148" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B148,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B148,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B148,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B148,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B148,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -47735,11 +47754,11 @@
         <v/>
       </c>
       <c r="E149" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B149,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B149,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B149,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B149,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B149,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F149" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B149,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B149,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B149,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B149,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B149,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -47762,11 +47781,11 @@
         <v/>
       </c>
       <c r="E150" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B150,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B150,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B150,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B150,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B150,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F150" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B150,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B150,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B150,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B150,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B150,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -47789,11 +47808,11 @@
         <v/>
       </c>
       <c r="E151" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B151,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B151,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B151,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B151,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B151,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F151" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B151,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B151,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B151,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B151,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B151,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -47812,11 +47831,11 @@
         <v/>
       </c>
       <c r="E152" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B152,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B152,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B152,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B152,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B152,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F152" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B152,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B152,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B152,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B152,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B152,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -47835,11 +47854,11 @@
         <v/>
       </c>
       <c r="E153" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B153,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B153,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B153,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B153,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B153,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F153" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B153,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B153,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B153,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B153,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B153,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -47862,11 +47881,11 @@
         <v/>
       </c>
       <c r="E154" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B154,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B154,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B154,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B154,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B154,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F154" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B154,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B154,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B154,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B154,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B154,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -47889,11 +47908,11 @@
         <v/>
       </c>
       <c r="E155" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B155,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B155,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B155,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B155,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B155,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F155" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B155,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B155,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B155,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B155,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B155,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
@@ -47916,11 +47935,11 @@
         <v/>
       </c>
       <c r="E156" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B156,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B156,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B156,Fact_Expenses[Date],"&gt;="&amp;CurMonthStart,Fact_Expenses[Date],"&lt;="&amp;CurMonthEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B156,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B156,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurMonthStart,BankImportRaw[Date],"&lt;="&amp;CurMonthEnd)</f>
         <v/>
       </c>
       <c r="F156" s="39">
-        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B156,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B156,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
+        <f>SUMIFS(Fact_Expenses[Amount],Fact_Expenses[VendorName],$B156,Fact_Expenses[Date],"&gt;="&amp;CurYearStart,Fact_Expenses[Date],"&lt;="&amp;CurYearEnd)+SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B156,BankImportRaw[TransactionType],"Expense",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)-SUMIFS(BankImportRaw[AbsAmount],BankImportRaw[VendorName],$B156,BankImportRaw[TransactionType],"Return",BankImportRaw[Date],"&gt;="&amp;CurYearStart,BankImportRaw[Date],"&lt;="&amp;CurYearEnd)</f>
         <v/>
       </c>
     </row>
